--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -340,10 +340,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2024-10-01</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
+    <t>2024-10-25</t>
+  </si>
+  <si>
+    <t>2024-11-05</t>
   </si>
   <si>
     <t>第一批白图鉴</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -331,7 +331,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>国庆活动</t>
+    <t>万圣节</t>
   </si>
   <si>
     <t>1005</t>
@@ -340,7 +340,7 @@
     <t>50</t>
   </si>
   <si>
-    <t>2024-10-25</t>
+    <t>2024-10-28</t>
   </si>
   <si>
     <t>2024-11-05</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -340,10 +340,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2024-10-28</t>
-  </si>
-  <si>
-    <t>2024-11-05</t>
+    <t>2024-10-31</t>
+  </si>
+  <si>
+    <t>2024-11-04</t>
   </si>
   <si>
     <t>第一批白图鉴</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="324">
   <si>
     <t>_id</t>
   </si>
@@ -493,31 +493,70 @@
     <t>1004</t>
   </si>
   <si>
+    <t>冠名图鉴</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>30000</t>
+  </si>
+  <si>
+    <t>冠名图鉴2</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>龙之图鉴</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>龙之图鉴2</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>40000</t>
+  </si>
+  <si>
+    <t>160000</t>
+  </si>
+  <si>
+    <t>金图鉴1</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
     <t>50000</t>
   </si>
   <si>
-    <t>冠名图鉴</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>30000</t>
-  </si>
-  <si>
-    <t>70000</t>
-  </si>
-  <si>
-    <t>龙之图鉴</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>200000</t>
+    <t>2000000</t>
+  </si>
+  <si>
+    <t>金图鉴2</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>500000</t>
+  </si>
+  <si>
+    <t>1000000</t>
+  </si>
+  <si>
+    <t>金图鉴3</t>
+  </si>
+  <si>
+    <t>2009</t>
   </si>
   <si>
     <t>镜像挑战</t>
@@ -1394,12 +1433,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2229,7 +2268,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O39"/>
+  <dimension ref="C1:O44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -3163,8 +3202,8 @@
       <c r="J28" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="K28" s="19" t="s">
-        <v>78</v>
+      <c r="K28" s="11">
+        <v>0</v>
       </c>
       <c r="L28" s="2">
         <v>0</v>
@@ -3184,7 +3223,7 @@
         <v>802</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -3196,16 +3235,16 @@
         <v>2000</v>
       </c>
       <c r="H29" s="19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I29" s="18" t="s">
         <v>45</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="K29" s="18" t="s">
-        <v>82</v>
+        <v>80</v>
+      </c>
+      <c r="K29" s="11">
+        <v>0</v>
       </c>
       <c r="L29" s="11">
         <v>1</v>
@@ -3225,28 +3264,28 @@
         <v>803</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E30" s="2">
         <v>98</v>
       </c>
       <c r="F30" s="2">
-        <v>1000</v>
+        <v>1105</v>
       </c>
       <c r="G30" s="2">
         <v>2000</v>
       </c>
       <c r="H30" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="I30" s="19" t="s">
-        <v>54</v>
+        <v>82</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>45</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="K30" s="18" t="s">
-        <v>86</v>
+        <v>80</v>
+      </c>
+      <c r="K30" s="11">
+        <v>0</v>
       </c>
       <c r="L30" s="2">
         <v>0</v>
@@ -3261,37 +3300,79 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="10:15">
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="9:15">
+      <c r="I31" s="11"/>
       <c r="J31" s="11"/>
       <c r="K31" s="11"/>
       <c r="M31" s="11"/>
       <c r="N31" s="11"/>
       <c r="O31" s="11"/>
     </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C32" s="2">
+        <v>804</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" s="2">
+        <v>98</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G32" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="I32" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="J32" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="K32" s="11">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2">
+        <v>0</v>
+      </c>
+      <c r="M32" s="11">
+        <v>0</v>
+      </c>
+      <c r="N32" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O32" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C33" s="2">
-        <v>991</v>
+        <v>805</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E33" s="2">
+        <v>98</v>
+      </c>
+      <c r="F33" s="2">
+        <v>1105</v>
+      </c>
+      <c r="G33" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H33" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E33" s="2">
-        <v>99</v>
-      </c>
-      <c r="F33" s="2">
-        <v>0</v>
-      </c>
-      <c r="G33" s="2">
-        <v>0</v>
-      </c>
-      <c r="H33" s="18" t="s">
+      <c r="I33" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="I33" s="11">
-        <v>0</v>
-      </c>
-      <c r="J33" s="2">
-        <v>1</v>
+      <c r="J33" s="18" t="s">
+        <v>89</v>
       </c>
       <c r="K33" s="11">
         <v>0</v>
@@ -3299,8 +3380,8 @@
       <c r="L33" s="2">
         <v>0</v>
       </c>
-      <c r="M33" s="2">
-        <v>1</v>
+      <c r="M33" s="11">
+        <v>0</v>
       </c>
       <c r="N33" s="18" t="s">
         <v>32</v>
@@ -3311,28 +3392,28 @@
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C34" s="2">
-        <v>992</v>
+        <v>806</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E34" s="2">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F34" s="2">
-        <v>0</v>
+        <v>1105</v>
       </c>
       <c r="G34" s="2">
-        <v>0</v>
-      </c>
-      <c r="H34" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="I34" s="11">
-        <v>0</v>
-      </c>
-      <c r="J34" s="2">
-        <v>1</v>
+        <v>2000</v>
+      </c>
+      <c r="H34" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="I34" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="J34" s="18" t="s">
+        <v>93</v>
       </c>
       <c r="K34" s="11">
         <v>0</v>
@@ -3340,8 +3421,8 @@
       <c r="L34" s="2">
         <v>0</v>
       </c>
-      <c r="M34" s="2">
-        <v>1</v>
+      <c r="M34" s="11">
+        <v>0</v>
       </c>
       <c r="N34" s="18" t="s">
         <v>32</v>
@@ -3350,18 +3431,94 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" s="2" customFormat="1" customHeight="1"/>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="8:15">
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="16"/>
-      <c r="O36" s="16"/>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="8:15">
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C35" s="2">
+        <v>807</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E35" s="2">
+        <v>98</v>
+      </c>
+      <c r="F35" s="2">
+        <v>1105</v>
+      </c>
+      <c r="G35" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H35" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="I35" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="J35" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="K35" s="11">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2">
+        <v>0</v>
+      </c>
+      <c r="M35" s="11">
+        <v>0</v>
+      </c>
+      <c r="N35" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O35" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C36" s="2">
+        <v>808</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E36" s="2">
+        <v>98</v>
+      </c>
+      <c r="F36" s="2">
+        <v>1105</v>
+      </c>
+      <c r="G36" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H36" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I36" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="J36" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="K36" s="11">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2">
+        <v>0</v>
+      </c>
+      <c r="M36" s="11">
+        <v>0</v>
+      </c>
+      <c r="N36" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O36" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
       <c r="H37" s="16"/>
       <c r="I37" s="16"/>
       <c r="J37" s="16"/>
@@ -3371,32 +3528,153 @@
       <c r="N37" s="16"/>
       <c r="O37" s="16"/>
     </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="8:15">
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-    </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="8:15">
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C38" s="2">
+        <v>991</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E38" s="2">
+        <v>99</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2">
+        <v>0</v>
+      </c>
+      <c r="H38" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="I38" s="11">
+        <v>0</v>
+      </c>
+      <c r="J38" s="2">
+        <v>1</v>
+      </c>
+      <c r="K38" s="11">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2">
+        <v>0</v>
+      </c>
+      <c r="M38" s="2">
+        <v>1</v>
+      </c>
+      <c r="N38" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O38" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C39" s="2">
+        <v>992</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E39" s="2">
+        <v>101</v>
+      </c>
+      <c r="F39" s="2">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2">
+        <v>0</v>
+      </c>
+      <c r="H39" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="I39" s="11">
+        <v>0</v>
+      </c>
+      <c r="J39" s="2">
+        <v>1</v>
+      </c>
+      <c r="K39" s="11">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2">
+        <v>1</v>
+      </c>
+      <c r="N39" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O39" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1"/>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="8:15">
+      <c r="H41" s="16"/>
+      <c r="I41" s="16"/>
+      <c r="J41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+      <c r="M41" s="16"/>
+      <c r="N41" s="16"/>
+      <c r="O41" s="16"/>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="8:15">
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="16"/>
+      <c r="N42" s="16"/>
+      <c r="O42" s="16"/>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="8:15">
+      <c r="H43" s="16"/>
+      <c r="I43" s="16"/>
+      <c r="J43" s="16"/>
+      <c r="K43" s="16"/>
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
+      <c r="N43" s="16"/>
+      <c r="O43" s="16"/>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="8:15">
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="16"/>
+      <c r="K44" s="16"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="16"/>
+      <c r="N44" s="16"/>
+      <c r="O44" s="16"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F29">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F34">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F35">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F36">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F29 C2:C5 F3:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F29 F30 F31 F33 F34 F35 F36 C2:C5 F3:G5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -3445,7 +3723,7 @@
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="1" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -3576,7 +3854,7 @@
         <v>1000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -3588,7 +3866,7 @@
         <v>1051</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I6" s="2">
         <v>40000</v>
@@ -3612,7 +3890,7 @@
         <v>33</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3620,7 +3898,7 @@
         <v>1001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -3632,7 +3910,7 @@
         <v>1052</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="I7" s="2">
         <v>40000</v>
@@ -3656,7 +3934,7 @@
         <v>33</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3664,7 +3942,7 @@
         <v>1002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -3676,7 +3954,7 @@
         <v>1053</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="I8" s="2">
         <v>40000</v>
@@ -3700,7 +3978,7 @@
         <v>33</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3708,7 +3986,7 @@
         <v>1003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -3720,7 +3998,7 @@
         <v>1054</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="I9" s="2">
         <v>40000</v>
@@ -3744,7 +4022,7 @@
         <v>33</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3752,7 +4030,7 @@
         <v>1004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -3764,7 +4042,7 @@
         <v>1055</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="I10" s="2">
         <v>40000</v>
@@ -3788,7 +4066,7 @@
         <v>33</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3796,7 +4074,7 @@
         <v>1005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -3808,7 +4086,7 @@
         <v>1056</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="I11" s="2">
         <v>40000</v>
@@ -3832,7 +4110,7 @@
         <v>33</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3840,7 +4118,7 @@
         <v>1006</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
@@ -3852,7 +4130,7 @@
         <v>1057</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I12" s="2">
         <v>40000</v>
@@ -3876,7 +4154,7 @@
         <v>33</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3884,7 +4162,7 @@
         <v>1007</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
@@ -3896,7 +4174,7 @@
         <v>1058</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="I13" s="2">
         <v>40000</v>
@@ -3920,7 +4198,7 @@
         <v>33</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3928,7 +4206,7 @@
         <v>1008</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -3940,7 +4218,7 @@
         <v>1059</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="I14" s="2">
         <v>40000</v>
@@ -3964,7 +4242,7 @@
         <v>33</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3972,7 +4250,7 @@
         <v>1009</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -3984,7 +4262,7 @@
         <v>1060</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="I15" s="2">
         <v>40000</v>
@@ -4008,7 +4286,7 @@
         <v>33</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4016,7 +4294,7 @@
         <v>1010</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -4028,7 +4306,7 @@
         <v>1061</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="I16" s="2">
         <v>40000</v>
@@ -4052,7 +4330,7 @@
         <v>33</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4060,7 +4338,7 @@
         <v>1011</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -4072,7 +4350,7 @@
         <v>1062</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="I17" s="2">
         <v>40000</v>
@@ -4096,7 +4374,7 @@
         <v>33</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4104,7 +4382,7 @@
         <v>1012</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -4116,7 +4394,7 @@
         <v>1063</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="I18" s="2">
         <v>40000</v>
@@ -4140,7 +4418,7 @@
         <v>33</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4148,7 +4426,7 @@
         <v>1013</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -4160,7 +4438,7 @@
         <v>1064</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -4184,7 +4462,7 @@
         <v>33</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4192,7 +4470,7 @@
         <v>1014</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="E20" s="2">
         <v>98</v>
@@ -4204,7 +4482,7 @@
         <v>1065</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="I20" s="2">
         <v>40000</v>
@@ -4228,7 +4506,7 @@
         <v>33</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4236,7 +4514,7 @@
         <v>1015</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -4248,7 +4526,7 @@
         <v>1066</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="I21" s="2">
         <v>40000</v>
@@ -4272,7 +4550,7 @@
         <v>33</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4280,7 +4558,7 @@
         <v>1016</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -4292,7 +4570,7 @@
         <v>1067</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="I22" s="2">
         <v>40000</v>
@@ -4316,7 +4594,7 @@
         <v>33</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4324,7 +4602,7 @@
         <v>1017</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -4336,7 +4614,7 @@
         <v>1068</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="I23" s="2">
         <v>40000</v>
@@ -4360,7 +4638,7 @@
         <v>33</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4368,7 +4646,7 @@
         <v>1018</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -4380,7 +4658,7 @@
         <v>1069</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="I24" s="2">
         <v>40000</v>
@@ -4404,7 +4682,7 @@
         <v>33</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4412,7 +4690,7 @@
         <v>1019</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -4424,7 +4702,7 @@
         <v>1070</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="I25" s="2">
         <v>40000</v>
@@ -4448,7 +4726,7 @@
         <v>33</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4456,7 +4734,7 @@
         <v>1020</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -4468,7 +4746,7 @@
         <v>1071</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="I26" s="2">
         <v>40000</v>
@@ -4492,7 +4770,7 @@
         <v>33</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4500,7 +4778,7 @@
         <v>1021</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -4512,7 +4790,7 @@
         <v>1072</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>
@@ -4536,7 +4814,7 @@
         <v>33</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4544,7 +4822,7 @@
         <v>1022</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="E28" s="2">
         <v>98</v>
@@ -4556,7 +4834,7 @@
         <v>1073</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="I28" s="2">
         <v>40000</v>
@@ -4580,7 +4858,7 @@
         <v>33</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:16">
@@ -4588,7 +4866,7 @@
         <v>1023</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -4600,7 +4878,7 @@
         <v>1074</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="I29" s="2">
         <v>40000</v>
@@ -4624,7 +4902,7 @@
         <v>33</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4632,7 +4910,7 @@
         <v>1024</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="E30" s="2">
         <v>98</v>
@@ -4644,7 +4922,7 @@
         <v>1075</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="I30" s="2">
         <v>4000</v>
@@ -4668,7 +4946,7 @@
         <v>33</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4676,7 +4954,7 @@
         <v>1025</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="E31" s="2">
         <v>98</v>
@@ -4688,7 +4966,7 @@
         <v>1076</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="I31" s="2">
         <v>4000</v>
@@ -4712,7 +4990,7 @@
         <v>33</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4720,7 +4998,7 @@
         <v>1026</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="E32" s="2">
         <v>98</v>
@@ -4732,7 +5010,7 @@
         <v>1077</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="I32" s="2">
         <v>4000</v>
@@ -4756,7 +5034,7 @@
         <v>33</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4764,7 +5042,7 @@
         <v>1027</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
@@ -4776,7 +5054,7 @@
         <v>1078</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="I33" s="2">
         <v>4000</v>
@@ -4800,7 +5078,7 @@
         <v>33</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:16">
@@ -4808,7 +5086,7 @@
         <v>1028</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="E34" s="2">
         <v>98</v>
@@ -4820,7 +5098,7 @@
         <v>1079</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="I34" s="2">
         <v>4000</v>
@@ -4844,7 +5122,7 @@
         <v>33</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:16">
@@ -4852,7 +5130,7 @@
         <v>1029</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
@@ -4864,7 +5142,7 @@
         <v>1080</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="I35" s="2">
         <v>4000</v>
@@ -4888,7 +5166,7 @@
         <v>33</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:16">
@@ -4896,7 +5174,7 @@
         <v>1030</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -4908,7 +5186,7 @@
         <v>1081</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="I36" s="2">
         <v>4000</v>
@@ -4932,7 +5210,7 @@
         <v>33</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:16">
@@ -4940,7 +5218,7 @@
         <v>1031</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -4952,7 +5230,7 @@
         <v>1082</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="I37" s="2">
         <v>4000</v>
@@ -4976,7 +5254,7 @@
         <v>33</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:16">
@@ -4984,7 +5262,7 @@
         <v>1032</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="E38" s="2">
         <v>98</v>
@@ -4996,7 +5274,7 @@
         <v>1083</v>
       </c>
       <c r="H38" s="20" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="I38" s="2">
         <v>4000</v>
@@ -5020,7 +5298,7 @@
         <v>33</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:16">
@@ -5028,7 +5306,7 @@
         <v>1033</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="E39" s="2">
         <v>98</v>
@@ -5040,7 +5318,7 @@
         <v>1084</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="I39" s="2">
         <v>4000</v>
@@ -5064,7 +5342,7 @@
         <v>33</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:16">
@@ -5072,7 +5350,7 @@
         <v>1034</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="E40" s="2">
         <v>98</v>
@@ -5084,7 +5362,7 @@
         <v>1085</v>
       </c>
       <c r="H40" s="20" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="I40" s="2">
         <v>4000</v>
@@ -5108,7 +5386,7 @@
         <v>33</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:16">
@@ -5116,7 +5394,7 @@
         <v>1035</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="E41" s="2">
         <v>98</v>
@@ -5128,7 +5406,7 @@
         <v>1086</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="I41" s="2">
         <v>4000</v>
@@ -5152,7 +5430,7 @@
         <v>33</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:16">
@@ -5160,7 +5438,7 @@
         <v>1036</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E42" s="2">
         <v>98</v>
@@ -5172,7 +5450,7 @@
         <v>1087</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="I42" s="2">
         <v>4000</v>
@@ -5196,7 +5474,7 @@
         <v>33</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:16">
@@ -5204,7 +5482,7 @@
         <v>1037</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="E43" s="2">
         <v>98</v>
@@ -5216,7 +5494,7 @@
         <v>1088</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="I43" s="2">
         <v>4000</v>
@@ -5240,7 +5518,7 @@
         <v>33</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:16">
@@ -5248,7 +5526,7 @@
         <v>1038</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E44" s="2">
         <v>98</v>
@@ -5260,7 +5538,7 @@
         <v>1089</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="I44" s="2">
         <v>4000</v>
@@ -5284,7 +5562,7 @@
         <v>33</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:16">
@@ -5292,7 +5570,7 @@
         <v>1039</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="E45" s="2">
         <v>98</v>
@@ -5304,7 +5582,7 @@
         <v>1090</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="I45" s="2">
         <v>4000</v>
@@ -5328,7 +5606,7 @@
         <v>33</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:16">
@@ -5336,7 +5614,7 @@
         <v>1040</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="E46" s="2">
         <v>98</v>
@@ -5348,7 +5626,7 @@
         <v>1091</v>
       </c>
       <c r="H46" s="20" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="I46" s="2">
         <v>4000</v>
@@ -5372,7 +5650,7 @@
         <v>33</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:16">
@@ -5380,7 +5658,7 @@
         <v>1041</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="E47" s="2">
         <v>98</v>
@@ -5392,7 +5670,7 @@
         <v>1092</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="I47" s="2">
         <v>4000</v>
@@ -5416,7 +5694,7 @@
         <v>33</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:16">
@@ -5424,7 +5702,7 @@
         <v>1042</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="E48" s="2">
         <v>98</v>
@@ -5436,7 +5714,7 @@
         <v>1093</v>
       </c>
       <c r="H48" s="20" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="I48" s="2">
         <v>4000</v>
@@ -5460,7 +5738,7 @@
         <v>33</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:16">
@@ -5468,7 +5746,7 @@
         <v>1043</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="E49" s="2">
         <v>98</v>
@@ -5480,7 +5758,7 @@
         <v>1094</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="I49" s="2">
         <v>4000</v>
@@ -5504,7 +5782,7 @@
         <v>33</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:16">
@@ -5512,7 +5790,7 @@
         <v>1044</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="E50" s="2">
         <v>98</v>
@@ -5524,7 +5802,7 @@
         <v>1095</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="I50" s="2">
         <v>4000</v>
@@ -5548,7 +5826,7 @@
         <v>33</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:16">
@@ -5556,7 +5834,7 @@
         <v>1045</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="E51" s="2">
         <v>98</v>
@@ -5568,7 +5846,7 @@
         <v>1096</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="I51" s="2">
         <v>4000</v>
@@ -5592,7 +5870,7 @@
         <v>33</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:16">
@@ -5600,7 +5878,7 @@
         <v>1046</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="E52" s="2">
         <v>98</v>
@@ -5612,7 +5890,7 @@
         <v>1097</v>
       </c>
       <c r="H52" s="20" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="I52" s="2">
         <v>4000</v>
@@ -5636,7 +5914,7 @@
         <v>33</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:16">
@@ -5644,7 +5922,7 @@
         <v>1047</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="E53" s="2">
         <v>98</v>
@@ -5656,7 +5934,7 @@
         <v>1098</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="I53" s="2">
         <v>4000</v>
@@ -5680,7 +5958,7 @@
         <v>33</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:16">
@@ -5688,7 +5966,7 @@
         <v>1048</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="E54" s="2">
         <v>98</v>
@@ -5700,7 +5978,7 @@
         <v>1099</v>
       </c>
       <c r="H54" s="20" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="I54" s="2">
         <v>4000</v>
@@ -5724,7 +6002,7 @@
         <v>33</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:16">
@@ -5732,7 +6010,7 @@
         <v>1049</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="E55" s="2">
         <v>98</v>
@@ -5744,7 +6022,7 @@
         <v>1100</v>
       </c>
       <c r="H55" s="20" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="I55" s="2">
         <v>4000</v>
@@ -5768,7 +6046,7 @@
         <v>33</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:16">
@@ -5776,7 +6054,7 @@
         <v>1050</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="E56" s="2">
         <v>98</v>
@@ -5788,7 +6066,7 @@
         <v>1101</v>
       </c>
       <c r="H56" s="20" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="I56" s="2">
         <v>4000</v>
@@ -5812,7 +6090,7 @@
         <v>33</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:16">
@@ -5820,7 +6098,7 @@
         <v>1051</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="E57" s="2">
         <v>98</v>
@@ -5832,7 +6110,7 @@
         <v>1102</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="I57" s="2">
         <v>4000</v>
@@ -5856,7 +6134,7 @@
         <v>33</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:16">
@@ -5864,7 +6142,7 @@
         <v>1052</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="E58" s="2">
         <v>98</v>
@@ -5876,7 +6154,7 @@
         <v>1103</v>
       </c>
       <c r="H58" s="20" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="I58" s="2">
         <v>4000</v>
@@ -5900,7 +6178,7 @@
         <v>33</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:16">
@@ -5908,7 +6186,7 @@
         <v>1053</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="E59" s="2">
         <v>98</v>
@@ -5920,7 +6198,7 @@
         <v>1104</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="I59" s="2">
         <v>4000</v>
@@ -5944,7 +6222,7 @@
         <v>33</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" s="12" customFormat="1" customHeight="1" spans="3:16">
@@ -5952,7 +6230,7 @@
         <v>1054</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E60" s="12">
         <v>98</v>
@@ -5964,7 +6242,7 @@
         <v>1105</v>
       </c>
       <c r="H60" s="21" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="I60" s="12">
         <v>20000</v>
@@ -5988,7 +6266,7 @@
         <v>33</v>
       </c>
       <c r="P60" s="12" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -5996,7 +6274,7 @@
         <v>1055</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="E61" s="2">
         <v>98</v>
@@ -6008,7 +6286,7 @@
         <v>1106</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="I61" s="2">
         <v>20000</v>
@@ -6032,7 +6310,7 @@
         <v>33</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6040,7 +6318,7 @@
         <v>1056</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="E62" s="2">
         <v>98</v>
@@ -6052,7 +6330,7 @@
         <v>1107</v>
       </c>
       <c r="H62" s="20" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="I62" s="2">
         <v>20000</v>
@@ -6076,7 +6354,7 @@
         <v>33</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6084,7 +6362,7 @@
         <v>1057</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="E63" s="2">
         <v>98</v>
@@ -6096,7 +6374,7 @@
         <v>1108</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="I63" s="2">
         <v>20000</v>
@@ -6120,7 +6398,7 @@
         <v>33</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:16">
@@ -6128,7 +6406,7 @@
         <v>1058</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="E64" s="2">
         <v>98</v>
@@ -6140,7 +6418,7 @@
         <v>1109</v>
       </c>
       <c r="H64" s="20" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="I64" s="2">
         <v>20000</v>
@@ -6164,7 +6442,7 @@
         <v>33</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6172,7 +6450,7 @@
         <v>1059</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="E65" s="2">
         <v>98</v>
@@ -6184,7 +6462,7 @@
         <v>1110</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="I65" s="2">
         <v>20000</v>
@@ -6208,7 +6486,7 @@
         <v>33</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6216,7 +6494,7 @@
         <v>1060</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="E66" s="2">
         <v>98</v>
@@ -6228,7 +6506,7 @@
         <v>1111</v>
       </c>
       <c r="H66" s="20" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="I66" s="2">
         <v>20000</v>
@@ -6252,7 +6530,7 @@
         <v>33</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6260,7 +6538,7 @@
         <v>1061</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="E67" s="2">
         <v>98</v>
@@ -6272,7 +6550,7 @@
         <v>1112</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="I67" s="2">
         <v>20000</v>
@@ -6296,7 +6574,7 @@
         <v>33</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6304,7 +6582,7 @@
         <v>1062</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="E68" s="2">
         <v>98</v>
@@ -6316,7 +6594,7 @@
         <v>1113</v>
       </c>
       <c r="H68" s="20" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="I68" s="2">
         <v>20000</v>
@@ -6340,7 +6618,7 @@
         <v>33</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:16">
@@ -6348,7 +6626,7 @@
         <v>1063</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="E69" s="2">
         <v>98</v>
@@ -6360,7 +6638,7 @@
         <v>1114</v>
       </c>
       <c r="H69" s="20" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="I69" s="2">
         <v>20000</v>
@@ -6384,7 +6662,7 @@
         <v>33</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:16">
@@ -6392,7 +6670,7 @@
         <v>1064</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="E70" s="2">
         <v>98</v>
@@ -6404,7 +6682,7 @@
         <v>1115</v>
       </c>
       <c r="H70" s="20" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="I70" s="2">
         <v>20000</v>
@@ -6428,7 +6706,7 @@
         <v>33</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:16">
@@ -6436,7 +6714,7 @@
         <v>1065</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="E71" s="2">
         <v>98</v>
@@ -6448,7 +6726,7 @@
         <v>1116</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="I71" s="2">
         <v>20000</v>
@@ -6472,7 +6750,7 @@
         <v>33</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:16">
@@ -6480,7 +6758,7 @@
         <v>1066</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="E72" s="2">
         <v>98</v>
@@ -6492,7 +6770,7 @@
         <v>1117</v>
       </c>
       <c r="H72" s="20" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="I72" s="2">
         <v>20000</v>
@@ -6516,7 +6794,7 @@
         <v>33</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:16">
@@ -6524,7 +6802,7 @@
         <v>1067</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="E73" s="2">
         <v>98</v>
@@ -6536,7 +6814,7 @@
         <v>1118</v>
       </c>
       <c r="H73" s="20" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="I73" s="2">
         <v>20000</v>
@@ -6560,7 +6838,7 @@
         <v>33</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:16">
@@ -6568,7 +6846,7 @@
         <v>1068</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="E74" s="2">
         <v>98</v>
@@ -6580,7 +6858,7 @@
         <v>1119</v>
       </c>
       <c r="H74" s="20" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="I74" s="2">
         <v>20000</v>
@@ -6604,7 +6882,7 @@
         <v>33</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:16">
@@ -6612,7 +6890,7 @@
         <v>1069</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="E75" s="2">
         <v>98</v>
@@ -6624,7 +6902,7 @@
         <v>1120</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="I75" s="2">
         <v>20000</v>
@@ -6648,7 +6926,7 @@
         <v>33</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:16">
@@ -6656,7 +6934,7 @@
         <v>1070</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="E76" s="2">
         <v>98</v>
@@ -6668,7 +6946,7 @@
         <v>1121</v>
       </c>
       <c r="H76" s="20" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="I76" s="2">
         <v>20000</v>
@@ -6692,7 +6970,7 @@
         <v>33</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:16">
@@ -6700,7 +6978,7 @@
         <v>1071</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="E77" s="2">
         <v>98</v>
@@ -6712,7 +6990,7 @@
         <v>1122</v>
       </c>
       <c r="H77" s="20" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="I77" s="2">
         <v>20000</v>
@@ -6736,7 +7014,7 @@
         <v>33</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:16">
@@ -6744,7 +7022,7 @@
         <v>1072</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="E78" s="2">
         <v>98</v>
@@ -6756,7 +7034,7 @@
         <v>1123</v>
       </c>
       <c r="H78" s="20" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="I78" s="2">
         <v>20000</v>
@@ -6780,7 +7058,7 @@
         <v>33</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:16">
@@ -6788,7 +7066,7 @@
         <v>1073</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="E79" s="2">
         <v>98</v>
@@ -6800,7 +7078,7 @@
         <v>1124</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="I79" s="2">
         <v>20000</v>
@@ -6824,7 +7102,7 @@
         <v>33</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:16">
@@ -6832,7 +7110,7 @@
         <v>1074</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="E80" s="2">
         <v>98</v>
@@ -6844,7 +7122,7 @@
         <v>1125</v>
       </c>
       <c r="H80" s="20" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="I80" s="2">
         <v>20000</v>
@@ -6868,7 +7146,7 @@
         <v>33</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:16">
@@ -6876,7 +7154,7 @@
         <v>1075</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="E81" s="2">
         <v>98</v>
@@ -6888,7 +7166,7 @@
         <v>1126</v>
       </c>
       <c r="H81" s="20" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="I81" s="2">
         <v>20000</v>
@@ -6912,7 +7190,7 @@
         <v>33</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:16">
@@ -6920,7 +7198,7 @@
         <v>1076</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="E82" s="2">
         <v>98</v>
@@ -6932,7 +7210,7 @@
         <v>1127</v>
       </c>
       <c r="H82" s="20" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="I82" s="2">
         <v>20000</v>
@@ -6956,7 +7234,7 @@
         <v>33</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:16">
@@ -6964,7 +7242,7 @@
         <v>1077</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="E83" s="2">
         <v>98</v>
@@ -6976,7 +7254,7 @@
         <v>1128</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="I83" s="2">
         <v>20000</v>
@@ -7000,7 +7278,7 @@
         <v>33</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:16">
@@ -7008,7 +7286,7 @@
         <v>1078</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="E84" s="2">
         <v>98</v>
@@ -7020,7 +7298,7 @@
         <v>1129</v>
       </c>
       <c r="H84" s="20" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="I84" s="2">
         <v>20000</v>
@@ -7044,7 +7322,7 @@
         <v>33</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:16">
@@ -7052,7 +7330,7 @@
         <v>1079</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="E85" s="2">
         <v>98</v>
@@ -7064,7 +7342,7 @@
         <v>1130</v>
       </c>
       <c r="H85" s="20" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="I85" s="2">
         <v>20000</v>
@@ -7088,7 +7366,7 @@
         <v>33</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:16">
@@ -7096,7 +7374,7 @@
         <v>1080</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="E86" s="2">
         <v>98</v>
@@ -7108,7 +7386,7 @@
         <v>1131</v>
       </c>
       <c r="H86" s="20" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="I86" s="2">
         <v>20000</v>
@@ -7132,7 +7410,7 @@
         <v>33</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:16">
@@ -7140,7 +7418,7 @@
         <v>1081</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="E87" s="2">
         <v>98</v>
@@ -7152,7 +7430,7 @@
         <v>1132</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="I87" s="2">
         <v>20000</v>
@@ -7176,7 +7454,7 @@
         <v>33</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:16">
@@ -7184,7 +7462,7 @@
         <v>1082</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E88" s="2">
         <v>98</v>
@@ -7196,7 +7474,7 @@
         <v>1133</v>
       </c>
       <c r="H88" s="20" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="I88" s="2">
         <v>20000</v>
@@ -7220,7 +7498,7 @@
         <v>33</v>
       </c>
       <c r="P88" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:16">
@@ -7228,7 +7506,7 @@
         <v>1083</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="E89" s="2">
         <v>98</v>
@@ -7240,7 +7518,7 @@
         <v>1134</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="I89" s="2">
         <v>20000</v>
@@ -7264,7 +7542,7 @@
         <v>33</v>
       </c>
       <c r="P89" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:16">
@@ -7272,7 +7550,7 @@
         <v>1084</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="E90" s="2">
         <v>98</v>
@@ -7284,7 +7562,7 @@
         <v>1135</v>
       </c>
       <c r="H90" s="20" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="I90" s="2">
         <v>20000</v>
@@ -7308,7 +7586,7 @@
         <v>33</v>
       </c>
       <c r="P90" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:16">
@@ -7316,7 +7594,7 @@
         <v>1085</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="E91" s="2">
         <v>98</v>
@@ -7328,7 +7606,7 @@
         <v>1136</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="I91" s="2">
         <v>20000</v>
@@ -7352,7 +7630,7 @@
         <v>33</v>
       </c>
       <c r="P91" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:16">
@@ -7360,7 +7638,7 @@
         <v>1086</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="E92" s="2">
         <v>98</v>
@@ -7372,7 +7650,7 @@
         <v>1137</v>
       </c>
       <c r="H92" s="20" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="I92" s="2">
         <v>20000</v>
@@ -7396,7 +7674,7 @@
         <v>33</v>
       </c>
       <c r="P92" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:16">
@@ -7404,7 +7682,7 @@
         <v>1087</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="E93" s="2">
         <v>98</v>
@@ -7416,7 +7694,7 @@
         <v>1138</v>
       </c>
       <c r="H93" s="20" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="I93" s="2">
         <v>20000</v>
@@ -7440,7 +7718,7 @@
         <v>33</v>
       </c>
       <c r="P93" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:16">
@@ -7448,7 +7726,7 @@
         <v>1088</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="E94" s="2">
         <v>98</v>
@@ -7460,7 +7738,7 @@
         <v>1139</v>
       </c>
       <c r="H94" s="20" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="I94" s="2">
         <v>20000</v>
@@ -7484,7 +7762,7 @@
         <v>33</v>
       </c>
       <c r="P94" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -7569,7 +7847,7 @@
         <v>8</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>9</v>
@@ -7613,7 +7891,7 @@
         <v>18</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="M4" s="7" t="s">
         <v>19</v>
@@ -7677,7 +7955,7 @@
         <v>2000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -7689,7 +7967,7 @@
         <v>1070</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="I6" s="2">
         <v>120000</v>
@@ -7721,7 +7999,7 @@
         <v>2001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -7733,7 +8011,7 @@
         <v>1071</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="I7" s="2">
         <v>120000</v>
@@ -7765,7 +8043,7 @@
         <v>2002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -7777,7 +8055,7 @@
         <v>1072</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="I8" s="2">
         <v>120000</v>
@@ -7809,7 +8087,7 @@
         <v>2003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -7821,7 +8099,7 @@
         <v>1073</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="I9" s="2">
         <v>120000</v>
@@ -7853,7 +8131,7 @@
         <v>2004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -7865,7 +8143,7 @@
         <v>1074</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="I10" s="2">
         <v>120000</v>
@@ -7897,7 +8175,7 @@
         <v>2005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -7909,7 +8187,7 @@
         <v>1104</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="I11" s="2">
         <v>20000</v>
@@ -7955,7 +8233,7 @@
         <v>2006</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -7967,7 +8245,7 @@
         <v>1105</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="I14" s="2">
         <v>360000</v>
@@ -7999,7 +8277,7 @@
         <v>2007</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -8011,7 +8289,7 @@
         <v>1106</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="I15" s="2">
         <v>360000</v>
@@ -8043,7 +8321,7 @@
         <v>2008</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -8055,7 +8333,7 @@
         <v>1107</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="I16" s="2">
         <v>360000</v>
@@ -8087,7 +8365,7 @@
         <v>2009</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -8099,7 +8377,7 @@
         <v>1108</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="I17" s="2">
         <v>360000</v>
@@ -8131,7 +8409,7 @@
         <v>2010</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -8143,7 +8421,7 @@
         <v>1139</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="I18" s="2">
         <v>360000</v>
@@ -8175,7 +8453,7 @@
         <v>2011</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -8187,7 +8465,7 @@
         <v>1139</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -523,10 +523,10 @@
     <t>2006</t>
   </si>
   <si>
-    <t>40000</t>
-  </si>
-  <si>
-    <t>160000</t>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>240000</t>
   </si>
   <si>
     <t>金图鉴1</t>
@@ -1433,12 +1433,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3674,7 +3674,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F29 F30 F31 F33 F34 F35 F36 C2:C5 F3:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:C5 F29:F31 F33:F36 F3:G5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N3" authorId="0">
+    <comment ref="O3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -78,7 +78,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="0">
+    <comment ref="P3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="326">
   <si>
     <t>_id</t>
   </si>
@@ -286,6 +286,9 @@
     <t>保底掉落</t>
   </si>
   <si>
+    <t>保底爆率</t>
+  </si>
+  <si>
     <t>享受爆率加成</t>
   </si>
   <si>
@@ -316,6 +319,9 @@
     <t>EndRate</t>
   </si>
   <si>
+    <t>MinRate</t>
+  </si>
+  <si>
     <t>ShareRise</t>
   </si>
   <si>
@@ -538,7 +544,7 @@
     <t>50000</t>
   </si>
   <si>
-    <t>2000000</t>
+    <t>250000</t>
   </si>
   <si>
     <t>金图鉴2</t>
@@ -547,7 +553,7 @@
     <t>2008</t>
   </si>
   <si>
-    <t>500000</t>
+    <t>400000</t>
   </si>
   <si>
     <t>1000000</t>
@@ -559,6 +565,12 @@
     <t>2009</t>
   </si>
   <si>
+    <t>600000</t>
+  </si>
+  <si>
+    <t>1500000</t>
+  </si>
+  <si>
     <t>镜像挑战</t>
   </si>
   <si>
@@ -1163,12 +1175,6 @@
   </si>
   <si>
     <t>1400088</t>
-  </si>
-  <si>
-    <t>保底爆率</t>
-  </si>
-  <si>
-    <t>MinRate</t>
   </si>
   <si>
     <t>武器衣服红装</t>
@@ -2268,7 +2274,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O44"/>
+  <dimension ref="C1:P44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -2277,13 +2283,13 @@
     <col min="5" max="7" width="13.625" style="2" customWidth="1"/>
     <col min="8" max="8" width="17.5" style="16" customWidth="1"/>
     <col min="9" max="9" width="17.875" style="16" customWidth="1"/>
-    <col min="10" max="11" width="13.75" style="16" customWidth="1"/>
-    <col min="12" max="13" width="14.125" style="16" customWidth="1"/>
-    <col min="14" max="15" width="20.625" style="16" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="2"/>
+    <col min="10" max="12" width="13.75" style="16" customWidth="1"/>
+    <col min="13" max="14" width="14.125" style="16" customWidth="1"/>
+    <col min="15" max="16" width="20.625" style="16" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" customHeight="1" spans="8:15">
+    <row r="1" s="2" customFormat="1" customHeight="1" spans="8:16">
       <c r="H1" s="16"/>
       <c r="I1" s="16"/>
       <c r="J1" s="16"/>
@@ -2292,8 +2298,9 @@
       <c r="M1" s="16"/>
       <c r="N1" s="16"/>
       <c r="O1" s="16"/>
-    </row>
-    <row r="2" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P1" s="16"/>
+    </row>
+    <row r="2" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C2" s="17"/>
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
@@ -2303,8 +2310,9 @@
       <c r="M2" s="16"/>
       <c r="N2" s="16"/>
       <c r="O2" s="16"/>
-    </row>
-    <row r="3" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P2" s="16"/>
+    </row>
+    <row r="3" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
@@ -2344,13 +2352,16 @@
       <c r="O3" s="10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P3" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C4" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>2</v>
@@ -2362,77 +2373,83 @@
         <v>4</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>22</v>
+      </c>
+      <c r="P4" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="O5" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>25</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
@@ -2444,13 +2461,13 @@
         <v>9999</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I6" s="11">
         <v>0</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K6" s="11">
         <v>0</v>
@@ -2461,19 +2478,22 @@
       <c r="M6" s="11">
         <v>0</v>
       </c>
-      <c r="N6" s="18" t="s">
-        <v>27</v>
+      <c r="N6" s="11">
+        <v>0</v>
       </c>
       <c r="O6" s="18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>29</v>
+      </c>
+      <c r="P6" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C8" s="2">
         <v>101</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -2485,36 +2505,39 @@
         <v>2000</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I8" s="11">
         <v>0</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K8" s="11">
         <v>0</v>
       </c>
       <c r="L8" s="11">
+        <v>0</v>
+      </c>
+      <c r="M8" s="11">
         <v>1</v>
       </c>
-      <c r="M8" s="11">
-        <v>0</v>
-      </c>
-      <c r="N8" s="18" t="s">
-        <v>32</v>
+      <c r="N8" s="11">
+        <v>0</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P8" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C9" s="2">
         <v>102</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -2526,36 +2549,39 @@
         <v>2000</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I9" s="11">
         <v>0</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K9" s="11">
         <v>0</v>
       </c>
       <c r="L9" s="11">
+        <v>0</v>
+      </c>
+      <c r="M9" s="11">
         <v>1</v>
       </c>
-      <c r="M9" s="11">
-        <v>0</v>
-      </c>
-      <c r="N9" s="18" t="s">
-        <v>32</v>
+      <c r="N9" s="11">
+        <v>0</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P9" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C10" s="2">
         <v>103</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -2567,36 +2593,39 @@
         <v>2000</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I10" s="11">
         <v>0</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K10" s="11">
         <v>0</v>
       </c>
       <c r="L10" s="11">
+        <v>0</v>
+      </c>
+      <c r="M10" s="11">
         <v>1</v>
       </c>
-      <c r="M10" s="11">
-        <v>0</v>
-      </c>
-      <c r="N10" s="18" t="s">
-        <v>32</v>
+      <c r="N10" s="11">
+        <v>0</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P10" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C11" s="2">
         <v>104</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -2608,36 +2637,39 @@
         <v>2000</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I11" s="11">
         <v>0</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K11" s="11">
         <v>0</v>
       </c>
       <c r="L11" s="11">
+        <v>0</v>
+      </c>
+      <c r="M11" s="11">
         <v>1</v>
       </c>
-      <c r="M11" s="11">
-        <v>0</v>
-      </c>
-      <c r="N11" s="18" t="s">
-        <v>32</v>
+      <c r="N11" s="11">
+        <v>0</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P11" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C12" s="2">
         <v>105</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
@@ -2649,36 +2681,39 @@
         <v>2000</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I12" s="11">
         <v>0</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K12" s="11">
         <v>0</v>
       </c>
       <c r="L12" s="11">
+        <v>0</v>
+      </c>
+      <c r="M12" s="11">
         <v>1</v>
       </c>
-      <c r="M12" s="11">
-        <v>0</v>
-      </c>
-      <c r="N12" s="18" t="s">
-        <v>32</v>
+      <c r="N12" s="11">
+        <v>0</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P12" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C13" s="2">
         <v>106</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
@@ -2690,36 +2725,39 @@
         <v>2000</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I13" s="11">
         <v>0</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K13" s="11">
         <v>0</v>
       </c>
       <c r="L13" s="11">
+        <v>0</v>
+      </c>
+      <c r="M13" s="11">
         <v>1</v>
       </c>
-      <c r="M13" s="11">
-        <v>0</v>
-      </c>
-      <c r="N13" s="18" t="s">
-        <v>32</v>
+      <c r="N13" s="11">
+        <v>0</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P13" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C14" s="2">
         <v>107</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -2731,36 +2769,39 @@
         <v>2000</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I14" s="11">
         <v>0</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K14" s="11">
         <v>0</v>
       </c>
       <c r="L14" s="11">
+        <v>0</v>
+      </c>
+      <c r="M14" s="11">
         <v>1</v>
       </c>
-      <c r="M14" s="11">
-        <v>0</v>
-      </c>
-      <c r="N14" s="18" t="s">
-        <v>32</v>
+      <c r="N14" s="11">
+        <v>0</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P14" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C15" s="2">
         <v>108</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -2772,36 +2813,39 @@
         <v>2000</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I15" s="11">
         <v>0</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K15" s="11">
         <v>0</v>
       </c>
       <c r="L15" s="11">
+        <v>0</v>
+      </c>
+      <c r="M15" s="11">
         <v>1</v>
       </c>
-      <c r="M15" s="11">
-        <v>0</v>
-      </c>
-      <c r="N15" s="18" t="s">
-        <v>32</v>
+      <c r="N15" s="11">
+        <v>0</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P15" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C16" s="2">
         <v>109</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -2813,36 +2857,39 @@
         <v>2000</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I16" s="11">
         <v>0</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K16" s="11">
         <v>0</v>
       </c>
       <c r="L16" s="11">
+        <v>0</v>
+      </c>
+      <c r="M16" s="11">
         <v>1</v>
       </c>
-      <c r="M16" s="11">
-        <v>0</v>
-      </c>
-      <c r="N16" s="18" t="s">
-        <v>32</v>
+      <c r="N16" s="11">
+        <v>0</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P16" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C17" s="2">
         <v>110</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -2854,36 +2901,39 @@
         <v>2000</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I17" s="11">
         <v>0</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K17" s="11">
         <v>0</v>
       </c>
       <c r="L17" s="11">
+        <v>0</v>
+      </c>
+      <c r="M17" s="11">
         <v>1</v>
       </c>
-      <c r="M17" s="11">
-        <v>0</v>
-      </c>
-      <c r="N17" s="18" t="s">
-        <v>32</v>
+      <c r="N17" s="11">
+        <v>0</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P17" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C18" s="2">
         <v>111</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -2895,36 +2945,39 @@
         <v>2000</v>
       </c>
       <c r="H18" s="19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I18" s="11">
         <v>0</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K18" s="11">
         <v>0</v>
       </c>
       <c r="L18" s="11">
+        <v>0</v>
+      </c>
+      <c r="M18" s="11">
         <v>1</v>
       </c>
-      <c r="M18" s="11">
-        <v>0</v>
-      </c>
-      <c r="N18" s="18" t="s">
-        <v>32</v>
+      <c r="N18" s="11">
+        <v>0</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P18" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C19" s="2">
         <v>112</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -2936,37 +2989,40 @@
         <v>2000</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I19" s="11">
         <v>0</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K19" s="11">
         <v>0</v>
       </c>
       <c r="L19" s="11">
+        <v>0</v>
+      </c>
+      <c r="M19" s="11">
         <v>1</v>
       </c>
-      <c r="M19" s="11">
-        <v>0</v>
-      </c>
-      <c r="N19" s="18" t="s">
-        <v>32</v>
+      <c r="N19" s="11">
+        <v>0</v>
       </c>
       <c r="O19" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="P19" s="18" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1"/>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C21" s="2">
         <v>201</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E21" s="2">
         <v>100</v>
@@ -2978,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I21" s="11">
         <v>0</v>
@@ -2989,25 +3045,28 @@
       <c r="K21" s="11">
         <v>0</v>
       </c>
-      <c r="L21" s="2">
-        <v>0</v>
-      </c>
-      <c r="M21" s="11">
+      <c r="L21" s="11">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0</v>
+      </c>
+      <c r="N21" s="11">
         <v>1</v>
       </c>
-      <c r="N21" s="18" t="s">
-        <v>32</v>
-      </c>
       <c r="O21" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P21" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C22" s="2">
         <v>202</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E22" s="2">
         <v>100</v>
@@ -3019,7 +3078,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I22" s="11">
         <v>0</v>
@@ -3030,25 +3089,28 @@
       <c r="K22" s="11">
         <v>0</v>
       </c>
-      <c r="L22" s="2">
-        <v>0</v>
-      </c>
-      <c r="M22" s="11">
+      <c r="L22" s="11">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="N22" s="11">
         <v>1</v>
       </c>
-      <c r="N22" s="18" t="s">
-        <v>32</v>
-      </c>
       <c r="O22" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P22" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C23" s="2">
         <v>203</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E23" s="2">
         <v>100</v>
@@ -3060,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I23" s="11">
         <v>0</v>
@@ -3071,35 +3133,39 @@
       <c r="K23" s="11">
         <v>0</v>
       </c>
-      <c r="L23" s="2">
-        <v>0</v>
-      </c>
-      <c r="M23" s="11">
+      <c r="L23" s="11">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2">
+        <v>0</v>
+      </c>
+      <c r="N23" s="11">
         <v>1</v>
       </c>
-      <c r="N23" s="18" t="s">
-        <v>32</v>
-      </c>
       <c r="O23" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="8:15">
+        <v>34</v>
+      </c>
+      <c r="P23" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="8:16">
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
       <c r="K24" s="11">
         <v>0</v>
       </c>
-      <c r="M24" s="11"/>
+      <c r="L24" s="11"/>
       <c r="N24" s="11"/>
       <c r="O24" s="11"/>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P24" s="11"/>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C25" s="2">
         <v>301</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -3111,36 +3177,39 @@
         <v>2000</v>
       </c>
       <c r="H25" s="19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I25" s="2">
         <v>0</v>
       </c>
       <c r="J25" s="19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K25" s="11">
         <v>0</v>
       </c>
-      <c r="L25" s="2">
+      <c r="L25" s="11">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2">
         <v>1</v>
       </c>
-      <c r="M25" s="11">
-        <v>0</v>
-      </c>
-      <c r="N25" s="18" t="s">
-        <v>32</v>
+      <c r="N25" s="11">
+        <v>0</v>
       </c>
       <c r="O25" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P25" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C26" s="2">
         <v>302</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -3152,37 +3221,40 @@
         <v>2000</v>
       </c>
       <c r="H26" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="19" t="s">
-        <v>73</v>
-      </c>
       <c r="K26" s="11">
         <v>0</v>
       </c>
-      <c r="L26" s="2">
+      <c r="L26" s="11">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2">
         <v>1</v>
       </c>
-      <c r="M26" s="11">
-        <v>0</v>
-      </c>
-      <c r="N26" s="18" t="s">
-        <v>32</v>
+      <c r="N26" s="11">
+        <v>0</v>
       </c>
       <c r="O26" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="P26" s="18" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1"/>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C28" s="2">
         <v>801</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E28" s="2">
         <v>98</v>
@@ -3194,36 +3266,39 @@
         <v>2000</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I28" s="19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J28" s="19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K28" s="11">
         <v>0</v>
       </c>
-      <c r="L28" s="2">
-        <v>0</v>
-      </c>
-      <c r="M28" s="11">
-        <v>0</v>
-      </c>
-      <c r="N28" s="18" t="s">
-        <v>32</v>
+      <c r="L28" s="11">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2">
+        <v>0</v>
+      </c>
+      <c r="N28" s="11">
+        <v>0</v>
       </c>
       <c r="O28" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P28" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C29" s="2">
         <v>802</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -3235,36 +3310,39 @@
         <v>2000</v>
       </c>
       <c r="H29" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K29" s="11">
         <v>0</v>
       </c>
       <c r="L29" s="11">
+        <v>0</v>
+      </c>
+      <c r="M29" s="11">
         <v>1</v>
       </c>
-      <c r="M29" s="11">
-        <v>0</v>
-      </c>
-      <c r="N29" s="18" t="s">
-        <v>32</v>
+      <c r="N29" s="11">
+        <v>0</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P29" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C30" s="2">
         <v>803</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E30" s="2">
         <v>98</v>
@@ -3276,44 +3354,48 @@
         <v>2000</v>
       </c>
       <c r="H30" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="J30" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="I30" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="J30" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="K30" s="11">
         <v>0</v>
       </c>
-      <c r="L30" s="2">
-        <v>0</v>
-      </c>
-      <c r="M30" s="11">
-        <v>0</v>
-      </c>
-      <c r="N30" s="18" t="s">
-        <v>32</v>
+      <c r="L30" s="11">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2">
+        <v>0</v>
+      </c>
+      <c r="N30" s="11">
+        <v>0</v>
       </c>
       <c r="O30" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="9:15">
+        <v>34</v>
+      </c>
+      <c r="P30" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="9:16">
       <c r="I31" s="11"/>
       <c r="J31" s="11"/>
       <c r="K31" s="11"/>
-      <c r="M31" s="11"/>
+      <c r="L31" s="11"/>
       <c r="N31" s="11"/>
       <c r="O31" s="11"/>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P31" s="11"/>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C32" s="2">
         <v>804</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E32" s="2">
         <v>98</v>
@@ -3325,36 +3407,39 @@
         <v>2000</v>
       </c>
       <c r="H32" s="19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K32" s="11">
         <v>0</v>
       </c>
-      <c r="L32" s="2">
-        <v>0</v>
-      </c>
-      <c r="M32" s="11">
-        <v>0</v>
-      </c>
-      <c r="N32" s="18" t="s">
-        <v>32</v>
+      <c r="L32" s="11">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2">
+        <v>0</v>
+      </c>
+      <c r="N32" s="11">
+        <v>0</v>
       </c>
       <c r="O32" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P32" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C33" s="2">
         <v>805</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
@@ -3366,36 +3451,39 @@
         <v>2000</v>
       </c>
       <c r="H33" s="19" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J33" s="18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K33" s="11">
         <v>0</v>
       </c>
-      <c r="L33" s="2">
-        <v>0</v>
-      </c>
-      <c r="M33" s="11">
-        <v>0</v>
-      </c>
-      <c r="N33" s="18" t="s">
-        <v>32</v>
+      <c r="L33" s="11">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2">
+        <v>0</v>
+      </c>
+      <c r="N33" s="11">
+        <v>0</v>
       </c>
       <c r="O33" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P33" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C34" s="2">
         <v>806</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E34" s="2">
         <v>98</v>
@@ -3407,13 +3495,13 @@
         <v>2000</v>
       </c>
       <c r="H34" s="19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I34" s="19" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J34" s="18" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K34" s="11">
         <v>0</v>
@@ -3421,22 +3509,25 @@
       <c r="L34" s="2">
         <v>0</v>
       </c>
-      <c r="M34" s="11">
-        <v>0</v>
-      </c>
-      <c r="N34" s="18" t="s">
-        <v>32</v>
+      <c r="M34" s="2">
+        <v>0</v>
+      </c>
+      <c r="N34" s="11">
+        <v>0</v>
       </c>
       <c r="O34" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P34" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C35" s="2">
         <v>807</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
@@ -3448,36 +3539,39 @@
         <v>2000</v>
       </c>
       <c r="H35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I35" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J35" s="18" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K35" s="11">
         <v>0</v>
       </c>
       <c r="L35" s="2">
-        <v>0</v>
-      </c>
-      <c r="M35" s="11">
-        <v>0</v>
-      </c>
-      <c r="N35" s="18" t="s">
-        <v>32</v>
+        <v>200000</v>
+      </c>
+      <c r="M35" s="2">
+        <v>0</v>
+      </c>
+      <c r="N35" s="11">
+        <v>0</v>
       </c>
       <c r="O35" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P35" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C36" s="2">
         <v>808</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -3489,31 +3583,34 @@
         <v>2000</v>
       </c>
       <c r="H36" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="I36" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="J36" s="2">
-        <v>2000000</v>
+        <v>101</v>
+      </c>
+      <c r="I36" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="J36" s="18" t="s">
+        <v>103</v>
       </c>
       <c r="K36" s="11">
         <v>0</v>
       </c>
       <c r="L36" s="2">
-        <v>0</v>
-      </c>
-      <c r="M36" s="11">
-        <v>0</v>
-      </c>
-      <c r="N36" s="18" t="s">
-        <v>32</v>
+        <v>400000</v>
+      </c>
+      <c r="M36" s="2">
+        <v>0</v>
+      </c>
+      <c r="N36" s="11">
+        <v>0</v>
       </c>
       <c r="O36" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P36" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" customHeight="1" spans="3:16">
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -3527,13 +3624,14 @@
       <c r="M37" s="16"/>
       <c r="N37" s="16"/>
       <c r="O37" s="16"/>
-    </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P37" s="16"/>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C38" s="2">
         <v>991</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E38" s="2">
         <v>99</v>
@@ -3545,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I38" s="11">
         <v>0</v>
@@ -3556,25 +3654,28 @@
       <c r="K38" s="11">
         <v>0</v>
       </c>
-      <c r="L38" s="2">
+      <c r="L38" s="11">
         <v>0</v>
       </c>
       <c r="M38" s="2">
+        <v>0</v>
+      </c>
+      <c r="N38" s="2">
         <v>1</v>
       </c>
-      <c r="N38" s="18" t="s">
-        <v>32</v>
-      </c>
       <c r="O38" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:15">
+        <v>34</v>
+      </c>
+      <c r="P38" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C39" s="2">
         <v>992</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E39" s="2">
         <v>101</v>
@@ -3586,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I39" s="11">
         <v>0</v>
@@ -3597,21 +3698,24 @@
       <c r="K39" s="11">
         <v>0</v>
       </c>
-      <c r="L39" s="2">
+      <c r="L39" s="11">
         <v>0</v>
       </c>
       <c r="M39" s="2">
+        <v>0</v>
+      </c>
+      <c r="N39" s="2">
         <v>1</v>
       </c>
-      <c r="N39" s="18" t="s">
-        <v>32</v>
-      </c>
       <c r="O39" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="P39" s="18" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1"/>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="8:15">
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="8:16">
       <c r="H41" s="16"/>
       <c r="I41" s="16"/>
       <c r="J41" s="16"/>
@@ -3620,8 +3724,9 @@
       <c r="M41" s="16"/>
       <c r="N41" s="16"/>
       <c r="O41" s="16"/>
-    </row>
-    <row r="42" s="2" customFormat="1" customHeight="1" spans="8:15">
+      <c r="P41" s="16"/>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="8:16">
       <c r="H42" s="16"/>
       <c r="I42" s="16"/>
       <c r="J42" s="16"/>
@@ -3630,8 +3735,9 @@
       <c r="M42" s="16"/>
       <c r="N42" s="16"/>
       <c r="O42" s="16"/>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="8:15">
+      <c r="P42" s="16"/>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="8:16">
       <c r="H43" s="16"/>
       <c r="I43" s="16"/>
       <c r="J43" s="16"/>
@@ -3640,8 +3746,9 @@
       <c r="M43" s="16"/>
       <c r="N43" s="16"/>
       <c r="O43" s="16"/>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="8:15">
+      <c r="P43" s="16"/>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="8:16">
       <c r="H44" s="16"/>
       <c r="I44" s="16"/>
       <c r="J44" s="16"/>
@@ -3650,6 +3757,7 @@
       <c r="M44" s="16"/>
       <c r="N44" s="16"/>
       <c r="O44" s="16"/>
+      <c r="P44" s="16"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F29">
@@ -3723,7 +3831,7 @@
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -3731,7 +3839,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>2</v>
@@ -3755,24 +3863,24 @@
         <v>8</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C4" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>2</v>
@@ -3784,69 +3892,69 @@
         <v>4</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3854,7 +3962,7 @@
         <v>1000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -3866,7 +3974,7 @@
         <v>1051</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I6" s="2">
         <v>40000</v>
@@ -3884,13 +3992,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O6" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3898,7 +4006,7 @@
         <v>1001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -3910,7 +4018,7 @@
         <v>1052</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I7" s="2">
         <v>40000</v>
@@ -3928,13 +4036,13 @@
         <v>0</v>
       </c>
       <c r="N7" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3942,7 +4050,7 @@
         <v>1002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -3954,7 +4062,7 @@
         <v>1053</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I8" s="2">
         <v>40000</v>
@@ -3972,13 +4080,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3986,7 +4094,7 @@
         <v>1003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -3998,7 +4106,7 @@
         <v>1054</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I9" s="2">
         <v>40000</v>
@@ -4016,13 +4124,13 @@
         <v>0</v>
       </c>
       <c r="N9" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4030,7 +4138,7 @@
         <v>1004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -4042,7 +4150,7 @@
         <v>1055</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="I10" s="2">
         <v>40000</v>
@@ -4060,13 +4168,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4074,7 +4182,7 @@
         <v>1005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -4086,7 +4194,7 @@
         <v>1056</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I11" s="2">
         <v>40000</v>
@@ -4104,13 +4212,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4118,7 +4226,7 @@
         <v>1006</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
@@ -4130,7 +4238,7 @@
         <v>1057</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I12" s="2">
         <v>40000</v>
@@ -4148,13 +4256,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4162,7 +4270,7 @@
         <v>1007</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
@@ -4174,7 +4282,7 @@
         <v>1058</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I13" s="2">
         <v>40000</v>
@@ -4192,13 +4300,13 @@
         <v>0</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4206,7 +4314,7 @@
         <v>1008</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -4218,7 +4326,7 @@
         <v>1059</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="I14" s="2">
         <v>40000</v>
@@ -4236,13 +4344,13 @@
         <v>0</v>
       </c>
       <c r="N14" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4250,7 +4358,7 @@
         <v>1009</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -4262,7 +4370,7 @@
         <v>1060</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="I15" s="2">
         <v>40000</v>
@@ -4280,13 +4388,13 @@
         <v>0</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4294,7 +4402,7 @@
         <v>1010</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -4306,7 +4414,7 @@
         <v>1061</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I16" s="2">
         <v>40000</v>
@@ -4324,13 +4432,13 @@
         <v>0</v>
       </c>
       <c r="N16" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4338,7 +4446,7 @@
         <v>1011</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -4350,7 +4458,7 @@
         <v>1062</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I17" s="2">
         <v>40000</v>
@@ -4368,13 +4476,13 @@
         <v>0</v>
       </c>
       <c r="N17" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4382,7 +4490,7 @@
         <v>1012</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -4394,7 +4502,7 @@
         <v>1063</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I18" s="2">
         <v>40000</v>
@@ -4412,13 +4520,13 @@
         <v>0</v>
       </c>
       <c r="N18" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4426,7 +4534,7 @@
         <v>1013</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -4438,7 +4546,7 @@
         <v>1064</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -4456,13 +4564,13 @@
         <v>0</v>
       </c>
       <c r="N19" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O19" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4470,7 +4578,7 @@
         <v>1014</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E20" s="2">
         <v>98</v>
@@ -4482,7 +4590,7 @@
         <v>1065</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I20" s="2">
         <v>40000</v>
@@ -4500,13 +4608,13 @@
         <v>0</v>
       </c>
       <c r="N20" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O20" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4514,7 +4622,7 @@
         <v>1015</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -4526,7 +4634,7 @@
         <v>1066</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I21" s="2">
         <v>40000</v>
@@ -4544,13 +4652,13 @@
         <v>0</v>
       </c>
       <c r="N21" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O21" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4558,7 +4666,7 @@
         <v>1016</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -4570,7 +4678,7 @@
         <v>1067</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I22" s="2">
         <v>40000</v>
@@ -4588,13 +4696,13 @@
         <v>0</v>
       </c>
       <c r="N22" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4602,7 +4710,7 @@
         <v>1017</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -4614,7 +4722,7 @@
         <v>1068</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I23" s="2">
         <v>40000</v>
@@ -4632,13 +4740,13 @@
         <v>0</v>
       </c>
       <c r="N23" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4646,7 +4754,7 @@
         <v>1018</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -4658,7 +4766,7 @@
         <v>1069</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I24" s="2">
         <v>40000</v>
@@ -4676,13 +4784,13 @@
         <v>0</v>
       </c>
       <c r="N24" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O24" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4690,7 +4798,7 @@
         <v>1019</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -4702,7 +4810,7 @@
         <v>1070</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I25" s="2">
         <v>40000</v>
@@ -4720,13 +4828,13 @@
         <v>0</v>
       </c>
       <c r="N25" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O25" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4734,7 +4842,7 @@
         <v>1020</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -4746,7 +4854,7 @@
         <v>1071</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I26" s="2">
         <v>40000</v>
@@ -4764,13 +4872,13 @@
         <v>0</v>
       </c>
       <c r="N26" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O26" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4778,7 +4886,7 @@
         <v>1021</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -4790,7 +4898,7 @@
         <v>1072</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>
@@ -4808,13 +4916,13 @@
         <v>0</v>
       </c>
       <c r="N27" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O27" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4822,7 +4930,7 @@
         <v>1022</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E28" s="2">
         <v>98</v>
@@ -4834,7 +4942,7 @@
         <v>1073</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I28" s="2">
         <v>40000</v>
@@ -4852,13 +4960,13 @@
         <v>0</v>
       </c>
       <c r="N28" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O28" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:16">
@@ -4866,7 +4974,7 @@
         <v>1023</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -4878,7 +4986,7 @@
         <v>1074</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="I29" s="2">
         <v>40000</v>
@@ -4896,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="N29" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4910,7 +5018,7 @@
         <v>1024</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E30" s="2">
         <v>98</v>
@@ -4922,7 +5030,7 @@
         <v>1075</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="I30" s="2">
         <v>4000</v>
@@ -4940,13 +5048,13 @@
         <v>0</v>
       </c>
       <c r="N30" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O30" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4954,7 +5062,7 @@
         <v>1025</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E31" s="2">
         <v>98</v>
@@ -4966,7 +5074,7 @@
         <v>1076</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="I31" s="2">
         <v>4000</v>
@@ -4984,13 +5092,13 @@
         <v>0</v>
       </c>
       <c r="N31" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O31" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4998,7 +5106,7 @@
         <v>1026</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E32" s="2">
         <v>98</v>
@@ -5010,7 +5118,7 @@
         <v>1077</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="I32" s="2">
         <v>4000</v>
@@ -5028,13 +5136,13 @@
         <v>0</v>
       </c>
       <c r="N32" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O32" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -5042,7 +5150,7 @@
         <v>1027</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
@@ -5054,7 +5162,7 @@
         <v>1078</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="I33" s="2">
         <v>4000</v>
@@ -5072,13 +5180,13 @@
         <v>0</v>
       </c>
       <c r="N33" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O33" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:16">
@@ -5086,7 +5194,7 @@
         <v>1028</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E34" s="2">
         <v>98</v>
@@ -5098,7 +5206,7 @@
         <v>1079</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I34" s="2">
         <v>4000</v>
@@ -5116,13 +5224,13 @@
         <v>0</v>
       </c>
       <c r="N34" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O34" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:16">
@@ -5130,7 +5238,7 @@
         <v>1029</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
@@ -5142,7 +5250,7 @@
         <v>1080</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I35" s="2">
         <v>4000</v>
@@ -5160,13 +5268,13 @@
         <v>0</v>
       </c>
       <c r="N35" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O35" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:16">
@@ -5174,7 +5282,7 @@
         <v>1030</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -5186,7 +5294,7 @@
         <v>1081</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="I36" s="2">
         <v>4000</v>
@@ -5204,13 +5312,13 @@
         <v>0</v>
       </c>
       <c r="N36" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O36" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:16">
@@ -5218,7 +5326,7 @@
         <v>1031</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -5230,7 +5338,7 @@
         <v>1082</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I37" s="2">
         <v>4000</v>
@@ -5248,13 +5356,13 @@
         <v>0</v>
       </c>
       <c r="N37" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O37" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:16">
@@ -5262,7 +5370,7 @@
         <v>1032</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E38" s="2">
         <v>98</v>
@@ -5274,7 +5382,7 @@
         <v>1083</v>
       </c>
       <c r="H38" s="20" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I38" s="2">
         <v>4000</v>
@@ -5292,13 +5400,13 @@
         <v>0</v>
       </c>
       <c r="N38" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O38" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:16">
@@ -5306,7 +5414,7 @@
         <v>1033</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E39" s="2">
         <v>98</v>
@@ -5318,7 +5426,7 @@
         <v>1084</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I39" s="2">
         <v>4000</v>
@@ -5336,13 +5444,13 @@
         <v>0</v>
       </c>
       <c r="N39" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O39" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:16">
@@ -5350,7 +5458,7 @@
         <v>1034</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E40" s="2">
         <v>98</v>
@@ -5362,7 +5470,7 @@
         <v>1085</v>
       </c>
       <c r="H40" s="20" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I40" s="2">
         <v>4000</v>
@@ -5380,13 +5488,13 @@
         <v>0</v>
       </c>
       <c r="N40" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O40" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:16">
@@ -5394,7 +5502,7 @@
         <v>1035</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E41" s="2">
         <v>98</v>
@@ -5406,7 +5514,7 @@
         <v>1086</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="I41" s="2">
         <v>4000</v>
@@ -5424,13 +5532,13 @@
         <v>0</v>
       </c>
       <c r="N41" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O41" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:16">
@@ -5438,7 +5546,7 @@
         <v>1036</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E42" s="2">
         <v>98</v>
@@ -5450,7 +5558,7 @@
         <v>1087</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="I42" s="2">
         <v>4000</v>
@@ -5468,13 +5576,13 @@
         <v>0</v>
       </c>
       <c r="N42" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O42" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:16">
@@ -5482,7 +5590,7 @@
         <v>1037</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E43" s="2">
         <v>98</v>
@@ -5494,7 +5602,7 @@
         <v>1088</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="I43" s="2">
         <v>4000</v>
@@ -5512,13 +5620,13 @@
         <v>0</v>
       </c>
       <c r="N43" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O43" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:16">
@@ -5526,7 +5634,7 @@
         <v>1038</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E44" s="2">
         <v>98</v>
@@ -5538,7 +5646,7 @@
         <v>1089</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="I44" s="2">
         <v>4000</v>
@@ -5556,13 +5664,13 @@
         <v>0</v>
       </c>
       <c r="N44" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O44" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:16">
@@ -5570,7 +5678,7 @@
         <v>1039</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E45" s="2">
         <v>98</v>
@@ -5582,7 +5690,7 @@
         <v>1090</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I45" s="2">
         <v>4000</v>
@@ -5600,13 +5708,13 @@
         <v>0</v>
       </c>
       <c r="N45" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O45" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:16">
@@ -5614,7 +5722,7 @@
         <v>1040</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E46" s="2">
         <v>98</v>
@@ -5626,7 +5734,7 @@
         <v>1091</v>
       </c>
       <c r="H46" s="20" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I46" s="2">
         <v>4000</v>
@@ -5644,13 +5752,13 @@
         <v>0</v>
       </c>
       <c r="N46" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O46" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:16">
@@ -5658,7 +5766,7 @@
         <v>1041</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E47" s="2">
         <v>98</v>
@@ -5670,7 +5778,7 @@
         <v>1092</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="I47" s="2">
         <v>4000</v>
@@ -5688,13 +5796,13 @@
         <v>0</v>
       </c>
       <c r="N47" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O47" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:16">
@@ -5702,7 +5810,7 @@
         <v>1042</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E48" s="2">
         <v>98</v>
@@ -5714,7 +5822,7 @@
         <v>1093</v>
       </c>
       <c r="H48" s="20" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="I48" s="2">
         <v>4000</v>
@@ -5732,13 +5840,13 @@
         <v>0</v>
       </c>
       <c r="N48" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O48" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:16">
@@ -5746,7 +5854,7 @@
         <v>1043</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E49" s="2">
         <v>98</v>
@@ -5758,7 +5866,7 @@
         <v>1094</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="I49" s="2">
         <v>4000</v>
@@ -5776,13 +5884,13 @@
         <v>0</v>
       </c>
       <c r="N49" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O49" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:16">
@@ -5790,7 +5898,7 @@
         <v>1044</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E50" s="2">
         <v>98</v>
@@ -5802,7 +5910,7 @@
         <v>1095</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I50" s="2">
         <v>4000</v>
@@ -5820,13 +5928,13 @@
         <v>0</v>
       </c>
       <c r="N50" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O50" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:16">
@@ -5834,7 +5942,7 @@
         <v>1045</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E51" s="2">
         <v>98</v>
@@ -5846,7 +5954,7 @@
         <v>1096</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I51" s="2">
         <v>4000</v>
@@ -5864,13 +5972,13 @@
         <v>0</v>
       </c>
       <c r="N51" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O51" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:16">
@@ -5878,7 +5986,7 @@
         <v>1046</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E52" s="2">
         <v>98</v>
@@ -5890,7 +5998,7 @@
         <v>1097</v>
       </c>
       <c r="H52" s="20" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I52" s="2">
         <v>4000</v>
@@ -5908,13 +6016,13 @@
         <v>0</v>
       </c>
       <c r="N52" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O52" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:16">
@@ -5922,7 +6030,7 @@
         <v>1047</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E53" s="2">
         <v>98</v>
@@ -5934,7 +6042,7 @@
         <v>1098</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I53" s="2">
         <v>4000</v>
@@ -5952,13 +6060,13 @@
         <v>0</v>
       </c>
       <c r="N53" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O53" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:16">
@@ -5966,7 +6074,7 @@
         <v>1048</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E54" s="2">
         <v>98</v>
@@ -5978,7 +6086,7 @@
         <v>1099</v>
       </c>
       <c r="H54" s="20" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="I54" s="2">
         <v>4000</v>
@@ -5996,13 +6104,13 @@
         <v>0</v>
       </c>
       <c r="N54" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O54" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:16">
@@ -6010,7 +6118,7 @@
         <v>1049</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E55" s="2">
         <v>98</v>
@@ -6022,7 +6130,7 @@
         <v>1100</v>
       </c>
       <c r="H55" s="20" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I55" s="2">
         <v>4000</v>
@@ -6040,13 +6148,13 @@
         <v>0</v>
       </c>
       <c r="N55" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O55" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:16">
@@ -6054,7 +6162,7 @@
         <v>1050</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E56" s="2">
         <v>98</v>
@@ -6066,7 +6174,7 @@
         <v>1101</v>
       </c>
       <c r="H56" s="20" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="I56" s="2">
         <v>4000</v>
@@ -6084,13 +6192,13 @@
         <v>0</v>
       </c>
       <c r="N56" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O56" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:16">
@@ -6098,7 +6206,7 @@
         <v>1051</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E57" s="2">
         <v>98</v>
@@ -6110,7 +6218,7 @@
         <v>1102</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I57" s="2">
         <v>4000</v>
@@ -6128,13 +6236,13 @@
         <v>0</v>
       </c>
       <c r="N57" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O57" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:16">
@@ -6142,7 +6250,7 @@
         <v>1052</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E58" s="2">
         <v>98</v>
@@ -6154,7 +6262,7 @@
         <v>1103</v>
       </c>
       <c r="H58" s="20" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I58" s="2">
         <v>4000</v>
@@ -6172,13 +6280,13 @@
         <v>0</v>
       </c>
       <c r="N58" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O58" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:16">
@@ -6186,7 +6294,7 @@
         <v>1053</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E59" s="2">
         <v>98</v>
@@ -6198,7 +6306,7 @@
         <v>1104</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="I59" s="2">
         <v>4000</v>
@@ -6216,13 +6324,13 @@
         <v>0</v>
       </c>
       <c r="N59" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O59" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60" s="12" customFormat="1" customHeight="1" spans="3:16">
@@ -6230,7 +6338,7 @@
         <v>1054</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E60" s="12">
         <v>98</v>
@@ -6242,7 +6350,7 @@
         <v>1105</v>
       </c>
       <c r="H60" s="21" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="I60" s="12">
         <v>20000</v>
@@ -6260,13 +6368,13 @@
         <v>0</v>
       </c>
       <c r="N60" s="22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O60" s="22" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P60" s="12" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6274,7 +6382,7 @@
         <v>1055</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E61" s="2">
         <v>98</v>
@@ -6286,7 +6394,7 @@
         <v>1106</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="I61" s="2">
         <v>20000</v>
@@ -6304,13 +6412,13 @@
         <v>0</v>
       </c>
       <c r="N61" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O61" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6318,7 +6426,7 @@
         <v>1056</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E62" s="2">
         <v>98</v>
@@ -6330,7 +6438,7 @@
         <v>1107</v>
       </c>
       <c r="H62" s="20" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="I62" s="2">
         <v>20000</v>
@@ -6348,13 +6456,13 @@
         <v>0</v>
       </c>
       <c r="N62" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O62" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6362,7 +6470,7 @@
         <v>1057</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E63" s="2">
         <v>98</v>
@@ -6374,7 +6482,7 @@
         <v>1108</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="I63" s="2">
         <v>20000</v>
@@ -6392,13 +6500,13 @@
         <v>0</v>
       </c>
       <c r="N63" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O63" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:16">
@@ -6406,7 +6514,7 @@
         <v>1058</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E64" s="2">
         <v>98</v>
@@ -6418,7 +6526,7 @@
         <v>1109</v>
       </c>
       <c r="H64" s="20" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I64" s="2">
         <v>20000</v>
@@ -6436,13 +6544,13 @@
         <v>0</v>
       </c>
       <c r="N64" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O64" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6450,7 +6558,7 @@
         <v>1059</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E65" s="2">
         <v>98</v>
@@ -6462,7 +6570,7 @@
         <v>1110</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="I65" s="2">
         <v>20000</v>
@@ -6480,13 +6588,13 @@
         <v>0</v>
       </c>
       <c r="N65" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O65" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6494,7 +6602,7 @@
         <v>1060</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E66" s="2">
         <v>98</v>
@@ -6506,7 +6614,7 @@
         <v>1111</v>
       </c>
       <c r="H66" s="20" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I66" s="2">
         <v>20000</v>
@@ -6524,13 +6632,13 @@
         <v>0</v>
       </c>
       <c r="N66" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O66" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6538,7 +6646,7 @@
         <v>1061</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E67" s="2">
         <v>98</v>
@@ -6550,7 +6658,7 @@
         <v>1112</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="I67" s="2">
         <v>20000</v>
@@ -6568,13 +6676,13 @@
         <v>0</v>
       </c>
       <c r="N67" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O67" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6582,7 +6690,7 @@
         <v>1062</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E68" s="2">
         <v>98</v>
@@ -6594,7 +6702,7 @@
         <v>1113</v>
       </c>
       <c r="H68" s="20" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I68" s="2">
         <v>20000</v>
@@ -6612,13 +6720,13 @@
         <v>0</v>
       </c>
       <c r="N68" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O68" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:16">
@@ -6626,7 +6734,7 @@
         <v>1063</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E69" s="2">
         <v>98</v>
@@ -6638,7 +6746,7 @@
         <v>1114</v>
       </c>
       <c r="H69" s="20" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I69" s="2">
         <v>20000</v>
@@ -6656,13 +6764,13 @@
         <v>0</v>
       </c>
       <c r="N69" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O69" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:16">
@@ -6670,7 +6778,7 @@
         <v>1064</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E70" s="2">
         <v>98</v>
@@ -6682,7 +6790,7 @@
         <v>1115</v>
       </c>
       <c r="H70" s="20" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I70" s="2">
         <v>20000</v>
@@ -6700,13 +6808,13 @@
         <v>0</v>
       </c>
       <c r="N70" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O70" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:16">
@@ -6714,7 +6822,7 @@
         <v>1065</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E71" s="2">
         <v>98</v>
@@ -6726,7 +6834,7 @@
         <v>1116</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="I71" s="2">
         <v>20000</v>
@@ -6744,13 +6852,13 @@
         <v>0</v>
       </c>
       <c r="N71" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O71" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:16">
@@ -6758,7 +6866,7 @@
         <v>1066</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E72" s="2">
         <v>98</v>
@@ -6770,7 +6878,7 @@
         <v>1117</v>
       </c>
       <c r="H72" s="20" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I72" s="2">
         <v>20000</v>
@@ -6788,13 +6896,13 @@
         <v>0</v>
       </c>
       <c r="N72" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O72" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:16">
@@ -6802,7 +6910,7 @@
         <v>1067</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E73" s="2">
         <v>98</v>
@@ -6814,7 +6922,7 @@
         <v>1118</v>
       </c>
       <c r="H73" s="20" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I73" s="2">
         <v>20000</v>
@@ -6832,13 +6940,13 @@
         <v>0</v>
       </c>
       <c r="N73" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O73" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:16">
@@ -6846,7 +6954,7 @@
         <v>1068</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E74" s="2">
         <v>98</v>
@@ -6858,7 +6966,7 @@
         <v>1119</v>
       </c>
       <c r="H74" s="20" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="I74" s="2">
         <v>20000</v>
@@ -6876,13 +6984,13 @@
         <v>0</v>
       </c>
       <c r="N74" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O74" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:16">
@@ -6890,7 +6998,7 @@
         <v>1069</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E75" s="2">
         <v>98</v>
@@ -6902,7 +7010,7 @@
         <v>1120</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I75" s="2">
         <v>20000</v>
@@ -6920,13 +7028,13 @@
         <v>0</v>
       </c>
       <c r="N75" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O75" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:16">
@@ -6934,7 +7042,7 @@
         <v>1070</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E76" s="2">
         <v>98</v>
@@ -6946,7 +7054,7 @@
         <v>1121</v>
       </c>
       <c r="H76" s="20" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="I76" s="2">
         <v>20000</v>
@@ -6964,13 +7072,13 @@
         <v>0</v>
       </c>
       <c r="N76" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O76" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:16">
@@ -6978,7 +7086,7 @@
         <v>1071</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E77" s="2">
         <v>98</v>
@@ -6990,7 +7098,7 @@
         <v>1122</v>
       </c>
       <c r="H77" s="20" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="I77" s="2">
         <v>20000</v>
@@ -7008,13 +7116,13 @@
         <v>0</v>
       </c>
       <c r="N77" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O77" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:16">
@@ -7022,7 +7130,7 @@
         <v>1072</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E78" s="2">
         <v>98</v>
@@ -7034,7 +7142,7 @@
         <v>1123</v>
       </c>
       <c r="H78" s="20" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="I78" s="2">
         <v>20000</v>
@@ -7052,13 +7160,13 @@
         <v>0</v>
       </c>
       <c r="N78" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O78" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:16">
@@ -7066,7 +7174,7 @@
         <v>1073</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E79" s="2">
         <v>98</v>
@@ -7078,7 +7186,7 @@
         <v>1124</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="I79" s="2">
         <v>20000</v>
@@ -7096,13 +7204,13 @@
         <v>0</v>
       </c>
       <c r="N79" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O79" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:16">
@@ -7110,7 +7218,7 @@
         <v>1074</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E80" s="2">
         <v>98</v>
@@ -7122,7 +7230,7 @@
         <v>1125</v>
       </c>
       <c r="H80" s="20" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I80" s="2">
         <v>20000</v>
@@ -7140,13 +7248,13 @@
         <v>0</v>
       </c>
       <c r="N80" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O80" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:16">
@@ -7154,7 +7262,7 @@
         <v>1075</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E81" s="2">
         <v>98</v>
@@ -7166,7 +7274,7 @@
         <v>1126</v>
       </c>
       <c r="H81" s="20" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I81" s="2">
         <v>20000</v>
@@ -7184,13 +7292,13 @@
         <v>0</v>
       </c>
       <c r="N81" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O81" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:16">
@@ -7198,7 +7306,7 @@
         <v>1076</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E82" s="2">
         <v>98</v>
@@ -7210,7 +7318,7 @@
         <v>1127</v>
       </c>
       <c r="H82" s="20" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="I82" s="2">
         <v>20000</v>
@@ -7228,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="N82" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O82" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:16">
@@ -7242,7 +7350,7 @@
         <v>1077</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E83" s="2">
         <v>98</v>
@@ -7254,7 +7362,7 @@
         <v>1128</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="I83" s="2">
         <v>20000</v>
@@ -7272,13 +7380,13 @@
         <v>0</v>
       </c>
       <c r="N83" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O83" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:16">
@@ -7286,7 +7394,7 @@
         <v>1078</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E84" s="2">
         <v>98</v>
@@ -7298,7 +7406,7 @@
         <v>1129</v>
       </c>
       <c r="H84" s="20" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="I84" s="2">
         <v>20000</v>
@@ -7316,13 +7424,13 @@
         <v>0</v>
       </c>
       <c r="N84" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O84" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:16">
@@ -7330,7 +7438,7 @@
         <v>1079</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E85" s="2">
         <v>98</v>
@@ -7342,7 +7450,7 @@
         <v>1130</v>
       </c>
       <c r="H85" s="20" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="I85" s="2">
         <v>20000</v>
@@ -7360,13 +7468,13 @@
         <v>0</v>
       </c>
       <c r="N85" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O85" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:16">
@@ -7374,7 +7482,7 @@
         <v>1080</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E86" s="2">
         <v>98</v>
@@ -7386,7 +7494,7 @@
         <v>1131</v>
       </c>
       <c r="H86" s="20" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="I86" s="2">
         <v>20000</v>
@@ -7404,13 +7512,13 @@
         <v>0</v>
       </c>
       <c r="N86" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O86" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:16">
@@ -7418,7 +7526,7 @@
         <v>1081</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E87" s="2">
         <v>98</v>
@@ -7430,7 +7538,7 @@
         <v>1132</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="I87" s="2">
         <v>20000</v>
@@ -7448,13 +7556,13 @@
         <v>0</v>
       </c>
       <c r="N87" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O87" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:16">
@@ -7462,7 +7570,7 @@
         <v>1082</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E88" s="2">
         <v>98</v>
@@ -7474,7 +7582,7 @@
         <v>1133</v>
       </c>
       <c r="H88" s="20" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="I88" s="2">
         <v>20000</v>
@@ -7492,13 +7600,13 @@
         <v>0</v>
       </c>
       <c r="N88" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O88" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P88" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:16">
@@ -7506,7 +7614,7 @@
         <v>1083</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E89" s="2">
         <v>98</v>
@@ -7518,7 +7626,7 @@
         <v>1134</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="I89" s="2">
         <v>20000</v>
@@ -7536,13 +7644,13 @@
         <v>0</v>
       </c>
       <c r="N89" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O89" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P89" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:16">
@@ -7550,7 +7658,7 @@
         <v>1084</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E90" s="2">
         <v>98</v>
@@ -7562,7 +7670,7 @@
         <v>1135</v>
       </c>
       <c r="H90" s="20" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="I90" s="2">
         <v>20000</v>
@@ -7580,13 +7688,13 @@
         <v>0</v>
       </c>
       <c r="N90" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O90" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P90" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:16">
@@ -7594,7 +7702,7 @@
         <v>1085</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E91" s="2">
         <v>98</v>
@@ -7606,7 +7714,7 @@
         <v>1136</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="I91" s="2">
         <v>20000</v>
@@ -7624,13 +7732,13 @@
         <v>0</v>
       </c>
       <c r="N91" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O91" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P91" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:16">
@@ -7638,7 +7746,7 @@
         <v>1086</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E92" s="2">
         <v>98</v>
@@ -7650,7 +7758,7 @@
         <v>1137</v>
       </c>
       <c r="H92" s="20" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="I92" s="2">
         <v>20000</v>
@@ -7668,13 +7776,13 @@
         <v>0</v>
       </c>
       <c r="N92" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O92" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P92" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:16">
@@ -7682,7 +7790,7 @@
         <v>1087</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E93" s="2">
         <v>98</v>
@@ -7694,7 +7802,7 @@
         <v>1138</v>
       </c>
       <c r="H93" s="20" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="I93" s="2">
         <v>20000</v>
@@ -7712,13 +7820,13 @@
         <v>0</v>
       </c>
       <c r="N93" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O93" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P93" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:16">
@@ -7726,7 +7834,7 @@
         <v>1088</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E94" s="2">
         <v>98</v>
@@ -7738,7 +7846,7 @@
         <v>1139</v>
       </c>
       <c r="H94" s="20" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="I94" s="2">
         <v>20000</v>
@@ -7756,13 +7864,13 @@
         <v>0</v>
       </c>
       <c r="N94" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O94" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P94" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -7823,7 +7931,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>2</v>
@@ -7847,27 +7955,27 @@
         <v>8</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>302</v>
+        <v>9</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="3:16">
       <c r="C4" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>2</v>
@@ -7879,75 +7987,75 @@
         <v>4</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="3:16">
       <c r="C5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -7955,7 +8063,7 @@
         <v>2000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -7967,7 +8075,7 @@
         <v>1070</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I6" s="2">
         <v>120000</v>
@@ -7988,10 +8096,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P6" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -7999,7 +8107,7 @@
         <v>2001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -8011,7 +8119,7 @@
         <v>1071</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I7" s="2">
         <v>120000</v>
@@ -8032,10 +8140,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P7" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8043,7 +8151,7 @@
         <v>2002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -8055,7 +8163,7 @@
         <v>1072</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I8" s="2">
         <v>120000</v>
@@ -8076,10 +8184,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P8" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8087,7 +8195,7 @@
         <v>2003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -8099,7 +8207,7 @@
         <v>1073</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I9" s="2">
         <v>120000</v>
@@ -8120,10 +8228,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P9" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8131,7 +8239,7 @@
         <v>2004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -8143,7 +8251,7 @@
         <v>1074</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I10" s="2">
         <v>120000</v>
@@ -8164,10 +8272,10 @@
         <v>0</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P10" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8175,7 +8283,7 @@
         <v>2005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -8187,7 +8295,7 @@
         <v>1104</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I11" s="2">
         <v>20000</v>
@@ -8208,10 +8316,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P11" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
@@ -8233,7 +8341,7 @@
         <v>2006</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -8245,7 +8353,7 @@
         <v>1105</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I14" s="2">
         <v>360000</v>
@@ -8266,10 +8374,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P14" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8277,7 +8385,7 @@
         <v>2007</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -8289,7 +8397,7 @@
         <v>1106</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I15" s="2">
         <v>360000</v>
@@ -8310,10 +8418,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P15" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8321,7 +8429,7 @@
         <v>2008</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -8333,7 +8441,7 @@
         <v>1107</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I16" s="2">
         <v>360000</v>
@@ -8354,10 +8462,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8365,7 +8473,7 @@
         <v>2009</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -8377,7 +8485,7 @@
         <v>1108</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I17" s="2">
         <v>360000</v>
@@ -8398,10 +8506,10 @@
         <v>0</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P17" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8409,7 +8517,7 @@
         <v>2010</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -8421,7 +8529,7 @@
         <v>1139</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="I18" s="2">
         <v>360000</v>
@@ -8442,10 +8550,10 @@
         <v>0</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P18" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8453,7 +8561,7 @@
         <v>2011</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -8465,7 +8573,7 @@
         <v>1139</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -8486,10 +8594,10 @@
         <v>0</v>
       </c>
       <c r="O19" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P19" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="328">
   <si>
     <t>_id</t>
   </si>
@@ -352,6 +352,15 @@
     <t>2024-11-04</t>
   </si>
   <si>
+    <t>平时部分掉落</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>2025-10-21</t>
+  </si>
+  <si>
     <t>第一批白图鉴</t>
   </si>
   <si>
@@ -362,9 +371,6 @@
   </si>
   <si>
     <t>2023-10-21</t>
-  </si>
-  <si>
-    <t>2025-10-21</t>
   </si>
   <si>
     <t>第一批绿图鉴</t>
@@ -2274,7 +2280,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P44"/>
+  <dimension ref="C1:P45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -2488,56 +2494,72 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C8" s="2">
-        <v>101</v>
-      </c>
-      <c r="D8" s="2" t="s">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="2">
-        <v>98</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G8" s="2">
-        <v>2000</v>
-      </c>
-      <c r="H8" s="19" t="s">
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>9999</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="11">
+        <v>0</v>
+      </c>
+      <c r="J7" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="11">
-        <v>0</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8" s="11">
-        <v>0</v>
-      </c>
-      <c r="L8" s="11">
-        <v>0</v>
-      </c>
-      <c r="M8" s="11">
-        <v>1</v>
-      </c>
-      <c r="N8" s="11">
-        <v>0</v>
-      </c>
-      <c r="O8" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="P8" s="18" t="s">
-        <v>35</v>
-      </c>
+      <c r="K7" s="11">
+        <v>0</v>
+      </c>
+      <c r="L7" s="11">
+        <v>0</v>
+      </c>
+      <c r="M7" s="11">
+        <v>0</v>
+      </c>
+      <c r="N7" s="11">
+        <v>0</v>
+      </c>
+      <c r="O7" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C9" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -2549,13 +2571,13 @@
         <v>2000</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I9" s="11">
         <v>0</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K9" s="11">
         <v>0</v>
@@ -2570,18 +2592,18 @@
         <v>0</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P9" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C10" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -2593,13 +2615,13 @@
         <v>2000</v>
       </c>
       <c r="H10" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="11">
+        <v>0</v>
+      </c>
+      <c r="J10" s="18" t="s">
         <v>40</v>
-      </c>
-      <c r="I10" s="11">
-        <v>0</v>
-      </c>
-      <c r="J10" s="18" t="s">
-        <v>41</v>
       </c>
       <c r="K10" s="11">
         <v>0</v>
@@ -2614,18 +2636,18 @@
         <v>0</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P10" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C11" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -2637,13 +2659,13 @@
         <v>2000</v>
       </c>
       <c r="H11" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="11">
+        <v>0</v>
+      </c>
+      <c r="J11" s="18" t="s">
         <v>43</v>
-      </c>
-      <c r="I11" s="11">
-        <v>0</v>
-      </c>
-      <c r="J11" s="18" t="s">
-        <v>44</v>
       </c>
       <c r="K11" s="11">
         <v>0</v>
@@ -2658,36 +2680,36 @@
         <v>0</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P11" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C12" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
       </c>
       <c r="F12" s="2">
-        <v>1035</v>
+        <v>1000</v>
       </c>
       <c r="G12" s="2">
         <v>2000</v>
       </c>
       <c r="H12" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" s="11">
+        <v>0</v>
+      </c>
+      <c r="J12" s="18" t="s">
         <v>46</v>
-      </c>
-      <c r="I12" s="11">
-        <v>0</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>47</v>
       </c>
       <c r="K12" s="11">
         <v>0</v>
@@ -2702,18 +2724,18 @@
         <v>0</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P12" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C13" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
@@ -2725,13 +2747,13 @@
         <v>2000</v>
       </c>
       <c r="H13" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="11">
+        <v>0</v>
+      </c>
+      <c r="J13" s="18" t="s">
         <v>49</v>
-      </c>
-      <c r="I13" s="11">
-        <v>0</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>50</v>
       </c>
       <c r="K13" s="11">
         <v>0</v>
@@ -2746,18 +2768,18 @@
         <v>0</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P13" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C14" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -2769,13 +2791,13 @@
         <v>2000</v>
       </c>
       <c r="H14" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" s="11">
+        <v>0</v>
+      </c>
+      <c r="J14" s="18" t="s">
         <v>52</v>
-      </c>
-      <c r="I14" s="11">
-        <v>0</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>53</v>
       </c>
       <c r="K14" s="11">
         <v>0</v>
@@ -2790,18 +2812,18 @@
         <v>0</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P14" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C15" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -2813,13 +2835,13 @@
         <v>2000</v>
       </c>
       <c r="H15" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15" s="11">
+        <v>0</v>
+      </c>
+      <c r="J15" s="18" t="s">
         <v>55</v>
-      </c>
-      <c r="I15" s="11">
-        <v>0</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>56</v>
       </c>
       <c r="K15" s="11">
         <v>0</v>
@@ -2834,36 +2856,36 @@
         <v>0</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P15" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C16" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
       </c>
       <c r="F16" s="2">
-        <v>1070</v>
+        <v>1035</v>
       </c>
       <c r="G16" s="2">
         <v>2000</v>
       </c>
       <c r="H16" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="I16" s="11">
+        <v>0</v>
+      </c>
+      <c r="J16" s="18" t="s">
         <v>58</v>
-      </c>
-      <c r="I16" s="11">
-        <v>0</v>
-      </c>
-      <c r="J16" s="18" t="s">
-        <v>59</v>
       </c>
       <c r="K16" s="11">
         <v>0</v>
@@ -2878,18 +2900,18 @@
         <v>0</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C17" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -2901,13 +2923,13 @@
         <v>2000</v>
       </c>
       <c r="H17" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" s="11">
+        <v>0</v>
+      </c>
+      <c r="J17" s="18" t="s">
         <v>61</v>
-      </c>
-      <c r="I17" s="11">
-        <v>0</v>
-      </c>
-      <c r="J17" s="18" t="s">
-        <v>62</v>
       </c>
       <c r="K17" s="11">
         <v>0</v>
@@ -2922,18 +2944,18 @@
         <v>0</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P17" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C18" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -2945,13 +2967,13 @@
         <v>2000</v>
       </c>
       <c r="H18" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="I18" s="11">
+        <v>0</v>
+      </c>
+      <c r="J18" s="18" t="s">
         <v>64</v>
-      </c>
-      <c r="I18" s="11">
-        <v>0</v>
-      </c>
-      <c r="J18" s="18" t="s">
-        <v>38</v>
       </c>
       <c r="K18" s="11">
         <v>0</v>
@@ -2966,15 +2988,15 @@
         <v>0</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P18" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C19" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>65</v>
@@ -2995,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="K19" s="11">
         <v>0</v>
@@ -3010,60 +3032,60 @@
         <v>0</v>
       </c>
       <c r="O19" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P19" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1"/>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C21" s="2">
-        <v>201</v>
-      </c>
-      <c r="D21" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C20" s="2">
+        <v>112</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="2">
+        <v>98</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1070</v>
+      </c>
+      <c r="G20" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H20" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="2">
-        <v>100</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0</v>
-      </c>
-      <c r="G21" s="2">
-        <v>0</v>
-      </c>
-      <c r="H21" s="18" t="s">
+      <c r="I20" s="11">
+        <v>0</v>
+      </c>
+      <c r="J20" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="I21" s="11">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2">
+      <c r="K20" s="11">
+        <v>0</v>
+      </c>
+      <c r="L20" s="11">
+        <v>0</v>
+      </c>
+      <c r="M20" s="11">
         <v>1</v>
       </c>
-      <c r="K21" s="11">
-        <v>0</v>
-      </c>
-      <c r="L21" s="11">
-        <v>0</v>
-      </c>
-      <c r="M21" s="2">
-        <v>0</v>
-      </c>
-      <c r="N21" s="11">
-        <v>1</v>
-      </c>
-      <c r="O21" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="P21" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
+      <c r="N20" s="11">
+        <v>0</v>
+      </c>
+      <c r="O20" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="P20" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1"/>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C22" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>70</v>
@@ -3077,7 +3099,7 @@
       <c r="G22" s="2">
         <v>0</v>
       </c>
-      <c r="H22" s="19" t="s">
+      <c r="H22" s="18" t="s">
         <v>71</v>
       </c>
       <c r="I22" s="11">
@@ -3099,15 +3121,15 @@
         <v>1</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P22" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C23" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>72</v>
@@ -3121,7 +3143,7 @@
       <c r="G23" s="2">
         <v>0</v>
       </c>
-      <c r="H23" s="18" t="s">
+      <c r="H23" s="19" t="s">
         <v>73</v>
       </c>
       <c r="I23" s="11">
@@ -3143,70 +3165,70 @@
         <v>1</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P23" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="8:16">
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C24" s="2">
+        <v>203</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="2">
+        <v>100</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0</v>
+      </c>
+      <c r="H24" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="I24" s="11">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
+        <v>1</v>
+      </c>
       <c r="K24" s="11">
         <v>0</v>
       </c>
-      <c r="L24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C25" s="2">
-        <v>301</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" s="2">
-        <v>98</v>
-      </c>
-      <c r="F25" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G25" s="2">
-        <v>2000</v>
-      </c>
-      <c r="H25" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="I25" s="2">
-        <v>0</v>
-      </c>
-      <c r="J25" s="19" t="s">
-        <v>75</v>
-      </c>
+      <c r="L24" s="11">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2">
+        <v>0</v>
+      </c>
+      <c r="N24" s="11">
+        <v>1</v>
+      </c>
+      <c r="O24" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="P24" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="8:16">
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
       <c r="K25" s="11">
         <v>0</v>
       </c>
-      <c r="L25" s="11">
-        <v>0</v>
-      </c>
-      <c r="M25" s="2">
-        <v>1</v>
-      </c>
-      <c r="N25" s="11">
-        <v>0</v>
-      </c>
-      <c r="O25" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="P25" s="18" t="s">
-        <v>35</v>
-      </c>
+      <c r="L25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C26" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>76</v>
@@ -3215,19 +3237,19 @@
         <v>98</v>
       </c>
       <c r="F26" s="2">
-        <v>1070</v>
+        <v>1000</v>
       </c>
       <c r="G26" s="2">
         <v>2000</v>
       </c>
-      <c r="H26" s="18" t="s">
+      <c r="H26" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="19" t="s">
         <v>77</v>
-      </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="19" t="s">
-        <v>75</v>
       </c>
       <c r="K26" s="11">
         <v>0</v>
@@ -3242,60 +3264,60 @@
         <v>0</v>
       </c>
       <c r="O26" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P26" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1"/>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C28" s="2">
-        <v>801</v>
-      </c>
-      <c r="D28" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C27" s="2">
+        <v>302</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E28" s="2">
-        <v>98</v>
-      </c>
-      <c r="F28" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G28" s="2">
+      <c r="E27" s="2">
+        <v>98</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1070</v>
+      </c>
+      <c r="G27" s="2">
         <v>2000</v>
       </c>
-      <c r="H28" s="18" t="s">
+      <c r="H27" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="I28" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="J28" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="K28" s="11">
-        <v>0</v>
-      </c>
-      <c r="L28" s="11">
-        <v>0</v>
-      </c>
-      <c r="M28" s="2">
-        <v>0</v>
-      </c>
-      <c r="N28" s="11">
-        <v>0</v>
-      </c>
-      <c r="O28" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="P28" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="K27" s="11">
+        <v>0</v>
+      </c>
+      <c r="L27" s="11">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2">
+        <v>1</v>
+      </c>
+      <c r="N27" s="11">
+        <v>0</v>
+      </c>
+      <c r="O27" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="P27" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1"/>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C29" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>80</v>
@@ -3309,14 +3331,14 @@
       <c r="G29" s="2">
         <v>2000</v>
       </c>
-      <c r="H29" s="19" t="s">
+      <c r="H29" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="I29" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="J29" s="18" t="s">
-        <v>82</v>
+      <c r="I29" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="J29" s="19" t="s">
+        <v>58</v>
       </c>
       <c r="K29" s="11">
         <v>0</v>
@@ -3324,141 +3346,141 @@
       <c r="L29" s="11">
         <v>0</v>
       </c>
-      <c r="M29" s="11">
-        <v>1</v>
+      <c r="M29" s="2">
+        <v>0</v>
       </c>
       <c r="N29" s="11">
         <v>0</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P29" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C30" s="2">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2">
         <v>98</v>
       </c>
       <c r="F30" s="2">
-        <v>1105</v>
+        <v>1000</v>
       </c>
       <c r="G30" s="2">
         <v>2000</v>
       </c>
       <c r="H30" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="J30" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="I30" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="J30" s="18" t="s">
-        <v>82</v>
-      </c>
       <c r="K30" s="11">
         <v>0</v>
       </c>
       <c r="L30" s="11">
         <v>0</v>
       </c>
-      <c r="M30" s="2">
-        <v>0</v>
+      <c r="M30" s="11">
+        <v>1</v>
       </c>
       <c r="N30" s="11">
         <v>0</v>
       </c>
       <c r="O30" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P30" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="9:16">
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="11"/>
-      <c r="P31" s="11"/>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C32" s="2">
-        <v>804</v>
-      </c>
-      <c r="D32" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C31" s="2">
+        <v>803</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E32" s="2">
-        <v>98</v>
-      </c>
-      <c r="F32" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G32" s="2">
+      <c r="E31" s="2">
+        <v>98</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1105</v>
+      </c>
+      <c r="G31" s="2">
         <v>2000</v>
       </c>
-      <c r="H32" s="19" t="s">
+      <c r="H31" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="I32" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="J32" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="K32" s="11">
-        <v>0</v>
-      </c>
-      <c r="L32" s="11">
-        <v>0</v>
-      </c>
-      <c r="M32" s="2">
-        <v>0</v>
-      </c>
-      <c r="N32" s="11">
-        <v>0</v>
-      </c>
-      <c r="O32" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="P32" s="18" t="s">
-        <v>35</v>
-      </c>
+      <c r="I31" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="J31" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="K31" s="11">
+        <v>0</v>
+      </c>
+      <c r="L31" s="11">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2">
+        <v>0</v>
+      </c>
+      <c r="N31" s="11">
+        <v>0</v>
+      </c>
+      <c r="O31" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="P31" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="9:16">
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="11"/>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C33" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
       </c>
       <c r="F33" s="2">
-        <v>1105</v>
+        <v>1000</v>
       </c>
       <c r="G33" s="2">
         <v>2000</v>
       </c>
       <c r="H33" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="I33" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="J33" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="I33" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="J33" s="18" t="s">
-        <v>91</v>
-      </c>
       <c r="K33" s="11">
         <v>0</v>
       </c>
@@ -3472,18 +3494,18 @@
         <v>0</v>
       </c>
       <c r="O33" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P33" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C34" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E34" s="2">
         <v>98</v>
@@ -3495,18 +3517,18 @@
         <v>2000</v>
       </c>
       <c r="H34" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="I34" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="J34" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="I34" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="J34" s="18" t="s">
-        <v>95</v>
-      </c>
       <c r="K34" s="11">
         <v>0</v>
       </c>
-      <c r="L34" s="2">
+      <c r="L34" s="11">
         <v>0</v>
       </c>
       <c r="M34" s="2">
@@ -3516,18 +3538,18 @@
         <v>0</v>
       </c>
       <c r="O34" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P34" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C35" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
@@ -3539,19 +3561,19 @@
         <v>2000</v>
       </c>
       <c r="H35" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="I35" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="J35" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="I35" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="J35" s="18" t="s">
-        <v>99</v>
-      </c>
       <c r="K35" s="11">
         <v>0</v>
       </c>
       <c r="L35" s="2">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2">
         <v>0</v>
@@ -3560,18 +3582,18 @@
         <v>0</v>
       </c>
       <c r="O35" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P35" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C36" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -3583,102 +3605,102 @@
         <v>2000</v>
       </c>
       <c r="H36" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I36" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="J36" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="I36" s="19" t="s">
+      <c r="K36" s="11">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2">
+        <v>200000</v>
+      </c>
+      <c r="M36" s="2">
+        <v>0</v>
+      </c>
+      <c r="N36" s="11">
+        <v>0</v>
+      </c>
+      <c r="O36" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="P36" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C37" s="2">
+        <v>808</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="J36" s="18" t="s">
+      <c r="E37" s="2">
+        <v>98</v>
+      </c>
+      <c r="F37" s="2">
+        <v>1105</v>
+      </c>
+      <c r="G37" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H37" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="K36" s="11">
-        <v>0</v>
-      </c>
-      <c r="L36" s="2">
+      <c r="I37" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="J37" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="K37" s="11">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2">
         <v>400000</v>
       </c>
-      <c r="M36" s="2">
-        <v>0</v>
-      </c>
-      <c r="N36" s="11">
-        <v>0</v>
-      </c>
-      <c r="O36" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="P36" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="16"/>
-      <c r="O37" s="16"/>
-      <c r="P37" s="16"/>
-    </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C38" s="2">
-        <v>991</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E38" s="2">
-        <v>99</v>
-      </c>
-      <c r="F38" s="2">
-        <v>0</v>
-      </c>
-      <c r="G38" s="2">
-        <v>0</v>
-      </c>
-      <c r="H38" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="I38" s="11">
-        <v>0</v>
-      </c>
-      <c r="J38" s="2">
-        <v>1</v>
-      </c>
-      <c r="K38" s="11">
-        <v>0</v>
-      </c>
-      <c r="L38" s="11">
-        <v>0</v>
-      </c>
-      <c r="M38" s="2">
-        <v>0</v>
-      </c>
-      <c r="N38" s="2">
-        <v>1</v>
-      </c>
-      <c r="O38" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="P38" s="18" t="s">
-        <v>35</v>
-      </c>
+      <c r="M37" s="2">
+        <v>0</v>
+      </c>
+      <c r="N37" s="11">
+        <v>0</v>
+      </c>
+      <c r="O37" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="P37" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="16"/>
+      <c r="N38" s="16"/>
+      <c r="O38" s="16"/>
+      <c r="P38" s="16"/>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C39" s="2">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>106</v>
       </c>
       <c r="E39" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
@@ -3708,24 +3730,57 @@
         <v>1</v>
       </c>
       <c r="O39" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P39" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="40" s="2" customFormat="1" customHeight="1"/>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="8:16">
-      <c r="H41" s="16"/>
-      <c r="I41" s="16"/>
-      <c r="J41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="16"/>
-      <c r="O41" s="16"/>
-      <c r="P41" s="16"/>
-    </row>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C40" s="2">
+        <v>992</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E40" s="2">
+        <v>101</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2">
+        <v>0</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="I40" s="11">
+        <v>0</v>
+      </c>
+      <c r="J40" s="2">
+        <v>1</v>
+      </c>
+      <c r="K40" s="11">
+        <v>0</v>
+      </c>
+      <c r="L40" s="11">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2">
+        <v>0</v>
+      </c>
+      <c r="N40" s="2">
+        <v>1</v>
+      </c>
+      <c r="O40" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="P40" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1"/>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="8:16">
       <c r="H42" s="16"/>
       <c r="I42" s="16"/>
@@ -3759,30 +3814,41 @@
       <c r="O44" s="16"/>
       <c r="P44" s="16"/>
     </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="8:16">
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="16"/>
+      <c r="O45" s="16"/>
+      <c r="P45" s="16"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F29">
+  <conditionalFormatting sqref="F30">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F30">
+  <conditionalFormatting sqref="F31">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F31">
+  <conditionalFormatting sqref="F32">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
+  <conditionalFormatting sqref="F34">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F34">
+  <conditionalFormatting sqref="F35">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F35">
+  <conditionalFormatting sqref="F36">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F36">
+  <conditionalFormatting sqref="F37">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:C5 F29:F31 F33:F36 F3:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:C5 F30:F32 F34:F37 F3:G5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -3831,7 +3897,7 @@
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -3962,7 +4028,7 @@
         <v>1000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -3974,7 +4040,7 @@
         <v>1051</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I6" s="2">
         <v>40000</v>
@@ -3992,13 +4058,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O6" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4006,7 +4072,7 @@
         <v>1001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -4018,7 +4084,7 @@
         <v>1052</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I7" s="2">
         <v>40000</v>
@@ -4036,13 +4102,13 @@
         <v>0</v>
       </c>
       <c r="N7" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4050,7 +4116,7 @@
         <v>1002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -4062,7 +4128,7 @@
         <v>1053</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I8" s="2">
         <v>40000</v>
@@ -4080,13 +4146,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4094,7 +4160,7 @@
         <v>1003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -4106,7 +4172,7 @@
         <v>1054</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I9" s="2">
         <v>40000</v>
@@ -4124,13 +4190,13 @@
         <v>0</v>
       </c>
       <c r="N9" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4138,7 +4204,7 @@
         <v>1004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -4150,7 +4216,7 @@
         <v>1055</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I10" s="2">
         <v>40000</v>
@@ -4168,13 +4234,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4182,7 +4248,7 @@
         <v>1005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -4194,7 +4260,7 @@
         <v>1056</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I11" s="2">
         <v>40000</v>
@@ -4212,13 +4278,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4226,7 +4292,7 @@
         <v>1006</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
@@ -4238,7 +4304,7 @@
         <v>1057</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I12" s="2">
         <v>40000</v>
@@ -4256,13 +4322,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4270,7 +4336,7 @@
         <v>1007</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
@@ -4282,7 +4348,7 @@
         <v>1058</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I13" s="2">
         <v>40000</v>
@@ -4300,13 +4366,13 @@
         <v>0</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4314,7 +4380,7 @@
         <v>1008</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -4326,7 +4392,7 @@
         <v>1059</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I14" s="2">
         <v>40000</v>
@@ -4344,13 +4410,13 @@
         <v>0</v>
       </c>
       <c r="N14" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4358,7 +4424,7 @@
         <v>1009</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -4370,7 +4436,7 @@
         <v>1060</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I15" s="2">
         <v>40000</v>
@@ -4388,13 +4454,13 @@
         <v>0</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4402,7 +4468,7 @@
         <v>1010</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -4414,7 +4480,7 @@
         <v>1061</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I16" s="2">
         <v>40000</v>
@@ -4432,13 +4498,13 @@
         <v>0</v>
       </c>
       <c r="N16" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4446,7 +4512,7 @@
         <v>1011</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -4458,7 +4524,7 @@
         <v>1062</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I17" s="2">
         <v>40000</v>
@@ -4476,13 +4542,13 @@
         <v>0</v>
       </c>
       <c r="N17" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4490,7 +4556,7 @@
         <v>1012</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -4502,7 +4568,7 @@
         <v>1063</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I18" s="2">
         <v>40000</v>
@@ -4520,13 +4586,13 @@
         <v>0</v>
       </c>
       <c r="N18" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4534,7 +4600,7 @@
         <v>1013</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -4546,7 +4612,7 @@
         <v>1064</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -4564,13 +4630,13 @@
         <v>0</v>
       </c>
       <c r="N19" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O19" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4578,7 +4644,7 @@
         <v>1014</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E20" s="2">
         <v>98</v>
@@ -4590,7 +4656,7 @@
         <v>1065</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I20" s="2">
         <v>40000</v>
@@ -4608,13 +4674,13 @@
         <v>0</v>
       </c>
       <c r="N20" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O20" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4622,7 +4688,7 @@
         <v>1015</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -4634,7 +4700,7 @@
         <v>1066</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I21" s="2">
         <v>40000</v>
@@ -4652,13 +4718,13 @@
         <v>0</v>
       </c>
       <c r="N21" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O21" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4666,7 +4732,7 @@
         <v>1016</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -4678,7 +4744,7 @@
         <v>1067</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I22" s="2">
         <v>40000</v>
@@ -4696,13 +4762,13 @@
         <v>0</v>
       </c>
       <c r="N22" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4710,7 +4776,7 @@
         <v>1017</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -4722,7 +4788,7 @@
         <v>1068</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I23" s="2">
         <v>40000</v>
@@ -4740,13 +4806,13 @@
         <v>0</v>
       </c>
       <c r="N23" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4754,7 +4820,7 @@
         <v>1018</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -4766,7 +4832,7 @@
         <v>1069</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I24" s="2">
         <v>40000</v>
@@ -4784,13 +4850,13 @@
         <v>0</v>
       </c>
       <c r="N24" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O24" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4798,7 +4864,7 @@
         <v>1019</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -4810,7 +4876,7 @@
         <v>1070</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I25" s="2">
         <v>40000</v>
@@ -4828,13 +4894,13 @@
         <v>0</v>
       </c>
       <c r="N25" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O25" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4842,7 +4908,7 @@
         <v>1020</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -4854,7 +4920,7 @@
         <v>1071</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I26" s="2">
         <v>40000</v>
@@ -4872,13 +4938,13 @@
         <v>0</v>
       </c>
       <c r="N26" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O26" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4886,7 +4952,7 @@
         <v>1021</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -4898,7 +4964,7 @@
         <v>1072</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>
@@ -4916,13 +4982,13 @@
         <v>0</v>
       </c>
       <c r="N27" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O27" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4930,7 +4996,7 @@
         <v>1022</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E28" s="2">
         <v>98</v>
@@ -4942,7 +5008,7 @@
         <v>1073</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I28" s="2">
         <v>40000</v>
@@ -4960,13 +5026,13 @@
         <v>0</v>
       </c>
       <c r="N28" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O28" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:16">
@@ -4974,7 +5040,7 @@
         <v>1023</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -4986,7 +5052,7 @@
         <v>1074</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I29" s="2">
         <v>40000</v>
@@ -5004,13 +5070,13 @@
         <v>0</v>
       </c>
       <c r="N29" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -5018,7 +5084,7 @@
         <v>1024</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E30" s="2">
         <v>98</v>
@@ -5030,7 +5096,7 @@
         <v>1075</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I30" s="2">
         <v>4000</v>
@@ -5048,13 +5114,13 @@
         <v>0</v>
       </c>
       <c r="N30" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O30" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -5062,7 +5128,7 @@
         <v>1025</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E31" s="2">
         <v>98</v>
@@ -5074,7 +5140,7 @@
         <v>1076</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I31" s="2">
         <v>4000</v>
@@ -5092,13 +5158,13 @@
         <v>0</v>
       </c>
       <c r="N31" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O31" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -5106,7 +5172,7 @@
         <v>1026</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E32" s="2">
         <v>98</v>
@@ -5118,7 +5184,7 @@
         <v>1077</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I32" s="2">
         <v>4000</v>
@@ -5136,13 +5202,13 @@
         <v>0</v>
       </c>
       <c r="N32" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O32" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -5150,7 +5216,7 @@
         <v>1027</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
@@ -5162,7 +5228,7 @@
         <v>1078</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I33" s="2">
         <v>4000</v>
@@ -5180,13 +5246,13 @@
         <v>0</v>
       </c>
       <c r="N33" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O33" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:16">
@@ -5194,7 +5260,7 @@
         <v>1028</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E34" s="2">
         <v>98</v>
@@ -5206,7 +5272,7 @@
         <v>1079</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I34" s="2">
         <v>4000</v>
@@ -5224,13 +5290,13 @@
         <v>0</v>
       </c>
       <c r="N34" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O34" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:16">
@@ -5238,7 +5304,7 @@
         <v>1029</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
@@ -5250,7 +5316,7 @@
         <v>1080</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I35" s="2">
         <v>4000</v>
@@ -5268,13 +5334,13 @@
         <v>0</v>
       </c>
       <c r="N35" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O35" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:16">
@@ -5282,7 +5348,7 @@
         <v>1030</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -5294,7 +5360,7 @@
         <v>1081</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I36" s="2">
         <v>4000</v>
@@ -5312,13 +5378,13 @@
         <v>0</v>
       </c>
       <c r="N36" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O36" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:16">
@@ -5326,7 +5392,7 @@
         <v>1031</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -5338,7 +5404,7 @@
         <v>1082</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I37" s="2">
         <v>4000</v>
@@ -5356,13 +5422,13 @@
         <v>0</v>
       </c>
       <c r="N37" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O37" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:16">
@@ -5370,7 +5436,7 @@
         <v>1032</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E38" s="2">
         <v>98</v>
@@ -5382,7 +5448,7 @@
         <v>1083</v>
       </c>
       <c r="H38" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I38" s="2">
         <v>4000</v>
@@ -5400,13 +5466,13 @@
         <v>0</v>
       </c>
       <c r="N38" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O38" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:16">
@@ -5414,7 +5480,7 @@
         <v>1033</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E39" s="2">
         <v>98</v>
@@ -5426,7 +5492,7 @@
         <v>1084</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I39" s="2">
         <v>4000</v>
@@ -5444,13 +5510,13 @@
         <v>0</v>
       </c>
       <c r="N39" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O39" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:16">
@@ -5458,7 +5524,7 @@
         <v>1034</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E40" s="2">
         <v>98</v>
@@ -5470,7 +5536,7 @@
         <v>1085</v>
       </c>
       <c r="H40" s="20" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I40" s="2">
         <v>4000</v>
@@ -5488,13 +5554,13 @@
         <v>0</v>
       </c>
       <c r="N40" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O40" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:16">
@@ -5502,7 +5568,7 @@
         <v>1035</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E41" s="2">
         <v>98</v>
@@ -5514,7 +5580,7 @@
         <v>1086</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I41" s="2">
         <v>4000</v>
@@ -5532,13 +5598,13 @@
         <v>0</v>
       </c>
       <c r="N41" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O41" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:16">
@@ -5546,7 +5612,7 @@
         <v>1036</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E42" s="2">
         <v>98</v>
@@ -5558,7 +5624,7 @@
         <v>1087</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I42" s="2">
         <v>4000</v>
@@ -5576,13 +5642,13 @@
         <v>0</v>
       </c>
       <c r="N42" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O42" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:16">
@@ -5590,7 +5656,7 @@
         <v>1037</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E43" s="2">
         <v>98</v>
@@ -5602,7 +5668,7 @@
         <v>1088</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I43" s="2">
         <v>4000</v>
@@ -5620,13 +5686,13 @@
         <v>0</v>
       </c>
       <c r="N43" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O43" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:16">
@@ -5634,7 +5700,7 @@
         <v>1038</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E44" s="2">
         <v>98</v>
@@ -5646,7 +5712,7 @@
         <v>1089</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I44" s="2">
         <v>4000</v>
@@ -5664,13 +5730,13 @@
         <v>0</v>
       </c>
       <c r="N44" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O44" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:16">
@@ -5678,7 +5744,7 @@
         <v>1039</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E45" s="2">
         <v>98</v>
@@ -5690,7 +5756,7 @@
         <v>1090</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I45" s="2">
         <v>4000</v>
@@ -5708,13 +5774,13 @@
         <v>0</v>
       </c>
       <c r="N45" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O45" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:16">
@@ -5722,7 +5788,7 @@
         <v>1040</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E46" s="2">
         <v>98</v>
@@ -5734,7 +5800,7 @@
         <v>1091</v>
       </c>
       <c r="H46" s="20" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I46" s="2">
         <v>4000</v>
@@ -5752,13 +5818,13 @@
         <v>0</v>
       </c>
       <c r="N46" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O46" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:16">
@@ -5766,7 +5832,7 @@
         <v>1041</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E47" s="2">
         <v>98</v>
@@ -5778,7 +5844,7 @@
         <v>1092</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I47" s="2">
         <v>4000</v>
@@ -5796,13 +5862,13 @@
         <v>0</v>
       </c>
       <c r="N47" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O47" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:16">
@@ -5810,7 +5876,7 @@
         <v>1042</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E48" s="2">
         <v>98</v>
@@ -5822,7 +5888,7 @@
         <v>1093</v>
       </c>
       <c r="H48" s="20" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I48" s="2">
         <v>4000</v>
@@ -5840,13 +5906,13 @@
         <v>0</v>
       </c>
       <c r="N48" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O48" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:16">
@@ -5854,7 +5920,7 @@
         <v>1043</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E49" s="2">
         <v>98</v>
@@ -5866,7 +5932,7 @@
         <v>1094</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I49" s="2">
         <v>4000</v>
@@ -5884,13 +5950,13 @@
         <v>0</v>
       </c>
       <c r="N49" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O49" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:16">
@@ -5898,7 +5964,7 @@
         <v>1044</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E50" s="2">
         <v>98</v>
@@ -5910,7 +5976,7 @@
         <v>1095</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I50" s="2">
         <v>4000</v>
@@ -5928,13 +5994,13 @@
         <v>0</v>
       </c>
       <c r="N50" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O50" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:16">
@@ -5942,7 +6008,7 @@
         <v>1045</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E51" s="2">
         <v>98</v>
@@ -5954,7 +6020,7 @@
         <v>1096</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I51" s="2">
         <v>4000</v>
@@ -5972,13 +6038,13 @@
         <v>0</v>
       </c>
       <c r="N51" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O51" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:16">
@@ -5986,7 +6052,7 @@
         <v>1046</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E52" s="2">
         <v>98</v>
@@ -5998,7 +6064,7 @@
         <v>1097</v>
       </c>
       <c r="H52" s="20" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I52" s="2">
         <v>4000</v>
@@ -6016,13 +6082,13 @@
         <v>0</v>
       </c>
       <c r="N52" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O52" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:16">
@@ -6030,7 +6096,7 @@
         <v>1047</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E53" s="2">
         <v>98</v>
@@ -6042,7 +6108,7 @@
         <v>1098</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I53" s="2">
         <v>4000</v>
@@ -6060,13 +6126,13 @@
         <v>0</v>
       </c>
       <c r="N53" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O53" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:16">
@@ -6074,7 +6140,7 @@
         <v>1048</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E54" s="2">
         <v>98</v>
@@ -6086,7 +6152,7 @@
         <v>1099</v>
       </c>
       <c r="H54" s="20" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I54" s="2">
         <v>4000</v>
@@ -6104,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="N54" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O54" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:16">
@@ -6118,7 +6184,7 @@
         <v>1049</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E55" s="2">
         <v>98</v>
@@ -6130,7 +6196,7 @@
         <v>1100</v>
       </c>
       <c r="H55" s="20" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I55" s="2">
         <v>4000</v>
@@ -6148,13 +6214,13 @@
         <v>0</v>
       </c>
       <c r="N55" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O55" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:16">
@@ -6162,7 +6228,7 @@
         <v>1050</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E56" s="2">
         <v>98</v>
@@ -6174,7 +6240,7 @@
         <v>1101</v>
       </c>
       <c r="H56" s="20" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I56" s="2">
         <v>4000</v>
@@ -6192,13 +6258,13 @@
         <v>0</v>
       </c>
       <c r="N56" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O56" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:16">
@@ -6206,7 +6272,7 @@
         <v>1051</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E57" s="2">
         <v>98</v>
@@ -6218,7 +6284,7 @@
         <v>1102</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I57" s="2">
         <v>4000</v>
@@ -6236,13 +6302,13 @@
         <v>0</v>
       </c>
       <c r="N57" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O57" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:16">
@@ -6250,7 +6316,7 @@
         <v>1052</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E58" s="2">
         <v>98</v>
@@ -6262,7 +6328,7 @@
         <v>1103</v>
       </c>
       <c r="H58" s="20" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I58" s="2">
         <v>4000</v>
@@ -6280,13 +6346,13 @@
         <v>0</v>
       </c>
       <c r="N58" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O58" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:16">
@@ -6294,7 +6360,7 @@
         <v>1053</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E59" s="2">
         <v>98</v>
@@ -6306,7 +6372,7 @@
         <v>1104</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I59" s="2">
         <v>4000</v>
@@ -6324,13 +6390,13 @@
         <v>0</v>
       </c>
       <c r="N59" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O59" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" s="12" customFormat="1" customHeight="1" spans="3:16">
@@ -6338,7 +6404,7 @@
         <v>1054</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E60" s="12">
         <v>98</v>
@@ -6350,7 +6416,7 @@
         <v>1105</v>
       </c>
       <c r="H60" s="21" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I60" s="12">
         <v>20000</v>
@@ -6368,13 +6434,13 @@
         <v>0</v>
       </c>
       <c r="N60" s="22" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O60" s="22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P60" s="12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6382,7 +6448,7 @@
         <v>1055</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E61" s="2">
         <v>98</v>
@@ -6394,7 +6460,7 @@
         <v>1106</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I61" s="2">
         <v>20000</v>
@@ -6412,13 +6478,13 @@
         <v>0</v>
       </c>
       <c r="N61" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O61" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6426,7 +6492,7 @@
         <v>1056</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E62" s="2">
         <v>98</v>
@@ -6438,7 +6504,7 @@
         <v>1107</v>
       </c>
       <c r="H62" s="20" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I62" s="2">
         <v>20000</v>
@@ -6456,13 +6522,13 @@
         <v>0</v>
       </c>
       <c r="N62" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O62" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6470,7 +6536,7 @@
         <v>1057</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E63" s="2">
         <v>98</v>
@@ -6482,7 +6548,7 @@
         <v>1108</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I63" s="2">
         <v>20000</v>
@@ -6500,13 +6566,13 @@
         <v>0</v>
       </c>
       <c r="N63" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O63" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:16">
@@ -6514,7 +6580,7 @@
         <v>1058</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E64" s="2">
         <v>98</v>
@@ -6526,7 +6592,7 @@
         <v>1109</v>
       </c>
       <c r="H64" s="20" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I64" s="2">
         <v>20000</v>
@@ -6544,13 +6610,13 @@
         <v>0</v>
       </c>
       <c r="N64" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O64" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6558,7 +6624,7 @@
         <v>1059</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E65" s="2">
         <v>98</v>
@@ -6570,7 +6636,7 @@
         <v>1110</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I65" s="2">
         <v>20000</v>
@@ -6588,13 +6654,13 @@
         <v>0</v>
       </c>
       <c r="N65" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O65" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6602,7 +6668,7 @@
         <v>1060</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E66" s="2">
         <v>98</v>
@@ -6614,7 +6680,7 @@
         <v>1111</v>
       </c>
       <c r="H66" s="20" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I66" s="2">
         <v>20000</v>
@@ -6632,13 +6698,13 @@
         <v>0</v>
       </c>
       <c r="N66" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O66" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6646,7 +6712,7 @@
         <v>1061</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E67" s="2">
         <v>98</v>
@@ -6658,7 +6724,7 @@
         <v>1112</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I67" s="2">
         <v>20000</v>
@@ -6676,13 +6742,13 @@
         <v>0</v>
       </c>
       <c r="N67" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O67" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -6690,7 +6756,7 @@
         <v>1062</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E68" s="2">
         <v>98</v>
@@ -6702,7 +6768,7 @@
         <v>1113</v>
       </c>
       <c r="H68" s="20" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="I68" s="2">
         <v>20000</v>
@@ -6720,13 +6786,13 @@
         <v>0</v>
       </c>
       <c r="N68" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O68" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:16">
@@ -6734,7 +6800,7 @@
         <v>1063</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E69" s="2">
         <v>98</v>
@@ -6746,7 +6812,7 @@
         <v>1114</v>
       </c>
       <c r="H69" s="20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I69" s="2">
         <v>20000</v>
@@ -6764,13 +6830,13 @@
         <v>0</v>
       </c>
       <c r="N69" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O69" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:16">
@@ -6778,7 +6844,7 @@
         <v>1064</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E70" s="2">
         <v>98</v>
@@ -6790,7 +6856,7 @@
         <v>1115</v>
       </c>
       <c r="H70" s="20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I70" s="2">
         <v>20000</v>
@@ -6808,13 +6874,13 @@
         <v>0</v>
       </c>
       <c r="N70" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O70" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:16">
@@ -6822,7 +6888,7 @@
         <v>1065</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E71" s="2">
         <v>98</v>
@@ -6834,7 +6900,7 @@
         <v>1116</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I71" s="2">
         <v>20000</v>
@@ -6852,13 +6918,13 @@
         <v>0</v>
       </c>
       <c r="N71" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O71" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:16">
@@ -6866,7 +6932,7 @@
         <v>1066</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E72" s="2">
         <v>98</v>
@@ -6878,7 +6944,7 @@
         <v>1117</v>
       </c>
       <c r="H72" s="20" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="I72" s="2">
         <v>20000</v>
@@ -6896,13 +6962,13 @@
         <v>0</v>
       </c>
       <c r="N72" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O72" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:16">
@@ -6910,7 +6976,7 @@
         <v>1067</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E73" s="2">
         <v>98</v>
@@ -6922,7 +6988,7 @@
         <v>1118</v>
       </c>
       <c r="H73" s="20" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I73" s="2">
         <v>20000</v>
@@ -6940,13 +7006,13 @@
         <v>0</v>
       </c>
       <c r="N73" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O73" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:16">
@@ -6954,7 +7020,7 @@
         <v>1068</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E74" s="2">
         <v>98</v>
@@ -6966,7 +7032,7 @@
         <v>1119</v>
       </c>
       <c r="H74" s="20" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I74" s="2">
         <v>20000</v>
@@ -6984,13 +7050,13 @@
         <v>0</v>
       </c>
       <c r="N74" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O74" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:16">
@@ -6998,7 +7064,7 @@
         <v>1069</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E75" s="2">
         <v>98</v>
@@ -7010,7 +7076,7 @@
         <v>1120</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I75" s="2">
         <v>20000</v>
@@ -7028,13 +7094,13 @@
         <v>0</v>
       </c>
       <c r="N75" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O75" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:16">
@@ -7042,7 +7108,7 @@
         <v>1070</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E76" s="2">
         <v>98</v>
@@ -7054,7 +7120,7 @@
         <v>1121</v>
       </c>
       <c r="H76" s="20" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I76" s="2">
         <v>20000</v>
@@ -7072,13 +7138,13 @@
         <v>0</v>
       </c>
       <c r="N76" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O76" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:16">
@@ -7086,7 +7152,7 @@
         <v>1071</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E77" s="2">
         <v>98</v>
@@ -7098,7 +7164,7 @@
         <v>1122</v>
       </c>
       <c r="H77" s="20" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I77" s="2">
         <v>20000</v>
@@ -7116,13 +7182,13 @@
         <v>0</v>
       </c>
       <c r="N77" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O77" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:16">
@@ -7130,7 +7196,7 @@
         <v>1072</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E78" s="2">
         <v>98</v>
@@ -7142,7 +7208,7 @@
         <v>1123</v>
       </c>
       <c r="H78" s="20" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I78" s="2">
         <v>20000</v>
@@ -7160,13 +7226,13 @@
         <v>0</v>
       </c>
       <c r="N78" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O78" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:16">
@@ -7174,7 +7240,7 @@
         <v>1073</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E79" s="2">
         <v>98</v>
@@ -7186,7 +7252,7 @@
         <v>1124</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I79" s="2">
         <v>20000</v>
@@ -7204,13 +7270,13 @@
         <v>0</v>
       </c>
       <c r="N79" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O79" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:16">
@@ -7218,7 +7284,7 @@
         <v>1074</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E80" s="2">
         <v>98</v>
@@ -7230,7 +7296,7 @@
         <v>1125</v>
       </c>
       <c r="H80" s="20" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I80" s="2">
         <v>20000</v>
@@ -7248,13 +7314,13 @@
         <v>0</v>
       </c>
       <c r="N80" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O80" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:16">
@@ -7262,7 +7328,7 @@
         <v>1075</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E81" s="2">
         <v>98</v>
@@ -7274,7 +7340,7 @@
         <v>1126</v>
       </c>
       <c r="H81" s="20" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I81" s="2">
         <v>20000</v>
@@ -7292,13 +7358,13 @@
         <v>0</v>
       </c>
       <c r="N81" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O81" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:16">
@@ -7306,7 +7372,7 @@
         <v>1076</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E82" s="2">
         <v>98</v>
@@ -7318,7 +7384,7 @@
         <v>1127</v>
       </c>
       <c r="H82" s="20" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I82" s="2">
         <v>20000</v>
@@ -7336,13 +7402,13 @@
         <v>0</v>
       </c>
       <c r="N82" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O82" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:16">
@@ -7350,7 +7416,7 @@
         <v>1077</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E83" s="2">
         <v>98</v>
@@ -7362,7 +7428,7 @@
         <v>1128</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I83" s="2">
         <v>20000</v>
@@ -7380,13 +7446,13 @@
         <v>0</v>
       </c>
       <c r="N83" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O83" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:16">
@@ -7394,7 +7460,7 @@
         <v>1078</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E84" s="2">
         <v>98</v>
@@ -7406,7 +7472,7 @@
         <v>1129</v>
       </c>
       <c r="H84" s="20" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I84" s="2">
         <v>20000</v>
@@ -7424,13 +7490,13 @@
         <v>0</v>
       </c>
       <c r="N84" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O84" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:16">
@@ -7438,7 +7504,7 @@
         <v>1079</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E85" s="2">
         <v>98</v>
@@ -7450,7 +7516,7 @@
         <v>1130</v>
       </c>
       <c r="H85" s="20" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I85" s="2">
         <v>20000</v>
@@ -7468,13 +7534,13 @@
         <v>0</v>
       </c>
       <c r="N85" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O85" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:16">
@@ -7482,7 +7548,7 @@
         <v>1080</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E86" s="2">
         <v>98</v>
@@ -7494,7 +7560,7 @@
         <v>1131</v>
       </c>
       <c r="H86" s="20" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I86" s="2">
         <v>20000</v>
@@ -7512,13 +7578,13 @@
         <v>0</v>
       </c>
       <c r="N86" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O86" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:16">
@@ -7526,7 +7592,7 @@
         <v>1081</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E87" s="2">
         <v>98</v>
@@ -7538,7 +7604,7 @@
         <v>1132</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I87" s="2">
         <v>20000</v>
@@ -7556,13 +7622,13 @@
         <v>0</v>
       </c>
       <c r="N87" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O87" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:16">
@@ -7570,7 +7636,7 @@
         <v>1082</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E88" s="2">
         <v>98</v>
@@ -7582,7 +7648,7 @@
         <v>1133</v>
       </c>
       <c r="H88" s="20" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I88" s="2">
         <v>20000</v>
@@ -7600,13 +7666,13 @@
         <v>0</v>
       </c>
       <c r="N88" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O88" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P88" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:16">
@@ -7614,7 +7680,7 @@
         <v>1083</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E89" s="2">
         <v>98</v>
@@ -7626,7 +7692,7 @@
         <v>1134</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I89" s="2">
         <v>20000</v>
@@ -7644,13 +7710,13 @@
         <v>0</v>
       </c>
       <c r="N89" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O89" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P89" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:16">
@@ -7658,7 +7724,7 @@
         <v>1084</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E90" s="2">
         <v>98</v>
@@ -7670,7 +7736,7 @@
         <v>1135</v>
       </c>
       <c r="H90" s="20" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I90" s="2">
         <v>20000</v>
@@ -7688,13 +7754,13 @@
         <v>0</v>
       </c>
       <c r="N90" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O90" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P90" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:16">
@@ -7702,7 +7768,7 @@
         <v>1085</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E91" s="2">
         <v>98</v>
@@ -7714,7 +7780,7 @@
         <v>1136</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I91" s="2">
         <v>20000</v>
@@ -7732,13 +7798,13 @@
         <v>0</v>
       </c>
       <c r="N91" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O91" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P91" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:16">
@@ -7746,7 +7812,7 @@
         <v>1086</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E92" s="2">
         <v>98</v>
@@ -7758,7 +7824,7 @@
         <v>1137</v>
       </c>
       <c r="H92" s="20" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="I92" s="2">
         <v>20000</v>
@@ -7776,13 +7842,13 @@
         <v>0</v>
       </c>
       <c r="N92" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O92" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P92" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:16">
@@ -7790,7 +7856,7 @@
         <v>1087</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E93" s="2">
         <v>98</v>
@@ -7802,7 +7868,7 @@
         <v>1138</v>
       </c>
       <c r="H93" s="20" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I93" s="2">
         <v>20000</v>
@@ -7820,13 +7886,13 @@
         <v>0</v>
       </c>
       <c r="N93" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O93" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P93" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:16">
@@ -7834,7 +7900,7 @@
         <v>1088</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E94" s="2">
         <v>98</v>
@@ -7846,7 +7912,7 @@
         <v>1139</v>
       </c>
       <c r="H94" s="20" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I94" s="2">
         <v>20000</v>
@@ -7864,13 +7930,13 @@
         <v>0</v>
       </c>
       <c r="N94" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O94" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P94" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -8063,7 +8129,7 @@
         <v>2000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -8075,7 +8141,7 @@
         <v>1070</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I6" s="2">
         <v>120000</v>
@@ -8096,10 +8162,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P6" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8107,7 +8173,7 @@
         <v>2001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -8119,7 +8185,7 @@
         <v>1071</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I7" s="2">
         <v>120000</v>
@@ -8140,10 +8206,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P7" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8151,7 +8217,7 @@
         <v>2002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -8163,7 +8229,7 @@
         <v>1072</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I8" s="2">
         <v>120000</v>
@@ -8184,10 +8250,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P8" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8195,7 +8261,7 @@
         <v>2003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -8207,7 +8273,7 @@
         <v>1073</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I9" s="2">
         <v>120000</v>
@@ -8228,10 +8294,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P9" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8239,7 +8305,7 @@
         <v>2004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -8251,7 +8317,7 @@
         <v>1074</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I10" s="2">
         <v>120000</v>
@@ -8272,10 +8338,10 @@
         <v>0</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P10" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8283,7 +8349,7 @@
         <v>2005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -8295,7 +8361,7 @@
         <v>1104</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I11" s="2">
         <v>20000</v>
@@ -8316,10 +8382,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P11" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
@@ -8341,7 +8407,7 @@
         <v>2006</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -8353,7 +8419,7 @@
         <v>1105</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I14" s="2">
         <v>360000</v>
@@ -8374,10 +8440,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P14" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8385,7 +8451,7 @@
         <v>2007</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -8397,7 +8463,7 @@
         <v>1106</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I15" s="2">
         <v>360000</v>
@@ -8418,10 +8484,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P15" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8429,7 +8495,7 @@
         <v>2008</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -8441,7 +8507,7 @@
         <v>1107</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I16" s="2">
         <v>360000</v>
@@ -8462,10 +8528,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8473,7 +8539,7 @@
         <v>2009</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -8485,7 +8551,7 @@
         <v>1108</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="I17" s="2">
         <v>360000</v>
@@ -8506,10 +8572,10 @@
         <v>0</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P17" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8517,7 +8583,7 @@
         <v>2010</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -8529,7 +8595,7 @@
         <v>1139</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I18" s="2">
         <v>360000</v>
@@ -8550,10 +8616,10 @@
         <v>0</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P18" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8561,7 +8627,7 @@
         <v>2011</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -8573,7 +8639,7 @@
         <v>1139</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -8594,10 +8660,10 @@
         <v>0</v>
       </c>
       <c r="O19" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P19" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="308">
   <si>
     <t>_id</t>
   </si>
@@ -589,81 +589,54 @@
     <t>1008</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
     <t>触龙之心</t>
   </si>
   <si>
     <t>1400000</t>
   </si>
   <si>
-    <t>生命基础</t>
-  </si>
-  <si>
     <t>白猪之心</t>
   </si>
   <si>
     <t>1400001</t>
   </si>
   <si>
-    <t>生命比例</t>
-  </si>
-  <si>
     <t>猪王之心</t>
   </si>
   <si>
     <t>1400002</t>
   </si>
   <si>
-    <t>生命倍率</t>
-  </si>
-  <si>
     <t>蝎王宝甲</t>
   </si>
   <si>
     <t>1400003</t>
   </si>
   <si>
-    <t>防御基础</t>
-  </si>
-  <si>
     <t>沃玛宝甲</t>
   </si>
   <si>
     <t>1400004</t>
   </si>
   <si>
-    <t>防御比例</t>
-  </si>
-  <si>
     <t>沃玛号角</t>
   </si>
   <si>
     <t>1400005</t>
   </si>
   <si>
-    <t>物攻基础</t>
-  </si>
-  <si>
     <t>祖玛头像</t>
   </si>
   <si>
     <t>1400006</t>
   </si>
   <si>
-    <t>魔法基础</t>
-  </si>
-  <si>
     <t>祖玛号角</t>
   </si>
   <si>
     <t>1400007</t>
   </si>
   <si>
-    <t>道术基础</t>
-  </si>
-  <si>
     <t>虹猪宝甲</t>
   </si>
   <si>
@@ -694,27 +667,18 @@
     <t>1400012</t>
   </si>
   <si>
-    <t>物伤</t>
-  </si>
-  <si>
     <t>牛魔权杖</t>
   </si>
   <si>
     <t>1400013</t>
   </si>
   <si>
-    <t>法伤</t>
-  </si>
-  <si>
     <t>金刚战锤</t>
   </si>
   <si>
     <t>1400014</t>
   </si>
   <si>
-    <t>道伤</t>
-  </si>
-  <si>
     <t>巨人之心</t>
   </si>
   <si>
@@ -733,36 +697,24 @@
     <t>1400017</t>
   </si>
   <si>
-    <t>减伤倍率</t>
-  </si>
-  <si>
     <t>龙神利爪</t>
   </si>
   <si>
     <t>1400018</t>
   </si>
   <si>
-    <t>物攻倍率</t>
-  </si>
-  <si>
     <t>梦魇鸡爪</t>
   </si>
   <si>
     <t>1400019</t>
   </si>
   <si>
-    <t>法术倍率</t>
-  </si>
-  <si>
     <t>梦魇鹿茸</t>
   </si>
   <si>
     <t>1400020</t>
   </si>
   <si>
-    <t>道术倍率</t>
-  </si>
-  <si>
     <t>梦魇草帽</t>
   </si>
   <si>
@@ -775,18 +727,12 @@
     <t>1400022</t>
   </si>
   <si>
-    <t>防御倍率</t>
-  </si>
-  <si>
     <t>梦魇花朵</t>
   </si>
   <si>
     <t>1400023</t>
   </si>
   <si>
-    <t>攻击倍率</t>
-  </si>
-  <si>
     <t>梦魇冰晶</t>
   </si>
   <si>
@@ -823,16 +769,10 @@
     <t>1400029</t>
   </si>
   <si>
-    <t>伤害增加</t>
-  </si>
-  <si>
     <t>梦魇虫皮</t>
   </si>
   <si>
     <t>1400030</t>
-  </si>
-  <si>
-    <t>攻击比例</t>
   </si>
   <si>
     <t>梦魇鹰羽</t>
@@ -3886,7 +3826,7 @@
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C2" s="4"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
@@ -3896,9 +3836,6 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
-      <c r="P2" s="1" t="s">
-        <v>110</v>
-      </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C3" s="5" t="s">
@@ -4023,12 +3960,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:16">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C6" s="2">
         <v>1000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -4040,7 +3977,7 @@
         <v>1051</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I6" s="2">
         <v>40000</v>
@@ -4063,16 +4000,13 @@
       <c r="O6" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C7" s="2">
         <v>1001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -4084,7 +4018,7 @@
         <v>1052</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I7" s="2">
         <v>40000</v>
@@ -4107,16 +4041,13 @@
       <c r="O7" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C8" s="2">
         <v>1002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -4128,7 +4059,7 @@
         <v>1053</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I8" s="2">
         <v>40000</v>
@@ -4151,16 +4082,13 @@
       <c r="O8" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C9" s="2">
         <v>1003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -4172,7 +4100,7 @@
         <v>1054</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I9" s="2">
         <v>40000</v>
@@ -4195,16 +4123,13 @@
       <c r="O9" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C10" s="2">
         <v>1004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -4216,7 +4141,7 @@
         <v>1055</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="I10" s="2">
         <v>40000</v>
@@ -4239,16 +4164,13 @@
       <c r="O10" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P10" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C11" s="2">
         <v>1005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -4260,7 +4182,7 @@
         <v>1056</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="I11" s="2">
         <v>40000</v>
@@ -4283,16 +4205,13 @@
       <c r="O11" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P11" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C12" s="2">
         <v>1006</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
@@ -4304,7 +4223,7 @@
         <v>1057</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="I12" s="2">
         <v>40000</v>
@@ -4327,16 +4246,13 @@
       <c r="O12" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P12" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C13" s="2">
         <v>1007</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
@@ -4348,7 +4264,7 @@
         <v>1058</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I13" s="2">
         <v>40000</v>
@@ -4371,16 +4287,13 @@
       <c r="O13" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C14" s="2">
         <v>1008</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -4392,7 +4305,7 @@
         <v>1059</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="I14" s="2">
         <v>40000</v>
@@ -4415,16 +4328,13 @@
       <c r="O14" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C15" s="2">
         <v>1009</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -4436,7 +4346,7 @@
         <v>1060</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="I15" s="2">
         <v>40000</v>
@@ -4459,16 +4369,13 @@
       <c r="O15" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P15" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C16" s="2">
         <v>1010</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -4480,7 +4387,7 @@
         <v>1061</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="I16" s="2">
         <v>40000</v>
@@ -4503,16 +4410,13 @@
       <c r="O16" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P16" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C17" s="2">
         <v>1011</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -4524,7 +4428,7 @@
         <v>1062</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="I17" s="2">
         <v>40000</v>
@@ -4547,16 +4451,13 @@
       <c r="O17" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P17" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C18" s="2">
         <v>1012</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -4568,7 +4469,7 @@
         <v>1063</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="I18" s="2">
         <v>40000</v>
@@ -4591,16 +4492,13 @@
       <c r="O18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P18" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C19" s="2">
         <v>1013</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -4612,7 +4510,7 @@
         <v>1064</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -4635,16 +4533,13 @@
       <c r="O19" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P19" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C20" s="2">
         <v>1014</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E20" s="2">
         <v>98</v>
@@ -4656,7 +4551,7 @@
         <v>1065</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="I20" s="2">
         <v>40000</v>
@@ -4679,16 +4574,13 @@
       <c r="O20" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P20" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C21" s="2">
         <v>1015</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -4700,7 +4592,7 @@
         <v>1066</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I21" s="2">
         <v>40000</v>
@@ -4723,16 +4615,13 @@
       <c r="O21" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P21" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C22" s="2">
         <v>1016</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -4744,7 +4633,7 @@
         <v>1067</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I22" s="2">
         <v>40000</v>
@@ -4767,16 +4656,13 @@
       <c r="O22" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P22" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C23" s="2">
         <v>1017</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -4788,7 +4674,7 @@
         <v>1068</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I23" s="2">
         <v>40000</v>
@@ -4811,16 +4697,13 @@
       <c r="O23" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P23" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C24" s="2">
         <v>1018</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -4832,7 +4715,7 @@
         <v>1069</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="I24" s="2">
         <v>40000</v>
@@ -4855,16 +4738,13 @@
       <c r="O24" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P24" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C25" s="2">
         <v>1019</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -4876,7 +4756,7 @@
         <v>1070</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="I25" s="2">
         <v>40000</v>
@@ -4899,16 +4779,13 @@
       <c r="O25" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P25" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C26" s="2">
         <v>1020</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -4920,7 +4797,7 @@
         <v>1071</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="I26" s="2">
         <v>40000</v>
@@ -4943,16 +4820,13 @@
       <c r="O26" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P26" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C27" s="2">
         <v>1021</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -4964,7 +4838,7 @@
         <v>1072</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>
@@ -4987,16 +4861,13 @@
       <c r="O27" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P27" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C28" s="2">
         <v>1022</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="E28" s="2">
         <v>98</v>
@@ -5008,7 +4879,7 @@
         <v>1073</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="I28" s="2">
         <v>40000</v>
@@ -5030,9 +4901,6 @@
       </c>
       <c r="O28" s="18" t="s">
         <v>33</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:16">
@@ -5040,7 +4908,7 @@
         <v>1023</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -5052,7 +4920,7 @@
         <v>1074</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="I29" s="2">
         <v>40000</v>
@@ -5075,16 +4943,14 @@
       <c r="O29" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P29" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P29" s="2"/>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C30" s="2">
         <v>1024</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="E30" s="2">
         <v>98</v>
@@ -5096,7 +4962,7 @@
         <v>1075</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="I30" s="2">
         <v>4000</v>
@@ -5119,16 +4985,13 @@
       <c r="O30" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P30" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C31" s="2">
         <v>1025</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="E31" s="2">
         <v>98</v>
@@ -5140,7 +5003,7 @@
         <v>1076</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="I31" s="2">
         <v>4000</v>
@@ -5163,16 +5026,13 @@
       <c r="O31" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P31" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C32" s="2">
         <v>1026</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="E32" s="2">
         <v>98</v>
@@ -5184,7 +5044,7 @@
         <v>1077</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="I32" s="2">
         <v>4000</v>
@@ -5207,16 +5067,13 @@
       <c r="O32" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P32" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C33" s="2">
         <v>1027</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
@@ -5228,7 +5085,7 @@
         <v>1078</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="I33" s="2">
         <v>4000</v>
@@ -5250,9 +5107,6 @@
       </c>
       <c r="O33" s="18" t="s">
         <v>33</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:16">
@@ -5260,7 +5114,7 @@
         <v>1028</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="E34" s="2">
         <v>98</v>
@@ -5272,7 +5126,7 @@
         <v>1079</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="I34" s="2">
         <v>4000</v>
@@ -5295,16 +5149,14 @@
       <c r="O34" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P34" s="2" t="s">
-        <v>125</v>
-      </c>
+      <c r="P34" s="2"/>
     </row>
     <row r="35" customHeight="1" spans="3:16">
       <c r="C35" s="2">
         <v>1029</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
@@ -5316,7 +5168,7 @@
         <v>1080</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="I35" s="2">
         <v>4000</v>
@@ -5339,16 +5191,14 @@
       <c r="O35" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P35" s="2" t="s">
-        <v>188</v>
-      </c>
+      <c r="P35" s="2"/>
     </row>
     <row r="36" customHeight="1" spans="3:16">
       <c r="C36" s="2">
         <v>1030</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -5360,7 +5210,7 @@
         <v>1081</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="I36" s="2">
         <v>4000</v>
@@ -5383,16 +5233,14 @@
       <c r="O36" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P36" s="2" t="s">
-        <v>191</v>
-      </c>
+      <c r="P36" s="2"/>
     </row>
     <row r="37" customHeight="1" spans="3:16">
       <c r="C37" s="2">
         <v>1031</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -5404,7 +5252,7 @@
         <v>1082</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="I37" s="2">
         <v>4000</v>
@@ -5427,16 +5275,14 @@
       <c r="O37" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P37" s="2" t="s">
-        <v>161</v>
-      </c>
+      <c r="P37" s="2"/>
     </row>
     <row r="38" customHeight="1" spans="3:16">
       <c r="C38" s="2">
         <v>1032</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="E38" s="2">
         <v>98</v>
@@ -5448,7 +5294,7 @@
         <v>1083</v>
       </c>
       <c r="H38" s="20" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="I38" s="2">
         <v>4000</v>
@@ -5471,16 +5317,14 @@
       <c r="O38" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>164</v>
-      </c>
+      <c r="P38" s="2"/>
     </row>
     <row r="39" customHeight="1" spans="3:16">
       <c r="C39" s="2">
         <v>1033</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="E39" s="2">
         <v>98</v>
@@ -5492,7 +5336,7 @@
         <v>1084</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="I39" s="2">
         <v>4000</v>
@@ -5515,16 +5359,14 @@
       <c r="O39" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P39" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P39" s="2"/>
     </row>
     <row r="40" customHeight="1" spans="3:16">
       <c r="C40" s="2">
         <v>1034</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="E40" s="2">
         <v>98</v>
@@ -5536,7 +5378,7 @@
         <v>1085</v>
       </c>
       <c r="H40" s="20" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="I40" s="2">
         <v>4000</v>
@@ -5559,16 +5401,14 @@
       <c r="O40" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P40" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P40" s="2"/>
     </row>
     <row r="41" customHeight="1" spans="3:16">
       <c r="C41" s="2">
         <v>1035</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="E41" s="2">
         <v>98</v>
@@ -5580,7 +5420,7 @@
         <v>1086</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="I41" s="2">
         <v>4000</v>
@@ -5603,16 +5443,14 @@
       <c r="O41" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P41" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P41" s="2"/>
     </row>
     <row r="42" customHeight="1" spans="3:16">
       <c r="C42" s="2">
         <v>1036</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="E42" s="2">
         <v>98</v>
@@ -5624,7 +5462,7 @@
         <v>1087</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="I42" s="2">
         <v>4000</v>
@@ -5647,16 +5485,14 @@
       <c r="O42" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P42" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P42" s="2"/>
     </row>
     <row r="43" customHeight="1" spans="3:16">
       <c r="C43" s="2">
         <v>1037</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="E43" s="2">
         <v>98</v>
@@ -5668,7 +5504,7 @@
         <v>1088</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="I43" s="2">
         <v>4000</v>
@@ -5691,16 +5527,14 @@
       <c r="O43" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P43" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P43" s="2"/>
     </row>
     <row r="44" customHeight="1" spans="3:16">
       <c r="C44" s="2">
         <v>1038</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="E44" s="2">
         <v>98</v>
@@ -5712,7 +5546,7 @@
         <v>1089</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="I44" s="2">
         <v>4000</v>
@@ -5735,16 +5569,14 @@
       <c r="O44" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P44" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P44" s="2"/>
     </row>
     <row r="45" customHeight="1" spans="3:16">
       <c r="C45" s="2">
         <v>1039</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E45" s="2">
         <v>98</v>
@@ -5756,7 +5588,7 @@
         <v>1090</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="I45" s="2">
         <v>4000</v>
@@ -5779,16 +5611,14 @@
       <c r="O45" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P45" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P45" s="2"/>
     </row>
     <row r="46" customHeight="1" spans="3:16">
       <c r="C46" s="2">
         <v>1040</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="E46" s="2">
         <v>98</v>
@@ -5800,7 +5630,7 @@
         <v>1091</v>
       </c>
       <c r="H46" s="20" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="I46" s="2">
         <v>4000</v>
@@ -5823,16 +5653,14 @@
       <c r="O46" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P46" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P46" s="2"/>
     </row>
     <row r="47" customHeight="1" spans="3:16">
       <c r="C47" s="2">
         <v>1041</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="E47" s="2">
         <v>98</v>
@@ -5844,7 +5672,7 @@
         <v>1092</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="I47" s="2">
         <v>4000</v>
@@ -5867,16 +5695,14 @@
       <c r="O47" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P47" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P47" s="2"/>
     </row>
     <row r="48" customHeight="1" spans="3:16">
       <c r="C48" s="2">
         <v>1042</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="E48" s="2">
         <v>98</v>
@@ -5888,7 +5714,7 @@
         <v>1093</v>
       </c>
       <c r="H48" s="20" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="I48" s="2">
         <v>4000</v>
@@ -5911,16 +5737,14 @@
       <c r="O48" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P48" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P48" s="2"/>
     </row>
     <row r="49" customHeight="1" spans="3:16">
       <c r="C49" s="2">
         <v>1043</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="E49" s="2">
         <v>98</v>
@@ -5932,7 +5756,7 @@
         <v>1094</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="I49" s="2">
         <v>4000</v>
@@ -5955,16 +5779,14 @@
       <c r="O49" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P49" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P49" s="2"/>
     </row>
     <row r="50" customHeight="1" spans="3:16">
       <c r="C50" s="2">
         <v>1044</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="E50" s="2">
         <v>98</v>
@@ -5976,7 +5798,7 @@
         <v>1095</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="I50" s="2">
         <v>4000</v>
@@ -5999,16 +5821,14 @@
       <c r="O50" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P50" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P50" s="2"/>
     </row>
     <row r="51" customHeight="1" spans="3:16">
       <c r="C51" s="2">
         <v>1045</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E51" s="2">
         <v>98</v>
@@ -6020,7 +5840,7 @@
         <v>1096</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="I51" s="2">
         <v>4000</v>
@@ -6043,16 +5863,14 @@
       <c r="O51" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P51" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P51" s="2"/>
     </row>
     <row r="52" customHeight="1" spans="3:16">
       <c r="C52" s="2">
         <v>1046</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="E52" s="2">
         <v>98</v>
@@ -6064,7 +5882,7 @@
         <v>1097</v>
       </c>
       <c r="H52" s="20" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="I52" s="2">
         <v>4000</v>
@@ -6087,16 +5905,14 @@
       <c r="O52" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P52" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P52" s="2"/>
     </row>
     <row r="53" customHeight="1" spans="3:16">
       <c r="C53" s="2">
         <v>1047</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="E53" s="2">
         <v>98</v>
@@ -6108,7 +5924,7 @@
         <v>1098</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="I53" s="2">
         <v>4000</v>
@@ -6131,16 +5947,14 @@
       <c r="O53" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P53" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P53" s="2"/>
     </row>
     <row r="54" customHeight="1" spans="3:16">
       <c r="C54" s="2">
         <v>1048</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="E54" s="2">
         <v>98</v>
@@ -6152,7 +5966,7 @@
         <v>1099</v>
       </c>
       <c r="H54" s="20" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="I54" s="2">
         <v>4000</v>
@@ -6175,16 +5989,14 @@
       <c r="O54" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P54" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P54" s="2"/>
     </row>
     <row r="55" customHeight="1" spans="3:16">
       <c r="C55" s="2">
         <v>1049</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="E55" s="2">
         <v>98</v>
@@ -6196,7 +6008,7 @@
         <v>1100</v>
       </c>
       <c r="H55" s="20" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="I55" s="2">
         <v>4000</v>
@@ -6219,16 +6031,14 @@
       <c r="O55" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P55" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P55" s="2"/>
     </row>
     <row r="56" customHeight="1" spans="3:16">
       <c r="C56" s="2">
         <v>1050</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="E56" s="2">
         <v>98</v>
@@ -6240,7 +6050,7 @@
         <v>1101</v>
       </c>
       <c r="H56" s="20" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="I56" s="2">
         <v>4000</v>
@@ -6263,16 +6073,14 @@
       <c r="O56" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P56" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P56" s="2"/>
     </row>
     <row r="57" customHeight="1" spans="3:16">
       <c r="C57" s="2">
         <v>1051</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="E57" s="2">
         <v>98</v>
@@ -6284,7 +6092,7 @@
         <v>1102</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="I57" s="2">
         <v>4000</v>
@@ -6307,16 +6115,14 @@
       <c r="O57" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P57" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P57" s="2"/>
     </row>
     <row r="58" customHeight="1" spans="3:16">
       <c r="C58" s="2">
         <v>1052</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="E58" s="2">
         <v>98</v>
@@ -6328,7 +6134,7 @@
         <v>1103</v>
       </c>
       <c r="H58" s="20" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="I58" s="2">
         <v>4000</v>
@@ -6351,16 +6157,14 @@
       <c r="O58" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P58" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P58" s="2"/>
     </row>
     <row r="59" customHeight="1" spans="3:16">
       <c r="C59" s="2">
         <v>1053</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="E59" s="2">
         <v>98</v>
@@ -6372,7 +6176,7 @@
         <v>1104</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="I59" s="2">
         <v>4000</v>
@@ -6395,16 +6199,14 @@
       <c r="O59" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P59" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="60" s="12" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P59" s="2"/>
+    </row>
+    <row r="60" s="12" customFormat="1" customHeight="1" spans="3:15">
       <c r="C60" s="12">
         <v>1054</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="E60" s="12">
         <v>98</v>
@@ -6416,7 +6218,7 @@
         <v>1105</v>
       </c>
       <c r="H60" s="21" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="I60" s="12">
         <v>20000</v>
@@ -6439,16 +6241,13 @@
       <c r="O60" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="P60" s="12" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C61" s="2">
         <v>1055</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="E61" s="2">
         <v>98</v>
@@ -6460,7 +6259,7 @@
         <v>1106</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="I61" s="2">
         <v>20000</v>
@@ -6483,16 +6282,13 @@
       <c r="O61" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P61" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C62" s="2">
         <v>1056</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="E62" s="2">
         <v>98</v>
@@ -6504,7 +6300,7 @@
         <v>1107</v>
       </c>
       <c r="H62" s="20" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="I62" s="2">
         <v>20000</v>
@@ -6527,16 +6323,13 @@
       <c r="O62" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P62" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C63" s="2">
         <v>1057</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="E63" s="2">
         <v>98</v>
@@ -6548,7 +6341,7 @@
         <v>1108</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="I63" s="2">
         <v>20000</v>
@@ -6570,9 +6363,6 @@
       </c>
       <c r="O63" s="18" t="s">
         <v>33</v>
-      </c>
-      <c r="P63" s="2" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:16">
@@ -6580,7 +6370,7 @@
         <v>1058</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="E64" s="2">
         <v>98</v>
@@ -6592,7 +6382,7 @@
         <v>1109</v>
       </c>
       <c r="H64" s="20" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="I64" s="2">
         <v>20000</v>
@@ -6615,16 +6405,14 @@
       <c r="O64" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P64" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P64" s="2"/>
+    </row>
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C65" s="2">
         <v>1059</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="E65" s="2">
         <v>98</v>
@@ -6636,7 +6424,7 @@
         <v>1110</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="I65" s="2">
         <v>20000</v>
@@ -6659,16 +6447,13 @@
       <c r="O65" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P65" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C66" s="2">
         <v>1060</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="E66" s="2">
         <v>98</v>
@@ -6680,7 +6465,7 @@
         <v>1111</v>
       </c>
       <c r="H66" s="20" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="I66" s="2">
         <v>20000</v>
@@ -6703,16 +6488,13 @@
       <c r="O66" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P66" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C67" s="2">
         <v>1061</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="E67" s="2">
         <v>98</v>
@@ -6724,7 +6506,7 @@
         <v>1112</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="I67" s="2">
         <v>20000</v>
@@ -6747,16 +6529,13 @@
       <c r="O67" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P67" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C68" s="2">
         <v>1062</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="E68" s="2">
         <v>98</v>
@@ -6768,7 +6547,7 @@
         <v>1113</v>
       </c>
       <c r="H68" s="20" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="I68" s="2">
         <v>20000</v>
@@ -6790,9 +6569,6 @@
       </c>
       <c r="O68" s="18" t="s">
         <v>33</v>
-      </c>
-      <c r="P68" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:16">
@@ -6800,7 +6576,7 @@
         <v>1063</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="E69" s="2">
         <v>98</v>
@@ -6812,7 +6588,7 @@
         <v>1114</v>
       </c>
       <c r="H69" s="20" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="I69" s="2">
         <v>20000</v>
@@ -6835,16 +6611,14 @@
       <c r="O69" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P69" s="2" t="s">
-        <v>125</v>
-      </c>
+      <c r="P69" s="2"/>
     </row>
     <row r="70" customHeight="1" spans="3:16">
       <c r="C70" s="2">
         <v>1064</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="E70" s="2">
         <v>98</v>
@@ -6856,7 +6630,7 @@
         <v>1115</v>
       </c>
       <c r="H70" s="20" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="I70" s="2">
         <v>20000</v>
@@ -6879,16 +6653,14 @@
       <c r="O70" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P70" s="2" t="s">
-        <v>188</v>
-      </c>
+      <c r="P70" s="2"/>
     </row>
     <row r="71" customHeight="1" spans="3:16">
       <c r="C71" s="2">
         <v>1065</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="E71" s="2">
         <v>98</v>
@@ -6900,7 +6672,7 @@
         <v>1116</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="I71" s="2">
         <v>20000</v>
@@ -6923,16 +6695,14 @@
       <c r="O71" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P71" s="2" t="s">
-        <v>191</v>
-      </c>
+      <c r="P71" s="2"/>
     </row>
     <row r="72" customHeight="1" spans="3:16">
       <c r="C72" s="2">
         <v>1066</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="E72" s="2">
         <v>98</v>
@@ -6944,7 +6714,7 @@
         <v>1117</v>
       </c>
       <c r="H72" s="20" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="I72" s="2">
         <v>20000</v>
@@ -6967,16 +6737,14 @@
       <c r="O72" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P72" s="2" t="s">
-        <v>161</v>
-      </c>
+      <c r="P72" s="2"/>
     </row>
     <row r="73" customHeight="1" spans="3:16">
       <c r="C73" s="2">
         <v>1067</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="E73" s="2">
         <v>98</v>
@@ -6988,7 +6756,7 @@
         <v>1118</v>
       </c>
       <c r="H73" s="20" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="I73" s="2">
         <v>20000</v>
@@ -7011,16 +6779,14 @@
       <c r="O73" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P73" s="2" t="s">
-        <v>164</v>
-      </c>
+      <c r="P73" s="2"/>
     </row>
     <row r="74" customHeight="1" spans="3:16">
       <c r="C74" s="2">
         <v>1068</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="E74" s="2">
         <v>98</v>
@@ -7032,7 +6798,7 @@
         <v>1119</v>
       </c>
       <c r="H74" s="20" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="I74" s="2">
         <v>20000</v>
@@ -7055,16 +6821,14 @@
       <c r="O74" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P74" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P74" s="2"/>
     </row>
     <row r="75" customHeight="1" spans="3:16">
       <c r="C75" s="2">
         <v>1069</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="E75" s="2">
         <v>98</v>
@@ -7076,7 +6840,7 @@
         <v>1120</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="I75" s="2">
         <v>20000</v>
@@ -7099,16 +6863,14 @@
       <c r="O75" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P75" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P75" s="2"/>
     </row>
     <row r="76" customHeight="1" spans="3:16">
       <c r="C76" s="2">
         <v>1070</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="E76" s="2">
         <v>98</v>
@@ -7120,7 +6882,7 @@
         <v>1121</v>
       </c>
       <c r="H76" s="20" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="I76" s="2">
         <v>20000</v>
@@ -7143,16 +6905,14 @@
       <c r="O76" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P76" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P76" s="2"/>
     </row>
     <row r="77" customHeight="1" spans="3:16">
       <c r="C77" s="2">
         <v>1071</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="E77" s="2">
         <v>98</v>
@@ -7164,7 +6924,7 @@
         <v>1122</v>
       </c>
       <c r="H77" s="20" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="I77" s="2">
         <v>20000</v>
@@ -7187,16 +6947,14 @@
       <c r="O77" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P77" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P77" s="2"/>
     </row>
     <row r="78" customHeight="1" spans="3:16">
       <c r="C78" s="2">
         <v>1072</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="E78" s="2">
         <v>98</v>
@@ -7208,7 +6966,7 @@
         <v>1123</v>
       </c>
       <c r="H78" s="20" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="I78" s="2">
         <v>20000</v>
@@ -7231,16 +6989,14 @@
       <c r="O78" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P78" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P78" s="2"/>
     </row>
     <row r="79" customHeight="1" spans="3:16">
       <c r="C79" s="2">
         <v>1073</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="E79" s="2">
         <v>98</v>
@@ -7252,7 +7008,7 @@
         <v>1124</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="I79" s="2">
         <v>20000</v>
@@ -7275,16 +7031,14 @@
       <c r="O79" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P79" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P79" s="2"/>
     </row>
     <row r="80" customHeight="1" spans="3:16">
       <c r="C80" s="2">
         <v>1074</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="E80" s="2">
         <v>98</v>
@@ -7296,7 +7050,7 @@
         <v>1125</v>
       </c>
       <c r="H80" s="20" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="I80" s="2">
         <v>20000</v>
@@ -7319,16 +7073,14 @@
       <c r="O80" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P80" s="2"/>
     </row>
     <row r="81" customHeight="1" spans="3:16">
       <c r="C81" s="2">
         <v>1075</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="E81" s="2">
         <v>98</v>
@@ -7340,7 +7092,7 @@
         <v>1126</v>
       </c>
       <c r="H81" s="20" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="I81" s="2">
         <v>20000</v>
@@ -7363,16 +7115,14 @@
       <c r="O81" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P81" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P81" s="2"/>
     </row>
     <row r="82" customHeight="1" spans="3:16">
       <c r="C82" s="2">
         <v>1076</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="E82" s="2">
         <v>98</v>
@@ -7384,7 +7134,7 @@
         <v>1127</v>
       </c>
       <c r="H82" s="20" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="I82" s="2">
         <v>20000</v>
@@ -7407,16 +7157,14 @@
       <c r="O82" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P82" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P82" s="2"/>
     </row>
     <row r="83" customHeight="1" spans="3:16">
       <c r="C83" s="2">
         <v>1077</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="E83" s="2">
         <v>98</v>
@@ -7428,7 +7176,7 @@
         <v>1128</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="I83" s="2">
         <v>20000</v>
@@ -7451,16 +7199,14 @@
       <c r="O83" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P83" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P83" s="2"/>
     </row>
     <row r="84" customHeight="1" spans="3:16">
       <c r="C84" s="2">
         <v>1078</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="E84" s="2">
         <v>98</v>
@@ -7472,7 +7218,7 @@
         <v>1129</v>
       </c>
       <c r="H84" s="20" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="I84" s="2">
         <v>20000</v>
@@ -7495,16 +7241,14 @@
       <c r="O84" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P84" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P84" s="2"/>
     </row>
     <row r="85" customHeight="1" spans="3:16">
       <c r="C85" s="2">
         <v>1079</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="E85" s="2">
         <v>98</v>
@@ -7516,7 +7260,7 @@
         <v>1130</v>
       </c>
       <c r="H85" s="20" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="I85" s="2">
         <v>20000</v>
@@ -7539,16 +7283,14 @@
       <c r="O85" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P85" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P85" s="2"/>
     </row>
     <row r="86" customHeight="1" spans="3:16">
       <c r="C86" s="2">
         <v>1080</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="E86" s="2">
         <v>98</v>
@@ -7560,7 +7302,7 @@
         <v>1131</v>
       </c>
       <c r="H86" s="20" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="I86" s="2">
         <v>20000</v>
@@ -7583,16 +7325,14 @@
       <c r="O86" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P86" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P86" s="2"/>
     </row>
     <row r="87" customHeight="1" spans="3:16">
       <c r="C87" s="2">
         <v>1081</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="E87" s="2">
         <v>98</v>
@@ -7604,7 +7344,7 @@
         <v>1132</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="I87" s="2">
         <v>20000</v>
@@ -7627,16 +7367,14 @@
       <c r="O87" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P87" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P87" s="2"/>
     </row>
     <row r="88" customHeight="1" spans="3:16">
       <c r="C88" s="2">
         <v>1082</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="E88" s="2">
         <v>98</v>
@@ -7648,7 +7386,7 @@
         <v>1133</v>
       </c>
       <c r="H88" s="20" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="I88" s="2">
         <v>20000</v>
@@ -7671,16 +7409,14 @@
       <c r="O88" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P88" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P88" s="2"/>
     </row>
     <row r="89" customHeight="1" spans="3:16">
       <c r="C89" s="2">
         <v>1083</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="E89" s="2">
         <v>98</v>
@@ -7692,7 +7428,7 @@
         <v>1134</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="I89" s="2">
         <v>20000</v>
@@ -7715,16 +7451,14 @@
       <c r="O89" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P89" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P89" s="2"/>
     </row>
     <row r="90" customHeight="1" spans="3:16">
       <c r="C90" s="2">
         <v>1084</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="E90" s="2">
         <v>98</v>
@@ -7736,7 +7470,7 @@
         <v>1135</v>
       </c>
       <c r="H90" s="20" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="I90" s="2">
         <v>20000</v>
@@ -7759,16 +7493,14 @@
       <c r="O90" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P90" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P90" s="2"/>
     </row>
     <row r="91" customHeight="1" spans="3:16">
       <c r="C91" s="2">
         <v>1085</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="E91" s="2">
         <v>98</v>
@@ -7780,7 +7512,7 @@
         <v>1136</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="I91" s="2">
         <v>20000</v>
@@ -7803,16 +7535,14 @@
       <c r="O91" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P91" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P91" s="2"/>
     </row>
     <row r="92" customHeight="1" spans="3:16">
       <c r="C92" s="2">
         <v>1086</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="E92" s="2">
         <v>98</v>
@@ -7824,7 +7554,7 @@
         <v>1137</v>
       </c>
       <c r="H92" s="20" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="I92" s="2">
         <v>20000</v>
@@ -7847,16 +7577,14 @@
       <c r="O92" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P92" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P92" s="2"/>
     </row>
     <row r="93" customHeight="1" spans="3:16">
       <c r="C93" s="2">
         <v>1087</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="E93" s="2">
         <v>98</v>
@@ -7868,7 +7596,7 @@
         <v>1138</v>
       </c>
       <c r="H93" s="20" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="I93" s="2">
         <v>20000</v>
@@ -7891,16 +7619,14 @@
       <c r="O93" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P93" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P93" s="2"/>
     </row>
     <row r="94" customHeight="1" spans="3:16">
       <c r="C94" s="2">
         <v>1088</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="E94" s="2">
         <v>98</v>
@@ -7912,7 +7638,7 @@
         <v>1139</v>
       </c>
       <c r="H94" s="20" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="I94" s="2">
         <v>20000</v>
@@ -7935,9 +7661,7 @@
       <c r="O94" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P94" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="P94" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -8129,7 +7853,7 @@
         <v>2000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -8141,7 +7865,7 @@
         <v>1070</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="I6" s="2">
         <v>120000</v>
@@ -8173,7 +7897,7 @@
         <v>2001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -8185,7 +7909,7 @@
         <v>1071</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="I7" s="2">
         <v>120000</v>
@@ -8217,7 +7941,7 @@
         <v>2002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -8229,7 +7953,7 @@
         <v>1072</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="I8" s="2">
         <v>120000</v>
@@ -8261,7 +7985,7 @@
         <v>2003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -8273,7 +7997,7 @@
         <v>1073</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="I9" s="2">
         <v>120000</v>
@@ -8305,7 +8029,7 @@
         <v>2004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -8317,7 +8041,7 @@
         <v>1074</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="I10" s="2">
         <v>120000</v>
@@ -8349,7 +8073,7 @@
         <v>2005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -8361,7 +8085,7 @@
         <v>1104</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="I11" s="2">
         <v>20000</v>
@@ -8407,7 +8131,7 @@
         <v>2006</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -8419,7 +8143,7 @@
         <v>1105</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="I14" s="2">
         <v>360000</v>
@@ -8451,7 +8175,7 @@
         <v>2007</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -8463,7 +8187,7 @@
         <v>1106</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="I15" s="2">
         <v>360000</v>
@@ -8495,7 +8219,7 @@
         <v>2008</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -8507,7 +8231,7 @@
         <v>1107</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="I16" s="2">
         <v>360000</v>
@@ -8539,7 +8263,7 @@
         <v>2009</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -8551,7 +8275,7 @@
         <v>1108</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="I17" s="2">
         <v>360000</v>
@@ -8583,7 +8307,7 @@
         <v>2010</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -8595,7 +8319,7 @@
         <v>1139</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="I18" s="2">
         <v>360000</v>
@@ -8627,7 +8351,7 @@
         <v>2011</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -8639,7 +8363,7 @@
         <v>1139</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="309">
   <si>
     <t>_id</t>
   </si>
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>万圣节</t>
+    <t>感恩节</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,16 +346,19 @@
     <t>50</t>
   </si>
   <si>
+    <t>2024-11-28</t>
+  </si>
+  <si>
+    <t>2024-12-01</t>
+  </si>
+  <si>
+    <t>平时部分掉落</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>2024-10-31</t>
-  </si>
-  <si>
-    <t>2024-11-04</t>
-  </si>
-  <si>
-    <t>平时部分掉落</t>
-  </si>
-  <si>
-    <t>150</t>
   </si>
   <si>
     <t>2025-10-21</t>
@@ -2472,10 +2475,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="P7" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" customFormat="1" customHeight="1" spans="3:16">
@@ -2499,7 +2502,7 @@
         <v>101</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -2511,13 +2514,13 @@
         <v>2000</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I9" s="11">
         <v>0</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K9" s="11">
         <v>0</v>
@@ -2532,10 +2535,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P9" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2543,7 +2546,7 @@
         <v>102</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -2555,13 +2558,13 @@
         <v>2000</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I10" s="11">
         <v>0</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K10" s="11">
         <v>0</v>
@@ -2576,10 +2579,10 @@
         <v>0</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P10" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2587,7 +2590,7 @@
         <v>103</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -2599,13 +2602,13 @@
         <v>2000</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I11" s="11">
         <v>0</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K11" s="11">
         <v>0</v>
@@ -2620,10 +2623,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P11" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2631,7 +2634,7 @@
         <v>104</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
@@ -2643,13 +2646,13 @@
         <v>2000</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I12" s="11">
         <v>0</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K12" s="11">
         <v>0</v>
@@ -2664,10 +2667,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P12" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2675,7 +2678,7 @@
         <v>105</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
@@ -2687,13 +2690,13 @@
         <v>2000</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I13" s="11">
         <v>0</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K13" s="11">
         <v>0</v>
@@ -2708,10 +2711,10 @@
         <v>0</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P13" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2719,7 +2722,7 @@
         <v>106</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -2731,13 +2734,13 @@
         <v>2000</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I14" s="11">
         <v>0</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K14" s="11">
         <v>0</v>
@@ -2752,10 +2755,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P14" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2763,7 +2766,7 @@
         <v>107</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -2775,13 +2778,13 @@
         <v>2000</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I15" s="11">
         <v>0</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K15" s="11">
         <v>0</v>
@@ -2796,10 +2799,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P15" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2807,7 +2810,7 @@
         <v>108</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -2819,13 +2822,13 @@
         <v>2000</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I16" s="11">
         <v>0</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K16" s="11">
         <v>0</v>
@@ -2840,10 +2843,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2851,7 +2854,7 @@
         <v>109</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -2863,13 +2866,13 @@
         <v>2000</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I17" s="11">
         <v>0</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K17" s="11">
         <v>0</v>
@@ -2884,10 +2887,10 @@
         <v>0</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P17" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2895,7 +2898,7 @@
         <v>110</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -2907,13 +2910,13 @@
         <v>2000</v>
       </c>
       <c r="H18" s="19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I18" s="11">
         <v>0</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K18" s="11">
         <v>0</v>
@@ -2928,10 +2931,10 @@
         <v>0</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P18" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2939,7 +2942,7 @@
         <v>111</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -2951,13 +2954,13 @@
         <v>2000</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I19" s="11">
         <v>0</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K19" s="11">
         <v>0</v>
@@ -2972,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="O19" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P19" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -2983,7 +2986,7 @@
         <v>112</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E20" s="2">
         <v>98</v>
@@ -2995,13 +2998,13 @@
         <v>2000</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I20" s="11">
         <v>0</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K20" s="11">
         <v>0</v>
@@ -3016,10 +3019,10 @@
         <v>0</v>
       </c>
       <c r="O20" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P20" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1"/>
@@ -3028,7 +3031,7 @@
         <v>201</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E22" s="2">
         <v>100</v>
@@ -3040,7 +3043,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I22" s="11">
         <v>0</v>
@@ -3061,10 +3064,10 @@
         <v>1</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P22" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3072,7 +3075,7 @@
         <v>202</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E23" s="2">
         <v>100</v>
@@ -3084,7 +3087,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I23" s="11">
         <v>0</v>
@@ -3105,10 +3108,10 @@
         <v>1</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P23" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3116,7 +3119,7 @@
         <v>203</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2">
         <v>100</v>
@@ -3128,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I24" s="11">
         <v>0</v>
@@ -3149,10 +3152,10 @@
         <v>1</v>
       </c>
       <c r="O24" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P24" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="8:16">
@@ -3171,7 +3174,7 @@
         <v>301</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -3183,13 +3186,13 @@
         <v>2000</v>
       </c>
       <c r="H26" s="19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I26" s="2">
         <v>0</v>
       </c>
       <c r="J26" s="19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K26" s="11">
         <v>0</v>
@@ -3204,10 +3207,10 @@
         <v>0</v>
       </c>
       <c r="O26" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P26" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3215,7 +3218,7 @@
         <v>302</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -3227,13 +3230,13 @@
         <v>2000</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I27" s="2">
         <v>0</v>
       </c>
       <c r="J27" s="19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K27" s="11">
         <v>0</v>
@@ -3248,10 +3251,10 @@
         <v>0</v>
       </c>
       <c r="O27" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P27" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1"/>
@@ -3260,7 +3263,7 @@
         <v>801</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -3272,13 +3275,13 @@
         <v>2000</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J29" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K29" s="11">
         <v>0</v>
@@ -3293,10 +3296,10 @@
         <v>0</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P29" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3304,7 +3307,7 @@
         <v>802</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E30" s="2">
         <v>98</v>
@@ -3316,13 +3319,13 @@
         <v>2000</v>
       </c>
       <c r="H30" s="19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K30" s="11">
         <v>0</v>
@@ -3337,10 +3340,10 @@
         <v>0</v>
       </c>
       <c r="O30" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P30" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3348,7 +3351,7 @@
         <v>803</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E31" s="2">
         <v>98</v>
@@ -3360,13 +3363,13 @@
         <v>2000</v>
       </c>
       <c r="H31" s="19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I31" s="18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J31" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K31" s="11">
         <v>0</v>
@@ -3381,10 +3384,10 @@
         <v>0</v>
       </c>
       <c r="O31" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P31" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="9:16">
@@ -3401,7 +3404,7 @@
         <v>804</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
@@ -3413,13 +3416,13 @@
         <v>2000</v>
       </c>
       <c r="H33" s="19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J33" s="18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K33" s="11">
         <v>0</v>
@@ -3434,10 +3437,10 @@
         <v>0</v>
       </c>
       <c r="O33" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P33" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3445,7 +3448,7 @@
         <v>805</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E34" s="2">
         <v>98</v>
@@ -3457,13 +3460,13 @@
         <v>2000</v>
       </c>
       <c r="H34" s="19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I34" s="19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J34" s="18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K34" s="11">
         <v>0</v>
@@ -3478,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="O34" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P34" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3489,7 +3492,7 @@
         <v>806</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
@@ -3501,13 +3504,13 @@
         <v>2000</v>
       </c>
       <c r="H35" s="19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I35" s="19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J35" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K35" s="11">
         <v>0</v>
@@ -3522,10 +3525,10 @@
         <v>0</v>
       </c>
       <c r="O35" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P35" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3533,7 +3536,7 @@
         <v>807</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -3545,13 +3548,13 @@
         <v>2000</v>
       </c>
       <c r="H36" s="19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I36" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J36" s="18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K36" s="11">
         <v>0</v>
@@ -3566,10 +3569,10 @@
         <v>0</v>
       </c>
       <c r="O36" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P36" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3577,7 +3580,7 @@
         <v>808</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -3589,13 +3592,13 @@
         <v>2000</v>
       </c>
       <c r="H37" s="19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J37" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K37" s="11">
         <v>0</v>
@@ -3610,10 +3613,10 @@
         <v>0</v>
       </c>
       <c r="O37" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P37" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="3:16">
@@ -3637,7 +3640,7 @@
         <v>991</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E39" s="2">
         <v>99</v>
@@ -3649,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I39" s="11">
         <v>0</v>
@@ -3670,10 +3673,10 @@
         <v>1</v>
       </c>
       <c r="O39" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P39" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3681,7 +3684,7 @@
         <v>992</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E40" s="2">
         <v>101</v>
@@ -3693,7 +3696,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I40" s="11">
         <v>0</v>
@@ -3714,10 +3717,10 @@
         <v>1</v>
       </c>
       <c r="O40" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P40" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1"/>
@@ -3965,7 +3968,7 @@
         <v>1000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -3977,7 +3980,7 @@
         <v>1051</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I6" s="2">
         <v>40000</v>
@@ -3995,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="N6" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O6" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4006,7 +4009,7 @@
         <v>1001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -4018,7 +4021,7 @@
         <v>1052</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I7" s="2">
         <v>40000</v>
@@ -4036,10 +4039,10 @@
         <v>0</v>
       </c>
       <c r="N7" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4047,7 +4050,7 @@
         <v>1002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -4059,7 +4062,7 @@
         <v>1053</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I8" s="2">
         <v>40000</v>
@@ -4077,10 +4080,10 @@
         <v>0</v>
       </c>
       <c r="N8" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4088,7 +4091,7 @@
         <v>1003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -4100,7 +4103,7 @@
         <v>1054</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I9" s="2">
         <v>40000</v>
@@ -4118,10 +4121,10 @@
         <v>0</v>
       </c>
       <c r="N9" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4129,7 +4132,7 @@
         <v>1004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -4141,7 +4144,7 @@
         <v>1055</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I10" s="2">
         <v>40000</v>
@@ -4159,10 +4162,10 @@
         <v>0</v>
       </c>
       <c r="N10" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4170,7 +4173,7 @@
         <v>1005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -4182,7 +4185,7 @@
         <v>1056</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I11" s="2">
         <v>40000</v>
@@ -4200,10 +4203,10 @@
         <v>0</v>
       </c>
       <c r="N11" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4211,7 +4214,7 @@
         <v>1006</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
@@ -4223,7 +4226,7 @@
         <v>1057</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I12" s="2">
         <v>40000</v>
@@ -4241,10 +4244,10 @@
         <v>0</v>
       </c>
       <c r="N12" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4252,7 +4255,7 @@
         <v>1007</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
@@ -4264,7 +4267,7 @@
         <v>1058</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2">
         <v>40000</v>
@@ -4282,10 +4285,10 @@
         <v>0</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4293,7 +4296,7 @@
         <v>1008</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -4305,7 +4308,7 @@
         <v>1059</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I14" s="2">
         <v>40000</v>
@@ -4323,10 +4326,10 @@
         <v>0</v>
       </c>
       <c r="N14" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4334,7 +4337,7 @@
         <v>1009</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -4346,7 +4349,7 @@
         <v>1060</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I15" s="2">
         <v>40000</v>
@@ -4364,10 +4367,10 @@
         <v>0</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4375,7 +4378,7 @@
         <v>1010</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -4387,7 +4390,7 @@
         <v>1061</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I16" s="2">
         <v>40000</v>
@@ -4405,10 +4408,10 @@
         <v>0</v>
       </c>
       <c r="N16" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4416,7 +4419,7 @@
         <v>1011</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -4428,7 +4431,7 @@
         <v>1062</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I17" s="2">
         <v>40000</v>
@@ -4446,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="N17" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4457,7 +4460,7 @@
         <v>1012</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -4469,7 +4472,7 @@
         <v>1063</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I18" s="2">
         <v>40000</v>
@@ -4487,10 +4490,10 @@
         <v>0</v>
       </c>
       <c r="N18" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4498,7 +4501,7 @@
         <v>1013</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -4510,7 +4513,7 @@
         <v>1064</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -4528,10 +4531,10 @@
         <v>0</v>
       </c>
       <c r="N19" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O19" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4539,7 +4542,7 @@
         <v>1014</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E20" s="2">
         <v>98</v>
@@ -4551,7 +4554,7 @@
         <v>1065</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I20" s="2">
         <v>40000</v>
@@ -4569,10 +4572,10 @@
         <v>0</v>
       </c>
       <c r="N20" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O20" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4580,7 +4583,7 @@
         <v>1015</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -4592,7 +4595,7 @@
         <v>1066</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I21" s="2">
         <v>40000</v>
@@ -4610,10 +4613,10 @@
         <v>0</v>
       </c>
       <c r="N21" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O21" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4621,7 +4624,7 @@
         <v>1016</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -4633,7 +4636,7 @@
         <v>1067</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I22" s="2">
         <v>40000</v>
@@ -4651,10 +4654,10 @@
         <v>0</v>
       </c>
       <c r="N22" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4662,7 +4665,7 @@
         <v>1017</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -4674,7 +4677,7 @@
         <v>1068</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I23" s="2">
         <v>40000</v>
@@ -4692,10 +4695,10 @@
         <v>0</v>
       </c>
       <c r="N23" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4703,7 +4706,7 @@
         <v>1018</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -4715,7 +4718,7 @@
         <v>1069</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I24" s="2">
         <v>40000</v>
@@ -4733,10 +4736,10 @@
         <v>0</v>
       </c>
       <c r="N24" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O24" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4744,7 +4747,7 @@
         <v>1019</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -4756,7 +4759,7 @@
         <v>1070</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I25" s="2">
         <v>40000</v>
@@ -4774,10 +4777,10 @@
         <v>0</v>
       </c>
       <c r="N25" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O25" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4785,7 +4788,7 @@
         <v>1020</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -4797,7 +4800,7 @@
         <v>1071</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I26" s="2">
         <v>40000</v>
@@ -4815,10 +4818,10 @@
         <v>0</v>
       </c>
       <c r="N26" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O26" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4826,7 +4829,7 @@
         <v>1021</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -4838,7 +4841,7 @@
         <v>1072</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>
@@ -4856,10 +4859,10 @@
         <v>0</v>
       </c>
       <c r="N27" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O27" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4867,7 +4870,7 @@
         <v>1022</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E28" s="2">
         <v>98</v>
@@ -4879,7 +4882,7 @@
         <v>1073</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I28" s="2">
         <v>40000</v>
@@ -4897,10 +4900,10 @@
         <v>0</v>
       </c>
       <c r="N28" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O28" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:16">
@@ -4908,7 +4911,7 @@
         <v>1023</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -4920,7 +4923,7 @@
         <v>1074</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I29" s="2">
         <v>40000</v>
@@ -4938,10 +4941,10 @@
         <v>0</v>
       </c>
       <c r="N29" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P29" s="2"/>
     </row>
@@ -4950,7 +4953,7 @@
         <v>1024</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E30" s="2">
         <v>98</v>
@@ -4962,7 +4965,7 @@
         <v>1075</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I30" s="2">
         <v>4000</v>
@@ -4980,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="N30" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O30" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4991,7 +4994,7 @@
         <v>1025</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E31" s="2">
         <v>98</v>
@@ -5003,7 +5006,7 @@
         <v>1076</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I31" s="2">
         <v>4000</v>
@@ -5021,10 +5024,10 @@
         <v>0</v>
       </c>
       <c r="N31" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O31" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5032,7 +5035,7 @@
         <v>1026</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E32" s="2">
         <v>98</v>
@@ -5044,7 +5047,7 @@
         <v>1077</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I32" s="2">
         <v>4000</v>
@@ -5062,10 +5065,10 @@
         <v>0</v>
       </c>
       <c r="N32" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O32" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5073,7 +5076,7 @@
         <v>1027</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
@@ -5085,7 +5088,7 @@
         <v>1078</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I33" s="2">
         <v>4000</v>
@@ -5103,10 +5106,10 @@
         <v>0</v>
       </c>
       <c r="N33" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O33" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:16">
@@ -5114,7 +5117,7 @@
         <v>1028</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E34" s="2">
         <v>98</v>
@@ -5126,7 +5129,7 @@
         <v>1079</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I34" s="2">
         <v>4000</v>
@@ -5144,10 +5147,10 @@
         <v>0</v>
       </c>
       <c r="N34" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O34" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P34" s="2"/>
     </row>
@@ -5156,7 +5159,7 @@
         <v>1029</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
@@ -5168,7 +5171,7 @@
         <v>1080</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I35" s="2">
         <v>4000</v>
@@ -5186,10 +5189,10 @@
         <v>0</v>
       </c>
       <c r="N35" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O35" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P35" s="2"/>
     </row>
@@ -5198,7 +5201,7 @@
         <v>1030</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -5210,7 +5213,7 @@
         <v>1081</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I36" s="2">
         <v>4000</v>
@@ -5228,10 +5231,10 @@
         <v>0</v>
       </c>
       <c r="N36" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O36" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P36" s="2"/>
     </row>
@@ -5240,7 +5243,7 @@
         <v>1031</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -5252,7 +5255,7 @@
         <v>1082</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I37" s="2">
         <v>4000</v>
@@ -5270,10 +5273,10 @@
         <v>0</v>
       </c>
       <c r="N37" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O37" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P37" s="2"/>
     </row>
@@ -5282,7 +5285,7 @@
         <v>1032</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E38" s="2">
         <v>98</v>
@@ -5294,7 +5297,7 @@
         <v>1083</v>
       </c>
       <c r="H38" s="20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I38" s="2">
         <v>4000</v>
@@ -5312,10 +5315,10 @@
         <v>0</v>
       </c>
       <c r="N38" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O38" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P38" s="2"/>
     </row>
@@ -5324,7 +5327,7 @@
         <v>1033</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E39" s="2">
         <v>98</v>
@@ -5336,7 +5339,7 @@
         <v>1084</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I39" s="2">
         <v>4000</v>
@@ -5354,10 +5357,10 @@
         <v>0</v>
       </c>
       <c r="N39" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O39" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P39" s="2"/>
     </row>
@@ -5366,7 +5369,7 @@
         <v>1034</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E40" s="2">
         <v>98</v>
@@ -5378,7 +5381,7 @@
         <v>1085</v>
       </c>
       <c r="H40" s="20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I40" s="2">
         <v>4000</v>
@@ -5396,10 +5399,10 @@
         <v>0</v>
       </c>
       <c r="N40" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O40" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P40" s="2"/>
     </row>
@@ -5408,7 +5411,7 @@
         <v>1035</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E41" s="2">
         <v>98</v>
@@ -5420,7 +5423,7 @@
         <v>1086</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I41" s="2">
         <v>4000</v>
@@ -5438,10 +5441,10 @@
         <v>0</v>
       </c>
       <c r="N41" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O41" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P41" s="2"/>
     </row>
@@ -5450,7 +5453,7 @@
         <v>1036</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E42" s="2">
         <v>98</v>
@@ -5462,7 +5465,7 @@
         <v>1087</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I42" s="2">
         <v>4000</v>
@@ -5480,10 +5483,10 @@
         <v>0</v>
       </c>
       <c r="N42" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O42" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P42" s="2"/>
     </row>
@@ -5492,7 +5495,7 @@
         <v>1037</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E43" s="2">
         <v>98</v>
@@ -5504,7 +5507,7 @@
         <v>1088</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I43" s="2">
         <v>4000</v>
@@ -5522,10 +5525,10 @@
         <v>0</v>
       </c>
       <c r="N43" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O43" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P43" s="2"/>
     </row>
@@ -5534,7 +5537,7 @@
         <v>1038</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E44" s="2">
         <v>98</v>
@@ -5546,7 +5549,7 @@
         <v>1089</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I44" s="2">
         <v>4000</v>
@@ -5564,10 +5567,10 @@
         <v>0</v>
       </c>
       <c r="N44" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O44" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P44" s="2"/>
     </row>
@@ -5576,7 +5579,7 @@
         <v>1039</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E45" s="2">
         <v>98</v>
@@ -5588,7 +5591,7 @@
         <v>1090</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I45" s="2">
         <v>4000</v>
@@ -5606,10 +5609,10 @@
         <v>0</v>
       </c>
       <c r="N45" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O45" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P45" s="2"/>
     </row>
@@ -5618,7 +5621,7 @@
         <v>1040</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E46" s="2">
         <v>98</v>
@@ -5630,7 +5633,7 @@
         <v>1091</v>
       </c>
       <c r="H46" s="20" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I46" s="2">
         <v>4000</v>
@@ -5648,10 +5651,10 @@
         <v>0</v>
       </c>
       <c r="N46" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O46" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P46" s="2"/>
     </row>
@@ -5660,7 +5663,7 @@
         <v>1041</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E47" s="2">
         <v>98</v>
@@ -5672,7 +5675,7 @@
         <v>1092</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I47" s="2">
         <v>4000</v>
@@ -5690,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="N47" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O47" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P47" s="2"/>
     </row>
@@ -5702,7 +5705,7 @@
         <v>1042</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E48" s="2">
         <v>98</v>
@@ -5714,7 +5717,7 @@
         <v>1093</v>
       </c>
       <c r="H48" s="20" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I48" s="2">
         <v>4000</v>
@@ -5732,10 +5735,10 @@
         <v>0</v>
       </c>
       <c r="N48" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O48" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P48" s="2"/>
     </row>
@@ -5744,7 +5747,7 @@
         <v>1043</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E49" s="2">
         <v>98</v>
@@ -5756,7 +5759,7 @@
         <v>1094</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I49" s="2">
         <v>4000</v>
@@ -5774,10 +5777,10 @@
         <v>0</v>
       </c>
       <c r="N49" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O49" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P49" s="2"/>
     </row>
@@ -5786,7 +5789,7 @@
         <v>1044</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E50" s="2">
         <v>98</v>
@@ -5798,7 +5801,7 @@
         <v>1095</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I50" s="2">
         <v>4000</v>
@@ -5816,10 +5819,10 @@
         <v>0</v>
       </c>
       <c r="N50" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O50" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P50" s="2"/>
     </row>
@@ -5828,7 +5831,7 @@
         <v>1045</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E51" s="2">
         <v>98</v>
@@ -5840,7 +5843,7 @@
         <v>1096</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I51" s="2">
         <v>4000</v>
@@ -5858,10 +5861,10 @@
         <v>0</v>
       </c>
       <c r="N51" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O51" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P51" s="2"/>
     </row>
@@ -5870,7 +5873,7 @@
         <v>1046</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E52" s="2">
         <v>98</v>
@@ -5882,7 +5885,7 @@
         <v>1097</v>
       </c>
       <c r="H52" s="20" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I52" s="2">
         <v>4000</v>
@@ -5900,10 +5903,10 @@
         <v>0</v>
       </c>
       <c r="N52" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O52" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P52" s="2"/>
     </row>
@@ -5912,7 +5915,7 @@
         <v>1047</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E53" s="2">
         <v>98</v>
@@ -5924,7 +5927,7 @@
         <v>1098</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I53" s="2">
         <v>4000</v>
@@ -5942,10 +5945,10 @@
         <v>0</v>
       </c>
       <c r="N53" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O53" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P53" s="2"/>
     </row>
@@ -5954,7 +5957,7 @@
         <v>1048</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E54" s="2">
         <v>98</v>
@@ -5966,7 +5969,7 @@
         <v>1099</v>
       </c>
       <c r="H54" s="20" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I54" s="2">
         <v>4000</v>
@@ -5984,10 +5987,10 @@
         <v>0</v>
       </c>
       <c r="N54" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O54" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P54" s="2"/>
     </row>
@@ -5996,7 +5999,7 @@
         <v>1049</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E55" s="2">
         <v>98</v>
@@ -6008,7 +6011,7 @@
         <v>1100</v>
       </c>
       <c r="H55" s="20" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I55" s="2">
         <v>4000</v>
@@ -6026,10 +6029,10 @@
         <v>0</v>
       </c>
       <c r="N55" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O55" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P55" s="2"/>
     </row>
@@ -6038,7 +6041,7 @@
         <v>1050</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E56" s="2">
         <v>98</v>
@@ -6050,7 +6053,7 @@
         <v>1101</v>
       </c>
       <c r="H56" s="20" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I56" s="2">
         <v>4000</v>
@@ -6068,10 +6071,10 @@
         <v>0</v>
       </c>
       <c r="N56" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O56" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P56" s="2"/>
     </row>
@@ -6080,7 +6083,7 @@
         <v>1051</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E57" s="2">
         <v>98</v>
@@ -6092,7 +6095,7 @@
         <v>1102</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I57" s="2">
         <v>4000</v>
@@ -6110,10 +6113,10 @@
         <v>0</v>
       </c>
       <c r="N57" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O57" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P57" s="2"/>
     </row>
@@ -6122,7 +6125,7 @@
         <v>1052</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E58" s="2">
         <v>98</v>
@@ -6134,7 +6137,7 @@
         <v>1103</v>
       </c>
       <c r="H58" s="20" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I58" s="2">
         <v>4000</v>
@@ -6152,10 +6155,10 @@
         <v>0</v>
       </c>
       <c r="N58" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O58" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P58" s="2"/>
     </row>
@@ -6164,7 +6167,7 @@
         <v>1053</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E59" s="2">
         <v>98</v>
@@ -6176,7 +6179,7 @@
         <v>1104</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I59" s="2">
         <v>4000</v>
@@ -6194,10 +6197,10 @@
         <v>0</v>
       </c>
       <c r="N59" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O59" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P59" s="2"/>
     </row>
@@ -6206,7 +6209,7 @@
         <v>1054</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E60" s="12">
         <v>98</v>
@@ -6218,7 +6221,7 @@
         <v>1105</v>
       </c>
       <c r="H60" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I60" s="12">
         <v>20000</v>
@@ -6236,10 +6239,10 @@
         <v>0</v>
       </c>
       <c r="N60" s="22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O60" s="22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6247,7 +6250,7 @@
         <v>1055</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E61" s="2">
         <v>98</v>
@@ -6259,7 +6262,7 @@
         <v>1106</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I61" s="2">
         <v>20000</v>
@@ -6277,10 +6280,10 @@
         <v>0</v>
       </c>
       <c r="N61" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O61" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6288,7 +6291,7 @@
         <v>1056</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E62" s="2">
         <v>98</v>
@@ -6300,7 +6303,7 @@
         <v>1107</v>
       </c>
       <c r="H62" s="20" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I62" s="2">
         <v>20000</v>
@@ -6318,10 +6321,10 @@
         <v>0</v>
       </c>
       <c r="N62" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O62" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6329,7 +6332,7 @@
         <v>1057</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E63" s="2">
         <v>98</v>
@@ -6341,7 +6344,7 @@
         <v>1108</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I63" s="2">
         <v>20000</v>
@@ -6359,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="N63" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O63" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:16">
@@ -6370,7 +6373,7 @@
         <v>1058</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E64" s="2">
         <v>98</v>
@@ -6382,7 +6385,7 @@
         <v>1109</v>
       </c>
       <c r="H64" s="20" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I64" s="2">
         <v>20000</v>
@@ -6400,10 +6403,10 @@
         <v>0</v>
       </c>
       <c r="N64" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O64" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P64" s="2"/>
     </row>
@@ -6412,7 +6415,7 @@
         <v>1059</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E65" s="2">
         <v>98</v>
@@ -6424,7 +6427,7 @@
         <v>1110</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I65" s="2">
         <v>20000</v>
@@ -6442,10 +6445,10 @@
         <v>0</v>
       </c>
       <c r="N65" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O65" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6453,7 +6456,7 @@
         <v>1060</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E66" s="2">
         <v>98</v>
@@ -6465,7 +6468,7 @@
         <v>1111</v>
       </c>
       <c r="H66" s="20" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I66" s="2">
         <v>20000</v>
@@ -6483,10 +6486,10 @@
         <v>0</v>
       </c>
       <c r="N66" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O66" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6494,7 +6497,7 @@
         <v>1061</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E67" s="2">
         <v>98</v>
@@ -6506,7 +6509,7 @@
         <v>1112</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I67" s="2">
         <v>20000</v>
@@ -6524,10 +6527,10 @@
         <v>0</v>
       </c>
       <c r="N67" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O67" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6535,7 +6538,7 @@
         <v>1062</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E68" s="2">
         <v>98</v>
@@ -6547,7 +6550,7 @@
         <v>1113</v>
       </c>
       <c r="H68" s="20" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I68" s="2">
         <v>20000</v>
@@ -6565,10 +6568,10 @@
         <v>0</v>
       </c>
       <c r="N68" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O68" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:16">
@@ -6576,7 +6579,7 @@
         <v>1063</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E69" s="2">
         <v>98</v>
@@ -6588,7 +6591,7 @@
         <v>1114</v>
       </c>
       <c r="H69" s="20" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I69" s="2">
         <v>20000</v>
@@ -6606,10 +6609,10 @@
         <v>0</v>
       </c>
       <c r="N69" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O69" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P69" s="2"/>
     </row>
@@ -6618,7 +6621,7 @@
         <v>1064</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E70" s="2">
         <v>98</v>
@@ -6630,7 +6633,7 @@
         <v>1115</v>
       </c>
       <c r="H70" s="20" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I70" s="2">
         <v>20000</v>
@@ -6648,10 +6651,10 @@
         <v>0</v>
       </c>
       <c r="N70" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O70" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P70" s="2"/>
     </row>
@@ -6660,7 +6663,7 @@
         <v>1065</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E71" s="2">
         <v>98</v>
@@ -6672,7 +6675,7 @@
         <v>1116</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I71" s="2">
         <v>20000</v>
@@ -6690,10 +6693,10 @@
         <v>0</v>
       </c>
       <c r="N71" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O71" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P71" s="2"/>
     </row>
@@ -6702,7 +6705,7 @@
         <v>1066</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E72" s="2">
         <v>98</v>
@@ -6714,7 +6717,7 @@
         <v>1117</v>
       </c>
       <c r="H72" s="20" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I72" s="2">
         <v>20000</v>
@@ -6732,10 +6735,10 @@
         <v>0</v>
       </c>
       <c r="N72" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O72" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P72" s="2"/>
     </row>
@@ -6744,7 +6747,7 @@
         <v>1067</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E73" s="2">
         <v>98</v>
@@ -6756,7 +6759,7 @@
         <v>1118</v>
       </c>
       <c r="H73" s="20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I73" s="2">
         <v>20000</v>
@@ -6774,10 +6777,10 @@
         <v>0</v>
       </c>
       <c r="N73" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O73" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P73" s="2"/>
     </row>
@@ -6786,7 +6789,7 @@
         <v>1068</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E74" s="2">
         <v>98</v>
@@ -6798,7 +6801,7 @@
         <v>1119</v>
       </c>
       <c r="H74" s="20" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I74" s="2">
         <v>20000</v>
@@ -6816,10 +6819,10 @@
         <v>0</v>
       </c>
       <c r="N74" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O74" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P74" s="2"/>
     </row>
@@ -6828,7 +6831,7 @@
         <v>1069</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E75" s="2">
         <v>98</v>
@@ -6840,7 +6843,7 @@
         <v>1120</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I75" s="2">
         <v>20000</v>
@@ -6858,10 +6861,10 @@
         <v>0</v>
       </c>
       <c r="N75" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O75" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P75" s="2"/>
     </row>
@@ -6870,7 +6873,7 @@
         <v>1070</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E76" s="2">
         <v>98</v>
@@ -6882,7 +6885,7 @@
         <v>1121</v>
       </c>
       <c r="H76" s="20" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I76" s="2">
         <v>20000</v>
@@ -6900,10 +6903,10 @@
         <v>0</v>
       </c>
       <c r="N76" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O76" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P76" s="2"/>
     </row>
@@ -6912,7 +6915,7 @@
         <v>1071</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E77" s="2">
         <v>98</v>
@@ -6924,7 +6927,7 @@
         <v>1122</v>
       </c>
       <c r="H77" s="20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I77" s="2">
         <v>20000</v>
@@ -6942,10 +6945,10 @@
         <v>0</v>
       </c>
       <c r="N77" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O77" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P77" s="2"/>
     </row>
@@ -6954,7 +6957,7 @@
         <v>1072</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E78" s="2">
         <v>98</v>
@@ -6966,7 +6969,7 @@
         <v>1123</v>
       </c>
       <c r="H78" s="20" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I78" s="2">
         <v>20000</v>
@@ -6984,10 +6987,10 @@
         <v>0</v>
       </c>
       <c r="N78" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O78" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P78" s="2"/>
     </row>
@@ -6996,7 +6999,7 @@
         <v>1073</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E79" s="2">
         <v>98</v>
@@ -7008,7 +7011,7 @@
         <v>1124</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I79" s="2">
         <v>20000</v>
@@ -7026,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="N79" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O79" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P79" s="2"/>
     </row>
@@ -7038,7 +7041,7 @@
         <v>1074</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E80" s="2">
         <v>98</v>
@@ -7050,7 +7053,7 @@
         <v>1125</v>
       </c>
       <c r="H80" s="20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I80" s="2">
         <v>20000</v>
@@ -7068,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="N80" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O80" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P80" s="2"/>
     </row>
@@ -7080,7 +7083,7 @@
         <v>1075</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E81" s="2">
         <v>98</v>
@@ -7092,7 +7095,7 @@
         <v>1126</v>
       </c>
       <c r="H81" s="20" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I81" s="2">
         <v>20000</v>
@@ -7110,10 +7113,10 @@
         <v>0</v>
       </c>
       <c r="N81" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O81" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P81" s="2"/>
     </row>
@@ -7122,7 +7125,7 @@
         <v>1076</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E82" s="2">
         <v>98</v>
@@ -7134,7 +7137,7 @@
         <v>1127</v>
       </c>
       <c r="H82" s="20" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I82" s="2">
         <v>20000</v>
@@ -7152,10 +7155,10 @@
         <v>0</v>
       </c>
       <c r="N82" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O82" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P82" s="2"/>
     </row>
@@ -7164,7 +7167,7 @@
         <v>1077</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E83" s="2">
         <v>98</v>
@@ -7176,7 +7179,7 @@
         <v>1128</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I83" s="2">
         <v>20000</v>
@@ -7194,10 +7197,10 @@
         <v>0</v>
       </c>
       <c r="N83" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O83" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P83" s="2"/>
     </row>
@@ -7206,7 +7209,7 @@
         <v>1078</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E84" s="2">
         <v>98</v>
@@ -7218,7 +7221,7 @@
         <v>1129</v>
       </c>
       <c r="H84" s="20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I84" s="2">
         <v>20000</v>
@@ -7236,10 +7239,10 @@
         <v>0</v>
       </c>
       <c r="N84" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O84" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P84" s="2"/>
     </row>
@@ -7248,7 +7251,7 @@
         <v>1079</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E85" s="2">
         <v>98</v>
@@ -7260,7 +7263,7 @@
         <v>1130</v>
       </c>
       <c r="H85" s="20" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I85" s="2">
         <v>20000</v>
@@ -7278,10 +7281,10 @@
         <v>0</v>
       </c>
       <c r="N85" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O85" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P85" s="2"/>
     </row>
@@ -7290,7 +7293,7 @@
         <v>1080</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E86" s="2">
         <v>98</v>
@@ -7302,7 +7305,7 @@
         <v>1131</v>
       </c>
       <c r="H86" s="20" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I86" s="2">
         <v>20000</v>
@@ -7320,10 +7323,10 @@
         <v>0</v>
       </c>
       <c r="N86" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O86" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P86" s="2"/>
     </row>
@@ -7332,7 +7335,7 @@
         <v>1081</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E87" s="2">
         <v>98</v>
@@ -7344,7 +7347,7 @@
         <v>1132</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I87" s="2">
         <v>20000</v>
@@ -7362,10 +7365,10 @@
         <v>0</v>
       </c>
       <c r="N87" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O87" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P87" s="2"/>
     </row>
@@ -7374,7 +7377,7 @@
         <v>1082</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E88" s="2">
         <v>98</v>
@@ -7386,7 +7389,7 @@
         <v>1133</v>
       </c>
       <c r="H88" s="20" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I88" s="2">
         <v>20000</v>
@@ -7404,10 +7407,10 @@
         <v>0</v>
       </c>
       <c r="N88" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O88" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P88" s="2"/>
     </row>
@@ -7416,7 +7419,7 @@
         <v>1083</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E89" s="2">
         <v>98</v>
@@ -7428,7 +7431,7 @@
         <v>1134</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I89" s="2">
         <v>20000</v>
@@ -7446,10 +7449,10 @@
         <v>0</v>
       </c>
       <c r="N89" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O89" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P89" s="2"/>
     </row>
@@ -7458,7 +7461,7 @@
         <v>1084</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E90" s="2">
         <v>98</v>
@@ -7470,7 +7473,7 @@
         <v>1135</v>
       </c>
       <c r="H90" s="20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I90" s="2">
         <v>20000</v>
@@ -7488,10 +7491,10 @@
         <v>0</v>
       </c>
       <c r="N90" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O90" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P90" s="2"/>
     </row>
@@ -7500,7 +7503,7 @@
         <v>1085</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E91" s="2">
         <v>98</v>
@@ -7512,7 +7515,7 @@
         <v>1136</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I91" s="2">
         <v>20000</v>
@@ -7530,10 +7533,10 @@
         <v>0</v>
       </c>
       <c r="N91" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O91" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P91" s="2"/>
     </row>
@@ -7542,7 +7545,7 @@
         <v>1086</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E92" s="2">
         <v>98</v>
@@ -7554,7 +7557,7 @@
         <v>1137</v>
       </c>
       <c r="H92" s="20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I92" s="2">
         <v>20000</v>
@@ -7572,10 +7575,10 @@
         <v>0</v>
       </c>
       <c r="N92" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O92" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P92" s="2"/>
     </row>
@@ -7584,7 +7587,7 @@
         <v>1087</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E93" s="2">
         <v>98</v>
@@ -7596,7 +7599,7 @@
         <v>1138</v>
       </c>
       <c r="H93" s="20" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I93" s="2">
         <v>20000</v>
@@ -7614,10 +7617,10 @@
         <v>0</v>
       </c>
       <c r="N93" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O93" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P93" s="2"/>
     </row>
@@ -7626,7 +7629,7 @@
         <v>1088</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E94" s="2">
         <v>98</v>
@@ -7638,7 +7641,7 @@
         <v>1139</v>
       </c>
       <c r="H94" s="20" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I94" s="2">
         <v>20000</v>
@@ -7656,10 +7659,10 @@
         <v>0</v>
       </c>
       <c r="N94" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O94" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P94" s="2"/>
     </row>
@@ -7853,7 +7856,7 @@
         <v>2000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -7865,7 +7868,7 @@
         <v>1070</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I6" s="2">
         <v>120000</v>
@@ -7886,10 +7889,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P6" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -7897,7 +7900,7 @@
         <v>2001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -7909,7 +7912,7 @@
         <v>1071</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I7" s="2">
         <v>120000</v>
@@ -7930,10 +7933,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P7" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -7941,7 +7944,7 @@
         <v>2002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -7953,7 +7956,7 @@
         <v>1072</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I8" s="2">
         <v>120000</v>
@@ -7974,10 +7977,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P8" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -7985,7 +7988,7 @@
         <v>2003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -7997,7 +8000,7 @@
         <v>1073</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I9" s="2">
         <v>120000</v>
@@ -8018,10 +8021,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P9" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8029,7 +8032,7 @@
         <v>2004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -8041,7 +8044,7 @@
         <v>1074</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I10" s="2">
         <v>120000</v>
@@ -8062,10 +8065,10 @@
         <v>0</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P10" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8073,7 +8076,7 @@
         <v>2005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -8085,7 +8088,7 @@
         <v>1104</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I11" s="2">
         <v>20000</v>
@@ -8106,10 +8109,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P11" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
@@ -8131,7 +8134,7 @@
         <v>2006</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -8143,7 +8146,7 @@
         <v>1105</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I14" s="2">
         <v>360000</v>
@@ -8164,10 +8167,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P14" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8175,7 +8178,7 @@
         <v>2007</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -8187,7 +8190,7 @@
         <v>1106</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I15" s="2">
         <v>360000</v>
@@ -8208,10 +8211,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P15" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8219,7 +8222,7 @@
         <v>2008</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -8231,7 +8234,7 @@
         <v>1107</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I16" s="2">
         <v>360000</v>
@@ -8252,10 +8255,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8263,7 +8266,7 @@
         <v>2009</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -8275,7 +8278,7 @@
         <v>1108</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I17" s="2">
         <v>360000</v>
@@ -8296,10 +8299,10 @@
         <v>0</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P17" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8307,7 +8310,7 @@
         <v>2010</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -8319,7 +8322,7 @@
         <v>1139</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I18" s="2">
         <v>360000</v>
@@ -8340,10 +8343,10 @@
         <v>0</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P18" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -8351,7 +8354,7 @@
         <v>2011</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -8363,7 +8366,7 @@
         <v>1139</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -8384,10 +8387,10 @@
         <v>0</v>
       </c>
       <c r="O19" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P19" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -349,7 +349,7 @@
     <t>2024-11-28</t>
   </si>
   <si>
-    <t>2024-12-01</t>
+    <t>2024-12-02</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>感恩节</t>
+    <t>圣诞节</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2024-11-28</t>
-  </si>
-  <si>
-    <t>2024-12-02</t>
+    <t>2024-12-24</t>
+  </si>
+  <si>
+    <t>2024-12-27</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2024-12-24</t>
-  </si>
-  <si>
-    <t>2024-12-27</t>
+    <t>2024-12-23</t>
+  </si>
+  <si>
+    <t>2024-12-26</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -346,7 +346,7 @@
     <t>50</t>
   </si>
   <si>
-    <t>2024-12-23</t>
+    <t>2024-12-22</t>
   </si>
   <si>
     <t>2024-12-26</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>圣诞节</t>
+    <t>元旦快乐</t>
   </si>
   <si>
     <t>1005</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2024-12-22</t>
-  </si>
-  <si>
-    <t>2024-12-26</t>
+    <t>2025-01-01</t>
+  </si>
+  <si>
+    <t>2025-01-05</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>元旦快乐</t>
+    <t>元旦节</t>
   </si>
   <si>
     <t>1005</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -472,19 +472,19 @@
     <t>16000</t>
   </si>
   <si>
-    <t>守沙100书页</t>
+    <t>龙城100书页</t>
   </si>
   <si>
     <t>1002</t>
   </si>
   <si>
-    <t>守沙图鉴</t>
+    <t>龙城图鉴</t>
   </si>
   <si>
     <t>2000</t>
   </si>
   <si>
-    <t>守沙时装</t>
+    <t>龙城时装</t>
   </si>
   <si>
     <t>3001</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>元旦节</t>
+    <t>春节</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
-    <t>2025-01-05</t>
+    <t>2025-01-27</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-01-27</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
+    <t>2025-01-26</t>
+  </si>
+  <si>
+    <t>2025-02-04</t>
   </si>
   <si>
     <t>平时部分掉落</t>
@@ -7682,7 +7682,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C1:P46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
@@ -7719,7 +7719,7 @@
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="3:16">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="3:16">
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
@@ -7763,7 +7763,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="3:16">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="3:16">
       <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
@@ -7807,7 +7807,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="3:16">
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="3:16">
       <c r="C5" s="5" t="s">
         <v>24</v>
       </c>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>春节</t>
+    <t>元宵节</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-01-26</t>
-  </si>
-  <si>
-    <t>2025-02-04</t>
+    <t>2025-02-12</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
   </si>
   <si>
     <t>平时部分掉落</t>
@@ -1388,12 +1388,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -346,7 +346,7 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-02-12</t>
+    <t>2025-02-11</t>
   </si>
   <si>
     <t>2025-02-15</t>
@@ -1388,12 +1388,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>元宵节</t>
+    <t>植树节</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-02-11</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
   </si>
   <si>
     <t>平时部分掉落</t>
@@ -7682,7 +7682,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C1:P46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
@@ -7719,7 +7719,7 @@
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="13.5" spans="3:16">
+    <row r="3" s="1" customFormat="1" spans="3:16">
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
@@ -7763,7 +7763,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="13.5" spans="3:16">
+    <row r="4" s="1" customFormat="1" spans="3:16">
       <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
@@ -7807,7 +7807,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="13.5" spans="3:16">
+    <row r="5" s="1" customFormat="1" spans="3:16">
       <c r="C5" s="5" t="s">
         <v>24</v>
       </c>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="384">
   <si>
     <t>_id</t>
   </si>
@@ -1126,6 +1126,216 @@
     <t>1400088</t>
   </si>
   <si>
+    <t>深渊鸡爪</t>
+  </si>
+  <si>
+    <t>1400089</t>
+  </si>
+  <si>
+    <t>深渊鹿茸</t>
+  </si>
+  <si>
+    <t>1400090</t>
+  </si>
+  <si>
+    <t>深渊草帽</t>
+  </si>
+  <si>
+    <t>1400091</t>
+  </si>
+  <si>
+    <t>深渊猫爪</t>
+  </si>
+  <si>
+    <t>1400092</t>
+  </si>
+  <si>
+    <t>深渊花朵</t>
+  </si>
+  <si>
+    <t>1400093</t>
+  </si>
+  <si>
+    <t>深渊冰晶</t>
+  </si>
+  <si>
+    <t>1400094</t>
+  </si>
+  <si>
+    <t>深渊蝠翼</t>
+  </si>
+  <si>
+    <t>1400095</t>
+  </si>
+  <si>
+    <t>深渊魂火</t>
+  </si>
+  <si>
+    <t>1400096</t>
+  </si>
+  <si>
+    <t>深渊腐肉</t>
+  </si>
+  <si>
+    <t>1400097</t>
+  </si>
+  <si>
+    <t>深渊蛇胆</t>
+  </si>
+  <si>
+    <t>1400098</t>
+  </si>
+  <si>
+    <t>深渊狼爪</t>
+  </si>
+  <si>
+    <t>1400099</t>
+  </si>
+  <si>
+    <t>深渊虫皮</t>
+  </si>
+  <si>
+    <t>1400100</t>
+  </si>
+  <si>
+    <t>深渊鹰羽</t>
+  </si>
+  <si>
+    <t>1400101</t>
+  </si>
+  <si>
+    <t>深渊虫角</t>
+  </si>
+  <si>
+    <t>1400102</t>
+  </si>
+  <si>
+    <t>深渊蜈膏</t>
+  </si>
+  <si>
+    <t>1400103</t>
+  </si>
+  <si>
+    <t>深渊虫心</t>
+  </si>
+  <si>
+    <t>1400104</t>
+  </si>
+  <si>
+    <t>深渊龙皮</t>
+  </si>
+  <si>
+    <t>1400105</t>
+  </si>
+  <si>
+    <t>深渊猪皮</t>
+  </si>
+  <si>
+    <t>1400106</t>
+  </si>
+  <si>
+    <t>深渊猪心</t>
+  </si>
+  <si>
+    <t>1400107</t>
+  </si>
+  <si>
+    <t>深渊蝎皮</t>
+  </si>
+  <si>
+    <t>1400108</t>
+  </si>
+  <si>
+    <t>深渊宝甲</t>
+  </si>
+  <si>
+    <t>1400109</t>
+  </si>
+  <si>
+    <t>深渊号角</t>
+  </si>
+  <si>
+    <t>1400110</t>
+  </si>
+  <si>
+    <t>深渊雕像</t>
+  </si>
+  <si>
+    <t>1400111</t>
+  </si>
+  <si>
+    <t>深渊神像</t>
+  </si>
+  <si>
+    <t>1400112</t>
+  </si>
+  <si>
+    <t>深渊獠牙</t>
+  </si>
+  <si>
+    <t>1400113</t>
+  </si>
+  <si>
+    <t>深渊树心</t>
+  </si>
+  <si>
+    <t>1400114</t>
+  </si>
+  <si>
+    <t>深渊魔心</t>
+  </si>
+  <si>
+    <t>1400115</t>
+  </si>
+  <si>
+    <t>深渊尸心</t>
+  </si>
+  <si>
+    <t>1400116</t>
+  </si>
+  <si>
+    <t>深渊法杖</t>
+  </si>
+  <si>
+    <t>1400117</t>
+  </si>
+  <si>
+    <t>深渊权杖</t>
+  </si>
+  <si>
+    <t>1400118</t>
+  </si>
+  <si>
+    <t>深渊战锤</t>
+  </si>
+  <si>
+    <t>1400119</t>
+  </si>
+  <si>
+    <t>深渊血核</t>
+  </si>
+  <si>
+    <t>1400120</t>
+  </si>
+  <si>
+    <t>深渊魔核</t>
+  </si>
+  <si>
+    <t>1400121</t>
+  </si>
+  <si>
+    <t>深渊龙甲</t>
+  </si>
+  <si>
+    <t>1400122</t>
+  </si>
+  <si>
+    <t>深渊龙爪</t>
+  </si>
+  <si>
+    <t>1400123</t>
+  </si>
+  <si>
     <t>武器衣服红装</t>
   </si>
   <si>
@@ -1184,6 +1394,21 @@
   </si>
   <si>
     <t>209999</t>
+  </si>
+  <si>
+    <t>武器衣服暗金</t>
+  </si>
+  <si>
+    <t>项链头盔暗金</t>
+  </si>
+  <si>
+    <t>手镯戒指暗金</t>
+  </si>
+  <si>
+    <t>腰带鞋子暗金</t>
+  </si>
+  <si>
+    <t>随机暗金</t>
   </si>
 </sst>
 </file>
@@ -3804,7 +4029,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P94"/>
+  <dimension ref="C1:P129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -7665,6 +7890,1468 @@
         <v>34</v>
       </c>
       <c r="P94" s="2"/>
+    </row>
+    <row r="95" s="12" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C95" s="12">
+        <v>1089</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="E95" s="12">
+        <v>98</v>
+      </c>
+      <c r="F95" s="13">
+        <v>1140</v>
+      </c>
+      <c r="G95" s="13">
+        <v>1140</v>
+      </c>
+      <c r="H95" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="I95" s="12">
+        <v>30000</v>
+      </c>
+      <c r="J95" s="12">
+        <v>240000</v>
+      </c>
+      <c r="K95" s="12">
+        <v>0</v>
+      </c>
+      <c r="L95" s="12">
+        <v>0</v>
+      </c>
+      <c r="M95" s="12">
+        <v>0</v>
+      </c>
+      <c r="N95" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="O95" s="22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="96" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C96" s="2">
+        <v>1090</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E96" s="2">
+        <v>98</v>
+      </c>
+      <c r="F96" s="8">
+        <v>1141</v>
+      </c>
+      <c r="G96" s="8">
+        <v>1141</v>
+      </c>
+      <c r="H96" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="I96" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J96" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K96" s="2">
+        <v>0</v>
+      </c>
+      <c r="L96" s="2">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2">
+        <v>0</v>
+      </c>
+      <c r="N96" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O96" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="97" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C97" s="2">
+        <v>1091</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E97" s="2">
+        <v>98</v>
+      </c>
+      <c r="F97" s="8">
+        <v>1142</v>
+      </c>
+      <c r="G97" s="8">
+        <v>1142</v>
+      </c>
+      <c r="H97" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="I97" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J97" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K97" s="2">
+        <v>0</v>
+      </c>
+      <c r="L97" s="2">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2">
+        <v>0</v>
+      </c>
+      <c r="N97" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O97" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="98" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C98" s="2">
+        <v>1092</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E98" s="2">
+        <v>98</v>
+      </c>
+      <c r="F98" s="8">
+        <v>1143</v>
+      </c>
+      <c r="G98" s="8">
+        <v>1143</v>
+      </c>
+      <c r="H98" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="I98" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J98" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K98" s="2">
+        <v>0</v>
+      </c>
+      <c r="L98" s="2">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2">
+        <v>0</v>
+      </c>
+      <c r="N98" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O98" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:16">
+      <c r="C99" s="2">
+        <v>1093</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E99" s="2">
+        <v>98</v>
+      </c>
+      <c r="F99" s="8">
+        <v>1144</v>
+      </c>
+      <c r="G99" s="8">
+        <v>1144</v>
+      </c>
+      <c r="H99" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="I99" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J99" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K99" s="2">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2">
+        <v>0</v>
+      </c>
+      <c r="N99" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O99" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P99" s="2"/>
+    </row>
+    <row r="100" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C100" s="2">
+        <v>1094</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E100" s="2">
+        <v>98</v>
+      </c>
+      <c r="F100" s="8">
+        <v>1145</v>
+      </c>
+      <c r="G100" s="8">
+        <v>1145</v>
+      </c>
+      <c r="H100" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="I100" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J100" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K100" s="2">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2">
+        <v>0</v>
+      </c>
+      <c r="N100" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O100" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="101" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C101" s="2">
+        <v>1095</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E101" s="2">
+        <v>98</v>
+      </c>
+      <c r="F101" s="8">
+        <v>1146</v>
+      </c>
+      <c r="G101" s="8">
+        <v>1146</v>
+      </c>
+      <c r="H101" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="I101" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J101" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K101" s="2">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2">
+        <v>0</v>
+      </c>
+      <c r="N101" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O101" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="102" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C102" s="2">
+        <v>1096</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E102" s="2">
+        <v>98</v>
+      </c>
+      <c r="F102" s="8">
+        <v>1147</v>
+      </c>
+      <c r="G102" s="8">
+        <v>1147</v>
+      </c>
+      <c r="H102" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="I102" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J102" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K102" s="2">
+        <v>0</v>
+      </c>
+      <c r="L102" s="2">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2">
+        <v>0</v>
+      </c>
+      <c r="N102" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O102" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="103" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C103" s="2">
+        <v>1097</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E103" s="2">
+        <v>98</v>
+      </c>
+      <c r="F103" s="8">
+        <v>1148</v>
+      </c>
+      <c r="G103" s="8">
+        <v>1148</v>
+      </c>
+      <c r="H103" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="I103" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J103" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K103" s="2">
+        <v>0</v>
+      </c>
+      <c r="L103" s="2">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2">
+        <v>0</v>
+      </c>
+      <c r="N103" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O103" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:16">
+      <c r="C104" s="2">
+        <v>1098</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E104" s="2">
+        <v>98</v>
+      </c>
+      <c r="F104" s="8">
+        <v>1149</v>
+      </c>
+      <c r="G104" s="8">
+        <v>1149</v>
+      </c>
+      <c r="H104" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="I104" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J104" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K104" s="2">
+        <v>0</v>
+      </c>
+      <c r="L104" s="2">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2">
+        <v>0</v>
+      </c>
+      <c r="N104" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O104" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P104" s="2"/>
+    </row>
+    <row r="105" customHeight="1" spans="3:16">
+      <c r="C105" s="2">
+        <v>1099</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E105" s="2">
+        <v>98</v>
+      </c>
+      <c r="F105" s="8">
+        <v>1150</v>
+      </c>
+      <c r="G105" s="8">
+        <v>1150</v>
+      </c>
+      <c r="H105" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="I105" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J105" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K105" s="2">
+        <v>0</v>
+      </c>
+      <c r="L105" s="2">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2">
+        <v>0</v>
+      </c>
+      <c r="N105" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O105" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P105" s="2"/>
+    </row>
+    <row r="106" customHeight="1" spans="3:16">
+      <c r="C106" s="2">
+        <v>1100</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E106" s="2">
+        <v>98</v>
+      </c>
+      <c r="F106" s="8">
+        <v>1151</v>
+      </c>
+      <c r="G106" s="8">
+        <v>1151</v>
+      </c>
+      <c r="H106" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="I106" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J106" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K106" s="2">
+        <v>0</v>
+      </c>
+      <c r="L106" s="2">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2">
+        <v>0</v>
+      </c>
+      <c r="N106" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O106" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P106" s="2"/>
+    </row>
+    <row r="107" customHeight="1" spans="3:16">
+      <c r="C107" s="2">
+        <v>1101</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E107" s="2">
+        <v>98</v>
+      </c>
+      <c r="F107" s="8">
+        <v>1152</v>
+      </c>
+      <c r="G107" s="8">
+        <v>1152</v>
+      </c>
+      <c r="H107" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="I107" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J107" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K107" s="2">
+        <v>0</v>
+      </c>
+      <c r="L107" s="2">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2">
+        <v>0</v>
+      </c>
+      <c r="N107" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O107" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P107" s="2"/>
+    </row>
+    <row r="108" customHeight="1" spans="3:16">
+      <c r="C108" s="2">
+        <v>1102</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E108" s="2">
+        <v>98</v>
+      </c>
+      <c r="F108" s="8">
+        <v>1153</v>
+      </c>
+      <c r="G108" s="8">
+        <v>1153</v>
+      </c>
+      <c r="H108" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="I108" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J108" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K108" s="2">
+        <v>0</v>
+      </c>
+      <c r="L108" s="2">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2">
+        <v>0</v>
+      </c>
+      <c r="N108" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O108" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P108" s="2"/>
+    </row>
+    <row r="109" customHeight="1" spans="3:16">
+      <c r="C109" s="2">
+        <v>1103</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E109" s="2">
+        <v>98</v>
+      </c>
+      <c r="F109" s="8">
+        <v>1154</v>
+      </c>
+      <c r="G109" s="8">
+        <v>1154</v>
+      </c>
+      <c r="H109" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="I109" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J109" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K109" s="2">
+        <v>0</v>
+      </c>
+      <c r="L109" s="2">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2">
+        <v>0</v>
+      </c>
+      <c r="N109" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O109" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P109" s="2"/>
+    </row>
+    <row r="110" customHeight="1" spans="3:16">
+      <c r="C110" s="2">
+        <v>1104</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E110" s="2">
+        <v>98</v>
+      </c>
+      <c r="F110" s="8">
+        <v>1155</v>
+      </c>
+      <c r="G110" s="8">
+        <v>1155</v>
+      </c>
+      <c r="H110" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="I110" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J110" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K110" s="2">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2">
+        <v>0</v>
+      </c>
+      <c r="N110" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O110" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P110" s="2"/>
+    </row>
+    <row r="111" customHeight="1" spans="3:16">
+      <c r="C111" s="2">
+        <v>1105</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E111" s="2">
+        <v>98</v>
+      </c>
+      <c r="F111" s="8">
+        <v>1156</v>
+      </c>
+      <c r="G111" s="8">
+        <v>1156</v>
+      </c>
+      <c r="H111" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="I111" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J111" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K111" s="2">
+        <v>0</v>
+      </c>
+      <c r="L111" s="2">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2">
+        <v>0</v>
+      </c>
+      <c r="N111" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O111" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P111" s="2"/>
+    </row>
+    <row r="112" customHeight="1" spans="3:16">
+      <c r="C112" s="2">
+        <v>1106</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E112" s="2">
+        <v>98</v>
+      </c>
+      <c r="F112" s="8">
+        <v>1157</v>
+      </c>
+      <c r="G112" s="8">
+        <v>1157</v>
+      </c>
+      <c r="H112" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="I112" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J112" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K112" s="2">
+        <v>0</v>
+      </c>
+      <c r="L112" s="2">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2">
+        <v>0</v>
+      </c>
+      <c r="N112" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O112" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P112" s="2"/>
+    </row>
+    <row r="113" customHeight="1" spans="3:16">
+      <c r="C113" s="2">
+        <v>1107</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E113" s="2">
+        <v>98</v>
+      </c>
+      <c r="F113" s="8">
+        <v>1158</v>
+      </c>
+      <c r="G113" s="8">
+        <v>1158</v>
+      </c>
+      <c r="H113" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="I113" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J113" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K113" s="2">
+        <v>0</v>
+      </c>
+      <c r="L113" s="2">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2">
+        <v>0</v>
+      </c>
+      <c r="N113" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O113" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P113" s="2"/>
+    </row>
+    <row r="114" customHeight="1" spans="3:16">
+      <c r="C114" s="2">
+        <v>1108</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E114" s="2">
+        <v>98</v>
+      </c>
+      <c r="F114" s="8">
+        <v>1159</v>
+      </c>
+      <c r="G114" s="8">
+        <v>1159</v>
+      </c>
+      <c r="H114" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="I114" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J114" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K114" s="2">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2">
+        <v>0</v>
+      </c>
+      <c r="N114" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O114" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P114" s="2"/>
+    </row>
+    <row r="115" customHeight="1" spans="3:16">
+      <c r="C115" s="2">
+        <v>1109</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E115" s="2">
+        <v>98</v>
+      </c>
+      <c r="F115" s="8">
+        <v>1160</v>
+      </c>
+      <c r="G115" s="8">
+        <v>1160</v>
+      </c>
+      <c r="H115" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="I115" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J115" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K115" s="2">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2">
+        <v>0</v>
+      </c>
+      <c r="N115" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O115" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P115" s="2"/>
+    </row>
+    <row r="116" customHeight="1" spans="3:16">
+      <c r="C116" s="2">
+        <v>1110</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E116" s="2">
+        <v>98</v>
+      </c>
+      <c r="F116" s="8">
+        <v>1161</v>
+      </c>
+      <c r="G116" s="8">
+        <v>1161</v>
+      </c>
+      <c r="H116" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="I116" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J116" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K116" s="2">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2">
+        <v>0</v>
+      </c>
+      <c r="N116" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O116" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P116" s="2"/>
+    </row>
+    <row r="117" customHeight="1" spans="3:16">
+      <c r="C117" s="2">
+        <v>1111</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E117" s="2">
+        <v>98</v>
+      </c>
+      <c r="F117" s="8">
+        <v>1162</v>
+      </c>
+      <c r="G117" s="8">
+        <v>1162</v>
+      </c>
+      <c r="H117" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="I117" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J117" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K117" s="2">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2">
+        <v>0</v>
+      </c>
+      <c r="N117" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O117" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P117" s="2"/>
+    </row>
+    <row r="118" customHeight="1" spans="3:16">
+      <c r="C118" s="2">
+        <v>1112</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E118" s="2">
+        <v>98</v>
+      </c>
+      <c r="F118" s="8">
+        <v>1163</v>
+      </c>
+      <c r="G118" s="8">
+        <v>1163</v>
+      </c>
+      <c r="H118" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="I118" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J118" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K118" s="2">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2">
+        <v>0</v>
+      </c>
+      <c r="N118" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O118" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P118" s="2"/>
+    </row>
+    <row r="119" customHeight="1" spans="3:16">
+      <c r="C119" s="2">
+        <v>1113</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E119" s="2">
+        <v>98</v>
+      </c>
+      <c r="F119" s="8">
+        <v>1164</v>
+      </c>
+      <c r="G119" s="8">
+        <v>1164</v>
+      </c>
+      <c r="H119" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="I119" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J119" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K119" s="2">
+        <v>0</v>
+      </c>
+      <c r="L119" s="2">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2">
+        <v>0</v>
+      </c>
+      <c r="N119" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O119" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P119" s="2"/>
+    </row>
+    <row r="120" customHeight="1" spans="3:16">
+      <c r="C120" s="2">
+        <v>1114</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E120" s="2">
+        <v>98</v>
+      </c>
+      <c r="F120" s="8">
+        <v>1165</v>
+      </c>
+      <c r="G120" s="8">
+        <v>1165</v>
+      </c>
+      <c r="H120" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="I120" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J120" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K120" s="2">
+        <v>0</v>
+      </c>
+      <c r="L120" s="2">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2">
+        <v>0</v>
+      </c>
+      <c r="N120" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O120" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P120" s="2"/>
+    </row>
+    <row r="121" customHeight="1" spans="3:16">
+      <c r="C121" s="2">
+        <v>1115</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E121" s="2">
+        <v>98</v>
+      </c>
+      <c r="F121" s="8">
+        <v>1166</v>
+      </c>
+      <c r="G121" s="8">
+        <v>1166</v>
+      </c>
+      <c r="H121" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="I121" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J121" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K121" s="2">
+        <v>0</v>
+      </c>
+      <c r="L121" s="2">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2">
+        <v>0</v>
+      </c>
+      <c r="N121" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O121" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P121" s="2"/>
+    </row>
+    <row r="122" customHeight="1" spans="3:16">
+      <c r="C122" s="2">
+        <v>1116</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E122" s="2">
+        <v>98</v>
+      </c>
+      <c r="F122" s="8">
+        <v>1167</v>
+      </c>
+      <c r="G122" s="8">
+        <v>1167</v>
+      </c>
+      <c r="H122" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="I122" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J122" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K122" s="2">
+        <v>0</v>
+      </c>
+      <c r="L122" s="2">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2">
+        <v>0</v>
+      </c>
+      <c r="N122" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O122" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P122" s="2"/>
+    </row>
+    <row r="123" customHeight="1" spans="3:16">
+      <c r="C123" s="2">
+        <v>1117</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E123" s="2">
+        <v>98</v>
+      </c>
+      <c r="F123" s="8">
+        <v>1168</v>
+      </c>
+      <c r="G123" s="8">
+        <v>1168</v>
+      </c>
+      <c r="H123" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="I123" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J123" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K123" s="2">
+        <v>0</v>
+      </c>
+      <c r="L123" s="2">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2">
+        <v>0</v>
+      </c>
+      <c r="N123" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O123" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P123" s="2"/>
+    </row>
+    <row r="124" customHeight="1" spans="3:16">
+      <c r="C124" s="2">
+        <v>1118</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E124" s="2">
+        <v>98</v>
+      </c>
+      <c r="F124" s="8">
+        <v>1169</v>
+      </c>
+      <c r="G124" s="8">
+        <v>1169</v>
+      </c>
+      <c r="H124" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="I124" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J124" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K124" s="2">
+        <v>0</v>
+      </c>
+      <c r="L124" s="2">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2">
+        <v>0</v>
+      </c>
+      <c r="N124" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O124" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P124" s="2"/>
+    </row>
+    <row r="125" customHeight="1" spans="3:16">
+      <c r="C125" s="2">
+        <v>1119</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E125" s="2">
+        <v>98</v>
+      </c>
+      <c r="F125" s="8">
+        <v>1170</v>
+      </c>
+      <c r="G125" s="8">
+        <v>1170</v>
+      </c>
+      <c r="H125" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="I125" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J125" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K125" s="2">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2">
+        <v>0</v>
+      </c>
+      <c r="N125" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O125" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P125" s="2"/>
+    </row>
+    <row r="126" customHeight="1" spans="3:16">
+      <c r="C126" s="2">
+        <v>1120</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E126" s="2">
+        <v>98</v>
+      </c>
+      <c r="F126" s="8">
+        <v>1171</v>
+      </c>
+      <c r="G126" s="8">
+        <v>1171</v>
+      </c>
+      <c r="H126" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="I126" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J126" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K126" s="2">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2">
+        <v>0</v>
+      </c>
+      <c r="N126" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O126" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P126" s="2"/>
+    </row>
+    <row r="127" customHeight="1" spans="3:16">
+      <c r="C127" s="2">
+        <v>1121</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E127" s="2">
+        <v>98</v>
+      </c>
+      <c r="F127" s="8">
+        <v>1172</v>
+      </c>
+      <c r="G127" s="8">
+        <v>1172</v>
+      </c>
+      <c r="H127" s="20" t="s">
+        <v>354</v>
+      </c>
+      <c r="I127" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J127" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K127" s="2">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2">
+        <v>0</v>
+      </c>
+      <c r="N127" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O127" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P127" s="2"/>
+    </row>
+    <row r="128" customHeight="1" spans="3:16">
+      <c r="C128" s="2">
+        <v>1122</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E128" s="2">
+        <v>98</v>
+      </c>
+      <c r="F128" s="8">
+        <v>1173</v>
+      </c>
+      <c r="G128" s="8">
+        <v>1173</v>
+      </c>
+      <c r="H128" s="20" t="s">
+        <v>356</v>
+      </c>
+      <c r="I128" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J128" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K128" s="2">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2">
+        <v>0</v>
+      </c>
+      <c r="N128" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O128" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P128" s="2"/>
+    </row>
+    <row r="129" customHeight="1" spans="3:16">
+      <c r="C129" s="2">
+        <v>1123</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E129" s="2">
+        <v>98</v>
+      </c>
+      <c r="F129" s="8">
+        <v>1174</v>
+      </c>
+      <c r="G129" s="8">
+        <v>1174</v>
+      </c>
+      <c r="H129" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="I129" s="2">
+        <v>30000</v>
+      </c>
+      <c r="J129" s="2">
+        <v>240000</v>
+      </c>
+      <c r="K129" s="2">
+        <v>0</v>
+      </c>
+      <c r="L129" s="2">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2">
+        <v>0</v>
+      </c>
+      <c r="N129" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O129" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="P129" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -7856,7 +9543,7 @@
         <v>2000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>289</v>
+        <v>359</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -7868,7 +9555,7 @@
         <v>1070</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>290</v>
+        <v>360</v>
       </c>
       <c r="I6" s="2">
         <v>120000</v>
@@ -7900,7 +9587,7 @@
         <v>2001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>291</v>
+        <v>361</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -7912,7 +9599,7 @@
         <v>1071</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="I7" s="2">
         <v>120000</v>
@@ -7944,7 +9631,7 @@
         <v>2002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>293</v>
+        <v>363</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -7956,7 +9643,7 @@
         <v>1072</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>294</v>
+        <v>364</v>
       </c>
       <c r="I8" s="2">
         <v>120000</v>
@@ -7988,7 +9675,7 @@
         <v>2003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>295</v>
+        <v>365</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -8000,7 +9687,7 @@
         <v>1073</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>296</v>
+        <v>366</v>
       </c>
       <c r="I9" s="2">
         <v>120000</v>
@@ -8032,7 +9719,7 @@
         <v>2004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>297</v>
+        <v>367</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -8044,7 +9731,7 @@
         <v>1074</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>298</v>
+        <v>368</v>
       </c>
       <c r="I10" s="2">
         <v>120000</v>
@@ -8076,7 +9763,7 @@
         <v>2005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>297</v>
+        <v>367</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -8088,7 +9775,7 @@
         <v>1104</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>298</v>
+        <v>368</v>
       </c>
       <c r="I11" s="2">
         <v>20000</v>
@@ -8134,7 +9821,7 @@
         <v>2006</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>299</v>
+        <v>369</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -8146,7 +9833,7 @@
         <v>1105</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>300</v>
+        <v>370</v>
       </c>
       <c r="I14" s="2">
         <v>360000</v>
@@ -8178,7 +9865,7 @@
         <v>2007</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>301</v>
+        <v>371</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -8190,7 +9877,7 @@
         <v>1106</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>302</v>
+        <v>372</v>
       </c>
       <c r="I15" s="2">
         <v>360000</v>
@@ -8222,7 +9909,7 @@
         <v>2008</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>303</v>
+        <v>373</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -8234,7 +9921,7 @@
         <v>1107</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>304</v>
+        <v>374</v>
       </c>
       <c r="I16" s="2">
         <v>360000</v>
@@ -8266,7 +9953,7 @@
         <v>2009</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>305</v>
+        <v>375</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -8278,7 +9965,7 @@
         <v>1108</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>306</v>
+        <v>376</v>
       </c>
       <c r="I17" s="2">
         <v>360000</v>
@@ -8310,7 +9997,7 @@
         <v>2010</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>307</v>
+        <v>377</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -8322,7 +10009,7 @@
         <v>1139</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>308</v>
+        <v>378</v>
       </c>
       <c r="I18" s="2">
         <v>360000</v>
@@ -8354,7 +10041,7 @@
         <v>2011</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>297</v>
+        <v>367</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -8366,7 +10053,7 @@
         <v>1139</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>298</v>
+        <v>368</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -8400,54 +10087,313 @@
       <c r="O20" s="11"/>
       <c r="P20" s="11"/>
     </row>
-    <row r="21" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="9"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-    </row>
-    <row r="22" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="9"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-    </row>
-    <row r="23" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="9"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-    </row>
-    <row r="24" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="9"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-    </row>
-    <row r="25" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="9"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-    </row>
-    <row r="26" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="9"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-    </row>
-    <row r="27" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="9"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="11"/>
+    <row r="21" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+      <c r="C21" s="2">
+        <v>2012</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E21" s="2">
+        <v>98</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1140</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1140</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="I21" s="2">
+        <v>360000</v>
+      </c>
+      <c r="J21" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="K21" s="2">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2">
+        <v>100000</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2">
+        <v>0</v>
+      </c>
+      <c r="O21" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P21" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+      <c r="C22" s="2">
+        <v>2013</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E22" s="2">
+        <v>98</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1141</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1141</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="I22" s="2">
+        <v>360000</v>
+      </c>
+      <c r="J22" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2">
+        <v>100000</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2">
+        <v>0</v>
+      </c>
+      <c r="O22" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P22" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+      <c r="C23" s="2">
+        <v>2014</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E23" s="2">
+        <v>98</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1142</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1142</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>374</v>
+      </c>
+      <c r="I23" s="2">
+        <v>360000</v>
+      </c>
+      <c r="J23" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="K23" s="2">
+        <v>0</v>
+      </c>
+      <c r="L23" s="2">
+        <v>100000</v>
+      </c>
+      <c r="M23" s="2">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2">
+        <v>0</v>
+      </c>
+      <c r="O23" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P23" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+      <c r="C24" s="2">
+        <v>2015</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E24" s="2">
+        <v>98</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1143</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1143</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>376</v>
+      </c>
+      <c r="I24" s="2">
+        <v>360000</v>
+      </c>
+      <c r="J24" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="K24" s="2">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2">
+        <v>100000</v>
+      </c>
+      <c r="M24" s="2">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2">
+        <v>0</v>
+      </c>
+      <c r="O24" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P24" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+      <c r="C25" s="2">
+        <v>2016</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E25" s="2">
+        <v>98</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1144</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1174</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="I25" s="2">
+        <v>360000</v>
+      </c>
+      <c r="J25" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="K25" s="2">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2">
+        <v>100000</v>
+      </c>
+      <c r="M25" s="2">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2">
+        <v>0</v>
+      </c>
+      <c r="O25" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P25" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+      <c r="C26" s="2">
+        <v>2017</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E26" s="2">
+        <v>98</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1140</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1174</v>
+      </c>
+      <c r="H26" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="I26" s="2">
+        <v>120000</v>
+      </c>
+      <c r="J26" s="2">
+        <v>1080000</v>
+      </c>
+      <c r="K26" s="2">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2">
+        <v>60000</v>
+      </c>
+      <c r="M26" s="2">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2">
+        <v>0</v>
+      </c>
+      <c r="O26" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P26" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+      <c r="C27" s="2">
+        <v>2018</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E27" s="2">
+        <v>98</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1140</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1174</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="I27" s="2">
+        <v>40000</v>
+      </c>
+      <c r="J27" s="2">
+        <v>540000</v>
+      </c>
+      <c r="K27" s="2">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2">
+        <v>30000</v>
+      </c>
+      <c r="M27" s="2">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2">
+        <v>0</v>
+      </c>
+      <c r="O27" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P27" s="18" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="28" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
       <c r="F28" s="8"/>
@@ -8584,25 +10530,43 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G11">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G26">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G18">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
+  <conditionalFormatting sqref="G27">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G19">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  <conditionalFormatting sqref="F14:F18">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14:F18">
+  <conditionalFormatting sqref="F21:F25">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G14:G17">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G21:G25">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:G17">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 C2:C5 F3:G5 F14:G19" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 F27 G27 C2:C5 F21:G26 F3:G5 F14:G19" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="390">
   <si>
     <t>_id</t>
   </si>
@@ -1399,16 +1399,34 @@
     <t>武器衣服暗金</t>
   </si>
   <si>
+    <t>209990</t>
+  </si>
+  <si>
     <t>项链头盔暗金</t>
   </si>
   <si>
+    <t>209991</t>
+  </si>
+  <si>
     <t>手镯戒指暗金</t>
   </si>
   <si>
+    <t>209992</t>
+  </si>
+  <si>
     <t>腰带鞋子暗金</t>
   </si>
   <si>
+    <t>209993</t>
+  </si>
+  <si>
     <t>随机暗金</t>
+  </si>
+  <si>
+    <t>209994</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
 </sst>
 </file>
@@ -9368,7 +9386,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P46"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -10104,19 +10122,19 @@
         <v>1140</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="I21" s="2">
-        <v>360000</v>
+        <v>360</v>
       </c>
       <c r="J21" s="2">
-        <v>1800000</v>
+        <v>1800</v>
       </c>
       <c r="K21" s="2">
         <v>0</v>
       </c>
       <c r="L21" s="2">
-        <v>100000</v>
+        <v>100</v>
       </c>
       <c r="M21" s="2">
         <v>0</v>
@@ -10136,7 +10154,7 @@
         <v>2013</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -10148,19 +10166,19 @@
         <v>1141</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="I22" s="2">
-        <v>360000</v>
+        <v>360</v>
       </c>
       <c r="J22" s="2">
-        <v>1800000</v>
+        <v>1800</v>
       </c>
       <c r="K22" s="2">
         <v>0</v>
       </c>
       <c r="L22" s="2">
-        <v>100000</v>
+        <v>100</v>
       </c>
       <c r="M22" s="2">
         <v>0</v>
@@ -10180,7 +10198,7 @@
         <v>2014</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -10192,19 +10210,19 @@
         <v>1142</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="I23" s="2">
-        <v>360000</v>
+        <v>360</v>
       </c>
       <c r="J23" s="2">
-        <v>1800000</v>
+        <v>1800</v>
       </c>
       <c r="K23" s="2">
         <v>0</v>
       </c>
       <c r="L23" s="2">
-        <v>100000</v>
+        <v>100</v>
       </c>
       <c r="M23" s="2">
         <v>0</v>
@@ -10224,7 +10242,7 @@
         <v>2015</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -10236,19 +10254,19 @@
         <v>1143</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="I24" s="2">
-        <v>360000</v>
+        <v>360</v>
       </c>
       <c r="J24" s="2">
-        <v>1800000</v>
+        <v>1800</v>
       </c>
       <c r="K24" s="2">
         <v>0</v>
       </c>
       <c r="L24" s="2">
-        <v>100000</v>
+        <v>100</v>
       </c>
       <c r="M24" s="2">
         <v>0</v>
@@ -10268,7 +10286,7 @@
         <v>2016</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -10280,19 +10298,19 @@
         <v>1174</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="I25" s="2">
-        <v>360000</v>
+        <v>360</v>
       </c>
       <c r="J25" s="2">
-        <v>1800000</v>
+        <v>1800</v>
       </c>
       <c r="K25" s="2">
         <v>0</v>
       </c>
       <c r="L25" s="2">
-        <v>100000</v>
+        <v>100</v>
       </c>
       <c r="M25" s="2">
         <v>0</v>
@@ -10351,7 +10369,13 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+    <row r="27" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+      <c r="A27" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>389</v>
+      </c>
       <c r="C27" s="2">
         <v>2018</v>
       </c>
@@ -10566,7 +10590,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 F27 G27 C2:C5 F21:G26 F3:G5 F14:G19" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 C2:C5 F3:G5 F14:G19 F21:G27" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -9387,7 +9387,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
@@ -9424,7 +9424,7 @@
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="3:16">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="3:16">
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
@@ -9468,7 +9468,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="3:16">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="3:16">
       <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
@@ -9512,7 +9512,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="3:16">
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="3:16">
       <c r="C5" s="5" t="s">
         <v>24</v>
       </c>
@@ -10128,13 +10128,13 @@
         <v>360</v>
       </c>
       <c r="J21" s="2">
-        <v>1800</v>
+        <v>1800000</v>
       </c>
       <c r="K21" s="2">
         <v>0</v>
       </c>
       <c r="L21" s="2">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="M21" s="2">
         <v>0</v>
@@ -10172,13 +10172,13 @@
         <v>360</v>
       </c>
       <c r="J22" s="2">
-        <v>1800</v>
+        <v>1800000</v>
       </c>
       <c r="K22" s="2">
         <v>0</v>
       </c>
       <c r="L22" s="2">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="M22" s="2">
         <v>0</v>
@@ -10216,13 +10216,13 @@
         <v>360</v>
       </c>
       <c r="J23" s="2">
-        <v>1800</v>
+        <v>1800000</v>
       </c>
       <c r="K23" s="2">
         <v>0</v>
       </c>
       <c r="L23" s="2">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="M23" s="2">
         <v>0</v>
@@ -10260,13 +10260,13 @@
         <v>360</v>
       </c>
       <c r="J24" s="2">
-        <v>1800</v>
+        <v>1800000</v>
       </c>
       <c r="K24" s="2">
         <v>0</v>
       </c>
       <c r="L24" s="2">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="M24" s="2">
         <v>0</v>
@@ -10304,13 +10304,13 @@
         <v>360</v>
       </c>
       <c r="J25" s="2">
-        <v>1800</v>
+        <v>1800000</v>
       </c>
       <c r="K25" s="2">
         <v>0</v>
       </c>
       <c r="L25" s="2">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="M25" s="2">
         <v>0</v>
@@ -10348,13 +10348,13 @@
         <v>120000</v>
       </c>
       <c r="J26" s="2">
-        <v>1080000</v>
+        <v>900000</v>
       </c>
       <c r="K26" s="2">
         <v>0</v>
       </c>
       <c r="L26" s="2">
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="M26" s="2">
         <v>0</v>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -9387,7 +9387,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
@@ -9424,7 +9424,7 @@
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="13.5" spans="3:16">
+    <row r="3" s="1" customFormat="1" spans="3:16">
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
@@ -9468,7 +9468,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="13.5" spans="3:16">
+    <row r="4" s="1" customFormat="1" spans="3:16">
       <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
@@ -9512,7 +9512,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="13.5" spans="3:16">
+    <row r="5" s="1" customFormat="1" spans="3:16">
       <c r="C5" s="5" t="s">
         <v>24</v>
       </c>
@@ -10125,7 +10125,7 @@
         <v>380</v>
       </c>
       <c r="I21" s="2">
-        <v>360</v>
+        <v>360000</v>
       </c>
       <c r="J21" s="2">
         <v>1800000</v>
@@ -10169,7 +10169,7 @@
         <v>382</v>
       </c>
       <c r="I22" s="2">
-        <v>360</v>
+        <v>360000</v>
       </c>
       <c r="J22" s="2">
         <v>1800000</v>
@@ -10213,7 +10213,7 @@
         <v>384</v>
       </c>
       <c r="I23" s="2">
-        <v>360</v>
+        <v>360000</v>
       </c>
       <c r="J23" s="2">
         <v>1800000</v>
@@ -10257,7 +10257,7 @@
         <v>386</v>
       </c>
       <c r="I24" s="2">
-        <v>360</v>
+        <v>360000</v>
       </c>
       <c r="J24" s="2">
         <v>1800000</v>
@@ -10301,7 +10301,7 @@
         <v>388</v>
       </c>
       <c r="I25" s="2">
-        <v>360</v>
+        <v>360000</v>
       </c>
       <c r="J25" s="2">
         <v>1800000</v>
@@ -10345,7 +10345,7 @@
         <v>378</v>
       </c>
       <c r="I26" s="2">
-        <v>120000</v>
+        <v>180000</v>
       </c>
       <c r="J26" s="2">
         <v>900000</v>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>植树节</t>
+    <t>清明节</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>2025-04-09</t>
   </si>
   <si>
     <t>平时部分掉落</t>
@@ -9387,7 +9387,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
@@ -9424,7 +9424,7 @@
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="3:16">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="3:16">
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
@@ -9468,7 +9468,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="3:16">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="3:16">
       <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
@@ -9512,7 +9512,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="3:16">
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="3:16">
       <c r="C5" s="5" t="s">
         <v>24</v>
       </c>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>清明节</t>
+    <t>劳动节</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>2025-04-09</t>
+    <t>2025-04-30</t>
+  </si>
+  <si>
+    <t>2025-05-06</t>
   </si>
   <si>
     <t>平时部分掉落</t>
@@ -9387,7 +9387,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
@@ -9424,7 +9424,7 @@
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="13.5" spans="3:16">
+    <row r="3" s="1" customFormat="1" spans="3:16">
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
@@ -9468,7 +9468,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="13.5" spans="3:16">
+    <row r="4" s="1" customFormat="1" spans="3:16">
       <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
@@ -9512,7 +9512,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="13.5" spans="3:16">
+    <row r="5" s="1" customFormat="1" spans="3:16">
       <c r="C5" s="5" t="s">
         <v>24</v>
       </c>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -349,7 +349,7 @@
     <t>2025-04-30</t>
   </si>
   <si>
-    <t>2025-05-06</t>
+    <t>2025-05-01</t>
   </si>
   <si>
     <t>平时部分掉落</t>
@@ -2470,14 +2470,14 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="8.75" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.875" style="2" customWidth="1"/>
-    <col min="5" max="7" width="13.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.5" style="16" customWidth="1"/>
-    <col min="9" max="9" width="17.875" style="16" customWidth="1"/>
-    <col min="10" max="12" width="13.75" style="16" customWidth="1"/>
-    <col min="13" max="14" width="14.125" style="16" customWidth="1"/>
-    <col min="15" max="16" width="20.625" style="16" customWidth="1"/>
+    <col min="3" max="3" width="8.75221238938053" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.8761061946903" style="2" customWidth="1"/>
+    <col min="5" max="7" width="13.6283185840708" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17.5044247787611" style="16" customWidth="1"/>
+    <col min="9" max="9" width="17.8761061946903" style="16" customWidth="1"/>
+    <col min="10" max="12" width="13.7522123893805" style="16" customWidth="1"/>
+    <col min="13" max="14" width="14.1238938053097" style="16" customWidth="1"/>
+    <col min="15" max="16" width="20.6283185840708" style="16" customWidth="1"/>
     <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -4051,14 +4051,14 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.875" style="1" customWidth="1"/>
-    <col min="5" max="7" width="13.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5" style="3" customWidth="1"/>
-    <col min="9" max="9" width="17.875" style="3" customWidth="1"/>
-    <col min="10" max="11" width="13.75" style="3" customWidth="1"/>
-    <col min="12" max="13" width="14.125" style="3" customWidth="1"/>
-    <col min="14" max="15" width="20.625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.75221238938053" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.8761061946903" style="1" customWidth="1"/>
+    <col min="5" max="7" width="13.6283185840708" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5044247787611" style="3" customWidth="1"/>
+    <col min="9" max="9" width="17.8761061946903" style="3" customWidth="1"/>
+    <col min="10" max="11" width="13.7522123893805" style="3" customWidth="1"/>
+    <col min="12" max="13" width="14.1238938053097" style="3" customWidth="1"/>
+    <col min="14" max="15" width="20.6283185840708" style="3" customWidth="1"/>
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -9387,17 +9387,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.875" style="1" customWidth="1"/>
-    <col min="5" max="7" width="13.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5" style="3" customWidth="1"/>
-    <col min="9" max="9" width="17.875" style="3" customWidth="1"/>
-    <col min="10" max="12" width="13.75" style="3" customWidth="1"/>
-    <col min="13" max="14" width="14.125" style="3" customWidth="1"/>
-    <col min="15" max="16" width="20.625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.75221238938053" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.8761061946903" style="1" customWidth="1"/>
+    <col min="5" max="7" width="13.6283185840708" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5044247787611" style="3" customWidth="1"/>
+    <col min="9" max="9" width="17.8761061946903" style="3" customWidth="1"/>
+    <col min="10" max="12" width="13.7522123893805" style="3" customWidth="1"/>
+    <col min="13" max="14" width="14.1238938053097" style="3" customWidth="1"/>
+    <col min="15" max="16" width="20.6283185840708" style="3" customWidth="1"/>
     <col min="17" max="16383" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>劳动节</t>
+    <t>快乐端午</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-04-30</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
+    <t>2025-05-31</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="393">
   <si>
     <t>_id</t>
   </si>
@@ -502,6 +502,21 @@
     <t>3002</t>
   </si>
   <si>
+    <t>3003</t>
+  </si>
+  <si>
+    <t>30000</t>
+  </si>
+  <si>
+    <t>120000</t>
+  </si>
+  <si>
+    <t>3004</t>
+  </si>
+  <si>
+    <t>40000</t>
+  </si>
+  <si>
     <t>专属之心</t>
   </si>
   <si>
@@ -514,9 +529,6 @@
     <t>2001</t>
   </si>
   <si>
-    <t>30000</t>
-  </si>
-  <si>
     <t>冠名图鉴2</t>
   </si>
   <si>
@@ -562,22 +574,19 @@
     <t>2008</t>
   </si>
   <si>
-    <t>400000</t>
+    <t>200000</t>
+  </si>
+  <si>
+    <t>800000</t>
+  </si>
+  <si>
+    <t>金图鉴3</t>
+  </si>
+  <si>
+    <t>2009</t>
   </si>
   <si>
     <t>1000000</t>
-  </si>
-  <si>
-    <t>金图鉴3</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>600000</t>
-  </si>
-  <si>
-    <t>1500000</t>
   </si>
   <si>
     <t>镜像挑战</t>
@@ -1631,12 +1640,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2466,7 +2475,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P45"/>
+  <dimension ref="C1:P47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -3500,40 +3509,83 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28" s="2" customFormat="1" customHeight="1"/>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C28" s="2">
+        <v>303</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" s="2">
+        <v>98</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1070</v>
+      </c>
+      <c r="G28" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="I28" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="J28" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="K28" s="11">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2">
+        <v>20000</v>
+      </c>
+      <c r="M28" s="2">
+        <v>1</v>
+      </c>
+      <c r="N28" s="11">
+        <v>0</v>
+      </c>
+      <c r="O28" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P28" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C29" s="2">
-        <v>801</v>
+        <v>304</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
       </c>
       <c r="F29" s="2">
-        <v>1000</v>
+        <v>1070</v>
       </c>
       <c r="G29" s="2">
         <v>2000</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="J29" s="19" t="s">
-        <v>59</v>
+        <v>85</v>
+      </c>
+      <c r="J29" s="18" t="s">
+        <v>78</v>
       </c>
       <c r="K29" s="11">
         <v>0</v>
       </c>
-      <c r="L29" s="11">
-        <v>0</v>
+      <c r="L29" s="2">
+        <v>40000</v>
       </c>
       <c r="M29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" s="11">
         <v>0</v>
@@ -3545,53 +3597,10 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C30" s="2">
-        <v>802</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E30" s="2">
-        <v>98</v>
-      </c>
-      <c r="F30" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G30" s="2">
-        <v>2000</v>
-      </c>
-      <c r="H30" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="I30" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="J30" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="K30" s="11">
-        <v>0</v>
-      </c>
-      <c r="L30" s="11">
-        <v>0</v>
-      </c>
-      <c r="M30" s="11">
-        <v>1</v>
-      </c>
-      <c r="N30" s="11">
-        <v>0</v>
-      </c>
-      <c r="O30" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P30" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1"/>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C31" s="2">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>86</v>
@@ -3600,19 +3609,19 @@
         <v>98</v>
       </c>
       <c r="F31" s="2">
-        <v>1105</v>
+        <v>1000</v>
       </c>
       <c r="G31" s="2">
         <v>2000</v>
       </c>
-      <c r="H31" s="19" t="s">
+      <c r="H31" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="I31" s="18" t="s">
+      <c r="I31" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J31" s="18" t="s">
-        <v>85</v>
+      <c r="J31" s="19" t="s">
+        <v>59</v>
       </c>
       <c r="K31" s="11">
         <v>0</v>
@@ -3633,39 +3642,74 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="9:16">
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
-      <c r="P32" s="11"/>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C32" s="2">
+        <v>802</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E32" s="2">
+        <v>98</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G32" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="I32" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="J32" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="K32" s="11">
+        <v>0</v>
+      </c>
+      <c r="L32" s="11">
+        <v>0</v>
+      </c>
+      <c r="M32" s="11">
+        <v>1</v>
+      </c>
+      <c r="N32" s="11">
+        <v>0</v>
+      </c>
+      <c r="O32" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P32" s="18" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C33" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
       </c>
       <c r="F33" s="2">
-        <v>1000</v>
+        <v>1105</v>
       </c>
       <c r="G33" s="2">
         <v>2000</v>
       </c>
       <c r="H33" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="I33" s="19" t="s">
-        <v>59</v>
+        <v>91</v>
+      </c>
+      <c r="I33" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="J33" s="18" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="K33" s="11">
         <v>0</v>
@@ -3686,79 +3730,44 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C34" s="2">
-        <v>805</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E34" s="2">
-        <v>98</v>
-      </c>
-      <c r="F34" s="2">
-        <v>1105</v>
-      </c>
-      <c r="G34" s="2">
-        <v>2000</v>
-      </c>
-      <c r="H34" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="I34" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="J34" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="K34" s="11">
-        <v>0</v>
-      </c>
-      <c r="L34" s="11">
-        <v>0</v>
-      </c>
-      <c r="M34" s="2">
-        <v>0</v>
-      </c>
-      <c r="N34" s="11">
-        <v>0</v>
-      </c>
-      <c r="O34" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P34" s="18" t="s">
-        <v>34</v>
-      </c>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="9:16">
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="11"/>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C35" s="2">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
       </c>
       <c r="F35" s="2">
-        <v>1105</v>
+        <v>1000</v>
       </c>
       <c r="G35" s="2">
         <v>2000</v>
       </c>
       <c r="H35" s="19" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I35" s="19" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="J35" s="18" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="K35" s="11">
         <v>0</v>
       </c>
-      <c r="L35" s="2">
+      <c r="L35" s="11">
         <v>0</v>
       </c>
       <c r="M35" s="2">
@@ -3776,10 +3785,10 @@
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C36" s="2">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -3791,19 +3800,19 @@
         <v>2000</v>
       </c>
       <c r="H36" s="19" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I36" s="19" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J36" s="18" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="K36" s="11">
         <v>0</v>
       </c>
-      <c r="L36" s="2">
-        <v>200000</v>
+      <c r="L36" s="11">
+        <v>0</v>
       </c>
       <c r="M36" s="2">
         <v>0</v>
@@ -3820,10 +3829,10 @@
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C37" s="2">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -3835,160 +3844,226 @@
         <v>2000</v>
       </c>
       <c r="H37" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="I37" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="J37" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="K37" s="11">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2">
+        <v>0</v>
+      </c>
+      <c r="N37" s="11">
+        <v>0</v>
+      </c>
+      <c r="O37" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P37" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C38" s="2">
+        <v>807</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E38" s="2">
+        <v>98</v>
+      </c>
+      <c r="F38" s="2">
+        <v>1105</v>
+      </c>
+      <c r="G38" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H38" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="I37" s="19" t="s">
+      <c r="I38" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="J37" s="18" t="s">
+      <c r="J38" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="K37" s="11">
-        <v>0</v>
-      </c>
-      <c r="L37" s="2">
-        <v>400000</v>
-      </c>
-      <c r="M37" s="2">
-        <v>0</v>
-      </c>
-      <c r="N37" s="11">
-        <v>0</v>
-      </c>
-      <c r="O37" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P37" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-      <c r="P38" s="16"/>
+      <c r="K38" s="11">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2">
+        <v>150000</v>
+      </c>
+      <c r="M38" s="2">
+        <v>0</v>
+      </c>
+      <c r="N38" s="11">
+        <v>0</v>
+      </c>
+      <c r="O38" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P38" s="18" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C39" s="2">
-        <v>991</v>
+        <v>808</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>107</v>
       </c>
       <c r="E39" s="2">
+        <v>98</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1105</v>
+      </c>
+      <c r="G39" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H39" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="I39" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="J39" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="K39" s="11">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2">
+        <v>200000</v>
+      </c>
+      <c r="M39" s="2">
+        <v>0</v>
+      </c>
+      <c r="N39" s="11">
+        <v>0</v>
+      </c>
+      <c r="O39" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P39" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="16"/>
+      <c r="N40" s="16"/>
+      <c r="O40" s="16"/>
+      <c r="P40" s="16"/>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C41" s="2">
+        <v>991</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E41" s="2">
         <v>99</v>
       </c>
-      <c r="F39" s="2">
-        <v>0</v>
-      </c>
-      <c r="G39" s="2">
-        <v>0</v>
-      </c>
-      <c r="H39" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="I39" s="11">
-        <v>0</v>
-      </c>
-      <c r="J39" s="2">
+      <c r="F41" s="2">
+        <v>0</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0</v>
+      </c>
+      <c r="H41" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="I41" s="11">
+        <v>0</v>
+      </c>
+      <c r="J41" s="2">
         <v>1</v>
       </c>
-      <c r="K39" s="11">
-        <v>0</v>
-      </c>
-      <c r="L39" s="11">
-        <v>0</v>
-      </c>
-      <c r="M39" s="2">
-        <v>0</v>
-      </c>
-      <c r="N39" s="2">
+      <c r="K41" s="11">
+        <v>0</v>
+      </c>
+      <c r="L41" s="11">
+        <v>0</v>
+      </c>
+      <c r="M41" s="2">
+        <v>0</v>
+      </c>
+      <c r="N41" s="2">
         <v>1</v>
       </c>
-      <c r="O39" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P39" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C40" s="2">
+      <c r="O41" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P41" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C42" s="2">
         <v>992</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E40" s="2">
+      <c r="D42" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E42" s="2">
         <v>101</v>
       </c>
-      <c r="F40" s="2">
-        <v>0</v>
-      </c>
-      <c r="G40" s="2">
-        <v>0</v>
-      </c>
-      <c r="H40" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="I40" s="11">
-        <v>0</v>
-      </c>
-      <c r="J40" s="2">
+      <c r="F42" s="2">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2">
+        <v>0</v>
+      </c>
+      <c r="H42" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="I42" s="11">
+        <v>0</v>
+      </c>
+      <c r="J42" s="2">
         <v>1</v>
       </c>
-      <c r="K40" s="11">
-        <v>0</v>
-      </c>
-      <c r="L40" s="11">
-        <v>0</v>
-      </c>
-      <c r="M40" s="2">
-        <v>0</v>
-      </c>
-      <c r="N40" s="2">
+      <c r="K42" s="11">
+        <v>0</v>
+      </c>
+      <c r="L42" s="11">
+        <v>0</v>
+      </c>
+      <c r="M42" s="2">
+        <v>0</v>
+      </c>
+      <c r="N42" s="2">
         <v>1</v>
       </c>
-      <c r="O40" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P40" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="41" s="2" customFormat="1" customHeight="1"/>
-    <row r="42" s="2" customFormat="1" customHeight="1" spans="8:16">
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
-      <c r="J42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="16"/>
-      <c r="O42" s="16"/>
-      <c r="P42" s="16"/>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="8:16">
-      <c r="H43" s="16"/>
-      <c r="I43" s="16"/>
-      <c r="J43" s="16"/>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="16"/>
-      <c r="O43" s="16"/>
-      <c r="P43" s="16"/>
-    </row>
+      <c r="O42" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P42" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1"/>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="8:16">
       <c r="H44" s="16"/>
       <c r="I44" s="16"/>
@@ -4011,30 +4086,52 @@
       <c r="O45" s="16"/>
       <c r="P45" s="16"/>
     </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="8:16">
+      <c r="H46" s="16"/>
+      <c r="I46" s="16"/>
+      <c r="J46" s="16"/>
+      <c r="K46" s="16"/>
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
+      <c r="N46" s="16"/>
+      <c r="O46" s="16"/>
+      <c r="P46" s="16"/>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="8:16">
+      <c r="H47" s="16"/>
+      <c r="I47" s="16"/>
+      <c r="J47" s="16"/>
+      <c r="K47" s="16"/>
+      <c r="L47" s="16"/>
+      <c r="M47" s="16"/>
+      <c r="N47" s="16"/>
+      <c r="O47" s="16"/>
+      <c r="P47" s="16"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F30">
+  <conditionalFormatting sqref="F32">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F31">
+  <conditionalFormatting sqref="F33">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F32">
+  <conditionalFormatting sqref="F34">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F34">
+  <conditionalFormatting sqref="F36">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F35">
+  <conditionalFormatting sqref="F37">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F36">
+  <conditionalFormatting sqref="F38">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F37">
+  <conditionalFormatting sqref="F39">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:C5 F30:F32 F34:F37 F3:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:C5 F32:F34 F36:F39 F3:G5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -4211,7 +4308,7 @@
         <v>1000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -4223,7 +4320,7 @@
         <v>1051</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I6" s="2">
         <v>40000</v>
@@ -4252,7 +4349,7 @@
         <v>1001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -4264,7 +4361,7 @@
         <v>1052</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I7" s="2">
         <v>40000</v>
@@ -4293,7 +4390,7 @@
         <v>1002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -4305,7 +4402,7 @@
         <v>1053</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I8" s="2">
         <v>40000</v>
@@ -4334,7 +4431,7 @@
         <v>1003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -4346,7 +4443,7 @@
         <v>1054</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I9" s="2">
         <v>40000</v>
@@ -4375,7 +4472,7 @@
         <v>1004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -4387,7 +4484,7 @@
         <v>1055</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I10" s="2">
         <v>40000</v>
@@ -4416,7 +4513,7 @@
         <v>1005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -4428,7 +4525,7 @@
         <v>1056</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I11" s="2">
         <v>40000</v>
@@ -4457,7 +4554,7 @@
         <v>1006</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
@@ -4469,7 +4566,7 @@
         <v>1057</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="I12" s="2">
         <v>40000</v>
@@ -4498,7 +4595,7 @@
         <v>1007</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
@@ -4510,7 +4607,7 @@
         <v>1058</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I13" s="2">
         <v>40000</v>
@@ -4539,7 +4636,7 @@
         <v>1008</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -4551,7 +4648,7 @@
         <v>1059</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I14" s="2">
         <v>40000</v>
@@ -4580,7 +4677,7 @@
         <v>1009</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -4592,7 +4689,7 @@
         <v>1060</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I15" s="2">
         <v>40000</v>
@@ -4621,7 +4718,7 @@
         <v>1010</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -4633,7 +4730,7 @@
         <v>1061</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I16" s="2">
         <v>40000</v>
@@ -4662,7 +4759,7 @@
         <v>1011</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -4674,7 +4771,7 @@
         <v>1062</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I17" s="2">
         <v>40000</v>
@@ -4703,7 +4800,7 @@
         <v>1012</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -4715,7 +4812,7 @@
         <v>1063</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I18" s="2">
         <v>40000</v>
@@ -4744,7 +4841,7 @@
         <v>1013</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -4756,7 +4853,7 @@
         <v>1064</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -4785,7 +4882,7 @@
         <v>1014</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E20" s="2">
         <v>98</v>
@@ -4797,7 +4894,7 @@
         <v>1065</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I20" s="2">
         <v>40000</v>
@@ -4826,7 +4923,7 @@
         <v>1015</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -4838,7 +4935,7 @@
         <v>1066</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I21" s="2">
         <v>40000</v>
@@ -4867,7 +4964,7 @@
         <v>1016</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -4879,7 +4976,7 @@
         <v>1067</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I22" s="2">
         <v>40000</v>
@@ -4908,7 +5005,7 @@
         <v>1017</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -4920,7 +5017,7 @@
         <v>1068</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I23" s="2">
         <v>40000</v>
@@ -4949,7 +5046,7 @@
         <v>1018</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -4961,7 +5058,7 @@
         <v>1069</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I24" s="2">
         <v>40000</v>
@@ -4990,7 +5087,7 @@
         <v>1019</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -5002,7 +5099,7 @@
         <v>1070</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I25" s="2">
         <v>40000</v>
@@ -5031,7 +5128,7 @@
         <v>1020</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -5043,7 +5140,7 @@
         <v>1071</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I26" s="2">
         <v>40000</v>
@@ -5072,7 +5169,7 @@
         <v>1021</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -5084,7 +5181,7 @@
         <v>1072</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>
@@ -5113,7 +5210,7 @@
         <v>1022</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E28" s="2">
         <v>98</v>
@@ -5125,7 +5222,7 @@
         <v>1073</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I28" s="2">
         <v>40000</v>
@@ -5154,7 +5251,7 @@
         <v>1023</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -5166,7 +5263,7 @@
         <v>1074</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I29" s="2">
         <v>40000</v>
@@ -5196,7 +5293,7 @@
         <v>1024</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E30" s="2">
         <v>98</v>
@@ -5208,7 +5305,7 @@
         <v>1075</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I30" s="2">
         <v>4000</v>
@@ -5237,7 +5334,7 @@
         <v>1025</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E31" s="2">
         <v>98</v>
@@ -5249,7 +5346,7 @@
         <v>1076</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I31" s="2">
         <v>4000</v>
@@ -5278,7 +5375,7 @@
         <v>1026</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E32" s="2">
         <v>98</v>
@@ -5290,7 +5387,7 @@
         <v>1077</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I32" s="2">
         <v>4000</v>
@@ -5319,7 +5416,7 @@
         <v>1027</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
@@ -5331,7 +5428,7 @@
         <v>1078</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I33" s="2">
         <v>4000</v>
@@ -5360,7 +5457,7 @@
         <v>1028</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E34" s="2">
         <v>98</v>
@@ -5372,7 +5469,7 @@
         <v>1079</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I34" s="2">
         <v>4000</v>
@@ -5402,7 +5499,7 @@
         <v>1029</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
@@ -5414,7 +5511,7 @@
         <v>1080</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I35" s="2">
         <v>4000</v>
@@ -5444,7 +5541,7 @@
         <v>1030</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -5456,7 +5553,7 @@
         <v>1081</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I36" s="2">
         <v>4000</v>
@@ -5486,7 +5583,7 @@
         <v>1031</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -5498,7 +5595,7 @@
         <v>1082</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I37" s="2">
         <v>4000</v>
@@ -5528,7 +5625,7 @@
         <v>1032</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E38" s="2">
         <v>98</v>
@@ -5540,7 +5637,7 @@
         <v>1083</v>
       </c>
       <c r="H38" s="20" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I38" s="2">
         <v>4000</v>
@@ -5570,7 +5667,7 @@
         <v>1033</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E39" s="2">
         <v>98</v>
@@ -5582,7 +5679,7 @@
         <v>1084</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="I39" s="2">
         <v>4000</v>
@@ -5612,7 +5709,7 @@
         <v>1034</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E40" s="2">
         <v>98</v>
@@ -5624,7 +5721,7 @@
         <v>1085</v>
       </c>
       <c r="H40" s="20" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I40" s="2">
         <v>4000</v>
@@ -5654,7 +5751,7 @@
         <v>1035</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E41" s="2">
         <v>98</v>
@@ -5666,7 +5763,7 @@
         <v>1086</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I41" s="2">
         <v>4000</v>
@@ -5696,7 +5793,7 @@
         <v>1036</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E42" s="2">
         <v>98</v>
@@ -5708,7 +5805,7 @@
         <v>1087</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="I42" s="2">
         <v>4000</v>
@@ -5738,7 +5835,7 @@
         <v>1037</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E43" s="2">
         <v>98</v>
@@ -5750,7 +5847,7 @@
         <v>1088</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I43" s="2">
         <v>4000</v>
@@ -5780,7 +5877,7 @@
         <v>1038</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E44" s="2">
         <v>98</v>
@@ -5792,7 +5889,7 @@
         <v>1089</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I44" s="2">
         <v>4000</v>
@@ -5822,7 +5919,7 @@
         <v>1039</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E45" s="2">
         <v>98</v>
@@ -5834,7 +5931,7 @@
         <v>1090</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I45" s="2">
         <v>4000</v>
@@ -5864,7 +5961,7 @@
         <v>1040</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E46" s="2">
         <v>98</v>
@@ -5876,7 +5973,7 @@
         <v>1091</v>
       </c>
       <c r="H46" s="20" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I46" s="2">
         <v>4000</v>
@@ -5906,7 +6003,7 @@
         <v>1041</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E47" s="2">
         <v>98</v>
@@ -5918,7 +6015,7 @@
         <v>1092</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I47" s="2">
         <v>4000</v>
@@ -5948,7 +6045,7 @@
         <v>1042</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E48" s="2">
         <v>98</v>
@@ -5960,7 +6057,7 @@
         <v>1093</v>
       </c>
       <c r="H48" s="20" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I48" s="2">
         <v>4000</v>
@@ -5990,7 +6087,7 @@
         <v>1043</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E49" s="2">
         <v>98</v>
@@ -6002,7 +6099,7 @@
         <v>1094</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="I49" s="2">
         <v>4000</v>
@@ -6032,7 +6129,7 @@
         <v>1044</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E50" s="2">
         <v>98</v>
@@ -6044,7 +6141,7 @@
         <v>1095</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I50" s="2">
         <v>4000</v>
@@ -6074,7 +6171,7 @@
         <v>1045</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E51" s="2">
         <v>98</v>
@@ -6086,7 +6183,7 @@
         <v>1096</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="I51" s="2">
         <v>4000</v>
@@ -6116,7 +6213,7 @@
         <v>1046</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E52" s="2">
         <v>98</v>
@@ -6128,7 +6225,7 @@
         <v>1097</v>
       </c>
       <c r="H52" s="20" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I52" s="2">
         <v>4000</v>
@@ -6158,7 +6255,7 @@
         <v>1047</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E53" s="2">
         <v>98</v>
@@ -6170,7 +6267,7 @@
         <v>1098</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I53" s="2">
         <v>4000</v>
@@ -6200,7 +6297,7 @@
         <v>1048</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E54" s="2">
         <v>98</v>
@@ -6212,7 +6309,7 @@
         <v>1099</v>
       </c>
       <c r="H54" s="20" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="I54" s="2">
         <v>4000</v>
@@ -6242,7 +6339,7 @@
         <v>1049</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E55" s="2">
         <v>98</v>
@@ -6254,7 +6351,7 @@
         <v>1100</v>
       </c>
       <c r="H55" s="20" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I55" s="2">
         <v>4000</v>
@@ -6284,7 +6381,7 @@
         <v>1050</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E56" s="2">
         <v>98</v>
@@ -6296,7 +6393,7 @@
         <v>1101</v>
       </c>
       <c r="H56" s="20" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="I56" s="2">
         <v>4000</v>
@@ -6326,7 +6423,7 @@
         <v>1051</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E57" s="2">
         <v>98</v>
@@ -6338,7 +6435,7 @@
         <v>1102</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I57" s="2">
         <v>4000</v>
@@ -6368,7 +6465,7 @@
         <v>1052</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E58" s="2">
         <v>98</v>
@@ -6380,7 +6477,7 @@
         <v>1103</v>
       </c>
       <c r="H58" s="20" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="I58" s="2">
         <v>4000</v>
@@ -6410,7 +6507,7 @@
         <v>1053</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E59" s="2">
         <v>98</v>
@@ -6422,7 +6519,7 @@
         <v>1104</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="I59" s="2">
         <v>4000</v>
@@ -6452,7 +6549,7 @@
         <v>1054</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E60" s="12">
         <v>98</v>
@@ -6464,7 +6561,7 @@
         <v>1105</v>
       </c>
       <c r="H60" s="21" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="I60" s="12">
         <v>20000</v>
@@ -6493,7 +6590,7 @@
         <v>1055</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E61" s="2">
         <v>98</v>
@@ -6505,7 +6602,7 @@
         <v>1106</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="I61" s="2">
         <v>20000</v>
@@ -6534,7 +6631,7 @@
         <v>1056</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E62" s="2">
         <v>98</v>
@@ -6546,7 +6643,7 @@
         <v>1107</v>
       </c>
       <c r="H62" s="20" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="I62" s="2">
         <v>20000</v>
@@ -6575,7 +6672,7 @@
         <v>1057</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E63" s="2">
         <v>98</v>
@@ -6587,7 +6684,7 @@
         <v>1108</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I63" s="2">
         <v>20000</v>
@@ -6616,7 +6713,7 @@
         <v>1058</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E64" s="2">
         <v>98</v>
@@ -6628,7 +6725,7 @@
         <v>1109</v>
       </c>
       <c r="H64" s="20" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="I64" s="2">
         <v>20000</v>
@@ -6658,7 +6755,7 @@
         <v>1059</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E65" s="2">
         <v>98</v>
@@ -6670,7 +6767,7 @@
         <v>1110</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I65" s="2">
         <v>20000</v>
@@ -6699,7 +6796,7 @@
         <v>1060</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E66" s="2">
         <v>98</v>
@@ -6711,7 +6808,7 @@
         <v>1111</v>
       </c>
       <c r="H66" s="20" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I66" s="2">
         <v>20000</v>
@@ -6740,7 +6837,7 @@
         <v>1061</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E67" s="2">
         <v>98</v>
@@ -6752,7 +6849,7 @@
         <v>1112</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I67" s="2">
         <v>20000</v>
@@ -6781,7 +6878,7 @@
         <v>1062</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E68" s="2">
         <v>98</v>
@@ -6793,7 +6890,7 @@
         <v>1113</v>
       </c>
       <c r="H68" s="20" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="I68" s="2">
         <v>20000</v>
@@ -6822,7 +6919,7 @@
         <v>1063</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E69" s="2">
         <v>98</v>
@@ -6834,7 +6931,7 @@
         <v>1114</v>
       </c>
       <c r="H69" s="20" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I69" s="2">
         <v>20000</v>
@@ -6864,7 +6961,7 @@
         <v>1064</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E70" s="2">
         <v>98</v>
@@ -6876,7 +6973,7 @@
         <v>1115</v>
       </c>
       <c r="H70" s="20" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I70" s="2">
         <v>20000</v>
@@ -6906,7 +7003,7 @@
         <v>1065</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E71" s="2">
         <v>98</v>
@@ -6918,7 +7015,7 @@
         <v>1116</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="I71" s="2">
         <v>20000</v>
@@ -6948,7 +7045,7 @@
         <v>1066</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E72" s="2">
         <v>98</v>
@@ -6960,7 +7057,7 @@
         <v>1117</v>
       </c>
       <c r="H72" s="20" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="I72" s="2">
         <v>20000</v>
@@ -6990,7 +7087,7 @@
         <v>1067</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E73" s="2">
         <v>98</v>
@@ -7002,7 +7099,7 @@
         <v>1118</v>
       </c>
       <c r="H73" s="20" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="I73" s="2">
         <v>20000</v>
@@ -7032,7 +7129,7 @@
         <v>1068</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E74" s="2">
         <v>98</v>
@@ -7044,7 +7141,7 @@
         <v>1119</v>
       </c>
       <c r="H74" s="20" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="I74" s="2">
         <v>20000</v>
@@ -7074,7 +7171,7 @@
         <v>1069</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E75" s="2">
         <v>98</v>
@@ -7086,7 +7183,7 @@
         <v>1120</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="I75" s="2">
         <v>20000</v>
@@ -7116,7 +7213,7 @@
         <v>1070</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E76" s="2">
         <v>98</v>
@@ -7128,7 +7225,7 @@
         <v>1121</v>
       </c>
       <c r="H76" s="20" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="I76" s="2">
         <v>20000</v>
@@ -7158,7 +7255,7 @@
         <v>1071</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E77" s="2">
         <v>98</v>
@@ -7170,7 +7267,7 @@
         <v>1122</v>
       </c>
       <c r="H77" s="20" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="I77" s="2">
         <v>20000</v>
@@ -7200,7 +7297,7 @@
         <v>1072</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E78" s="2">
         <v>98</v>
@@ -7212,7 +7309,7 @@
         <v>1123</v>
       </c>
       <c r="H78" s="20" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="I78" s="2">
         <v>20000</v>
@@ -7242,7 +7339,7 @@
         <v>1073</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E79" s="2">
         <v>98</v>
@@ -7254,7 +7351,7 @@
         <v>1124</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="I79" s="2">
         <v>20000</v>
@@ -7284,7 +7381,7 @@
         <v>1074</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E80" s="2">
         <v>98</v>
@@ -7296,7 +7393,7 @@
         <v>1125</v>
       </c>
       <c r="H80" s="20" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="I80" s="2">
         <v>20000</v>
@@ -7326,7 +7423,7 @@
         <v>1075</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E81" s="2">
         <v>98</v>
@@ -7338,7 +7435,7 @@
         <v>1126</v>
       </c>
       <c r="H81" s="20" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="I81" s="2">
         <v>20000</v>
@@ -7368,7 +7465,7 @@
         <v>1076</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E82" s="2">
         <v>98</v>
@@ -7380,7 +7477,7 @@
         <v>1127</v>
       </c>
       <c r="H82" s="20" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I82" s="2">
         <v>20000</v>
@@ -7410,7 +7507,7 @@
         <v>1077</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E83" s="2">
         <v>98</v>
@@ -7422,7 +7519,7 @@
         <v>1128</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="I83" s="2">
         <v>20000</v>
@@ -7452,7 +7549,7 @@
         <v>1078</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E84" s="2">
         <v>98</v>
@@ -7464,7 +7561,7 @@
         <v>1129</v>
       </c>
       <c r="H84" s="20" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I84" s="2">
         <v>20000</v>
@@ -7494,7 +7591,7 @@
         <v>1079</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E85" s="2">
         <v>98</v>
@@ -7506,7 +7603,7 @@
         <v>1130</v>
       </c>
       <c r="H85" s="20" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="I85" s="2">
         <v>20000</v>
@@ -7536,7 +7633,7 @@
         <v>1080</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E86" s="2">
         <v>98</v>
@@ -7548,7 +7645,7 @@
         <v>1131</v>
       </c>
       <c r="H86" s="20" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="I86" s="2">
         <v>20000</v>
@@ -7578,7 +7675,7 @@
         <v>1081</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E87" s="2">
         <v>98</v>
@@ -7590,7 +7687,7 @@
         <v>1132</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="I87" s="2">
         <v>20000</v>
@@ -7620,7 +7717,7 @@
         <v>1082</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E88" s="2">
         <v>98</v>
@@ -7632,7 +7729,7 @@
         <v>1133</v>
       </c>
       <c r="H88" s="20" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="I88" s="2">
         <v>20000</v>
@@ -7662,7 +7759,7 @@
         <v>1083</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E89" s="2">
         <v>98</v>
@@ -7674,7 +7771,7 @@
         <v>1134</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="I89" s="2">
         <v>20000</v>
@@ -7704,7 +7801,7 @@
         <v>1084</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E90" s="2">
         <v>98</v>
@@ -7716,7 +7813,7 @@
         <v>1135</v>
       </c>
       <c r="H90" s="20" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I90" s="2">
         <v>20000</v>
@@ -7746,7 +7843,7 @@
         <v>1085</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E91" s="2">
         <v>98</v>
@@ -7758,7 +7855,7 @@
         <v>1136</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="I91" s="2">
         <v>20000</v>
@@ -7788,7 +7885,7 @@
         <v>1086</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E92" s="2">
         <v>98</v>
@@ -7800,7 +7897,7 @@
         <v>1137</v>
       </c>
       <c r="H92" s="20" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="I92" s="2">
         <v>20000</v>
@@ -7830,7 +7927,7 @@
         <v>1087</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E93" s="2">
         <v>98</v>
@@ -7842,7 +7939,7 @@
         <v>1138</v>
       </c>
       <c r="H93" s="20" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="I93" s="2">
         <v>20000</v>
@@ -7872,7 +7969,7 @@
         <v>1088</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E94" s="2">
         <v>98</v>
@@ -7884,7 +7981,7 @@
         <v>1139</v>
       </c>
       <c r="H94" s="20" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="I94" s="2">
         <v>20000</v>
@@ -7914,7 +8011,7 @@
         <v>1089</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E95" s="12">
         <v>98</v>
@@ -7926,7 +8023,7 @@
         <v>1140</v>
       </c>
       <c r="H95" s="21" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I95" s="12">
         <v>30000</v>
@@ -7955,7 +8052,7 @@
         <v>1090</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E96" s="2">
         <v>98</v>
@@ -7967,7 +8064,7 @@
         <v>1141</v>
       </c>
       <c r="H96" s="20" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="I96" s="2">
         <v>30000</v>
@@ -7996,7 +8093,7 @@
         <v>1091</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E97" s="2">
         <v>98</v>
@@ -8008,7 +8105,7 @@
         <v>1142</v>
       </c>
       <c r="H97" s="20" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="I97" s="2">
         <v>30000</v>
@@ -8037,7 +8134,7 @@
         <v>1092</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E98" s="2">
         <v>98</v>
@@ -8049,7 +8146,7 @@
         <v>1143</v>
       </c>
       <c r="H98" s="20" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I98" s="2">
         <v>30000</v>
@@ -8078,7 +8175,7 @@
         <v>1093</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E99" s="2">
         <v>98</v>
@@ -8090,7 +8187,7 @@
         <v>1144</v>
       </c>
       <c r="H99" s="20" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="I99" s="2">
         <v>30000</v>
@@ -8120,7 +8217,7 @@
         <v>1094</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E100" s="2">
         <v>98</v>
@@ -8132,7 +8229,7 @@
         <v>1145</v>
       </c>
       <c r="H100" s="20" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="I100" s="2">
         <v>30000</v>
@@ -8161,7 +8258,7 @@
         <v>1095</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E101" s="2">
         <v>98</v>
@@ -8173,7 +8270,7 @@
         <v>1146</v>
       </c>
       <c r="H101" s="20" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="I101" s="2">
         <v>30000</v>
@@ -8202,7 +8299,7 @@
         <v>1096</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E102" s="2">
         <v>98</v>
@@ -8214,7 +8311,7 @@
         <v>1147</v>
       </c>
       <c r="H102" s="20" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="I102" s="2">
         <v>30000</v>
@@ -8243,7 +8340,7 @@
         <v>1097</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E103" s="2">
         <v>98</v>
@@ -8255,7 +8352,7 @@
         <v>1148</v>
       </c>
       <c r="H103" s="20" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="I103" s="2">
         <v>30000</v>
@@ -8284,7 +8381,7 @@
         <v>1098</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E104" s="2">
         <v>98</v>
@@ -8296,7 +8393,7 @@
         <v>1149</v>
       </c>
       <c r="H104" s="20" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="I104" s="2">
         <v>30000</v>
@@ -8326,7 +8423,7 @@
         <v>1099</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E105" s="2">
         <v>98</v>
@@ -8338,7 +8435,7 @@
         <v>1150</v>
       </c>
       <c r="H105" s="20" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I105" s="2">
         <v>30000</v>
@@ -8368,7 +8465,7 @@
         <v>1100</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E106" s="2">
         <v>98</v>
@@ -8380,7 +8477,7 @@
         <v>1151</v>
       </c>
       <c r="H106" s="20" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="I106" s="2">
         <v>30000</v>
@@ -8410,7 +8507,7 @@
         <v>1101</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E107" s="2">
         <v>98</v>
@@ -8422,7 +8519,7 @@
         <v>1152</v>
       </c>
       <c r="H107" s="20" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="I107" s="2">
         <v>30000</v>
@@ -8452,7 +8549,7 @@
         <v>1102</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E108" s="2">
         <v>98</v>
@@ -8464,7 +8561,7 @@
         <v>1153</v>
       </c>
       <c r="H108" s="20" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I108" s="2">
         <v>30000</v>
@@ -8494,7 +8591,7 @@
         <v>1103</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E109" s="2">
         <v>98</v>
@@ -8506,7 +8603,7 @@
         <v>1154</v>
       </c>
       <c r="H109" s="20" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I109" s="2">
         <v>30000</v>
@@ -8536,7 +8633,7 @@
         <v>1104</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E110" s="2">
         <v>98</v>
@@ -8548,7 +8645,7 @@
         <v>1155</v>
       </c>
       <c r="H110" s="20" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="I110" s="2">
         <v>30000</v>
@@ -8578,7 +8675,7 @@
         <v>1105</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E111" s="2">
         <v>98</v>
@@ -8590,7 +8687,7 @@
         <v>1156</v>
       </c>
       <c r="H111" s="20" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="I111" s="2">
         <v>30000</v>
@@ -8620,7 +8717,7 @@
         <v>1106</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E112" s="2">
         <v>98</v>
@@ -8632,7 +8729,7 @@
         <v>1157</v>
       </c>
       <c r="H112" s="20" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="I112" s="2">
         <v>30000</v>
@@ -8662,7 +8759,7 @@
         <v>1107</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E113" s="2">
         <v>98</v>
@@ -8674,7 +8771,7 @@
         <v>1158</v>
       </c>
       <c r="H113" s="20" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I113" s="2">
         <v>30000</v>
@@ -8704,7 +8801,7 @@
         <v>1108</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E114" s="2">
         <v>98</v>
@@ -8716,7 +8813,7 @@
         <v>1159</v>
       </c>
       <c r="H114" s="20" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="I114" s="2">
         <v>30000</v>
@@ -8746,7 +8843,7 @@
         <v>1109</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E115" s="2">
         <v>98</v>
@@ -8758,7 +8855,7 @@
         <v>1160</v>
       </c>
       <c r="H115" s="20" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="I115" s="2">
         <v>30000</v>
@@ -8788,7 +8885,7 @@
         <v>1110</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E116" s="2">
         <v>98</v>
@@ -8800,7 +8897,7 @@
         <v>1161</v>
       </c>
       <c r="H116" s="20" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I116" s="2">
         <v>30000</v>
@@ -8830,7 +8927,7 @@
         <v>1111</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E117" s="2">
         <v>98</v>
@@ -8842,7 +8939,7 @@
         <v>1162</v>
       </c>
       <c r="H117" s="20" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="I117" s="2">
         <v>30000</v>
@@ -8872,7 +8969,7 @@
         <v>1112</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E118" s="2">
         <v>98</v>
@@ -8884,7 +8981,7 @@
         <v>1163</v>
       </c>
       <c r="H118" s="20" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I118" s="2">
         <v>30000</v>
@@ -8914,7 +9011,7 @@
         <v>1113</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E119" s="2">
         <v>98</v>
@@ -8926,7 +9023,7 @@
         <v>1164</v>
       </c>
       <c r="H119" s="20" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="I119" s="2">
         <v>30000</v>
@@ -8956,7 +9053,7 @@
         <v>1114</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E120" s="2">
         <v>98</v>
@@ -8968,7 +9065,7 @@
         <v>1165</v>
       </c>
       <c r="H120" s="20" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="I120" s="2">
         <v>30000</v>
@@ -8998,7 +9095,7 @@
         <v>1115</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E121" s="2">
         <v>98</v>
@@ -9010,7 +9107,7 @@
         <v>1166</v>
       </c>
       <c r="H121" s="20" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="I121" s="2">
         <v>30000</v>
@@ -9040,7 +9137,7 @@
         <v>1116</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E122" s="2">
         <v>98</v>
@@ -9052,7 +9149,7 @@
         <v>1167</v>
       </c>
       <c r="H122" s="20" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="I122" s="2">
         <v>30000</v>
@@ -9082,7 +9179,7 @@
         <v>1117</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E123" s="2">
         <v>98</v>
@@ -9094,7 +9191,7 @@
         <v>1168</v>
       </c>
       <c r="H123" s="20" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="I123" s="2">
         <v>30000</v>
@@ -9124,7 +9221,7 @@
         <v>1118</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E124" s="2">
         <v>98</v>
@@ -9136,7 +9233,7 @@
         <v>1169</v>
       </c>
       <c r="H124" s="20" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="I124" s="2">
         <v>30000</v>
@@ -9166,7 +9263,7 @@
         <v>1119</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E125" s="2">
         <v>98</v>
@@ -9178,7 +9275,7 @@
         <v>1170</v>
       </c>
       <c r="H125" s="20" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="I125" s="2">
         <v>30000</v>
@@ -9208,7 +9305,7 @@
         <v>1120</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E126" s="2">
         <v>98</v>
@@ -9220,7 +9317,7 @@
         <v>1171</v>
       </c>
       <c r="H126" s="20" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="I126" s="2">
         <v>30000</v>
@@ -9250,7 +9347,7 @@
         <v>1121</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E127" s="2">
         <v>98</v>
@@ -9262,7 +9359,7 @@
         <v>1172</v>
       </c>
       <c r="H127" s="20" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="I127" s="2">
         <v>30000</v>
@@ -9292,7 +9389,7 @@
         <v>1122</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E128" s="2">
         <v>98</v>
@@ -9304,7 +9401,7 @@
         <v>1173</v>
       </c>
       <c r="H128" s="20" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="I128" s="2">
         <v>30000</v>
@@ -9334,7 +9431,7 @@
         <v>1123</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E129" s="2">
         <v>98</v>
@@ -9346,7 +9443,7 @@
         <v>1174</v>
       </c>
       <c r="H129" s="20" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="I129" s="2">
         <v>30000</v>
@@ -9561,7 +9658,7 @@
         <v>2000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -9573,7 +9670,7 @@
         <v>1070</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="I6" s="2">
         <v>120000</v>
@@ -9605,7 +9702,7 @@
         <v>2001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -9617,7 +9714,7 @@
         <v>1071</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="I7" s="2">
         <v>120000</v>
@@ -9649,7 +9746,7 @@
         <v>2002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -9661,7 +9758,7 @@
         <v>1072</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="I8" s="2">
         <v>120000</v>
@@ -9693,7 +9790,7 @@
         <v>2003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -9705,7 +9802,7 @@
         <v>1073</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="I9" s="2">
         <v>120000</v>
@@ -9737,7 +9834,7 @@
         <v>2004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -9749,7 +9846,7 @@
         <v>1074</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I10" s="2">
         <v>120000</v>
@@ -9781,7 +9878,7 @@
         <v>2005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -9793,7 +9890,7 @@
         <v>1104</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I11" s="2">
         <v>20000</v>
@@ -9839,7 +9936,7 @@
         <v>2006</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -9851,7 +9948,7 @@
         <v>1105</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="I14" s="2">
         <v>360000</v>
@@ -9883,7 +9980,7 @@
         <v>2007</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -9895,7 +9992,7 @@
         <v>1106</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="I15" s="2">
         <v>360000</v>
@@ -9927,7 +10024,7 @@
         <v>2008</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -9939,7 +10036,7 @@
         <v>1107</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="I16" s="2">
         <v>360000</v>
@@ -9971,7 +10068,7 @@
         <v>2009</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -9983,7 +10080,7 @@
         <v>1108</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="I17" s="2">
         <v>360000</v>
@@ -10015,7 +10112,7 @@
         <v>2010</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -10027,7 +10124,7 @@
         <v>1139</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="I18" s="2">
         <v>360000</v>
@@ -10059,7 +10156,7 @@
         <v>2011</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -10071,7 +10168,7 @@
         <v>1139</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -10110,7 +10207,7 @@
         <v>2012</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -10122,7 +10219,7 @@
         <v>1140</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="I21" s="2">
         <v>360000</v>
@@ -10154,7 +10251,7 @@
         <v>2013</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -10166,7 +10263,7 @@
         <v>1141</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="I22" s="2">
         <v>360000</v>
@@ -10198,7 +10295,7 @@
         <v>2014</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -10210,7 +10307,7 @@
         <v>1142</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="I23" s="2">
         <v>360000</v>
@@ -10242,7 +10339,7 @@
         <v>2015</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -10254,7 +10351,7 @@
         <v>1143</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="I24" s="2">
         <v>360000</v>
@@ -10286,7 +10383,7 @@
         <v>2016</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -10298,7 +10395,7 @@
         <v>1174</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="I25" s="2">
         <v>360000</v>
@@ -10330,7 +10427,7 @@
         <v>2017</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -10342,7 +10439,7 @@
         <v>1174</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="I26" s="2">
         <v>180000</v>
@@ -10371,16 +10468,16 @@
     </row>
     <row r="27" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C27" s="2">
         <v>2018</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -10392,7 +10489,7 @@
         <v>1174</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="395">
   <si>
     <t>_id</t>
   </si>
@@ -502,6 +502,9 @@
     <t>3002</t>
   </si>
   <si>
+    <t>第三时装</t>
+  </si>
+  <si>
     <t>3003</t>
   </si>
   <si>
@@ -509,6 +512,9 @@
   </si>
   <si>
     <t>120000</t>
+  </si>
+  <si>
+    <t>第四时装</t>
   </si>
   <si>
     <t>3004</t>
@@ -1640,12 +1646,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3514,7 +3520,7 @@
         <v>303</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E28" s="2">
         <v>98</v>
@@ -3526,13 +3532,13 @@
         <v>2000</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I28" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J28" s="18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K28" s="11">
         <v>0</v>
@@ -3558,7 +3564,7 @@
         <v>304</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -3570,10 +3576,10 @@
         <v>2000</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J29" s="18" t="s">
         <v>78</v>
@@ -3603,7 +3609,7 @@
         <v>801</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E31" s="2">
         <v>98</v>
@@ -3615,7 +3621,7 @@
         <v>2000</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I31" s="19" t="s">
         <v>50</v>
@@ -3647,7 +3653,7 @@
         <v>802</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E32" s="2">
         <v>98</v>
@@ -3659,13 +3665,13 @@
         <v>2000</v>
       </c>
       <c r="H32" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I32" s="18" t="s">
         <v>50</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K32" s="11">
         <v>0</v>
@@ -3691,7 +3697,7 @@
         <v>803</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
@@ -3703,13 +3709,13 @@
         <v>2000</v>
       </c>
       <c r="H33" s="19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I33" s="18" t="s">
         <v>50</v>
       </c>
       <c r="J33" s="18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K33" s="11">
         <v>0</v>
@@ -3744,7 +3750,7 @@
         <v>804</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
@@ -3756,13 +3762,13 @@
         <v>2000</v>
       </c>
       <c r="H35" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I35" s="19" t="s">
         <v>59</v>
       </c>
       <c r="J35" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K35" s="11">
         <v>0</v>
@@ -3788,7 +3794,7 @@
         <v>805</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -3800,13 +3806,13 @@
         <v>2000</v>
       </c>
       <c r="H36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I36" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J36" s="18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K36" s="11">
         <v>0</v>
@@ -3832,7 +3838,7 @@
         <v>806</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -3844,13 +3850,13 @@
         <v>2000</v>
       </c>
       <c r="H37" s="19" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J37" s="18" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K37" s="11">
         <v>0</v>
@@ -3876,7 +3882,7 @@
         <v>807</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E38" s="2">
         <v>98</v>
@@ -3888,13 +3894,13 @@
         <v>2000</v>
       </c>
       <c r="H38" s="19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J38" s="18" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K38" s="11">
         <v>0</v>
@@ -3920,7 +3926,7 @@
         <v>808</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E39" s="2">
         <v>98</v>
@@ -3932,13 +3938,13 @@
         <v>2000</v>
       </c>
       <c r="H39" s="19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I39" s="19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J39" s="18" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K39" s="11">
         <v>0</v>
@@ -3980,7 +3986,7 @@
         <v>991</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E41" s="2">
         <v>99</v>
@@ -3992,7 +3998,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I41" s="11">
         <v>0</v>
@@ -4024,7 +4030,7 @@
         <v>992</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E42" s="2">
         <v>101</v>
@@ -4036,7 +4042,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I42" s="11">
         <v>0</v>
@@ -4308,7 +4314,7 @@
         <v>1000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -4320,7 +4326,7 @@
         <v>1051</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I6" s="2">
         <v>40000</v>
@@ -4349,7 +4355,7 @@
         <v>1001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -4361,7 +4367,7 @@
         <v>1052</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I7" s="2">
         <v>40000</v>
@@ -4390,7 +4396,7 @@
         <v>1002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -4402,7 +4408,7 @@
         <v>1053</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I8" s="2">
         <v>40000</v>
@@ -4431,7 +4437,7 @@
         <v>1003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -4443,7 +4449,7 @@
         <v>1054</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I9" s="2">
         <v>40000</v>
@@ -4472,7 +4478,7 @@
         <v>1004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -4484,7 +4490,7 @@
         <v>1055</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I10" s="2">
         <v>40000</v>
@@ -4513,7 +4519,7 @@
         <v>1005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -4525,7 +4531,7 @@
         <v>1056</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I11" s="2">
         <v>40000</v>
@@ -4554,7 +4560,7 @@
         <v>1006</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
@@ -4566,7 +4572,7 @@
         <v>1057</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I12" s="2">
         <v>40000</v>
@@ -4595,7 +4601,7 @@
         <v>1007</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
@@ -4607,7 +4613,7 @@
         <v>1058</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I13" s="2">
         <v>40000</v>
@@ -4636,7 +4642,7 @@
         <v>1008</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -4648,7 +4654,7 @@
         <v>1059</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I14" s="2">
         <v>40000</v>
@@ -4677,7 +4683,7 @@
         <v>1009</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -4689,7 +4695,7 @@
         <v>1060</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I15" s="2">
         <v>40000</v>
@@ -4718,7 +4724,7 @@
         <v>1010</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -4730,7 +4736,7 @@
         <v>1061</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I16" s="2">
         <v>40000</v>
@@ -4759,7 +4765,7 @@
         <v>1011</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -4771,7 +4777,7 @@
         <v>1062</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I17" s="2">
         <v>40000</v>
@@ -4800,7 +4806,7 @@
         <v>1012</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -4812,7 +4818,7 @@
         <v>1063</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I18" s="2">
         <v>40000</v>
@@ -4841,7 +4847,7 @@
         <v>1013</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -4853,7 +4859,7 @@
         <v>1064</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -4882,7 +4888,7 @@
         <v>1014</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E20" s="2">
         <v>98</v>
@@ -4894,7 +4900,7 @@
         <v>1065</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I20" s="2">
         <v>40000</v>
@@ -4923,7 +4929,7 @@
         <v>1015</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -4935,7 +4941,7 @@
         <v>1066</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I21" s="2">
         <v>40000</v>
@@ -4964,7 +4970,7 @@
         <v>1016</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -4976,7 +4982,7 @@
         <v>1067</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I22" s="2">
         <v>40000</v>
@@ -5005,7 +5011,7 @@
         <v>1017</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -5017,7 +5023,7 @@
         <v>1068</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I23" s="2">
         <v>40000</v>
@@ -5046,7 +5052,7 @@
         <v>1018</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -5058,7 +5064,7 @@
         <v>1069</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I24" s="2">
         <v>40000</v>
@@ -5087,7 +5093,7 @@
         <v>1019</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -5099,7 +5105,7 @@
         <v>1070</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I25" s="2">
         <v>40000</v>
@@ -5128,7 +5134,7 @@
         <v>1020</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -5140,7 +5146,7 @@
         <v>1071</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I26" s="2">
         <v>40000</v>
@@ -5169,7 +5175,7 @@
         <v>1021</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -5181,7 +5187,7 @@
         <v>1072</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>
@@ -5210,7 +5216,7 @@
         <v>1022</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E28" s="2">
         <v>98</v>
@@ -5222,7 +5228,7 @@
         <v>1073</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I28" s="2">
         <v>40000</v>
@@ -5251,7 +5257,7 @@
         <v>1023</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -5263,7 +5269,7 @@
         <v>1074</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I29" s="2">
         <v>40000</v>
@@ -5293,7 +5299,7 @@
         <v>1024</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E30" s="2">
         <v>98</v>
@@ -5305,7 +5311,7 @@
         <v>1075</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I30" s="2">
         <v>4000</v>
@@ -5334,7 +5340,7 @@
         <v>1025</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E31" s="2">
         <v>98</v>
@@ -5346,7 +5352,7 @@
         <v>1076</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I31" s="2">
         <v>4000</v>
@@ -5375,7 +5381,7 @@
         <v>1026</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E32" s="2">
         <v>98</v>
@@ -5387,7 +5393,7 @@
         <v>1077</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I32" s="2">
         <v>4000</v>
@@ -5416,7 +5422,7 @@
         <v>1027</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
@@ -5428,7 +5434,7 @@
         <v>1078</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I33" s="2">
         <v>4000</v>
@@ -5457,7 +5463,7 @@
         <v>1028</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E34" s="2">
         <v>98</v>
@@ -5469,7 +5475,7 @@
         <v>1079</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I34" s="2">
         <v>4000</v>
@@ -5499,7 +5505,7 @@
         <v>1029</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
@@ -5511,7 +5517,7 @@
         <v>1080</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I35" s="2">
         <v>4000</v>
@@ -5541,7 +5547,7 @@
         <v>1030</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -5553,7 +5559,7 @@
         <v>1081</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I36" s="2">
         <v>4000</v>
@@ -5583,7 +5589,7 @@
         <v>1031</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -5595,7 +5601,7 @@
         <v>1082</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I37" s="2">
         <v>4000</v>
@@ -5625,7 +5631,7 @@
         <v>1032</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E38" s="2">
         <v>98</v>
@@ -5637,7 +5643,7 @@
         <v>1083</v>
       </c>
       <c r="H38" s="20" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I38" s="2">
         <v>4000</v>
@@ -5667,7 +5673,7 @@
         <v>1033</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E39" s="2">
         <v>98</v>
@@ -5679,7 +5685,7 @@
         <v>1084</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I39" s="2">
         <v>4000</v>
@@ -5709,7 +5715,7 @@
         <v>1034</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E40" s="2">
         <v>98</v>
@@ -5721,7 +5727,7 @@
         <v>1085</v>
       </c>
       <c r="H40" s="20" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I40" s="2">
         <v>4000</v>
@@ -5751,7 +5757,7 @@
         <v>1035</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E41" s="2">
         <v>98</v>
@@ -5763,7 +5769,7 @@
         <v>1086</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I41" s="2">
         <v>4000</v>
@@ -5793,7 +5799,7 @@
         <v>1036</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E42" s="2">
         <v>98</v>
@@ -5805,7 +5811,7 @@
         <v>1087</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I42" s="2">
         <v>4000</v>
@@ -5835,7 +5841,7 @@
         <v>1037</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E43" s="2">
         <v>98</v>
@@ -5847,7 +5853,7 @@
         <v>1088</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I43" s="2">
         <v>4000</v>
@@ -5877,7 +5883,7 @@
         <v>1038</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E44" s="2">
         <v>98</v>
@@ -5889,7 +5895,7 @@
         <v>1089</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I44" s="2">
         <v>4000</v>
@@ -5919,7 +5925,7 @@
         <v>1039</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E45" s="2">
         <v>98</v>
@@ -5931,7 +5937,7 @@
         <v>1090</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I45" s="2">
         <v>4000</v>
@@ -5961,7 +5967,7 @@
         <v>1040</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E46" s="2">
         <v>98</v>
@@ -5973,7 +5979,7 @@
         <v>1091</v>
       </c>
       <c r="H46" s="20" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I46" s="2">
         <v>4000</v>
@@ -6003,7 +6009,7 @@
         <v>1041</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E47" s="2">
         <v>98</v>
@@ -6015,7 +6021,7 @@
         <v>1092</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I47" s="2">
         <v>4000</v>
@@ -6045,7 +6051,7 @@
         <v>1042</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E48" s="2">
         <v>98</v>
@@ -6057,7 +6063,7 @@
         <v>1093</v>
       </c>
       <c r="H48" s="20" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I48" s="2">
         <v>4000</v>
@@ -6087,7 +6093,7 @@
         <v>1043</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E49" s="2">
         <v>98</v>
@@ -6099,7 +6105,7 @@
         <v>1094</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I49" s="2">
         <v>4000</v>
@@ -6129,7 +6135,7 @@
         <v>1044</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E50" s="2">
         <v>98</v>
@@ -6141,7 +6147,7 @@
         <v>1095</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I50" s="2">
         <v>4000</v>
@@ -6171,7 +6177,7 @@
         <v>1045</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E51" s="2">
         <v>98</v>
@@ -6183,7 +6189,7 @@
         <v>1096</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I51" s="2">
         <v>4000</v>
@@ -6213,7 +6219,7 @@
         <v>1046</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E52" s="2">
         <v>98</v>
@@ -6225,7 +6231,7 @@
         <v>1097</v>
       </c>
       <c r="H52" s="20" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I52" s="2">
         <v>4000</v>
@@ -6255,7 +6261,7 @@
         <v>1047</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E53" s="2">
         <v>98</v>
@@ -6267,7 +6273,7 @@
         <v>1098</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I53" s="2">
         <v>4000</v>
@@ -6297,7 +6303,7 @@
         <v>1048</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E54" s="2">
         <v>98</v>
@@ -6309,7 +6315,7 @@
         <v>1099</v>
       </c>
       <c r="H54" s="20" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I54" s="2">
         <v>4000</v>
@@ -6339,7 +6345,7 @@
         <v>1049</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E55" s="2">
         <v>98</v>
@@ -6351,7 +6357,7 @@
         <v>1100</v>
       </c>
       <c r="H55" s="20" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I55" s="2">
         <v>4000</v>
@@ -6381,7 +6387,7 @@
         <v>1050</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E56" s="2">
         <v>98</v>
@@ -6393,7 +6399,7 @@
         <v>1101</v>
       </c>
       <c r="H56" s="20" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I56" s="2">
         <v>4000</v>
@@ -6423,7 +6429,7 @@
         <v>1051</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E57" s="2">
         <v>98</v>
@@ -6435,7 +6441,7 @@
         <v>1102</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I57" s="2">
         <v>4000</v>
@@ -6465,7 +6471,7 @@
         <v>1052</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E58" s="2">
         <v>98</v>
@@ -6477,7 +6483,7 @@
         <v>1103</v>
       </c>
       <c r="H58" s="20" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I58" s="2">
         <v>4000</v>
@@ -6507,7 +6513,7 @@
         <v>1053</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E59" s="2">
         <v>98</v>
@@ -6519,7 +6525,7 @@
         <v>1104</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I59" s="2">
         <v>4000</v>
@@ -6549,7 +6555,7 @@
         <v>1054</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E60" s="12">
         <v>98</v>
@@ -6561,7 +6567,7 @@
         <v>1105</v>
       </c>
       <c r="H60" s="21" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I60" s="12">
         <v>20000</v>
@@ -6590,7 +6596,7 @@
         <v>1055</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E61" s="2">
         <v>98</v>
@@ -6602,7 +6608,7 @@
         <v>1106</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I61" s="2">
         <v>20000</v>
@@ -6631,7 +6637,7 @@
         <v>1056</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E62" s="2">
         <v>98</v>
@@ -6643,7 +6649,7 @@
         <v>1107</v>
       </c>
       <c r="H62" s="20" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I62" s="2">
         <v>20000</v>
@@ -6672,7 +6678,7 @@
         <v>1057</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E63" s="2">
         <v>98</v>
@@ -6684,7 +6690,7 @@
         <v>1108</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I63" s="2">
         <v>20000</v>
@@ -6713,7 +6719,7 @@
         <v>1058</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E64" s="2">
         <v>98</v>
@@ -6725,7 +6731,7 @@
         <v>1109</v>
       </c>
       <c r="H64" s="20" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I64" s="2">
         <v>20000</v>
@@ -6755,7 +6761,7 @@
         <v>1059</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E65" s="2">
         <v>98</v>
@@ -6767,7 +6773,7 @@
         <v>1110</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I65" s="2">
         <v>20000</v>
@@ -6796,7 +6802,7 @@
         <v>1060</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E66" s="2">
         <v>98</v>
@@ -6808,7 +6814,7 @@
         <v>1111</v>
       </c>
       <c r="H66" s="20" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I66" s="2">
         <v>20000</v>
@@ -6837,7 +6843,7 @@
         <v>1061</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E67" s="2">
         <v>98</v>
@@ -6849,7 +6855,7 @@
         <v>1112</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I67" s="2">
         <v>20000</v>
@@ -6878,7 +6884,7 @@
         <v>1062</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E68" s="2">
         <v>98</v>
@@ -6890,7 +6896,7 @@
         <v>1113</v>
       </c>
       <c r="H68" s="20" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I68" s="2">
         <v>20000</v>
@@ -6919,7 +6925,7 @@
         <v>1063</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E69" s="2">
         <v>98</v>
@@ -6931,7 +6937,7 @@
         <v>1114</v>
       </c>
       <c r="H69" s="20" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I69" s="2">
         <v>20000</v>
@@ -6961,7 +6967,7 @@
         <v>1064</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E70" s="2">
         <v>98</v>
@@ -6973,7 +6979,7 @@
         <v>1115</v>
       </c>
       <c r="H70" s="20" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I70" s="2">
         <v>20000</v>
@@ -7003,7 +7009,7 @@
         <v>1065</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E71" s="2">
         <v>98</v>
@@ -7015,7 +7021,7 @@
         <v>1116</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I71" s="2">
         <v>20000</v>
@@ -7045,7 +7051,7 @@
         <v>1066</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E72" s="2">
         <v>98</v>
@@ -7057,7 +7063,7 @@
         <v>1117</v>
       </c>
       <c r="H72" s="20" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I72" s="2">
         <v>20000</v>
@@ -7087,7 +7093,7 @@
         <v>1067</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E73" s="2">
         <v>98</v>
@@ -7099,7 +7105,7 @@
         <v>1118</v>
       </c>
       <c r="H73" s="20" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I73" s="2">
         <v>20000</v>
@@ -7129,7 +7135,7 @@
         <v>1068</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E74" s="2">
         <v>98</v>
@@ -7141,7 +7147,7 @@
         <v>1119</v>
       </c>
       <c r="H74" s="20" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I74" s="2">
         <v>20000</v>
@@ -7171,7 +7177,7 @@
         <v>1069</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E75" s="2">
         <v>98</v>
@@ -7183,7 +7189,7 @@
         <v>1120</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="I75" s="2">
         <v>20000</v>
@@ -7213,7 +7219,7 @@
         <v>1070</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E76" s="2">
         <v>98</v>
@@ -7225,7 +7231,7 @@
         <v>1121</v>
       </c>
       <c r="H76" s="20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I76" s="2">
         <v>20000</v>
@@ -7255,7 +7261,7 @@
         <v>1071</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E77" s="2">
         <v>98</v>
@@ -7267,7 +7273,7 @@
         <v>1122</v>
       </c>
       <c r="H77" s="20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I77" s="2">
         <v>20000</v>
@@ -7297,7 +7303,7 @@
         <v>1072</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E78" s="2">
         <v>98</v>
@@ -7309,7 +7315,7 @@
         <v>1123</v>
       </c>
       <c r="H78" s="20" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I78" s="2">
         <v>20000</v>
@@ -7339,7 +7345,7 @@
         <v>1073</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E79" s="2">
         <v>98</v>
@@ -7351,7 +7357,7 @@
         <v>1124</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="I79" s="2">
         <v>20000</v>
@@ -7381,7 +7387,7 @@
         <v>1074</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E80" s="2">
         <v>98</v>
@@ -7393,7 +7399,7 @@
         <v>1125</v>
       </c>
       <c r="H80" s="20" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I80" s="2">
         <v>20000</v>
@@ -7423,7 +7429,7 @@
         <v>1075</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E81" s="2">
         <v>98</v>
@@ -7435,7 +7441,7 @@
         <v>1126</v>
       </c>
       <c r="H81" s="20" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I81" s="2">
         <v>20000</v>
@@ -7465,7 +7471,7 @@
         <v>1076</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E82" s="2">
         <v>98</v>
@@ -7477,7 +7483,7 @@
         <v>1127</v>
       </c>
       <c r="H82" s="20" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I82" s="2">
         <v>20000</v>
@@ -7507,7 +7513,7 @@
         <v>1077</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E83" s="2">
         <v>98</v>
@@ -7519,7 +7525,7 @@
         <v>1128</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I83" s="2">
         <v>20000</v>
@@ -7549,7 +7555,7 @@
         <v>1078</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E84" s="2">
         <v>98</v>
@@ -7561,7 +7567,7 @@
         <v>1129</v>
       </c>
       <c r="H84" s="20" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I84" s="2">
         <v>20000</v>
@@ -7591,7 +7597,7 @@
         <v>1079</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E85" s="2">
         <v>98</v>
@@ -7603,7 +7609,7 @@
         <v>1130</v>
       </c>
       <c r="H85" s="20" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I85" s="2">
         <v>20000</v>
@@ -7633,7 +7639,7 @@
         <v>1080</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E86" s="2">
         <v>98</v>
@@ -7645,7 +7651,7 @@
         <v>1131</v>
       </c>
       <c r="H86" s="20" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I86" s="2">
         <v>20000</v>
@@ -7675,7 +7681,7 @@
         <v>1081</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E87" s="2">
         <v>98</v>
@@ -7687,7 +7693,7 @@
         <v>1132</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I87" s="2">
         <v>20000</v>
@@ -7717,7 +7723,7 @@
         <v>1082</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E88" s="2">
         <v>98</v>
@@ -7729,7 +7735,7 @@
         <v>1133</v>
       </c>
       <c r="H88" s="20" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I88" s="2">
         <v>20000</v>
@@ -7759,7 +7765,7 @@
         <v>1083</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E89" s="2">
         <v>98</v>
@@ -7771,7 +7777,7 @@
         <v>1134</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I89" s="2">
         <v>20000</v>
@@ -7801,7 +7807,7 @@
         <v>1084</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E90" s="2">
         <v>98</v>
@@ -7813,7 +7819,7 @@
         <v>1135</v>
       </c>
       <c r="H90" s="20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I90" s="2">
         <v>20000</v>
@@ -7843,7 +7849,7 @@
         <v>1085</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E91" s="2">
         <v>98</v>
@@ -7855,7 +7861,7 @@
         <v>1136</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I91" s="2">
         <v>20000</v>
@@ -7885,7 +7891,7 @@
         <v>1086</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E92" s="2">
         <v>98</v>
@@ -7897,7 +7903,7 @@
         <v>1137</v>
       </c>
       <c r="H92" s="20" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I92" s="2">
         <v>20000</v>
@@ -7927,7 +7933,7 @@
         <v>1087</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E93" s="2">
         <v>98</v>
@@ -7939,7 +7945,7 @@
         <v>1138</v>
       </c>
       <c r="H93" s="20" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I93" s="2">
         <v>20000</v>
@@ -7969,7 +7975,7 @@
         <v>1088</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E94" s="2">
         <v>98</v>
@@ -7981,7 +7987,7 @@
         <v>1139</v>
       </c>
       <c r="H94" s="20" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I94" s="2">
         <v>20000</v>
@@ -8011,7 +8017,7 @@
         <v>1089</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E95" s="12">
         <v>98</v>
@@ -8023,7 +8029,7 @@
         <v>1140</v>
       </c>
       <c r="H95" s="21" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I95" s="12">
         <v>30000</v>
@@ -8052,7 +8058,7 @@
         <v>1090</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E96" s="2">
         <v>98</v>
@@ -8064,7 +8070,7 @@
         <v>1141</v>
       </c>
       <c r="H96" s="20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I96" s="2">
         <v>30000</v>
@@ -8093,7 +8099,7 @@
         <v>1091</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E97" s="2">
         <v>98</v>
@@ -8105,7 +8111,7 @@
         <v>1142</v>
       </c>
       <c r="H97" s="20" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I97" s="2">
         <v>30000</v>
@@ -8134,7 +8140,7 @@
         <v>1092</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E98" s="2">
         <v>98</v>
@@ -8146,7 +8152,7 @@
         <v>1143</v>
       </c>
       <c r="H98" s="20" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I98" s="2">
         <v>30000</v>
@@ -8175,7 +8181,7 @@
         <v>1093</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E99" s="2">
         <v>98</v>
@@ -8187,7 +8193,7 @@
         <v>1144</v>
       </c>
       <c r="H99" s="20" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="I99" s="2">
         <v>30000</v>
@@ -8217,7 +8223,7 @@
         <v>1094</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E100" s="2">
         <v>98</v>
@@ -8229,7 +8235,7 @@
         <v>1145</v>
       </c>
       <c r="H100" s="20" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I100" s="2">
         <v>30000</v>
@@ -8258,7 +8264,7 @@
         <v>1095</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E101" s="2">
         <v>98</v>
@@ -8270,7 +8276,7 @@
         <v>1146</v>
       </c>
       <c r="H101" s="20" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I101" s="2">
         <v>30000</v>
@@ -8299,7 +8305,7 @@
         <v>1096</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E102" s="2">
         <v>98</v>
@@ -8311,7 +8317,7 @@
         <v>1147</v>
       </c>
       <c r="H102" s="20" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I102" s="2">
         <v>30000</v>
@@ -8340,7 +8346,7 @@
         <v>1097</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E103" s="2">
         <v>98</v>
@@ -8352,7 +8358,7 @@
         <v>1148</v>
       </c>
       <c r="H103" s="20" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I103" s="2">
         <v>30000</v>
@@ -8381,7 +8387,7 @@
         <v>1098</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E104" s="2">
         <v>98</v>
@@ -8393,7 +8399,7 @@
         <v>1149</v>
       </c>
       <c r="H104" s="20" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I104" s="2">
         <v>30000</v>
@@ -8423,7 +8429,7 @@
         <v>1099</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E105" s="2">
         <v>98</v>
@@ -8435,7 +8441,7 @@
         <v>1150</v>
       </c>
       <c r="H105" s="20" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I105" s="2">
         <v>30000</v>
@@ -8465,7 +8471,7 @@
         <v>1100</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E106" s="2">
         <v>98</v>
@@ -8477,7 +8483,7 @@
         <v>1151</v>
       </c>
       <c r="H106" s="20" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I106" s="2">
         <v>30000</v>
@@ -8507,7 +8513,7 @@
         <v>1101</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E107" s="2">
         <v>98</v>
@@ -8519,7 +8525,7 @@
         <v>1152</v>
       </c>
       <c r="H107" s="20" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I107" s="2">
         <v>30000</v>
@@ -8549,7 +8555,7 @@
         <v>1102</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E108" s="2">
         <v>98</v>
@@ -8561,7 +8567,7 @@
         <v>1153</v>
       </c>
       <c r="H108" s="20" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I108" s="2">
         <v>30000</v>
@@ -8591,7 +8597,7 @@
         <v>1103</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E109" s="2">
         <v>98</v>
@@ -8603,7 +8609,7 @@
         <v>1154</v>
       </c>
       <c r="H109" s="20" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I109" s="2">
         <v>30000</v>
@@ -8633,7 +8639,7 @@
         <v>1104</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E110" s="2">
         <v>98</v>
@@ -8645,7 +8651,7 @@
         <v>1155</v>
       </c>
       <c r="H110" s="20" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="I110" s="2">
         <v>30000</v>
@@ -8675,7 +8681,7 @@
         <v>1105</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E111" s="2">
         <v>98</v>
@@ -8687,7 +8693,7 @@
         <v>1156</v>
       </c>
       <c r="H111" s="20" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I111" s="2">
         <v>30000</v>
@@ -8717,7 +8723,7 @@
         <v>1106</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E112" s="2">
         <v>98</v>
@@ -8729,7 +8735,7 @@
         <v>1157</v>
       </c>
       <c r="H112" s="20" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I112" s="2">
         <v>30000</v>
@@ -8759,7 +8765,7 @@
         <v>1107</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E113" s="2">
         <v>98</v>
@@ -8771,7 +8777,7 @@
         <v>1158</v>
       </c>
       <c r="H113" s="20" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I113" s="2">
         <v>30000</v>
@@ -8801,7 +8807,7 @@
         <v>1108</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E114" s="2">
         <v>98</v>
@@ -8813,7 +8819,7 @@
         <v>1159</v>
       </c>
       <c r="H114" s="20" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I114" s="2">
         <v>30000</v>
@@ -8843,7 +8849,7 @@
         <v>1109</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E115" s="2">
         <v>98</v>
@@ -8855,7 +8861,7 @@
         <v>1160</v>
       </c>
       <c r="H115" s="20" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I115" s="2">
         <v>30000</v>
@@ -8885,7 +8891,7 @@
         <v>1110</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E116" s="2">
         <v>98</v>
@@ -8897,7 +8903,7 @@
         <v>1161</v>
       </c>
       <c r="H116" s="20" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I116" s="2">
         <v>30000</v>
@@ -8927,7 +8933,7 @@
         <v>1111</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E117" s="2">
         <v>98</v>
@@ -8939,7 +8945,7 @@
         <v>1162</v>
       </c>
       <c r="H117" s="20" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I117" s="2">
         <v>30000</v>
@@ -8969,7 +8975,7 @@
         <v>1112</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E118" s="2">
         <v>98</v>
@@ -8981,7 +8987,7 @@
         <v>1163</v>
       </c>
       <c r="H118" s="20" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I118" s="2">
         <v>30000</v>
@@ -9011,7 +9017,7 @@
         <v>1113</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E119" s="2">
         <v>98</v>
@@ -9023,7 +9029,7 @@
         <v>1164</v>
       </c>
       <c r="H119" s="20" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="I119" s="2">
         <v>30000</v>
@@ -9053,7 +9059,7 @@
         <v>1114</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E120" s="2">
         <v>98</v>
@@ -9065,7 +9071,7 @@
         <v>1165</v>
       </c>
       <c r="H120" s="20" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="I120" s="2">
         <v>30000</v>
@@ -9095,7 +9101,7 @@
         <v>1115</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E121" s="2">
         <v>98</v>
@@ -9107,7 +9113,7 @@
         <v>1166</v>
       </c>
       <c r="H121" s="20" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="I121" s="2">
         <v>30000</v>
@@ -9137,7 +9143,7 @@
         <v>1116</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E122" s="2">
         <v>98</v>
@@ -9149,7 +9155,7 @@
         <v>1167</v>
       </c>
       <c r="H122" s="20" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I122" s="2">
         <v>30000</v>
@@ -9179,7 +9185,7 @@
         <v>1117</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E123" s="2">
         <v>98</v>
@@ -9191,7 +9197,7 @@
         <v>1168</v>
       </c>
       <c r="H123" s="20" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="I123" s="2">
         <v>30000</v>
@@ -9221,7 +9227,7 @@
         <v>1118</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E124" s="2">
         <v>98</v>
@@ -9233,7 +9239,7 @@
         <v>1169</v>
       </c>
       <c r="H124" s="20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="I124" s="2">
         <v>30000</v>
@@ -9263,7 +9269,7 @@
         <v>1119</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E125" s="2">
         <v>98</v>
@@ -9275,7 +9281,7 @@
         <v>1170</v>
       </c>
       <c r="H125" s="20" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I125" s="2">
         <v>30000</v>
@@ -9305,7 +9311,7 @@
         <v>1120</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E126" s="2">
         <v>98</v>
@@ -9317,7 +9323,7 @@
         <v>1171</v>
       </c>
       <c r="H126" s="20" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="I126" s="2">
         <v>30000</v>
@@ -9347,7 +9353,7 @@
         <v>1121</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E127" s="2">
         <v>98</v>
@@ -9359,7 +9365,7 @@
         <v>1172</v>
       </c>
       <c r="H127" s="20" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I127" s="2">
         <v>30000</v>
@@ -9389,7 +9395,7 @@
         <v>1122</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E128" s="2">
         <v>98</v>
@@ -9401,7 +9407,7 @@
         <v>1173</v>
       </c>
       <c r="H128" s="20" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="I128" s="2">
         <v>30000</v>
@@ -9431,7 +9437,7 @@
         <v>1123</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E129" s="2">
         <v>98</v>
@@ -9443,7 +9449,7 @@
         <v>1174</v>
       </c>
       <c r="H129" s="20" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="I129" s="2">
         <v>30000</v>
@@ -9658,7 +9664,7 @@
         <v>2000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -9670,7 +9676,7 @@
         <v>1070</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="I6" s="2">
         <v>120000</v>
@@ -9702,7 +9708,7 @@
         <v>2001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -9714,7 +9720,7 @@
         <v>1071</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I7" s="2">
         <v>120000</v>
@@ -9746,7 +9752,7 @@
         <v>2002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -9758,7 +9764,7 @@
         <v>1072</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I8" s="2">
         <v>120000</v>
@@ -9790,7 +9796,7 @@
         <v>2003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -9802,7 +9808,7 @@
         <v>1073</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="I9" s="2">
         <v>120000</v>
@@ -9834,7 +9840,7 @@
         <v>2004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -9846,7 +9852,7 @@
         <v>1074</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="I10" s="2">
         <v>120000</v>
@@ -9878,7 +9884,7 @@
         <v>2005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -9890,7 +9896,7 @@
         <v>1104</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="I11" s="2">
         <v>20000</v>
@@ -9936,7 +9942,7 @@
         <v>2006</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -9948,7 +9954,7 @@
         <v>1105</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I14" s="2">
         <v>360000</v>
@@ -9980,7 +9986,7 @@
         <v>2007</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -9992,7 +9998,7 @@
         <v>1106</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="I15" s="2">
         <v>360000</v>
@@ -10024,7 +10030,7 @@
         <v>2008</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -10036,7 +10042,7 @@
         <v>1107</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I16" s="2">
         <v>360000</v>
@@ -10068,7 +10074,7 @@
         <v>2009</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -10080,7 +10086,7 @@
         <v>1108</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I17" s="2">
         <v>360000</v>
@@ -10112,7 +10118,7 @@
         <v>2010</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -10124,7 +10130,7 @@
         <v>1139</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="I18" s="2">
         <v>360000</v>
@@ -10156,7 +10162,7 @@
         <v>2011</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -10168,7 +10174,7 @@
         <v>1139</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -10207,7 +10213,7 @@
         <v>2012</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -10219,7 +10225,7 @@
         <v>1140</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I21" s="2">
         <v>360000</v>
@@ -10251,7 +10257,7 @@
         <v>2013</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -10263,7 +10269,7 @@
         <v>1141</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I22" s="2">
         <v>360000</v>
@@ -10295,7 +10301,7 @@
         <v>2014</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -10307,7 +10313,7 @@
         <v>1142</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I23" s="2">
         <v>360000</v>
@@ -10339,7 +10345,7 @@
         <v>2015</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -10351,7 +10357,7 @@
         <v>1143</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I24" s="2">
         <v>360000</v>
@@ -10383,7 +10389,7 @@
         <v>2016</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -10395,7 +10401,7 @@
         <v>1174</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="I25" s="2">
         <v>360000</v>
@@ -10427,7 +10433,7 @@
         <v>2017</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -10439,7 +10445,7 @@
         <v>1174</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="I26" s="2">
         <v>180000</v>
@@ -10468,16 +10474,16 @@
     </row>
     <row r="27" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C27" s="2">
         <v>2018</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -10489,7 +10495,7 @@
         <v>1174</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -3547,7 +3547,7 @@
         <v>20000</v>
       </c>
       <c r="M28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="11">
         <v>0</v>
@@ -3591,7 +3591,7 @@
         <v>40000</v>
       </c>
       <c r="M29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" s="11">
         <v>0</v>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -3526,7 +3526,7 @@
         <v>98</v>
       </c>
       <c r="F28" s="2">
-        <v>1070</v>
+        <v>1105</v>
       </c>
       <c r="G28" s="2">
         <v>2000</v>
@@ -3570,7 +3570,7 @@
         <v>98</v>
       </c>
       <c r="F29" s="2">
-        <v>1070</v>
+        <v>1105</v>
       </c>
       <c r="G29" s="2">
         <v>2000</v>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>快乐端午</t>
+    <t>快乐暑假</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-05-31</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
+    <t>2025-07-04</t>
+  </si>
+  <si>
+    <t>2025-07-08</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -349,7 +349,7 @@
     <t>2025-07-04</t>
   </si>
   <si>
-    <t>2025-07-08</t>
+    <t>2025-07-09</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowWidth="27952" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="399">
   <si>
     <t>_id</t>
   </si>
@@ -337,6 +337,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>#</t>
+  </si>
+  <si>
     <t>快乐暑假</t>
   </si>
   <si>
@@ -352,6 +355,18 @@
     <t>2025-07-09</t>
   </si>
   <si>
+    <t>周年庆</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>2025-08-07</t>
+  </si>
+  <si>
     <t>平时部分掉落</t>
   </si>
   <si>
@@ -1439,9 +1454,6 @@
   </si>
   <si>
     <t>209994</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
 </sst>
 </file>
@@ -2481,18 +2493,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P47"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="8.75221238938053" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.8761061946903" style="2" customWidth="1"/>
-    <col min="5" max="7" width="13.6283185840708" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.5044247787611" style="16" customWidth="1"/>
-    <col min="9" max="9" width="17.8761061946903" style="16" customWidth="1"/>
-    <col min="10" max="12" width="13.7522123893805" style="16" customWidth="1"/>
-    <col min="13" max="14" width="14.1238938053097" style="16" customWidth="1"/>
-    <col min="15" max="16" width="20.6283185840708" style="16" customWidth="1"/>
+    <col min="3" max="3" width="8.75" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.875" style="2" customWidth="1"/>
+    <col min="5" max="7" width="13.625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17.5083333333333" style="16" customWidth="1"/>
+    <col min="9" max="9" width="17.875" style="16" customWidth="1"/>
+    <col min="10" max="12" width="13.75" style="16" customWidth="1"/>
+    <col min="13" max="14" width="14.125" style="16" customWidth="1"/>
+    <col min="15" max="16" width="20.625" style="16" customWidth="1"/>
     <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -2651,12 +2663,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:16">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
@@ -2668,13 +2686,13 @@
         <v>9999</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I6" s="11">
         <v>0</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K6" s="11">
         <v>0</v>
@@ -2689,18 +2707,18 @@
         <v>0</v>
       </c>
       <c r="O6" s="18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P6" s="18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -2712,13 +2730,13 @@
         <v>9999</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I7" s="11">
         <v>0</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K7" s="11">
         <v>0</v>
@@ -2733,78 +2751,78 @@
         <v>0</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P7" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-    </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C9" s="2">
-        <v>101</v>
-      </c>
-      <c r="D9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="2">
-        <v>98</v>
-      </c>
-      <c r="F9" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G9" s="2">
-        <v>2000</v>
-      </c>
-      <c r="H9" s="19" t="s">
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="11">
-        <v>0</v>
-      </c>
-      <c r="J9" s="18" t="s">
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>9999</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="11">
+        <v>0</v>
+      </c>
+      <c r="J8" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="K9" s="11">
-        <v>0</v>
-      </c>
-      <c r="L9" s="11">
-        <v>0</v>
-      </c>
-      <c r="M9" s="11">
-        <v>1</v>
-      </c>
-      <c r="N9" s="11">
-        <v>0</v>
-      </c>
-      <c r="O9" s="18" t="s">
+      <c r="K8" s="11">
+        <v>0</v>
+      </c>
+      <c r="L8" s="11">
+        <v>0</v>
+      </c>
+      <c r="M8" s="11">
+        <v>0</v>
+      </c>
+      <c r="N8" s="11">
+        <v>0</v>
+      </c>
+      <c r="O8" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="18" t="s">
-        <v>34</v>
-      </c>
+      <c r="P8" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C10" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -2816,13 +2834,13 @@
         <v>2000</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I10" s="11">
         <v>0</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K10" s="11">
         <v>0</v>
@@ -2837,18 +2855,18 @@
         <v>0</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P10" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C11" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -2860,13 +2878,13 @@
         <v>2000</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I11" s="11">
         <v>0</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K11" s="11">
         <v>0</v>
@@ -2881,18 +2899,18 @@
         <v>0</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P11" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C12" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
@@ -2904,13 +2922,13 @@
         <v>2000</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I12" s="11">
         <v>0</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K12" s="11">
         <v>0</v>
@@ -2925,36 +2943,36 @@
         <v>0</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P12" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C13" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
       </c>
       <c r="F13" s="2">
-        <v>1035</v>
+        <v>1000</v>
       </c>
       <c r="G13" s="2">
         <v>2000</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I13" s="11">
         <v>0</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K13" s="11">
         <v>0</v>
@@ -2969,18 +2987,18 @@
         <v>0</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P13" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C14" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -2992,13 +3010,13 @@
         <v>2000</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I14" s="11">
         <v>0</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K14" s="11">
         <v>0</v>
@@ -3013,18 +3031,18 @@
         <v>0</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P14" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C15" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -3036,13 +3054,13 @@
         <v>2000</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I15" s="11">
         <v>0</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K15" s="11">
         <v>0</v>
@@ -3057,18 +3075,18 @@
         <v>0</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P15" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C16" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -3080,13 +3098,13 @@
         <v>2000</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I16" s="11">
         <v>0</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K16" s="11">
         <v>0</v>
@@ -3101,36 +3119,36 @@
         <v>0</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C17" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
       </c>
       <c r="F17" s="2">
-        <v>1070</v>
+        <v>1035</v>
       </c>
       <c r="G17" s="2">
         <v>2000</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I17" s="11">
         <v>0</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K17" s="11">
         <v>0</v>
@@ -3145,18 +3163,18 @@
         <v>0</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P17" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C18" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -3168,13 +3186,13 @@
         <v>2000</v>
       </c>
       <c r="H18" s="19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I18" s="11">
         <v>0</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K18" s="11">
         <v>0</v>
@@ -3189,18 +3207,18 @@
         <v>0</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P18" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C19" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -3212,13 +3230,13 @@
         <v>2000</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I19" s="11">
         <v>0</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="K19" s="11">
         <v>0</v>
@@ -3233,18 +3251,18 @@
         <v>0</v>
       </c>
       <c r="O19" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P19" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C20" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E20" s="2">
         <v>98</v>
@@ -3256,13 +3274,13 @@
         <v>2000</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I20" s="11">
         <v>0</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="K20" s="11">
         <v>0</v>
@@ -3277,63 +3295,63 @@
         <v>0</v>
       </c>
       <c r="O20" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P20" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1"/>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C22" s="2">
-        <v>201</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" s="2">
-        <v>100</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2">
-        <v>0</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="I22" s="11">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C21" s="2">
+        <v>112</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2">
+        <v>98</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1070</v>
+      </c>
+      <c r="G21" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="I21" s="11">
+        <v>0</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="K21" s="11">
+        <v>0</v>
+      </c>
+      <c r="L21" s="11">
+        <v>0</v>
+      </c>
+      <c r="M21" s="11">
         <v>1</v>
       </c>
-      <c r="K22" s="11">
-        <v>0</v>
-      </c>
-      <c r="L22" s="11">
-        <v>0</v>
-      </c>
-      <c r="M22" s="2">
-        <v>0</v>
-      </c>
-      <c r="N22" s="11">
-        <v>1</v>
-      </c>
-      <c r="O22" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P22" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
+      <c r="N21" s="11">
+        <v>0</v>
+      </c>
+      <c r="O21" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="P21" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1"/>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C23" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E23" s="2">
         <v>100</v>
@@ -3344,8 +3362,8 @@
       <c r="G23" s="2">
         <v>0</v>
       </c>
-      <c r="H23" s="19" t="s">
-        <v>74</v>
+      <c r="H23" s="18" t="s">
+        <v>77</v>
       </c>
       <c r="I23" s="11">
         <v>0</v>
@@ -3366,18 +3384,18 @@
         <v>1</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P23" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C24" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2">
         <v>100</v>
@@ -3388,8 +3406,8 @@
       <c r="G24" s="2">
         <v>0</v>
       </c>
-      <c r="H24" s="18" t="s">
-        <v>76</v>
+      <c r="H24" s="19" t="s">
+        <v>79</v>
       </c>
       <c r="I24" s="11">
         <v>0</v>
@@ -3410,91 +3428,91 @@
         <v>1</v>
       </c>
       <c r="O24" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P24" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="8:16">
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C25" s="2">
+        <v>203</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="2">
+        <v>100</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="I25" s="11">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
+        <v>1</v>
+      </c>
       <c r="K25" s="11">
         <v>0</v>
       </c>
-      <c r="L25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C26" s="2">
-        <v>301</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" s="2">
-        <v>98</v>
-      </c>
-      <c r="F26" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G26" s="2">
-        <v>2000</v>
-      </c>
-      <c r="H26" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="19" t="s">
-        <v>78</v>
-      </c>
+      <c r="L25" s="11">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2">
+        <v>0</v>
+      </c>
+      <c r="N25" s="11">
+        <v>1</v>
+      </c>
+      <c r="O25" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="P25" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="8:16">
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
       <c r="K26" s="11">
         <v>0</v>
       </c>
-      <c r="L26" s="11">
-        <v>0</v>
-      </c>
-      <c r="M26" s="2">
-        <v>1</v>
-      </c>
-      <c r="N26" s="11">
-        <v>0</v>
-      </c>
-      <c r="O26" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P26" s="18" t="s">
-        <v>34</v>
-      </c>
+      <c r="L26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C27" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
       </c>
       <c r="F27" s="2">
-        <v>1070</v>
+        <v>1000</v>
       </c>
       <c r="G27" s="2">
         <v>2000</v>
       </c>
-      <c r="H27" s="18" t="s">
-        <v>80</v>
+      <c r="H27" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="I27" s="2">
         <v>0</v>
       </c>
       <c r="J27" s="19" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K27" s="11">
         <v>0</v>
@@ -3509,62 +3527,62 @@
         <v>0</v>
       </c>
       <c r="O27" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P27" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C28" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E28" s="2">
         <v>98</v>
       </c>
       <c r="F28" s="2">
-        <v>1105</v>
+        <v>1070</v>
       </c>
       <c r="G28" s="2">
         <v>2000</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="I28" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="J28" s="18" t="s">
-        <v>84</v>
-      </c>
       <c r="K28" s="11">
         <v>0</v>
       </c>
-      <c r="L28" s="2">
-        <v>20000</v>
+      <c r="L28" s="11">
+        <v>0</v>
       </c>
       <c r="M28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" s="11">
         <v>0</v>
       </c>
       <c r="O28" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P28" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C29" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -3576,84 +3594,84 @@
         <v>2000</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K29" s="11">
         <v>0</v>
       </c>
       <c r="L29" s="2">
+        <v>20000</v>
+      </c>
+      <c r="M29" s="2">
+        <v>0</v>
+      </c>
+      <c r="N29" s="11">
+        <v>0</v>
+      </c>
+      <c r="O29" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="P29" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C30" s="2">
+        <v>304</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" s="2">
+        <v>98</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1105</v>
+      </c>
+      <c r="G30" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H30" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="I30" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="J30" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="K30" s="11">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2">
         <v>40000</v>
       </c>
-      <c r="M29" s="2">
-        <v>0</v>
-      </c>
-      <c r="N29" s="11">
-        <v>0</v>
-      </c>
-      <c r="O29" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P29" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1"/>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C31" s="2">
-        <v>801</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" s="2">
-        <v>98</v>
-      </c>
-      <c r="F31" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G31" s="2">
-        <v>2000</v>
-      </c>
-      <c r="H31" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="I31" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="J31" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="K31" s="11">
-        <v>0</v>
-      </c>
-      <c r="L31" s="11">
-        <v>0</v>
-      </c>
-      <c r="M31" s="2">
-        <v>0</v>
-      </c>
-      <c r="N31" s="11">
-        <v>0</v>
-      </c>
-      <c r="O31" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P31" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
+      <c r="M30" s="2">
+        <v>0</v>
+      </c>
+      <c r="N30" s="11">
+        <v>0</v>
+      </c>
+      <c r="O30" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="P30" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1"/>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C32" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E32" s="2">
         <v>98</v>
@@ -3664,14 +3682,14 @@
       <c r="G32" s="2">
         <v>2000</v>
       </c>
-      <c r="H32" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I32" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="J32" s="18" t="s">
-        <v>83</v>
+      <c r="H32" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="I32" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="J32" s="19" t="s">
+        <v>64</v>
       </c>
       <c r="K32" s="11">
         <v>0</v>
@@ -3679,43 +3697,43 @@
       <c r="L32" s="11">
         <v>0</v>
       </c>
-      <c r="M32" s="11">
-        <v>1</v>
+      <c r="M32" s="2">
+        <v>0</v>
       </c>
       <c r="N32" s="11">
         <v>0</v>
       </c>
       <c r="O32" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P32" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C33" s="2">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
       </c>
       <c r="F33" s="2">
-        <v>1105</v>
+        <v>1000</v>
       </c>
       <c r="G33" s="2">
         <v>2000</v>
       </c>
       <c r="H33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I33" s="18" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J33" s="18" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="K33" s="11">
         <v>0</v>
@@ -3723,96 +3741,96 @@
       <c r="L33" s="11">
         <v>0</v>
       </c>
-      <c r="M33" s="2">
-        <v>0</v>
+      <c r="M33" s="11">
+        <v>1</v>
       </c>
       <c r="N33" s="11">
         <v>0</v>
       </c>
       <c r="O33" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P33" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="9:16">
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="11"/>
-      <c r="P34" s="11"/>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C35" s="2">
-        <v>804</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E35" s="2">
-        <v>98</v>
-      </c>
-      <c r="F35" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G35" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C34" s="2">
+        <v>803</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E34" s="2">
+        <v>98</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1105</v>
+      </c>
+      <c r="G34" s="2">
         <v>2000</v>
       </c>
-      <c r="H35" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="I35" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="J35" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="K35" s="11">
-        <v>0</v>
-      </c>
-      <c r="L35" s="11">
-        <v>0</v>
-      </c>
-      <c r="M35" s="2">
-        <v>0</v>
-      </c>
-      <c r="N35" s="11">
-        <v>0</v>
-      </c>
-      <c r="O35" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P35" s="18" t="s">
-        <v>34</v>
-      </c>
+      <c r="H34" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="I34" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="J34" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="K34" s="11">
+        <v>0</v>
+      </c>
+      <c r="L34" s="11">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2">
+        <v>0</v>
+      </c>
+      <c r="N34" s="11">
+        <v>0</v>
+      </c>
+      <c r="O34" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="P34" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="9:16">
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="11"/>
+      <c r="P35" s="11"/>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C36" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
       </c>
       <c r="F36" s="2">
-        <v>1105</v>
+        <v>1000</v>
       </c>
       <c r="G36" s="2">
         <v>2000</v>
       </c>
       <c r="H36" s="19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I36" s="19" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="J36" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K36" s="11">
         <v>0</v>
@@ -3827,18 +3845,18 @@
         <v>0</v>
       </c>
       <c r="O36" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P36" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C37" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -3850,18 +3868,18 @@
         <v>2000</v>
       </c>
       <c r="H37" s="19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J37" s="18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K37" s="11">
         <v>0</v>
       </c>
-      <c r="L37" s="2">
+      <c r="L37" s="11">
         <v>0</v>
       </c>
       <c r="M37" s="2">
@@ -3871,18 +3889,18 @@
         <v>0</v>
       </c>
       <c r="O37" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P37" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C38" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E38" s="2">
         <v>98</v>
@@ -3894,19 +3912,19 @@
         <v>2000</v>
       </c>
       <c r="H38" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J38" s="18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K38" s="11">
         <v>0</v>
       </c>
       <c r="L38" s="2">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2">
         <v>0</v>
@@ -3915,18 +3933,18 @@
         <v>0</v>
       </c>
       <c r="O38" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P38" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C39" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E39" s="2">
         <v>98</v>
@@ -3938,102 +3956,102 @@
         <v>2000</v>
       </c>
       <c r="H39" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I39" s="19" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="J39" s="18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K39" s="11">
         <v>0</v>
       </c>
       <c r="L39" s="2">
+        <v>150000</v>
+      </c>
+      <c r="M39" s="2">
+        <v>0</v>
+      </c>
+      <c r="N39" s="11">
+        <v>0</v>
+      </c>
+      <c r="O39" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="P39" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C40" s="2">
+        <v>808</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E40" s="2">
+        <v>98</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1105</v>
+      </c>
+      <c r="G40" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="I40" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="J40" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="K40" s="11">
+        <v>0</v>
+      </c>
+      <c r="L40" s="2">
         <v>200000</v>
       </c>
-      <c r="M39" s="2">
-        <v>0</v>
-      </c>
-      <c r="N39" s="11">
-        <v>0</v>
-      </c>
-      <c r="O39" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P39" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="16"/>
-      <c r="O40" s="16"/>
-      <c r="P40" s="16"/>
-    </row>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C41" s="2">
-        <v>991</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E41" s="2">
-        <v>99</v>
-      </c>
-      <c r="F41" s="2">
-        <v>0</v>
-      </c>
-      <c r="G41" s="2">
-        <v>0</v>
-      </c>
-      <c r="H41" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="I41" s="11">
-        <v>0</v>
-      </c>
-      <c r="J41" s="2">
-        <v>1</v>
-      </c>
-      <c r="K41" s="11">
-        <v>0</v>
-      </c>
-      <c r="L41" s="11">
-        <v>0</v>
-      </c>
-      <c r="M41" s="2">
-        <v>0</v>
-      </c>
-      <c r="N41" s="2">
-        <v>1</v>
-      </c>
-      <c r="O41" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P41" s="18" t="s">
-        <v>34</v>
-      </c>
+      <c r="M40" s="2">
+        <v>0</v>
+      </c>
+      <c r="N40" s="11">
+        <v>0</v>
+      </c>
+      <c r="O40" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="P40" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="16"/>
+      <c r="J41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+      <c r="M41" s="16"/>
+      <c r="N41" s="16"/>
+      <c r="O41" s="16"/>
+      <c r="P41" s="16"/>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C42" s="2">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E42" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F42" s="2">
         <v>0</v>
@@ -4042,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I42" s="11">
         <v>0</v>
@@ -4063,24 +4081,57 @@
         <v>1</v>
       </c>
       <c r="O42" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P42" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1"/>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="8:16">
-      <c r="H44" s="16"/>
-      <c r="I44" s="16"/>
-      <c r="J44" s="16"/>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="16"/>
-      <c r="O44" s="16"/>
-      <c r="P44" s="16"/>
-    </row>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C43" s="2">
+        <v>992</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E43" s="2">
+        <v>101</v>
+      </c>
+      <c r="F43" s="2">
+        <v>0</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0</v>
+      </c>
+      <c r="H43" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="I43" s="11">
+        <v>0</v>
+      </c>
+      <c r="J43" s="2">
+        <v>1</v>
+      </c>
+      <c r="K43" s="11">
+        <v>0</v>
+      </c>
+      <c r="L43" s="11">
+        <v>0</v>
+      </c>
+      <c r="M43" s="2">
+        <v>0</v>
+      </c>
+      <c r="N43" s="2">
+        <v>1</v>
+      </c>
+      <c r="O43" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="P43" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1"/>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="8:16">
       <c r="H45" s="16"/>
       <c r="I45" s="16"/>
@@ -4114,30 +4165,41 @@
       <c r="O47" s="16"/>
       <c r="P47" s="16"/>
     </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="8:16">
+      <c r="H48" s="16"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="16"/>
+      <c r="O48" s="16"/>
+      <c r="P48" s="16"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F32">
+  <conditionalFormatting sqref="F33">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
+  <conditionalFormatting sqref="F34">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F34">
+  <conditionalFormatting sqref="F35">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F36">
+  <conditionalFormatting sqref="F37">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F37">
+  <conditionalFormatting sqref="F38">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F38">
+  <conditionalFormatting sqref="F39">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F39">
+  <conditionalFormatting sqref="F40">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:C5 F32:F34 F36:F39 F3:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:C5 F33:F35 F37:F40 F3:G5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -4154,14 +4216,14 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="8.75221238938053" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.8761061946903" style="1" customWidth="1"/>
-    <col min="5" max="7" width="13.6283185840708" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5044247787611" style="3" customWidth="1"/>
-    <col min="9" max="9" width="17.8761061946903" style="3" customWidth="1"/>
-    <col min="10" max="11" width="13.7522123893805" style="3" customWidth="1"/>
-    <col min="12" max="13" width="14.1238938053097" style="3" customWidth="1"/>
-    <col min="14" max="15" width="20.6283185840708" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.875" style="1" customWidth="1"/>
+    <col min="5" max="7" width="13.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5083333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="17.875" style="3" customWidth="1"/>
+    <col min="10" max="11" width="13.75" style="3" customWidth="1"/>
+    <col min="12" max="13" width="14.125" style="3" customWidth="1"/>
+    <col min="14" max="15" width="20.625" style="3" customWidth="1"/>
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4314,7 +4376,7 @@
         <v>1000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -4326,7 +4388,7 @@
         <v>1051</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I6" s="2">
         <v>40000</v>
@@ -4344,10 +4406,10 @@
         <v>0</v>
       </c>
       <c r="N6" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O6" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4355,7 +4417,7 @@
         <v>1001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -4367,7 +4429,7 @@
         <v>1052</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="I7" s="2">
         <v>40000</v>
@@ -4385,10 +4447,10 @@
         <v>0</v>
       </c>
       <c r="N7" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4396,7 +4458,7 @@
         <v>1002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -4408,7 +4470,7 @@
         <v>1053</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I8" s="2">
         <v>40000</v>
@@ -4426,10 +4488,10 @@
         <v>0</v>
       </c>
       <c r="N8" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4437,7 +4499,7 @@
         <v>1003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -4449,7 +4511,7 @@
         <v>1054</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="I9" s="2">
         <v>40000</v>
@@ -4467,10 +4529,10 @@
         <v>0</v>
       </c>
       <c r="N9" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4478,7 +4540,7 @@
         <v>1004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -4490,7 +4552,7 @@
         <v>1055</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I10" s="2">
         <v>40000</v>
@@ -4508,10 +4570,10 @@
         <v>0</v>
       </c>
       <c r="N10" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4519,7 +4581,7 @@
         <v>1005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -4531,7 +4593,7 @@
         <v>1056</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="I11" s="2">
         <v>40000</v>
@@ -4549,10 +4611,10 @@
         <v>0</v>
       </c>
       <c r="N11" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4560,7 +4622,7 @@
         <v>1006</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
@@ -4572,7 +4634,7 @@
         <v>1057</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="I12" s="2">
         <v>40000</v>
@@ -4590,10 +4652,10 @@
         <v>0</v>
       </c>
       <c r="N12" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4601,7 +4663,7 @@
         <v>1007</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
@@ -4613,7 +4675,7 @@
         <v>1058</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I13" s="2">
         <v>40000</v>
@@ -4631,10 +4693,10 @@
         <v>0</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4642,7 +4704,7 @@
         <v>1008</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -4654,7 +4716,7 @@
         <v>1059</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I14" s="2">
         <v>40000</v>
@@ -4672,10 +4734,10 @@
         <v>0</v>
       </c>
       <c r="N14" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4683,7 +4745,7 @@
         <v>1009</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -4695,7 +4757,7 @@
         <v>1060</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="I15" s="2">
         <v>40000</v>
@@ -4713,10 +4775,10 @@
         <v>0</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4724,7 +4786,7 @@
         <v>1010</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -4736,7 +4798,7 @@
         <v>1061</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I16" s="2">
         <v>40000</v>
@@ -4754,10 +4816,10 @@
         <v>0</v>
       </c>
       <c r="N16" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4765,7 +4827,7 @@
         <v>1011</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -4777,7 +4839,7 @@
         <v>1062</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I17" s="2">
         <v>40000</v>
@@ -4795,10 +4857,10 @@
         <v>0</v>
       </c>
       <c r="N17" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4806,7 +4868,7 @@
         <v>1012</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -4818,7 +4880,7 @@
         <v>1063</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I18" s="2">
         <v>40000</v>
@@ -4836,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="N18" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4847,7 +4909,7 @@
         <v>1013</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -4859,7 +4921,7 @@
         <v>1064</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -4877,10 +4939,10 @@
         <v>0</v>
       </c>
       <c r="N19" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O19" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4888,7 +4950,7 @@
         <v>1014</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E20" s="2">
         <v>98</v>
@@ -4900,7 +4962,7 @@
         <v>1065</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="I20" s="2">
         <v>40000</v>
@@ -4918,10 +4980,10 @@
         <v>0</v>
       </c>
       <c r="N20" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O20" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4929,7 +4991,7 @@
         <v>1015</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -4941,7 +5003,7 @@
         <v>1066</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I21" s="2">
         <v>40000</v>
@@ -4959,10 +5021,10 @@
         <v>0</v>
       </c>
       <c r="N21" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O21" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4970,7 +5032,7 @@
         <v>1016</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -4982,7 +5044,7 @@
         <v>1067</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="I22" s="2">
         <v>40000</v>
@@ -5000,10 +5062,10 @@
         <v>0</v>
       </c>
       <c r="N22" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5011,7 +5073,7 @@
         <v>1017</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -5023,7 +5085,7 @@
         <v>1068</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="I23" s="2">
         <v>40000</v>
@@ -5041,10 +5103,10 @@
         <v>0</v>
       </c>
       <c r="N23" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5052,7 +5114,7 @@
         <v>1018</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -5064,7 +5126,7 @@
         <v>1069</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="I24" s="2">
         <v>40000</v>
@@ -5082,10 +5144,10 @@
         <v>0</v>
       </c>
       <c r="N24" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O24" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5093,7 +5155,7 @@
         <v>1019</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -5105,7 +5167,7 @@
         <v>1070</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="I25" s="2">
         <v>40000</v>
@@ -5123,10 +5185,10 @@
         <v>0</v>
       </c>
       <c r="N25" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O25" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5134,7 +5196,7 @@
         <v>1020</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -5146,7 +5208,7 @@
         <v>1071</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="I26" s="2">
         <v>40000</v>
@@ -5164,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="N26" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O26" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5175,7 +5237,7 @@
         <v>1021</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -5187,7 +5249,7 @@
         <v>1072</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>
@@ -5205,10 +5267,10 @@
         <v>0</v>
       </c>
       <c r="N27" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O27" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5216,7 +5278,7 @@
         <v>1022</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E28" s="2">
         <v>98</v>
@@ -5228,7 +5290,7 @@
         <v>1073</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="I28" s="2">
         <v>40000</v>
@@ -5246,10 +5308,10 @@
         <v>0</v>
       </c>
       <c r="N28" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O28" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:16">
@@ -5257,7 +5319,7 @@
         <v>1023</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -5269,7 +5331,7 @@
         <v>1074</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I29" s="2">
         <v>40000</v>
@@ -5287,10 +5349,10 @@
         <v>0</v>
       </c>
       <c r="N29" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P29" s="2"/>
     </row>
@@ -5299,7 +5361,7 @@
         <v>1024</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E30" s="2">
         <v>98</v>
@@ -5311,7 +5373,7 @@
         <v>1075</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I30" s="2">
         <v>4000</v>
@@ -5329,10 +5391,10 @@
         <v>0</v>
       </c>
       <c r="N30" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O30" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5340,7 +5402,7 @@
         <v>1025</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E31" s="2">
         <v>98</v>
@@ -5352,7 +5414,7 @@
         <v>1076</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="I31" s="2">
         <v>4000</v>
@@ -5370,10 +5432,10 @@
         <v>0</v>
       </c>
       <c r="N31" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O31" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5381,7 +5443,7 @@
         <v>1026</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E32" s="2">
         <v>98</v>
@@ -5393,7 +5455,7 @@
         <v>1077</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="I32" s="2">
         <v>4000</v>
@@ -5411,10 +5473,10 @@
         <v>0</v>
       </c>
       <c r="N32" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O32" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5422,7 +5484,7 @@
         <v>1027</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
@@ -5434,7 +5496,7 @@
         <v>1078</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="I33" s="2">
         <v>4000</v>
@@ -5452,10 +5514,10 @@
         <v>0</v>
       </c>
       <c r="N33" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O33" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:16">
@@ -5463,7 +5525,7 @@
         <v>1028</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E34" s="2">
         <v>98</v>
@@ -5475,7 +5537,7 @@
         <v>1079</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="I34" s="2">
         <v>4000</v>
@@ -5493,10 +5555,10 @@
         <v>0</v>
       </c>
       <c r="N34" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O34" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P34" s="2"/>
     </row>
@@ -5505,7 +5567,7 @@
         <v>1029</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
@@ -5517,7 +5579,7 @@
         <v>1080</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="I35" s="2">
         <v>4000</v>
@@ -5535,10 +5597,10 @@
         <v>0</v>
       </c>
       <c r="N35" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O35" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P35" s="2"/>
     </row>
@@ -5547,7 +5609,7 @@
         <v>1030</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -5559,7 +5621,7 @@
         <v>1081</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="I36" s="2">
         <v>4000</v>
@@ -5577,10 +5639,10 @@
         <v>0</v>
       </c>
       <c r="N36" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O36" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P36" s="2"/>
     </row>
@@ -5589,7 +5651,7 @@
         <v>1031</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -5601,7 +5663,7 @@
         <v>1082</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="I37" s="2">
         <v>4000</v>
@@ -5619,10 +5681,10 @@
         <v>0</v>
       </c>
       <c r="N37" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O37" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P37" s="2"/>
     </row>
@@ -5631,7 +5693,7 @@
         <v>1032</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E38" s="2">
         <v>98</v>
@@ -5643,7 +5705,7 @@
         <v>1083</v>
       </c>
       <c r="H38" s="20" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I38" s="2">
         <v>4000</v>
@@ -5661,10 +5723,10 @@
         <v>0</v>
       </c>
       <c r="N38" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O38" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P38" s="2"/>
     </row>
@@ -5673,7 +5735,7 @@
         <v>1033</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E39" s="2">
         <v>98</v>
@@ -5685,7 +5747,7 @@
         <v>1084</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="I39" s="2">
         <v>4000</v>
@@ -5703,10 +5765,10 @@
         <v>0</v>
       </c>
       <c r="N39" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O39" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P39" s="2"/>
     </row>
@@ -5715,7 +5777,7 @@
         <v>1034</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E40" s="2">
         <v>98</v>
@@ -5727,7 +5789,7 @@
         <v>1085</v>
       </c>
       <c r="H40" s="20" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="I40" s="2">
         <v>4000</v>
@@ -5745,10 +5807,10 @@
         <v>0</v>
       </c>
       <c r="N40" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O40" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P40" s="2"/>
     </row>
@@ -5757,7 +5819,7 @@
         <v>1035</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E41" s="2">
         <v>98</v>
@@ -5769,7 +5831,7 @@
         <v>1086</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="I41" s="2">
         <v>4000</v>
@@ -5787,10 +5849,10 @@
         <v>0</v>
       </c>
       <c r="N41" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O41" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P41" s="2"/>
     </row>
@@ -5799,7 +5861,7 @@
         <v>1036</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E42" s="2">
         <v>98</v>
@@ -5811,7 +5873,7 @@
         <v>1087</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="I42" s="2">
         <v>4000</v>
@@ -5829,10 +5891,10 @@
         <v>0</v>
       </c>
       <c r="N42" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O42" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P42" s="2"/>
     </row>
@@ -5841,7 +5903,7 @@
         <v>1037</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E43" s="2">
         <v>98</v>
@@ -5853,7 +5915,7 @@
         <v>1088</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="I43" s="2">
         <v>4000</v>
@@ -5871,10 +5933,10 @@
         <v>0</v>
       </c>
       <c r="N43" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O43" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P43" s="2"/>
     </row>
@@ -5883,7 +5945,7 @@
         <v>1038</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E44" s="2">
         <v>98</v>
@@ -5895,7 +5957,7 @@
         <v>1089</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="I44" s="2">
         <v>4000</v>
@@ -5913,10 +5975,10 @@
         <v>0</v>
       </c>
       <c r="N44" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O44" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P44" s="2"/>
     </row>
@@ -5925,7 +5987,7 @@
         <v>1039</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E45" s="2">
         <v>98</v>
@@ -5937,7 +5999,7 @@
         <v>1090</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="I45" s="2">
         <v>4000</v>
@@ -5955,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="N45" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O45" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P45" s="2"/>
     </row>
@@ -5967,7 +6029,7 @@
         <v>1040</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E46" s="2">
         <v>98</v>
@@ -5979,7 +6041,7 @@
         <v>1091</v>
       </c>
       <c r="H46" s="20" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I46" s="2">
         <v>4000</v>
@@ -5997,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="N46" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O46" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P46" s="2"/>
     </row>
@@ -6009,7 +6071,7 @@
         <v>1041</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E47" s="2">
         <v>98</v>
@@ -6021,7 +6083,7 @@
         <v>1092</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="I47" s="2">
         <v>4000</v>
@@ -6039,10 +6101,10 @@
         <v>0</v>
       </c>
       <c r="N47" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O47" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P47" s="2"/>
     </row>
@@ -6051,7 +6113,7 @@
         <v>1042</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E48" s="2">
         <v>98</v>
@@ -6063,7 +6125,7 @@
         <v>1093</v>
       </c>
       <c r="H48" s="20" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="I48" s="2">
         <v>4000</v>
@@ -6081,10 +6143,10 @@
         <v>0</v>
       </c>
       <c r="N48" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O48" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P48" s="2"/>
     </row>
@@ -6093,7 +6155,7 @@
         <v>1043</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E49" s="2">
         <v>98</v>
@@ -6105,7 +6167,7 @@
         <v>1094</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="I49" s="2">
         <v>4000</v>
@@ -6123,10 +6185,10 @@
         <v>0</v>
       </c>
       <c r="N49" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O49" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P49" s="2"/>
     </row>
@@ -6135,7 +6197,7 @@
         <v>1044</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E50" s="2">
         <v>98</v>
@@ -6147,7 +6209,7 @@
         <v>1095</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="I50" s="2">
         <v>4000</v>
@@ -6165,10 +6227,10 @@
         <v>0</v>
       </c>
       <c r="N50" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O50" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P50" s="2"/>
     </row>
@@ -6177,7 +6239,7 @@
         <v>1045</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E51" s="2">
         <v>98</v>
@@ -6189,7 +6251,7 @@
         <v>1096</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="I51" s="2">
         <v>4000</v>
@@ -6207,10 +6269,10 @@
         <v>0</v>
       </c>
       <c r="N51" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O51" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P51" s="2"/>
     </row>
@@ -6219,7 +6281,7 @@
         <v>1046</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E52" s="2">
         <v>98</v>
@@ -6231,7 +6293,7 @@
         <v>1097</v>
       </c>
       <c r="H52" s="20" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="I52" s="2">
         <v>4000</v>
@@ -6249,10 +6311,10 @@
         <v>0</v>
       </c>
       <c r="N52" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O52" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P52" s="2"/>
     </row>
@@ -6261,7 +6323,7 @@
         <v>1047</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E53" s="2">
         <v>98</v>
@@ -6273,7 +6335,7 @@
         <v>1098</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="I53" s="2">
         <v>4000</v>
@@ -6291,10 +6353,10 @@
         <v>0</v>
       </c>
       <c r="N53" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O53" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P53" s="2"/>
     </row>
@@ -6303,7 +6365,7 @@
         <v>1048</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E54" s="2">
         <v>98</v>
@@ -6315,7 +6377,7 @@
         <v>1099</v>
       </c>
       <c r="H54" s="20" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="I54" s="2">
         <v>4000</v>
@@ -6333,10 +6395,10 @@
         <v>0</v>
       </c>
       <c r="N54" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O54" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P54" s="2"/>
     </row>
@@ -6345,7 +6407,7 @@
         <v>1049</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E55" s="2">
         <v>98</v>
@@ -6357,7 +6419,7 @@
         <v>1100</v>
       </c>
       <c r="H55" s="20" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="I55" s="2">
         <v>4000</v>
@@ -6375,10 +6437,10 @@
         <v>0</v>
       </c>
       <c r="N55" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O55" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P55" s="2"/>
     </row>
@@ -6387,7 +6449,7 @@
         <v>1050</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E56" s="2">
         <v>98</v>
@@ -6399,7 +6461,7 @@
         <v>1101</v>
       </c>
       <c r="H56" s="20" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I56" s="2">
         <v>4000</v>
@@ -6417,10 +6479,10 @@
         <v>0</v>
       </c>
       <c r="N56" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O56" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P56" s="2"/>
     </row>
@@ -6429,7 +6491,7 @@
         <v>1051</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E57" s="2">
         <v>98</v>
@@ -6441,7 +6503,7 @@
         <v>1102</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="I57" s="2">
         <v>4000</v>
@@ -6459,10 +6521,10 @@
         <v>0</v>
       </c>
       <c r="N57" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O57" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P57" s="2"/>
     </row>
@@ -6471,7 +6533,7 @@
         <v>1052</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E58" s="2">
         <v>98</v>
@@ -6483,7 +6545,7 @@
         <v>1103</v>
       </c>
       <c r="H58" s="20" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="I58" s="2">
         <v>4000</v>
@@ -6501,10 +6563,10 @@
         <v>0</v>
       </c>
       <c r="N58" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O58" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P58" s="2"/>
     </row>
@@ -6513,7 +6575,7 @@
         <v>1053</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E59" s="2">
         <v>98</v>
@@ -6525,7 +6587,7 @@
         <v>1104</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="I59" s="2">
         <v>4000</v>
@@ -6543,10 +6605,10 @@
         <v>0</v>
       </c>
       <c r="N59" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O59" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P59" s="2"/>
     </row>
@@ -6555,7 +6617,7 @@
         <v>1054</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E60" s="12">
         <v>98</v>
@@ -6567,7 +6629,7 @@
         <v>1105</v>
       </c>
       <c r="H60" s="21" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="I60" s="12">
         <v>20000</v>
@@ -6585,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="N60" s="22" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O60" s="22" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6596,7 +6658,7 @@
         <v>1055</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E61" s="2">
         <v>98</v>
@@ -6608,7 +6670,7 @@
         <v>1106</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="I61" s="2">
         <v>20000</v>
@@ -6626,10 +6688,10 @@
         <v>0</v>
       </c>
       <c r="N61" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O61" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6637,7 +6699,7 @@
         <v>1056</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E62" s="2">
         <v>98</v>
@@ -6649,7 +6711,7 @@
         <v>1107</v>
       </c>
       <c r="H62" s="20" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="I62" s="2">
         <v>20000</v>
@@ -6667,10 +6729,10 @@
         <v>0</v>
       </c>
       <c r="N62" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O62" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6678,7 +6740,7 @@
         <v>1057</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E63" s="2">
         <v>98</v>
@@ -6690,7 +6752,7 @@
         <v>1108</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I63" s="2">
         <v>20000</v>
@@ -6708,10 +6770,10 @@
         <v>0</v>
       </c>
       <c r="N63" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O63" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:16">
@@ -6719,7 +6781,7 @@
         <v>1058</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E64" s="2">
         <v>98</v>
@@ -6731,7 +6793,7 @@
         <v>1109</v>
       </c>
       <c r="H64" s="20" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="I64" s="2">
         <v>20000</v>
@@ -6749,10 +6811,10 @@
         <v>0</v>
       </c>
       <c r="N64" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O64" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P64" s="2"/>
     </row>
@@ -6761,7 +6823,7 @@
         <v>1059</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E65" s="2">
         <v>98</v>
@@ -6773,7 +6835,7 @@
         <v>1110</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="I65" s="2">
         <v>20000</v>
@@ -6791,10 +6853,10 @@
         <v>0</v>
       </c>
       <c r="N65" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O65" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6802,7 +6864,7 @@
         <v>1060</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="E66" s="2">
         <v>98</v>
@@ -6814,7 +6876,7 @@
         <v>1111</v>
       </c>
       <c r="H66" s="20" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="I66" s="2">
         <v>20000</v>
@@ -6832,10 +6894,10 @@
         <v>0</v>
       </c>
       <c r="N66" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O66" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6843,7 +6905,7 @@
         <v>1061</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="E67" s="2">
         <v>98</v>
@@ -6855,7 +6917,7 @@
         <v>1112</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="I67" s="2">
         <v>20000</v>
@@ -6873,10 +6935,10 @@
         <v>0</v>
       </c>
       <c r="N67" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O67" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6884,7 +6946,7 @@
         <v>1062</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E68" s="2">
         <v>98</v>
@@ -6896,7 +6958,7 @@
         <v>1113</v>
       </c>
       <c r="H68" s="20" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="I68" s="2">
         <v>20000</v>
@@ -6914,10 +6976,10 @@
         <v>0</v>
       </c>
       <c r="N68" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O68" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:16">
@@ -6925,7 +6987,7 @@
         <v>1063</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E69" s="2">
         <v>98</v>
@@ -6937,7 +6999,7 @@
         <v>1114</v>
       </c>
       <c r="H69" s="20" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="I69" s="2">
         <v>20000</v>
@@ -6955,10 +7017,10 @@
         <v>0</v>
       </c>
       <c r="N69" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O69" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P69" s="2"/>
     </row>
@@ -6967,7 +7029,7 @@
         <v>1064</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E70" s="2">
         <v>98</v>
@@ -6979,7 +7041,7 @@
         <v>1115</v>
       </c>
       <c r="H70" s="20" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="I70" s="2">
         <v>20000</v>
@@ -6997,10 +7059,10 @@
         <v>0</v>
       </c>
       <c r="N70" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O70" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P70" s="2"/>
     </row>
@@ -7009,7 +7071,7 @@
         <v>1065</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E71" s="2">
         <v>98</v>
@@ -7021,7 +7083,7 @@
         <v>1116</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I71" s="2">
         <v>20000</v>
@@ -7039,10 +7101,10 @@
         <v>0</v>
       </c>
       <c r="N71" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O71" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P71" s="2"/>
     </row>
@@ -7051,7 +7113,7 @@
         <v>1066</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E72" s="2">
         <v>98</v>
@@ -7063,7 +7125,7 @@
         <v>1117</v>
       </c>
       <c r="H72" s="20" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I72" s="2">
         <v>20000</v>
@@ -7081,10 +7143,10 @@
         <v>0</v>
       </c>
       <c r="N72" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O72" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P72" s="2"/>
     </row>
@@ -7093,7 +7155,7 @@
         <v>1067</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E73" s="2">
         <v>98</v>
@@ -7105,7 +7167,7 @@
         <v>1118</v>
       </c>
       <c r="H73" s="20" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="I73" s="2">
         <v>20000</v>
@@ -7123,10 +7185,10 @@
         <v>0</v>
       </c>
       <c r="N73" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O73" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P73" s="2"/>
     </row>
@@ -7135,7 +7197,7 @@
         <v>1068</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E74" s="2">
         <v>98</v>
@@ -7147,7 +7209,7 @@
         <v>1119</v>
       </c>
       <c r="H74" s="20" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I74" s="2">
         <v>20000</v>
@@ -7165,10 +7227,10 @@
         <v>0</v>
       </c>
       <c r="N74" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O74" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P74" s="2"/>
     </row>
@@ -7177,7 +7239,7 @@
         <v>1069</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E75" s="2">
         <v>98</v>
@@ -7189,7 +7251,7 @@
         <v>1120</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="I75" s="2">
         <v>20000</v>
@@ -7207,10 +7269,10 @@
         <v>0</v>
       </c>
       <c r="N75" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O75" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P75" s="2"/>
     </row>
@@ -7219,7 +7281,7 @@
         <v>1070</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E76" s="2">
         <v>98</v>
@@ -7231,7 +7293,7 @@
         <v>1121</v>
       </c>
       <c r="H76" s="20" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="I76" s="2">
         <v>20000</v>
@@ -7249,10 +7311,10 @@
         <v>0</v>
       </c>
       <c r="N76" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O76" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P76" s="2"/>
     </row>
@@ -7261,7 +7323,7 @@
         <v>1071</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E77" s="2">
         <v>98</v>
@@ -7273,7 +7335,7 @@
         <v>1122</v>
       </c>
       <c r="H77" s="20" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I77" s="2">
         <v>20000</v>
@@ -7291,10 +7353,10 @@
         <v>0</v>
       </c>
       <c r="N77" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O77" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P77" s="2"/>
     </row>
@@ -7303,7 +7365,7 @@
         <v>1072</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E78" s="2">
         <v>98</v>
@@ -7315,7 +7377,7 @@
         <v>1123</v>
       </c>
       <c r="H78" s="20" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="I78" s="2">
         <v>20000</v>
@@ -7333,10 +7395,10 @@
         <v>0</v>
       </c>
       <c r="N78" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O78" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P78" s="2"/>
     </row>
@@ -7345,7 +7407,7 @@
         <v>1073</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E79" s="2">
         <v>98</v>
@@ -7357,7 +7419,7 @@
         <v>1124</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="I79" s="2">
         <v>20000</v>
@@ -7375,10 +7437,10 @@
         <v>0</v>
       </c>
       <c r="N79" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O79" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P79" s="2"/>
     </row>
@@ -7387,7 +7449,7 @@
         <v>1074</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E80" s="2">
         <v>98</v>
@@ -7399,7 +7461,7 @@
         <v>1125</v>
       </c>
       <c r="H80" s="20" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="I80" s="2">
         <v>20000</v>
@@ -7417,10 +7479,10 @@
         <v>0</v>
       </c>
       <c r="N80" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O80" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P80" s="2"/>
     </row>
@@ -7429,7 +7491,7 @@
         <v>1075</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E81" s="2">
         <v>98</v>
@@ -7441,7 +7503,7 @@
         <v>1126</v>
       </c>
       <c r="H81" s="20" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="I81" s="2">
         <v>20000</v>
@@ -7459,10 +7521,10 @@
         <v>0</v>
       </c>
       <c r="N81" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O81" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P81" s="2"/>
     </row>
@@ -7471,7 +7533,7 @@
         <v>1076</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E82" s="2">
         <v>98</v>
@@ -7483,7 +7545,7 @@
         <v>1127</v>
       </c>
       <c r="H82" s="20" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I82" s="2">
         <v>20000</v>
@@ -7501,10 +7563,10 @@
         <v>0</v>
       </c>
       <c r="N82" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O82" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P82" s="2"/>
     </row>
@@ -7513,7 +7575,7 @@
         <v>1077</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E83" s="2">
         <v>98</v>
@@ -7525,7 +7587,7 @@
         <v>1128</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="I83" s="2">
         <v>20000</v>
@@ -7543,10 +7605,10 @@
         <v>0</v>
       </c>
       <c r="N83" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O83" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P83" s="2"/>
     </row>
@@ -7555,7 +7617,7 @@
         <v>1078</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E84" s="2">
         <v>98</v>
@@ -7567,7 +7629,7 @@
         <v>1129</v>
       </c>
       <c r="H84" s="20" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="I84" s="2">
         <v>20000</v>
@@ -7585,10 +7647,10 @@
         <v>0</v>
       </c>
       <c r="N84" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O84" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P84" s="2"/>
     </row>
@@ -7597,7 +7659,7 @@
         <v>1079</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E85" s="2">
         <v>98</v>
@@ -7609,7 +7671,7 @@
         <v>1130</v>
       </c>
       <c r="H85" s="20" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I85" s="2">
         <v>20000</v>
@@ -7627,10 +7689,10 @@
         <v>0</v>
       </c>
       <c r="N85" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O85" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P85" s="2"/>
     </row>
@@ -7639,7 +7701,7 @@
         <v>1080</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E86" s="2">
         <v>98</v>
@@ -7651,7 +7713,7 @@
         <v>1131</v>
       </c>
       <c r="H86" s="20" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I86" s="2">
         <v>20000</v>
@@ -7669,10 +7731,10 @@
         <v>0</v>
       </c>
       <c r="N86" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O86" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P86" s="2"/>
     </row>
@@ -7681,7 +7743,7 @@
         <v>1081</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E87" s="2">
         <v>98</v>
@@ -7693,7 +7755,7 @@
         <v>1132</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I87" s="2">
         <v>20000</v>
@@ -7711,10 +7773,10 @@
         <v>0</v>
       </c>
       <c r="N87" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O87" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P87" s="2"/>
     </row>
@@ -7723,7 +7785,7 @@
         <v>1082</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E88" s="2">
         <v>98</v>
@@ -7735,7 +7797,7 @@
         <v>1133</v>
       </c>
       <c r="H88" s="20" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="I88" s="2">
         <v>20000</v>
@@ -7753,10 +7815,10 @@
         <v>0</v>
       </c>
       <c r="N88" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O88" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P88" s="2"/>
     </row>
@@ -7765,7 +7827,7 @@
         <v>1083</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E89" s="2">
         <v>98</v>
@@ -7777,7 +7839,7 @@
         <v>1134</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="I89" s="2">
         <v>20000</v>
@@ -7795,10 +7857,10 @@
         <v>0</v>
       </c>
       <c r="N89" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O89" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P89" s="2"/>
     </row>
@@ -7807,7 +7869,7 @@
         <v>1084</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E90" s="2">
         <v>98</v>
@@ -7819,7 +7881,7 @@
         <v>1135</v>
       </c>
       <c r="H90" s="20" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="I90" s="2">
         <v>20000</v>
@@ -7837,10 +7899,10 @@
         <v>0</v>
       </c>
       <c r="N90" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O90" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P90" s="2"/>
     </row>
@@ -7849,7 +7911,7 @@
         <v>1085</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E91" s="2">
         <v>98</v>
@@ -7861,7 +7923,7 @@
         <v>1136</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I91" s="2">
         <v>20000</v>
@@ -7879,10 +7941,10 @@
         <v>0</v>
       </c>
       <c r="N91" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O91" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P91" s="2"/>
     </row>
@@ -7891,7 +7953,7 @@
         <v>1086</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E92" s="2">
         <v>98</v>
@@ -7903,7 +7965,7 @@
         <v>1137</v>
       </c>
       <c r="H92" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="I92" s="2">
         <v>20000</v>
@@ -7921,10 +7983,10 @@
         <v>0</v>
       </c>
       <c r="N92" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O92" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P92" s="2"/>
     </row>
@@ -7933,7 +7995,7 @@
         <v>1087</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E93" s="2">
         <v>98</v>
@@ -7945,7 +8007,7 @@
         <v>1138</v>
       </c>
       <c r="H93" s="20" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="I93" s="2">
         <v>20000</v>
@@ -7963,10 +8025,10 @@
         <v>0</v>
       </c>
       <c r="N93" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O93" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P93" s="2"/>
     </row>
@@ -7975,7 +8037,7 @@
         <v>1088</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E94" s="2">
         <v>98</v>
@@ -7987,7 +8049,7 @@
         <v>1139</v>
       </c>
       <c r="H94" s="20" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="I94" s="2">
         <v>20000</v>
@@ -8005,10 +8067,10 @@
         <v>0</v>
       </c>
       <c r="N94" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O94" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P94" s="2"/>
     </row>
@@ -8017,7 +8079,7 @@
         <v>1089</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="E95" s="12">
         <v>98</v>
@@ -8029,7 +8091,7 @@
         <v>1140</v>
       </c>
       <c r="H95" s="21" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="I95" s="12">
         <v>30000</v>
@@ -8047,10 +8109,10 @@
         <v>0</v>
       </c>
       <c r="N95" s="22" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O95" s="22" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="96" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8058,7 +8120,7 @@
         <v>1090</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="E96" s="2">
         <v>98</v>
@@ -8070,7 +8132,7 @@
         <v>1141</v>
       </c>
       <c r="H96" s="20" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="I96" s="2">
         <v>30000</v>
@@ -8088,10 +8150,10 @@
         <v>0</v>
       </c>
       <c r="N96" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O96" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="97" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8099,7 +8161,7 @@
         <v>1091</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E97" s="2">
         <v>98</v>
@@ -8111,7 +8173,7 @@
         <v>1142</v>
       </c>
       <c r="H97" s="20" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="I97" s="2">
         <v>30000</v>
@@ -8129,10 +8191,10 @@
         <v>0</v>
       </c>
       <c r="N97" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O97" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="98" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8140,7 +8202,7 @@
         <v>1092</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="E98" s="2">
         <v>98</v>
@@ -8152,7 +8214,7 @@
         <v>1143</v>
       </c>
       <c r="H98" s="20" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="I98" s="2">
         <v>30000</v>
@@ -8170,10 +8232,10 @@
         <v>0</v>
       </c>
       <c r="N98" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O98" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:16">
@@ -8181,7 +8243,7 @@
         <v>1093</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E99" s="2">
         <v>98</v>
@@ -8193,7 +8255,7 @@
         <v>1144</v>
       </c>
       <c r="H99" s="20" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="I99" s="2">
         <v>30000</v>
@@ -8211,10 +8273,10 @@
         <v>0</v>
       </c>
       <c r="N99" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O99" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P99" s="2"/>
     </row>
@@ -8223,7 +8285,7 @@
         <v>1094</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E100" s="2">
         <v>98</v>
@@ -8235,7 +8297,7 @@
         <v>1145</v>
       </c>
       <c r="H100" s="20" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="I100" s="2">
         <v>30000</v>
@@ -8253,10 +8315,10 @@
         <v>0</v>
       </c>
       <c r="N100" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O100" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="101" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8264,7 +8326,7 @@
         <v>1095</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E101" s="2">
         <v>98</v>
@@ -8276,7 +8338,7 @@
         <v>1146</v>
       </c>
       <c r="H101" s="20" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="I101" s="2">
         <v>30000</v>
@@ -8294,10 +8356,10 @@
         <v>0</v>
       </c>
       <c r="N101" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O101" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="102" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8305,7 +8367,7 @@
         <v>1096</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E102" s="2">
         <v>98</v>
@@ -8317,7 +8379,7 @@
         <v>1147</v>
       </c>
       <c r="H102" s="20" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="I102" s="2">
         <v>30000</v>
@@ -8335,10 +8397,10 @@
         <v>0</v>
       </c>
       <c r="N102" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O102" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="103" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8346,7 +8408,7 @@
         <v>1097</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="E103" s="2">
         <v>98</v>
@@ -8358,7 +8420,7 @@
         <v>1148</v>
       </c>
       <c r="H103" s="20" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="I103" s="2">
         <v>30000</v>
@@ -8376,10 +8438,10 @@
         <v>0</v>
       </c>
       <c r="N103" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O103" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:16">
@@ -8387,7 +8449,7 @@
         <v>1098</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="E104" s="2">
         <v>98</v>
@@ -8399,7 +8461,7 @@
         <v>1149</v>
       </c>
       <c r="H104" s="20" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="I104" s="2">
         <v>30000</v>
@@ -8417,10 +8479,10 @@
         <v>0</v>
       </c>
       <c r="N104" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O104" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P104" s="2"/>
     </row>
@@ -8429,7 +8491,7 @@
         <v>1099</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E105" s="2">
         <v>98</v>
@@ -8441,7 +8503,7 @@
         <v>1150</v>
       </c>
       <c r="H105" s="20" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="I105" s="2">
         <v>30000</v>
@@ -8459,10 +8521,10 @@
         <v>0</v>
       </c>
       <c r="N105" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O105" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P105" s="2"/>
     </row>
@@ -8471,7 +8533,7 @@
         <v>1100</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E106" s="2">
         <v>98</v>
@@ -8483,7 +8545,7 @@
         <v>1151</v>
       </c>
       <c r="H106" s="20" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="I106" s="2">
         <v>30000</v>
@@ -8501,10 +8563,10 @@
         <v>0</v>
       </c>
       <c r="N106" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O106" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P106" s="2"/>
     </row>
@@ -8513,7 +8575,7 @@
         <v>1101</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E107" s="2">
         <v>98</v>
@@ -8525,7 +8587,7 @@
         <v>1152</v>
       </c>
       <c r="H107" s="20" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="I107" s="2">
         <v>30000</v>
@@ -8543,10 +8605,10 @@
         <v>0</v>
       </c>
       <c r="N107" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O107" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P107" s="2"/>
     </row>
@@ -8555,7 +8617,7 @@
         <v>1102</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E108" s="2">
         <v>98</v>
@@ -8567,7 +8629,7 @@
         <v>1153</v>
       </c>
       <c r="H108" s="20" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I108" s="2">
         <v>30000</v>
@@ -8585,10 +8647,10 @@
         <v>0</v>
       </c>
       <c r="N108" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O108" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P108" s="2"/>
     </row>
@@ -8597,7 +8659,7 @@
         <v>1103</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E109" s="2">
         <v>98</v>
@@ -8609,7 +8671,7 @@
         <v>1154</v>
       </c>
       <c r="H109" s="20" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="I109" s="2">
         <v>30000</v>
@@ -8627,10 +8689,10 @@
         <v>0</v>
       </c>
       <c r="N109" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O109" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P109" s="2"/>
     </row>
@@ -8639,7 +8701,7 @@
         <v>1104</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E110" s="2">
         <v>98</v>
@@ -8651,7 +8713,7 @@
         <v>1155</v>
       </c>
       <c r="H110" s="20" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="I110" s="2">
         <v>30000</v>
@@ -8669,10 +8731,10 @@
         <v>0</v>
       </c>
       <c r="N110" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O110" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P110" s="2"/>
     </row>
@@ -8681,7 +8743,7 @@
         <v>1105</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E111" s="2">
         <v>98</v>
@@ -8693,7 +8755,7 @@
         <v>1156</v>
       </c>
       <c r="H111" s="20" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="I111" s="2">
         <v>30000</v>
@@ -8711,10 +8773,10 @@
         <v>0</v>
       </c>
       <c r="N111" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O111" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P111" s="2"/>
     </row>
@@ -8723,7 +8785,7 @@
         <v>1106</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="E112" s="2">
         <v>98</v>
@@ -8735,7 +8797,7 @@
         <v>1157</v>
       </c>
       <c r="H112" s="20" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I112" s="2">
         <v>30000</v>
@@ -8753,10 +8815,10 @@
         <v>0</v>
       </c>
       <c r="N112" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O112" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P112" s="2"/>
     </row>
@@ -8765,7 +8827,7 @@
         <v>1107</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E113" s="2">
         <v>98</v>
@@ -8777,7 +8839,7 @@
         <v>1158</v>
       </c>
       <c r="H113" s="20" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="I113" s="2">
         <v>30000</v>
@@ -8795,10 +8857,10 @@
         <v>0</v>
       </c>
       <c r="N113" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O113" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P113" s="2"/>
     </row>
@@ -8807,7 +8869,7 @@
         <v>1108</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E114" s="2">
         <v>98</v>
@@ -8819,7 +8881,7 @@
         <v>1159</v>
       </c>
       <c r="H114" s="20" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="I114" s="2">
         <v>30000</v>
@@ -8837,10 +8899,10 @@
         <v>0</v>
       </c>
       <c r="N114" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O114" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P114" s="2"/>
     </row>
@@ -8849,7 +8911,7 @@
         <v>1109</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="E115" s="2">
         <v>98</v>
@@ -8861,7 +8923,7 @@
         <v>1160</v>
       </c>
       <c r="H115" s="20" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="I115" s="2">
         <v>30000</v>
@@ -8879,10 +8941,10 @@
         <v>0</v>
       </c>
       <c r="N115" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O115" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P115" s="2"/>
     </row>
@@ -8891,7 +8953,7 @@
         <v>1110</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="E116" s="2">
         <v>98</v>
@@ -8903,7 +8965,7 @@
         <v>1161</v>
       </c>
       <c r="H116" s="20" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="I116" s="2">
         <v>30000</v>
@@ -8921,10 +8983,10 @@
         <v>0</v>
       </c>
       <c r="N116" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O116" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P116" s="2"/>
     </row>
@@ -8933,7 +8995,7 @@
         <v>1111</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="E117" s="2">
         <v>98</v>
@@ -8945,7 +9007,7 @@
         <v>1162</v>
       </c>
       <c r="H117" s="20" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I117" s="2">
         <v>30000</v>
@@ -8963,10 +9025,10 @@
         <v>0</v>
       </c>
       <c r="N117" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O117" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P117" s="2"/>
     </row>
@@ -8975,7 +9037,7 @@
         <v>1112</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E118" s="2">
         <v>98</v>
@@ -8987,7 +9049,7 @@
         <v>1163</v>
       </c>
       <c r="H118" s="20" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="I118" s="2">
         <v>30000</v>
@@ -9005,10 +9067,10 @@
         <v>0</v>
       </c>
       <c r="N118" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O118" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P118" s="2"/>
     </row>
@@ -9017,7 +9079,7 @@
         <v>1113</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="E119" s="2">
         <v>98</v>
@@ -9029,7 +9091,7 @@
         <v>1164</v>
       </c>
       <c r="H119" s="20" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I119" s="2">
         <v>30000</v>
@@ -9047,10 +9109,10 @@
         <v>0</v>
       </c>
       <c r="N119" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O119" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P119" s="2"/>
     </row>
@@ -9059,7 +9121,7 @@
         <v>1114</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E120" s="2">
         <v>98</v>
@@ -9071,7 +9133,7 @@
         <v>1165</v>
       </c>
       <c r="H120" s="20" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="I120" s="2">
         <v>30000</v>
@@ -9089,10 +9151,10 @@
         <v>0</v>
       </c>
       <c r="N120" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O120" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P120" s="2"/>
     </row>
@@ -9101,7 +9163,7 @@
         <v>1115</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="E121" s="2">
         <v>98</v>
@@ -9113,7 +9175,7 @@
         <v>1166</v>
       </c>
       <c r="H121" s="20" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="I121" s="2">
         <v>30000</v>
@@ -9131,10 +9193,10 @@
         <v>0</v>
       </c>
       <c r="N121" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O121" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P121" s="2"/>
     </row>
@@ -9143,7 +9205,7 @@
         <v>1116</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E122" s="2">
         <v>98</v>
@@ -9155,7 +9217,7 @@
         <v>1167</v>
       </c>
       <c r="H122" s="20" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="I122" s="2">
         <v>30000</v>
@@ -9173,10 +9235,10 @@
         <v>0</v>
       </c>
       <c r="N122" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O122" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P122" s="2"/>
     </row>
@@ -9185,7 +9247,7 @@
         <v>1117</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="E123" s="2">
         <v>98</v>
@@ -9197,7 +9259,7 @@
         <v>1168</v>
       </c>
       <c r="H123" s="20" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="I123" s="2">
         <v>30000</v>
@@ -9215,10 +9277,10 @@
         <v>0</v>
       </c>
       <c r="N123" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O123" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P123" s="2"/>
     </row>
@@ -9227,7 +9289,7 @@
         <v>1118</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="E124" s="2">
         <v>98</v>
@@ -9239,7 +9301,7 @@
         <v>1169</v>
       </c>
       <c r="H124" s="20" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="I124" s="2">
         <v>30000</v>
@@ -9257,10 +9319,10 @@
         <v>0</v>
       </c>
       <c r="N124" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O124" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P124" s="2"/>
     </row>
@@ -9269,7 +9331,7 @@
         <v>1119</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="E125" s="2">
         <v>98</v>
@@ -9281,7 +9343,7 @@
         <v>1170</v>
       </c>
       <c r="H125" s="20" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="I125" s="2">
         <v>30000</v>
@@ -9299,10 +9361,10 @@
         <v>0</v>
       </c>
       <c r="N125" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O125" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P125" s="2"/>
     </row>
@@ -9311,7 +9373,7 @@
         <v>1120</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E126" s="2">
         <v>98</v>
@@ -9323,7 +9385,7 @@
         <v>1171</v>
       </c>
       <c r="H126" s="20" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="I126" s="2">
         <v>30000</v>
@@ -9341,10 +9403,10 @@
         <v>0</v>
       </c>
       <c r="N126" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O126" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P126" s="2"/>
     </row>
@@ -9353,7 +9415,7 @@
         <v>1121</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="E127" s="2">
         <v>98</v>
@@ -9365,7 +9427,7 @@
         <v>1172</v>
       </c>
       <c r="H127" s="20" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="I127" s="2">
         <v>30000</v>
@@ -9383,10 +9445,10 @@
         <v>0</v>
       </c>
       <c r="N127" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O127" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P127" s="2"/>
     </row>
@@ -9395,7 +9457,7 @@
         <v>1122</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E128" s="2">
         <v>98</v>
@@ -9407,7 +9469,7 @@
         <v>1173</v>
       </c>
       <c r="H128" s="20" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="I128" s="2">
         <v>30000</v>
@@ -9425,10 +9487,10 @@
         <v>0</v>
       </c>
       <c r="N128" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O128" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P128" s="2"/>
     </row>
@@ -9437,7 +9499,7 @@
         <v>1123</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="E129" s="2">
         <v>98</v>
@@ -9449,7 +9511,7 @@
         <v>1174</v>
       </c>
       <c r="H129" s="20" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="I129" s="2">
         <v>30000</v>
@@ -9467,10 +9529,10 @@
         <v>0</v>
       </c>
       <c r="N129" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O129" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P129" s="2"/>
     </row>
@@ -9490,17 +9552,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="8.75221238938053" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.8761061946903" style="1" customWidth="1"/>
-    <col min="5" max="7" width="13.6283185840708" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5044247787611" style="3" customWidth="1"/>
-    <col min="9" max="9" width="17.8761061946903" style="3" customWidth="1"/>
-    <col min="10" max="12" width="13.7522123893805" style="3" customWidth="1"/>
-    <col min="13" max="14" width="14.1238938053097" style="3" customWidth="1"/>
-    <col min="15" max="16" width="20.6283185840708" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.875" style="1" customWidth="1"/>
+    <col min="5" max="7" width="13.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5083333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="17.875" style="3" customWidth="1"/>
+    <col min="10" max="12" width="13.75" style="3" customWidth="1"/>
+    <col min="13" max="14" width="14.125" style="3" customWidth="1"/>
+    <col min="15" max="16" width="20.625" style="3" customWidth="1"/>
     <col min="17" max="16383" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -9527,7 +9589,7 @@
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="3:16">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="3:16">
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
@@ -9571,7 +9633,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="3:16">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="3:16">
       <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
@@ -9615,7 +9677,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="3:16">
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="3:16">
       <c r="C5" s="5" t="s">
         <v>24</v>
       </c>
@@ -9664,7 +9726,7 @@
         <v>2000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -9676,7 +9738,7 @@
         <v>1070</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="I6" s="2">
         <v>120000</v>
@@ -9697,10 +9759,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P6" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -9708,7 +9770,7 @@
         <v>2001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -9720,7 +9782,7 @@
         <v>1071</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="I7" s="2">
         <v>120000</v>
@@ -9741,10 +9803,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P7" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -9752,7 +9814,7 @@
         <v>2002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -9764,7 +9826,7 @@
         <v>1072</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I8" s="2">
         <v>120000</v>
@@ -9785,10 +9847,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P8" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -9796,7 +9858,7 @@
         <v>2003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -9808,7 +9870,7 @@
         <v>1073</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="I9" s="2">
         <v>120000</v>
@@ -9829,10 +9891,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P9" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -9840,7 +9902,7 @@
         <v>2004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -9852,7 +9914,7 @@
         <v>1074</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I10" s="2">
         <v>120000</v>
@@ -9873,10 +9935,10 @@
         <v>0</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P10" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -9884,7 +9946,7 @@
         <v>2005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -9896,7 +9958,7 @@
         <v>1104</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I11" s="2">
         <v>20000</v>
@@ -9917,10 +9979,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P11" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
@@ -9942,7 +10004,7 @@
         <v>2006</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -9954,7 +10016,7 @@
         <v>1105</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="I14" s="2">
         <v>360000</v>
@@ -9975,10 +10037,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P14" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -9986,7 +10048,7 @@
         <v>2007</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -9998,7 +10060,7 @@
         <v>1106</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="I15" s="2">
         <v>360000</v>
@@ -10019,10 +10081,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P15" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10030,7 +10092,7 @@
         <v>2008</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -10042,7 +10104,7 @@
         <v>1107</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="I16" s="2">
         <v>360000</v>
@@ -10063,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10074,7 +10136,7 @@
         <v>2009</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -10086,7 +10148,7 @@
         <v>1108</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="I17" s="2">
         <v>360000</v>
@@ -10107,10 +10169,10 @@
         <v>0</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P17" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10118,7 +10180,7 @@
         <v>2010</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -10130,7 +10192,7 @@
         <v>1139</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I18" s="2">
         <v>360000</v>
@@ -10151,10 +10213,10 @@
         <v>0</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P18" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10162,7 +10224,7 @@
         <v>2011</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -10174,7 +10236,7 @@
         <v>1139</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -10195,10 +10257,10 @@
         <v>0</v>
       </c>
       <c r="O19" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P19" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
@@ -10213,7 +10275,7 @@
         <v>2012</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -10225,7 +10287,7 @@
         <v>1140</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="I21" s="2">
         <v>360000</v>
@@ -10246,10 +10308,10 @@
         <v>0</v>
       </c>
       <c r="O21" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P21" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10257,7 +10319,7 @@
         <v>2013</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -10269,7 +10331,7 @@
         <v>1141</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="I22" s="2">
         <v>360000</v>
@@ -10290,10 +10352,10 @@
         <v>0</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P22" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10301,7 +10363,7 @@
         <v>2014</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -10313,7 +10375,7 @@
         <v>1142</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="I23" s="2">
         <v>360000</v>
@@ -10334,10 +10396,10 @@
         <v>0</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P23" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10345,7 +10407,7 @@
         <v>2015</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -10357,7 +10419,7 @@
         <v>1143</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="I24" s="2">
         <v>360000</v>
@@ -10378,10 +10440,10 @@
         <v>0</v>
       </c>
       <c r="O24" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P24" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10389,7 +10451,7 @@
         <v>2016</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -10401,7 +10463,7 @@
         <v>1174</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="I25" s="2">
         <v>360000</v>
@@ -10422,10 +10484,10 @@
         <v>0</v>
       </c>
       <c r="O25" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P25" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10433,7 +10495,7 @@
         <v>2017</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -10445,7 +10507,7 @@
         <v>1174</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="I26" s="2">
         <v>180000</v>
@@ -10466,24 +10528,24 @@
         <v>0</v>
       </c>
       <c r="O26" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P26" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>394</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>394</v>
+        <v>26</v>
       </c>
       <c r="C27" s="2">
         <v>2018</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -10495,7 +10557,7 @@
         <v>1174</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>
@@ -10516,10 +10578,10 @@
         <v>0</v>
       </c>
       <c r="O27" s="18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P27" s="18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
@@ -10693,7 +10755,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 C2:C5 F3:G5 F14:G19 F21:G27" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 C2:C5 F14:G19 F3:G5 F21:G27" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -1658,12 +1658,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2505,7 +2505,8 @@
     <col min="10" max="12" width="13.75" style="16" customWidth="1"/>
     <col min="13" max="14" width="14.125" style="16" customWidth="1"/>
     <col min="15" max="16" width="20.625" style="16" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="2"/>
+    <col min="17" max="17" width="9.66666666666667" style="2"/>
+    <col min="18" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="8:16">

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -361,7 +361,7 @@
     <t>30</t>
   </si>
   <si>
-    <t>2025-07-27</t>
+    <t>2025-08-01</t>
   </si>
   <si>
     <t>2025-08-07</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -364,7 +364,7 @@
     <t>2025-08-01</t>
   </si>
   <si>
-    <t>2025-08-07</t>
+    <t>2025-08-09</t>
   </si>
   <si>
     <t>平时部分掉落</t>
@@ -1658,12 +1658,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="395">
   <si>
     <t>_id</t>
   </si>
@@ -337,1123 +337,1111 @@
     <t>string</t>
   </si>
   <si>
+    <t>快乐暑假</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>2025-07-04</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>平时部分掉落</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>2024-10-31</t>
+  </si>
+  <si>
+    <t>2025-10-21</t>
+  </si>
+  <si>
+    <t>第一批白图鉴</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>6000</t>
+  </si>
+  <si>
+    <t>2023-10-21</t>
+  </si>
+  <si>
+    <t>第一批绿图鉴</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>12000</t>
+  </si>
+  <si>
+    <t>第一批蓝图鉴</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>第一批紫图鉴</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>第二批白图鉴</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>第二批绿图鉴</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>第二批蓝图鉴</t>
+  </si>
+  <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>第二批紫图鉴</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>20000</t>
+  </si>
+  <si>
+    <t>第三批白图鉴</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>4000</t>
+  </si>
+  <si>
+    <t>第三批绿图鉴</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>8000</t>
+  </si>
+  <si>
+    <t>第三批蓝图鉴</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>第三批紫图鉴</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>16000</t>
+  </si>
+  <si>
+    <t>龙城100书页</t>
+  </si>
+  <si>
+    <t>1002</t>
+  </si>
+  <si>
+    <t>龙城图鉴</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>龙城时装</t>
+  </si>
+  <si>
+    <t>3001</t>
+  </si>
+  <si>
+    <t>第一时装</t>
+  </si>
+  <si>
+    <t>150000</t>
+  </si>
+  <si>
+    <t>第二时装</t>
+  </si>
+  <si>
+    <t>3002</t>
+  </si>
+  <si>
+    <t>第三时装</t>
+  </si>
+  <si>
+    <t>3003</t>
+  </si>
+  <si>
+    <t>30000</t>
+  </si>
+  <si>
+    <t>120000</t>
+  </si>
+  <si>
+    <t>第四时装</t>
+  </si>
+  <si>
+    <t>3004</t>
+  </si>
+  <si>
+    <t>40000</t>
+  </si>
+  <si>
+    <t>专属之心</t>
+  </si>
+  <si>
+    <t>1004</t>
+  </si>
+  <si>
+    <t>冠名图鉴</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>冠名图鉴2</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>龙之图鉴</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>龙之图鉴2</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>240000</t>
+  </si>
+  <si>
+    <t>金图鉴1</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>250000</t>
+  </si>
+  <si>
+    <t>金图鉴2</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>200000</t>
+  </si>
+  <si>
+    <t>800000</t>
+  </si>
+  <si>
+    <t>金图鉴3</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>1000000</t>
+  </si>
+  <si>
+    <t>镜像挑战</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>幻境十层</t>
+  </si>
+  <si>
+    <t>1008</t>
+  </si>
+  <si>
+    <t>触龙之心</t>
+  </si>
+  <si>
+    <t>1400000</t>
+  </si>
+  <si>
+    <t>白猪之心</t>
+  </si>
+  <si>
+    <t>1400001</t>
+  </si>
+  <si>
+    <t>猪王之心</t>
+  </si>
+  <si>
+    <t>1400002</t>
+  </si>
+  <si>
+    <t>蝎王宝甲</t>
+  </si>
+  <si>
+    <t>1400003</t>
+  </si>
+  <si>
+    <t>沃玛宝甲</t>
+  </si>
+  <si>
+    <t>1400004</t>
+  </si>
+  <si>
+    <t>沃玛号角</t>
+  </si>
+  <si>
+    <t>1400005</t>
+  </si>
+  <si>
+    <t>祖玛头像</t>
+  </si>
+  <si>
+    <t>1400006</t>
+  </si>
+  <si>
+    <t>祖玛号角</t>
+  </si>
+  <si>
+    <t>1400007</t>
+  </si>
+  <si>
+    <t>虹猪宝甲</t>
+  </si>
+  <si>
+    <t>1400008</t>
+  </si>
+  <si>
+    <t>树妖之心</t>
+  </si>
+  <si>
+    <t>1400009</t>
+  </si>
+  <si>
+    <t>虹魔之心</t>
+  </si>
+  <si>
+    <t>1400010</t>
+  </si>
+  <si>
+    <t>尸王之心</t>
+  </si>
+  <si>
+    <t>1400011</t>
+  </si>
+  <si>
+    <t>黄泉法杖</t>
+  </si>
+  <si>
+    <t>1400012</t>
+  </si>
+  <si>
+    <t>牛魔权杖</t>
+  </si>
+  <si>
+    <t>1400013</t>
+  </si>
+  <si>
+    <t>金刚战锤</t>
+  </si>
+  <si>
+    <t>1400014</t>
+  </si>
+  <si>
+    <t>巨人之心</t>
+  </si>
+  <si>
+    <t>1400015</t>
+  </si>
+  <si>
+    <t>恶魔之心</t>
+  </si>
+  <si>
+    <t>1400016</t>
+  </si>
+  <si>
+    <t>魔龙宝甲</t>
+  </si>
+  <si>
+    <t>1400017</t>
+  </si>
+  <si>
+    <t>龙神利爪</t>
+  </si>
+  <si>
+    <t>1400018</t>
+  </si>
+  <si>
+    <t>梦魇鸡爪</t>
+  </si>
+  <si>
+    <t>1400019</t>
+  </si>
+  <si>
+    <t>梦魇鹿茸</t>
+  </si>
+  <si>
+    <t>1400020</t>
+  </si>
+  <si>
+    <t>梦魇草帽</t>
+  </si>
+  <si>
+    <t>1400021</t>
+  </si>
+  <si>
+    <t>梦魇猫爪</t>
+  </si>
+  <si>
+    <t>1400022</t>
+  </si>
+  <si>
+    <t>梦魇花朵</t>
+  </si>
+  <si>
+    <t>1400023</t>
+  </si>
+  <si>
+    <t>梦魇冰晶</t>
+  </si>
+  <si>
+    <t>1400024</t>
+  </si>
+  <si>
+    <t>梦魇蝠翼</t>
+  </si>
+  <si>
+    <t>1400025</t>
+  </si>
+  <si>
+    <t>梦魇魂火</t>
+  </si>
+  <si>
+    <t>1400026</t>
+  </si>
+  <si>
+    <t>梦魇腐肉</t>
+  </si>
+  <si>
+    <t>1400027</t>
+  </si>
+  <si>
+    <t>梦魇蛇胆</t>
+  </si>
+  <si>
+    <t>1400028</t>
+  </si>
+  <si>
+    <t>梦魇狼爪</t>
+  </si>
+  <si>
+    <t>1400029</t>
+  </si>
+  <si>
+    <t>梦魇虫皮</t>
+  </si>
+  <si>
+    <t>1400030</t>
+  </si>
+  <si>
+    <t>梦魇鹰羽</t>
+  </si>
+  <si>
+    <t>1400031</t>
+  </si>
+  <si>
+    <t>梦魇虫角</t>
+  </si>
+  <si>
+    <t>1400032</t>
+  </si>
+  <si>
+    <t>梦魇蜈膏</t>
+  </si>
+  <si>
+    <t>1400033</t>
+  </si>
+  <si>
+    <t>梦魇虫心</t>
+  </si>
+  <si>
+    <t>1400034</t>
+  </si>
+  <si>
+    <t>梦魇龙皮</t>
+  </si>
+  <si>
+    <t>1400035</t>
+  </si>
+  <si>
+    <t>梦魇猪皮</t>
+  </si>
+  <si>
+    <t>1400036</t>
+  </si>
+  <si>
+    <t>梦魇猪心</t>
+  </si>
+  <si>
+    <t>1400037</t>
+  </si>
+  <si>
+    <t>梦魇蝎皮</t>
+  </si>
+  <si>
+    <t>1400038</t>
+  </si>
+  <si>
+    <t>噩梦宝甲</t>
+  </si>
+  <si>
+    <t>1400039</t>
+  </si>
+  <si>
+    <t>噩梦号角</t>
+  </si>
+  <si>
+    <t>1400040</t>
+  </si>
+  <si>
+    <t>噩梦雕像</t>
+  </si>
+  <si>
+    <t>1400041</t>
+  </si>
+  <si>
+    <t>噩梦神像</t>
+  </si>
+  <si>
+    <t>1400042</t>
+  </si>
+  <si>
+    <t>噩梦獠牙</t>
+  </si>
+  <si>
+    <t>1400043</t>
+  </si>
+  <si>
+    <t>噩梦树心</t>
+  </si>
+  <si>
+    <t>1400044</t>
+  </si>
+  <si>
+    <t>噩梦魔心</t>
+  </si>
+  <si>
+    <t>1400045</t>
+  </si>
+  <si>
+    <t>噩梦尸心</t>
+  </si>
+  <si>
+    <t>1400046</t>
+  </si>
+  <si>
+    <t>噩梦法杖</t>
+  </si>
+  <si>
+    <t>1400047</t>
+  </si>
+  <si>
+    <t>噩梦权杖</t>
+  </si>
+  <si>
+    <t>1400048</t>
+  </si>
+  <si>
+    <t>噩梦战锤</t>
+  </si>
+  <si>
+    <t>1400049</t>
+  </si>
+  <si>
+    <t>噩梦血核</t>
+  </si>
+  <si>
+    <t>1400050</t>
+  </si>
+  <si>
+    <t>噩梦魔核</t>
+  </si>
+  <si>
+    <t>1400051</t>
+  </si>
+  <si>
+    <t>噩梦龙甲</t>
+  </si>
+  <si>
+    <t>1400052</t>
+  </si>
+  <si>
+    <t>噩梦龙爪</t>
+  </si>
+  <si>
+    <t>1400053</t>
+  </si>
+  <si>
+    <t>地狱鸡爪</t>
+  </si>
+  <si>
+    <t>1400054</t>
+  </si>
+  <si>
+    <t>地狱鹿茸</t>
+  </si>
+  <si>
+    <t>1400055</t>
+  </si>
+  <si>
+    <t>地狱草帽</t>
+  </si>
+  <si>
+    <t>1400056</t>
+  </si>
+  <si>
+    <t>地狱猫爪</t>
+  </si>
+  <si>
+    <t>1400057</t>
+  </si>
+  <si>
+    <t>地狱花朵</t>
+  </si>
+  <si>
+    <t>1400058</t>
+  </si>
+  <si>
+    <t>地狱冰晶</t>
+  </si>
+  <si>
+    <t>1400059</t>
+  </si>
+  <si>
+    <t>地狱蝠翼</t>
+  </si>
+  <si>
+    <t>1400060</t>
+  </si>
+  <si>
+    <t>地狱魂火</t>
+  </si>
+  <si>
+    <t>1400061</t>
+  </si>
+  <si>
+    <t>地狱腐肉</t>
+  </si>
+  <si>
+    <t>1400062</t>
+  </si>
+  <si>
+    <t>地狱蛇胆</t>
+  </si>
+  <si>
+    <t>1400063</t>
+  </si>
+  <si>
+    <t>地狱狼爪</t>
+  </si>
+  <si>
+    <t>1400064</t>
+  </si>
+  <si>
+    <t>地狱虫皮</t>
+  </si>
+  <si>
+    <t>1400065</t>
+  </si>
+  <si>
+    <t>地狱鹰羽</t>
+  </si>
+  <si>
+    <t>1400066</t>
+  </si>
+  <si>
+    <t>地狱虫角</t>
+  </si>
+  <si>
+    <t>1400067</t>
+  </si>
+  <si>
+    <t>地狱蜈膏</t>
+  </si>
+  <si>
+    <t>1400068</t>
+  </si>
+  <si>
+    <t>地狱虫心</t>
+  </si>
+  <si>
+    <t>1400069</t>
+  </si>
+  <si>
+    <t>地狱龙皮</t>
+  </si>
+  <si>
+    <t>1400070</t>
+  </si>
+  <si>
+    <t>地狱猪皮</t>
+  </si>
+  <si>
+    <t>1400071</t>
+  </si>
+  <si>
+    <t>地狱猪心</t>
+  </si>
+  <si>
+    <t>1400072</t>
+  </si>
+  <si>
+    <t>地狱蝎皮</t>
+  </si>
+  <si>
+    <t>1400073</t>
+  </si>
+  <si>
+    <t>地狱宝甲</t>
+  </si>
+  <si>
+    <t>1400074</t>
+  </si>
+  <si>
+    <t>地狱号角</t>
+  </si>
+  <si>
+    <t>1400075</t>
+  </si>
+  <si>
+    <t>地狱雕像</t>
+  </si>
+  <si>
+    <t>1400076</t>
+  </si>
+  <si>
+    <t>地狱神像</t>
+  </si>
+  <si>
+    <t>1400077</t>
+  </si>
+  <si>
+    <t>地狱獠牙</t>
+  </si>
+  <si>
+    <t>1400078</t>
+  </si>
+  <si>
+    <t>地狱树心</t>
+  </si>
+  <si>
+    <t>1400079</t>
+  </si>
+  <si>
+    <t>地狱魔心</t>
+  </si>
+  <si>
+    <t>1400080</t>
+  </si>
+  <si>
+    <t>地狱尸心</t>
+  </si>
+  <si>
+    <t>1400081</t>
+  </si>
+  <si>
+    <t>地狱法杖</t>
+  </si>
+  <si>
+    <t>1400082</t>
+  </si>
+  <si>
+    <t>地狱权杖</t>
+  </si>
+  <si>
+    <t>1400083</t>
+  </si>
+  <si>
+    <t>地狱战锤</t>
+  </si>
+  <si>
+    <t>1400084</t>
+  </si>
+  <si>
+    <t>地狱血核</t>
+  </si>
+  <si>
+    <t>1400085</t>
+  </si>
+  <si>
+    <t>地狱魔核</t>
+  </si>
+  <si>
+    <t>1400086</t>
+  </si>
+  <si>
+    <t>地狱龙甲</t>
+  </si>
+  <si>
+    <t>1400087</t>
+  </si>
+  <si>
+    <t>地狱龙爪</t>
+  </si>
+  <si>
+    <t>1400088</t>
+  </si>
+  <si>
+    <t>深渊鸡爪</t>
+  </si>
+  <si>
+    <t>1400089</t>
+  </si>
+  <si>
+    <t>深渊鹿茸</t>
+  </si>
+  <si>
+    <t>1400090</t>
+  </si>
+  <si>
+    <t>深渊草帽</t>
+  </si>
+  <si>
+    <t>1400091</t>
+  </si>
+  <si>
+    <t>深渊猫爪</t>
+  </si>
+  <si>
+    <t>1400092</t>
+  </si>
+  <si>
+    <t>深渊花朵</t>
+  </si>
+  <si>
+    <t>1400093</t>
+  </si>
+  <si>
+    <t>深渊冰晶</t>
+  </si>
+  <si>
+    <t>1400094</t>
+  </si>
+  <si>
+    <t>深渊蝠翼</t>
+  </si>
+  <si>
+    <t>1400095</t>
+  </si>
+  <si>
+    <t>深渊魂火</t>
+  </si>
+  <si>
+    <t>1400096</t>
+  </si>
+  <si>
+    <t>深渊腐肉</t>
+  </si>
+  <si>
+    <t>1400097</t>
+  </si>
+  <si>
+    <t>深渊蛇胆</t>
+  </si>
+  <si>
+    <t>1400098</t>
+  </si>
+  <si>
+    <t>深渊狼爪</t>
+  </si>
+  <si>
+    <t>1400099</t>
+  </si>
+  <si>
+    <t>深渊虫皮</t>
+  </si>
+  <si>
+    <t>1400100</t>
+  </si>
+  <si>
+    <t>深渊鹰羽</t>
+  </si>
+  <si>
+    <t>1400101</t>
+  </si>
+  <si>
+    <t>深渊虫角</t>
+  </si>
+  <si>
+    <t>1400102</t>
+  </si>
+  <si>
+    <t>深渊蜈膏</t>
+  </si>
+  <si>
+    <t>1400103</t>
+  </si>
+  <si>
+    <t>深渊虫心</t>
+  </si>
+  <si>
+    <t>1400104</t>
+  </si>
+  <si>
+    <t>深渊龙皮</t>
+  </si>
+  <si>
+    <t>1400105</t>
+  </si>
+  <si>
+    <t>深渊猪皮</t>
+  </si>
+  <si>
+    <t>1400106</t>
+  </si>
+  <si>
+    <t>深渊猪心</t>
+  </si>
+  <si>
+    <t>1400107</t>
+  </si>
+  <si>
+    <t>深渊蝎皮</t>
+  </si>
+  <si>
+    <t>1400108</t>
+  </si>
+  <si>
+    <t>深渊宝甲</t>
+  </si>
+  <si>
+    <t>1400109</t>
+  </si>
+  <si>
+    <t>深渊号角</t>
+  </si>
+  <si>
+    <t>1400110</t>
+  </si>
+  <si>
+    <t>深渊雕像</t>
+  </si>
+  <si>
+    <t>1400111</t>
+  </si>
+  <si>
+    <t>深渊神像</t>
+  </si>
+  <si>
+    <t>1400112</t>
+  </si>
+  <si>
+    <t>深渊獠牙</t>
+  </si>
+  <si>
+    <t>1400113</t>
+  </si>
+  <si>
+    <t>深渊树心</t>
+  </si>
+  <si>
+    <t>1400114</t>
+  </si>
+  <si>
+    <t>深渊魔心</t>
+  </si>
+  <si>
+    <t>1400115</t>
+  </si>
+  <si>
+    <t>深渊尸心</t>
+  </si>
+  <si>
+    <t>1400116</t>
+  </si>
+  <si>
+    <t>深渊法杖</t>
+  </si>
+  <si>
+    <t>1400117</t>
+  </si>
+  <si>
+    <t>深渊权杖</t>
+  </si>
+  <si>
+    <t>1400118</t>
+  </si>
+  <si>
+    <t>深渊战锤</t>
+  </si>
+  <si>
+    <t>1400119</t>
+  </si>
+  <si>
+    <t>深渊血核</t>
+  </si>
+  <si>
+    <t>1400120</t>
+  </si>
+  <si>
+    <t>深渊魔核</t>
+  </si>
+  <si>
+    <t>1400121</t>
+  </si>
+  <si>
+    <t>深渊龙甲</t>
+  </si>
+  <si>
+    <t>1400122</t>
+  </si>
+  <si>
+    <t>深渊龙爪</t>
+  </si>
+  <si>
+    <t>1400123</t>
+  </si>
+  <si>
+    <t>武器衣服红装</t>
+  </si>
+  <si>
+    <t>210000</t>
+  </si>
+  <si>
+    <t>项链头盔红装</t>
+  </si>
+  <si>
+    <t>210001</t>
+  </si>
+  <si>
+    <t>手镯戒指红装</t>
+  </si>
+  <si>
+    <t>210002</t>
+  </si>
+  <si>
+    <t>腰带鞋子红装</t>
+  </si>
+  <si>
+    <t>210003</t>
+  </si>
+  <si>
+    <t>随机红装</t>
+  </si>
+  <si>
+    <t>210004</t>
+  </si>
+  <si>
+    <t>武器衣服金装</t>
+  </si>
+  <si>
+    <t>209995</t>
+  </si>
+  <si>
+    <t>项链头盔金装</t>
+  </si>
+  <si>
+    <t>209996</t>
+  </si>
+  <si>
+    <t>手镯戒指金装</t>
+  </si>
+  <si>
+    <t>209997</t>
+  </si>
+  <si>
+    <t>腰带鞋子金装</t>
+  </si>
+  <si>
+    <t>209998</t>
+  </si>
+  <si>
+    <t>随机金装</t>
+  </si>
+  <si>
+    <t>209999</t>
+  </si>
+  <si>
+    <t>武器衣服暗金</t>
+  </si>
+  <si>
+    <t>209990</t>
+  </si>
+  <si>
+    <t>项链头盔暗金</t>
+  </si>
+  <si>
+    <t>209991</t>
+  </si>
+  <si>
+    <t>手镯戒指暗金</t>
+  </si>
+  <si>
+    <t>209992</t>
+  </si>
+  <si>
+    <t>腰带鞋子暗金</t>
+  </si>
+  <si>
+    <t>209993</t>
+  </si>
+  <si>
+    <t>随机暗金</t>
+  </si>
+  <si>
+    <t>209994</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>快乐暑假</t>
-  </si>
-  <si>
-    <t>1005</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>2025-07-04</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>周年庆</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>2025-08-01</t>
-  </si>
-  <si>
-    <t>2025-08-09</t>
-  </si>
-  <si>
-    <t>平时部分掉落</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>2024-10-31</t>
-  </si>
-  <si>
-    <t>2025-10-21</t>
-  </si>
-  <si>
-    <t>第一批白图鉴</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>6000</t>
-  </si>
-  <si>
-    <t>2023-10-21</t>
-  </si>
-  <si>
-    <t>第一批绿图鉴</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>12000</t>
-  </si>
-  <si>
-    <t>第一批蓝图鉴</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>第一批紫图鉴</t>
-  </si>
-  <si>
-    <t>2013</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>第二批白图鉴</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>第二批绿图鉴</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>10000</t>
-  </si>
-  <si>
-    <t>第二批蓝图鉴</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
-    <t>15000</t>
-  </si>
-  <si>
-    <t>第二批紫图鉴</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>20000</t>
-  </si>
-  <si>
-    <t>第三批白图鉴</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>4000</t>
-  </si>
-  <si>
-    <t>第三批绿图鉴</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>8000</t>
-  </si>
-  <si>
-    <t>第三批蓝图鉴</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>第三批紫图鉴</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>16000</t>
-  </si>
-  <si>
-    <t>龙城100书页</t>
-  </si>
-  <si>
-    <t>1002</t>
-  </si>
-  <si>
-    <t>龙城图鉴</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>龙城时装</t>
-  </si>
-  <si>
-    <t>3001</t>
-  </si>
-  <si>
-    <t>第一时装</t>
-  </si>
-  <si>
-    <t>150000</t>
-  </si>
-  <si>
-    <t>第二时装</t>
-  </si>
-  <si>
-    <t>3002</t>
-  </si>
-  <si>
-    <t>第三时装</t>
-  </si>
-  <si>
-    <t>3003</t>
-  </si>
-  <si>
-    <t>30000</t>
-  </si>
-  <si>
-    <t>120000</t>
-  </si>
-  <si>
-    <t>第四时装</t>
-  </si>
-  <si>
-    <t>3004</t>
-  </si>
-  <si>
-    <t>40000</t>
-  </si>
-  <si>
-    <t>专属之心</t>
-  </si>
-  <si>
-    <t>1004</t>
-  </si>
-  <si>
-    <t>冠名图鉴</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>冠名图鉴2</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>龙之图鉴</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>龙之图鉴2</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>240000</t>
-  </si>
-  <si>
-    <t>金图鉴1</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>50000</t>
-  </si>
-  <si>
-    <t>250000</t>
-  </si>
-  <si>
-    <t>金图鉴2</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>200000</t>
-  </si>
-  <si>
-    <t>800000</t>
-  </si>
-  <si>
-    <t>金图鉴3</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>1000000</t>
-  </si>
-  <si>
-    <t>镜像挑战</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>幻境十层</t>
-  </si>
-  <si>
-    <t>1008</t>
-  </si>
-  <si>
-    <t>触龙之心</t>
-  </si>
-  <si>
-    <t>1400000</t>
-  </si>
-  <si>
-    <t>白猪之心</t>
-  </si>
-  <si>
-    <t>1400001</t>
-  </si>
-  <si>
-    <t>猪王之心</t>
-  </si>
-  <si>
-    <t>1400002</t>
-  </si>
-  <si>
-    <t>蝎王宝甲</t>
-  </si>
-  <si>
-    <t>1400003</t>
-  </si>
-  <si>
-    <t>沃玛宝甲</t>
-  </si>
-  <si>
-    <t>1400004</t>
-  </si>
-  <si>
-    <t>沃玛号角</t>
-  </si>
-  <si>
-    <t>1400005</t>
-  </si>
-  <si>
-    <t>祖玛头像</t>
-  </si>
-  <si>
-    <t>1400006</t>
-  </si>
-  <si>
-    <t>祖玛号角</t>
-  </si>
-  <si>
-    <t>1400007</t>
-  </si>
-  <si>
-    <t>虹猪宝甲</t>
-  </si>
-  <si>
-    <t>1400008</t>
-  </si>
-  <si>
-    <t>树妖之心</t>
-  </si>
-  <si>
-    <t>1400009</t>
-  </si>
-  <si>
-    <t>虹魔之心</t>
-  </si>
-  <si>
-    <t>1400010</t>
-  </si>
-  <si>
-    <t>尸王之心</t>
-  </si>
-  <si>
-    <t>1400011</t>
-  </si>
-  <si>
-    <t>黄泉法杖</t>
-  </si>
-  <si>
-    <t>1400012</t>
-  </si>
-  <si>
-    <t>牛魔权杖</t>
-  </si>
-  <si>
-    <t>1400013</t>
-  </si>
-  <si>
-    <t>金刚战锤</t>
-  </si>
-  <si>
-    <t>1400014</t>
-  </si>
-  <si>
-    <t>巨人之心</t>
-  </si>
-  <si>
-    <t>1400015</t>
-  </si>
-  <si>
-    <t>恶魔之心</t>
-  </si>
-  <si>
-    <t>1400016</t>
-  </si>
-  <si>
-    <t>魔龙宝甲</t>
-  </si>
-  <si>
-    <t>1400017</t>
-  </si>
-  <si>
-    <t>龙神利爪</t>
-  </si>
-  <si>
-    <t>1400018</t>
-  </si>
-  <si>
-    <t>梦魇鸡爪</t>
-  </si>
-  <si>
-    <t>1400019</t>
-  </si>
-  <si>
-    <t>梦魇鹿茸</t>
-  </si>
-  <si>
-    <t>1400020</t>
-  </si>
-  <si>
-    <t>梦魇草帽</t>
-  </si>
-  <si>
-    <t>1400021</t>
-  </si>
-  <si>
-    <t>梦魇猫爪</t>
-  </si>
-  <si>
-    <t>1400022</t>
-  </si>
-  <si>
-    <t>梦魇花朵</t>
-  </si>
-  <si>
-    <t>1400023</t>
-  </si>
-  <si>
-    <t>梦魇冰晶</t>
-  </si>
-  <si>
-    <t>1400024</t>
-  </si>
-  <si>
-    <t>梦魇蝠翼</t>
-  </si>
-  <si>
-    <t>1400025</t>
-  </si>
-  <si>
-    <t>梦魇魂火</t>
-  </si>
-  <si>
-    <t>1400026</t>
-  </si>
-  <si>
-    <t>梦魇腐肉</t>
-  </si>
-  <si>
-    <t>1400027</t>
-  </si>
-  <si>
-    <t>梦魇蛇胆</t>
-  </si>
-  <si>
-    <t>1400028</t>
-  </si>
-  <si>
-    <t>梦魇狼爪</t>
-  </si>
-  <si>
-    <t>1400029</t>
-  </si>
-  <si>
-    <t>梦魇虫皮</t>
-  </si>
-  <si>
-    <t>1400030</t>
-  </si>
-  <si>
-    <t>梦魇鹰羽</t>
-  </si>
-  <si>
-    <t>1400031</t>
-  </si>
-  <si>
-    <t>梦魇虫角</t>
-  </si>
-  <si>
-    <t>1400032</t>
-  </si>
-  <si>
-    <t>梦魇蜈膏</t>
-  </si>
-  <si>
-    <t>1400033</t>
-  </si>
-  <si>
-    <t>梦魇虫心</t>
-  </si>
-  <si>
-    <t>1400034</t>
-  </si>
-  <si>
-    <t>梦魇龙皮</t>
-  </si>
-  <si>
-    <t>1400035</t>
-  </si>
-  <si>
-    <t>梦魇猪皮</t>
-  </si>
-  <si>
-    <t>1400036</t>
-  </si>
-  <si>
-    <t>梦魇猪心</t>
-  </si>
-  <si>
-    <t>1400037</t>
-  </si>
-  <si>
-    <t>梦魇蝎皮</t>
-  </si>
-  <si>
-    <t>1400038</t>
-  </si>
-  <si>
-    <t>噩梦宝甲</t>
-  </si>
-  <si>
-    <t>1400039</t>
-  </si>
-  <si>
-    <t>噩梦号角</t>
-  </si>
-  <si>
-    <t>1400040</t>
-  </si>
-  <si>
-    <t>噩梦雕像</t>
-  </si>
-  <si>
-    <t>1400041</t>
-  </si>
-  <si>
-    <t>噩梦神像</t>
-  </si>
-  <si>
-    <t>1400042</t>
-  </si>
-  <si>
-    <t>噩梦獠牙</t>
-  </si>
-  <si>
-    <t>1400043</t>
-  </si>
-  <si>
-    <t>噩梦树心</t>
-  </si>
-  <si>
-    <t>1400044</t>
-  </si>
-  <si>
-    <t>噩梦魔心</t>
-  </si>
-  <si>
-    <t>1400045</t>
-  </si>
-  <si>
-    <t>噩梦尸心</t>
-  </si>
-  <si>
-    <t>1400046</t>
-  </si>
-  <si>
-    <t>噩梦法杖</t>
-  </si>
-  <si>
-    <t>1400047</t>
-  </si>
-  <si>
-    <t>噩梦权杖</t>
-  </si>
-  <si>
-    <t>1400048</t>
-  </si>
-  <si>
-    <t>噩梦战锤</t>
-  </si>
-  <si>
-    <t>1400049</t>
-  </si>
-  <si>
-    <t>噩梦血核</t>
-  </si>
-  <si>
-    <t>1400050</t>
-  </si>
-  <si>
-    <t>噩梦魔核</t>
-  </si>
-  <si>
-    <t>1400051</t>
-  </si>
-  <si>
-    <t>噩梦龙甲</t>
-  </si>
-  <si>
-    <t>1400052</t>
-  </si>
-  <si>
-    <t>噩梦龙爪</t>
-  </si>
-  <si>
-    <t>1400053</t>
-  </si>
-  <si>
-    <t>地狱鸡爪</t>
-  </si>
-  <si>
-    <t>1400054</t>
-  </si>
-  <si>
-    <t>地狱鹿茸</t>
-  </si>
-  <si>
-    <t>1400055</t>
-  </si>
-  <si>
-    <t>地狱草帽</t>
-  </si>
-  <si>
-    <t>1400056</t>
-  </si>
-  <si>
-    <t>地狱猫爪</t>
-  </si>
-  <si>
-    <t>1400057</t>
-  </si>
-  <si>
-    <t>地狱花朵</t>
-  </si>
-  <si>
-    <t>1400058</t>
-  </si>
-  <si>
-    <t>地狱冰晶</t>
-  </si>
-  <si>
-    <t>1400059</t>
-  </si>
-  <si>
-    <t>地狱蝠翼</t>
-  </si>
-  <si>
-    <t>1400060</t>
-  </si>
-  <si>
-    <t>地狱魂火</t>
-  </si>
-  <si>
-    <t>1400061</t>
-  </si>
-  <si>
-    <t>地狱腐肉</t>
-  </si>
-  <si>
-    <t>1400062</t>
-  </si>
-  <si>
-    <t>地狱蛇胆</t>
-  </si>
-  <si>
-    <t>1400063</t>
-  </si>
-  <si>
-    <t>地狱狼爪</t>
-  </si>
-  <si>
-    <t>1400064</t>
-  </si>
-  <si>
-    <t>地狱虫皮</t>
-  </si>
-  <si>
-    <t>1400065</t>
-  </si>
-  <si>
-    <t>地狱鹰羽</t>
-  </si>
-  <si>
-    <t>1400066</t>
-  </si>
-  <si>
-    <t>地狱虫角</t>
-  </si>
-  <si>
-    <t>1400067</t>
-  </si>
-  <si>
-    <t>地狱蜈膏</t>
-  </si>
-  <si>
-    <t>1400068</t>
-  </si>
-  <si>
-    <t>地狱虫心</t>
-  </si>
-  <si>
-    <t>1400069</t>
-  </si>
-  <si>
-    <t>地狱龙皮</t>
-  </si>
-  <si>
-    <t>1400070</t>
-  </si>
-  <si>
-    <t>地狱猪皮</t>
-  </si>
-  <si>
-    <t>1400071</t>
-  </si>
-  <si>
-    <t>地狱猪心</t>
-  </si>
-  <si>
-    <t>1400072</t>
-  </si>
-  <si>
-    <t>地狱蝎皮</t>
-  </si>
-  <si>
-    <t>1400073</t>
-  </si>
-  <si>
-    <t>地狱宝甲</t>
-  </si>
-  <si>
-    <t>1400074</t>
-  </si>
-  <si>
-    <t>地狱号角</t>
-  </si>
-  <si>
-    <t>1400075</t>
-  </si>
-  <si>
-    <t>地狱雕像</t>
-  </si>
-  <si>
-    <t>1400076</t>
-  </si>
-  <si>
-    <t>地狱神像</t>
-  </si>
-  <si>
-    <t>1400077</t>
-  </si>
-  <si>
-    <t>地狱獠牙</t>
-  </si>
-  <si>
-    <t>1400078</t>
-  </si>
-  <si>
-    <t>地狱树心</t>
-  </si>
-  <si>
-    <t>1400079</t>
-  </si>
-  <si>
-    <t>地狱魔心</t>
-  </si>
-  <si>
-    <t>1400080</t>
-  </si>
-  <si>
-    <t>地狱尸心</t>
-  </si>
-  <si>
-    <t>1400081</t>
-  </si>
-  <si>
-    <t>地狱法杖</t>
-  </si>
-  <si>
-    <t>1400082</t>
-  </si>
-  <si>
-    <t>地狱权杖</t>
-  </si>
-  <si>
-    <t>1400083</t>
-  </si>
-  <si>
-    <t>地狱战锤</t>
-  </si>
-  <si>
-    <t>1400084</t>
-  </si>
-  <si>
-    <t>地狱血核</t>
-  </si>
-  <si>
-    <t>1400085</t>
-  </si>
-  <si>
-    <t>地狱魔核</t>
-  </si>
-  <si>
-    <t>1400086</t>
-  </si>
-  <si>
-    <t>地狱龙甲</t>
-  </si>
-  <si>
-    <t>1400087</t>
-  </si>
-  <si>
-    <t>地狱龙爪</t>
-  </si>
-  <si>
-    <t>1400088</t>
-  </si>
-  <si>
-    <t>深渊鸡爪</t>
-  </si>
-  <si>
-    <t>1400089</t>
-  </si>
-  <si>
-    <t>深渊鹿茸</t>
-  </si>
-  <si>
-    <t>1400090</t>
-  </si>
-  <si>
-    <t>深渊草帽</t>
-  </si>
-  <si>
-    <t>1400091</t>
-  </si>
-  <si>
-    <t>深渊猫爪</t>
-  </si>
-  <si>
-    <t>1400092</t>
-  </si>
-  <si>
-    <t>深渊花朵</t>
-  </si>
-  <si>
-    <t>1400093</t>
-  </si>
-  <si>
-    <t>深渊冰晶</t>
-  </si>
-  <si>
-    <t>1400094</t>
-  </si>
-  <si>
-    <t>深渊蝠翼</t>
-  </si>
-  <si>
-    <t>1400095</t>
-  </si>
-  <si>
-    <t>深渊魂火</t>
-  </si>
-  <si>
-    <t>1400096</t>
-  </si>
-  <si>
-    <t>深渊腐肉</t>
-  </si>
-  <si>
-    <t>1400097</t>
-  </si>
-  <si>
-    <t>深渊蛇胆</t>
-  </si>
-  <si>
-    <t>1400098</t>
-  </si>
-  <si>
-    <t>深渊狼爪</t>
-  </si>
-  <si>
-    <t>1400099</t>
-  </si>
-  <si>
-    <t>深渊虫皮</t>
-  </si>
-  <si>
-    <t>1400100</t>
-  </si>
-  <si>
-    <t>深渊鹰羽</t>
-  </si>
-  <si>
-    <t>1400101</t>
-  </si>
-  <si>
-    <t>深渊虫角</t>
-  </si>
-  <si>
-    <t>1400102</t>
-  </si>
-  <si>
-    <t>深渊蜈膏</t>
-  </si>
-  <si>
-    <t>1400103</t>
-  </si>
-  <si>
-    <t>深渊虫心</t>
-  </si>
-  <si>
-    <t>1400104</t>
-  </si>
-  <si>
-    <t>深渊龙皮</t>
-  </si>
-  <si>
-    <t>1400105</t>
-  </si>
-  <si>
-    <t>深渊猪皮</t>
-  </si>
-  <si>
-    <t>1400106</t>
-  </si>
-  <si>
-    <t>深渊猪心</t>
-  </si>
-  <si>
-    <t>1400107</t>
-  </si>
-  <si>
-    <t>深渊蝎皮</t>
-  </si>
-  <si>
-    <t>1400108</t>
-  </si>
-  <si>
-    <t>深渊宝甲</t>
-  </si>
-  <si>
-    <t>1400109</t>
-  </si>
-  <si>
-    <t>深渊号角</t>
-  </si>
-  <si>
-    <t>1400110</t>
-  </si>
-  <si>
-    <t>深渊雕像</t>
-  </si>
-  <si>
-    <t>1400111</t>
-  </si>
-  <si>
-    <t>深渊神像</t>
-  </si>
-  <si>
-    <t>1400112</t>
-  </si>
-  <si>
-    <t>深渊獠牙</t>
-  </si>
-  <si>
-    <t>1400113</t>
-  </si>
-  <si>
-    <t>深渊树心</t>
-  </si>
-  <si>
-    <t>1400114</t>
-  </si>
-  <si>
-    <t>深渊魔心</t>
-  </si>
-  <si>
-    <t>1400115</t>
-  </si>
-  <si>
-    <t>深渊尸心</t>
-  </si>
-  <si>
-    <t>1400116</t>
-  </si>
-  <si>
-    <t>深渊法杖</t>
-  </si>
-  <si>
-    <t>1400117</t>
-  </si>
-  <si>
-    <t>深渊权杖</t>
-  </si>
-  <si>
-    <t>1400118</t>
-  </si>
-  <si>
-    <t>深渊战锤</t>
-  </si>
-  <si>
-    <t>1400119</t>
-  </si>
-  <si>
-    <t>深渊血核</t>
-  </si>
-  <si>
-    <t>1400120</t>
-  </si>
-  <si>
-    <t>深渊魔核</t>
-  </si>
-  <si>
-    <t>1400121</t>
-  </si>
-  <si>
-    <t>深渊龙甲</t>
-  </si>
-  <si>
-    <t>1400122</t>
-  </si>
-  <si>
-    <t>深渊龙爪</t>
-  </si>
-  <si>
-    <t>1400123</t>
-  </si>
-  <si>
-    <t>武器衣服红装</t>
-  </si>
-  <si>
-    <t>210000</t>
-  </si>
-  <si>
-    <t>项链头盔红装</t>
-  </si>
-  <si>
-    <t>210001</t>
-  </si>
-  <si>
-    <t>手镯戒指红装</t>
-  </si>
-  <si>
-    <t>210002</t>
-  </si>
-  <si>
-    <t>腰带鞋子红装</t>
-  </si>
-  <si>
-    <t>210003</t>
-  </si>
-  <si>
-    <t>随机红装</t>
-  </si>
-  <si>
-    <t>210004</t>
-  </si>
-  <si>
-    <t>武器衣服金装</t>
-  </si>
-  <si>
-    <t>209995</t>
-  </si>
-  <si>
-    <t>项链头盔金装</t>
-  </si>
-  <si>
-    <t>209996</t>
-  </si>
-  <si>
-    <t>手镯戒指金装</t>
-  </si>
-  <si>
-    <t>209997</t>
-  </si>
-  <si>
-    <t>腰带鞋子金装</t>
-  </si>
-  <si>
-    <t>209998</t>
-  </si>
-  <si>
-    <t>随机金装</t>
-  </si>
-  <si>
-    <t>209999</t>
-  </si>
-  <si>
-    <t>武器衣服暗金</t>
-  </si>
-  <si>
-    <t>209990</t>
-  </si>
-  <si>
-    <t>项链头盔暗金</t>
-  </si>
-  <si>
-    <t>209991</t>
-  </si>
-  <si>
-    <t>手镯戒指暗金</t>
-  </si>
-  <si>
-    <t>209992</t>
-  </si>
-  <si>
-    <t>腰带鞋子暗金</t>
-  </si>
-  <si>
-    <t>209993</t>
-  </si>
-  <si>
-    <t>随机暗金</t>
-  </si>
-  <si>
-    <t>209994</t>
   </si>
 </sst>
 </file>
@@ -2493,7 +2481,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P48"/>
+  <dimension ref="C1:P47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -2664,18 +2652,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>26</v>
-      </c>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
@@ -2687,39 +2669,39 @@
         <v>9999</v>
       </c>
       <c r="H6" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="11">
+        <v>0</v>
+      </c>
+      <c r="J6" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="11">
-        <v>0</v>
-      </c>
-      <c r="J6" s="18" t="s">
+      <c r="K6" s="11">
+        <v>0</v>
+      </c>
+      <c r="L6" s="11">
+        <v>0</v>
+      </c>
+      <c r="M6" s="11">
+        <v>0</v>
+      </c>
+      <c r="N6" s="11">
+        <v>0</v>
+      </c>
+      <c r="O6" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="11">
-        <v>0</v>
-      </c>
-      <c r="L6" s="11">
-        <v>0</v>
-      </c>
-      <c r="M6" s="11">
-        <v>0</v>
-      </c>
-      <c r="N6" s="11">
-        <v>0</v>
-      </c>
-      <c r="O6" s="18" t="s">
+      <c r="P6" s="18" t="s">
         <v>30</v>
-      </c>
-      <c r="P6" s="18" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C7" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -2731,99 +2713,99 @@
         <v>9999</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I7" s="11">
         <v>0</v>
       </c>
       <c r="J7" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" s="11">
+        <v>0</v>
+      </c>
+      <c r="L7" s="11">
+        <v>0</v>
+      </c>
+      <c r="M7" s="11">
+        <v>0</v>
+      </c>
+      <c r="N7" s="11">
+        <v>0</v>
+      </c>
+      <c r="O7" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="K7" s="11">
-        <v>0</v>
-      </c>
-      <c r="L7" s="11">
-        <v>0</v>
-      </c>
-      <c r="M7" s="11">
-        <v>0</v>
-      </c>
-      <c r="N7" s="11">
-        <v>0</v>
-      </c>
-      <c r="O7" s="18" t="s">
-        <v>34</v>
-      </c>
       <c r="P7" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C9" s="2">
+        <v>101</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C8" s="2">
-        <v>2</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="E9" s="2">
+        <v>98</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G9" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H9" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="2">
+      <c r="I9" s="11">
+        <v>0</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="11">
+        <v>0</v>
+      </c>
+      <c r="L9" s="11">
+        <v>0</v>
+      </c>
+      <c r="M9" s="11">
         <v>1</v>
       </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>9999</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="11">
-        <v>0</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="K8" s="11">
-        <v>0</v>
-      </c>
-      <c r="L8" s="11">
-        <v>0</v>
-      </c>
-      <c r="M8" s="11">
-        <v>0</v>
-      </c>
-      <c r="N8" s="11">
-        <v>0</v>
-      </c>
-      <c r="O8" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P8" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
+      <c r="N9" s="11">
+        <v>0</v>
+      </c>
+      <c r="O9" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P9" s="18" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C10" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -2835,13 +2817,13 @@
         <v>2000</v>
       </c>
       <c r="H10" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="11">
+        <v>0</v>
+      </c>
+      <c r="J10" s="18" t="s">
         <v>41</v>
-      </c>
-      <c r="I10" s="11">
-        <v>0</v>
-      </c>
-      <c r="J10" s="18" t="s">
-        <v>42</v>
       </c>
       <c r="K10" s="11">
         <v>0</v>
@@ -2856,18 +2838,18 @@
         <v>0</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P10" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C11" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -2879,13 +2861,13 @@
         <v>2000</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I11" s="11">
         <v>0</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K11" s="11">
         <v>0</v>
@@ -2900,18 +2882,18 @@
         <v>0</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P11" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C12" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
@@ -2923,13 +2905,13 @@
         <v>2000</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I12" s="11">
         <v>0</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K12" s="11">
         <v>0</v>
@@ -2944,36 +2926,36 @@
         <v>0</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P12" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C13" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
       </c>
       <c r="F13" s="2">
-        <v>1000</v>
+        <v>1035</v>
       </c>
       <c r="G13" s="2">
         <v>2000</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I13" s="11">
         <v>0</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K13" s="11">
         <v>0</v>
@@ -2988,18 +2970,18 @@
         <v>0</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P13" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C14" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -3011,13 +2993,13 @@
         <v>2000</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I14" s="11">
         <v>0</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K14" s="11">
         <v>0</v>
@@ -3032,18 +3014,18 @@
         <v>0</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P14" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C15" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -3055,13 +3037,13 @@
         <v>2000</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I15" s="11">
         <v>0</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K15" s="11">
         <v>0</v>
@@ -3076,18 +3058,18 @@
         <v>0</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P15" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C16" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -3099,13 +3081,13 @@
         <v>2000</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I16" s="11">
         <v>0</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K16" s="11">
         <v>0</v>
@@ -3120,36 +3102,36 @@
         <v>0</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C17" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
       </c>
       <c r="F17" s="2">
-        <v>1035</v>
+        <v>1070</v>
       </c>
       <c r="G17" s="2">
         <v>2000</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I17" s="11">
         <v>0</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K17" s="11">
         <v>0</v>
@@ -3164,18 +3146,18 @@
         <v>0</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P17" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C18" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -3187,13 +3169,13 @@
         <v>2000</v>
       </c>
       <c r="H18" s="19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I18" s="11">
         <v>0</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K18" s="11">
         <v>0</v>
@@ -3208,18 +3190,18 @@
         <v>0</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P18" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C19" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -3231,13 +3213,13 @@
         <v>2000</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I19" s="11">
         <v>0</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="K19" s="11">
         <v>0</v>
@@ -3252,18 +3234,18 @@
         <v>0</v>
       </c>
       <c r="O19" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P19" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C20" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E20" s="2">
         <v>98</v>
@@ -3275,13 +3257,13 @@
         <v>2000</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I20" s="11">
         <v>0</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="K20" s="11">
         <v>0</v>
@@ -3296,63 +3278,63 @@
         <v>0</v>
       </c>
       <c r="O20" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P20" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C21" s="2">
-        <v>112</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E21" s="2">
-        <v>98</v>
-      </c>
-      <c r="F21" s="2">
-        <v>1070</v>
-      </c>
-      <c r="G21" s="2">
-        <v>2000</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="I21" s="11">
-        <v>0</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="K21" s="11">
-        <v>0</v>
-      </c>
-      <c r="L21" s="11">
-        <v>0</v>
-      </c>
-      <c r="M21" s="11">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1"/>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C22" s="2">
+        <v>201</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="2">
+        <v>100</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="I22" s="11">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
         <v>1</v>
       </c>
-      <c r="N21" s="11">
-        <v>0</v>
-      </c>
-      <c r="O21" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="P21" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1"/>
+      <c r="K22" s="11">
+        <v>0</v>
+      </c>
+      <c r="L22" s="11">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="N22" s="11">
+        <v>1</v>
+      </c>
+      <c r="O22" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P22" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C23" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E23" s="2">
         <v>100</v>
@@ -3363,8 +3345,8 @@
       <c r="G23" s="2">
         <v>0</v>
       </c>
-      <c r="H23" s="18" t="s">
-        <v>77</v>
+      <c r="H23" s="19" t="s">
+        <v>74</v>
       </c>
       <c r="I23" s="11">
         <v>0</v>
@@ -3385,18 +3367,18 @@
         <v>1</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P23" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C24" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2">
         <v>100</v>
@@ -3407,8 +3389,8 @@
       <c r="G24" s="2">
         <v>0</v>
       </c>
-      <c r="H24" s="19" t="s">
-        <v>79</v>
+      <c r="H24" s="18" t="s">
+        <v>76</v>
       </c>
       <c r="I24" s="11">
         <v>0</v>
@@ -3429,91 +3411,91 @@
         <v>1</v>
       </c>
       <c r="O24" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P24" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C25" s="2">
-        <v>203</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E25" s="2">
-        <v>100</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2">
-        <v>0</v>
-      </c>
-      <c r="H25" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="I25" s="11">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="8:16">
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="K25" s="11">
+        <v>0</v>
+      </c>
+      <c r="L25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C26" s="2">
+        <v>301</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" s="2">
+        <v>98</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G26" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="K26" s="11">
+        <v>0</v>
+      </c>
+      <c r="L26" s="11">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2">
         <v>1</v>
       </c>
-      <c r="K25" s="11">
-        <v>0</v>
-      </c>
-      <c r="L25" s="11">
-        <v>0</v>
-      </c>
-      <c r="M25" s="2">
-        <v>0</v>
-      </c>
-      <c r="N25" s="11">
-        <v>1</v>
-      </c>
-      <c r="O25" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="P25" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="8:16">
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="K26" s="11">
-        <v>0</v>
-      </c>
-      <c r="L26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
+      <c r="N26" s="11">
+        <v>0</v>
+      </c>
+      <c r="O26" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P26" s="18" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C27" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
       </c>
       <c r="F27" s="2">
-        <v>1000</v>
+        <v>1070</v>
       </c>
       <c r="G27" s="2">
         <v>2000</v>
       </c>
-      <c r="H27" s="19" t="s">
-        <v>81</v>
+      <c r="H27" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="I27" s="2">
         <v>0</v>
       </c>
       <c r="J27" s="19" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K27" s="11">
         <v>0</v>
@@ -3528,62 +3510,62 @@
         <v>0</v>
       </c>
       <c r="O27" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P27" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C28" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E28" s="2">
         <v>98</v>
       </c>
       <c r="F28" s="2">
-        <v>1070</v>
+        <v>1105</v>
       </c>
       <c r="G28" s="2">
         <v>2000</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="I28" s="2">
-        <v>0</v>
-      </c>
-      <c r="J28" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="I28" s="19" t="s">
         <v>83</v>
       </c>
+      <c r="J28" s="18" t="s">
+        <v>84</v>
+      </c>
       <c r="K28" s="11">
         <v>0</v>
       </c>
-      <c r="L28" s="11">
-        <v>0</v>
+      <c r="L28" s="2">
+        <v>20000</v>
       </c>
       <c r="M28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="11">
         <v>0</v>
       </c>
       <c r="O28" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P28" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C29" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -3595,84 +3577,84 @@
         <v>2000</v>
       </c>
       <c r="H29" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="I29" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="I29" s="19" t="s">
+      <c r="J29" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="K29" s="11">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2">
+        <v>40000</v>
+      </c>
+      <c r="M29" s="2">
+        <v>0</v>
+      </c>
+      <c r="N29" s="11">
+        <v>0</v>
+      </c>
+      <c r="O29" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P29" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1"/>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C31" s="2">
+        <v>801</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="J29" s="18" t="s">
+      <c r="E31" s="2">
+        <v>98</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G31" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H31" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="K29" s="11">
-        <v>0</v>
-      </c>
-      <c r="L29" s="2">
-        <v>20000</v>
-      </c>
-      <c r="M29" s="2">
-        <v>0</v>
-      </c>
-      <c r="N29" s="11">
-        <v>0</v>
-      </c>
-      <c r="O29" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="P29" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C30" s="2">
-        <v>304</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E30" s="2">
-        <v>98</v>
-      </c>
-      <c r="F30" s="2">
-        <v>1105</v>
-      </c>
-      <c r="G30" s="2">
-        <v>2000</v>
-      </c>
-      <c r="H30" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="I30" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="J30" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="K30" s="11">
-        <v>0</v>
-      </c>
-      <c r="L30" s="2">
-        <v>40000</v>
-      </c>
-      <c r="M30" s="2">
-        <v>0</v>
-      </c>
-      <c r="N30" s="11">
-        <v>0</v>
-      </c>
-      <c r="O30" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="P30" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1"/>
+      <c r="I31" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J31" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="K31" s="11">
+        <v>0</v>
+      </c>
+      <c r="L31" s="11">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2">
+        <v>0</v>
+      </c>
+      <c r="N31" s="11">
+        <v>0</v>
+      </c>
+      <c r="O31" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P31" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C32" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E32" s="2">
         <v>98</v>
@@ -3683,14 +3665,14 @@
       <c r="G32" s="2">
         <v>2000</v>
       </c>
-      <c r="H32" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="I32" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="J32" s="19" t="s">
-        <v>64</v>
+      <c r="H32" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="I32" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="J32" s="18" t="s">
+        <v>83</v>
       </c>
       <c r="K32" s="11">
         <v>0</v>
@@ -3698,141 +3680,141 @@
       <c r="L32" s="11">
         <v>0</v>
       </c>
-      <c r="M32" s="2">
-        <v>0</v>
+      <c r="M32" s="11">
+        <v>1</v>
       </c>
       <c r="N32" s="11">
         <v>0</v>
       </c>
       <c r="O32" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P32" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C33" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
       </c>
       <c r="F33" s="2">
-        <v>1000</v>
+        <v>1105</v>
       </c>
       <c r="G33" s="2">
         <v>2000</v>
       </c>
       <c r="H33" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="I33" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="J33" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="K33" s="11">
+        <v>0</v>
+      </c>
+      <c r="L33" s="11">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2">
+        <v>0</v>
+      </c>
+      <c r="N33" s="11">
+        <v>0</v>
+      </c>
+      <c r="O33" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P33" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="9:16">
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="11"/>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C35" s="2">
+        <v>804</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E35" s="2">
+        <v>98</v>
+      </c>
+      <c r="F35" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G35" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H35" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="I35" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="J35" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="I33" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="J33" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="K33" s="11">
-        <v>0</v>
-      </c>
-      <c r="L33" s="11">
-        <v>0</v>
-      </c>
-      <c r="M33" s="11">
-        <v>1</v>
-      </c>
-      <c r="N33" s="11">
-        <v>0</v>
-      </c>
-      <c r="O33" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="P33" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C34" s="2">
-        <v>803</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E34" s="2">
-        <v>98</v>
-      </c>
-      <c r="F34" s="2">
-        <v>1105</v>
-      </c>
-      <c r="G34" s="2">
-        <v>2000</v>
-      </c>
-      <c r="H34" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="I34" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="J34" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="K34" s="11">
-        <v>0</v>
-      </c>
-      <c r="L34" s="11">
-        <v>0</v>
-      </c>
-      <c r="M34" s="2">
-        <v>0</v>
-      </c>
-      <c r="N34" s="11">
-        <v>0</v>
-      </c>
-      <c r="O34" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="P34" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="9:16">
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="11"/>
-      <c r="P35" s="11"/>
+      <c r="K35" s="11">
+        <v>0</v>
+      </c>
+      <c r="L35" s="11">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2">
+        <v>0</v>
+      </c>
+      <c r="N35" s="11">
+        <v>0</v>
+      </c>
+      <c r="O35" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P35" s="18" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C36" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
       </c>
       <c r="F36" s="2">
-        <v>1000</v>
+        <v>1105</v>
       </c>
       <c r="G36" s="2">
         <v>2000</v>
       </c>
       <c r="H36" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="I36" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="J36" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="I36" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="J36" s="18" t="s">
-        <v>101</v>
-      </c>
       <c r="K36" s="11">
         <v>0</v>
       </c>
@@ -3846,18 +3828,18 @@
         <v>0</v>
       </c>
       <c r="O36" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P36" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C37" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -3869,18 +3851,18 @@
         <v>2000</v>
       </c>
       <c r="H37" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="I37" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="I37" s="19" t="s">
+      <c r="J37" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="J37" s="18" t="s">
-        <v>105</v>
-      </c>
       <c r="K37" s="11">
         <v>0</v>
       </c>
-      <c r="L37" s="11">
+      <c r="L37" s="2">
         <v>0</v>
       </c>
       <c r="M37" s="2">
@@ -3890,18 +3872,18 @@
         <v>0</v>
       </c>
       <c r="O37" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P37" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C38" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E38" s="2">
         <v>98</v>
@@ -3913,19 +3895,19 @@
         <v>2000</v>
       </c>
       <c r="H38" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="I38" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="I38" s="19" t="s">
+      <c r="J38" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="J38" s="18" t="s">
-        <v>109</v>
-      </c>
       <c r="K38" s="11">
         <v>0</v>
       </c>
       <c r="L38" s="2">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="M38" s="2">
         <v>0</v>
@@ -3934,18 +3916,18 @@
         <v>0</v>
       </c>
       <c r="O38" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P38" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C39" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E39" s="2">
         <v>98</v>
@@ -3957,102 +3939,102 @@
         <v>2000</v>
       </c>
       <c r="H39" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="I39" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="J39" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="I39" s="19" t="s">
+      <c r="K39" s="11">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2">
+        <v>200000</v>
+      </c>
+      <c r="M39" s="2">
+        <v>0</v>
+      </c>
+      <c r="N39" s="11">
+        <v>0</v>
+      </c>
+      <c r="O39" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P39" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="16"/>
+      <c r="N40" s="16"/>
+      <c r="O40" s="16"/>
+      <c r="P40" s="16"/>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C41" s="2">
+        <v>991</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="J39" s="18" t="s">
+      <c r="E41" s="2">
+        <v>99</v>
+      </c>
+      <c r="F41" s="2">
+        <v>0</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0</v>
+      </c>
+      <c r="H41" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="K39" s="11">
-        <v>0</v>
-      </c>
-      <c r="L39" s="2">
-        <v>150000</v>
-      </c>
-      <c r="M39" s="2">
-        <v>0</v>
-      </c>
-      <c r="N39" s="11">
-        <v>0</v>
-      </c>
-      <c r="O39" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="P39" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C40" s="2">
-        <v>808</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E40" s="2">
-        <v>98</v>
-      </c>
-      <c r="F40" s="2">
-        <v>1105</v>
-      </c>
-      <c r="G40" s="2">
-        <v>2000</v>
-      </c>
-      <c r="H40" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="I40" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="J40" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="K40" s="11">
-        <v>0</v>
-      </c>
-      <c r="L40" s="2">
-        <v>200000</v>
-      </c>
-      <c r="M40" s="2">
-        <v>0</v>
-      </c>
-      <c r="N40" s="11">
-        <v>0</v>
-      </c>
-      <c r="O40" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="P40" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="16"/>
-      <c r="I41" s="16"/>
-      <c r="J41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="16"/>
-      <c r="O41" s="16"/>
-      <c r="P41" s="16"/>
+      <c r="I41" s="11">
+        <v>0</v>
+      </c>
+      <c r="J41" s="2">
+        <v>1</v>
+      </c>
+      <c r="K41" s="11">
+        <v>0</v>
+      </c>
+      <c r="L41" s="11">
+        <v>0</v>
+      </c>
+      <c r="M41" s="2">
+        <v>0</v>
+      </c>
+      <c r="N41" s="2">
+        <v>1</v>
+      </c>
+      <c r="O41" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P41" s="18" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C42" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E42" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F42" s="2">
         <v>0</v>
@@ -4061,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I42" s="11">
         <v>0</v>
@@ -4082,57 +4064,24 @@
         <v>1</v>
       </c>
       <c r="O42" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P42" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C43" s="2">
-        <v>992</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E43" s="2">
-        <v>101</v>
-      </c>
-      <c r="F43" s="2">
-        <v>0</v>
-      </c>
-      <c r="G43" s="2">
-        <v>0</v>
-      </c>
-      <c r="H43" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="I43" s="11">
-        <v>0</v>
-      </c>
-      <c r="J43" s="2">
-        <v>1</v>
-      </c>
-      <c r="K43" s="11">
-        <v>0</v>
-      </c>
-      <c r="L43" s="11">
-        <v>0</v>
-      </c>
-      <c r="M43" s="2">
-        <v>0</v>
-      </c>
-      <c r="N43" s="2">
-        <v>1</v>
-      </c>
-      <c r="O43" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="P43" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1"/>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="8:16">
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="16"/>
+      <c r="K44" s="16"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="16"/>
+      <c r="N44" s="16"/>
+      <c r="O44" s="16"/>
+      <c r="P44" s="16"/>
+    </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="8:16">
       <c r="H45" s="16"/>
       <c r="I45" s="16"/>
@@ -4166,41 +4115,30 @@
       <c r="O47" s="16"/>
       <c r="P47" s="16"/>
     </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="8:16">
-      <c r="H48" s="16"/>
-      <c r="I48" s="16"/>
-      <c r="J48" s="16"/>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="16"/>
-      <c r="O48" s="16"/>
-      <c r="P48" s="16"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="F33">
+  <conditionalFormatting sqref="F32">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F34">
+  <conditionalFormatting sqref="F33">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F35">
+  <conditionalFormatting sqref="F34">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F37">
+  <conditionalFormatting sqref="F36">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F38">
+  <conditionalFormatting sqref="F37">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F39">
+  <conditionalFormatting sqref="F38">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F40">
+  <conditionalFormatting sqref="F39">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:C5 F33:F35 F37:F40 F3:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:C5 F32:F34 F36:F39 F3:G5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -4377,7 +4315,7 @@
         <v>1000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -4389,7 +4327,7 @@
         <v>1051</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I6" s="2">
         <v>40000</v>
@@ -4407,10 +4345,10 @@
         <v>0</v>
       </c>
       <c r="N6" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O6" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4418,7 +4356,7 @@
         <v>1001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -4430,7 +4368,7 @@
         <v>1052</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="I7" s="2">
         <v>40000</v>
@@ -4448,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="N7" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4459,7 +4397,7 @@
         <v>1002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -4471,7 +4409,7 @@
         <v>1053</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="I8" s="2">
         <v>40000</v>
@@ -4489,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="N8" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4500,7 +4438,7 @@
         <v>1003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -4512,7 +4450,7 @@
         <v>1054</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="I9" s="2">
         <v>40000</v>
@@ -4530,10 +4468,10 @@
         <v>0</v>
       </c>
       <c r="N9" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4541,7 +4479,7 @@
         <v>1004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -4553,7 +4491,7 @@
         <v>1055</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I10" s="2">
         <v>40000</v>
@@ -4571,10 +4509,10 @@
         <v>0</v>
       </c>
       <c r="N10" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4582,7 +4520,7 @@
         <v>1005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -4594,7 +4532,7 @@
         <v>1056</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I11" s="2">
         <v>40000</v>
@@ -4612,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="N11" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4623,7 +4561,7 @@
         <v>1006</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
@@ -4635,7 +4573,7 @@
         <v>1057</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I12" s="2">
         <v>40000</v>
@@ -4653,10 +4591,10 @@
         <v>0</v>
       </c>
       <c r="N12" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4664,7 +4602,7 @@
         <v>1007</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
@@ -4676,7 +4614,7 @@
         <v>1058</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I13" s="2">
         <v>40000</v>
@@ -4694,10 +4632,10 @@
         <v>0</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4705,7 +4643,7 @@
         <v>1008</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -4717,7 +4655,7 @@
         <v>1059</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I14" s="2">
         <v>40000</v>
@@ -4735,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="N14" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4746,7 +4684,7 @@
         <v>1009</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -4758,7 +4696,7 @@
         <v>1060</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I15" s="2">
         <v>40000</v>
@@ -4776,10 +4714,10 @@
         <v>0</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4787,7 +4725,7 @@
         <v>1010</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -4799,7 +4737,7 @@
         <v>1061</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="I16" s="2">
         <v>40000</v>
@@ -4817,10 +4755,10 @@
         <v>0</v>
       </c>
       <c r="N16" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4828,7 +4766,7 @@
         <v>1011</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -4840,7 +4778,7 @@
         <v>1062</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I17" s="2">
         <v>40000</v>
@@ -4858,10 +4796,10 @@
         <v>0</v>
       </c>
       <c r="N17" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4869,7 +4807,7 @@
         <v>1012</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -4881,7 +4819,7 @@
         <v>1063</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I18" s="2">
         <v>40000</v>
@@ -4899,10 +4837,10 @@
         <v>0</v>
       </c>
       <c r="N18" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4910,7 +4848,7 @@
         <v>1013</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -4922,7 +4860,7 @@
         <v>1064</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -4940,10 +4878,10 @@
         <v>0</v>
       </c>
       <c r="N19" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O19" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4951,7 +4889,7 @@
         <v>1014</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E20" s="2">
         <v>98</v>
@@ -4963,7 +4901,7 @@
         <v>1065</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I20" s="2">
         <v>40000</v>
@@ -4981,10 +4919,10 @@
         <v>0</v>
       </c>
       <c r="N20" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O20" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4992,7 +4930,7 @@
         <v>1015</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -5004,7 +4942,7 @@
         <v>1066</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I21" s="2">
         <v>40000</v>
@@ -5022,10 +4960,10 @@
         <v>0</v>
       </c>
       <c r="N21" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O21" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5033,7 +4971,7 @@
         <v>1016</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -5045,7 +4983,7 @@
         <v>1067</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I22" s="2">
         <v>40000</v>
@@ -5063,10 +5001,10 @@
         <v>0</v>
       </c>
       <c r="N22" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5074,7 +5012,7 @@
         <v>1017</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -5086,7 +5024,7 @@
         <v>1068</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="I23" s="2">
         <v>40000</v>
@@ -5104,10 +5042,10 @@
         <v>0</v>
       </c>
       <c r="N23" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5115,7 +5053,7 @@
         <v>1018</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -5127,7 +5065,7 @@
         <v>1069</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="I24" s="2">
         <v>40000</v>
@@ -5145,10 +5083,10 @@
         <v>0</v>
       </c>
       <c r="N24" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O24" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5156,7 +5094,7 @@
         <v>1019</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -5168,7 +5106,7 @@
         <v>1070</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="I25" s="2">
         <v>40000</v>
@@ -5186,10 +5124,10 @@
         <v>0</v>
       </c>
       <c r="N25" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O25" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5197,7 +5135,7 @@
         <v>1020</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -5209,7 +5147,7 @@
         <v>1071</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I26" s="2">
         <v>40000</v>
@@ -5227,10 +5165,10 @@
         <v>0</v>
       </c>
       <c r="N26" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O26" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5238,7 +5176,7 @@
         <v>1021</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -5250,7 +5188,7 @@
         <v>1072</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>
@@ -5268,10 +5206,10 @@
         <v>0</v>
       </c>
       <c r="N27" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O27" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5279,7 +5217,7 @@
         <v>1022</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E28" s="2">
         <v>98</v>
@@ -5291,7 +5229,7 @@
         <v>1073</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="I28" s="2">
         <v>40000</v>
@@ -5309,10 +5247,10 @@
         <v>0</v>
       </c>
       <c r="N28" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O28" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:16">
@@ -5320,7 +5258,7 @@
         <v>1023</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -5332,7 +5270,7 @@
         <v>1074</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="I29" s="2">
         <v>40000</v>
@@ -5350,10 +5288,10 @@
         <v>0</v>
       </c>
       <c r="N29" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O29" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P29" s="2"/>
     </row>
@@ -5362,7 +5300,7 @@
         <v>1024</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E30" s="2">
         <v>98</v>
@@ -5374,7 +5312,7 @@
         <v>1075</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="I30" s="2">
         <v>4000</v>
@@ -5392,10 +5330,10 @@
         <v>0</v>
       </c>
       <c r="N30" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O30" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5403,7 +5341,7 @@
         <v>1025</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E31" s="2">
         <v>98</v>
@@ -5415,7 +5353,7 @@
         <v>1076</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="I31" s="2">
         <v>4000</v>
@@ -5433,10 +5371,10 @@
         <v>0</v>
       </c>
       <c r="N31" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O31" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5444,7 +5382,7 @@
         <v>1026</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E32" s="2">
         <v>98</v>
@@ -5456,7 +5394,7 @@
         <v>1077</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="I32" s="2">
         <v>4000</v>
@@ -5474,10 +5412,10 @@
         <v>0</v>
       </c>
       <c r="N32" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O32" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5485,7 +5423,7 @@
         <v>1027</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
@@ -5497,7 +5435,7 @@
         <v>1078</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I33" s="2">
         <v>4000</v>
@@ -5515,10 +5453,10 @@
         <v>0</v>
       </c>
       <c r="N33" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O33" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:16">
@@ -5526,7 +5464,7 @@
         <v>1028</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E34" s="2">
         <v>98</v>
@@ -5538,7 +5476,7 @@
         <v>1079</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I34" s="2">
         <v>4000</v>
@@ -5556,10 +5494,10 @@
         <v>0</v>
       </c>
       <c r="N34" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O34" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P34" s="2"/>
     </row>
@@ -5568,7 +5506,7 @@
         <v>1029</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
@@ -5580,7 +5518,7 @@
         <v>1080</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I35" s="2">
         <v>4000</v>
@@ -5598,10 +5536,10 @@
         <v>0</v>
       </c>
       <c r="N35" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O35" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P35" s="2"/>
     </row>
@@ -5610,7 +5548,7 @@
         <v>1030</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -5622,7 +5560,7 @@
         <v>1081</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I36" s="2">
         <v>4000</v>
@@ -5640,10 +5578,10 @@
         <v>0</v>
       </c>
       <c r="N36" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O36" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P36" s="2"/>
     </row>
@@ -5652,7 +5590,7 @@
         <v>1031</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -5664,7 +5602,7 @@
         <v>1082</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I37" s="2">
         <v>4000</v>
@@ -5682,10 +5620,10 @@
         <v>0</v>
       </c>
       <c r="N37" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O37" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P37" s="2"/>
     </row>
@@ -5694,7 +5632,7 @@
         <v>1032</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E38" s="2">
         <v>98</v>
@@ -5706,7 +5644,7 @@
         <v>1083</v>
       </c>
       <c r="H38" s="20" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="I38" s="2">
         <v>4000</v>
@@ -5724,10 +5662,10 @@
         <v>0</v>
       </c>
       <c r="N38" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O38" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P38" s="2"/>
     </row>
@@ -5736,7 +5674,7 @@
         <v>1033</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E39" s="2">
         <v>98</v>
@@ -5748,7 +5686,7 @@
         <v>1084</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I39" s="2">
         <v>4000</v>
@@ -5766,10 +5704,10 @@
         <v>0</v>
       </c>
       <c r="N39" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O39" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P39" s="2"/>
     </row>
@@ -5778,7 +5716,7 @@
         <v>1034</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E40" s="2">
         <v>98</v>
@@ -5790,7 +5728,7 @@
         <v>1085</v>
       </c>
       <c r="H40" s="20" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I40" s="2">
         <v>4000</v>
@@ -5808,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="N40" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O40" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P40" s="2"/>
     </row>
@@ -5820,7 +5758,7 @@
         <v>1035</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="E41" s="2">
         <v>98</v>
@@ -5832,7 +5770,7 @@
         <v>1086</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="I41" s="2">
         <v>4000</v>
@@ -5850,10 +5788,10 @@
         <v>0</v>
       </c>
       <c r="N41" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O41" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P41" s="2"/>
     </row>
@@ -5862,7 +5800,7 @@
         <v>1036</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E42" s="2">
         <v>98</v>
@@ -5874,7 +5812,7 @@
         <v>1087</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I42" s="2">
         <v>4000</v>
@@ -5892,10 +5830,10 @@
         <v>0</v>
       </c>
       <c r="N42" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O42" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P42" s="2"/>
     </row>
@@ -5904,7 +5842,7 @@
         <v>1037</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E43" s="2">
         <v>98</v>
@@ -5916,7 +5854,7 @@
         <v>1088</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="I43" s="2">
         <v>4000</v>
@@ -5934,10 +5872,10 @@
         <v>0</v>
       </c>
       <c r="N43" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O43" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P43" s="2"/>
     </row>
@@ -5946,7 +5884,7 @@
         <v>1038</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E44" s="2">
         <v>98</v>
@@ -5958,7 +5896,7 @@
         <v>1089</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I44" s="2">
         <v>4000</v>
@@ -5976,10 +5914,10 @@
         <v>0</v>
       </c>
       <c r="N44" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O44" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P44" s="2"/>
     </row>
@@ -5988,7 +5926,7 @@
         <v>1039</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E45" s="2">
         <v>98</v>
@@ -6000,7 +5938,7 @@
         <v>1090</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="I45" s="2">
         <v>4000</v>
@@ -6018,10 +5956,10 @@
         <v>0</v>
       </c>
       <c r="N45" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O45" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P45" s="2"/>
     </row>
@@ -6030,7 +5968,7 @@
         <v>1040</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E46" s="2">
         <v>98</v>
@@ -6042,7 +5980,7 @@
         <v>1091</v>
       </c>
       <c r="H46" s="20" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="I46" s="2">
         <v>4000</v>
@@ -6060,10 +5998,10 @@
         <v>0</v>
       </c>
       <c r="N46" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O46" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P46" s="2"/>
     </row>
@@ -6072,7 +6010,7 @@
         <v>1041</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E47" s="2">
         <v>98</v>
@@ -6084,7 +6022,7 @@
         <v>1092</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="I47" s="2">
         <v>4000</v>
@@ -6102,10 +6040,10 @@
         <v>0</v>
       </c>
       <c r="N47" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O47" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P47" s="2"/>
     </row>
@@ -6114,7 +6052,7 @@
         <v>1042</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E48" s="2">
         <v>98</v>
@@ -6126,7 +6064,7 @@
         <v>1093</v>
       </c>
       <c r="H48" s="20" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="I48" s="2">
         <v>4000</v>
@@ -6144,10 +6082,10 @@
         <v>0</v>
       </c>
       <c r="N48" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O48" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P48" s="2"/>
     </row>
@@ -6156,7 +6094,7 @@
         <v>1043</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E49" s="2">
         <v>98</v>
@@ -6168,7 +6106,7 @@
         <v>1094</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="I49" s="2">
         <v>4000</v>
@@ -6186,10 +6124,10 @@
         <v>0</v>
       </c>
       <c r="N49" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O49" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P49" s="2"/>
     </row>
@@ -6198,7 +6136,7 @@
         <v>1044</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E50" s="2">
         <v>98</v>
@@ -6210,7 +6148,7 @@
         <v>1095</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="I50" s="2">
         <v>4000</v>
@@ -6228,10 +6166,10 @@
         <v>0</v>
       </c>
       <c r="N50" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O50" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P50" s="2"/>
     </row>
@@ -6240,7 +6178,7 @@
         <v>1045</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E51" s="2">
         <v>98</v>
@@ -6252,7 +6190,7 @@
         <v>1096</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="I51" s="2">
         <v>4000</v>
@@ -6270,10 +6208,10 @@
         <v>0</v>
       </c>
       <c r="N51" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O51" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P51" s="2"/>
     </row>
@@ -6282,7 +6220,7 @@
         <v>1046</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E52" s="2">
         <v>98</v>
@@ -6294,7 +6232,7 @@
         <v>1097</v>
       </c>
       <c r="H52" s="20" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I52" s="2">
         <v>4000</v>
@@ -6312,10 +6250,10 @@
         <v>0</v>
       </c>
       <c r="N52" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O52" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P52" s="2"/>
     </row>
@@ -6324,7 +6262,7 @@
         <v>1047</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E53" s="2">
         <v>98</v>
@@ -6336,7 +6274,7 @@
         <v>1098</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="I53" s="2">
         <v>4000</v>
@@ -6354,10 +6292,10 @@
         <v>0</v>
       </c>
       <c r="N53" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O53" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P53" s="2"/>
     </row>
@@ -6366,7 +6304,7 @@
         <v>1048</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E54" s="2">
         <v>98</v>
@@ -6378,7 +6316,7 @@
         <v>1099</v>
       </c>
       <c r="H54" s="20" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="I54" s="2">
         <v>4000</v>
@@ -6396,10 +6334,10 @@
         <v>0</v>
       </c>
       <c r="N54" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O54" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P54" s="2"/>
     </row>
@@ -6408,7 +6346,7 @@
         <v>1049</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E55" s="2">
         <v>98</v>
@@ -6420,7 +6358,7 @@
         <v>1100</v>
       </c>
       <c r="H55" s="20" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="I55" s="2">
         <v>4000</v>
@@ -6438,10 +6376,10 @@
         <v>0</v>
       </c>
       <c r="N55" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O55" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P55" s="2"/>
     </row>
@@ -6450,7 +6388,7 @@
         <v>1050</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E56" s="2">
         <v>98</v>
@@ -6462,7 +6400,7 @@
         <v>1101</v>
       </c>
       <c r="H56" s="20" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="I56" s="2">
         <v>4000</v>
@@ -6480,10 +6418,10 @@
         <v>0</v>
       </c>
       <c r="N56" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O56" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P56" s="2"/>
     </row>
@@ -6492,7 +6430,7 @@
         <v>1051</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E57" s="2">
         <v>98</v>
@@ -6504,7 +6442,7 @@
         <v>1102</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="I57" s="2">
         <v>4000</v>
@@ -6522,10 +6460,10 @@
         <v>0</v>
       </c>
       <c r="N57" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O57" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P57" s="2"/>
     </row>
@@ -6534,7 +6472,7 @@
         <v>1052</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E58" s="2">
         <v>98</v>
@@ -6546,7 +6484,7 @@
         <v>1103</v>
       </c>
       <c r="H58" s="20" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I58" s="2">
         <v>4000</v>
@@ -6564,10 +6502,10 @@
         <v>0</v>
       </c>
       <c r="N58" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O58" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P58" s="2"/>
     </row>
@@ -6576,7 +6514,7 @@
         <v>1053</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E59" s="2">
         <v>98</v>
@@ -6588,7 +6526,7 @@
         <v>1104</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I59" s="2">
         <v>4000</v>
@@ -6606,10 +6544,10 @@
         <v>0</v>
       </c>
       <c r="N59" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O59" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P59" s="2"/>
     </row>
@@ -6618,7 +6556,7 @@
         <v>1054</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E60" s="12">
         <v>98</v>
@@ -6630,7 +6568,7 @@
         <v>1105</v>
       </c>
       <c r="H60" s="21" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I60" s="12">
         <v>20000</v>
@@ -6648,10 +6586,10 @@
         <v>0</v>
       </c>
       <c r="N60" s="22" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O60" s="22" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6659,7 +6597,7 @@
         <v>1055</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E61" s="2">
         <v>98</v>
@@ -6671,7 +6609,7 @@
         <v>1106</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="I61" s="2">
         <v>20000</v>
@@ -6689,10 +6627,10 @@
         <v>0</v>
       </c>
       <c r="N61" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O61" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6700,7 +6638,7 @@
         <v>1056</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E62" s="2">
         <v>98</v>
@@ -6712,7 +6650,7 @@
         <v>1107</v>
       </c>
       <c r="H62" s="20" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="I62" s="2">
         <v>20000</v>
@@ -6730,10 +6668,10 @@
         <v>0</v>
       </c>
       <c r="N62" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O62" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6741,7 +6679,7 @@
         <v>1057</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E63" s="2">
         <v>98</v>
@@ -6753,7 +6691,7 @@
         <v>1108</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I63" s="2">
         <v>20000</v>
@@ -6771,10 +6709,10 @@
         <v>0</v>
       </c>
       <c r="N63" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O63" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:16">
@@ -6782,7 +6720,7 @@
         <v>1058</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E64" s="2">
         <v>98</v>
@@ -6794,7 +6732,7 @@
         <v>1109</v>
       </c>
       <c r="H64" s="20" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="I64" s="2">
         <v>20000</v>
@@ -6812,10 +6750,10 @@
         <v>0</v>
       </c>
       <c r="N64" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O64" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P64" s="2"/>
     </row>
@@ -6824,7 +6762,7 @@
         <v>1059</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E65" s="2">
         <v>98</v>
@@ -6836,7 +6774,7 @@
         <v>1110</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I65" s="2">
         <v>20000</v>
@@ -6854,10 +6792,10 @@
         <v>0</v>
       </c>
       <c r="N65" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O65" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6865,7 +6803,7 @@
         <v>1060</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E66" s="2">
         <v>98</v>
@@ -6877,7 +6815,7 @@
         <v>1111</v>
       </c>
       <c r="H66" s="20" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="I66" s="2">
         <v>20000</v>
@@ -6895,10 +6833,10 @@
         <v>0</v>
       </c>
       <c r="N66" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O66" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6906,7 +6844,7 @@
         <v>1061</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="E67" s="2">
         <v>98</v>
@@ -6918,7 +6856,7 @@
         <v>1112</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I67" s="2">
         <v>20000</v>
@@ -6936,10 +6874,10 @@
         <v>0</v>
       </c>
       <c r="N67" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O67" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6947,7 +6885,7 @@
         <v>1062</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E68" s="2">
         <v>98</v>
@@ -6959,7 +6897,7 @@
         <v>1113</v>
       </c>
       <c r="H68" s="20" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I68" s="2">
         <v>20000</v>
@@ -6977,10 +6915,10 @@
         <v>0</v>
       </c>
       <c r="N68" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O68" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:16">
@@ -6988,7 +6926,7 @@
         <v>1063</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E69" s="2">
         <v>98</v>
@@ -7000,7 +6938,7 @@
         <v>1114</v>
       </c>
       <c r="H69" s="20" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="I69" s="2">
         <v>20000</v>
@@ -7018,10 +6956,10 @@
         <v>0</v>
       </c>
       <c r="N69" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O69" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P69" s="2"/>
     </row>
@@ -7030,7 +6968,7 @@
         <v>1064</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E70" s="2">
         <v>98</v>
@@ -7042,7 +6980,7 @@
         <v>1115</v>
       </c>
       <c r="H70" s="20" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="I70" s="2">
         <v>20000</v>
@@ -7060,10 +6998,10 @@
         <v>0</v>
       </c>
       <c r="N70" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O70" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P70" s="2"/>
     </row>
@@ -7072,7 +7010,7 @@
         <v>1065</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E71" s="2">
         <v>98</v>
@@ -7084,7 +7022,7 @@
         <v>1116</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I71" s="2">
         <v>20000</v>
@@ -7102,10 +7040,10 @@
         <v>0</v>
       </c>
       <c r="N71" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O71" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P71" s="2"/>
     </row>
@@ -7114,7 +7052,7 @@
         <v>1066</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E72" s="2">
         <v>98</v>
@@ -7126,7 +7064,7 @@
         <v>1117</v>
       </c>
       <c r="H72" s="20" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="I72" s="2">
         <v>20000</v>
@@ -7144,10 +7082,10 @@
         <v>0</v>
       </c>
       <c r="N72" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O72" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P72" s="2"/>
     </row>
@@ -7156,7 +7094,7 @@
         <v>1067</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E73" s="2">
         <v>98</v>
@@ -7168,7 +7106,7 @@
         <v>1118</v>
       </c>
       <c r="H73" s="20" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I73" s="2">
         <v>20000</v>
@@ -7186,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="N73" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O73" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P73" s="2"/>
     </row>
@@ -7198,7 +7136,7 @@
         <v>1068</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="E74" s="2">
         <v>98</v>
@@ -7210,7 +7148,7 @@
         <v>1119</v>
       </c>
       <c r="H74" s="20" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="I74" s="2">
         <v>20000</v>
@@ -7228,10 +7166,10 @@
         <v>0</v>
       </c>
       <c r="N74" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O74" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P74" s="2"/>
     </row>
@@ -7240,7 +7178,7 @@
         <v>1069</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E75" s="2">
         <v>98</v>
@@ -7252,7 +7190,7 @@
         <v>1120</v>
       </c>
       <c r="H75" s="20" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="I75" s="2">
         <v>20000</v>
@@ -7270,10 +7208,10 @@
         <v>0</v>
       </c>
       <c r="N75" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O75" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P75" s="2"/>
     </row>
@@ -7282,7 +7220,7 @@
         <v>1070</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E76" s="2">
         <v>98</v>
@@ -7294,7 +7232,7 @@
         <v>1121</v>
       </c>
       <c r="H76" s="20" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="I76" s="2">
         <v>20000</v>
@@ -7312,10 +7250,10 @@
         <v>0</v>
       </c>
       <c r="N76" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O76" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P76" s="2"/>
     </row>
@@ -7324,7 +7262,7 @@
         <v>1071</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E77" s="2">
         <v>98</v>
@@ -7336,7 +7274,7 @@
         <v>1122</v>
       </c>
       <c r="H77" s="20" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="I77" s="2">
         <v>20000</v>
@@ -7354,10 +7292,10 @@
         <v>0</v>
       </c>
       <c r="N77" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O77" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P77" s="2"/>
     </row>
@@ -7366,7 +7304,7 @@
         <v>1072</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E78" s="2">
         <v>98</v>
@@ -7378,7 +7316,7 @@
         <v>1123</v>
       </c>
       <c r="H78" s="20" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="I78" s="2">
         <v>20000</v>
@@ -7396,10 +7334,10 @@
         <v>0</v>
       </c>
       <c r="N78" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O78" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P78" s="2"/>
     </row>
@@ -7408,7 +7346,7 @@
         <v>1073</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="E79" s="2">
         <v>98</v>
@@ -7420,7 +7358,7 @@
         <v>1124</v>
       </c>
       <c r="H79" s="20" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="I79" s="2">
         <v>20000</v>
@@ -7438,10 +7376,10 @@
         <v>0</v>
       </c>
       <c r="N79" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O79" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P79" s="2"/>
     </row>
@@ -7450,7 +7388,7 @@
         <v>1074</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E80" s="2">
         <v>98</v>
@@ -7462,7 +7400,7 @@
         <v>1125</v>
       </c>
       <c r="H80" s="20" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="I80" s="2">
         <v>20000</v>
@@ -7480,10 +7418,10 @@
         <v>0</v>
       </c>
       <c r="N80" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O80" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P80" s="2"/>
     </row>
@@ -7492,7 +7430,7 @@
         <v>1075</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E81" s="2">
         <v>98</v>
@@ -7504,7 +7442,7 @@
         <v>1126</v>
       </c>
       <c r="H81" s="20" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="I81" s="2">
         <v>20000</v>
@@ -7522,10 +7460,10 @@
         <v>0</v>
       </c>
       <c r="N81" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O81" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P81" s="2"/>
     </row>
@@ -7534,7 +7472,7 @@
         <v>1076</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="E82" s="2">
         <v>98</v>
@@ -7546,7 +7484,7 @@
         <v>1127</v>
       </c>
       <c r="H82" s="20" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="I82" s="2">
         <v>20000</v>
@@ -7564,10 +7502,10 @@
         <v>0</v>
       </c>
       <c r="N82" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O82" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P82" s="2"/>
     </row>
@@ -7576,7 +7514,7 @@
         <v>1077</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E83" s="2">
         <v>98</v>
@@ -7588,7 +7526,7 @@
         <v>1128</v>
       </c>
       <c r="H83" s="20" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="I83" s="2">
         <v>20000</v>
@@ -7606,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="N83" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O83" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P83" s="2"/>
     </row>
@@ -7618,7 +7556,7 @@
         <v>1078</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="E84" s="2">
         <v>98</v>
@@ -7630,7 +7568,7 @@
         <v>1129</v>
       </c>
       <c r="H84" s="20" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="I84" s="2">
         <v>20000</v>
@@ -7648,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="N84" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O84" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P84" s="2"/>
     </row>
@@ -7660,7 +7598,7 @@
         <v>1079</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="E85" s="2">
         <v>98</v>
@@ -7672,7 +7610,7 @@
         <v>1130</v>
       </c>
       <c r="H85" s="20" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="I85" s="2">
         <v>20000</v>
@@ -7690,10 +7628,10 @@
         <v>0</v>
       </c>
       <c r="N85" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O85" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P85" s="2"/>
     </row>
@@ -7702,7 +7640,7 @@
         <v>1080</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E86" s="2">
         <v>98</v>
@@ -7714,7 +7652,7 @@
         <v>1131</v>
       </c>
       <c r="H86" s="20" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I86" s="2">
         <v>20000</v>
@@ -7732,10 +7670,10 @@
         <v>0</v>
       </c>
       <c r="N86" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O86" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P86" s="2"/>
     </row>
@@ -7744,7 +7682,7 @@
         <v>1081</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E87" s="2">
         <v>98</v>
@@ -7756,7 +7694,7 @@
         <v>1132</v>
       </c>
       <c r="H87" s="20" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I87" s="2">
         <v>20000</v>
@@ -7774,10 +7712,10 @@
         <v>0</v>
       </c>
       <c r="N87" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O87" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P87" s="2"/>
     </row>
@@ -7786,7 +7724,7 @@
         <v>1082</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E88" s="2">
         <v>98</v>
@@ -7798,7 +7736,7 @@
         <v>1133</v>
       </c>
       <c r="H88" s="20" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="I88" s="2">
         <v>20000</v>
@@ -7816,10 +7754,10 @@
         <v>0</v>
       </c>
       <c r="N88" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O88" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P88" s="2"/>
     </row>
@@ -7828,7 +7766,7 @@
         <v>1083</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="E89" s="2">
         <v>98</v>
@@ -7840,7 +7778,7 @@
         <v>1134</v>
       </c>
       <c r="H89" s="20" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="I89" s="2">
         <v>20000</v>
@@ -7858,10 +7796,10 @@
         <v>0</v>
       </c>
       <c r="N89" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O89" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P89" s="2"/>
     </row>
@@ -7870,7 +7808,7 @@
         <v>1084</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E90" s="2">
         <v>98</v>
@@ -7882,7 +7820,7 @@
         <v>1135</v>
       </c>
       <c r="H90" s="20" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="I90" s="2">
         <v>20000</v>
@@ -7900,10 +7838,10 @@
         <v>0</v>
       </c>
       <c r="N90" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O90" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P90" s="2"/>
     </row>
@@ -7912,7 +7850,7 @@
         <v>1085</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="E91" s="2">
         <v>98</v>
@@ -7924,7 +7862,7 @@
         <v>1136</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I91" s="2">
         <v>20000</v>
@@ -7942,10 +7880,10 @@
         <v>0</v>
       </c>
       <c r="N91" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O91" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P91" s="2"/>
     </row>
@@ -7954,7 +7892,7 @@
         <v>1086</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="E92" s="2">
         <v>98</v>
@@ -7966,7 +7904,7 @@
         <v>1137</v>
       </c>
       <c r="H92" s="20" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="I92" s="2">
         <v>20000</v>
@@ -7984,10 +7922,10 @@
         <v>0</v>
       </c>
       <c r="N92" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O92" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P92" s="2"/>
     </row>
@@ -7996,7 +7934,7 @@
         <v>1087</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E93" s="2">
         <v>98</v>
@@ -8008,7 +7946,7 @@
         <v>1138</v>
       </c>
       <c r="H93" s="20" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="I93" s="2">
         <v>20000</v>
@@ -8026,10 +7964,10 @@
         <v>0</v>
       </c>
       <c r="N93" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O93" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P93" s="2"/>
     </row>
@@ -8038,7 +7976,7 @@
         <v>1088</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="E94" s="2">
         <v>98</v>
@@ -8050,7 +7988,7 @@
         <v>1139</v>
       </c>
       <c r="H94" s="20" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="I94" s="2">
         <v>20000</v>
@@ -8068,10 +8006,10 @@
         <v>0</v>
       </c>
       <c r="N94" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O94" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P94" s="2"/>
     </row>
@@ -8080,7 +8018,7 @@
         <v>1089</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="E95" s="12">
         <v>98</v>
@@ -8092,7 +8030,7 @@
         <v>1140</v>
       </c>
       <c r="H95" s="21" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="I95" s="12">
         <v>30000</v>
@@ -8110,10 +8048,10 @@
         <v>0</v>
       </c>
       <c r="N95" s="22" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O95" s="22" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="96" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8121,7 +8059,7 @@
         <v>1090</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="E96" s="2">
         <v>98</v>
@@ -8133,7 +8071,7 @@
         <v>1141</v>
       </c>
       <c r="H96" s="20" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="I96" s="2">
         <v>30000</v>
@@ -8151,10 +8089,10 @@
         <v>0</v>
       </c>
       <c r="N96" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O96" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="97" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8162,7 +8100,7 @@
         <v>1091</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="E97" s="2">
         <v>98</v>
@@ -8174,7 +8112,7 @@
         <v>1142</v>
       </c>
       <c r="H97" s="20" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="I97" s="2">
         <v>30000</v>
@@ -8192,10 +8130,10 @@
         <v>0</v>
       </c>
       <c r="N97" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O97" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="98" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8203,7 +8141,7 @@
         <v>1092</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="E98" s="2">
         <v>98</v>
@@ -8215,7 +8153,7 @@
         <v>1143</v>
       </c>
       <c r="H98" s="20" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="I98" s="2">
         <v>30000</v>
@@ -8233,10 +8171,10 @@
         <v>0</v>
       </c>
       <c r="N98" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O98" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:16">
@@ -8244,7 +8182,7 @@
         <v>1093</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E99" s="2">
         <v>98</v>
@@ -8256,7 +8194,7 @@
         <v>1144</v>
       </c>
       <c r="H99" s="20" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="I99" s="2">
         <v>30000</v>
@@ -8274,10 +8212,10 @@
         <v>0</v>
       </c>
       <c r="N99" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O99" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P99" s="2"/>
     </row>
@@ -8286,7 +8224,7 @@
         <v>1094</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="E100" s="2">
         <v>98</v>
@@ -8298,7 +8236,7 @@
         <v>1145</v>
       </c>
       <c r="H100" s="20" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="I100" s="2">
         <v>30000</v>
@@ -8316,10 +8254,10 @@
         <v>0</v>
       </c>
       <c r="N100" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O100" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="101" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8327,7 +8265,7 @@
         <v>1095</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="E101" s="2">
         <v>98</v>
@@ -8339,7 +8277,7 @@
         <v>1146</v>
       </c>
       <c r="H101" s="20" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="I101" s="2">
         <v>30000</v>
@@ -8357,10 +8295,10 @@
         <v>0</v>
       </c>
       <c r="N101" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O101" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="102" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8368,7 +8306,7 @@
         <v>1096</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E102" s="2">
         <v>98</v>
@@ -8380,7 +8318,7 @@
         <v>1147</v>
       </c>
       <c r="H102" s="20" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="I102" s="2">
         <v>30000</v>
@@ -8398,10 +8336,10 @@
         <v>0</v>
       </c>
       <c r="N102" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O102" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="103" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8409,7 +8347,7 @@
         <v>1097</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="E103" s="2">
         <v>98</v>
@@ -8421,7 +8359,7 @@
         <v>1148</v>
       </c>
       <c r="H103" s="20" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="I103" s="2">
         <v>30000</v>
@@ -8439,10 +8377,10 @@
         <v>0</v>
       </c>
       <c r="N103" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O103" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:16">
@@ -8450,7 +8388,7 @@
         <v>1098</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E104" s="2">
         <v>98</v>
@@ -8462,7 +8400,7 @@
         <v>1149</v>
       </c>
       <c r="H104" s="20" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="I104" s="2">
         <v>30000</v>
@@ -8480,10 +8418,10 @@
         <v>0</v>
       </c>
       <c r="N104" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O104" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P104" s="2"/>
     </row>
@@ -8492,7 +8430,7 @@
         <v>1099</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E105" s="2">
         <v>98</v>
@@ -8504,7 +8442,7 @@
         <v>1150</v>
       </c>
       <c r="H105" s="20" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="I105" s="2">
         <v>30000</v>
@@ -8522,10 +8460,10 @@
         <v>0</v>
       </c>
       <c r="N105" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O105" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P105" s="2"/>
     </row>
@@ -8534,7 +8472,7 @@
         <v>1100</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E106" s="2">
         <v>98</v>
@@ -8546,7 +8484,7 @@
         <v>1151</v>
       </c>
       <c r="H106" s="20" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I106" s="2">
         <v>30000</v>
@@ -8564,10 +8502,10 @@
         <v>0</v>
       </c>
       <c r="N106" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O106" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P106" s="2"/>
     </row>
@@ -8576,7 +8514,7 @@
         <v>1101</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E107" s="2">
         <v>98</v>
@@ -8588,7 +8526,7 @@
         <v>1152</v>
       </c>
       <c r="H107" s="20" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="I107" s="2">
         <v>30000</v>
@@ -8606,10 +8544,10 @@
         <v>0</v>
       </c>
       <c r="N107" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O107" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P107" s="2"/>
     </row>
@@ -8618,7 +8556,7 @@
         <v>1102</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E108" s="2">
         <v>98</v>
@@ -8630,7 +8568,7 @@
         <v>1153</v>
       </c>
       <c r="H108" s="20" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="I108" s="2">
         <v>30000</v>
@@ -8648,10 +8586,10 @@
         <v>0</v>
       </c>
       <c r="N108" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O108" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P108" s="2"/>
     </row>
@@ -8660,7 +8598,7 @@
         <v>1103</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E109" s="2">
         <v>98</v>
@@ -8672,7 +8610,7 @@
         <v>1154</v>
       </c>
       <c r="H109" s="20" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="I109" s="2">
         <v>30000</v>
@@ -8690,10 +8628,10 @@
         <v>0</v>
       </c>
       <c r="N109" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O109" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P109" s="2"/>
     </row>
@@ -8702,7 +8640,7 @@
         <v>1104</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E110" s="2">
         <v>98</v>
@@ -8714,7 +8652,7 @@
         <v>1155</v>
       </c>
       <c r="H110" s="20" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="I110" s="2">
         <v>30000</v>
@@ -8732,10 +8670,10 @@
         <v>0</v>
       </c>
       <c r="N110" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O110" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P110" s="2"/>
     </row>
@@ -8744,7 +8682,7 @@
         <v>1105</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E111" s="2">
         <v>98</v>
@@ -8756,7 +8694,7 @@
         <v>1156</v>
       </c>
       <c r="H111" s="20" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="I111" s="2">
         <v>30000</v>
@@ -8774,10 +8712,10 @@
         <v>0</v>
       </c>
       <c r="N111" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O111" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P111" s="2"/>
     </row>
@@ -8786,7 +8724,7 @@
         <v>1106</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E112" s="2">
         <v>98</v>
@@ -8798,7 +8736,7 @@
         <v>1157</v>
       </c>
       <c r="H112" s="20" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="I112" s="2">
         <v>30000</v>
@@ -8816,10 +8754,10 @@
         <v>0</v>
       </c>
       <c r="N112" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O112" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P112" s="2"/>
     </row>
@@ -8828,7 +8766,7 @@
         <v>1107</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="E113" s="2">
         <v>98</v>
@@ -8840,7 +8778,7 @@
         <v>1158</v>
       </c>
       <c r="H113" s="20" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="I113" s="2">
         <v>30000</v>
@@ -8858,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="N113" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O113" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P113" s="2"/>
     </row>
@@ -8870,7 +8808,7 @@
         <v>1108</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="E114" s="2">
         <v>98</v>
@@ -8882,7 +8820,7 @@
         <v>1159</v>
       </c>
       <c r="H114" s="20" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="I114" s="2">
         <v>30000</v>
@@ -8900,10 +8838,10 @@
         <v>0</v>
       </c>
       <c r="N114" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O114" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P114" s="2"/>
     </row>
@@ -8912,7 +8850,7 @@
         <v>1109</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="E115" s="2">
         <v>98</v>
@@ -8924,7 +8862,7 @@
         <v>1160</v>
       </c>
       <c r="H115" s="20" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="I115" s="2">
         <v>30000</v>
@@ -8942,10 +8880,10 @@
         <v>0</v>
       </c>
       <c r="N115" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O115" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P115" s="2"/>
     </row>
@@ -8954,7 +8892,7 @@
         <v>1110</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E116" s="2">
         <v>98</v>
@@ -8966,7 +8904,7 @@
         <v>1161</v>
       </c>
       <c r="H116" s="20" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="I116" s="2">
         <v>30000</v>
@@ -8984,10 +8922,10 @@
         <v>0</v>
       </c>
       <c r="N116" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O116" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P116" s="2"/>
     </row>
@@ -8996,7 +8934,7 @@
         <v>1111</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E117" s="2">
         <v>98</v>
@@ -9008,7 +8946,7 @@
         <v>1162</v>
       </c>
       <c r="H117" s="20" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="I117" s="2">
         <v>30000</v>
@@ -9026,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="N117" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O117" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P117" s="2"/>
     </row>
@@ -9038,7 +8976,7 @@
         <v>1112</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E118" s="2">
         <v>98</v>
@@ -9050,7 +8988,7 @@
         <v>1163</v>
       </c>
       <c r="H118" s="20" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="I118" s="2">
         <v>30000</v>
@@ -9068,10 +9006,10 @@
         <v>0</v>
       </c>
       <c r="N118" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O118" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P118" s="2"/>
     </row>
@@ -9080,7 +9018,7 @@
         <v>1113</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E119" s="2">
         <v>98</v>
@@ -9092,7 +9030,7 @@
         <v>1164</v>
       </c>
       <c r="H119" s="20" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="I119" s="2">
         <v>30000</v>
@@ -9110,10 +9048,10 @@
         <v>0</v>
       </c>
       <c r="N119" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O119" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P119" s="2"/>
     </row>
@@ -9122,7 +9060,7 @@
         <v>1114</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E120" s="2">
         <v>98</v>
@@ -9134,7 +9072,7 @@
         <v>1165</v>
       </c>
       <c r="H120" s="20" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="I120" s="2">
         <v>30000</v>
@@ -9152,10 +9090,10 @@
         <v>0</v>
       </c>
       <c r="N120" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O120" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P120" s="2"/>
     </row>
@@ -9164,7 +9102,7 @@
         <v>1115</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="E121" s="2">
         <v>98</v>
@@ -9176,7 +9114,7 @@
         <v>1166</v>
       </c>
       <c r="H121" s="20" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="I121" s="2">
         <v>30000</v>
@@ -9194,10 +9132,10 @@
         <v>0</v>
       </c>
       <c r="N121" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O121" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P121" s="2"/>
     </row>
@@ -9206,7 +9144,7 @@
         <v>1116</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="E122" s="2">
         <v>98</v>
@@ -9218,7 +9156,7 @@
         <v>1167</v>
       </c>
       <c r="H122" s="20" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="I122" s="2">
         <v>30000</v>
@@ -9236,10 +9174,10 @@
         <v>0</v>
       </c>
       <c r="N122" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O122" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P122" s="2"/>
     </row>
@@ -9248,7 +9186,7 @@
         <v>1117</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E123" s="2">
         <v>98</v>
@@ -9260,7 +9198,7 @@
         <v>1168</v>
       </c>
       <c r="H123" s="20" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="I123" s="2">
         <v>30000</v>
@@ -9278,10 +9216,10 @@
         <v>0</v>
       </c>
       <c r="N123" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O123" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P123" s="2"/>
     </row>
@@ -9290,7 +9228,7 @@
         <v>1118</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E124" s="2">
         <v>98</v>
@@ -9302,7 +9240,7 @@
         <v>1169</v>
       </c>
       <c r="H124" s="20" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="I124" s="2">
         <v>30000</v>
@@ -9320,10 +9258,10 @@
         <v>0</v>
       </c>
       <c r="N124" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O124" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P124" s="2"/>
     </row>
@@ -9332,7 +9270,7 @@
         <v>1119</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="E125" s="2">
         <v>98</v>
@@ -9344,7 +9282,7 @@
         <v>1170</v>
       </c>
       <c r="H125" s="20" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="I125" s="2">
         <v>30000</v>
@@ -9362,10 +9300,10 @@
         <v>0</v>
       </c>
       <c r="N125" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O125" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P125" s="2"/>
     </row>
@@ -9374,7 +9312,7 @@
         <v>1120</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="E126" s="2">
         <v>98</v>
@@ -9386,7 +9324,7 @@
         <v>1171</v>
       </c>
       <c r="H126" s="20" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="I126" s="2">
         <v>30000</v>
@@ -9404,10 +9342,10 @@
         <v>0</v>
       </c>
       <c r="N126" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O126" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P126" s="2"/>
     </row>
@@ -9416,7 +9354,7 @@
         <v>1121</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E127" s="2">
         <v>98</v>
@@ -9428,7 +9366,7 @@
         <v>1172</v>
       </c>
       <c r="H127" s="20" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="I127" s="2">
         <v>30000</v>
@@ -9446,10 +9384,10 @@
         <v>0</v>
       </c>
       <c r="N127" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O127" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P127" s="2"/>
     </row>
@@ -9458,7 +9396,7 @@
         <v>1122</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E128" s="2">
         <v>98</v>
@@ -9470,7 +9408,7 @@
         <v>1173</v>
       </c>
       <c r="H128" s="20" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="I128" s="2">
         <v>30000</v>
@@ -9488,10 +9426,10 @@
         <v>0</v>
       </c>
       <c r="N128" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O128" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P128" s="2"/>
     </row>
@@ -9500,7 +9438,7 @@
         <v>1123</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E129" s="2">
         <v>98</v>
@@ -9512,7 +9450,7 @@
         <v>1174</v>
       </c>
       <c r="H129" s="20" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="I129" s="2">
         <v>30000</v>
@@ -9530,10 +9468,10 @@
         <v>0</v>
       </c>
       <c r="N129" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O129" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P129" s="2"/>
     </row>
@@ -9727,7 +9665,7 @@
         <v>2000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -9739,7 +9677,7 @@
         <v>1070</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I6" s="2">
         <v>120000</v>
@@ -9760,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P6" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -9771,7 +9709,7 @@
         <v>2001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -9783,7 +9721,7 @@
         <v>1071</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="I7" s="2">
         <v>120000</v>
@@ -9804,10 +9742,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P7" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -9815,7 +9753,7 @@
         <v>2002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -9827,7 +9765,7 @@
         <v>1072</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="I8" s="2">
         <v>120000</v>
@@ -9848,10 +9786,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P8" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -9859,7 +9797,7 @@
         <v>2003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -9871,7 +9809,7 @@
         <v>1073</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="I9" s="2">
         <v>120000</v>
@@ -9892,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P9" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -9903,7 +9841,7 @@
         <v>2004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -9915,7 +9853,7 @@
         <v>1074</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="I10" s="2">
         <v>120000</v>
@@ -9936,10 +9874,10 @@
         <v>0</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P10" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -9947,7 +9885,7 @@
         <v>2005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -9959,7 +9897,7 @@
         <v>1104</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="I11" s="2">
         <v>20000</v>
@@ -9980,10 +9918,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P11" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
@@ -10005,7 +9943,7 @@
         <v>2006</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -10017,7 +9955,7 @@
         <v>1105</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="I14" s="2">
         <v>360000</v>
@@ -10038,10 +9976,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P14" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10049,7 +9987,7 @@
         <v>2007</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -10061,7 +9999,7 @@
         <v>1106</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="I15" s="2">
         <v>360000</v>
@@ -10082,10 +10020,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P15" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10093,7 +10031,7 @@
         <v>2008</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -10105,7 +10043,7 @@
         <v>1107</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="I16" s="2">
         <v>360000</v>
@@ -10126,10 +10064,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10137,7 +10075,7 @@
         <v>2009</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -10149,7 +10087,7 @@
         <v>1108</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="I17" s="2">
         <v>360000</v>
@@ -10170,10 +10108,10 @@
         <v>0</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P17" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10181,7 +10119,7 @@
         <v>2010</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -10193,7 +10131,7 @@
         <v>1139</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="I18" s="2">
         <v>360000</v>
@@ -10214,10 +10152,10 @@
         <v>0</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P18" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10225,7 +10163,7 @@
         <v>2011</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -10237,7 +10175,7 @@
         <v>1139</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -10258,10 +10196,10 @@
         <v>0</v>
       </c>
       <c r="O19" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P19" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
@@ -10276,7 +10214,7 @@
         <v>2012</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -10288,7 +10226,7 @@
         <v>1140</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="I21" s="2">
         <v>360000</v>
@@ -10309,10 +10247,10 @@
         <v>0</v>
       </c>
       <c r="O21" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P21" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10320,7 +10258,7 @@
         <v>2013</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -10332,7 +10270,7 @@
         <v>1141</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="I22" s="2">
         <v>360000</v>
@@ -10353,10 +10291,10 @@
         <v>0</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P22" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10364,7 +10302,7 @@
         <v>2014</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -10376,7 +10314,7 @@
         <v>1142</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="I23" s="2">
         <v>360000</v>
@@ -10397,10 +10335,10 @@
         <v>0</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P23" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10408,7 +10346,7 @@
         <v>2015</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -10420,7 +10358,7 @@
         <v>1143</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="I24" s="2">
         <v>360000</v>
@@ -10441,10 +10379,10 @@
         <v>0</v>
       </c>
       <c r="O24" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P24" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10452,7 +10390,7 @@
         <v>2016</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -10464,7 +10402,7 @@
         <v>1174</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="I25" s="2">
         <v>360000</v>
@@ -10485,10 +10423,10 @@
         <v>0</v>
       </c>
       <c r="O25" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P25" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -10496,7 +10434,7 @@
         <v>2017</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -10508,7 +10446,7 @@
         <v>1174</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="I26" s="2">
         <v>180000</v>
@@ -10529,24 +10467,24 @@
         <v>0</v>
       </c>
       <c r="O26" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P26" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="C27" s="2">
         <v>2018</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -10558,7 +10496,7 @@
         <v>1174</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>
@@ -10579,10 +10517,10 @@
         <v>0</v>
       </c>
       <c r="O27" s="18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P27" s="18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
@@ -10756,7 +10694,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 C2:C5 F14:G19 F3:G5 F21:G27" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 C2:C5 F3:G5 F14:G19 F21:G27" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="465">
   <si>
     <t>_id</t>
   </si>
@@ -1349,6 +1349,216 @@
   </si>
   <si>
     <t>1400123</t>
+  </si>
+  <si>
+    <t>混沌鸡爪</t>
+  </si>
+  <si>
+    <t>1400124</t>
+  </si>
+  <si>
+    <t>混沌鹿茸</t>
+  </si>
+  <si>
+    <t>1400125</t>
+  </si>
+  <si>
+    <t>混沌草帽</t>
+  </si>
+  <si>
+    <t>1400126</t>
+  </si>
+  <si>
+    <t>混沌猫爪</t>
+  </si>
+  <si>
+    <t>1400127</t>
+  </si>
+  <si>
+    <t>混沌花朵</t>
+  </si>
+  <si>
+    <t>1400128</t>
+  </si>
+  <si>
+    <t>混沌冰晶</t>
+  </si>
+  <si>
+    <t>1400129</t>
+  </si>
+  <si>
+    <t>混沌蝠翼</t>
+  </si>
+  <si>
+    <t>1400130</t>
+  </si>
+  <si>
+    <t>混沌魂火</t>
+  </si>
+  <si>
+    <t>1400131</t>
+  </si>
+  <si>
+    <t>混沌腐肉</t>
+  </si>
+  <si>
+    <t>1400132</t>
+  </si>
+  <si>
+    <t>混沌蛇胆</t>
+  </si>
+  <si>
+    <t>1400133</t>
+  </si>
+  <si>
+    <t>混沌狼爪</t>
+  </si>
+  <si>
+    <t>1400134</t>
+  </si>
+  <si>
+    <t>混沌虫皮</t>
+  </si>
+  <si>
+    <t>1400135</t>
+  </si>
+  <si>
+    <t>混沌鹰羽</t>
+  </si>
+  <si>
+    <t>1400136</t>
+  </si>
+  <si>
+    <t>混沌虫角</t>
+  </si>
+  <si>
+    <t>1400137</t>
+  </si>
+  <si>
+    <t>混沌蜈膏</t>
+  </si>
+  <si>
+    <t>1400138</t>
+  </si>
+  <si>
+    <t>混沌虫心</t>
+  </si>
+  <si>
+    <t>1400139</t>
+  </si>
+  <si>
+    <t>混沌龙皮</t>
+  </si>
+  <si>
+    <t>1400140</t>
+  </si>
+  <si>
+    <t>混沌猪皮</t>
+  </si>
+  <si>
+    <t>1400141</t>
+  </si>
+  <si>
+    <t>混沌猪心</t>
+  </si>
+  <si>
+    <t>1400142</t>
+  </si>
+  <si>
+    <t>混沌蝎皮</t>
+  </si>
+  <si>
+    <t>1400143</t>
+  </si>
+  <si>
+    <t>混沌宝甲</t>
+  </si>
+  <si>
+    <t>1400144</t>
+  </si>
+  <si>
+    <t>混沌号角</t>
+  </si>
+  <si>
+    <t>1400145</t>
+  </si>
+  <si>
+    <t>混沌雕像</t>
+  </si>
+  <si>
+    <t>1400146</t>
+  </si>
+  <si>
+    <t>混沌神像</t>
+  </si>
+  <si>
+    <t>1400147</t>
+  </si>
+  <si>
+    <t>混沌獠牙</t>
+  </si>
+  <si>
+    <t>1400148</t>
+  </si>
+  <si>
+    <t>混沌树心</t>
+  </si>
+  <si>
+    <t>1400149</t>
+  </si>
+  <si>
+    <t>混沌魔心</t>
+  </si>
+  <si>
+    <t>1400150</t>
+  </si>
+  <si>
+    <t>混沌尸心</t>
+  </si>
+  <si>
+    <t>1400151</t>
+  </si>
+  <si>
+    <t>混沌法杖</t>
+  </si>
+  <si>
+    <t>1400152</t>
+  </si>
+  <si>
+    <t>混沌权杖</t>
+  </si>
+  <si>
+    <t>1400153</t>
+  </si>
+  <si>
+    <t>混沌战锤</t>
+  </si>
+  <si>
+    <t>1400154</t>
+  </si>
+  <si>
+    <t>混沌血核</t>
+  </si>
+  <si>
+    <t>1400155</t>
+  </si>
+  <si>
+    <t>混沌魔核</t>
+  </si>
+  <si>
+    <t>1400156</t>
+  </si>
+  <si>
+    <t>混沌龙甲</t>
+  </si>
+  <si>
+    <t>1400157</t>
+  </si>
+  <si>
+    <t>混沌龙爪</t>
+  </si>
+  <si>
+    <t>1400158</t>
   </si>
   <si>
     <t>武器衣服红装</t>
@@ -2117,7 +2327,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2141,9 +2351,11 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2488,37 +2700,37 @@
     <col min="3" max="3" width="8.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="13.875" style="2" customWidth="1"/>
     <col min="5" max="7" width="13.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.5083333333333" style="16" customWidth="1"/>
-    <col min="9" max="9" width="17.875" style="16" customWidth="1"/>
-    <col min="10" max="12" width="13.75" style="16" customWidth="1"/>
-    <col min="13" max="14" width="14.125" style="16" customWidth="1"/>
-    <col min="15" max="16" width="20.625" style="16" customWidth="1"/>
+    <col min="8" max="8" width="17.5083333333333" style="18" customWidth="1"/>
+    <col min="9" max="9" width="17.875" style="18" customWidth="1"/>
+    <col min="10" max="12" width="13.75" style="18" customWidth="1"/>
+    <col min="13" max="14" width="14.125" style="18" customWidth="1"/>
+    <col min="15" max="16" width="20.625" style="18" customWidth="1"/>
     <col min="17" max="17" width="9.66666666666667" style="2"/>
     <col min="18" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="8:16">
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
     </row>
     <row r="2" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C2" s="17"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
+      <c r="C2" s="19"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
     </row>
     <row r="3" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C3" s="6" t="s">
@@ -2668,13 +2880,13 @@
       <c r="G6" s="2">
         <v>9999</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="20" t="s">
         <v>27</v>
       </c>
       <c r="I6" s="11">
         <v>0</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="J6" s="20" t="s">
         <v>28</v>
       </c>
       <c r="K6" s="11">
@@ -2689,10 +2901,10 @@
       <c r="N6" s="11">
         <v>0</v>
       </c>
-      <c r="O6" s="18" t="s">
+      <c r="O6" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="P6" s="18" t="s">
+      <c r="P6" s="20" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2712,13 +2924,13 @@
       <c r="G7" s="2">
         <v>9999</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="20" t="s">
         <v>27</v>
       </c>
       <c r="I7" s="11">
         <v>0</v>
       </c>
-      <c r="J7" s="18" t="s">
+      <c r="J7" s="20" t="s">
         <v>32</v>
       </c>
       <c r="K7" s="11">
@@ -2733,10 +2945,10 @@
       <c r="N7" s="11">
         <v>0</v>
       </c>
-      <c r="O7" s="18" t="s">
+      <c r="O7" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="P7" s="18" t="s">
+      <c r="P7" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2746,15 +2958,15 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C9" s="2">
@@ -2772,13 +2984,13 @@
       <c r="G9" s="2">
         <v>2000</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="21" t="s">
         <v>36</v>
       </c>
       <c r="I9" s="11">
         <v>0</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="20" t="s">
         <v>37</v>
       </c>
       <c r="K9" s="11">
@@ -2793,10 +3005,10 @@
       <c r="N9" s="11">
         <v>0</v>
       </c>
-      <c r="O9" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P9" s="18" t="s">
+      <c r="O9" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P9" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2816,13 +3028,13 @@
       <c r="G10" s="2">
         <v>2000</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="21" t="s">
         <v>40</v>
       </c>
       <c r="I10" s="11">
         <v>0</v>
       </c>
-      <c r="J10" s="18" t="s">
+      <c r="J10" s="20" t="s">
         <v>41</v>
       </c>
       <c r="K10" s="11">
@@ -2837,10 +3049,10 @@
       <c r="N10" s="11">
         <v>0</v>
       </c>
-      <c r="O10" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P10" s="18" t="s">
+      <c r="O10" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P10" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2860,13 +3072,13 @@
       <c r="G11" s="2">
         <v>2000</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="21" t="s">
         <v>43</v>
       </c>
       <c r="I11" s="11">
         <v>0</v>
       </c>
-      <c r="J11" s="18" t="s">
+      <c r="J11" s="20" t="s">
         <v>44</v>
       </c>
       <c r="K11" s="11">
@@ -2881,10 +3093,10 @@
       <c r="N11" s="11">
         <v>0</v>
       </c>
-      <c r="O11" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P11" s="18" t="s">
+      <c r="O11" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P11" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2904,13 +3116,13 @@
       <c r="G12" s="2">
         <v>2000</v>
       </c>
-      <c r="H12" s="19" t="s">
+      <c r="H12" s="21" t="s">
         <v>46</v>
       </c>
       <c r="I12" s="11">
         <v>0</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="J12" s="20" t="s">
         <v>47</v>
       </c>
       <c r="K12" s="11">
@@ -2925,10 +3137,10 @@
       <c r="N12" s="11">
         <v>0</v>
       </c>
-      <c r="O12" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P12" s="18" t="s">
+      <c r="O12" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P12" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2948,13 +3160,13 @@
       <c r="G13" s="2">
         <v>2000</v>
       </c>
-      <c r="H13" s="19" t="s">
+      <c r="H13" s="21" t="s">
         <v>49</v>
       </c>
       <c r="I13" s="11">
         <v>0</v>
       </c>
-      <c r="J13" s="18" t="s">
+      <c r="J13" s="20" t="s">
         <v>50</v>
       </c>
       <c r="K13" s="11">
@@ -2969,10 +3181,10 @@
       <c r="N13" s="11">
         <v>0</v>
       </c>
-      <c r="O13" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P13" s="18" t="s">
+      <c r="O13" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P13" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2992,13 +3204,13 @@
       <c r="G14" s="2">
         <v>2000</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="H14" s="21" t="s">
         <v>52</v>
       </c>
       <c r="I14" s="11">
         <v>0</v>
       </c>
-      <c r="J14" s="18" t="s">
+      <c r="J14" s="20" t="s">
         <v>53</v>
       </c>
       <c r="K14" s="11">
@@ -3013,10 +3225,10 @@
       <c r="N14" s="11">
         <v>0</v>
       </c>
-      <c r="O14" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P14" s="18" t="s">
+      <c r="O14" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P14" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3036,13 +3248,13 @@
       <c r="G15" s="2">
         <v>2000</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="H15" s="21" t="s">
         <v>55</v>
       </c>
       <c r="I15" s="11">
         <v>0</v>
       </c>
-      <c r="J15" s="18" t="s">
+      <c r="J15" s="20" t="s">
         <v>56</v>
       </c>
       <c r="K15" s="11">
@@ -3057,10 +3269,10 @@
       <c r="N15" s="11">
         <v>0</v>
       </c>
-      <c r="O15" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P15" s="18" t="s">
+      <c r="O15" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P15" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3080,13 +3292,13 @@
       <c r="G16" s="2">
         <v>2000</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="H16" s="21" t="s">
         <v>58</v>
       </c>
       <c r="I16" s="11">
         <v>0</v>
       </c>
-      <c r="J16" s="18" t="s">
+      <c r="J16" s="20" t="s">
         <v>59</v>
       </c>
       <c r="K16" s="11">
@@ -3101,10 +3313,10 @@
       <c r="N16" s="11">
         <v>0</v>
       </c>
-      <c r="O16" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P16" s="18" t="s">
+      <c r="O16" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P16" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3124,13 +3336,13 @@
       <c r="G17" s="2">
         <v>2000</v>
       </c>
-      <c r="H17" s="19" t="s">
+      <c r="H17" s="21" t="s">
         <v>61</v>
       </c>
       <c r="I17" s="11">
         <v>0</v>
       </c>
-      <c r="J17" s="18" t="s">
+      <c r="J17" s="20" t="s">
         <v>62</v>
       </c>
       <c r="K17" s="11">
@@ -3145,10 +3357,10 @@
       <c r="N17" s="11">
         <v>0</v>
       </c>
-      <c r="O17" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P17" s="18" t="s">
+      <c r="O17" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P17" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3168,13 +3380,13 @@
       <c r="G18" s="2">
         <v>2000</v>
       </c>
-      <c r="H18" s="19" t="s">
+      <c r="H18" s="21" t="s">
         <v>64</v>
       </c>
       <c r="I18" s="11">
         <v>0</v>
       </c>
-      <c r="J18" s="18" t="s">
+      <c r="J18" s="20" t="s">
         <v>65</v>
       </c>
       <c r="K18" s="11">
@@ -3189,10 +3401,10 @@
       <c r="N18" s="11">
         <v>0</v>
       </c>
-      <c r="O18" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P18" s="18" t="s">
+      <c r="O18" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P18" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3212,13 +3424,13 @@
       <c r="G19" s="2">
         <v>2000</v>
       </c>
-      <c r="H19" s="19" t="s">
+      <c r="H19" s="21" t="s">
         <v>67</v>
       </c>
       <c r="I19" s="11">
         <v>0</v>
       </c>
-      <c r="J19" s="18" t="s">
+      <c r="J19" s="20" t="s">
         <v>41</v>
       </c>
       <c r="K19" s="11">
@@ -3233,10 +3445,10 @@
       <c r="N19" s="11">
         <v>0</v>
       </c>
-      <c r="O19" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P19" s="18" t="s">
+      <c r="O19" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P19" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3256,13 +3468,13 @@
       <c r="G20" s="2">
         <v>2000</v>
       </c>
-      <c r="H20" s="19" t="s">
+      <c r="H20" s="21" t="s">
         <v>69</v>
       </c>
       <c r="I20" s="11">
         <v>0</v>
       </c>
-      <c r="J20" s="18" t="s">
+      <c r="J20" s="20" t="s">
         <v>70</v>
       </c>
       <c r="K20" s="11">
@@ -3277,10 +3489,10 @@
       <c r="N20" s="11">
         <v>0</v>
       </c>
-      <c r="O20" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P20" s="18" t="s">
+      <c r="O20" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P20" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3301,7 +3513,7 @@
       <c r="G22" s="2">
         <v>0</v>
       </c>
-      <c r="H22" s="18" t="s">
+      <c r="H22" s="20" t="s">
         <v>72</v>
       </c>
       <c r="I22" s="11">
@@ -3322,10 +3534,10 @@
       <c r="N22" s="11">
         <v>1</v>
       </c>
-      <c r="O22" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P22" s="18" t="s">
+      <c r="O22" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P22" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3345,7 +3557,7 @@
       <c r="G23" s="2">
         <v>0</v>
       </c>
-      <c r="H23" s="19" t="s">
+      <c r="H23" s="21" t="s">
         <v>74</v>
       </c>
       <c r="I23" s="11">
@@ -3366,10 +3578,10 @@
       <c r="N23" s="11">
         <v>1</v>
       </c>
-      <c r="O23" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P23" s="18" t="s">
+      <c r="O23" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P23" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3389,7 +3601,7 @@
       <c r="G24" s="2">
         <v>0</v>
       </c>
-      <c r="H24" s="18" t="s">
+      <c r="H24" s="20" t="s">
         <v>76</v>
       </c>
       <c r="I24" s="11">
@@ -3410,10 +3622,10 @@
       <c r="N24" s="11">
         <v>1</v>
       </c>
-      <c r="O24" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P24" s="18" t="s">
+      <c r="O24" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P24" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3444,13 +3656,13 @@
       <c r="G26" s="2">
         <v>2000</v>
       </c>
-      <c r="H26" s="19" t="s">
+      <c r="H26" s="21" t="s">
         <v>76</v>
       </c>
       <c r="I26" s="2">
         <v>0</v>
       </c>
-      <c r="J26" s="19" t="s">
+      <c r="J26" s="21" t="s">
         <v>78</v>
       </c>
       <c r="K26" s="11">
@@ -3465,10 +3677,10 @@
       <c r="N26" s="11">
         <v>0</v>
       </c>
-      <c r="O26" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P26" s="18" t="s">
+      <c r="O26" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P26" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3488,13 +3700,13 @@
       <c r="G27" s="2">
         <v>2000</v>
       </c>
-      <c r="H27" s="18" t="s">
+      <c r="H27" s="20" t="s">
         <v>80</v>
       </c>
       <c r="I27" s="2">
         <v>0</v>
       </c>
-      <c r="J27" s="19" t="s">
+      <c r="J27" s="21" t="s">
         <v>78</v>
       </c>
       <c r="K27" s="11">
@@ -3509,10 +3721,10 @@
       <c r="N27" s="11">
         <v>0</v>
       </c>
-      <c r="O27" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P27" s="18" t="s">
+      <c r="O27" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P27" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3532,13 +3744,13 @@
       <c r="G28" s="2">
         <v>2000</v>
       </c>
-      <c r="H28" s="18" t="s">
+      <c r="H28" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="I28" s="19" t="s">
+      <c r="I28" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="J28" s="18" t="s">
+      <c r="J28" s="20" t="s">
         <v>84</v>
       </c>
       <c r="K28" s="11">
@@ -3553,10 +3765,10 @@
       <c r="N28" s="11">
         <v>0</v>
       </c>
-      <c r="O28" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P28" s="18" t="s">
+      <c r="O28" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P28" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3576,13 +3788,13 @@
       <c r="G29" s="2">
         <v>2000</v>
       </c>
-      <c r="H29" s="18" t="s">
+      <c r="H29" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="I29" s="19" t="s">
+      <c r="I29" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="J29" s="18" t="s">
+      <c r="J29" s="20" t="s">
         <v>78</v>
       </c>
       <c r="K29" s="11">
@@ -3597,10 +3809,10 @@
       <c r="N29" s="11">
         <v>0</v>
       </c>
-      <c r="O29" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P29" s="18" t="s">
+      <c r="O29" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P29" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3621,13 +3833,13 @@
       <c r="G31" s="2">
         <v>2000</v>
       </c>
-      <c r="H31" s="18" t="s">
+      <c r="H31" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="I31" s="19" t="s">
+      <c r="I31" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="J31" s="19" t="s">
+      <c r="J31" s="21" t="s">
         <v>59</v>
       </c>
       <c r="K31" s="11">
@@ -3642,10 +3854,10 @@
       <c r="N31" s="11">
         <v>0</v>
       </c>
-      <c r="O31" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P31" s="18" t="s">
+      <c r="O31" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P31" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3665,13 +3877,13 @@
       <c r="G32" s="2">
         <v>2000</v>
       </c>
-      <c r="H32" s="19" t="s">
+      <c r="H32" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="I32" s="18" t="s">
+      <c r="I32" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="J32" s="18" t="s">
+      <c r="J32" s="20" t="s">
         <v>83</v>
       </c>
       <c r="K32" s="11">
@@ -3686,10 +3898,10 @@
       <c r="N32" s="11">
         <v>0</v>
       </c>
-      <c r="O32" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P32" s="18" t="s">
+      <c r="O32" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P32" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3709,13 +3921,13 @@
       <c r="G33" s="2">
         <v>2000</v>
       </c>
-      <c r="H33" s="19" t="s">
+      <c r="H33" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="I33" s="18" t="s">
+      <c r="I33" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="J33" s="18" t="s">
+      <c r="J33" s="20" t="s">
         <v>83</v>
       </c>
       <c r="K33" s="11">
@@ -3730,10 +3942,10 @@
       <c r="N33" s="11">
         <v>0</v>
       </c>
-      <c r="O33" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P33" s="18" t="s">
+      <c r="O33" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P33" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3762,13 +3974,13 @@
       <c r="G35" s="2">
         <v>2000</v>
       </c>
-      <c r="H35" s="19" t="s">
+      <c r="H35" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="I35" s="19" t="s">
+      <c r="I35" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="J35" s="18" t="s">
+      <c r="J35" s="20" t="s">
         <v>96</v>
       </c>
       <c r="K35" s="11">
@@ -3783,10 +3995,10 @@
       <c r="N35" s="11">
         <v>0</v>
       </c>
-      <c r="O35" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P35" s="18" t="s">
+      <c r="O35" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P35" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3806,13 +4018,13 @@
       <c r="G36" s="2">
         <v>2000</v>
       </c>
-      <c r="H36" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="I36" s="19" t="s">
+      <c r="H36" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="I36" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="J36" s="18" t="s">
+      <c r="J36" s="20" t="s">
         <v>100</v>
       </c>
       <c r="K36" s="11">
@@ -3827,10 +4039,10 @@
       <c r="N36" s="11">
         <v>0</v>
       </c>
-      <c r="O36" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P36" s="18" t="s">
+      <c r="O36" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P36" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3850,13 +4062,13 @@
       <c r="G37" s="2">
         <v>2000</v>
       </c>
-      <c r="H37" s="19" t="s">
+      <c r="H37" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="I37" s="19" t="s">
+      <c r="I37" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="J37" s="18" t="s">
+      <c r="J37" s="20" t="s">
         <v>104</v>
       </c>
       <c r="K37" s="11">
@@ -3871,10 +4083,10 @@
       <c r="N37" s="11">
         <v>0</v>
       </c>
-      <c r="O37" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P37" s="18" t="s">
+      <c r="O37" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P37" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3894,13 +4106,13 @@
       <c r="G38" s="2">
         <v>2000</v>
       </c>
-      <c r="H38" s="19" t="s">
+      <c r="H38" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="I38" s="19" t="s">
+      <c r="I38" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="J38" s="18" t="s">
+      <c r="J38" s="20" t="s">
         <v>108</v>
       </c>
       <c r="K38" s="11">
@@ -3915,10 +4127,10 @@
       <c r="N38" s="11">
         <v>0</v>
       </c>
-      <c r="O38" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P38" s="18" t="s">
+      <c r="O38" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P38" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3938,13 +4150,13 @@
       <c r="G39" s="2">
         <v>2000</v>
       </c>
-      <c r="H39" s="19" t="s">
+      <c r="H39" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="I39" s="19" t="s">
+      <c r="I39" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="J39" s="18" t="s">
+      <c r="J39" s="20" t="s">
         <v>111</v>
       </c>
       <c r="K39" s="11">
@@ -3959,10 +4171,10 @@
       <c r="N39" s="11">
         <v>0</v>
       </c>
-      <c r="O39" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P39" s="18" t="s">
+      <c r="O39" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P39" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3972,15 +4184,15 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="16"/>
-      <c r="O40" s="16"/>
-      <c r="P40" s="16"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="18"/>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C41" s="2">
@@ -3998,7 +4210,7 @@
       <c r="G41" s="2">
         <v>0</v>
       </c>
-      <c r="H41" s="18" t="s">
+      <c r="H41" s="20" t="s">
         <v>113</v>
       </c>
       <c r="I41" s="11">
@@ -4019,10 +4231,10 @@
       <c r="N41" s="2">
         <v>1</v>
       </c>
-      <c r="O41" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P41" s="18" t="s">
+      <c r="O41" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P41" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4042,7 +4254,7 @@
       <c r="G42" s="2">
         <v>0</v>
       </c>
-      <c r="H42" s="18" t="s">
+      <c r="H42" s="20" t="s">
         <v>115</v>
       </c>
       <c r="I42" s="11">
@@ -4063,57 +4275,57 @@
       <c r="N42" s="2">
         <v>1</v>
       </c>
-      <c r="O42" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P42" s="18" t="s">
+      <c r="O42" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P42" s="20" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1"/>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="8:16">
-      <c r="H44" s="16"/>
-      <c r="I44" s="16"/>
-      <c r="J44" s="16"/>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="16"/>
-      <c r="O44" s="16"/>
-      <c r="P44" s="16"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18"/>
+      <c r="N44" s="18"/>
+      <c r="O44" s="18"/>
+      <c r="P44" s="18"/>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="8:16">
-      <c r="H45" s="16"/>
-      <c r="I45" s="16"/>
-      <c r="J45" s="16"/>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="16"/>
-      <c r="O45" s="16"/>
-      <c r="P45" s="16"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="18"/>
+      <c r="P45" s="18"/>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="8:16">
-      <c r="H46" s="16"/>
-      <c r="I46" s="16"/>
-      <c r="J46" s="16"/>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="16"/>
-      <c r="O46" s="16"/>
-      <c r="P46" s="16"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="18"/>
+      <c r="L46" s="18"/>
+      <c r="M46" s="18"/>
+      <c r="N46" s="18"/>
+      <c r="O46" s="18"/>
+      <c r="P46" s="18"/>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="8:16">
-      <c r="H47" s="16"/>
-      <c r="I47" s="16"/>
-      <c r="J47" s="16"/>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="16"/>
-      <c r="O47" s="16"/>
-      <c r="P47" s="16"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="18"/>
+      <c r="L47" s="18"/>
+      <c r="M47" s="18"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="18"/>
+      <c r="P47" s="18"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F32">
@@ -4151,7 +4363,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P129"/>
+  <dimension ref="C1:P164"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -4326,7 +4538,7 @@
       <c r="G6" s="8">
         <v>1051</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="H6" s="22" t="s">
         <v>117</v>
       </c>
       <c r="I6" s="2">
@@ -4344,10 +4556,10 @@
       <c r="M6" s="2">
         <v>0</v>
       </c>
-      <c r="N6" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O6" s="18" t="s">
+      <c r="N6" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O6" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4367,7 +4579,7 @@
       <c r="G7" s="8">
         <v>1052</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="22" t="s">
         <v>119</v>
       </c>
       <c r="I7" s="2">
@@ -4385,10 +4597,10 @@
       <c r="M7" s="2">
         <v>0</v>
       </c>
-      <c r="N7" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O7" s="18" t="s">
+      <c r="N7" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O7" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4408,7 +4620,7 @@
       <c r="G8" s="8">
         <v>1053</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="22" t="s">
         <v>121</v>
       </c>
       <c r="I8" s="2">
@@ -4426,10 +4638,10 @@
       <c r="M8" s="2">
         <v>0</v>
       </c>
-      <c r="N8" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O8" s="18" t="s">
+      <c r="N8" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O8" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4449,7 +4661,7 @@
       <c r="G9" s="8">
         <v>1054</v>
       </c>
-      <c r="H9" s="20" t="s">
+      <c r="H9" s="22" t="s">
         <v>123</v>
       </c>
       <c r="I9" s="2">
@@ -4467,10 +4679,10 @@
       <c r="M9" s="2">
         <v>0</v>
       </c>
-      <c r="N9" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O9" s="18" t="s">
+      <c r="N9" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O9" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4490,7 +4702,7 @@
       <c r="G10" s="8">
         <v>1055</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="22" t="s">
         <v>125</v>
       </c>
       <c r="I10" s="2">
@@ -4508,10 +4720,10 @@
       <c r="M10" s="2">
         <v>0</v>
       </c>
-      <c r="N10" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O10" s="18" t="s">
+      <c r="N10" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O10" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4531,7 +4743,7 @@
       <c r="G11" s="8">
         <v>1056</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="22" t="s">
         <v>127</v>
       </c>
       <c r="I11" s="2">
@@ -4549,10 +4761,10 @@
       <c r="M11" s="2">
         <v>0</v>
       </c>
-      <c r="N11" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O11" s="18" t="s">
+      <c r="N11" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O11" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4572,7 +4784,7 @@
       <c r="G12" s="8">
         <v>1057</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="H12" s="22" t="s">
         <v>129</v>
       </c>
       <c r="I12" s="2">
@@ -4590,10 +4802,10 @@
       <c r="M12" s="2">
         <v>0</v>
       </c>
-      <c r="N12" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O12" s="18" t="s">
+      <c r="N12" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O12" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4613,7 +4825,7 @@
       <c r="G13" s="8">
         <v>1058</v>
       </c>
-      <c r="H13" s="20" t="s">
+      <c r="H13" s="22" t="s">
         <v>131</v>
       </c>
       <c r="I13" s="2">
@@ -4631,10 +4843,10 @@
       <c r="M13" s="2">
         <v>0</v>
       </c>
-      <c r="N13" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O13" s="18" t="s">
+      <c r="N13" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O13" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4654,7 +4866,7 @@
       <c r="G14" s="8">
         <v>1059</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="22" t="s">
         <v>133</v>
       </c>
       <c r="I14" s="2">
@@ -4672,10 +4884,10 @@
       <c r="M14" s="2">
         <v>0</v>
       </c>
-      <c r="N14" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O14" s="18" t="s">
+      <c r="N14" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O14" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4695,7 +4907,7 @@
       <c r="G15" s="8">
         <v>1060</v>
       </c>
-      <c r="H15" s="20" t="s">
+      <c r="H15" s="22" t="s">
         <v>135</v>
       </c>
       <c r="I15" s="2">
@@ -4713,10 +4925,10 @@
       <c r="M15" s="2">
         <v>0</v>
       </c>
-      <c r="N15" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O15" s="18" t="s">
+      <c r="N15" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O15" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4736,7 +4948,7 @@
       <c r="G16" s="8">
         <v>1061</v>
       </c>
-      <c r="H16" s="20" t="s">
+      <c r="H16" s="22" t="s">
         <v>137</v>
       </c>
       <c r="I16" s="2">
@@ -4754,10 +4966,10 @@
       <c r="M16" s="2">
         <v>0</v>
       </c>
-      <c r="N16" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O16" s="18" t="s">
+      <c r="N16" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O16" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4777,7 +4989,7 @@
       <c r="G17" s="8">
         <v>1062</v>
       </c>
-      <c r="H17" s="20" t="s">
+      <c r="H17" s="22" t="s">
         <v>139</v>
       </c>
       <c r="I17" s="2">
@@ -4795,10 +5007,10 @@
       <c r="M17" s="2">
         <v>0</v>
       </c>
-      <c r="N17" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O17" s="18" t="s">
+      <c r="N17" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O17" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4818,7 +5030,7 @@
       <c r="G18" s="8">
         <v>1063</v>
       </c>
-      <c r="H18" s="20" t="s">
+      <c r="H18" s="22" t="s">
         <v>141</v>
       </c>
       <c r="I18" s="2">
@@ -4836,10 +5048,10 @@
       <c r="M18" s="2">
         <v>0</v>
       </c>
-      <c r="N18" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O18" s="18" t="s">
+      <c r="N18" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O18" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4859,7 +5071,7 @@
       <c r="G19" s="8">
         <v>1064</v>
       </c>
-      <c r="H19" s="20" t="s">
+      <c r="H19" s="22" t="s">
         <v>143</v>
       </c>
       <c r="I19" s="2">
@@ -4877,10 +5089,10 @@
       <c r="M19" s="2">
         <v>0</v>
       </c>
-      <c r="N19" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O19" s="18" t="s">
+      <c r="N19" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O19" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4900,7 +5112,7 @@
       <c r="G20" s="8">
         <v>1065</v>
       </c>
-      <c r="H20" s="20" t="s">
+      <c r="H20" s="22" t="s">
         <v>145</v>
       </c>
       <c r="I20" s="2">
@@ -4918,10 +5130,10 @@
       <c r="M20" s="2">
         <v>0</v>
       </c>
-      <c r="N20" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O20" s="18" t="s">
+      <c r="N20" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O20" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4941,7 +5153,7 @@
       <c r="G21" s="8">
         <v>1066</v>
       </c>
-      <c r="H21" s="20" t="s">
+      <c r="H21" s="22" t="s">
         <v>147</v>
       </c>
       <c r="I21" s="2">
@@ -4959,10 +5171,10 @@
       <c r="M21" s="2">
         <v>0</v>
       </c>
-      <c r="N21" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O21" s="18" t="s">
+      <c r="N21" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O21" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4982,7 +5194,7 @@
       <c r="G22" s="8">
         <v>1067</v>
       </c>
-      <c r="H22" s="20" t="s">
+      <c r="H22" s="22" t="s">
         <v>149</v>
       </c>
       <c r="I22" s="2">
@@ -5000,10 +5212,10 @@
       <c r="M22" s="2">
         <v>0</v>
       </c>
-      <c r="N22" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O22" s="18" t="s">
+      <c r="N22" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O22" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5023,7 +5235,7 @@
       <c r="G23" s="8">
         <v>1068</v>
       </c>
-      <c r="H23" s="20" t="s">
+      <c r="H23" s="22" t="s">
         <v>151</v>
       </c>
       <c r="I23" s="2">
@@ -5041,10 +5253,10 @@
       <c r="M23" s="2">
         <v>0</v>
       </c>
-      <c r="N23" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O23" s="18" t="s">
+      <c r="N23" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O23" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5064,7 +5276,7 @@
       <c r="G24" s="8">
         <v>1069</v>
       </c>
-      <c r="H24" s="20" t="s">
+      <c r="H24" s="22" t="s">
         <v>153</v>
       </c>
       <c r="I24" s="2">
@@ -5082,10 +5294,10 @@
       <c r="M24" s="2">
         <v>0</v>
       </c>
-      <c r="N24" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O24" s="18" t="s">
+      <c r="N24" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O24" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5105,7 +5317,7 @@
       <c r="G25" s="8">
         <v>1070</v>
       </c>
-      <c r="H25" s="20" t="s">
+      <c r="H25" s="22" t="s">
         <v>155</v>
       </c>
       <c r="I25" s="2">
@@ -5123,10 +5335,10 @@
       <c r="M25" s="2">
         <v>0</v>
       </c>
-      <c r="N25" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O25" s="18" t="s">
+      <c r="N25" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O25" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5146,7 +5358,7 @@
       <c r="G26" s="8">
         <v>1071</v>
       </c>
-      <c r="H26" s="20" t="s">
+      <c r="H26" s="22" t="s">
         <v>157</v>
       </c>
       <c r="I26" s="2">
@@ -5164,10 +5376,10 @@
       <c r="M26" s="2">
         <v>0</v>
       </c>
-      <c r="N26" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O26" s="18" t="s">
+      <c r="N26" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O26" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5187,7 +5399,7 @@
       <c r="G27" s="8">
         <v>1072</v>
       </c>
-      <c r="H27" s="20" t="s">
+      <c r="H27" s="22" t="s">
         <v>159</v>
       </c>
       <c r="I27" s="2">
@@ -5205,10 +5417,10 @@
       <c r="M27" s="2">
         <v>0</v>
       </c>
-      <c r="N27" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O27" s="18" t="s">
+      <c r="N27" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O27" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5228,7 +5440,7 @@
       <c r="G28" s="8">
         <v>1073</v>
       </c>
-      <c r="H28" s="20" t="s">
+      <c r="H28" s="22" t="s">
         <v>161</v>
       </c>
       <c r="I28" s="2">
@@ -5246,10 +5458,10 @@
       <c r="M28" s="2">
         <v>0</v>
       </c>
-      <c r="N28" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O28" s="18" t="s">
+      <c r="N28" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O28" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5269,7 +5481,7 @@
       <c r="G29" s="8">
         <v>1074</v>
       </c>
-      <c r="H29" s="20" t="s">
+      <c r="H29" s="22" t="s">
         <v>163</v>
       </c>
       <c r="I29" s="2">
@@ -5287,10 +5499,10 @@
       <c r="M29" s="2">
         <v>0</v>
       </c>
-      <c r="N29" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O29" s="18" t="s">
+      <c r="N29" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O29" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P29" s="2"/>
@@ -5311,7 +5523,7 @@
       <c r="G30" s="8">
         <v>1075</v>
       </c>
-      <c r="H30" s="20" t="s">
+      <c r="H30" s="22" t="s">
         <v>165</v>
       </c>
       <c r="I30" s="2">
@@ -5329,10 +5541,10 @@
       <c r="M30" s="2">
         <v>0</v>
       </c>
-      <c r="N30" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O30" s="18" t="s">
+      <c r="N30" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O30" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5352,7 +5564,7 @@
       <c r="G31" s="8">
         <v>1076</v>
       </c>
-      <c r="H31" s="20" t="s">
+      <c r="H31" s="22" t="s">
         <v>167</v>
       </c>
       <c r="I31" s="2">
@@ -5370,10 +5582,10 @@
       <c r="M31" s="2">
         <v>0</v>
       </c>
-      <c r="N31" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O31" s="18" t="s">
+      <c r="N31" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O31" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5393,7 +5605,7 @@
       <c r="G32" s="8">
         <v>1077</v>
       </c>
-      <c r="H32" s="20" t="s">
+      <c r="H32" s="22" t="s">
         <v>169</v>
       </c>
       <c r="I32" s="2">
@@ -5411,10 +5623,10 @@
       <c r="M32" s="2">
         <v>0</v>
       </c>
-      <c r="N32" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O32" s="18" t="s">
+      <c r="N32" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O32" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5434,7 +5646,7 @@
       <c r="G33" s="8">
         <v>1078</v>
       </c>
-      <c r="H33" s="20" t="s">
+      <c r="H33" s="22" t="s">
         <v>171</v>
       </c>
       <c r="I33" s="2">
@@ -5452,10 +5664,10 @@
       <c r="M33" s="2">
         <v>0</v>
       </c>
-      <c r="N33" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O33" s="18" t="s">
+      <c r="N33" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O33" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5475,7 +5687,7 @@
       <c r="G34" s="8">
         <v>1079</v>
       </c>
-      <c r="H34" s="20" t="s">
+      <c r="H34" s="22" t="s">
         <v>173</v>
       </c>
       <c r="I34" s="2">
@@ -5493,10 +5705,10 @@
       <c r="M34" s="2">
         <v>0</v>
       </c>
-      <c r="N34" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O34" s="18" t="s">
+      <c r="N34" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O34" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P34" s="2"/>
@@ -5517,7 +5729,7 @@
       <c r="G35" s="8">
         <v>1080</v>
       </c>
-      <c r="H35" s="20" t="s">
+      <c r="H35" s="22" t="s">
         <v>175</v>
       </c>
       <c r="I35" s="2">
@@ -5535,10 +5747,10 @@
       <c r="M35" s="2">
         <v>0</v>
       </c>
-      <c r="N35" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O35" s="18" t="s">
+      <c r="N35" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O35" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P35" s="2"/>
@@ -5559,7 +5771,7 @@
       <c r="G36" s="8">
         <v>1081</v>
       </c>
-      <c r="H36" s="20" t="s">
+      <c r="H36" s="22" t="s">
         <v>177</v>
       </c>
       <c r="I36" s="2">
@@ -5577,10 +5789,10 @@
       <c r="M36" s="2">
         <v>0</v>
       </c>
-      <c r="N36" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O36" s="18" t="s">
+      <c r="N36" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O36" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P36" s="2"/>
@@ -5601,7 +5813,7 @@
       <c r="G37" s="8">
         <v>1082</v>
       </c>
-      <c r="H37" s="20" t="s">
+      <c r="H37" s="22" t="s">
         <v>179</v>
       </c>
       <c r="I37" s="2">
@@ -5619,10 +5831,10 @@
       <c r="M37" s="2">
         <v>0</v>
       </c>
-      <c r="N37" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O37" s="18" t="s">
+      <c r="N37" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O37" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P37" s="2"/>
@@ -5643,7 +5855,7 @@
       <c r="G38" s="8">
         <v>1083</v>
       </c>
-      <c r="H38" s="20" t="s">
+      <c r="H38" s="22" t="s">
         <v>181</v>
       </c>
       <c r="I38" s="2">
@@ -5661,10 +5873,10 @@
       <c r="M38" s="2">
         <v>0</v>
       </c>
-      <c r="N38" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O38" s="18" t="s">
+      <c r="N38" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O38" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P38" s="2"/>
@@ -5685,7 +5897,7 @@
       <c r="G39" s="8">
         <v>1084</v>
       </c>
-      <c r="H39" s="20" t="s">
+      <c r="H39" s="22" t="s">
         <v>183</v>
       </c>
       <c r="I39" s="2">
@@ -5703,10 +5915,10 @@
       <c r="M39" s="2">
         <v>0</v>
       </c>
-      <c r="N39" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O39" s="18" t="s">
+      <c r="N39" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O39" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P39" s="2"/>
@@ -5727,7 +5939,7 @@
       <c r="G40" s="8">
         <v>1085</v>
       </c>
-      <c r="H40" s="20" t="s">
+      <c r="H40" s="22" t="s">
         <v>185</v>
       </c>
       <c r="I40" s="2">
@@ -5745,10 +5957,10 @@
       <c r="M40" s="2">
         <v>0</v>
       </c>
-      <c r="N40" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O40" s="18" t="s">
+      <c r="N40" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O40" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P40" s="2"/>
@@ -5769,7 +5981,7 @@
       <c r="G41" s="8">
         <v>1086</v>
       </c>
-      <c r="H41" s="20" t="s">
+      <c r="H41" s="22" t="s">
         <v>187</v>
       </c>
       <c r="I41" s="2">
@@ -5787,10 +5999,10 @@
       <c r="M41" s="2">
         <v>0</v>
       </c>
-      <c r="N41" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O41" s="18" t="s">
+      <c r="N41" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O41" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P41" s="2"/>
@@ -5811,7 +6023,7 @@
       <c r="G42" s="8">
         <v>1087</v>
       </c>
-      <c r="H42" s="20" t="s">
+      <c r="H42" s="22" t="s">
         <v>189</v>
       </c>
       <c r="I42" s="2">
@@ -5829,10 +6041,10 @@
       <c r="M42" s="2">
         <v>0</v>
       </c>
-      <c r="N42" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O42" s="18" t="s">
+      <c r="N42" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O42" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P42" s="2"/>
@@ -5853,7 +6065,7 @@
       <c r="G43" s="8">
         <v>1088</v>
       </c>
-      <c r="H43" s="20" t="s">
+      <c r="H43" s="22" t="s">
         <v>191</v>
       </c>
       <c r="I43" s="2">
@@ -5871,10 +6083,10 @@
       <c r="M43" s="2">
         <v>0</v>
       </c>
-      <c r="N43" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O43" s="18" t="s">
+      <c r="N43" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O43" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P43" s="2"/>
@@ -5895,7 +6107,7 @@
       <c r="G44" s="8">
         <v>1089</v>
       </c>
-      <c r="H44" s="20" t="s">
+      <c r="H44" s="22" t="s">
         <v>193</v>
       </c>
       <c r="I44" s="2">
@@ -5913,10 +6125,10 @@
       <c r="M44" s="2">
         <v>0</v>
       </c>
-      <c r="N44" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O44" s="18" t="s">
+      <c r="N44" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O44" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P44" s="2"/>
@@ -5937,7 +6149,7 @@
       <c r="G45" s="8">
         <v>1090</v>
       </c>
-      <c r="H45" s="20" t="s">
+      <c r="H45" s="22" t="s">
         <v>195</v>
       </c>
       <c r="I45" s="2">
@@ -5955,10 +6167,10 @@
       <c r="M45" s="2">
         <v>0</v>
       </c>
-      <c r="N45" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O45" s="18" t="s">
+      <c r="N45" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O45" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P45" s="2"/>
@@ -5979,7 +6191,7 @@
       <c r="G46" s="8">
         <v>1091</v>
       </c>
-      <c r="H46" s="20" t="s">
+      <c r="H46" s="22" t="s">
         <v>197</v>
       </c>
       <c r="I46" s="2">
@@ -5997,10 +6209,10 @@
       <c r="M46" s="2">
         <v>0</v>
       </c>
-      <c r="N46" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O46" s="18" t="s">
+      <c r="N46" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O46" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P46" s="2"/>
@@ -6021,7 +6233,7 @@
       <c r="G47" s="8">
         <v>1092</v>
       </c>
-      <c r="H47" s="20" t="s">
+      <c r="H47" s="22" t="s">
         <v>199</v>
       </c>
       <c r="I47" s="2">
@@ -6039,10 +6251,10 @@
       <c r="M47" s="2">
         <v>0</v>
       </c>
-      <c r="N47" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O47" s="18" t="s">
+      <c r="N47" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O47" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P47" s="2"/>
@@ -6063,7 +6275,7 @@
       <c r="G48" s="8">
         <v>1093</v>
       </c>
-      <c r="H48" s="20" t="s">
+      <c r="H48" s="22" t="s">
         <v>201</v>
       </c>
       <c r="I48" s="2">
@@ -6081,10 +6293,10 @@
       <c r="M48" s="2">
         <v>0</v>
       </c>
-      <c r="N48" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O48" s="18" t="s">
+      <c r="N48" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O48" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P48" s="2"/>
@@ -6105,7 +6317,7 @@
       <c r="G49" s="8">
         <v>1094</v>
       </c>
-      <c r="H49" s="20" t="s">
+      <c r="H49" s="22" t="s">
         <v>203</v>
       </c>
       <c r="I49" s="2">
@@ -6123,10 +6335,10 @@
       <c r="M49" s="2">
         <v>0</v>
       </c>
-      <c r="N49" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O49" s="18" t="s">
+      <c r="N49" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O49" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P49" s="2"/>
@@ -6147,7 +6359,7 @@
       <c r="G50" s="8">
         <v>1095</v>
       </c>
-      <c r="H50" s="20" t="s">
+      <c r="H50" s="22" t="s">
         <v>205</v>
       </c>
       <c r="I50" s="2">
@@ -6165,10 +6377,10 @@
       <c r="M50" s="2">
         <v>0</v>
       </c>
-      <c r="N50" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O50" s="18" t="s">
+      <c r="N50" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O50" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P50" s="2"/>
@@ -6189,7 +6401,7 @@
       <c r="G51" s="8">
         <v>1096</v>
       </c>
-      <c r="H51" s="20" t="s">
+      <c r="H51" s="22" t="s">
         <v>207</v>
       </c>
       <c r="I51" s="2">
@@ -6207,10 +6419,10 @@
       <c r="M51" s="2">
         <v>0</v>
       </c>
-      <c r="N51" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O51" s="18" t="s">
+      <c r="N51" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O51" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P51" s="2"/>
@@ -6231,7 +6443,7 @@
       <c r="G52" s="8">
         <v>1097</v>
       </c>
-      <c r="H52" s="20" t="s">
+      <c r="H52" s="22" t="s">
         <v>209</v>
       </c>
       <c r="I52" s="2">
@@ -6249,10 +6461,10 @@
       <c r="M52" s="2">
         <v>0</v>
       </c>
-      <c r="N52" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O52" s="18" t="s">
+      <c r="N52" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O52" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P52" s="2"/>
@@ -6273,7 +6485,7 @@
       <c r="G53" s="8">
         <v>1098</v>
       </c>
-      <c r="H53" s="20" t="s">
+      <c r="H53" s="22" t="s">
         <v>211</v>
       </c>
       <c r="I53" s="2">
@@ -6291,10 +6503,10 @@
       <c r="M53" s="2">
         <v>0</v>
       </c>
-      <c r="N53" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O53" s="18" t="s">
+      <c r="N53" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O53" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P53" s="2"/>
@@ -6315,7 +6527,7 @@
       <c r="G54" s="8">
         <v>1099</v>
       </c>
-      <c r="H54" s="20" t="s">
+      <c r="H54" s="22" t="s">
         <v>213</v>
       </c>
       <c r="I54" s="2">
@@ -6333,10 +6545,10 @@
       <c r="M54" s="2">
         <v>0</v>
       </c>
-      <c r="N54" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O54" s="18" t="s">
+      <c r="N54" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O54" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P54" s="2"/>
@@ -6357,7 +6569,7 @@
       <c r="G55" s="8">
         <v>1100</v>
       </c>
-      <c r="H55" s="20" t="s">
+      <c r="H55" s="22" t="s">
         <v>215</v>
       </c>
       <c r="I55" s="2">
@@ -6375,10 +6587,10 @@
       <c r="M55" s="2">
         <v>0</v>
       </c>
-      <c r="N55" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O55" s="18" t="s">
+      <c r="N55" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O55" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P55" s="2"/>
@@ -6399,7 +6611,7 @@
       <c r="G56" s="8">
         <v>1101</v>
       </c>
-      <c r="H56" s="20" t="s">
+      <c r="H56" s="22" t="s">
         <v>217</v>
       </c>
       <c r="I56" s="2">
@@ -6417,10 +6629,10 @@
       <c r="M56" s="2">
         <v>0</v>
       </c>
-      <c r="N56" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O56" s="18" t="s">
+      <c r="N56" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O56" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P56" s="2"/>
@@ -6441,7 +6653,7 @@
       <c r="G57" s="8">
         <v>1102</v>
       </c>
-      <c r="H57" s="20" t="s">
+      <c r="H57" s="22" t="s">
         <v>219</v>
       </c>
       <c r="I57" s="2">
@@ -6459,10 +6671,10 @@
       <c r="M57" s="2">
         <v>0</v>
       </c>
-      <c r="N57" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O57" s="18" t="s">
+      <c r="N57" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O57" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P57" s="2"/>
@@ -6483,7 +6695,7 @@
       <c r="G58" s="8">
         <v>1103</v>
       </c>
-      <c r="H58" s="20" t="s">
+      <c r="H58" s="22" t="s">
         <v>221</v>
       </c>
       <c r="I58" s="2">
@@ -6501,10 +6713,10 @@
       <c r="M58" s="2">
         <v>0</v>
       </c>
-      <c r="N58" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O58" s="18" t="s">
+      <c r="N58" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O58" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P58" s="2"/>
@@ -6525,7 +6737,7 @@
       <c r="G59" s="8">
         <v>1104</v>
       </c>
-      <c r="H59" s="20" t="s">
+      <c r="H59" s="22" t="s">
         <v>223</v>
       </c>
       <c r="I59" s="2">
@@ -6543,10 +6755,10 @@
       <c r="M59" s="2">
         <v>0</v>
       </c>
-      <c r="N59" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O59" s="18" t="s">
+      <c r="N59" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O59" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P59" s="2"/>
@@ -6561,13 +6773,13 @@
       <c r="E60" s="12">
         <v>98</v>
       </c>
-      <c r="F60" s="13">
+      <c r="F60" s="14">
         <v>1105</v>
       </c>
-      <c r="G60" s="13">
+      <c r="G60" s="14">
         <v>1105</v>
       </c>
-      <c r="H60" s="21" t="s">
+      <c r="H60" s="23" t="s">
         <v>225</v>
       </c>
       <c r="I60" s="12">
@@ -6585,10 +6797,10 @@
       <c r="M60" s="12">
         <v>0</v>
       </c>
-      <c r="N60" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="O60" s="22" t="s">
+      <c r="N60" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="O60" s="24" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6608,7 +6820,7 @@
       <c r="G61" s="8">
         <v>1106</v>
       </c>
-      <c r="H61" s="20" t="s">
+      <c r="H61" s="22" t="s">
         <v>227</v>
       </c>
       <c r="I61" s="2">
@@ -6626,10 +6838,10 @@
       <c r="M61" s="2">
         <v>0</v>
       </c>
-      <c r="N61" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O61" s="18" t="s">
+      <c r="N61" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O61" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6649,7 +6861,7 @@
       <c r="G62" s="8">
         <v>1107</v>
       </c>
-      <c r="H62" s="20" t="s">
+      <c r="H62" s="22" t="s">
         <v>229</v>
       </c>
       <c r="I62" s="2">
@@ -6667,10 +6879,10 @@
       <c r="M62" s="2">
         <v>0</v>
       </c>
-      <c r="N62" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O62" s="18" t="s">
+      <c r="N62" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O62" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6690,7 +6902,7 @@
       <c r="G63" s="8">
         <v>1108</v>
       </c>
-      <c r="H63" s="20" t="s">
+      <c r="H63" s="22" t="s">
         <v>231</v>
       </c>
       <c r="I63" s="2">
@@ -6708,10 +6920,10 @@
       <c r="M63" s="2">
         <v>0</v>
       </c>
-      <c r="N63" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O63" s="18" t="s">
+      <c r="N63" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O63" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6731,7 +6943,7 @@
       <c r="G64" s="8">
         <v>1109</v>
       </c>
-      <c r="H64" s="20" t="s">
+      <c r="H64" s="22" t="s">
         <v>233</v>
       </c>
       <c r="I64" s="2">
@@ -6749,10 +6961,10 @@
       <c r="M64" s="2">
         <v>0</v>
       </c>
-      <c r="N64" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O64" s="18" t="s">
+      <c r="N64" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O64" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P64" s="2"/>
@@ -6773,7 +6985,7 @@
       <c r="G65" s="8">
         <v>1110</v>
       </c>
-      <c r="H65" s="20" t="s">
+      <c r="H65" s="22" t="s">
         <v>235</v>
       </c>
       <c r="I65" s="2">
@@ -6791,10 +7003,10 @@
       <c r="M65" s="2">
         <v>0</v>
       </c>
-      <c r="N65" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O65" s="18" t="s">
+      <c r="N65" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O65" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6814,7 +7026,7 @@
       <c r="G66" s="8">
         <v>1111</v>
       </c>
-      <c r="H66" s="20" t="s">
+      <c r="H66" s="22" t="s">
         <v>237</v>
       </c>
       <c r="I66" s="2">
@@ -6832,10 +7044,10 @@
       <c r="M66" s="2">
         <v>0</v>
       </c>
-      <c r="N66" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O66" s="18" t="s">
+      <c r="N66" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O66" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6855,7 +7067,7 @@
       <c r="G67" s="8">
         <v>1112</v>
       </c>
-      <c r="H67" s="20" t="s">
+      <c r="H67" s="22" t="s">
         <v>239</v>
       </c>
       <c r="I67" s="2">
@@ -6873,10 +7085,10 @@
       <c r="M67" s="2">
         <v>0</v>
       </c>
-      <c r="N67" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O67" s="18" t="s">
+      <c r="N67" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O67" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6896,7 +7108,7 @@
       <c r="G68" s="8">
         <v>1113</v>
       </c>
-      <c r="H68" s="20" t="s">
+      <c r="H68" s="22" t="s">
         <v>241</v>
       </c>
       <c r="I68" s="2">
@@ -6914,10 +7126,10 @@
       <c r="M68" s="2">
         <v>0</v>
       </c>
-      <c r="N68" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O68" s="18" t="s">
+      <c r="N68" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O68" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6937,7 +7149,7 @@
       <c r="G69" s="8">
         <v>1114</v>
       </c>
-      <c r="H69" s="20" t="s">
+      <c r="H69" s="22" t="s">
         <v>243</v>
       </c>
       <c r="I69" s="2">
@@ -6955,10 +7167,10 @@
       <c r="M69" s="2">
         <v>0</v>
       </c>
-      <c r="N69" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O69" s="18" t="s">
+      <c r="N69" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O69" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P69" s="2"/>
@@ -6979,7 +7191,7 @@
       <c r="G70" s="8">
         <v>1115</v>
       </c>
-      <c r="H70" s="20" t="s">
+      <c r="H70" s="22" t="s">
         <v>245</v>
       </c>
       <c r="I70" s="2">
@@ -6997,10 +7209,10 @@
       <c r="M70" s="2">
         <v>0</v>
       </c>
-      <c r="N70" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O70" s="18" t="s">
+      <c r="N70" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O70" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P70" s="2"/>
@@ -7021,7 +7233,7 @@
       <c r="G71" s="8">
         <v>1116</v>
       </c>
-      <c r="H71" s="20" t="s">
+      <c r="H71" s="22" t="s">
         <v>247</v>
       </c>
       <c r="I71" s="2">
@@ -7039,10 +7251,10 @@
       <c r="M71" s="2">
         <v>0</v>
       </c>
-      <c r="N71" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O71" s="18" t="s">
+      <c r="N71" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O71" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P71" s="2"/>
@@ -7063,7 +7275,7 @@
       <c r="G72" s="8">
         <v>1117</v>
       </c>
-      <c r="H72" s="20" t="s">
+      <c r="H72" s="22" t="s">
         <v>249</v>
       </c>
       <c r="I72" s="2">
@@ -7081,10 +7293,10 @@
       <c r="M72" s="2">
         <v>0</v>
       </c>
-      <c r="N72" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O72" s="18" t="s">
+      <c r="N72" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O72" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P72" s="2"/>
@@ -7105,7 +7317,7 @@
       <c r="G73" s="8">
         <v>1118</v>
       </c>
-      <c r="H73" s="20" t="s">
+      <c r="H73" s="22" t="s">
         <v>251</v>
       </c>
       <c r="I73" s="2">
@@ -7123,10 +7335,10 @@
       <c r="M73" s="2">
         <v>0</v>
       </c>
-      <c r="N73" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O73" s="18" t="s">
+      <c r="N73" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O73" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P73" s="2"/>
@@ -7147,7 +7359,7 @@
       <c r="G74" s="8">
         <v>1119</v>
       </c>
-      <c r="H74" s="20" t="s">
+      <c r="H74" s="22" t="s">
         <v>253</v>
       </c>
       <c r="I74" s="2">
@@ -7165,10 +7377,10 @@
       <c r="M74" s="2">
         <v>0</v>
       </c>
-      <c r="N74" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O74" s="18" t="s">
+      <c r="N74" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O74" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P74" s="2"/>
@@ -7189,7 +7401,7 @@
       <c r="G75" s="8">
         <v>1120</v>
       </c>
-      <c r="H75" s="20" t="s">
+      <c r="H75" s="22" t="s">
         <v>255</v>
       </c>
       <c r="I75" s="2">
@@ -7207,10 +7419,10 @@
       <c r="M75" s="2">
         <v>0</v>
       </c>
-      <c r="N75" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O75" s="18" t="s">
+      <c r="N75" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O75" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P75" s="2"/>
@@ -7231,7 +7443,7 @@
       <c r="G76" s="8">
         <v>1121</v>
       </c>
-      <c r="H76" s="20" t="s">
+      <c r="H76" s="22" t="s">
         <v>257</v>
       </c>
       <c r="I76" s="2">
@@ -7249,10 +7461,10 @@
       <c r="M76" s="2">
         <v>0</v>
       </c>
-      <c r="N76" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O76" s="18" t="s">
+      <c r="N76" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O76" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P76" s="2"/>
@@ -7273,7 +7485,7 @@
       <c r="G77" s="8">
         <v>1122</v>
       </c>
-      <c r="H77" s="20" t="s">
+      <c r="H77" s="22" t="s">
         <v>259</v>
       </c>
       <c r="I77" s="2">
@@ -7291,10 +7503,10 @@
       <c r="M77" s="2">
         <v>0</v>
       </c>
-      <c r="N77" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O77" s="18" t="s">
+      <c r="N77" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O77" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P77" s="2"/>
@@ -7315,7 +7527,7 @@
       <c r="G78" s="8">
         <v>1123</v>
       </c>
-      <c r="H78" s="20" t="s">
+      <c r="H78" s="22" t="s">
         <v>261</v>
       </c>
       <c r="I78" s="2">
@@ -7333,10 +7545,10 @@
       <c r="M78" s="2">
         <v>0</v>
       </c>
-      <c r="N78" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O78" s="18" t="s">
+      <c r="N78" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O78" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P78" s="2"/>
@@ -7357,7 +7569,7 @@
       <c r="G79" s="8">
         <v>1124</v>
       </c>
-      <c r="H79" s="20" t="s">
+      <c r="H79" s="22" t="s">
         <v>263</v>
       </c>
       <c r="I79" s="2">
@@ -7375,10 +7587,10 @@
       <c r="M79" s="2">
         <v>0</v>
       </c>
-      <c r="N79" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O79" s="18" t="s">
+      <c r="N79" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O79" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P79" s="2"/>
@@ -7399,7 +7611,7 @@
       <c r="G80" s="8">
         <v>1125</v>
       </c>
-      <c r="H80" s="20" t="s">
+      <c r="H80" s="22" t="s">
         <v>265</v>
       </c>
       <c r="I80" s="2">
@@ -7417,10 +7629,10 @@
       <c r="M80" s="2">
         <v>0</v>
       </c>
-      <c r="N80" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O80" s="18" t="s">
+      <c r="N80" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O80" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P80" s="2"/>
@@ -7441,7 +7653,7 @@
       <c r="G81" s="8">
         <v>1126</v>
       </c>
-      <c r="H81" s="20" t="s">
+      <c r="H81" s="22" t="s">
         <v>267</v>
       </c>
       <c r="I81" s="2">
@@ -7459,10 +7671,10 @@
       <c r="M81" s="2">
         <v>0</v>
       </c>
-      <c r="N81" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O81" s="18" t="s">
+      <c r="N81" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O81" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P81" s="2"/>
@@ -7483,7 +7695,7 @@
       <c r="G82" s="8">
         <v>1127</v>
       </c>
-      <c r="H82" s="20" t="s">
+      <c r="H82" s="22" t="s">
         <v>269</v>
       </c>
       <c r="I82" s="2">
@@ -7501,10 +7713,10 @@
       <c r="M82" s="2">
         <v>0</v>
       </c>
-      <c r="N82" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O82" s="18" t="s">
+      <c r="N82" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O82" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P82" s="2"/>
@@ -7525,7 +7737,7 @@
       <c r="G83" s="8">
         <v>1128</v>
       </c>
-      <c r="H83" s="20" t="s">
+      <c r="H83" s="22" t="s">
         <v>271</v>
       </c>
       <c r="I83" s="2">
@@ -7543,10 +7755,10 @@
       <c r="M83" s="2">
         <v>0</v>
       </c>
-      <c r="N83" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O83" s="18" t="s">
+      <c r="N83" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O83" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P83" s="2"/>
@@ -7567,7 +7779,7 @@
       <c r="G84" s="8">
         <v>1129</v>
       </c>
-      <c r="H84" s="20" t="s">
+      <c r="H84" s="22" t="s">
         <v>273</v>
       </c>
       <c r="I84" s="2">
@@ -7585,10 +7797,10 @@
       <c r="M84" s="2">
         <v>0</v>
       </c>
-      <c r="N84" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O84" s="18" t="s">
+      <c r="N84" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O84" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P84" s="2"/>
@@ -7609,7 +7821,7 @@
       <c r="G85" s="8">
         <v>1130</v>
       </c>
-      <c r="H85" s="20" t="s">
+      <c r="H85" s="22" t="s">
         <v>275</v>
       </c>
       <c r="I85" s="2">
@@ -7627,10 +7839,10 @@
       <c r="M85" s="2">
         <v>0</v>
       </c>
-      <c r="N85" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O85" s="18" t="s">
+      <c r="N85" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O85" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P85" s="2"/>
@@ -7651,7 +7863,7 @@
       <c r="G86" s="8">
         <v>1131</v>
       </c>
-      <c r="H86" s="20" t="s">
+      <c r="H86" s="22" t="s">
         <v>277</v>
       </c>
       <c r="I86" s="2">
@@ -7669,10 +7881,10 @@
       <c r="M86" s="2">
         <v>0</v>
       </c>
-      <c r="N86" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O86" s="18" t="s">
+      <c r="N86" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O86" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P86" s="2"/>
@@ -7693,7 +7905,7 @@
       <c r="G87" s="8">
         <v>1132</v>
       </c>
-      <c r="H87" s="20" t="s">
+      <c r="H87" s="22" t="s">
         <v>279</v>
       </c>
       <c r="I87" s="2">
@@ -7711,10 +7923,10 @@
       <c r="M87" s="2">
         <v>0</v>
       </c>
-      <c r="N87" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O87" s="18" t="s">
+      <c r="N87" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O87" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P87" s="2"/>
@@ -7735,7 +7947,7 @@
       <c r="G88" s="8">
         <v>1133</v>
       </c>
-      <c r="H88" s="20" t="s">
+      <c r="H88" s="22" t="s">
         <v>281</v>
       </c>
       <c r="I88" s="2">
@@ -7753,10 +7965,10 @@
       <c r="M88" s="2">
         <v>0</v>
       </c>
-      <c r="N88" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O88" s="18" t="s">
+      <c r="N88" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O88" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P88" s="2"/>
@@ -7777,7 +7989,7 @@
       <c r="G89" s="8">
         <v>1134</v>
       </c>
-      <c r="H89" s="20" t="s">
+      <c r="H89" s="22" t="s">
         <v>283</v>
       </c>
       <c r="I89" s="2">
@@ -7795,10 +8007,10 @@
       <c r="M89" s="2">
         <v>0</v>
       </c>
-      <c r="N89" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O89" s="18" t="s">
+      <c r="N89" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O89" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P89" s="2"/>
@@ -7819,7 +8031,7 @@
       <c r="G90" s="8">
         <v>1135</v>
       </c>
-      <c r="H90" s="20" t="s">
+      <c r="H90" s="22" t="s">
         <v>285</v>
       </c>
       <c r="I90" s="2">
@@ -7837,10 +8049,10 @@
       <c r="M90" s="2">
         <v>0</v>
       </c>
-      <c r="N90" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O90" s="18" t="s">
+      <c r="N90" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O90" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P90" s="2"/>
@@ -7861,7 +8073,7 @@
       <c r="G91" s="8">
         <v>1136</v>
       </c>
-      <c r="H91" s="20" t="s">
+      <c r="H91" s="22" t="s">
         <v>287</v>
       </c>
       <c r="I91" s="2">
@@ -7879,10 +8091,10 @@
       <c r="M91" s="2">
         <v>0</v>
       </c>
-      <c r="N91" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O91" s="18" t="s">
+      <c r="N91" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O91" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P91" s="2"/>
@@ -7903,7 +8115,7 @@
       <c r="G92" s="8">
         <v>1137</v>
       </c>
-      <c r="H92" s="20" t="s">
+      <c r="H92" s="22" t="s">
         <v>289</v>
       </c>
       <c r="I92" s="2">
@@ -7921,10 +8133,10 @@
       <c r="M92" s="2">
         <v>0</v>
       </c>
-      <c r="N92" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O92" s="18" t="s">
+      <c r="N92" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O92" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P92" s="2"/>
@@ -7945,7 +8157,7 @@
       <c r="G93" s="8">
         <v>1138</v>
       </c>
-      <c r="H93" s="20" t="s">
+      <c r="H93" s="22" t="s">
         <v>291</v>
       </c>
       <c r="I93" s="2">
@@ -7963,10 +8175,10 @@
       <c r="M93" s="2">
         <v>0</v>
       </c>
-      <c r="N93" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O93" s="18" t="s">
+      <c r="N93" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O93" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P93" s="2"/>
@@ -7987,7 +8199,7 @@
       <c r="G94" s="8">
         <v>1139</v>
       </c>
-      <c r="H94" s="20" t="s">
+      <c r="H94" s="22" t="s">
         <v>293</v>
       </c>
       <c r="I94" s="2">
@@ -8005,10 +8217,10 @@
       <c r="M94" s="2">
         <v>0</v>
       </c>
-      <c r="N94" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O94" s="18" t="s">
+      <c r="N94" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O94" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P94" s="2"/>
@@ -8023,13 +8235,13 @@
       <c r="E95" s="12">
         <v>98</v>
       </c>
-      <c r="F95" s="13">
+      <c r="F95" s="14">
         <v>1140</v>
       </c>
-      <c r="G95" s="13">
+      <c r="G95" s="14">
         <v>1140</v>
       </c>
-      <c r="H95" s="21" t="s">
+      <c r="H95" s="23" t="s">
         <v>295</v>
       </c>
       <c r="I95" s="12">
@@ -8047,10 +8259,10 @@
       <c r="M95" s="12">
         <v>0</v>
       </c>
-      <c r="N95" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="O95" s="22" t="s">
+      <c r="N95" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="O95" s="24" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8070,7 +8282,7 @@
       <c r="G96" s="8">
         <v>1141</v>
       </c>
-      <c r="H96" s="20" t="s">
+      <c r="H96" s="22" t="s">
         <v>297</v>
       </c>
       <c r="I96" s="2">
@@ -8088,10 +8300,10 @@
       <c r="M96" s="2">
         <v>0</v>
       </c>
-      <c r="N96" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O96" s="18" t="s">
+      <c r="N96" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O96" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8111,7 +8323,7 @@
       <c r="G97" s="8">
         <v>1142</v>
       </c>
-      <c r="H97" s="20" t="s">
+      <c r="H97" s="22" t="s">
         <v>299</v>
       </c>
       <c r="I97" s="2">
@@ -8129,10 +8341,10 @@
       <c r="M97" s="2">
         <v>0</v>
       </c>
-      <c r="N97" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O97" s="18" t="s">
+      <c r="N97" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O97" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8152,7 +8364,7 @@
       <c r="G98" s="8">
         <v>1143</v>
       </c>
-      <c r="H98" s="20" t="s">
+      <c r="H98" s="22" t="s">
         <v>301</v>
       </c>
       <c r="I98" s="2">
@@ -8170,10 +8382,10 @@
       <c r="M98" s="2">
         <v>0</v>
       </c>
-      <c r="N98" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O98" s="18" t="s">
+      <c r="N98" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O98" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8193,7 +8405,7 @@
       <c r="G99" s="8">
         <v>1144</v>
       </c>
-      <c r="H99" s="20" t="s">
+      <c r="H99" s="22" t="s">
         <v>303</v>
       </c>
       <c r="I99" s="2">
@@ -8211,10 +8423,10 @@
       <c r="M99" s="2">
         <v>0</v>
       </c>
-      <c r="N99" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O99" s="18" t="s">
+      <c r="N99" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O99" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P99" s="2"/>
@@ -8235,7 +8447,7 @@
       <c r="G100" s="8">
         <v>1145</v>
       </c>
-      <c r="H100" s="20" t="s">
+      <c r="H100" s="22" t="s">
         <v>305</v>
       </c>
       <c r="I100" s="2">
@@ -8253,10 +8465,10 @@
       <c r="M100" s="2">
         <v>0</v>
       </c>
-      <c r="N100" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O100" s="18" t="s">
+      <c r="N100" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O100" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8276,7 +8488,7 @@
       <c r="G101" s="8">
         <v>1146</v>
       </c>
-      <c r="H101" s="20" t="s">
+      <c r="H101" s="22" t="s">
         <v>307</v>
       </c>
       <c r="I101" s="2">
@@ -8294,10 +8506,10 @@
       <c r="M101" s="2">
         <v>0</v>
       </c>
-      <c r="N101" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O101" s="18" t="s">
+      <c r="N101" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O101" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8317,7 +8529,7 @@
       <c r="G102" s="8">
         <v>1147</v>
       </c>
-      <c r="H102" s="20" t="s">
+      <c r="H102" s="22" t="s">
         <v>309</v>
       </c>
       <c r="I102" s="2">
@@ -8335,10 +8547,10 @@
       <c r="M102" s="2">
         <v>0</v>
       </c>
-      <c r="N102" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O102" s="18" t="s">
+      <c r="N102" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O102" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8358,7 +8570,7 @@
       <c r="G103" s="8">
         <v>1148</v>
       </c>
-      <c r="H103" s="20" t="s">
+      <c r="H103" s="22" t="s">
         <v>311</v>
       </c>
       <c r="I103" s="2">
@@ -8376,10 +8588,10 @@
       <c r="M103" s="2">
         <v>0</v>
       </c>
-      <c r="N103" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O103" s="18" t="s">
+      <c r="N103" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O103" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8399,7 +8611,7 @@
       <c r="G104" s="8">
         <v>1149</v>
       </c>
-      <c r="H104" s="20" t="s">
+      <c r="H104" s="22" t="s">
         <v>313</v>
       </c>
       <c r="I104" s="2">
@@ -8417,10 +8629,10 @@
       <c r="M104" s="2">
         <v>0</v>
       </c>
-      <c r="N104" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O104" s="18" t="s">
+      <c r="N104" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O104" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P104" s="2"/>
@@ -8441,7 +8653,7 @@
       <c r="G105" s="8">
         <v>1150</v>
       </c>
-      <c r="H105" s="20" t="s">
+      <c r="H105" s="22" t="s">
         <v>315</v>
       </c>
       <c r="I105" s="2">
@@ -8459,10 +8671,10 @@
       <c r="M105" s="2">
         <v>0</v>
       </c>
-      <c r="N105" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O105" s="18" t="s">
+      <c r="N105" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O105" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P105" s="2"/>
@@ -8483,7 +8695,7 @@
       <c r="G106" s="8">
         <v>1151</v>
       </c>
-      <c r="H106" s="20" t="s">
+      <c r="H106" s="22" t="s">
         <v>317</v>
       </c>
       <c r="I106" s="2">
@@ -8501,10 +8713,10 @@
       <c r="M106" s="2">
         <v>0</v>
       </c>
-      <c r="N106" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O106" s="18" t="s">
+      <c r="N106" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O106" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P106" s="2"/>
@@ -8525,7 +8737,7 @@
       <c r="G107" s="8">
         <v>1152</v>
       </c>
-      <c r="H107" s="20" t="s">
+      <c r="H107" s="22" t="s">
         <v>319</v>
       </c>
       <c r="I107" s="2">
@@ -8543,10 +8755,10 @@
       <c r="M107" s="2">
         <v>0</v>
       </c>
-      <c r="N107" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O107" s="18" t="s">
+      <c r="N107" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O107" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P107" s="2"/>
@@ -8567,7 +8779,7 @@
       <c r="G108" s="8">
         <v>1153</v>
       </c>
-      <c r="H108" s="20" t="s">
+      <c r="H108" s="22" t="s">
         <v>321</v>
       </c>
       <c r="I108" s="2">
@@ -8585,10 +8797,10 @@
       <c r="M108" s="2">
         <v>0</v>
       </c>
-      <c r="N108" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O108" s="18" t="s">
+      <c r="N108" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O108" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P108" s="2"/>
@@ -8609,7 +8821,7 @@
       <c r="G109" s="8">
         <v>1154</v>
       </c>
-      <c r="H109" s="20" t="s">
+      <c r="H109" s="22" t="s">
         <v>323</v>
       </c>
       <c r="I109" s="2">
@@ -8627,10 +8839,10 @@
       <c r="M109" s="2">
         <v>0</v>
       </c>
-      <c r="N109" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O109" s="18" t="s">
+      <c r="N109" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O109" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P109" s="2"/>
@@ -8651,7 +8863,7 @@
       <c r="G110" s="8">
         <v>1155</v>
       </c>
-      <c r="H110" s="20" t="s">
+      <c r="H110" s="22" t="s">
         <v>325</v>
       </c>
       <c r="I110" s="2">
@@ -8669,10 +8881,10 @@
       <c r="M110" s="2">
         <v>0</v>
       </c>
-      <c r="N110" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O110" s="18" t="s">
+      <c r="N110" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O110" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P110" s="2"/>
@@ -8693,7 +8905,7 @@
       <c r="G111" s="8">
         <v>1156</v>
       </c>
-      <c r="H111" s="20" t="s">
+      <c r="H111" s="22" t="s">
         <v>327</v>
       </c>
       <c r="I111" s="2">
@@ -8711,10 +8923,10 @@
       <c r="M111" s="2">
         <v>0</v>
       </c>
-      <c r="N111" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O111" s="18" t="s">
+      <c r="N111" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O111" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P111" s="2"/>
@@ -8735,7 +8947,7 @@
       <c r="G112" s="8">
         <v>1157</v>
       </c>
-      <c r="H112" s="20" t="s">
+      <c r="H112" s="22" t="s">
         <v>329</v>
       </c>
       <c r="I112" s="2">
@@ -8753,10 +8965,10 @@
       <c r="M112" s="2">
         <v>0</v>
       </c>
-      <c r="N112" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O112" s="18" t="s">
+      <c r="N112" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O112" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P112" s="2"/>
@@ -8777,7 +8989,7 @@
       <c r="G113" s="8">
         <v>1158</v>
       </c>
-      <c r="H113" s="20" t="s">
+      <c r="H113" s="22" t="s">
         <v>331</v>
       </c>
       <c r="I113" s="2">
@@ -8795,10 +9007,10 @@
       <c r="M113" s="2">
         <v>0</v>
       </c>
-      <c r="N113" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O113" s="18" t="s">
+      <c r="N113" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O113" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P113" s="2"/>
@@ -8819,7 +9031,7 @@
       <c r="G114" s="8">
         <v>1159</v>
       </c>
-      <c r="H114" s="20" t="s">
+      <c r="H114" s="22" t="s">
         <v>333</v>
       </c>
       <c r="I114" s="2">
@@ -8837,10 +9049,10 @@
       <c r="M114" s="2">
         <v>0</v>
       </c>
-      <c r="N114" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O114" s="18" t="s">
+      <c r="N114" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O114" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P114" s="2"/>
@@ -8861,7 +9073,7 @@
       <c r="G115" s="8">
         <v>1160</v>
       </c>
-      <c r="H115" s="20" t="s">
+      <c r="H115" s="22" t="s">
         <v>335</v>
       </c>
       <c r="I115" s="2">
@@ -8879,10 +9091,10 @@
       <c r="M115" s="2">
         <v>0</v>
       </c>
-      <c r="N115" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O115" s="18" t="s">
+      <c r="N115" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O115" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P115" s="2"/>
@@ -8903,7 +9115,7 @@
       <c r="G116" s="8">
         <v>1161</v>
       </c>
-      <c r="H116" s="20" t="s">
+      <c r="H116" s="22" t="s">
         <v>337</v>
       </c>
       <c r="I116" s="2">
@@ -8921,10 +9133,10 @@
       <c r="M116" s="2">
         <v>0</v>
       </c>
-      <c r="N116" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O116" s="18" t="s">
+      <c r="N116" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O116" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P116" s="2"/>
@@ -8945,7 +9157,7 @@
       <c r="G117" s="8">
         <v>1162</v>
       </c>
-      <c r="H117" s="20" t="s">
+      <c r="H117" s="22" t="s">
         <v>339</v>
       </c>
       <c r="I117" s="2">
@@ -8963,10 +9175,10 @@
       <c r="M117" s="2">
         <v>0</v>
       </c>
-      <c r="N117" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O117" s="18" t="s">
+      <c r="N117" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O117" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P117" s="2"/>
@@ -8987,7 +9199,7 @@
       <c r="G118" s="8">
         <v>1163</v>
       </c>
-      <c r="H118" s="20" t="s">
+      <c r="H118" s="22" t="s">
         <v>341</v>
       </c>
       <c r="I118" s="2">
@@ -9005,10 +9217,10 @@
       <c r="M118" s="2">
         <v>0</v>
       </c>
-      <c r="N118" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O118" s="18" t="s">
+      <c r="N118" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O118" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P118" s="2"/>
@@ -9029,7 +9241,7 @@
       <c r="G119" s="8">
         <v>1164</v>
       </c>
-      <c r="H119" s="20" t="s">
+      <c r="H119" s="22" t="s">
         <v>343</v>
       </c>
       <c r="I119" s="2">
@@ -9047,10 +9259,10 @@
       <c r="M119" s="2">
         <v>0</v>
       </c>
-      <c r="N119" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O119" s="18" t="s">
+      <c r="N119" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O119" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P119" s="2"/>
@@ -9071,7 +9283,7 @@
       <c r="G120" s="8">
         <v>1165</v>
       </c>
-      <c r="H120" s="20" t="s">
+      <c r="H120" s="22" t="s">
         <v>345</v>
       </c>
       <c r="I120" s="2">
@@ -9089,10 +9301,10 @@
       <c r="M120" s="2">
         <v>0</v>
       </c>
-      <c r="N120" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O120" s="18" t="s">
+      <c r="N120" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O120" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P120" s="2"/>
@@ -9113,7 +9325,7 @@
       <c r="G121" s="8">
         <v>1166</v>
       </c>
-      <c r="H121" s="20" t="s">
+      <c r="H121" s="22" t="s">
         <v>347</v>
       </c>
       <c r="I121" s="2">
@@ -9131,10 +9343,10 @@
       <c r="M121" s="2">
         <v>0</v>
       </c>
-      <c r="N121" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O121" s="18" t="s">
+      <c r="N121" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O121" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P121" s="2"/>
@@ -9155,7 +9367,7 @@
       <c r="G122" s="8">
         <v>1167</v>
       </c>
-      <c r="H122" s="20" t="s">
+      <c r="H122" s="22" t="s">
         <v>349</v>
       </c>
       <c r="I122" s="2">
@@ -9173,10 +9385,10 @@
       <c r="M122" s="2">
         <v>0</v>
       </c>
-      <c r="N122" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O122" s="18" t="s">
+      <c r="N122" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O122" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P122" s="2"/>
@@ -9197,7 +9409,7 @@
       <c r="G123" s="8">
         <v>1168</v>
       </c>
-      <c r="H123" s="20" t="s">
+      <c r="H123" s="22" t="s">
         <v>351</v>
       </c>
       <c r="I123" s="2">
@@ -9215,10 +9427,10 @@
       <c r="M123" s="2">
         <v>0</v>
       </c>
-      <c r="N123" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O123" s="18" t="s">
+      <c r="N123" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O123" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P123" s="2"/>
@@ -9239,7 +9451,7 @@
       <c r="G124" s="8">
         <v>1169</v>
       </c>
-      <c r="H124" s="20" t="s">
+      <c r="H124" s="22" t="s">
         <v>353</v>
       </c>
       <c r="I124" s="2">
@@ -9257,10 +9469,10 @@
       <c r="M124" s="2">
         <v>0</v>
       </c>
-      <c r="N124" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O124" s="18" t="s">
+      <c r="N124" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O124" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P124" s="2"/>
@@ -9281,7 +9493,7 @@
       <c r="G125" s="8">
         <v>1170</v>
       </c>
-      <c r="H125" s="20" t="s">
+      <c r="H125" s="22" t="s">
         <v>355</v>
       </c>
       <c r="I125" s="2">
@@ -9299,10 +9511,10 @@
       <c r="M125" s="2">
         <v>0</v>
       </c>
-      <c r="N125" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O125" s="18" t="s">
+      <c r="N125" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O125" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P125" s="2"/>
@@ -9323,7 +9535,7 @@
       <c r="G126" s="8">
         <v>1171</v>
       </c>
-      <c r="H126" s="20" t="s">
+      <c r="H126" s="22" t="s">
         <v>357</v>
       </c>
       <c r="I126" s="2">
@@ -9341,10 +9553,10 @@
       <c r="M126" s="2">
         <v>0</v>
       </c>
-      <c r="N126" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O126" s="18" t="s">
+      <c r="N126" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O126" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P126" s="2"/>
@@ -9365,7 +9577,7 @@
       <c r="G127" s="8">
         <v>1172</v>
       </c>
-      <c r="H127" s="20" t="s">
+      <c r="H127" s="22" t="s">
         <v>359</v>
       </c>
       <c r="I127" s="2">
@@ -9383,10 +9595,10 @@
       <c r="M127" s="2">
         <v>0</v>
       </c>
-      <c r="N127" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O127" s="18" t="s">
+      <c r="N127" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O127" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P127" s="2"/>
@@ -9407,7 +9619,7 @@
       <c r="G128" s="8">
         <v>1173</v>
       </c>
-      <c r="H128" s="20" t="s">
+      <c r="H128" s="22" t="s">
         <v>361</v>
       </c>
       <c r="I128" s="2">
@@ -9425,10 +9637,10 @@
       <c r="M128" s="2">
         <v>0</v>
       </c>
-      <c r="N128" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O128" s="18" t="s">
+      <c r="N128" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O128" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P128" s="2"/>
@@ -9449,7 +9661,7 @@
       <c r="G129" s="8">
         <v>1174</v>
       </c>
-      <c r="H129" s="20" t="s">
+      <c r="H129" s="22" t="s">
         <v>363</v>
       </c>
       <c r="I129" s="2">
@@ -9467,13 +9679,1448 @@
       <c r="M129" s="2">
         <v>0</v>
       </c>
-      <c r="N129" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O129" s="18" t="s">
+      <c r="N129" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O129" s="20" t="s">
         <v>34</v>
       </c>
       <c r="P129" s="2"/>
+    </row>
+    <row r="130" s="13" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C130" s="12">
+        <v>1124</v>
+      </c>
+      <c r="D130" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="E130" s="12">
+        <v>98</v>
+      </c>
+      <c r="F130" s="14">
+        <v>1175</v>
+      </c>
+      <c r="G130" s="14">
+        <v>1175</v>
+      </c>
+      <c r="H130" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="I130" s="12">
+        <v>60000</v>
+      </c>
+      <c r="J130" s="12">
+        <v>500000</v>
+      </c>
+      <c r="K130" s="12">
+        <v>0</v>
+      </c>
+      <c r="L130" s="12">
+        <v>0</v>
+      </c>
+      <c r="M130" s="12">
+        <v>0</v>
+      </c>
+      <c r="N130" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="O130" s="24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="3:15">
+      <c r="C131" s="2">
+        <v>1125</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E131" s="2">
+        <v>98</v>
+      </c>
+      <c r="F131" s="8">
+        <v>1176</v>
+      </c>
+      <c r="G131" s="8">
+        <v>1176</v>
+      </c>
+      <c r="H131" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="I131" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J131" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K131" s="2">
+        <v>0</v>
+      </c>
+      <c r="L131" s="2">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2">
+        <v>0</v>
+      </c>
+      <c r="N131" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O131" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="3:15">
+      <c r="C132" s="2">
+        <v>1126</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E132" s="2">
+        <v>98</v>
+      </c>
+      <c r="F132" s="8">
+        <v>1177</v>
+      </c>
+      <c r="G132" s="8">
+        <v>1177</v>
+      </c>
+      <c r="H132" s="22" t="s">
+        <v>369</v>
+      </c>
+      <c r="I132" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J132" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K132" s="2">
+        <v>0</v>
+      </c>
+      <c r="L132" s="2">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2">
+        <v>0</v>
+      </c>
+      <c r="N132" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O132" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="3:15">
+      <c r="C133" s="2">
+        <v>1127</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E133" s="2">
+        <v>98</v>
+      </c>
+      <c r="F133" s="8">
+        <v>1178</v>
+      </c>
+      <c r="G133" s="8">
+        <v>1178</v>
+      </c>
+      <c r="H133" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="I133" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J133" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K133" s="2">
+        <v>0</v>
+      </c>
+      <c r="L133" s="2">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2">
+        <v>0</v>
+      </c>
+      <c r="N133" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O133" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="3:15">
+      <c r="C134" s="2">
+        <v>1128</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E134" s="2">
+        <v>98</v>
+      </c>
+      <c r="F134" s="8">
+        <v>1179</v>
+      </c>
+      <c r="G134" s="8">
+        <v>1179</v>
+      </c>
+      <c r="H134" s="22" t="s">
+        <v>373</v>
+      </c>
+      <c r="I134" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J134" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K134" s="2">
+        <v>0</v>
+      </c>
+      <c r="L134" s="2">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2">
+        <v>0</v>
+      </c>
+      <c r="N134" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O134" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="3:15">
+      <c r="C135" s="2">
+        <v>1129</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E135" s="2">
+        <v>98</v>
+      </c>
+      <c r="F135" s="8">
+        <v>1180</v>
+      </c>
+      <c r="G135" s="8">
+        <v>1180</v>
+      </c>
+      <c r="H135" s="22" t="s">
+        <v>375</v>
+      </c>
+      <c r="I135" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J135" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K135" s="2">
+        <v>0</v>
+      </c>
+      <c r="L135" s="2">
+        <v>0</v>
+      </c>
+      <c r="M135" s="2">
+        <v>0</v>
+      </c>
+      <c r="N135" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O135" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" spans="3:15">
+      <c r="C136" s="2">
+        <v>1130</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E136" s="2">
+        <v>98</v>
+      </c>
+      <c r="F136" s="8">
+        <v>1181</v>
+      </c>
+      <c r="G136" s="8">
+        <v>1181</v>
+      </c>
+      <c r="H136" s="22" t="s">
+        <v>377</v>
+      </c>
+      <c r="I136" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J136" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K136" s="2">
+        <v>0</v>
+      </c>
+      <c r="L136" s="2">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2">
+        <v>0</v>
+      </c>
+      <c r="N136" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O136" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" spans="3:15">
+      <c r="C137" s="2">
+        <v>1131</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E137" s="2">
+        <v>98</v>
+      </c>
+      <c r="F137" s="8">
+        <v>1182</v>
+      </c>
+      <c r="G137" s="8">
+        <v>1182</v>
+      </c>
+      <c r="H137" s="22" t="s">
+        <v>379</v>
+      </c>
+      <c r="I137" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J137" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K137" s="2">
+        <v>0</v>
+      </c>
+      <c r="L137" s="2">
+        <v>0</v>
+      </c>
+      <c r="M137" s="2">
+        <v>0</v>
+      </c>
+      <c r="N137" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O137" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" spans="3:15">
+      <c r="C138" s="2">
+        <v>1132</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E138" s="2">
+        <v>98</v>
+      </c>
+      <c r="F138" s="8">
+        <v>1183</v>
+      </c>
+      <c r="G138" s="8">
+        <v>1183</v>
+      </c>
+      <c r="H138" s="22" t="s">
+        <v>381</v>
+      </c>
+      <c r="I138" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J138" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K138" s="2">
+        <v>0</v>
+      </c>
+      <c r="L138" s="2">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2">
+        <v>0</v>
+      </c>
+      <c r="N138" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O138" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" spans="3:15">
+      <c r="C139" s="2">
+        <v>1133</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E139" s="2">
+        <v>98</v>
+      </c>
+      <c r="F139" s="8">
+        <v>1184</v>
+      </c>
+      <c r="G139" s="8">
+        <v>1184</v>
+      </c>
+      <c r="H139" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="I139" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J139" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K139" s="2">
+        <v>0</v>
+      </c>
+      <c r="L139" s="2">
+        <v>0</v>
+      </c>
+      <c r="M139" s="2">
+        <v>0</v>
+      </c>
+      <c r="N139" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O139" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" spans="3:15">
+      <c r="C140" s="2">
+        <v>1134</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E140" s="2">
+        <v>98</v>
+      </c>
+      <c r="F140" s="8">
+        <v>1185</v>
+      </c>
+      <c r="G140" s="8">
+        <v>1185</v>
+      </c>
+      <c r="H140" s="22" t="s">
+        <v>385</v>
+      </c>
+      <c r="I140" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J140" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K140" s="2">
+        <v>0</v>
+      </c>
+      <c r="L140" s="2">
+        <v>0</v>
+      </c>
+      <c r="M140" s="2">
+        <v>0</v>
+      </c>
+      <c r="N140" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O140" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" spans="3:15">
+      <c r="C141" s="2">
+        <v>1135</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E141" s="2">
+        <v>98</v>
+      </c>
+      <c r="F141" s="8">
+        <v>1186</v>
+      </c>
+      <c r="G141" s="8">
+        <v>1186</v>
+      </c>
+      <c r="H141" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="I141" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J141" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K141" s="2">
+        <v>0</v>
+      </c>
+      <c r="L141" s="2">
+        <v>0</v>
+      </c>
+      <c r="M141" s="2">
+        <v>0</v>
+      </c>
+      <c r="N141" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O141" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" spans="3:15">
+      <c r="C142" s="2">
+        <v>1136</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E142" s="2">
+        <v>98</v>
+      </c>
+      <c r="F142" s="8">
+        <v>1187</v>
+      </c>
+      <c r="G142" s="8">
+        <v>1187</v>
+      </c>
+      <c r="H142" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="I142" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J142" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K142" s="2">
+        <v>0</v>
+      </c>
+      <c r="L142" s="2">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2">
+        <v>0</v>
+      </c>
+      <c r="N142" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O142" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" spans="3:15">
+      <c r="C143" s="2">
+        <v>1137</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E143" s="2">
+        <v>98</v>
+      </c>
+      <c r="F143" s="8">
+        <v>1188</v>
+      </c>
+      <c r="G143" s="8">
+        <v>1188</v>
+      </c>
+      <c r="H143" s="22" t="s">
+        <v>391</v>
+      </c>
+      <c r="I143" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J143" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K143" s="2">
+        <v>0</v>
+      </c>
+      <c r="L143" s="2">
+        <v>0</v>
+      </c>
+      <c r="M143" s="2">
+        <v>0</v>
+      </c>
+      <c r="N143" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O143" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" spans="3:15">
+      <c r="C144" s="2">
+        <v>1138</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E144" s="2">
+        <v>98</v>
+      </c>
+      <c r="F144" s="8">
+        <v>1189</v>
+      </c>
+      <c r="G144" s="8">
+        <v>1189</v>
+      </c>
+      <c r="H144" s="22" t="s">
+        <v>393</v>
+      </c>
+      <c r="I144" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J144" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K144" s="2">
+        <v>0</v>
+      </c>
+      <c r="L144" s="2">
+        <v>0</v>
+      </c>
+      <c r="M144" s="2">
+        <v>0</v>
+      </c>
+      <c r="N144" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O144" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" spans="3:15">
+      <c r="C145" s="2">
+        <v>1139</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E145" s="2">
+        <v>98</v>
+      </c>
+      <c r="F145" s="8">
+        <v>1190</v>
+      </c>
+      <c r="G145" s="8">
+        <v>1190</v>
+      </c>
+      <c r="H145" s="22" t="s">
+        <v>395</v>
+      </c>
+      <c r="I145" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J145" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K145" s="2">
+        <v>0</v>
+      </c>
+      <c r="L145" s="2">
+        <v>0</v>
+      </c>
+      <c r="M145" s="2">
+        <v>0</v>
+      </c>
+      <c r="N145" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O145" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" spans="3:15">
+      <c r="C146" s="2">
+        <v>1140</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E146" s="2">
+        <v>98</v>
+      </c>
+      <c r="F146" s="8">
+        <v>1191</v>
+      </c>
+      <c r="G146" s="8">
+        <v>1191</v>
+      </c>
+      <c r="H146" s="22" t="s">
+        <v>397</v>
+      </c>
+      <c r="I146" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J146" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K146" s="2">
+        <v>0</v>
+      </c>
+      <c r="L146" s="2">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2">
+        <v>0</v>
+      </c>
+      <c r="N146" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O146" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="3:15">
+      <c r="C147" s="2">
+        <v>1141</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E147" s="2">
+        <v>98</v>
+      </c>
+      <c r="F147" s="8">
+        <v>1192</v>
+      </c>
+      <c r="G147" s="8">
+        <v>1192</v>
+      </c>
+      <c r="H147" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="I147" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J147" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K147" s="2">
+        <v>0</v>
+      </c>
+      <c r="L147" s="2">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2">
+        <v>0</v>
+      </c>
+      <c r="N147" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O147" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" spans="3:15">
+      <c r="C148" s="2">
+        <v>1142</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E148" s="2">
+        <v>98</v>
+      </c>
+      <c r="F148" s="8">
+        <v>1193</v>
+      </c>
+      <c r="G148" s="8">
+        <v>1193</v>
+      </c>
+      <c r="H148" s="22" t="s">
+        <v>401</v>
+      </c>
+      <c r="I148" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J148" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K148" s="2">
+        <v>0</v>
+      </c>
+      <c r="L148" s="2">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2">
+        <v>0</v>
+      </c>
+      <c r="N148" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O148" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" spans="3:15">
+      <c r="C149" s="2">
+        <v>1143</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E149" s="2">
+        <v>98</v>
+      </c>
+      <c r="F149" s="8">
+        <v>1194</v>
+      </c>
+      <c r="G149" s="8">
+        <v>1194</v>
+      </c>
+      <c r="H149" s="22" t="s">
+        <v>403</v>
+      </c>
+      <c r="I149" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J149" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K149" s="2">
+        <v>0</v>
+      </c>
+      <c r="L149" s="2">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2">
+        <v>0</v>
+      </c>
+      <c r="N149" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O149" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" spans="3:15">
+      <c r="C150" s="2">
+        <v>1144</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E150" s="2">
+        <v>98</v>
+      </c>
+      <c r="F150" s="8">
+        <v>1195</v>
+      </c>
+      <c r="G150" s="8">
+        <v>1195</v>
+      </c>
+      <c r="H150" s="22" t="s">
+        <v>405</v>
+      </c>
+      <c r="I150" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J150" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K150" s="2">
+        <v>0</v>
+      </c>
+      <c r="L150" s="2">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2">
+        <v>0</v>
+      </c>
+      <c r="N150" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O150" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="151" customHeight="1" spans="3:15">
+      <c r="C151" s="2">
+        <v>1145</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E151" s="2">
+        <v>98</v>
+      </c>
+      <c r="F151" s="8">
+        <v>1196</v>
+      </c>
+      <c r="G151" s="8">
+        <v>1196</v>
+      </c>
+      <c r="H151" s="22" t="s">
+        <v>407</v>
+      </c>
+      <c r="I151" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J151" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K151" s="2">
+        <v>0</v>
+      </c>
+      <c r="L151" s="2">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2">
+        <v>0</v>
+      </c>
+      <c r="N151" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O151" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" spans="3:15">
+      <c r="C152" s="2">
+        <v>1146</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E152" s="2">
+        <v>98</v>
+      </c>
+      <c r="F152" s="8">
+        <v>1197</v>
+      </c>
+      <c r="G152" s="8">
+        <v>1197</v>
+      </c>
+      <c r="H152" s="22" t="s">
+        <v>409</v>
+      </c>
+      <c r="I152" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J152" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K152" s="2">
+        <v>0</v>
+      </c>
+      <c r="L152" s="2">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2">
+        <v>0</v>
+      </c>
+      <c r="N152" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O152" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" spans="3:15">
+      <c r="C153" s="2">
+        <v>1147</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E153" s="2">
+        <v>98</v>
+      </c>
+      <c r="F153" s="8">
+        <v>1198</v>
+      </c>
+      <c r="G153" s="8">
+        <v>1198</v>
+      </c>
+      <c r="H153" s="22" t="s">
+        <v>411</v>
+      </c>
+      <c r="I153" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J153" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K153" s="2">
+        <v>0</v>
+      </c>
+      <c r="L153" s="2">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2">
+        <v>0</v>
+      </c>
+      <c r="N153" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O153" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="3:15">
+      <c r="C154" s="2">
+        <v>1148</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E154" s="2">
+        <v>98</v>
+      </c>
+      <c r="F154" s="8">
+        <v>1199</v>
+      </c>
+      <c r="G154" s="8">
+        <v>1199</v>
+      </c>
+      <c r="H154" s="22" t="s">
+        <v>413</v>
+      </c>
+      <c r="I154" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J154" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K154" s="2">
+        <v>0</v>
+      </c>
+      <c r="L154" s="2">
+        <v>0</v>
+      </c>
+      <c r="M154" s="2">
+        <v>0</v>
+      </c>
+      <c r="N154" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O154" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" spans="3:15">
+      <c r="C155" s="2">
+        <v>1149</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E155" s="2">
+        <v>98</v>
+      </c>
+      <c r="F155" s="8">
+        <v>1200</v>
+      </c>
+      <c r="G155" s="8">
+        <v>1200</v>
+      </c>
+      <c r="H155" s="22" t="s">
+        <v>415</v>
+      </c>
+      <c r="I155" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J155" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K155" s="2">
+        <v>0</v>
+      </c>
+      <c r="L155" s="2">
+        <v>0</v>
+      </c>
+      <c r="M155" s="2">
+        <v>0</v>
+      </c>
+      <c r="N155" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O155" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" spans="3:15">
+      <c r="C156" s="2">
+        <v>1150</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E156" s="2">
+        <v>98</v>
+      </c>
+      <c r="F156" s="8">
+        <v>1201</v>
+      </c>
+      <c r="G156" s="8">
+        <v>1201</v>
+      </c>
+      <c r="H156" s="22" t="s">
+        <v>417</v>
+      </c>
+      <c r="I156" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J156" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K156" s="2">
+        <v>0</v>
+      </c>
+      <c r="L156" s="2">
+        <v>0</v>
+      </c>
+      <c r="M156" s="2">
+        <v>0</v>
+      </c>
+      <c r="N156" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O156" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" spans="3:15">
+      <c r="C157" s="2">
+        <v>1151</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E157" s="2">
+        <v>98</v>
+      </c>
+      <c r="F157" s="8">
+        <v>1202</v>
+      </c>
+      <c r="G157" s="8">
+        <v>1202</v>
+      </c>
+      <c r="H157" s="22" t="s">
+        <v>419</v>
+      </c>
+      <c r="I157" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J157" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K157" s="2">
+        <v>0</v>
+      </c>
+      <c r="L157" s="2">
+        <v>0</v>
+      </c>
+      <c r="M157" s="2">
+        <v>0</v>
+      </c>
+      <c r="N157" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O157" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="158" customHeight="1" spans="3:15">
+      <c r="C158" s="2">
+        <v>1152</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E158" s="2">
+        <v>98</v>
+      </c>
+      <c r="F158" s="8">
+        <v>1203</v>
+      </c>
+      <c r="G158" s="8">
+        <v>1203</v>
+      </c>
+      <c r="H158" s="22" t="s">
+        <v>421</v>
+      </c>
+      <c r="I158" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J158" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K158" s="2">
+        <v>0</v>
+      </c>
+      <c r="L158" s="2">
+        <v>0</v>
+      </c>
+      <c r="M158" s="2">
+        <v>0</v>
+      </c>
+      <c r="N158" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O158" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="159" customHeight="1" spans="3:15">
+      <c r="C159" s="2">
+        <v>1153</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E159" s="2">
+        <v>98</v>
+      </c>
+      <c r="F159" s="8">
+        <v>1204</v>
+      </c>
+      <c r="G159" s="8">
+        <v>1204</v>
+      </c>
+      <c r="H159" s="22" t="s">
+        <v>423</v>
+      </c>
+      <c r="I159" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J159" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K159" s="2">
+        <v>0</v>
+      </c>
+      <c r="L159" s="2">
+        <v>0</v>
+      </c>
+      <c r="M159" s="2">
+        <v>0</v>
+      </c>
+      <c r="N159" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O159" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" spans="3:15">
+      <c r="C160" s="2">
+        <v>1154</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E160" s="2">
+        <v>98</v>
+      </c>
+      <c r="F160" s="8">
+        <v>1205</v>
+      </c>
+      <c r="G160" s="8">
+        <v>1205</v>
+      </c>
+      <c r="H160" s="22" t="s">
+        <v>425</v>
+      </c>
+      <c r="I160" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J160" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K160" s="2">
+        <v>0</v>
+      </c>
+      <c r="L160" s="2">
+        <v>0</v>
+      </c>
+      <c r="M160" s="2">
+        <v>0</v>
+      </c>
+      <c r="N160" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O160" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" spans="3:15">
+      <c r="C161" s="2">
+        <v>1155</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E161" s="2">
+        <v>98</v>
+      </c>
+      <c r="F161" s="8">
+        <v>1206</v>
+      </c>
+      <c r="G161" s="8">
+        <v>1206</v>
+      </c>
+      <c r="H161" s="22" t="s">
+        <v>427</v>
+      </c>
+      <c r="I161" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J161" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K161" s="2">
+        <v>0</v>
+      </c>
+      <c r="L161" s="2">
+        <v>0</v>
+      </c>
+      <c r="M161" s="2">
+        <v>0</v>
+      </c>
+      <c r="N161" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O161" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" spans="3:15">
+      <c r="C162" s="2">
+        <v>1156</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E162" s="2">
+        <v>98</v>
+      </c>
+      <c r="F162" s="8">
+        <v>1207</v>
+      </c>
+      <c r="G162" s="8">
+        <v>1207</v>
+      </c>
+      <c r="H162" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="I162" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J162" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K162" s="2">
+        <v>0</v>
+      </c>
+      <c r="L162" s="2">
+        <v>0</v>
+      </c>
+      <c r="M162" s="2">
+        <v>0</v>
+      </c>
+      <c r="N162" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O162" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" spans="3:15">
+      <c r="C163" s="2">
+        <v>1157</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E163" s="2">
+        <v>98</v>
+      </c>
+      <c r="F163" s="8">
+        <v>1208</v>
+      </c>
+      <c r="G163" s="8">
+        <v>1208</v>
+      </c>
+      <c r="H163" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="I163" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J163" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K163" s="2">
+        <v>0</v>
+      </c>
+      <c r="L163" s="2">
+        <v>0</v>
+      </c>
+      <c r="M163" s="2">
+        <v>0</v>
+      </c>
+      <c r="N163" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O163" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" spans="3:15">
+      <c r="C164" s="2">
+        <v>1158</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E164" s="2">
+        <v>98</v>
+      </c>
+      <c r="F164" s="8">
+        <v>1209</v>
+      </c>
+      <c r="G164" s="8">
+        <v>1209</v>
+      </c>
+      <c r="H164" s="22" t="s">
+        <v>433</v>
+      </c>
+      <c r="I164" s="17">
+        <v>60000</v>
+      </c>
+      <c r="J164" s="17">
+        <v>500000</v>
+      </c>
+      <c r="K164" s="2">
+        <v>0</v>
+      </c>
+      <c r="L164" s="2">
+        <v>0</v>
+      </c>
+      <c r="M164" s="2">
+        <v>0</v>
+      </c>
+      <c r="N164" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O164" s="20" t="s">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -9665,7 +11312,7 @@
         <v>2000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>364</v>
+        <v>434</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -9676,8 +11323,8 @@
       <c r="G6" s="8">
         <v>1070</v>
       </c>
-      <c r="H6" s="20" t="s">
-        <v>365</v>
+      <c r="H6" s="22" t="s">
+        <v>435</v>
       </c>
       <c r="I6" s="2">
         <v>120000</v>
@@ -9697,10 +11344,10 @@
       <c r="N6" s="2">
         <v>0</v>
       </c>
-      <c r="O6" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P6" s="18" t="s">
+      <c r="O6" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P6" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9709,7 +11356,7 @@
         <v>2001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>366</v>
+        <v>436</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -9720,8 +11367,8 @@
       <c r="G7" s="8">
         <v>1071</v>
       </c>
-      <c r="H7" s="20" t="s">
-        <v>367</v>
+      <c r="H7" s="22" t="s">
+        <v>437</v>
       </c>
       <c r="I7" s="2">
         <v>120000</v>
@@ -9741,10 +11388,10 @@
       <c r="N7" s="2">
         <v>0</v>
       </c>
-      <c r="O7" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P7" s="18" t="s">
+      <c r="O7" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P7" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9753,7 +11400,7 @@
         <v>2002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>368</v>
+        <v>438</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -9764,8 +11411,8 @@
       <c r="G8" s="8">
         <v>1072</v>
       </c>
-      <c r="H8" s="20" t="s">
-        <v>369</v>
+      <c r="H8" s="22" t="s">
+        <v>439</v>
       </c>
       <c r="I8" s="2">
         <v>120000</v>
@@ -9785,10 +11432,10 @@
       <c r="N8" s="2">
         <v>0</v>
       </c>
-      <c r="O8" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P8" s="18" t="s">
+      <c r="O8" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P8" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9797,7 +11444,7 @@
         <v>2003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>370</v>
+        <v>440</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -9808,8 +11455,8 @@
       <c r="G9" s="8">
         <v>1073</v>
       </c>
-      <c r="H9" s="20" t="s">
-        <v>371</v>
+      <c r="H9" s="22" t="s">
+        <v>441</v>
       </c>
       <c r="I9" s="2">
         <v>120000</v>
@@ -9829,10 +11476,10 @@
       <c r="N9" s="2">
         <v>0</v>
       </c>
-      <c r="O9" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P9" s="18" t="s">
+      <c r="O9" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P9" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9841,7 +11488,7 @@
         <v>2004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>372</v>
+        <v>442</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -9852,8 +11499,8 @@
       <c r="G10" s="8">
         <v>1074</v>
       </c>
-      <c r="H10" s="20" t="s">
-        <v>373</v>
+      <c r="H10" s="22" t="s">
+        <v>443</v>
       </c>
       <c r="I10" s="2">
         <v>120000</v>
@@ -9873,10 +11520,10 @@
       <c r="N10" s="2">
         <v>0</v>
       </c>
-      <c r="O10" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P10" s="18" t="s">
+      <c r="O10" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P10" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9885,7 +11532,7 @@
         <v>2005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>372</v>
+        <v>442</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -9896,8 +11543,8 @@
       <c r="G11" s="2">
         <v>1104</v>
       </c>
-      <c r="H11" s="20" t="s">
-        <v>373</v>
+      <c r="H11" s="22" t="s">
+        <v>443</v>
       </c>
       <c r="I11" s="2">
         <v>20000</v>
@@ -9917,10 +11564,10 @@
       <c r="N11" s="2">
         <v>0</v>
       </c>
-      <c r="O11" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P11" s="18" t="s">
+      <c r="O11" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P11" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9943,7 +11590,7 @@
         <v>2006</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>374</v>
+        <v>444</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -9954,8 +11601,8 @@
       <c r="G14" s="2">
         <v>1105</v>
       </c>
-      <c r="H14" s="20" t="s">
-        <v>375</v>
+      <c r="H14" s="22" t="s">
+        <v>445</v>
       </c>
       <c r="I14" s="2">
         <v>360000</v>
@@ -9975,10 +11622,10 @@
       <c r="N14" s="2">
         <v>0</v>
       </c>
-      <c r="O14" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P14" s="18" t="s">
+      <c r="O14" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P14" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9987,7 +11634,7 @@
         <v>2007</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>376</v>
+        <v>446</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -9998,8 +11645,8 @@
       <c r="G15" s="2">
         <v>1106</v>
       </c>
-      <c r="H15" s="20" t="s">
-        <v>377</v>
+      <c r="H15" s="22" t="s">
+        <v>447</v>
       </c>
       <c r="I15" s="2">
         <v>360000</v>
@@ -10019,10 +11666,10 @@
       <c r="N15" s="2">
         <v>0</v>
       </c>
-      <c r="O15" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P15" s="18" t="s">
+      <c r="O15" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P15" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10031,7 +11678,7 @@
         <v>2008</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>378</v>
+        <v>448</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -10042,8 +11689,8 @@
       <c r="G16" s="2">
         <v>1107</v>
       </c>
-      <c r="H16" s="20" t="s">
-        <v>379</v>
+      <c r="H16" s="22" t="s">
+        <v>449</v>
       </c>
       <c r="I16" s="2">
         <v>360000</v>
@@ -10063,10 +11710,10 @@
       <c r="N16" s="2">
         <v>0</v>
       </c>
-      <c r="O16" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P16" s="18" t="s">
+      <c r="O16" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P16" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10075,7 +11722,7 @@
         <v>2009</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>380</v>
+        <v>450</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -10086,8 +11733,8 @@
       <c r="G17" s="2">
         <v>1108</v>
       </c>
-      <c r="H17" s="20" t="s">
-        <v>381</v>
+      <c r="H17" s="22" t="s">
+        <v>451</v>
       </c>
       <c r="I17" s="2">
         <v>360000</v>
@@ -10107,10 +11754,10 @@
       <c r="N17" s="2">
         <v>0</v>
       </c>
-      <c r="O17" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P17" s="18" t="s">
+      <c r="O17" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P17" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10119,7 +11766,7 @@
         <v>2010</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>382</v>
+        <v>452</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -10130,8 +11777,8 @@
       <c r="G18" s="2">
         <v>1139</v>
       </c>
-      <c r="H18" s="20" t="s">
-        <v>383</v>
+      <c r="H18" s="22" t="s">
+        <v>453</v>
       </c>
       <c r="I18" s="2">
         <v>360000</v>
@@ -10151,10 +11798,10 @@
       <c r="N18" s="2">
         <v>0</v>
       </c>
-      <c r="O18" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P18" s="18" t="s">
+      <c r="O18" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P18" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10163,7 +11810,7 @@
         <v>2011</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>372</v>
+        <v>442</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -10174,8 +11821,8 @@
       <c r="G19" s="2">
         <v>1139</v>
       </c>
-      <c r="H19" s="20" t="s">
-        <v>373</v>
+      <c r="H19" s="22" t="s">
+        <v>443</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -10195,10 +11842,10 @@
       <c r="N19" s="2">
         <v>0</v>
       </c>
-      <c r="O19" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P19" s="18" t="s">
+      <c r="O19" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P19" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10214,7 +11861,7 @@
         <v>2012</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>384</v>
+        <v>454</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -10225,8 +11872,8 @@
       <c r="G21" s="2">
         <v>1140</v>
       </c>
-      <c r="H21" s="20" t="s">
-        <v>385</v>
+      <c r="H21" s="22" t="s">
+        <v>455</v>
       </c>
       <c r="I21" s="2">
         <v>360000</v>
@@ -10246,10 +11893,10 @@
       <c r="N21" s="2">
         <v>0</v>
       </c>
-      <c r="O21" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P21" s="18" t="s">
+      <c r="O21" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P21" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10258,7 +11905,7 @@
         <v>2013</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>386</v>
+        <v>456</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -10269,8 +11916,8 @@
       <c r="G22" s="2">
         <v>1141</v>
       </c>
-      <c r="H22" s="20" t="s">
-        <v>387</v>
+      <c r="H22" s="22" t="s">
+        <v>457</v>
       </c>
       <c r="I22" s="2">
         <v>360000</v>
@@ -10290,10 +11937,10 @@
       <c r="N22" s="2">
         <v>0</v>
       </c>
-      <c r="O22" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P22" s="18" t="s">
+      <c r="O22" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P22" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10302,7 +11949,7 @@
         <v>2014</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>388</v>
+        <v>458</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -10313,8 +11960,8 @@
       <c r="G23" s="2">
         <v>1142</v>
       </c>
-      <c r="H23" s="20" t="s">
-        <v>389</v>
+      <c r="H23" s="22" t="s">
+        <v>459</v>
       </c>
       <c r="I23" s="2">
         <v>360000</v>
@@ -10334,10 +11981,10 @@
       <c r="N23" s="2">
         <v>0</v>
       </c>
-      <c r="O23" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P23" s="18" t="s">
+      <c r="O23" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P23" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10346,7 +11993,7 @@
         <v>2015</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>390</v>
+        <v>460</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -10357,8 +12004,8 @@
       <c r="G24" s="2">
         <v>1143</v>
       </c>
-      <c r="H24" s="20" t="s">
-        <v>391</v>
+      <c r="H24" s="22" t="s">
+        <v>461</v>
       </c>
       <c r="I24" s="2">
         <v>360000</v>
@@ -10378,10 +12025,10 @@
       <c r="N24" s="2">
         <v>0</v>
       </c>
-      <c r="O24" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P24" s="18" t="s">
+      <c r="O24" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P24" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10390,7 +12037,7 @@
         <v>2016</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>392</v>
+        <v>462</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -10401,8 +12048,8 @@
       <c r="G25" s="2">
         <v>1174</v>
       </c>
-      <c r="H25" s="20" t="s">
-        <v>393</v>
+      <c r="H25" s="22" t="s">
+        <v>463</v>
       </c>
       <c r="I25" s="2">
         <v>360000</v>
@@ -10422,10 +12069,10 @@
       <c r="N25" s="2">
         <v>0</v>
       </c>
-      <c r="O25" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P25" s="18" t="s">
+      <c r="O25" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P25" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -10434,7 +12081,7 @@
         <v>2017</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>382</v>
+        <v>452</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -10445,8 +12092,8 @@
       <c r="G26" s="2">
         <v>1174</v>
       </c>
-      <c r="H26" s="20" t="s">
-        <v>383</v>
+      <c r="H26" s="22" t="s">
+        <v>453</v>
       </c>
       <c r="I26" s="2">
         <v>180000</v>
@@ -10466,25 +12113,25 @@
       <c r="N26" s="2">
         <v>0</v>
       </c>
-      <c r="O26" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P26" s="18" t="s">
+      <c r="O26" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P26" s="20" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>394</v>
+        <v>464</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>394</v>
+        <v>464</v>
       </c>
       <c r="C27" s="2">
         <v>2018</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>372</v>
+        <v>442</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -10495,8 +12142,8 @@
       <c r="G27" s="2">
         <v>1174</v>
       </c>
-      <c r="H27" s="20" t="s">
-        <v>373</v>
+      <c r="H27" s="22" t="s">
+        <v>443</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>
@@ -10516,10 +12163,10 @@
       <c r="N27" s="2">
         <v>0</v>
       </c>
-      <c r="O27" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="P27" s="18" t="s">
+      <c r="O27" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P27" s="20" t="s">
         <v>34</v>
       </c>
     </row>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -12046,7 +12046,7 @@
         <v>1144</v>
       </c>
       <c r="G25" s="2">
-        <v>1174</v>
+        <v>1209</v>
       </c>
       <c r="H25" s="22" t="s">
         <v>463</v>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -361,7 +361,7 @@
     <t>2024-10-31</t>
   </si>
   <si>
-    <t>2025-10-21</t>
+    <t>2026-10-21</t>
   </si>
   <si>
     <t>第一批白图鉴</t>
@@ -6800,7 +6800,7 @@
       <c r="N60" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="O60" s="24" t="s">
+      <c r="O60" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -8262,7 +8262,7 @@
       <c r="N95" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="O95" s="24" t="s">
+      <c r="O95" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       <c r="N130" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="O130" s="24" t="s">
+      <c r="O130" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -12090,7 +12090,7 @@
         <v>1140</v>
       </c>
       <c r="G26" s="2">
-        <v>1174</v>
+        <v>1209</v>
       </c>
       <c r="H26" s="22" t="s">
         <v>453</v>
@@ -12305,43 +12305,43 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G11">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G26">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14:F18">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21:F25">
     <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G18">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G19">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G26">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G27">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14:F18">
+  <conditionalFormatting sqref="G14:G17">
     <cfRule type="duplicateValues" dxfId="0" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F25">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G14:G17">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G21:G25">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 C2:C5 F3:G5 F14:G19 F21:G27" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 F26 G26 F27:G27 C2:C5 F3:G5 F14:G19 F21:G25" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-07-04</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
+    <t>2025-08-07</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
   </si>
   <si>
     <t>平时部分掉落</t>
@@ -12341,7 +12341,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 F26 G26 F27:G27 C2:C5 F3:G5 F14:G19 F21:G25" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 F26:G26 F27:G27 C2:C5 F3:G5 F14:G19 F21:G25" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>快乐暑假</t>
+    <t>教师节</t>
   </si>
   <si>
     <t>1005</t>
@@ -12341,7 +12341,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 F26:G26 F27:G27 C2:C5 F3:G5 F14:G19 F21:G25" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 C2:C5 F3:G5 F14:G19 F21:G27" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-08-07</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>2025-09-11</t>
   </si>
   <si>
     <t>平时部分掉落</t>
@@ -1856,12 +1856,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -349,7 +349,7 @@
     <t>2025-09-07</t>
   </si>
   <si>
-    <t>2025-09-11</t>
+    <t>2025-09-12</t>
   </si>
   <si>
     <t>平时部分掉落</t>
@@ -1856,12 +1856,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="464">
   <si>
     <t>_id</t>
   </si>
@@ -349,7 +349,7 @@
     <t>2025-09-07</t>
   </si>
   <si>
-    <t>2025-09-12</t>
+    <t>2026-10-21</t>
   </si>
   <si>
     <t>平时部分掉落</t>
@@ -359,9 +359,6 @@
   </si>
   <si>
     <t>2024-10-31</t>
-  </si>
-  <si>
-    <t>2026-10-21</t>
   </si>
   <si>
     <t>第一批白图鉴</t>
@@ -2949,7 +2946,7 @@
         <v>33</v>
       </c>
       <c r="P7" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" customFormat="1" customHeight="1" spans="3:16">
@@ -2973,7 +2970,7 @@
         <v>101</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -2985,13 +2982,13 @@
         <v>2000</v>
       </c>
       <c r="H9" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="11">
+        <v>0</v>
+      </c>
+      <c r="J9" s="20" t="s">
         <v>36</v>
-      </c>
-      <c r="I9" s="11">
-        <v>0</v>
-      </c>
-      <c r="J9" s="20" t="s">
-        <v>37</v>
       </c>
       <c r="K9" s="11">
         <v>0</v>
@@ -3006,10 +3003,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P9" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3017,7 +3014,7 @@
         <v>102</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -3029,13 +3026,13 @@
         <v>2000</v>
       </c>
       <c r="H10" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="11">
+        <v>0</v>
+      </c>
+      <c r="J10" s="20" t="s">
         <v>40</v>
-      </c>
-      <c r="I10" s="11">
-        <v>0</v>
-      </c>
-      <c r="J10" s="20" t="s">
-        <v>41</v>
       </c>
       <c r="K10" s="11">
         <v>0</v>
@@ -3050,10 +3047,10 @@
         <v>0</v>
       </c>
       <c r="O10" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P10" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3061,7 +3058,7 @@
         <v>103</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -3073,13 +3070,13 @@
         <v>2000</v>
       </c>
       <c r="H11" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="11">
+        <v>0</v>
+      </c>
+      <c r="J11" s="20" t="s">
         <v>43</v>
-      </c>
-      <c r="I11" s="11">
-        <v>0</v>
-      </c>
-      <c r="J11" s="20" t="s">
-        <v>44</v>
       </c>
       <c r="K11" s="11">
         <v>0</v>
@@ -3094,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P11" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3105,7 +3102,7 @@
         <v>104</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
@@ -3117,13 +3114,13 @@
         <v>2000</v>
       </c>
       <c r="H12" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" s="11">
+        <v>0</v>
+      </c>
+      <c r="J12" s="20" t="s">
         <v>46</v>
-      </c>
-      <c r="I12" s="11">
-        <v>0</v>
-      </c>
-      <c r="J12" s="20" t="s">
-        <v>47</v>
       </c>
       <c r="K12" s="11">
         <v>0</v>
@@ -3138,10 +3135,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P12" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3149,7 +3146,7 @@
         <v>105</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
@@ -3161,13 +3158,13 @@
         <v>2000</v>
       </c>
       <c r="H13" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="11">
+        <v>0</v>
+      </c>
+      <c r="J13" s="20" t="s">
         <v>49</v>
-      </c>
-      <c r="I13" s="11">
-        <v>0</v>
-      </c>
-      <c r="J13" s="20" t="s">
-        <v>50</v>
       </c>
       <c r="K13" s="11">
         <v>0</v>
@@ -3182,10 +3179,10 @@
         <v>0</v>
       </c>
       <c r="O13" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P13" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3193,7 +3190,7 @@
         <v>106</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -3205,13 +3202,13 @@
         <v>2000</v>
       </c>
       <c r="H14" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" s="11">
+        <v>0</v>
+      </c>
+      <c r="J14" s="20" t="s">
         <v>52</v>
-      </c>
-      <c r="I14" s="11">
-        <v>0</v>
-      </c>
-      <c r="J14" s="20" t="s">
-        <v>53</v>
       </c>
       <c r="K14" s="11">
         <v>0</v>
@@ -3226,10 +3223,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P14" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3237,7 +3234,7 @@
         <v>107</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -3249,13 +3246,13 @@
         <v>2000</v>
       </c>
       <c r="H15" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15" s="11">
+        <v>0</v>
+      </c>
+      <c r="J15" s="20" t="s">
         <v>55</v>
-      </c>
-      <c r="I15" s="11">
-        <v>0</v>
-      </c>
-      <c r="J15" s="20" t="s">
-        <v>56</v>
       </c>
       <c r="K15" s="11">
         <v>0</v>
@@ -3270,10 +3267,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P15" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3281,7 +3278,7 @@
         <v>108</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -3293,13 +3290,13 @@
         <v>2000</v>
       </c>
       <c r="H16" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="I16" s="11">
+        <v>0</v>
+      </c>
+      <c r="J16" s="20" t="s">
         <v>58</v>
-      </c>
-      <c r="I16" s="11">
-        <v>0</v>
-      </c>
-      <c r="J16" s="20" t="s">
-        <v>59</v>
       </c>
       <c r="K16" s="11">
         <v>0</v>
@@ -3314,10 +3311,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P16" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3325,7 +3322,7 @@
         <v>109</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -3337,13 +3334,13 @@
         <v>2000</v>
       </c>
       <c r="H17" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" s="11">
+        <v>0</v>
+      </c>
+      <c r="J17" s="20" t="s">
         <v>61</v>
-      </c>
-      <c r="I17" s="11">
-        <v>0</v>
-      </c>
-      <c r="J17" s="20" t="s">
-        <v>62</v>
       </c>
       <c r="K17" s="11">
         <v>0</v>
@@ -3358,10 +3355,10 @@
         <v>0</v>
       </c>
       <c r="O17" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P17" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3369,7 +3366,7 @@
         <v>110</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -3381,13 +3378,13 @@
         <v>2000</v>
       </c>
       <c r="H18" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="I18" s="11">
+        <v>0</v>
+      </c>
+      <c r="J18" s="20" t="s">
         <v>64</v>
-      </c>
-      <c r="I18" s="11">
-        <v>0</v>
-      </c>
-      <c r="J18" s="20" t="s">
-        <v>65</v>
       </c>
       <c r="K18" s="11">
         <v>0</v>
@@ -3402,10 +3399,10 @@
         <v>0</v>
       </c>
       <c r="O18" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P18" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3413,7 +3410,7 @@
         <v>111</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -3425,13 +3422,13 @@
         <v>2000</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I19" s="11">
         <v>0</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K19" s="11">
         <v>0</v>
@@ -3446,10 +3443,10 @@
         <v>0</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P19" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3457,7 +3454,7 @@
         <v>112</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E20" s="2">
         <v>98</v>
@@ -3469,13 +3466,13 @@
         <v>2000</v>
       </c>
       <c r="H20" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="I20" s="11">
+        <v>0</v>
+      </c>
+      <c r="J20" s="20" t="s">
         <v>69</v>
-      </c>
-      <c r="I20" s="11">
-        <v>0</v>
-      </c>
-      <c r="J20" s="20" t="s">
-        <v>70</v>
       </c>
       <c r="K20" s="11">
         <v>0</v>
@@ -3490,10 +3487,10 @@
         <v>0</v>
       </c>
       <c r="O20" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P20" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1"/>
@@ -3502,7 +3499,7 @@
         <v>201</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E22" s="2">
         <v>100</v>
@@ -3514,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I22" s="11">
         <v>0</v>
@@ -3535,10 +3532,10 @@
         <v>1</v>
       </c>
       <c r="O22" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P22" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3546,7 +3543,7 @@
         <v>202</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E23" s="2">
         <v>100</v>
@@ -3558,7 +3555,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I23" s="11">
         <v>0</v>
@@ -3579,10 +3576,10 @@
         <v>1</v>
       </c>
       <c r="O23" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P23" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3590,7 +3587,7 @@
         <v>203</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E24" s="2">
         <v>100</v>
@@ -3602,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I24" s="11">
         <v>0</v>
@@ -3623,10 +3620,10 @@
         <v>1</v>
       </c>
       <c r="O24" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P24" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="8:16">
@@ -3645,7 +3642,7 @@
         <v>301</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -3657,13 +3654,13 @@
         <v>2000</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I26" s="2">
         <v>0</v>
       </c>
       <c r="J26" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K26" s="11">
         <v>0</v>
@@ -3678,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="O26" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P26" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3689,7 +3686,7 @@
         <v>302</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -3701,13 +3698,13 @@
         <v>2000</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I27" s="2">
         <v>0</v>
       </c>
       <c r="J27" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K27" s="11">
         <v>0</v>
@@ -3722,10 +3719,10 @@
         <v>0</v>
       </c>
       <c r="O27" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P27" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3733,7 +3730,7 @@
         <v>303</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E28" s="2">
         <v>98</v>
@@ -3745,13 +3742,13 @@
         <v>2000</v>
       </c>
       <c r="H28" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="I28" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="I28" s="21" t="s">
+      <c r="J28" s="20" t="s">
         <v>83</v>
-      </c>
-      <c r="J28" s="20" t="s">
-        <v>84</v>
       </c>
       <c r="K28" s="11">
         <v>0</v>
@@ -3766,10 +3763,10 @@
         <v>0</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P28" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3777,7 +3774,7 @@
         <v>304</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -3789,13 +3786,13 @@
         <v>2000</v>
       </c>
       <c r="H29" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I29" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="I29" s="21" t="s">
-        <v>87</v>
-      </c>
       <c r="J29" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K29" s="11">
         <v>0</v>
@@ -3810,10 +3807,10 @@
         <v>0</v>
       </c>
       <c r="O29" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P29" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1"/>
@@ -3822,7 +3819,7 @@
         <v>801</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E31" s="2">
         <v>98</v>
@@ -3834,13 +3831,13 @@
         <v>2000</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I31" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J31" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K31" s="11">
         <v>0</v>
@@ -3855,10 +3852,10 @@
         <v>0</v>
       </c>
       <c r="O31" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P31" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3866,7 +3863,7 @@
         <v>802</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E32" s="2">
         <v>98</v>
@@ -3878,13 +3875,13 @@
         <v>2000</v>
       </c>
       <c r="H32" s="21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I32" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J32" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K32" s="11">
         <v>0</v>
@@ -3899,10 +3896,10 @@
         <v>0</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P32" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3910,7 +3907,7 @@
         <v>803</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
@@ -3922,13 +3919,13 @@
         <v>2000</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I33" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J33" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K33" s="11">
         <v>0</v>
@@ -3943,10 +3940,10 @@
         <v>0</v>
       </c>
       <c r="O33" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P33" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="9:16">
@@ -3963,7 +3960,7 @@
         <v>804</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
@@ -3975,14 +3972,14 @@
         <v>2000</v>
       </c>
       <c r="H35" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="I35" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="J35" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="I35" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="J35" s="20" t="s">
-        <v>96</v>
-      </c>
       <c r="K35" s="11">
         <v>0</v>
       </c>
@@ -3996,10 +3993,10 @@
         <v>0</v>
       </c>
       <c r="O35" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P35" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4007,7 +4004,7 @@
         <v>805</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -4019,14 +4016,14 @@
         <v>2000</v>
       </c>
       <c r="H36" s="21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I36" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="J36" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="J36" s="20" t="s">
-        <v>100</v>
-      </c>
       <c r="K36" s="11">
         <v>0</v>
       </c>
@@ -4040,10 +4037,10 @@
         <v>0</v>
       </c>
       <c r="O36" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P36" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4051,7 +4048,7 @@
         <v>806</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -4063,14 +4060,14 @@
         <v>2000</v>
       </c>
       <c r="H37" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="I37" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="I37" s="21" t="s">
+      <c r="J37" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="J37" s="20" t="s">
-        <v>104</v>
-      </c>
       <c r="K37" s="11">
         <v>0</v>
       </c>
@@ -4084,10 +4081,10 @@
         <v>0</v>
       </c>
       <c r="O37" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P37" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4095,7 +4092,7 @@
         <v>807</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E38" s="2">
         <v>98</v>
@@ -4107,13 +4104,13 @@
         <v>2000</v>
       </c>
       <c r="H38" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="I38" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="I38" s="21" t="s">
+      <c r="J38" s="20" t="s">
         <v>107</v>
-      </c>
-      <c r="J38" s="20" t="s">
-        <v>108</v>
       </c>
       <c r="K38" s="11">
         <v>0</v>
@@ -4128,10 +4125,10 @@
         <v>0</v>
       </c>
       <c r="O38" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P38" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4139,7 +4136,7 @@
         <v>808</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E39" s="2">
         <v>98</v>
@@ -4151,13 +4148,13 @@
         <v>2000</v>
       </c>
       <c r="H39" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="I39" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="J39" s="20" t="s">
         <v>110</v>
-      </c>
-      <c r="I39" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="J39" s="20" t="s">
-        <v>111</v>
       </c>
       <c r="K39" s="11">
         <v>0</v>
@@ -4172,10 +4169,10 @@
         <v>0</v>
       </c>
       <c r="O39" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P39" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" customFormat="1" customHeight="1" spans="3:16">
@@ -4199,7 +4196,7 @@
         <v>991</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E41" s="2">
         <v>99</v>
@@ -4211,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I41" s="11">
         <v>0</v>
@@ -4232,10 +4229,10 @@
         <v>1</v>
       </c>
       <c r="O41" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P41" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4243,7 +4240,7 @@
         <v>992</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E42" s="2">
         <v>101</v>
@@ -4255,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I42" s="11">
         <v>0</v>
@@ -4276,10 +4273,10 @@
         <v>1</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P42" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1"/>
@@ -4527,7 +4524,7 @@
         <v>1000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -4539,7 +4536,7 @@
         <v>1051</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I6" s="2">
         <v>40000</v>
@@ -4557,10 +4554,10 @@
         <v>0</v>
       </c>
       <c r="N6" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O6" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4568,7 +4565,7 @@
         <v>1001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -4580,7 +4577,7 @@
         <v>1052</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I7" s="2">
         <v>40000</v>
@@ -4598,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="N7" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4609,7 +4606,7 @@
         <v>1002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -4621,7 +4618,7 @@
         <v>1053</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I8" s="2">
         <v>40000</v>
@@ -4639,10 +4636,10 @@
         <v>0</v>
       </c>
       <c r="N8" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O8" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4650,7 +4647,7 @@
         <v>1003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -4662,7 +4659,7 @@
         <v>1054</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I9" s="2">
         <v>40000</v>
@@ -4680,10 +4677,10 @@
         <v>0</v>
       </c>
       <c r="N9" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4691,7 +4688,7 @@
         <v>1004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -4703,7 +4700,7 @@
         <v>1055</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I10" s="2">
         <v>40000</v>
@@ -4721,10 +4718,10 @@
         <v>0</v>
       </c>
       <c r="N10" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O10" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4732,7 +4729,7 @@
         <v>1005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -4744,7 +4741,7 @@
         <v>1056</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I11" s="2">
         <v>40000</v>
@@ -4762,10 +4759,10 @@
         <v>0</v>
       </c>
       <c r="N11" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O11" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4773,7 +4770,7 @@
         <v>1006</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
@@ -4785,7 +4782,7 @@
         <v>1057</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I12" s="2">
         <v>40000</v>
@@ -4803,10 +4800,10 @@
         <v>0</v>
       </c>
       <c r="N12" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O12" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4814,7 +4811,7 @@
         <v>1007</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
@@ -4826,7 +4823,7 @@
         <v>1058</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I13" s="2">
         <v>40000</v>
@@ -4844,10 +4841,10 @@
         <v>0</v>
       </c>
       <c r="N13" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O13" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4855,7 +4852,7 @@
         <v>1008</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -4867,7 +4864,7 @@
         <v>1059</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I14" s="2">
         <v>40000</v>
@@ -4885,10 +4882,10 @@
         <v>0</v>
       </c>
       <c r="N14" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O14" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4896,7 +4893,7 @@
         <v>1009</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -4908,7 +4905,7 @@
         <v>1060</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I15" s="2">
         <v>40000</v>
@@ -4926,10 +4923,10 @@
         <v>0</v>
       </c>
       <c r="N15" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O15" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4937,7 +4934,7 @@
         <v>1010</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -4949,7 +4946,7 @@
         <v>1061</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I16" s="2">
         <v>40000</v>
@@ -4967,10 +4964,10 @@
         <v>0</v>
       </c>
       <c r="N16" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O16" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4978,7 +4975,7 @@
         <v>1011</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -4990,7 +4987,7 @@
         <v>1062</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I17" s="2">
         <v>40000</v>
@@ -5008,10 +5005,10 @@
         <v>0</v>
       </c>
       <c r="N17" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O17" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5019,7 +5016,7 @@
         <v>1012</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -5031,7 +5028,7 @@
         <v>1063</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I18" s="2">
         <v>40000</v>
@@ -5049,10 +5046,10 @@
         <v>0</v>
       </c>
       <c r="N18" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O18" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5060,7 +5057,7 @@
         <v>1013</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -5072,7 +5069,7 @@
         <v>1064</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -5090,10 +5087,10 @@
         <v>0</v>
       </c>
       <c r="N19" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5101,7 +5098,7 @@
         <v>1014</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E20" s="2">
         <v>98</v>
@@ -5113,7 +5110,7 @@
         <v>1065</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I20" s="2">
         <v>40000</v>
@@ -5131,10 +5128,10 @@
         <v>0</v>
       </c>
       <c r="N20" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O20" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5142,7 +5139,7 @@
         <v>1015</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -5154,7 +5151,7 @@
         <v>1066</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I21" s="2">
         <v>40000</v>
@@ -5172,10 +5169,10 @@
         <v>0</v>
       </c>
       <c r="N21" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O21" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5183,7 +5180,7 @@
         <v>1016</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -5195,7 +5192,7 @@
         <v>1067</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I22" s="2">
         <v>40000</v>
@@ -5213,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="N22" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O22" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5224,7 +5221,7 @@
         <v>1017</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -5236,7 +5233,7 @@
         <v>1068</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I23" s="2">
         <v>40000</v>
@@ -5254,10 +5251,10 @@
         <v>0</v>
       </c>
       <c r="N23" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O23" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5265,7 +5262,7 @@
         <v>1018</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -5277,7 +5274,7 @@
         <v>1069</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I24" s="2">
         <v>40000</v>
@@ -5295,10 +5292,10 @@
         <v>0</v>
       </c>
       <c r="N24" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O24" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5306,7 +5303,7 @@
         <v>1019</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -5318,7 +5315,7 @@
         <v>1070</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I25" s="2">
         <v>40000</v>
@@ -5336,10 +5333,10 @@
         <v>0</v>
       </c>
       <c r="N25" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O25" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5347,7 +5344,7 @@
         <v>1020</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -5359,7 +5356,7 @@
         <v>1071</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I26" s="2">
         <v>40000</v>
@@ -5377,10 +5374,10 @@
         <v>0</v>
       </c>
       <c r="N26" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O26" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5388,7 +5385,7 @@
         <v>1021</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -5400,7 +5397,7 @@
         <v>1072</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>
@@ -5418,10 +5415,10 @@
         <v>0</v>
       </c>
       <c r="N27" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O27" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5429,7 +5426,7 @@
         <v>1022</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E28" s="2">
         <v>98</v>
@@ -5441,7 +5438,7 @@
         <v>1073</v>
       </c>
       <c r="H28" s="22" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I28" s="2">
         <v>40000</v>
@@ -5459,10 +5456,10 @@
         <v>0</v>
       </c>
       <c r="N28" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:16">
@@ -5470,7 +5467,7 @@
         <v>1023</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -5482,7 +5479,7 @@
         <v>1074</v>
       </c>
       <c r="H29" s="22" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I29" s="2">
         <v>40000</v>
@@ -5500,10 +5497,10 @@
         <v>0</v>
       </c>
       <c r="N29" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O29" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P29" s="2"/>
     </row>
@@ -5512,7 +5509,7 @@
         <v>1024</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E30" s="2">
         <v>98</v>
@@ -5524,7 +5521,7 @@
         <v>1075</v>
       </c>
       <c r="H30" s="22" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I30" s="2">
         <v>4000</v>
@@ -5542,10 +5539,10 @@
         <v>0</v>
       </c>
       <c r="N30" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O30" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5553,7 +5550,7 @@
         <v>1025</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E31" s="2">
         <v>98</v>
@@ -5565,7 +5562,7 @@
         <v>1076</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I31" s="2">
         <v>4000</v>
@@ -5583,10 +5580,10 @@
         <v>0</v>
       </c>
       <c r="N31" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O31" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5594,7 +5591,7 @@
         <v>1026</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E32" s="2">
         <v>98</v>
@@ -5606,7 +5603,7 @@
         <v>1077</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I32" s="2">
         <v>4000</v>
@@ -5624,10 +5621,10 @@
         <v>0</v>
       </c>
       <c r="N32" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5635,7 +5632,7 @@
         <v>1027</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
@@ -5647,7 +5644,7 @@
         <v>1078</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I33" s="2">
         <v>4000</v>
@@ -5665,10 +5662,10 @@
         <v>0</v>
       </c>
       <c r="N33" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O33" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:16">
@@ -5676,7 +5673,7 @@
         <v>1028</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E34" s="2">
         <v>98</v>
@@ -5688,7 +5685,7 @@
         <v>1079</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I34" s="2">
         <v>4000</v>
@@ -5706,10 +5703,10 @@
         <v>0</v>
       </c>
       <c r="N34" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O34" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P34" s="2"/>
     </row>
@@ -5718,7 +5715,7 @@
         <v>1029</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
@@ -5730,7 +5727,7 @@
         <v>1080</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I35" s="2">
         <v>4000</v>
@@ -5748,10 +5745,10 @@
         <v>0</v>
       </c>
       <c r="N35" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O35" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P35" s="2"/>
     </row>
@@ -5760,7 +5757,7 @@
         <v>1030</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -5772,7 +5769,7 @@
         <v>1081</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I36" s="2">
         <v>4000</v>
@@ -5790,10 +5787,10 @@
         <v>0</v>
       </c>
       <c r="N36" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O36" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P36" s="2"/>
     </row>
@@ -5802,7 +5799,7 @@
         <v>1031</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -5814,7 +5811,7 @@
         <v>1082</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I37" s="2">
         <v>4000</v>
@@ -5832,10 +5829,10 @@
         <v>0</v>
       </c>
       <c r="N37" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O37" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P37" s="2"/>
     </row>
@@ -5844,7 +5841,7 @@
         <v>1032</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E38" s="2">
         <v>98</v>
@@ -5856,7 +5853,7 @@
         <v>1083</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I38" s="2">
         <v>4000</v>
@@ -5874,10 +5871,10 @@
         <v>0</v>
       </c>
       <c r="N38" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O38" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P38" s="2"/>
     </row>
@@ -5886,7 +5883,7 @@
         <v>1033</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E39" s="2">
         <v>98</v>
@@ -5898,7 +5895,7 @@
         <v>1084</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I39" s="2">
         <v>4000</v>
@@ -5916,10 +5913,10 @@
         <v>0</v>
       </c>
       <c r="N39" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O39" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P39" s="2"/>
     </row>
@@ -5928,7 +5925,7 @@
         <v>1034</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E40" s="2">
         <v>98</v>
@@ -5940,7 +5937,7 @@
         <v>1085</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I40" s="2">
         <v>4000</v>
@@ -5958,10 +5955,10 @@
         <v>0</v>
       </c>
       <c r="N40" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O40" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P40" s="2"/>
     </row>
@@ -5970,7 +5967,7 @@
         <v>1035</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E41" s="2">
         <v>98</v>
@@ -5982,7 +5979,7 @@
         <v>1086</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I41" s="2">
         <v>4000</v>
@@ -6000,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="N41" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O41" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P41" s="2"/>
     </row>
@@ -6012,7 +6009,7 @@
         <v>1036</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E42" s="2">
         <v>98</v>
@@ -6024,7 +6021,7 @@
         <v>1087</v>
       </c>
       <c r="H42" s="22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I42" s="2">
         <v>4000</v>
@@ -6042,10 +6039,10 @@
         <v>0</v>
       </c>
       <c r="N42" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P42" s="2"/>
     </row>
@@ -6054,7 +6051,7 @@
         <v>1037</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E43" s="2">
         <v>98</v>
@@ -6066,7 +6063,7 @@
         <v>1088</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I43" s="2">
         <v>4000</v>
@@ -6084,10 +6081,10 @@
         <v>0</v>
       </c>
       <c r="N43" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O43" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P43" s="2"/>
     </row>
@@ -6096,7 +6093,7 @@
         <v>1038</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E44" s="2">
         <v>98</v>
@@ -6108,7 +6105,7 @@
         <v>1089</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I44" s="2">
         <v>4000</v>
@@ -6126,10 +6123,10 @@
         <v>0</v>
       </c>
       <c r="N44" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O44" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P44" s="2"/>
     </row>
@@ -6138,7 +6135,7 @@
         <v>1039</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E45" s="2">
         <v>98</v>
@@ -6150,7 +6147,7 @@
         <v>1090</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I45" s="2">
         <v>4000</v>
@@ -6168,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="N45" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O45" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P45" s="2"/>
     </row>
@@ -6180,7 +6177,7 @@
         <v>1040</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E46" s="2">
         <v>98</v>
@@ -6192,7 +6189,7 @@
         <v>1091</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I46" s="2">
         <v>4000</v>
@@ -6210,10 +6207,10 @@
         <v>0</v>
       </c>
       <c r="N46" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O46" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P46" s="2"/>
     </row>
@@ -6222,7 +6219,7 @@
         <v>1041</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E47" s="2">
         <v>98</v>
@@ -6234,7 +6231,7 @@
         <v>1092</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I47" s="2">
         <v>4000</v>
@@ -6252,10 +6249,10 @@
         <v>0</v>
       </c>
       <c r="N47" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O47" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P47" s="2"/>
     </row>
@@ -6264,7 +6261,7 @@
         <v>1042</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E48" s="2">
         <v>98</v>
@@ -6276,7 +6273,7 @@
         <v>1093</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I48" s="2">
         <v>4000</v>
@@ -6294,10 +6291,10 @@
         <v>0</v>
       </c>
       <c r="N48" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O48" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P48" s="2"/>
     </row>
@@ -6306,7 +6303,7 @@
         <v>1043</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E49" s="2">
         <v>98</v>
@@ -6318,7 +6315,7 @@
         <v>1094</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I49" s="2">
         <v>4000</v>
@@ -6336,10 +6333,10 @@
         <v>0</v>
       </c>
       <c r="N49" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O49" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P49" s="2"/>
     </row>
@@ -6348,7 +6345,7 @@
         <v>1044</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E50" s="2">
         <v>98</v>
@@ -6360,7 +6357,7 @@
         <v>1095</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I50" s="2">
         <v>4000</v>
@@ -6378,10 +6375,10 @@
         <v>0</v>
       </c>
       <c r="N50" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O50" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P50" s="2"/>
     </row>
@@ -6390,7 +6387,7 @@
         <v>1045</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E51" s="2">
         <v>98</v>
@@ -6402,7 +6399,7 @@
         <v>1096</v>
       </c>
       <c r="H51" s="22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I51" s="2">
         <v>4000</v>
@@ -6420,10 +6417,10 @@
         <v>0</v>
       </c>
       <c r="N51" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O51" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P51" s="2"/>
     </row>
@@ -6432,7 +6429,7 @@
         <v>1046</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E52" s="2">
         <v>98</v>
@@ -6444,7 +6441,7 @@
         <v>1097</v>
       </c>
       <c r="H52" s="22" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I52" s="2">
         <v>4000</v>
@@ -6462,10 +6459,10 @@
         <v>0</v>
       </c>
       <c r="N52" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O52" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P52" s="2"/>
     </row>
@@ -6474,7 +6471,7 @@
         <v>1047</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E53" s="2">
         <v>98</v>
@@ -6486,7 +6483,7 @@
         <v>1098</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I53" s="2">
         <v>4000</v>
@@ -6504,10 +6501,10 @@
         <v>0</v>
       </c>
       <c r="N53" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O53" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P53" s="2"/>
     </row>
@@ -6516,7 +6513,7 @@
         <v>1048</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E54" s="2">
         <v>98</v>
@@ -6528,7 +6525,7 @@
         <v>1099</v>
       </c>
       <c r="H54" s="22" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I54" s="2">
         <v>4000</v>
@@ -6546,10 +6543,10 @@
         <v>0</v>
       </c>
       <c r="N54" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O54" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P54" s="2"/>
     </row>
@@ -6558,7 +6555,7 @@
         <v>1049</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E55" s="2">
         <v>98</v>
@@ -6570,7 +6567,7 @@
         <v>1100</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I55" s="2">
         <v>4000</v>
@@ -6588,10 +6585,10 @@
         <v>0</v>
       </c>
       <c r="N55" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O55" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P55" s="2"/>
     </row>
@@ -6600,7 +6597,7 @@
         <v>1050</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E56" s="2">
         <v>98</v>
@@ -6612,7 +6609,7 @@
         <v>1101</v>
       </c>
       <c r="H56" s="22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I56" s="2">
         <v>4000</v>
@@ -6630,10 +6627,10 @@
         <v>0</v>
       </c>
       <c r="N56" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O56" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P56" s="2"/>
     </row>
@@ -6642,7 +6639,7 @@
         <v>1051</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E57" s="2">
         <v>98</v>
@@ -6654,7 +6651,7 @@
         <v>1102</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I57" s="2">
         <v>4000</v>
@@ -6672,10 +6669,10 @@
         <v>0</v>
       </c>
       <c r="N57" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O57" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P57" s="2"/>
     </row>
@@ -6684,7 +6681,7 @@
         <v>1052</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E58" s="2">
         <v>98</v>
@@ -6696,7 +6693,7 @@
         <v>1103</v>
       </c>
       <c r="H58" s="22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I58" s="2">
         <v>4000</v>
@@ -6714,10 +6711,10 @@
         <v>0</v>
       </c>
       <c r="N58" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O58" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P58" s="2"/>
     </row>
@@ -6726,7 +6723,7 @@
         <v>1053</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E59" s="2">
         <v>98</v>
@@ -6738,7 +6735,7 @@
         <v>1104</v>
       </c>
       <c r="H59" s="22" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I59" s="2">
         <v>4000</v>
@@ -6756,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="N59" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O59" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P59" s="2"/>
     </row>
@@ -6768,7 +6765,7 @@
         <v>1054</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E60" s="12">
         <v>98</v>
@@ -6780,7 +6777,7 @@
         <v>1105</v>
       </c>
       <c r="H60" s="23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I60" s="12">
         <v>20000</v>
@@ -6798,10 +6795,10 @@
         <v>0</v>
       </c>
       <c r="N60" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O60" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6809,7 +6806,7 @@
         <v>1055</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E61" s="2">
         <v>98</v>
@@ -6821,7 +6818,7 @@
         <v>1106</v>
       </c>
       <c r="H61" s="22" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I61" s="2">
         <v>20000</v>
@@ -6839,10 +6836,10 @@
         <v>0</v>
       </c>
       <c r="N61" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O61" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6850,7 +6847,7 @@
         <v>1056</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E62" s="2">
         <v>98</v>
@@ -6862,7 +6859,7 @@
         <v>1107</v>
       </c>
       <c r="H62" s="22" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I62" s="2">
         <v>20000</v>
@@ -6880,10 +6877,10 @@
         <v>0</v>
       </c>
       <c r="N62" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O62" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6891,7 +6888,7 @@
         <v>1057</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E63" s="2">
         <v>98</v>
@@ -6903,7 +6900,7 @@
         <v>1108</v>
       </c>
       <c r="H63" s="22" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I63" s="2">
         <v>20000</v>
@@ -6921,10 +6918,10 @@
         <v>0</v>
       </c>
       <c r="N63" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O63" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:16">
@@ -6932,7 +6929,7 @@
         <v>1058</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E64" s="2">
         <v>98</v>
@@ -6944,7 +6941,7 @@
         <v>1109</v>
       </c>
       <c r="H64" s="22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I64" s="2">
         <v>20000</v>
@@ -6962,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="N64" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O64" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P64" s="2"/>
     </row>
@@ -6974,7 +6971,7 @@
         <v>1059</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E65" s="2">
         <v>98</v>
@@ -6986,7 +6983,7 @@
         <v>1110</v>
       </c>
       <c r="H65" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I65" s="2">
         <v>20000</v>
@@ -7004,10 +7001,10 @@
         <v>0</v>
       </c>
       <c r="N65" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O65" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -7015,7 +7012,7 @@
         <v>1060</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E66" s="2">
         <v>98</v>
@@ -7027,7 +7024,7 @@
         <v>1111</v>
       </c>
       <c r="H66" s="22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I66" s="2">
         <v>20000</v>
@@ -7045,10 +7042,10 @@
         <v>0</v>
       </c>
       <c r="N66" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O66" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -7056,7 +7053,7 @@
         <v>1061</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E67" s="2">
         <v>98</v>
@@ -7068,7 +7065,7 @@
         <v>1112</v>
       </c>
       <c r="H67" s="22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I67" s="2">
         <v>20000</v>
@@ -7086,10 +7083,10 @@
         <v>0</v>
       </c>
       <c r="N67" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O67" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -7097,7 +7094,7 @@
         <v>1062</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E68" s="2">
         <v>98</v>
@@ -7109,7 +7106,7 @@
         <v>1113</v>
       </c>
       <c r="H68" s="22" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I68" s="2">
         <v>20000</v>
@@ -7127,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="N68" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O68" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:16">
@@ -7138,7 +7135,7 @@
         <v>1063</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E69" s="2">
         <v>98</v>
@@ -7150,7 +7147,7 @@
         <v>1114</v>
       </c>
       <c r="H69" s="22" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I69" s="2">
         <v>20000</v>
@@ -7168,10 +7165,10 @@
         <v>0</v>
       </c>
       <c r="N69" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O69" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P69" s="2"/>
     </row>
@@ -7180,7 +7177,7 @@
         <v>1064</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E70" s="2">
         <v>98</v>
@@ -7192,7 +7189,7 @@
         <v>1115</v>
       </c>
       <c r="H70" s="22" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I70" s="2">
         <v>20000</v>
@@ -7210,10 +7207,10 @@
         <v>0</v>
       </c>
       <c r="N70" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O70" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P70" s="2"/>
     </row>
@@ -7222,7 +7219,7 @@
         <v>1065</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E71" s="2">
         <v>98</v>
@@ -7234,7 +7231,7 @@
         <v>1116</v>
       </c>
       <c r="H71" s="22" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I71" s="2">
         <v>20000</v>
@@ -7252,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="N71" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O71" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P71" s="2"/>
     </row>
@@ -7264,7 +7261,7 @@
         <v>1066</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E72" s="2">
         <v>98</v>
@@ -7276,7 +7273,7 @@
         <v>1117</v>
       </c>
       <c r="H72" s="22" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I72" s="2">
         <v>20000</v>
@@ -7294,10 +7291,10 @@
         <v>0</v>
       </c>
       <c r="N72" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O72" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P72" s="2"/>
     </row>
@@ -7306,7 +7303,7 @@
         <v>1067</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E73" s="2">
         <v>98</v>
@@ -7318,7 +7315,7 @@
         <v>1118</v>
       </c>
       <c r="H73" s="22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I73" s="2">
         <v>20000</v>
@@ -7336,10 +7333,10 @@
         <v>0</v>
       </c>
       <c r="N73" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O73" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P73" s="2"/>
     </row>
@@ -7348,7 +7345,7 @@
         <v>1068</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E74" s="2">
         <v>98</v>
@@ -7360,7 +7357,7 @@
         <v>1119</v>
       </c>
       <c r="H74" s="22" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I74" s="2">
         <v>20000</v>
@@ -7378,10 +7375,10 @@
         <v>0</v>
       </c>
       <c r="N74" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O74" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P74" s="2"/>
     </row>
@@ -7390,7 +7387,7 @@
         <v>1069</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E75" s="2">
         <v>98</v>
@@ -7402,7 +7399,7 @@
         <v>1120</v>
       </c>
       <c r="H75" s="22" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I75" s="2">
         <v>20000</v>
@@ -7420,10 +7417,10 @@
         <v>0</v>
       </c>
       <c r="N75" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O75" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P75" s="2"/>
     </row>
@@ -7432,7 +7429,7 @@
         <v>1070</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E76" s="2">
         <v>98</v>
@@ -7444,7 +7441,7 @@
         <v>1121</v>
       </c>
       <c r="H76" s="22" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I76" s="2">
         <v>20000</v>
@@ -7462,10 +7459,10 @@
         <v>0</v>
       </c>
       <c r="N76" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O76" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P76" s="2"/>
     </row>
@@ -7474,7 +7471,7 @@
         <v>1071</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E77" s="2">
         <v>98</v>
@@ -7486,7 +7483,7 @@
         <v>1122</v>
       </c>
       <c r="H77" s="22" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I77" s="2">
         <v>20000</v>
@@ -7504,10 +7501,10 @@
         <v>0</v>
       </c>
       <c r="N77" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O77" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P77" s="2"/>
     </row>
@@ -7516,7 +7513,7 @@
         <v>1072</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E78" s="2">
         <v>98</v>
@@ -7528,7 +7525,7 @@
         <v>1123</v>
       </c>
       <c r="H78" s="22" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I78" s="2">
         <v>20000</v>
@@ -7546,10 +7543,10 @@
         <v>0</v>
       </c>
       <c r="N78" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O78" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P78" s="2"/>
     </row>
@@ -7558,7 +7555,7 @@
         <v>1073</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E79" s="2">
         <v>98</v>
@@ -7570,7 +7567,7 @@
         <v>1124</v>
       </c>
       <c r="H79" s="22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I79" s="2">
         <v>20000</v>
@@ -7588,10 +7585,10 @@
         <v>0</v>
       </c>
       <c r="N79" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O79" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P79" s="2"/>
     </row>
@@ -7600,7 +7597,7 @@
         <v>1074</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E80" s="2">
         <v>98</v>
@@ -7612,7 +7609,7 @@
         <v>1125</v>
       </c>
       <c r="H80" s="22" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I80" s="2">
         <v>20000</v>
@@ -7630,10 +7627,10 @@
         <v>0</v>
       </c>
       <c r="N80" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O80" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P80" s="2"/>
     </row>
@@ -7642,7 +7639,7 @@
         <v>1075</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E81" s="2">
         <v>98</v>
@@ -7654,7 +7651,7 @@
         <v>1126</v>
       </c>
       <c r="H81" s="22" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I81" s="2">
         <v>20000</v>
@@ -7672,10 +7669,10 @@
         <v>0</v>
       </c>
       <c r="N81" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O81" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P81" s="2"/>
     </row>
@@ -7684,7 +7681,7 @@
         <v>1076</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E82" s="2">
         <v>98</v>
@@ -7696,7 +7693,7 @@
         <v>1127</v>
       </c>
       <c r="H82" s="22" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I82" s="2">
         <v>20000</v>
@@ -7714,10 +7711,10 @@
         <v>0</v>
       </c>
       <c r="N82" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O82" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P82" s="2"/>
     </row>
@@ -7726,7 +7723,7 @@
         <v>1077</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E83" s="2">
         <v>98</v>
@@ -7738,7 +7735,7 @@
         <v>1128</v>
       </c>
       <c r="H83" s="22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I83" s="2">
         <v>20000</v>
@@ -7756,10 +7753,10 @@
         <v>0</v>
       </c>
       <c r="N83" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O83" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P83" s="2"/>
     </row>
@@ -7768,7 +7765,7 @@
         <v>1078</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E84" s="2">
         <v>98</v>
@@ -7780,7 +7777,7 @@
         <v>1129</v>
       </c>
       <c r="H84" s="22" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I84" s="2">
         <v>20000</v>
@@ -7798,10 +7795,10 @@
         <v>0</v>
       </c>
       <c r="N84" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O84" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P84" s="2"/>
     </row>
@@ -7810,7 +7807,7 @@
         <v>1079</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E85" s="2">
         <v>98</v>
@@ -7822,7 +7819,7 @@
         <v>1130</v>
       </c>
       <c r="H85" s="22" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I85" s="2">
         <v>20000</v>
@@ -7840,10 +7837,10 @@
         <v>0</v>
       </c>
       <c r="N85" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O85" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P85" s="2"/>
     </row>
@@ -7852,7 +7849,7 @@
         <v>1080</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E86" s="2">
         <v>98</v>
@@ -7864,7 +7861,7 @@
         <v>1131</v>
       </c>
       <c r="H86" s="22" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I86" s="2">
         <v>20000</v>
@@ -7882,10 +7879,10 @@
         <v>0</v>
       </c>
       <c r="N86" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O86" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P86" s="2"/>
     </row>
@@ -7894,7 +7891,7 @@
         <v>1081</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E87" s="2">
         <v>98</v>
@@ -7906,7 +7903,7 @@
         <v>1132</v>
       </c>
       <c r="H87" s="22" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I87" s="2">
         <v>20000</v>
@@ -7924,10 +7921,10 @@
         <v>0</v>
       </c>
       <c r="N87" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O87" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P87" s="2"/>
     </row>
@@ -7936,7 +7933,7 @@
         <v>1082</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E88" s="2">
         <v>98</v>
@@ -7948,7 +7945,7 @@
         <v>1133</v>
       </c>
       <c r="H88" s="22" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I88" s="2">
         <v>20000</v>
@@ -7966,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="N88" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O88" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P88" s="2"/>
     </row>
@@ -7978,7 +7975,7 @@
         <v>1083</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E89" s="2">
         <v>98</v>
@@ -7990,7 +7987,7 @@
         <v>1134</v>
       </c>
       <c r="H89" s="22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I89" s="2">
         <v>20000</v>
@@ -8008,10 +8005,10 @@
         <v>0</v>
       </c>
       <c r="N89" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O89" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P89" s="2"/>
     </row>
@@ -8020,7 +8017,7 @@
         <v>1084</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E90" s="2">
         <v>98</v>
@@ -8032,7 +8029,7 @@
         <v>1135</v>
       </c>
       <c r="H90" s="22" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I90" s="2">
         <v>20000</v>
@@ -8050,10 +8047,10 @@
         <v>0</v>
       </c>
       <c r="N90" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O90" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P90" s="2"/>
     </row>
@@ -8062,7 +8059,7 @@
         <v>1085</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E91" s="2">
         <v>98</v>
@@ -8074,7 +8071,7 @@
         <v>1136</v>
       </c>
       <c r="H91" s="22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I91" s="2">
         <v>20000</v>
@@ -8092,10 +8089,10 @@
         <v>0</v>
       </c>
       <c r="N91" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O91" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P91" s="2"/>
     </row>
@@ -8104,7 +8101,7 @@
         <v>1086</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E92" s="2">
         <v>98</v>
@@ -8116,7 +8113,7 @@
         <v>1137</v>
       </c>
       <c r="H92" s="22" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I92" s="2">
         <v>20000</v>
@@ -8134,10 +8131,10 @@
         <v>0</v>
       </c>
       <c r="N92" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O92" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P92" s="2"/>
     </row>
@@ -8146,7 +8143,7 @@
         <v>1087</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E93" s="2">
         <v>98</v>
@@ -8158,7 +8155,7 @@
         <v>1138</v>
       </c>
       <c r="H93" s="22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I93" s="2">
         <v>20000</v>
@@ -8176,10 +8173,10 @@
         <v>0</v>
       </c>
       <c r="N93" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O93" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P93" s="2"/>
     </row>
@@ -8188,7 +8185,7 @@
         <v>1088</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E94" s="2">
         <v>98</v>
@@ -8200,7 +8197,7 @@
         <v>1139</v>
       </c>
       <c r="H94" s="22" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I94" s="2">
         <v>20000</v>
@@ -8218,10 +8215,10 @@
         <v>0</v>
       </c>
       <c r="N94" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O94" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P94" s="2"/>
     </row>
@@ -8230,7 +8227,7 @@
         <v>1089</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E95" s="12">
         <v>98</v>
@@ -8242,7 +8239,7 @@
         <v>1140</v>
       </c>
       <c r="H95" s="23" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I95" s="12">
         <v>30000</v>
@@ -8260,10 +8257,10 @@
         <v>0</v>
       </c>
       <c r="N95" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O95" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="96" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8271,7 +8268,7 @@
         <v>1090</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E96" s="2">
         <v>98</v>
@@ -8283,7 +8280,7 @@
         <v>1141</v>
       </c>
       <c r="H96" s="22" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I96" s="2">
         <v>30000</v>
@@ -8301,10 +8298,10 @@
         <v>0</v>
       </c>
       <c r="N96" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O96" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="97" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8312,7 +8309,7 @@
         <v>1091</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E97" s="2">
         <v>98</v>
@@ -8324,7 +8321,7 @@
         <v>1142</v>
       </c>
       <c r="H97" s="22" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I97" s="2">
         <v>30000</v>
@@ -8342,10 +8339,10 @@
         <v>0</v>
       </c>
       <c r="N97" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O97" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="98" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8353,7 +8350,7 @@
         <v>1092</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E98" s="2">
         <v>98</v>
@@ -8365,7 +8362,7 @@
         <v>1143</v>
       </c>
       <c r="H98" s="22" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I98" s="2">
         <v>30000</v>
@@ -8383,10 +8380,10 @@
         <v>0</v>
       </c>
       <c r="N98" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O98" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:16">
@@ -8394,7 +8391,7 @@
         <v>1093</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E99" s="2">
         <v>98</v>
@@ -8406,7 +8403,7 @@
         <v>1144</v>
       </c>
       <c r="H99" s="22" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I99" s="2">
         <v>30000</v>
@@ -8424,10 +8421,10 @@
         <v>0</v>
       </c>
       <c r="N99" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O99" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P99" s="2"/>
     </row>
@@ -8436,7 +8433,7 @@
         <v>1094</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E100" s="2">
         <v>98</v>
@@ -8448,7 +8445,7 @@
         <v>1145</v>
       </c>
       <c r="H100" s="22" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I100" s="2">
         <v>30000</v>
@@ -8466,10 +8463,10 @@
         <v>0</v>
       </c>
       <c r="N100" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O100" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="101" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8477,7 +8474,7 @@
         <v>1095</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E101" s="2">
         <v>98</v>
@@ -8489,7 +8486,7 @@
         <v>1146</v>
       </c>
       <c r="H101" s="22" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I101" s="2">
         <v>30000</v>
@@ -8507,10 +8504,10 @@
         <v>0</v>
       </c>
       <c r="N101" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O101" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8518,7 +8515,7 @@
         <v>1096</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E102" s="2">
         <v>98</v>
@@ -8530,7 +8527,7 @@
         <v>1147</v>
       </c>
       <c r="H102" s="22" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I102" s="2">
         <v>30000</v>
@@ -8548,10 +8545,10 @@
         <v>0</v>
       </c>
       <c r="N102" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O102" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8559,7 +8556,7 @@
         <v>1097</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E103" s="2">
         <v>98</v>
@@ -8571,7 +8568,7 @@
         <v>1148</v>
       </c>
       <c r="H103" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I103" s="2">
         <v>30000</v>
@@ -8589,10 +8586,10 @@
         <v>0</v>
       </c>
       <c r="N103" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O103" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:16">
@@ -8600,7 +8597,7 @@
         <v>1098</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E104" s="2">
         <v>98</v>
@@ -8612,7 +8609,7 @@
         <v>1149</v>
       </c>
       <c r="H104" s="22" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I104" s="2">
         <v>30000</v>
@@ -8630,10 +8627,10 @@
         <v>0</v>
       </c>
       <c r="N104" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O104" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P104" s="2"/>
     </row>
@@ -8642,7 +8639,7 @@
         <v>1099</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E105" s="2">
         <v>98</v>
@@ -8654,7 +8651,7 @@
         <v>1150</v>
       </c>
       <c r="H105" s="22" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I105" s="2">
         <v>30000</v>
@@ -8672,10 +8669,10 @@
         <v>0</v>
       </c>
       <c r="N105" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O105" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P105" s="2"/>
     </row>
@@ -8684,7 +8681,7 @@
         <v>1100</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E106" s="2">
         <v>98</v>
@@ -8696,7 +8693,7 @@
         <v>1151</v>
       </c>
       <c r="H106" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I106" s="2">
         <v>30000</v>
@@ -8714,10 +8711,10 @@
         <v>0</v>
       </c>
       <c r="N106" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O106" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P106" s="2"/>
     </row>
@@ -8726,7 +8723,7 @@
         <v>1101</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E107" s="2">
         <v>98</v>
@@ -8738,7 +8735,7 @@
         <v>1152</v>
       </c>
       <c r="H107" s="22" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I107" s="2">
         <v>30000</v>
@@ -8756,10 +8753,10 @@
         <v>0</v>
       </c>
       <c r="N107" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O107" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P107" s="2"/>
     </row>
@@ -8768,7 +8765,7 @@
         <v>1102</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E108" s="2">
         <v>98</v>
@@ -8780,7 +8777,7 @@
         <v>1153</v>
       </c>
       <c r="H108" s="22" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I108" s="2">
         <v>30000</v>
@@ -8798,10 +8795,10 @@
         <v>0</v>
       </c>
       <c r="N108" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O108" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P108" s="2"/>
     </row>
@@ -8810,7 +8807,7 @@
         <v>1103</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E109" s="2">
         <v>98</v>
@@ -8822,7 +8819,7 @@
         <v>1154</v>
       </c>
       <c r="H109" s="22" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I109" s="2">
         <v>30000</v>
@@ -8840,10 +8837,10 @@
         <v>0</v>
       </c>
       <c r="N109" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O109" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P109" s="2"/>
     </row>
@@ -8852,7 +8849,7 @@
         <v>1104</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E110" s="2">
         <v>98</v>
@@ -8864,7 +8861,7 @@
         <v>1155</v>
       </c>
       <c r="H110" s="22" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I110" s="2">
         <v>30000</v>
@@ -8882,10 +8879,10 @@
         <v>0</v>
       </c>
       <c r="N110" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O110" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P110" s="2"/>
     </row>
@@ -8894,7 +8891,7 @@
         <v>1105</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E111" s="2">
         <v>98</v>
@@ -8906,7 +8903,7 @@
         <v>1156</v>
       </c>
       <c r="H111" s="22" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I111" s="2">
         <v>30000</v>
@@ -8924,10 +8921,10 @@
         <v>0</v>
       </c>
       <c r="N111" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O111" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P111" s="2"/>
     </row>
@@ -8936,7 +8933,7 @@
         <v>1106</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E112" s="2">
         <v>98</v>
@@ -8948,7 +8945,7 @@
         <v>1157</v>
       </c>
       <c r="H112" s="22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I112" s="2">
         <v>30000</v>
@@ -8966,10 +8963,10 @@
         <v>0</v>
       </c>
       <c r="N112" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O112" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P112" s="2"/>
     </row>
@@ -8978,7 +8975,7 @@
         <v>1107</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E113" s="2">
         <v>98</v>
@@ -8990,7 +8987,7 @@
         <v>1158</v>
       </c>
       <c r="H113" s="22" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I113" s="2">
         <v>30000</v>
@@ -9008,10 +9005,10 @@
         <v>0</v>
       </c>
       <c r="N113" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O113" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P113" s="2"/>
     </row>
@@ -9020,7 +9017,7 @@
         <v>1108</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E114" s="2">
         <v>98</v>
@@ -9032,7 +9029,7 @@
         <v>1159</v>
       </c>
       <c r="H114" s="22" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I114" s="2">
         <v>30000</v>
@@ -9050,10 +9047,10 @@
         <v>0</v>
       </c>
       <c r="N114" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O114" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P114" s="2"/>
     </row>
@@ -9062,7 +9059,7 @@
         <v>1109</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E115" s="2">
         <v>98</v>
@@ -9074,7 +9071,7 @@
         <v>1160</v>
       </c>
       <c r="H115" s="22" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I115" s="2">
         <v>30000</v>
@@ -9092,10 +9089,10 @@
         <v>0</v>
       </c>
       <c r="N115" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O115" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P115" s="2"/>
     </row>
@@ -9104,7 +9101,7 @@
         <v>1110</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E116" s="2">
         <v>98</v>
@@ -9116,7 +9113,7 @@
         <v>1161</v>
       </c>
       <c r="H116" s="22" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I116" s="2">
         <v>30000</v>
@@ -9134,10 +9131,10 @@
         <v>0</v>
       </c>
       <c r="N116" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O116" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P116" s="2"/>
     </row>
@@ -9146,7 +9143,7 @@
         <v>1111</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E117" s="2">
         <v>98</v>
@@ -9158,7 +9155,7 @@
         <v>1162</v>
       </c>
       <c r="H117" s="22" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I117" s="2">
         <v>30000</v>
@@ -9176,10 +9173,10 @@
         <v>0</v>
       </c>
       <c r="N117" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O117" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P117" s="2"/>
     </row>
@@ -9188,7 +9185,7 @@
         <v>1112</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E118" s="2">
         <v>98</v>
@@ -9200,7 +9197,7 @@
         <v>1163</v>
       </c>
       <c r="H118" s="22" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I118" s="2">
         <v>30000</v>
@@ -9218,10 +9215,10 @@
         <v>0</v>
       </c>
       <c r="N118" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O118" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P118" s="2"/>
     </row>
@@ -9230,7 +9227,7 @@
         <v>1113</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E119" s="2">
         <v>98</v>
@@ -9242,7 +9239,7 @@
         <v>1164</v>
       </c>
       <c r="H119" s="22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I119" s="2">
         <v>30000</v>
@@ -9260,10 +9257,10 @@
         <v>0</v>
       </c>
       <c r="N119" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O119" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P119" s="2"/>
     </row>
@@ -9272,7 +9269,7 @@
         <v>1114</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E120" s="2">
         <v>98</v>
@@ -9284,7 +9281,7 @@
         <v>1165</v>
       </c>
       <c r="H120" s="22" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I120" s="2">
         <v>30000</v>
@@ -9302,10 +9299,10 @@
         <v>0</v>
       </c>
       <c r="N120" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O120" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P120" s="2"/>
     </row>
@@ -9314,7 +9311,7 @@
         <v>1115</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E121" s="2">
         <v>98</v>
@@ -9326,7 +9323,7 @@
         <v>1166</v>
       </c>
       <c r="H121" s="22" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I121" s="2">
         <v>30000</v>
@@ -9344,10 +9341,10 @@
         <v>0</v>
       </c>
       <c r="N121" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O121" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P121" s="2"/>
     </row>
@@ -9356,7 +9353,7 @@
         <v>1116</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E122" s="2">
         <v>98</v>
@@ -9368,7 +9365,7 @@
         <v>1167</v>
       </c>
       <c r="H122" s="22" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I122" s="2">
         <v>30000</v>
@@ -9386,10 +9383,10 @@
         <v>0</v>
       </c>
       <c r="N122" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O122" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P122" s="2"/>
     </row>
@@ -9398,7 +9395,7 @@
         <v>1117</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E123" s="2">
         <v>98</v>
@@ -9410,7 +9407,7 @@
         <v>1168</v>
       </c>
       <c r="H123" s="22" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I123" s="2">
         <v>30000</v>
@@ -9428,10 +9425,10 @@
         <v>0</v>
       </c>
       <c r="N123" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O123" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P123" s="2"/>
     </row>
@@ -9440,7 +9437,7 @@
         <v>1118</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E124" s="2">
         <v>98</v>
@@ -9452,7 +9449,7 @@
         <v>1169</v>
       </c>
       <c r="H124" s="22" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I124" s="2">
         <v>30000</v>
@@ -9470,10 +9467,10 @@
         <v>0</v>
       </c>
       <c r="N124" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O124" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P124" s="2"/>
     </row>
@@ -9482,7 +9479,7 @@
         <v>1119</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E125" s="2">
         <v>98</v>
@@ -9494,7 +9491,7 @@
         <v>1170</v>
       </c>
       <c r="H125" s="22" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I125" s="2">
         <v>30000</v>
@@ -9512,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="N125" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O125" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P125" s="2"/>
     </row>
@@ -9524,7 +9521,7 @@
         <v>1120</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E126" s="2">
         <v>98</v>
@@ -9536,7 +9533,7 @@
         <v>1171</v>
       </c>
       <c r="H126" s="22" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I126" s="2">
         <v>30000</v>
@@ -9554,10 +9551,10 @@
         <v>0</v>
       </c>
       <c r="N126" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O126" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P126" s="2"/>
     </row>
@@ -9566,7 +9563,7 @@
         <v>1121</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E127" s="2">
         <v>98</v>
@@ -9578,7 +9575,7 @@
         <v>1172</v>
       </c>
       <c r="H127" s="22" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I127" s="2">
         <v>30000</v>
@@ -9596,10 +9593,10 @@
         <v>0</v>
       </c>
       <c r="N127" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O127" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P127" s="2"/>
     </row>
@@ -9608,7 +9605,7 @@
         <v>1122</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E128" s="2">
         <v>98</v>
@@ -9620,7 +9617,7 @@
         <v>1173</v>
       </c>
       <c r="H128" s="22" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I128" s="2">
         <v>30000</v>
@@ -9638,10 +9635,10 @@
         <v>0</v>
       </c>
       <c r="N128" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O128" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P128" s="2"/>
     </row>
@@ -9650,7 +9647,7 @@
         <v>1123</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E129" s="2">
         <v>98</v>
@@ -9662,7 +9659,7 @@
         <v>1174</v>
       </c>
       <c r="H129" s="22" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I129" s="2">
         <v>30000</v>
@@ -9680,10 +9677,10 @@
         <v>0</v>
       </c>
       <c r="N129" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O129" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P129" s="2"/>
     </row>
@@ -9692,7 +9689,7 @@
         <v>1124</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E130" s="12">
         <v>98</v>
@@ -9704,7 +9701,7 @@
         <v>1175</v>
       </c>
       <c r="H130" s="23" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I130" s="12">
         <v>60000</v>
@@ -9722,10 +9719,10 @@
         <v>0</v>
       </c>
       <c r="N130" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O130" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="131" customHeight="1" spans="3:15">
@@ -9733,7 +9730,7 @@
         <v>1125</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E131" s="2">
         <v>98</v>
@@ -9745,7 +9742,7 @@
         <v>1176</v>
       </c>
       <c r="H131" s="22" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I131" s="17">
         <v>60000</v>
@@ -9763,10 +9760,10 @@
         <v>0</v>
       </c>
       <c r="N131" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O131" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="132" customHeight="1" spans="3:15">
@@ -9774,7 +9771,7 @@
         <v>1126</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E132" s="2">
         <v>98</v>
@@ -9786,7 +9783,7 @@
         <v>1177</v>
       </c>
       <c r="H132" s="22" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I132" s="17">
         <v>60000</v>
@@ -9804,10 +9801,10 @@
         <v>0</v>
       </c>
       <c r="N132" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O132" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="3:15">
@@ -9815,7 +9812,7 @@
         <v>1127</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E133" s="2">
         <v>98</v>
@@ -9827,7 +9824,7 @@
         <v>1178</v>
       </c>
       <c r="H133" s="22" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I133" s="17">
         <v>60000</v>
@@ -9845,10 +9842,10 @@
         <v>0</v>
       </c>
       <c r="N133" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O133" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="3:15">
@@ -9856,7 +9853,7 @@
         <v>1128</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E134" s="2">
         <v>98</v>
@@ -9868,7 +9865,7 @@
         <v>1179</v>
       </c>
       <c r="H134" s="22" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I134" s="17">
         <v>60000</v>
@@ -9886,10 +9883,10 @@
         <v>0</v>
       </c>
       <c r="N134" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O134" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="3:15">
@@ -9897,7 +9894,7 @@
         <v>1129</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E135" s="2">
         <v>98</v>
@@ -9909,7 +9906,7 @@
         <v>1180</v>
       </c>
       <c r="H135" s="22" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I135" s="17">
         <v>60000</v>
@@ -9927,10 +9924,10 @@
         <v>0</v>
       </c>
       <c r="N135" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O135" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="3:15">
@@ -9938,7 +9935,7 @@
         <v>1130</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E136" s="2">
         <v>98</v>
@@ -9950,7 +9947,7 @@
         <v>1181</v>
       </c>
       <c r="H136" s="22" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I136" s="17">
         <v>60000</v>
@@ -9968,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="N136" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O136" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="3:15">
@@ -9979,7 +9976,7 @@
         <v>1131</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E137" s="2">
         <v>98</v>
@@ -9991,7 +9988,7 @@
         <v>1182</v>
       </c>
       <c r="H137" s="22" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I137" s="17">
         <v>60000</v>
@@ -10009,10 +10006,10 @@
         <v>0</v>
       </c>
       <c r="N137" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O137" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="3:15">
@@ -10020,7 +10017,7 @@
         <v>1132</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E138" s="2">
         <v>98</v>
@@ -10032,7 +10029,7 @@
         <v>1183</v>
       </c>
       <c r="H138" s="22" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I138" s="17">
         <v>60000</v>
@@ -10050,10 +10047,10 @@
         <v>0</v>
       </c>
       <c r="N138" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O138" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="3:15">
@@ -10061,7 +10058,7 @@
         <v>1133</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E139" s="2">
         <v>98</v>
@@ -10073,7 +10070,7 @@
         <v>1184</v>
       </c>
       <c r="H139" s="22" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I139" s="17">
         <v>60000</v>
@@ -10091,10 +10088,10 @@
         <v>0</v>
       </c>
       <c r="N139" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O139" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="3:15">
@@ -10102,7 +10099,7 @@
         <v>1134</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E140" s="2">
         <v>98</v>
@@ -10114,7 +10111,7 @@
         <v>1185</v>
       </c>
       <c r="H140" s="22" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I140" s="17">
         <v>60000</v>
@@ -10132,10 +10129,10 @@
         <v>0</v>
       </c>
       <c r="N140" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O140" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="141" customHeight="1" spans="3:15">
@@ -10143,7 +10140,7 @@
         <v>1135</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E141" s="2">
         <v>98</v>
@@ -10155,7 +10152,7 @@
         <v>1186</v>
       </c>
       <c r="H141" s="22" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I141" s="17">
         <v>60000</v>
@@ -10173,10 +10170,10 @@
         <v>0</v>
       </c>
       <c r="N141" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O141" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="142" customHeight="1" spans="3:15">
@@ -10184,7 +10181,7 @@
         <v>1136</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E142" s="2">
         <v>98</v>
@@ -10196,7 +10193,7 @@
         <v>1187</v>
       </c>
       <c r="H142" s="22" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I142" s="17">
         <v>60000</v>
@@ -10214,10 +10211,10 @@
         <v>0</v>
       </c>
       <c r="N142" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O142" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="143" customHeight="1" spans="3:15">
@@ -10225,7 +10222,7 @@
         <v>1137</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E143" s="2">
         <v>98</v>
@@ -10237,7 +10234,7 @@
         <v>1188</v>
       </c>
       <c r="H143" s="22" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I143" s="17">
         <v>60000</v>
@@ -10255,10 +10252,10 @@
         <v>0</v>
       </c>
       <c r="N143" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O143" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="144" customHeight="1" spans="3:15">
@@ -10266,7 +10263,7 @@
         <v>1138</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E144" s="2">
         <v>98</v>
@@ -10278,7 +10275,7 @@
         <v>1189</v>
       </c>
       <c r="H144" s="22" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I144" s="17">
         <v>60000</v>
@@ -10296,10 +10293,10 @@
         <v>0</v>
       </c>
       <c r="N144" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O144" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" customHeight="1" spans="3:15">
@@ -10307,7 +10304,7 @@
         <v>1139</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E145" s="2">
         <v>98</v>
@@ -10319,7 +10316,7 @@
         <v>1190</v>
       </c>
       <c r="H145" s="22" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I145" s="17">
         <v>60000</v>
@@ -10337,10 +10334,10 @@
         <v>0</v>
       </c>
       <c r="N145" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O145" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="146" customHeight="1" spans="3:15">
@@ -10348,7 +10345,7 @@
         <v>1140</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E146" s="2">
         <v>98</v>
@@ -10360,7 +10357,7 @@
         <v>1191</v>
       </c>
       <c r="H146" s="22" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I146" s="17">
         <v>60000</v>
@@ -10378,10 +10375,10 @@
         <v>0</v>
       </c>
       <c r="N146" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O146" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="147" customHeight="1" spans="3:15">
@@ -10389,7 +10386,7 @@
         <v>1141</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E147" s="2">
         <v>98</v>
@@ -10401,7 +10398,7 @@
         <v>1192</v>
       </c>
       <c r="H147" s="22" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I147" s="17">
         <v>60000</v>
@@ -10419,10 +10416,10 @@
         <v>0</v>
       </c>
       <c r="N147" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O147" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="148" customHeight="1" spans="3:15">
@@ -10430,7 +10427,7 @@
         <v>1142</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E148" s="2">
         <v>98</v>
@@ -10442,7 +10439,7 @@
         <v>1193</v>
       </c>
       <c r="H148" s="22" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I148" s="17">
         <v>60000</v>
@@ -10460,10 +10457,10 @@
         <v>0</v>
       </c>
       <c r="N148" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O148" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="149" customHeight="1" spans="3:15">
@@ -10471,7 +10468,7 @@
         <v>1143</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E149" s="2">
         <v>98</v>
@@ -10483,7 +10480,7 @@
         <v>1194</v>
       </c>
       <c r="H149" s="22" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I149" s="17">
         <v>60000</v>
@@ -10501,10 +10498,10 @@
         <v>0</v>
       </c>
       <c r="N149" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O149" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="150" customHeight="1" spans="3:15">
@@ -10512,7 +10509,7 @@
         <v>1144</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E150" s="2">
         <v>98</v>
@@ -10524,7 +10521,7 @@
         <v>1195</v>
       </c>
       <c r="H150" s="22" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I150" s="17">
         <v>60000</v>
@@ -10542,10 +10539,10 @@
         <v>0</v>
       </c>
       <c r="N150" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O150" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="151" customHeight="1" spans="3:15">
@@ -10553,7 +10550,7 @@
         <v>1145</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E151" s="2">
         <v>98</v>
@@ -10565,7 +10562,7 @@
         <v>1196</v>
       </c>
       <c r="H151" s="22" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I151" s="17">
         <v>60000</v>
@@ -10583,10 +10580,10 @@
         <v>0</v>
       </c>
       <c r="N151" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O151" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="152" customHeight="1" spans="3:15">
@@ -10594,7 +10591,7 @@
         <v>1146</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E152" s="2">
         <v>98</v>
@@ -10606,7 +10603,7 @@
         <v>1197</v>
       </c>
       <c r="H152" s="22" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I152" s="17">
         <v>60000</v>
@@ -10624,10 +10621,10 @@
         <v>0</v>
       </c>
       <c r="N152" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O152" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="153" customHeight="1" spans="3:15">
@@ -10635,7 +10632,7 @@
         <v>1147</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E153" s="2">
         <v>98</v>
@@ -10647,7 +10644,7 @@
         <v>1198</v>
       </c>
       <c r="H153" s="22" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I153" s="17">
         <v>60000</v>
@@ -10665,10 +10662,10 @@
         <v>0</v>
       </c>
       <c r="N153" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O153" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="154" customHeight="1" spans="3:15">
@@ -10676,7 +10673,7 @@
         <v>1148</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E154" s="2">
         <v>98</v>
@@ -10688,7 +10685,7 @@
         <v>1199</v>
       </c>
       <c r="H154" s="22" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I154" s="17">
         <v>60000</v>
@@ -10706,10 +10703,10 @@
         <v>0</v>
       </c>
       <c r="N154" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O154" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="155" customHeight="1" spans="3:15">
@@ -10717,7 +10714,7 @@
         <v>1149</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E155" s="2">
         <v>98</v>
@@ -10729,7 +10726,7 @@
         <v>1200</v>
       </c>
       <c r="H155" s="22" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I155" s="17">
         <v>60000</v>
@@ -10747,10 +10744,10 @@
         <v>0</v>
       </c>
       <c r="N155" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O155" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="156" customHeight="1" spans="3:15">
@@ -10758,7 +10755,7 @@
         <v>1150</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E156" s="2">
         <v>98</v>
@@ -10770,7 +10767,7 @@
         <v>1201</v>
       </c>
       <c r="H156" s="22" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I156" s="17">
         <v>60000</v>
@@ -10788,10 +10785,10 @@
         <v>0</v>
       </c>
       <c r="N156" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O156" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="157" customHeight="1" spans="3:15">
@@ -10799,7 +10796,7 @@
         <v>1151</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E157" s="2">
         <v>98</v>
@@ -10811,7 +10808,7 @@
         <v>1202</v>
       </c>
       <c r="H157" s="22" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I157" s="17">
         <v>60000</v>
@@ -10829,10 +10826,10 @@
         <v>0</v>
       </c>
       <c r="N157" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O157" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="158" customHeight="1" spans="3:15">
@@ -10840,7 +10837,7 @@
         <v>1152</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E158" s="2">
         <v>98</v>
@@ -10852,7 +10849,7 @@
         <v>1203</v>
       </c>
       <c r="H158" s="22" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I158" s="17">
         <v>60000</v>
@@ -10870,10 +10867,10 @@
         <v>0</v>
       </c>
       <c r="N158" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O158" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="159" customHeight="1" spans="3:15">
@@ -10881,7 +10878,7 @@
         <v>1153</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E159" s="2">
         <v>98</v>
@@ -10893,7 +10890,7 @@
         <v>1204</v>
       </c>
       <c r="H159" s="22" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I159" s="17">
         <v>60000</v>
@@ -10911,10 +10908,10 @@
         <v>0</v>
       </c>
       <c r="N159" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O159" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="160" customHeight="1" spans="3:15">
@@ -10922,7 +10919,7 @@
         <v>1154</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E160" s="2">
         <v>98</v>
@@ -10934,7 +10931,7 @@
         <v>1205</v>
       </c>
       <c r="H160" s="22" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I160" s="17">
         <v>60000</v>
@@ -10952,10 +10949,10 @@
         <v>0</v>
       </c>
       <c r="N160" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O160" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="161" customHeight="1" spans="3:15">
@@ -10963,7 +10960,7 @@
         <v>1155</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E161" s="2">
         <v>98</v>
@@ -10975,7 +10972,7 @@
         <v>1206</v>
       </c>
       <c r="H161" s="22" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I161" s="17">
         <v>60000</v>
@@ -10993,10 +10990,10 @@
         <v>0</v>
       </c>
       <c r="N161" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O161" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="162" customHeight="1" spans="3:15">
@@ -11004,7 +11001,7 @@
         <v>1156</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E162" s="2">
         <v>98</v>
@@ -11016,7 +11013,7 @@
         <v>1207</v>
       </c>
       <c r="H162" s="22" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I162" s="17">
         <v>60000</v>
@@ -11034,10 +11031,10 @@
         <v>0</v>
       </c>
       <c r="N162" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O162" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="163" customHeight="1" spans="3:15">
@@ -11045,7 +11042,7 @@
         <v>1157</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E163" s="2">
         <v>98</v>
@@ -11057,7 +11054,7 @@
         <v>1208</v>
       </c>
       <c r="H163" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I163" s="17">
         <v>60000</v>
@@ -11075,10 +11072,10 @@
         <v>0</v>
       </c>
       <c r="N163" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O163" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="164" customHeight="1" spans="3:15">
@@ -11086,7 +11083,7 @@
         <v>1158</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E164" s="2">
         <v>98</v>
@@ -11098,7 +11095,7 @@
         <v>1209</v>
       </c>
       <c r="H164" s="22" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I164" s="17">
         <v>60000</v>
@@ -11116,10 +11113,10 @@
         <v>0</v>
       </c>
       <c r="N164" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O164" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -11312,7 +11309,7 @@
         <v>2000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -11324,7 +11321,7 @@
         <v>1070</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I6" s="2">
         <v>120000</v>
@@ -11345,10 +11342,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P6" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11356,7 +11353,7 @@
         <v>2001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -11368,7 +11365,7 @@
         <v>1071</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I7" s="2">
         <v>120000</v>
@@ -11389,10 +11386,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P7" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11400,7 +11397,7 @@
         <v>2002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -11412,7 +11409,7 @@
         <v>1072</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I8" s="2">
         <v>120000</v>
@@ -11433,10 +11430,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P8" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11444,7 +11441,7 @@
         <v>2003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -11456,7 +11453,7 @@
         <v>1073</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I9" s="2">
         <v>120000</v>
@@ -11477,10 +11474,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P9" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11488,7 +11485,7 @@
         <v>2004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -11500,7 +11497,7 @@
         <v>1074</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I10" s="2">
         <v>120000</v>
@@ -11521,10 +11518,10 @@
         <v>0</v>
       </c>
       <c r="O10" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P10" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11532,7 +11529,7 @@
         <v>2005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -11544,7 +11541,7 @@
         <v>1104</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I11" s="2">
         <v>20000</v>
@@ -11565,10 +11562,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P11" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
@@ -11590,7 +11587,7 @@
         <v>2006</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -11602,7 +11599,7 @@
         <v>1105</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I14" s="2">
         <v>360000</v>
@@ -11623,10 +11620,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P14" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11634,7 +11631,7 @@
         <v>2007</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -11646,7 +11643,7 @@
         <v>1106</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I15" s="2">
         <v>360000</v>
@@ -11667,10 +11664,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P15" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11678,7 +11675,7 @@
         <v>2008</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -11690,7 +11687,7 @@
         <v>1107</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I16" s="2">
         <v>360000</v>
@@ -11711,10 +11708,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P16" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11722,7 +11719,7 @@
         <v>2009</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -11734,7 +11731,7 @@
         <v>1108</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I17" s="2">
         <v>360000</v>
@@ -11755,10 +11752,10 @@
         <v>0</v>
       </c>
       <c r="O17" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P17" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11766,7 +11763,7 @@
         <v>2010</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -11778,7 +11775,7 @@
         <v>1139</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I18" s="2">
         <v>360000</v>
@@ -11799,10 +11796,10 @@
         <v>0</v>
       </c>
       <c r="O18" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P18" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11810,7 +11807,7 @@
         <v>2011</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -11822,7 +11819,7 @@
         <v>1139</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -11843,10 +11840,10 @@
         <v>0</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P19" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
@@ -11861,7 +11858,7 @@
         <v>2012</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -11873,7 +11870,7 @@
         <v>1140</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I21" s="2">
         <v>360000</v>
@@ -11894,10 +11891,10 @@
         <v>0</v>
       </c>
       <c r="O21" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P21" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11905,7 +11902,7 @@
         <v>2013</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -11917,7 +11914,7 @@
         <v>1141</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I22" s="2">
         <v>360000</v>
@@ -11938,10 +11935,10 @@
         <v>0</v>
       </c>
       <c r="O22" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P22" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11949,7 +11946,7 @@
         <v>2014</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -11961,7 +11958,7 @@
         <v>1142</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I23" s="2">
         <v>360000</v>
@@ -11982,10 +11979,10 @@
         <v>0</v>
       </c>
       <c r="O23" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P23" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11993,7 +11990,7 @@
         <v>2015</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -12005,7 +12002,7 @@
         <v>1143</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I24" s="2">
         <v>360000</v>
@@ -12026,10 +12023,10 @@
         <v>0</v>
       </c>
       <c r="O24" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P24" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -12037,7 +12034,7 @@
         <v>2016</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -12049,7 +12046,7 @@
         <v>1209</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I25" s="2">
         <v>360000</v>
@@ -12070,10 +12067,10 @@
         <v>0</v>
       </c>
       <c r="O25" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P25" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -12081,7 +12078,7 @@
         <v>2017</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -12093,7 +12090,7 @@
         <v>1209</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I26" s="2">
         <v>180000</v>
@@ -12114,24 +12111,24 @@
         <v>0</v>
       </c>
       <c r="O26" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P26" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C27" s="2">
         <v>2018</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -12143,7 +12140,7 @@
         <v>1174</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>
@@ -12164,10 +12161,10 @@
         <v>0</v>
       </c>
       <c r="O27" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P27" s="20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="465">
   <si>
     <t>_id</t>
   </si>
@@ -349,16 +349,19 @@
     <t>2025-09-07</t>
   </si>
   <si>
+    <t>2025-09-12</t>
+  </si>
+  <si>
+    <t>平时部分掉落</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>2024-10-31</t>
+  </si>
+  <si>
     <t>2026-10-21</t>
-  </si>
-  <si>
-    <t>平时部分掉落</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>2024-10-31</t>
   </si>
   <si>
     <t>第一批白图鉴</t>
@@ -1853,12 +1856,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2946,7 +2949,7 @@
         <v>33</v>
       </c>
       <c r="P7" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" customFormat="1" customHeight="1" spans="3:16">
@@ -2970,7 +2973,7 @@
         <v>101</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -2982,13 +2985,13 @@
         <v>2000</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I9" s="11">
         <v>0</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K9" s="11">
         <v>0</v>
@@ -3003,10 +3006,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P9" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3014,7 +3017,7 @@
         <v>102</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -3026,13 +3029,13 @@
         <v>2000</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I10" s="11">
         <v>0</v>
       </c>
       <c r="J10" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K10" s="11">
         <v>0</v>
@@ -3047,10 +3050,10 @@
         <v>0</v>
       </c>
       <c r="O10" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P10" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3058,7 +3061,7 @@
         <v>103</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -3070,13 +3073,13 @@
         <v>2000</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I11" s="11">
         <v>0</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K11" s="11">
         <v>0</v>
@@ -3091,10 +3094,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P11" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3102,7 +3105,7 @@
         <v>104</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
@@ -3114,13 +3117,13 @@
         <v>2000</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I12" s="11">
         <v>0</v>
       </c>
       <c r="J12" s="20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K12" s="11">
         <v>0</v>
@@ -3135,10 +3138,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P12" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3146,7 +3149,7 @@
         <v>105</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
@@ -3158,13 +3161,13 @@
         <v>2000</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I13" s="11">
         <v>0</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K13" s="11">
         <v>0</v>
@@ -3179,10 +3182,10 @@
         <v>0</v>
       </c>
       <c r="O13" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P13" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3190,7 +3193,7 @@
         <v>106</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -3202,13 +3205,13 @@
         <v>2000</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I14" s="11">
         <v>0</v>
       </c>
       <c r="J14" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K14" s="11">
         <v>0</v>
@@ -3223,10 +3226,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P14" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3234,7 +3237,7 @@
         <v>107</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -3246,13 +3249,13 @@
         <v>2000</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I15" s="11">
         <v>0</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K15" s="11">
         <v>0</v>
@@ -3267,10 +3270,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P15" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3278,7 +3281,7 @@
         <v>108</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -3290,13 +3293,13 @@
         <v>2000</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I16" s="11">
         <v>0</v>
       </c>
       <c r="J16" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K16" s="11">
         <v>0</v>
@@ -3311,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P16" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3322,7 +3325,7 @@
         <v>109</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -3334,13 +3337,13 @@
         <v>2000</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I17" s="11">
         <v>0</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K17" s="11">
         <v>0</v>
@@ -3355,10 +3358,10 @@
         <v>0</v>
       </c>
       <c r="O17" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P17" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3366,7 +3369,7 @@
         <v>110</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -3378,13 +3381,13 @@
         <v>2000</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I18" s="11">
         <v>0</v>
       </c>
       <c r="J18" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K18" s="11">
         <v>0</v>
@@ -3399,10 +3402,10 @@
         <v>0</v>
       </c>
       <c r="O18" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P18" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3410,7 +3413,7 @@
         <v>111</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -3422,13 +3425,13 @@
         <v>2000</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I19" s="11">
         <v>0</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K19" s="11">
         <v>0</v>
@@ -3443,10 +3446,10 @@
         <v>0</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P19" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3454,7 +3457,7 @@
         <v>112</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E20" s="2">
         <v>98</v>
@@ -3466,13 +3469,13 @@
         <v>2000</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I20" s="11">
         <v>0</v>
       </c>
       <c r="J20" s="20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K20" s="11">
         <v>0</v>
@@ -3487,10 +3490,10 @@
         <v>0</v>
       </c>
       <c r="O20" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P20" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1"/>
@@ -3499,7 +3502,7 @@
         <v>201</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E22" s="2">
         <v>100</v>
@@ -3511,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I22" s="11">
         <v>0</v>
@@ -3532,10 +3535,10 @@
         <v>1</v>
       </c>
       <c r="O22" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P22" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3543,7 +3546,7 @@
         <v>202</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E23" s="2">
         <v>100</v>
@@ -3555,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I23" s="11">
         <v>0</v>
@@ -3576,10 +3579,10 @@
         <v>1</v>
       </c>
       <c r="O23" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P23" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3587,7 +3590,7 @@
         <v>203</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2">
         <v>100</v>
@@ -3599,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I24" s="11">
         <v>0</v>
@@ -3620,10 +3623,10 @@
         <v>1</v>
       </c>
       <c r="O24" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P24" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="8:16">
@@ -3642,7 +3645,7 @@
         <v>301</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -3654,13 +3657,13 @@
         <v>2000</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I26" s="2">
         <v>0</v>
       </c>
       <c r="J26" s="21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K26" s="11">
         <v>0</v>
@@ -3675,10 +3678,10 @@
         <v>0</v>
       </c>
       <c r="O26" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P26" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3686,7 +3689,7 @@
         <v>302</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -3698,13 +3701,13 @@
         <v>2000</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I27" s="2">
         <v>0</v>
       </c>
       <c r="J27" s="21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K27" s="11">
         <v>0</v>
@@ -3719,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="O27" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P27" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3730,7 +3733,7 @@
         <v>303</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E28" s="2">
         <v>98</v>
@@ -3742,13 +3745,13 @@
         <v>2000</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I28" s="21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J28" s="20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K28" s="11">
         <v>0</v>
@@ -3763,10 +3766,10 @@
         <v>0</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P28" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3774,7 +3777,7 @@
         <v>304</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -3786,13 +3789,13 @@
         <v>2000</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I29" s="21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K29" s="11">
         <v>0</v>
@@ -3807,10 +3810,10 @@
         <v>0</v>
       </c>
       <c r="O29" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P29" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1"/>
@@ -3819,7 +3822,7 @@
         <v>801</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E31" s="2">
         <v>98</v>
@@ -3831,13 +3834,13 @@
         <v>2000</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I31" s="21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J31" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K31" s="11">
         <v>0</v>
@@ -3852,10 +3855,10 @@
         <v>0</v>
       </c>
       <c r="O31" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P31" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3863,7 +3866,7 @@
         <v>802</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E32" s="2">
         <v>98</v>
@@ -3875,13 +3878,13 @@
         <v>2000</v>
       </c>
       <c r="H32" s="21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I32" s="20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J32" s="20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K32" s="11">
         <v>0</v>
@@ -3896,10 +3899,10 @@
         <v>0</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P32" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -3907,7 +3910,7 @@
         <v>803</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
@@ -3919,13 +3922,13 @@
         <v>2000</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I33" s="20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J33" s="20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K33" s="11">
         <v>0</v>
@@ -3940,10 +3943,10 @@
         <v>0</v>
       </c>
       <c r="O33" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P33" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="9:16">
@@ -3960,7 +3963,7 @@
         <v>804</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
@@ -3972,13 +3975,13 @@
         <v>2000</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I35" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J35" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K35" s="11">
         <v>0</v>
@@ -3993,10 +3996,10 @@
         <v>0</v>
       </c>
       <c r="O35" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P35" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4004,7 +4007,7 @@
         <v>805</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -4016,13 +4019,13 @@
         <v>2000</v>
       </c>
       <c r="H36" s="21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I36" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J36" s="20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K36" s="11">
         <v>0</v>
@@ -4037,10 +4040,10 @@
         <v>0</v>
       </c>
       <c r="O36" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P36" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4048,7 +4051,7 @@
         <v>806</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -4060,13 +4063,13 @@
         <v>2000</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I37" s="21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J37" s="20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K37" s="11">
         <v>0</v>
@@ -4081,10 +4084,10 @@
         <v>0</v>
       </c>
       <c r="O37" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P37" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4092,7 +4095,7 @@
         <v>807</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E38" s="2">
         <v>98</v>
@@ -4104,13 +4107,13 @@
         <v>2000</v>
       </c>
       <c r="H38" s="21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I38" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J38" s="20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K38" s="11">
         <v>0</v>
@@ -4125,10 +4128,10 @@
         <v>0</v>
       </c>
       <c r="O38" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P38" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4136,7 +4139,7 @@
         <v>808</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E39" s="2">
         <v>98</v>
@@ -4148,13 +4151,13 @@
         <v>2000</v>
       </c>
       <c r="H39" s="21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I39" s="21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J39" s="20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K39" s="11">
         <v>0</v>
@@ -4169,10 +4172,10 @@
         <v>0</v>
       </c>
       <c r="O39" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P39" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" customFormat="1" customHeight="1" spans="3:16">
@@ -4196,7 +4199,7 @@
         <v>991</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E41" s="2">
         <v>99</v>
@@ -4208,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I41" s="11">
         <v>0</v>
@@ -4229,10 +4232,10 @@
         <v>1</v>
       </c>
       <c r="O41" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P41" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:16">
@@ -4240,7 +4243,7 @@
         <v>992</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E42" s="2">
         <v>101</v>
@@ -4252,7 +4255,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I42" s="11">
         <v>0</v>
@@ -4273,10 +4276,10 @@
         <v>1</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P42" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1"/>
@@ -4524,7 +4527,7 @@
         <v>1000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -4536,7 +4539,7 @@
         <v>1051</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I6" s="2">
         <v>40000</v>
@@ -4554,10 +4557,10 @@
         <v>0</v>
       </c>
       <c r="N6" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O6" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4565,7 +4568,7 @@
         <v>1001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -4577,7 +4580,7 @@
         <v>1052</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I7" s="2">
         <v>40000</v>
@@ -4595,10 +4598,10 @@
         <v>0</v>
       </c>
       <c r="N7" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4606,7 +4609,7 @@
         <v>1002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -4618,7 +4621,7 @@
         <v>1053</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I8" s="2">
         <v>40000</v>
@@ -4636,10 +4639,10 @@
         <v>0</v>
       </c>
       <c r="N8" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O8" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4647,7 +4650,7 @@
         <v>1003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -4659,7 +4662,7 @@
         <v>1054</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I9" s="2">
         <v>40000</v>
@@ -4677,10 +4680,10 @@
         <v>0</v>
       </c>
       <c r="N9" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4688,7 +4691,7 @@
         <v>1004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -4700,7 +4703,7 @@
         <v>1055</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I10" s="2">
         <v>40000</v>
@@ -4718,10 +4721,10 @@
         <v>0</v>
       </c>
       <c r="N10" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O10" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4729,7 +4732,7 @@
         <v>1005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -4741,7 +4744,7 @@
         <v>1056</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I11" s="2">
         <v>40000</v>
@@ -4759,10 +4762,10 @@
         <v>0</v>
       </c>
       <c r="N11" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O11" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4770,7 +4773,7 @@
         <v>1006</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
@@ -4782,7 +4785,7 @@
         <v>1057</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I12" s="2">
         <v>40000</v>
@@ -4800,10 +4803,10 @@
         <v>0</v>
       </c>
       <c r="N12" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O12" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4811,7 +4814,7 @@
         <v>1007</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
@@ -4823,7 +4826,7 @@
         <v>1058</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I13" s="2">
         <v>40000</v>
@@ -4841,10 +4844,10 @@
         <v>0</v>
       </c>
       <c r="N13" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O13" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4852,7 +4855,7 @@
         <v>1008</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -4864,7 +4867,7 @@
         <v>1059</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I14" s="2">
         <v>40000</v>
@@ -4882,10 +4885,10 @@
         <v>0</v>
       </c>
       <c r="N14" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O14" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4893,7 +4896,7 @@
         <v>1009</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -4905,7 +4908,7 @@
         <v>1060</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I15" s="2">
         <v>40000</v>
@@ -4923,10 +4926,10 @@
         <v>0</v>
       </c>
       <c r="N15" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O15" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4934,7 +4937,7 @@
         <v>1010</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -4946,7 +4949,7 @@
         <v>1061</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I16" s="2">
         <v>40000</v>
@@ -4964,10 +4967,10 @@
         <v>0</v>
       </c>
       <c r="N16" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O16" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -4975,7 +4978,7 @@
         <v>1011</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -4987,7 +4990,7 @@
         <v>1062</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I17" s="2">
         <v>40000</v>
@@ -5005,10 +5008,10 @@
         <v>0</v>
       </c>
       <c r="N17" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O17" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5016,7 +5019,7 @@
         <v>1012</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -5028,7 +5031,7 @@
         <v>1063</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I18" s="2">
         <v>40000</v>
@@ -5046,10 +5049,10 @@
         <v>0</v>
       </c>
       <c r="N18" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O18" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5057,7 +5060,7 @@
         <v>1013</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -5069,7 +5072,7 @@
         <v>1064</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -5087,10 +5090,10 @@
         <v>0</v>
       </c>
       <c r="N19" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5098,7 +5101,7 @@
         <v>1014</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E20" s="2">
         <v>98</v>
@@ -5110,7 +5113,7 @@
         <v>1065</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I20" s="2">
         <v>40000</v>
@@ -5128,10 +5131,10 @@
         <v>0</v>
       </c>
       <c r="N20" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O20" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5139,7 +5142,7 @@
         <v>1015</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -5151,7 +5154,7 @@
         <v>1066</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I21" s="2">
         <v>40000</v>
@@ -5169,10 +5172,10 @@
         <v>0</v>
       </c>
       <c r="N21" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O21" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5180,7 +5183,7 @@
         <v>1016</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -5192,7 +5195,7 @@
         <v>1067</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I22" s="2">
         <v>40000</v>
@@ -5210,10 +5213,10 @@
         <v>0</v>
       </c>
       <c r="N22" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O22" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5221,7 +5224,7 @@
         <v>1017</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -5233,7 +5236,7 @@
         <v>1068</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I23" s="2">
         <v>40000</v>
@@ -5251,10 +5254,10 @@
         <v>0</v>
       </c>
       <c r="N23" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O23" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5262,7 +5265,7 @@
         <v>1018</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -5274,7 +5277,7 @@
         <v>1069</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I24" s="2">
         <v>40000</v>
@@ -5292,10 +5295,10 @@
         <v>0</v>
       </c>
       <c r="N24" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O24" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5303,7 +5306,7 @@
         <v>1019</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -5315,7 +5318,7 @@
         <v>1070</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I25" s="2">
         <v>40000</v>
@@ -5333,10 +5336,10 @@
         <v>0</v>
       </c>
       <c r="N25" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O25" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5344,7 +5347,7 @@
         <v>1020</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -5356,7 +5359,7 @@
         <v>1071</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I26" s="2">
         <v>40000</v>
@@ -5374,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="N26" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O26" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5385,7 +5388,7 @@
         <v>1021</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -5397,7 +5400,7 @@
         <v>1072</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>
@@ -5415,10 +5418,10 @@
         <v>0</v>
       </c>
       <c r="N27" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O27" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5426,7 +5429,7 @@
         <v>1022</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E28" s="2">
         <v>98</v>
@@ -5438,7 +5441,7 @@
         <v>1073</v>
       </c>
       <c r="H28" s="22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I28" s="2">
         <v>40000</v>
@@ -5456,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="N28" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:16">
@@ -5467,7 +5470,7 @@
         <v>1023</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -5479,7 +5482,7 @@
         <v>1074</v>
       </c>
       <c r="H29" s="22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I29" s="2">
         <v>40000</v>
@@ -5497,10 +5500,10 @@
         <v>0</v>
       </c>
       <c r="N29" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O29" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P29" s="2"/>
     </row>
@@ -5509,7 +5512,7 @@
         <v>1024</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E30" s="2">
         <v>98</v>
@@ -5521,7 +5524,7 @@
         <v>1075</v>
       </c>
       <c r="H30" s="22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I30" s="2">
         <v>4000</v>
@@ -5539,10 +5542,10 @@
         <v>0</v>
       </c>
       <c r="N30" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O30" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5550,7 +5553,7 @@
         <v>1025</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E31" s="2">
         <v>98</v>
@@ -5562,7 +5565,7 @@
         <v>1076</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I31" s="2">
         <v>4000</v>
@@ -5580,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="N31" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O31" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5591,7 +5594,7 @@
         <v>1026</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E32" s="2">
         <v>98</v>
@@ -5603,7 +5606,7 @@
         <v>1077</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I32" s="2">
         <v>4000</v>
@@ -5621,10 +5624,10 @@
         <v>0</v>
       </c>
       <c r="N32" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -5632,7 +5635,7 @@
         <v>1027</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
@@ -5644,7 +5647,7 @@
         <v>1078</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I33" s="2">
         <v>4000</v>
@@ -5662,10 +5665,10 @@
         <v>0</v>
       </c>
       <c r="N33" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O33" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:16">
@@ -5673,7 +5676,7 @@
         <v>1028</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E34" s="2">
         <v>98</v>
@@ -5685,7 +5688,7 @@
         <v>1079</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I34" s="2">
         <v>4000</v>
@@ -5703,10 +5706,10 @@
         <v>0</v>
       </c>
       <c r="N34" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O34" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P34" s="2"/>
     </row>
@@ -5715,7 +5718,7 @@
         <v>1029</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
@@ -5727,7 +5730,7 @@
         <v>1080</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I35" s="2">
         <v>4000</v>
@@ -5745,10 +5748,10 @@
         <v>0</v>
       </c>
       <c r="N35" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O35" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P35" s="2"/>
     </row>
@@ -5757,7 +5760,7 @@
         <v>1030</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -5769,7 +5772,7 @@
         <v>1081</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I36" s="2">
         <v>4000</v>
@@ -5787,10 +5790,10 @@
         <v>0</v>
       </c>
       <c r="N36" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O36" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P36" s="2"/>
     </row>
@@ -5799,7 +5802,7 @@
         <v>1031</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -5811,7 +5814,7 @@
         <v>1082</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I37" s="2">
         <v>4000</v>
@@ -5829,10 +5832,10 @@
         <v>0</v>
       </c>
       <c r="N37" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O37" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P37" s="2"/>
     </row>
@@ -5841,7 +5844,7 @@
         <v>1032</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E38" s="2">
         <v>98</v>
@@ -5853,7 +5856,7 @@
         <v>1083</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I38" s="2">
         <v>4000</v>
@@ -5871,10 +5874,10 @@
         <v>0</v>
       </c>
       <c r="N38" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O38" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P38" s="2"/>
     </row>
@@ -5883,7 +5886,7 @@
         <v>1033</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E39" s="2">
         <v>98</v>
@@ -5895,7 +5898,7 @@
         <v>1084</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I39" s="2">
         <v>4000</v>
@@ -5913,10 +5916,10 @@
         <v>0</v>
       </c>
       <c r="N39" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O39" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P39" s="2"/>
     </row>
@@ -5925,7 +5928,7 @@
         <v>1034</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E40" s="2">
         <v>98</v>
@@ -5937,7 +5940,7 @@
         <v>1085</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I40" s="2">
         <v>4000</v>
@@ -5955,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="N40" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O40" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P40" s="2"/>
     </row>
@@ -5967,7 +5970,7 @@
         <v>1035</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E41" s="2">
         <v>98</v>
@@ -5979,7 +5982,7 @@
         <v>1086</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I41" s="2">
         <v>4000</v>
@@ -5997,10 +6000,10 @@
         <v>0</v>
       </c>
       <c r="N41" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O41" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P41" s="2"/>
     </row>
@@ -6009,7 +6012,7 @@
         <v>1036</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E42" s="2">
         <v>98</v>
@@ -6021,7 +6024,7 @@
         <v>1087</v>
       </c>
       <c r="H42" s="22" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I42" s="2">
         <v>4000</v>
@@ -6039,10 +6042,10 @@
         <v>0</v>
       </c>
       <c r="N42" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P42" s="2"/>
     </row>
@@ -6051,7 +6054,7 @@
         <v>1037</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E43" s="2">
         <v>98</v>
@@ -6063,7 +6066,7 @@
         <v>1088</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I43" s="2">
         <v>4000</v>
@@ -6081,10 +6084,10 @@
         <v>0</v>
       </c>
       <c r="N43" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O43" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P43" s="2"/>
     </row>
@@ -6093,7 +6096,7 @@
         <v>1038</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E44" s="2">
         <v>98</v>
@@ -6105,7 +6108,7 @@
         <v>1089</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I44" s="2">
         <v>4000</v>
@@ -6123,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="N44" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O44" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P44" s="2"/>
     </row>
@@ -6135,7 +6138,7 @@
         <v>1039</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E45" s="2">
         <v>98</v>
@@ -6147,7 +6150,7 @@
         <v>1090</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I45" s="2">
         <v>4000</v>
@@ -6165,10 +6168,10 @@
         <v>0</v>
       </c>
       <c r="N45" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O45" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P45" s="2"/>
     </row>
@@ -6177,7 +6180,7 @@
         <v>1040</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E46" s="2">
         <v>98</v>
@@ -6189,7 +6192,7 @@
         <v>1091</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I46" s="2">
         <v>4000</v>
@@ -6207,10 +6210,10 @@
         <v>0</v>
       </c>
       <c r="N46" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O46" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P46" s="2"/>
     </row>
@@ -6219,7 +6222,7 @@
         <v>1041</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E47" s="2">
         <v>98</v>
@@ -6231,7 +6234,7 @@
         <v>1092</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I47" s="2">
         <v>4000</v>
@@ -6249,10 +6252,10 @@
         <v>0</v>
       </c>
       <c r="N47" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O47" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P47" s="2"/>
     </row>
@@ -6261,7 +6264,7 @@
         <v>1042</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E48" s="2">
         <v>98</v>
@@ -6273,7 +6276,7 @@
         <v>1093</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I48" s="2">
         <v>4000</v>
@@ -6291,10 +6294,10 @@
         <v>0</v>
       </c>
       <c r="N48" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O48" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P48" s="2"/>
     </row>
@@ -6303,7 +6306,7 @@
         <v>1043</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E49" s="2">
         <v>98</v>
@@ -6315,7 +6318,7 @@
         <v>1094</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I49" s="2">
         <v>4000</v>
@@ -6333,10 +6336,10 @@
         <v>0</v>
       </c>
       <c r="N49" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O49" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P49" s="2"/>
     </row>
@@ -6345,7 +6348,7 @@
         <v>1044</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E50" s="2">
         <v>98</v>
@@ -6357,7 +6360,7 @@
         <v>1095</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I50" s="2">
         <v>4000</v>
@@ -6375,10 +6378,10 @@
         <v>0</v>
       </c>
       <c r="N50" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O50" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P50" s="2"/>
     </row>
@@ -6387,7 +6390,7 @@
         <v>1045</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E51" s="2">
         <v>98</v>
@@ -6399,7 +6402,7 @@
         <v>1096</v>
       </c>
       <c r="H51" s="22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I51" s="2">
         <v>4000</v>
@@ -6417,10 +6420,10 @@
         <v>0</v>
       </c>
       <c r="N51" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O51" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P51" s="2"/>
     </row>
@@ -6429,7 +6432,7 @@
         <v>1046</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E52" s="2">
         <v>98</v>
@@ -6441,7 +6444,7 @@
         <v>1097</v>
       </c>
       <c r="H52" s="22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I52" s="2">
         <v>4000</v>
@@ -6459,10 +6462,10 @@
         <v>0</v>
       </c>
       <c r="N52" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O52" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P52" s="2"/>
     </row>
@@ -6471,7 +6474,7 @@
         <v>1047</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E53" s="2">
         <v>98</v>
@@ -6483,7 +6486,7 @@
         <v>1098</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I53" s="2">
         <v>4000</v>
@@ -6501,10 +6504,10 @@
         <v>0</v>
       </c>
       <c r="N53" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O53" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P53" s="2"/>
     </row>
@@ -6513,7 +6516,7 @@
         <v>1048</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E54" s="2">
         <v>98</v>
@@ -6525,7 +6528,7 @@
         <v>1099</v>
       </c>
       <c r="H54" s="22" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I54" s="2">
         <v>4000</v>
@@ -6543,10 +6546,10 @@
         <v>0</v>
       </c>
       <c r="N54" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O54" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P54" s="2"/>
     </row>
@@ -6555,7 +6558,7 @@
         <v>1049</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E55" s="2">
         <v>98</v>
@@ -6567,7 +6570,7 @@
         <v>1100</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I55" s="2">
         <v>4000</v>
@@ -6585,10 +6588,10 @@
         <v>0</v>
       </c>
       <c r="N55" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O55" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P55" s="2"/>
     </row>
@@ -6597,7 +6600,7 @@
         <v>1050</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E56" s="2">
         <v>98</v>
@@ -6609,7 +6612,7 @@
         <v>1101</v>
       </c>
       <c r="H56" s="22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I56" s="2">
         <v>4000</v>
@@ -6627,10 +6630,10 @@
         <v>0</v>
       </c>
       <c r="N56" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O56" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P56" s="2"/>
     </row>
@@ -6639,7 +6642,7 @@
         <v>1051</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E57" s="2">
         <v>98</v>
@@ -6651,7 +6654,7 @@
         <v>1102</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I57" s="2">
         <v>4000</v>
@@ -6669,10 +6672,10 @@
         <v>0</v>
       </c>
       <c r="N57" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O57" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P57" s="2"/>
     </row>
@@ -6681,7 +6684,7 @@
         <v>1052</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E58" s="2">
         <v>98</v>
@@ -6693,7 +6696,7 @@
         <v>1103</v>
       </c>
       <c r="H58" s="22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I58" s="2">
         <v>4000</v>
@@ -6711,10 +6714,10 @@
         <v>0</v>
       </c>
       <c r="N58" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O58" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P58" s="2"/>
     </row>
@@ -6723,7 +6726,7 @@
         <v>1053</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E59" s="2">
         <v>98</v>
@@ -6735,7 +6738,7 @@
         <v>1104</v>
       </c>
       <c r="H59" s="22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I59" s="2">
         <v>4000</v>
@@ -6753,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="N59" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O59" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P59" s="2"/>
     </row>
@@ -6765,7 +6768,7 @@
         <v>1054</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E60" s="12">
         <v>98</v>
@@ -6777,7 +6780,7 @@
         <v>1105</v>
       </c>
       <c r="H60" s="23" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I60" s="12">
         <v>20000</v>
@@ -6795,10 +6798,10 @@
         <v>0</v>
       </c>
       <c r="N60" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O60" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6806,7 +6809,7 @@
         <v>1055</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E61" s="2">
         <v>98</v>
@@ -6818,7 +6821,7 @@
         <v>1106</v>
       </c>
       <c r="H61" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I61" s="2">
         <v>20000</v>
@@ -6836,10 +6839,10 @@
         <v>0</v>
       </c>
       <c r="N61" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O61" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6847,7 +6850,7 @@
         <v>1056</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E62" s="2">
         <v>98</v>
@@ -6859,7 +6862,7 @@
         <v>1107</v>
       </c>
       <c r="H62" s="22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I62" s="2">
         <v>20000</v>
@@ -6877,10 +6880,10 @@
         <v>0</v>
       </c>
       <c r="N62" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O62" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -6888,7 +6891,7 @@
         <v>1057</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E63" s="2">
         <v>98</v>
@@ -6900,7 +6903,7 @@
         <v>1108</v>
       </c>
       <c r="H63" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I63" s="2">
         <v>20000</v>
@@ -6918,10 +6921,10 @@
         <v>0</v>
       </c>
       <c r="N63" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O63" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:16">
@@ -6929,7 +6932,7 @@
         <v>1058</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E64" s="2">
         <v>98</v>
@@ -6941,7 +6944,7 @@
         <v>1109</v>
       </c>
       <c r="H64" s="22" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I64" s="2">
         <v>20000</v>
@@ -6959,10 +6962,10 @@
         <v>0</v>
       </c>
       <c r="N64" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O64" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P64" s="2"/>
     </row>
@@ -6971,7 +6974,7 @@
         <v>1059</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E65" s="2">
         <v>98</v>
@@ -6983,7 +6986,7 @@
         <v>1110</v>
       </c>
       <c r="H65" s="22" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I65" s="2">
         <v>20000</v>
@@ -7001,10 +7004,10 @@
         <v>0</v>
       </c>
       <c r="N65" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O65" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -7012,7 +7015,7 @@
         <v>1060</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E66" s="2">
         <v>98</v>
@@ -7024,7 +7027,7 @@
         <v>1111</v>
       </c>
       <c r="H66" s="22" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I66" s="2">
         <v>20000</v>
@@ -7042,10 +7045,10 @@
         <v>0</v>
       </c>
       <c r="N66" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O66" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -7053,7 +7056,7 @@
         <v>1061</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E67" s="2">
         <v>98</v>
@@ -7065,7 +7068,7 @@
         <v>1112</v>
       </c>
       <c r="H67" s="22" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I67" s="2">
         <v>20000</v>
@@ -7083,10 +7086,10 @@
         <v>0</v>
       </c>
       <c r="N67" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O67" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -7094,7 +7097,7 @@
         <v>1062</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E68" s="2">
         <v>98</v>
@@ -7106,7 +7109,7 @@
         <v>1113</v>
       </c>
       <c r="H68" s="22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I68" s="2">
         <v>20000</v>
@@ -7124,10 +7127,10 @@
         <v>0</v>
       </c>
       <c r="N68" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O68" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:16">
@@ -7135,7 +7138,7 @@
         <v>1063</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E69" s="2">
         <v>98</v>
@@ -7147,7 +7150,7 @@
         <v>1114</v>
       </c>
       <c r="H69" s="22" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I69" s="2">
         <v>20000</v>
@@ -7165,10 +7168,10 @@
         <v>0</v>
       </c>
       <c r="N69" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O69" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P69" s="2"/>
     </row>
@@ -7177,7 +7180,7 @@
         <v>1064</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E70" s="2">
         <v>98</v>
@@ -7189,7 +7192,7 @@
         <v>1115</v>
       </c>
       <c r="H70" s="22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I70" s="2">
         <v>20000</v>
@@ -7207,10 +7210,10 @@
         <v>0</v>
       </c>
       <c r="N70" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O70" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P70" s="2"/>
     </row>
@@ -7219,7 +7222,7 @@
         <v>1065</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E71" s="2">
         <v>98</v>
@@ -7231,7 +7234,7 @@
         <v>1116</v>
       </c>
       <c r="H71" s="22" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I71" s="2">
         <v>20000</v>
@@ -7249,10 +7252,10 @@
         <v>0</v>
       </c>
       <c r="N71" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O71" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P71" s="2"/>
     </row>
@@ -7261,7 +7264,7 @@
         <v>1066</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E72" s="2">
         <v>98</v>
@@ -7273,7 +7276,7 @@
         <v>1117</v>
       </c>
       <c r="H72" s="22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I72" s="2">
         <v>20000</v>
@@ -7291,10 +7294,10 @@
         <v>0</v>
       </c>
       <c r="N72" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O72" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P72" s="2"/>
     </row>
@@ -7303,7 +7306,7 @@
         <v>1067</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E73" s="2">
         <v>98</v>
@@ -7315,7 +7318,7 @@
         <v>1118</v>
       </c>
       <c r="H73" s="22" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I73" s="2">
         <v>20000</v>
@@ -7333,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="N73" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O73" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P73" s="2"/>
     </row>
@@ -7345,7 +7348,7 @@
         <v>1068</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E74" s="2">
         <v>98</v>
@@ -7357,7 +7360,7 @@
         <v>1119</v>
       </c>
       <c r="H74" s="22" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I74" s="2">
         <v>20000</v>
@@ -7375,10 +7378,10 @@
         <v>0</v>
       </c>
       <c r="N74" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O74" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P74" s="2"/>
     </row>
@@ -7387,7 +7390,7 @@
         <v>1069</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E75" s="2">
         <v>98</v>
@@ -7399,7 +7402,7 @@
         <v>1120</v>
       </c>
       <c r="H75" s="22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I75" s="2">
         <v>20000</v>
@@ -7417,10 +7420,10 @@
         <v>0</v>
       </c>
       <c r="N75" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O75" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P75" s="2"/>
     </row>
@@ -7429,7 +7432,7 @@
         <v>1070</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E76" s="2">
         <v>98</v>
@@ -7441,7 +7444,7 @@
         <v>1121</v>
       </c>
       <c r="H76" s="22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I76" s="2">
         <v>20000</v>
@@ -7459,10 +7462,10 @@
         <v>0</v>
       </c>
       <c r="N76" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O76" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P76" s="2"/>
     </row>
@@ -7471,7 +7474,7 @@
         <v>1071</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E77" s="2">
         <v>98</v>
@@ -7483,7 +7486,7 @@
         <v>1122</v>
       </c>
       <c r="H77" s="22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I77" s="2">
         <v>20000</v>
@@ -7501,10 +7504,10 @@
         <v>0</v>
       </c>
       <c r="N77" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O77" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P77" s="2"/>
     </row>
@@ -7513,7 +7516,7 @@
         <v>1072</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E78" s="2">
         <v>98</v>
@@ -7525,7 +7528,7 @@
         <v>1123</v>
       </c>
       <c r="H78" s="22" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I78" s="2">
         <v>20000</v>
@@ -7543,10 +7546,10 @@
         <v>0</v>
       </c>
       <c r="N78" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O78" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P78" s="2"/>
     </row>
@@ -7555,7 +7558,7 @@
         <v>1073</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E79" s="2">
         <v>98</v>
@@ -7567,7 +7570,7 @@
         <v>1124</v>
       </c>
       <c r="H79" s="22" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I79" s="2">
         <v>20000</v>
@@ -7585,10 +7588,10 @@
         <v>0</v>
       </c>
       <c r="N79" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O79" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P79" s="2"/>
     </row>
@@ -7597,7 +7600,7 @@
         <v>1074</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E80" s="2">
         <v>98</v>
@@ -7609,7 +7612,7 @@
         <v>1125</v>
       </c>
       <c r="H80" s="22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I80" s="2">
         <v>20000</v>
@@ -7627,10 +7630,10 @@
         <v>0</v>
       </c>
       <c r="N80" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O80" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P80" s="2"/>
     </row>
@@ -7639,7 +7642,7 @@
         <v>1075</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E81" s="2">
         <v>98</v>
@@ -7651,7 +7654,7 @@
         <v>1126</v>
       </c>
       <c r="H81" s="22" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I81" s="2">
         <v>20000</v>
@@ -7669,10 +7672,10 @@
         <v>0</v>
       </c>
       <c r="N81" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O81" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P81" s="2"/>
     </row>
@@ -7681,7 +7684,7 @@
         <v>1076</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E82" s="2">
         <v>98</v>
@@ -7693,7 +7696,7 @@
         <v>1127</v>
       </c>
       <c r="H82" s="22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I82" s="2">
         <v>20000</v>
@@ -7711,10 +7714,10 @@
         <v>0</v>
       </c>
       <c r="N82" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O82" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P82" s="2"/>
     </row>
@@ -7723,7 +7726,7 @@
         <v>1077</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E83" s="2">
         <v>98</v>
@@ -7735,7 +7738,7 @@
         <v>1128</v>
       </c>
       <c r="H83" s="22" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I83" s="2">
         <v>20000</v>
@@ -7753,10 +7756,10 @@
         <v>0</v>
       </c>
       <c r="N83" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O83" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P83" s="2"/>
     </row>
@@ -7765,7 +7768,7 @@
         <v>1078</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E84" s="2">
         <v>98</v>
@@ -7777,7 +7780,7 @@
         <v>1129</v>
       </c>
       <c r="H84" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I84" s="2">
         <v>20000</v>
@@ -7795,10 +7798,10 @@
         <v>0</v>
       </c>
       <c r="N84" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O84" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P84" s="2"/>
     </row>
@@ -7807,7 +7810,7 @@
         <v>1079</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E85" s="2">
         <v>98</v>
@@ -7819,7 +7822,7 @@
         <v>1130</v>
       </c>
       <c r="H85" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I85" s="2">
         <v>20000</v>
@@ -7837,10 +7840,10 @@
         <v>0</v>
       </c>
       <c r="N85" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O85" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P85" s="2"/>
     </row>
@@ -7849,7 +7852,7 @@
         <v>1080</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E86" s="2">
         <v>98</v>
@@ -7861,7 +7864,7 @@
         <v>1131</v>
       </c>
       <c r="H86" s="22" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I86" s="2">
         <v>20000</v>
@@ -7879,10 +7882,10 @@
         <v>0</v>
       </c>
       <c r="N86" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O86" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P86" s="2"/>
     </row>
@@ -7891,7 +7894,7 @@
         <v>1081</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E87" s="2">
         <v>98</v>
@@ -7903,7 +7906,7 @@
         <v>1132</v>
       </c>
       <c r="H87" s="22" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I87" s="2">
         <v>20000</v>
@@ -7921,10 +7924,10 @@
         <v>0</v>
       </c>
       <c r="N87" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O87" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P87" s="2"/>
     </row>
@@ -7933,7 +7936,7 @@
         <v>1082</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E88" s="2">
         <v>98</v>
@@ -7945,7 +7948,7 @@
         <v>1133</v>
       </c>
       <c r="H88" s="22" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I88" s="2">
         <v>20000</v>
@@ -7963,10 +7966,10 @@
         <v>0</v>
       </c>
       <c r="N88" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O88" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P88" s="2"/>
     </row>
@@ -7975,7 +7978,7 @@
         <v>1083</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E89" s="2">
         <v>98</v>
@@ -7987,7 +7990,7 @@
         <v>1134</v>
       </c>
       <c r="H89" s="22" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I89" s="2">
         <v>20000</v>
@@ -8005,10 +8008,10 @@
         <v>0</v>
       </c>
       <c r="N89" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O89" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P89" s="2"/>
     </row>
@@ -8017,7 +8020,7 @@
         <v>1084</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E90" s="2">
         <v>98</v>
@@ -8029,7 +8032,7 @@
         <v>1135</v>
       </c>
       <c r="H90" s="22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I90" s="2">
         <v>20000</v>
@@ -8047,10 +8050,10 @@
         <v>0</v>
       </c>
       <c r="N90" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O90" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P90" s="2"/>
     </row>
@@ -8059,7 +8062,7 @@
         <v>1085</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E91" s="2">
         <v>98</v>
@@ -8071,7 +8074,7 @@
         <v>1136</v>
       </c>
       <c r="H91" s="22" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I91" s="2">
         <v>20000</v>
@@ -8089,10 +8092,10 @@
         <v>0</v>
       </c>
       <c r="N91" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O91" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P91" s="2"/>
     </row>
@@ -8101,7 +8104,7 @@
         <v>1086</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E92" s="2">
         <v>98</v>
@@ -8113,7 +8116,7 @@
         <v>1137</v>
       </c>
       <c r="H92" s="22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I92" s="2">
         <v>20000</v>
@@ -8131,10 +8134,10 @@
         <v>0</v>
       </c>
       <c r="N92" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O92" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P92" s="2"/>
     </row>
@@ -8143,7 +8146,7 @@
         <v>1087</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E93" s="2">
         <v>98</v>
@@ -8155,7 +8158,7 @@
         <v>1138</v>
       </c>
       <c r="H93" s="22" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I93" s="2">
         <v>20000</v>
@@ -8173,10 +8176,10 @@
         <v>0</v>
       </c>
       <c r="N93" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O93" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P93" s="2"/>
     </row>
@@ -8185,7 +8188,7 @@
         <v>1088</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E94" s="2">
         <v>98</v>
@@ -8197,7 +8200,7 @@
         <v>1139</v>
       </c>
       <c r="H94" s="22" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I94" s="2">
         <v>20000</v>
@@ -8215,10 +8218,10 @@
         <v>0</v>
       </c>
       <c r="N94" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O94" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P94" s="2"/>
     </row>
@@ -8227,7 +8230,7 @@
         <v>1089</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E95" s="12">
         <v>98</v>
@@ -8239,7 +8242,7 @@
         <v>1140</v>
       </c>
       <c r="H95" s="23" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I95" s="12">
         <v>30000</v>
@@ -8257,10 +8260,10 @@
         <v>0</v>
       </c>
       <c r="N95" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O95" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="96" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8268,7 +8271,7 @@
         <v>1090</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E96" s="2">
         <v>98</v>
@@ -8280,7 +8283,7 @@
         <v>1141</v>
       </c>
       <c r="H96" s="22" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I96" s="2">
         <v>30000</v>
@@ -8298,10 +8301,10 @@
         <v>0</v>
       </c>
       <c r="N96" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O96" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="97" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8309,7 +8312,7 @@
         <v>1091</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E97" s="2">
         <v>98</v>
@@ -8321,7 +8324,7 @@
         <v>1142</v>
       </c>
       <c r="H97" s="22" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I97" s="2">
         <v>30000</v>
@@ -8339,10 +8342,10 @@
         <v>0</v>
       </c>
       <c r="N97" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O97" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="98" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8350,7 +8353,7 @@
         <v>1092</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E98" s="2">
         <v>98</v>
@@ -8362,7 +8365,7 @@
         <v>1143</v>
       </c>
       <c r="H98" s="22" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I98" s="2">
         <v>30000</v>
@@ -8380,10 +8383,10 @@
         <v>0</v>
       </c>
       <c r="N98" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O98" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:16">
@@ -8391,7 +8394,7 @@
         <v>1093</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E99" s="2">
         <v>98</v>
@@ -8403,7 +8406,7 @@
         <v>1144</v>
       </c>
       <c r="H99" s="22" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I99" s="2">
         <v>30000</v>
@@ -8421,10 +8424,10 @@
         <v>0</v>
       </c>
       <c r="N99" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O99" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P99" s="2"/>
     </row>
@@ -8433,7 +8436,7 @@
         <v>1094</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E100" s="2">
         <v>98</v>
@@ -8445,7 +8448,7 @@
         <v>1145</v>
       </c>
       <c r="H100" s="22" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I100" s="2">
         <v>30000</v>
@@ -8463,10 +8466,10 @@
         <v>0</v>
       </c>
       <c r="N100" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O100" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="101" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8474,7 +8477,7 @@
         <v>1095</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E101" s="2">
         <v>98</v>
@@ -8486,7 +8489,7 @@
         <v>1146</v>
       </c>
       <c r="H101" s="22" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I101" s="2">
         <v>30000</v>
@@ -8504,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="N101" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O101" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="102" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8515,7 +8518,7 @@
         <v>1096</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E102" s="2">
         <v>98</v>
@@ -8527,7 +8530,7 @@
         <v>1147</v>
       </c>
       <c r="H102" s="22" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I102" s="2">
         <v>30000</v>
@@ -8545,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="N102" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O102" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="103" s="2" customFormat="1" customHeight="1" spans="3:15">
@@ -8556,7 +8559,7 @@
         <v>1097</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E103" s="2">
         <v>98</v>
@@ -8568,7 +8571,7 @@
         <v>1148</v>
       </c>
       <c r="H103" s="22" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I103" s="2">
         <v>30000</v>
@@ -8586,10 +8589,10 @@
         <v>0</v>
       </c>
       <c r="N103" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O103" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:16">
@@ -8597,7 +8600,7 @@
         <v>1098</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E104" s="2">
         <v>98</v>
@@ -8609,7 +8612,7 @@
         <v>1149</v>
       </c>
       <c r="H104" s="22" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I104" s="2">
         <v>30000</v>
@@ -8627,10 +8630,10 @@
         <v>0</v>
       </c>
       <c r="N104" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O104" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P104" s="2"/>
     </row>
@@ -8639,7 +8642,7 @@
         <v>1099</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E105" s="2">
         <v>98</v>
@@ -8651,7 +8654,7 @@
         <v>1150</v>
       </c>
       <c r="H105" s="22" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I105" s="2">
         <v>30000</v>
@@ -8669,10 +8672,10 @@
         <v>0</v>
       </c>
       <c r="N105" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O105" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P105" s="2"/>
     </row>
@@ -8681,7 +8684,7 @@
         <v>1100</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E106" s="2">
         <v>98</v>
@@ -8693,7 +8696,7 @@
         <v>1151</v>
       </c>
       <c r="H106" s="22" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I106" s="2">
         <v>30000</v>
@@ -8711,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="N106" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O106" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P106" s="2"/>
     </row>
@@ -8723,7 +8726,7 @@
         <v>1101</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E107" s="2">
         <v>98</v>
@@ -8735,7 +8738,7 @@
         <v>1152</v>
       </c>
       <c r="H107" s="22" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I107" s="2">
         <v>30000</v>
@@ -8753,10 +8756,10 @@
         <v>0</v>
       </c>
       <c r="N107" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O107" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P107" s="2"/>
     </row>
@@ -8765,7 +8768,7 @@
         <v>1102</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E108" s="2">
         <v>98</v>
@@ -8777,7 +8780,7 @@
         <v>1153</v>
       </c>
       <c r="H108" s="22" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I108" s="2">
         <v>30000</v>
@@ -8795,10 +8798,10 @@
         <v>0</v>
       </c>
       <c r="N108" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O108" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P108" s="2"/>
     </row>
@@ -8807,7 +8810,7 @@
         <v>1103</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E109" s="2">
         <v>98</v>
@@ -8819,7 +8822,7 @@
         <v>1154</v>
       </c>
       <c r="H109" s="22" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I109" s="2">
         <v>30000</v>
@@ -8837,10 +8840,10 @@
         <v>0</v>
       </c>
       <c r="N109" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O109" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P109" s="2"/>
     </row>
@@ -8849,7 +8852,7 @@
         <v>1104</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E110" s="2">
         <v>98</v>
@@ -8861,7 +8864,7 @@
         <v>1155</v>
       </c>
       <c r="H110" s="22" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I110" s="2">
         <v>30000</v>
@@ -8879,10 +8882,10 @@
         <v>0</v>
       </c>
       <c r="N110" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O110" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P110" s="2"/>
     </row>
@@ -8891,7 +8894,7 @@
         <v>1105</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E111" s="2">
         <v>98</v>
@@ -8903,7 +8906,7 @@
         <v>1156</v>
       </c>
       <c r="H111" s="22" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I111" s="2">
         <v>30000</v>
@@ -8921,10 +8924,10 @@
         <v>0</v>
       </c>
       <c r="N111" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O111" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P111" s="2"/>
     </row>
@@ -8933,7 +8936,7 @@
         <v>1106</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E112" s="2">
         <v>98</v>
@@ -8945,7 +8948,7 @@
         <v>1157</v>
       </c>
       <c r="H112" s="22" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I112" s="2">
         <v>30000</v>
@@ -8963,10 +8966,10 @@
         <v>0</v>
       </c>
       <c r="N112" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O112" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P112" s="2"/>
     </row>
@@ -8975,7 +8978,7 @@
         <v>1107</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E113" s="2">
         <v>98</v>
@@ -8987,7 +8990,7 @@
         <v>1158</v>
       </c>
       <c r="H113" s="22" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I113" s="2">
         <v>30000</v>
@@ -9005,10 +9008,10 @@
         <v>0</v>
       </c>
       <c r="N113" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O113" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P113" s="2"/>
     </row>
@@ -9017,7 +9020,7 @@
         <v>1108</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E114" s="2">
         <v>98</v>
@@ -9029,7 +9032,7 @@
         <v>1159</v>
       </c>
       <c r="H114" s="22" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I114" s="2">
         <v>30000</v>
@@ -9047,10 +9050,10 @@
         <v>0</v>
       </c>
       <c r="N114" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O114" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P114" s="2"/>
     </row>
@@ -9059,7 +9062,7 @@
         <v>1109</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E115" s="2">
         <v>98</v>
@@ -9071,7 +9074,7 @@
         <v>1160</v>
       </c>
       <c r="H115" s="22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I115" s="2">
         <v>30000</v>
@@ -9089,10 +9092,10 @@
         <v>0</v>
       </c>
       <c r="N115" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O115" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P115" s="2"/>
     </row>
@@ -9101,7 +9104,7 @@
         <v>1110</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E116" s="2">
         <v>98</v>
@@ -9113,7 +9116,7 @@
         <v>1161</v>
       </c>
       <c r="H116" s="22" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I116" s="2">
         <v>30000</v>
@@ -9131,10 +9134,10 @@
         <v>0</v>
       </c>
       <c r="N116" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O116" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P116" s="2"/>
     </row>
@@ -9143,7 +9146,7 @@
         <v>1111</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E117" s="2">
         <v>98</v>
@@ -9155,7 +9158,7 @@
         <v>1162</v>
       </c>
       <c r="H117" s="22" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I117" s="2">
         <v>30000</v>
@@ -9173,10 +9176,10 @@
         <v>0</v>
       </c>
       <c r="N117" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O117" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P117" s="2"/>
     </row>
@@ -9185,7 +9188,7 @@
         <v>1112</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E118" s="2">
         <v>98</v>
@@ -9197,7 +9200,7 @@
         <v>1163</v>
       </c>
       <c r="H118" s="22" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I118" s="2">
         <v>30000</v>
@@ -9215,10 +9218,10 @@
         <v>0</v>
       </c>
       <c r="N118" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O118" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P118" s="2"/>
     </row>
@@ -9227,7 +9230,7 @@
         <v>1113</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E119" s="2">
         <v>98</v>
@@ -9239,7 +9242,7 @@
         <v>1164</v>
       </c>
       <c r="H119" s="22" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I119" s="2">
         <v>30000</v>
@@ -9257,10 +9260,10 @@
         <v>0</v>
       </c>
       <c r="N119" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O119" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P119" s="2"/>
     </row>
@@ -9269,7 +9272,7 @@
         <v>1114</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E120" s="2">
         <v>98</v>
@@ -9281,7 +9284,7 @@
         <v>1165</v>
       </c>
       <c r="H120" s="22" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I120" s="2">
         <v>30000</v>
@@ -9299,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="N120" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O120" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P120" s="2"/>
     </row>
@@ -9311,7 +9314,7 @@
         <v>1115</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E121" s="2">
         <v>98</v>
@@ -9323,7 +9326,7 @@
         <v>1166</v>
       </c>
       <c r="H121" s="22" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I121" s="2">
         <v>30000</v>
@@ -9341,10 +9344,10 @@
         <v>0</v>
       </c>
       <c r="N121" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O121" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P121" s="2"/>
     </row>
@@ -9353,7 +9356,7 @@
         <v>1116</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E122" s="2">
         <v>98</v>
@@ -9365,7 +9368,7 @@
         <v>1167</v>
       </c>
       <c r="H122" s="22" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I122" s="2">
         <v>30000</v>
@@ -9383,10 +9386,10 @@
         <v>0</v>
       </c>
       <c r="N122" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O122" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P122" s="2"/>
     </row>
@@ -9395,7 +9398,7 @@
         <v>1117</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E123" s="2">
         <v>98</v>
@@ -9407,7 +9410,7 @@
         <v>1168</v>
       </c>
       <c r="H123" s="22" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I123" s="2">
         <v>30000</v>
@@ -9425,10 +9428,10 @@
         <v>0</v>
       </c>
       <c r="N123" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O123" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P123" s="2"/>
     </row>
@@ -9437,7 +9440,7 @@
         <v>1118</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E124" s="2">
         <v>98</v>
@@ -9449,7 +9452,7 @@
         <v>1169</v>
       </c>
       <c r="H124" s="22" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I124" s="2">
         <v>30000</v>
@@ -9467,10 +9470,10 @@
         <v>0</v>
       </c>
       <c r="N124" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O124" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P124" s="2"/>
     </row>
@@ -9479,7 +9482,7 @@
         <v>1119</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E125" s="2">
         <v>98</v>
@@ -9491,7 +9494,7 @@
         <v>1170</v>
       </c>
       <c r="H125" s="22" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I125" s="2">
         <v>30000</v>
@@ -9509,10 +9512,10 @@
         <v>0</v>
       </c>
       <c r="N125" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O125" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P125" s="2"/>
     </row>
@@ -9521,7 +9524,7 @@
         <v>1120</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E126" s="2">
         <v>98</v>
@@ -9533,7 +9536,7 @@
         <v>1171</v>
       </c>
       <c r="H126" s="22" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I126" s="2">
         <v>30000</v>
@@ -9551,10 +9554,10 @@
         <v>0</v>
       </c>
       <c r="N126" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O126" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P126" s="2"/>
     </row>
@@ -9563,7 +9566,7 @@
         <v>1121</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E127" s="2">
         <v>98</v>
@@ -9575,7 +9578,7 @@
         <v>1172</v>
       </c>
       <c r="H127" s="22" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I127" s="2">
         <v>30000</v>
@@ -9593,10 +9596,10 @@
         <v>0</v>
       </c>
       <c r="N127" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O127" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P127" s="2"/>
     </row>
@@ -9605,7 +9608,7 @@
         <v>1122</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E128" s="2">
         <v>98</v>
@@ -9617,7 +9620,7 @@
         <v>1173</v>
       </c>
       <c r="H128" s="22" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I128" s="2">
         <v>30000</v>
@@ -9635,10 +9638,10 @@
         <v>0</v>
       </c>
       <c r="N128" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O128" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P128" s="2"/>
     </row>
@@ -9647,7 +9650,7 @@
         <v>1123</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E129" s="2">
         <v>98</v>
@@ -9659,7 +9662,7 @@
         <v>1174</v>
       </c>
       <c r="H129" s="22" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I129" s="2">
         <v>30000</v>
@@ -9677,10 +9680,10 @@
         <v>0</v>
       </c>
       <c r="N129" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O129" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P129" s="2"/>
     </row>
@@ -9689,7 +9692,7 @@
         <v>1124</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E130" s="12">
         <v>98</v>
@@ -9701,7 +9704,7 @@
         <v>1175</v>
       </c>
       <c r="H130" s="23" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I130" s="12">
         <v>60000</v>
@@ -9719,10 +9722,10 @@
         <v>0</v>
       </c>
       <c r="N130" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O130" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="131" customHeight="1" spans="3:15">
@@ -9730,7 +9733,7 @@
         <v>1125</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E131" s="2">
         <v>98</v>
@@ -9742,7 +9745,7 @@
         <v>1176</v>
       </c>
       <c r="H131" s="22" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I131" s="17">
         <v>60000</v>
@@ -9760,10 +9763,10 @@
         <v>0</v>
       </c>
       <c r="N131" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O131" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="132" customHeight="1" spans="3:15">
@@ -9771,7 +9774,7 @@
         <v>1126</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E132" s="2">
         <v>98</v>
@@ -9783,7 +9786,7 @@
         <v>1177</v>
       </c>
       <c r="H132" s="22" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I132" s="17">
         <v>60000</v>
@@ -9801,10 +9804,10 @@
         <v>0</v>
       </c>
       <c r="N132" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O132" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="3:15">
@@ -9812,7 +9815,7 @@
         <v>1127</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E133" s="2">
         <v>98</v>
@@ -9824,7 +9827,7 @@
         <v>1178</v>
       </c>
       <c r="H133" s="22" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I133" s="17">
         <v>60000</v>
@@ -9842,10 +9845,10 @@
         <v>0</v>
       </c>
       <c r="N133" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O133" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="3:15">
@@ -9853,7 +9856,7 @@
         <v>1128</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E134" s="2">
         <v>98</v>
@@ -9865,7 +9868,7 @@
         <v>1179</v>
       </c>
       <c r="H134" s="22" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I134" s="17">
         <v>60000</v>
@@ -9883,10 +9886,10 @@
         <v>0</v>
       </c>
       <c r="N134" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O134" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="3:15">
@@ -9894,7 +9897,7 @@
         <v>1129</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E135" s="2">
         <v>98</v>
@@ -9906,7 +9909,7 @@
         <v>1180</v>
       </c>
       <c r="H135" s="22" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I135" s="17">
         <v>60000</v>
@@ -9924,10 +9927,10 @@
         <v>0</v>
       </c>
       <c r="N135" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O135" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="3:15">
@@ -9935,7 +9938,7 @@
         <v>1130</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E136" s="2">
         <v>98</v>
@@ -9947,7 +9950,7 @@
         <v>1181</v>
       </c>
       <c r="H136" s="22" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="I136" s="17">
         <v>60000</v>
@@ -9965,10 +9968,10 @@
         <v>0</v>
       </c>
       <c r="N136" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O136" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="3:15">
@@ -9976,7 +9979,7 @@
         <v>1131</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E137" s="2">
         <v>98</v>
@@ -9988,7 +9991,7 @@
         <v>1182</v>
       </c>
       <c r="H137" s="22" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I137" s="17">
         <v>60000</v>
@@ -10006,10 +10009,10 @@
         <v>0</v>
       </c>
       <c r="N137" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O137" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="3:15">
@@ -10017,7 +10020,7 @@
         <v>1132</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E138" s="2">
         <v>98</v>
@@ -10029,7 +10032,7 @@
         <v>1183</v>
       </c>
       <c r="H138" s="22" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="I138" s="17">
         <v>60000</v>
@@ -10047,10 +10050,10 @@
         <v>0</v>
       </c>
       <c r="N138" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O138" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="3:15">
@@ -10058,7 +10061,7 @@
         <v>1133</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E139" s="2">
         <v>98</v>
@@ -10070,7 +10073,7 @@
         <v>1184</v>
       </c>
       <c r="H139" s="22" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I139" s="17">
         <v>60000</v>
@@ -10088,10 +10091,10 @@
         <v>0</v>
       </c>
       <c r="N139" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O139" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="3:15">
@@ -10099,7 +10102,7 @@
         <v>1134</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E140" s="2">
         <v>98</v>
@@ -10111,7 +10114,7 @@
         <v>1185</v>
       </c>
       <c r="H140" s="22" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I140" s="17">
         <v>60000</v>
@@ -10129,10 +10132,10 @@
         <v>0</v>
       </c>
       <c r="N140" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O140" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="141" customHeight="1" spans="3:15">
@@ -10140,7 +10143,7 @@
         <v>1135</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E141" s="2">
         <v>98</v>
@@ -10152,7 +10155,7 @@
         <v>1186</v>
       </c>
       <c r="H141" s="22" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I141" s="17">
         <v>60000</v>
@@ -10170,10 +10173,10 @@
         <v>0</v>
       </c>
       <c r="N141" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O141" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="142" customHeight="1" spans="3:15">
@@ -10181,7 +10184,7 @@
         <v>1136</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E142" s="2">
         <v>98</v>
@@ -10193,7 +10196,7 @@
         <v>1187</v>
       </c>
       <c r="H142" s="22" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I142" s="17">
         <v>60000</v>
@@ -10211,10 +10214,10 @@
         <v>0</v>
       </c>
       <c r="N142" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O142" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="143" customHeight="1" spans="3:15">
@@ -10222,7 +10225,7 @@
         <v>1137</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E143" s="2">
         <v>98</v>
@@ -10234,7 +10237,7 @@
         <v>1188</v>
       </c>
       <c r="H143" s="22" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I143" s="17">
         <v>60000</v>
@@ -10252,10 +10255,10 @@
         <v>0</v>
       </c>
       <c r="N143" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O143" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="144" customHeight="1" spans="3:15">
@@ -10263,7 +10266,7 @@
         <v>1138</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E144" s="2">
         <v>98</v>
@@ -10275,7 +10278,7 @@
         <v>1189</v>
       </c>
       <c r="H144" s="22" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I144" s="17">
         <v>60000</v>
@@ -10293,10 +10296,10 @@
         <v>0</v>
       </c>
       <c r="N144" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O144" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="145" customHeight="1" spans="3:15">
@@ -10304,7 +10307,7 @@
         <v>1139</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E145" s="2">
         <v>98</v>
@@ -10316,7 +10319,7 @@
         <v>1190</v>
       </c>
       <c r="H145" s="22" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I145" s="17">
         <v>60000</v>
@@ -10334,10 +10337,10 @@
         <v>0</v>
       </c>
       <c r="N145" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O145" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="146" customHeight="1" spans="3:15">
@@ -10345,7 +10348,7 @@
         <v>1140</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E146" s="2">
         <v>98</v>
@@ -10357,7 +10360,7 @@
         <v>1191</v>
       </c>
       <c r="H146" s="22" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I146" s="17">
         <v>60000</v>
@@ -10375,10 +10378,10 @@
         <v>0</v>
       </c>
       <c r="N146" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O146" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="147" customHeight="1" spans="3:15">
@@ -10386,7 +10389,7 @@
         <v>1141</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E147" s="2">
         <v>98</v>
@@ -10398,7 +10401,7 @@
         <v>1192</v>
       </c>
       <c r="H147" s="22" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I147" s="17">
         <v>60000</v>
@@ -10416,10 +10419,10 @@
         <v>0</v>
       </c>
       <c r="N147" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O147" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="148" customHeight="1" spans="3:15">
@@ -10427,7 +10430,7 @@
         <v>1142</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E148" s="2">
         <v>98</v>
@@ -10439,7 +10442,7 @@
         <v>1193</v>
       </c>
       <c r="H148" s="22" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I148" s="17">
         <v>60000</v>
@@ -10457,10 +10460,10 @@
         <v>0</v>
       </c>
       <c r="N148" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O148" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="149" customHeight="1" spans="3:15">
@@ -10468,7 +10471,7 @@
         <v>1143</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E149" s="2">
         <v>98</v>
@@ -10480,7 +10483,7 @@
         <v>1194</v>
       </c>
       <c r="H149" s="22" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I149" s="17">
         <v>60000</v>
@@ -10498,10 +10501,10 @@
         <v>0</v>
       </c>
       <c r="N149" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O149" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="150" customHeight="1" spans="3:15">
@@ -10509,7 +10512,7 @@
         <v>1144</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E150" s="2">
         <v>98</v>
@@ -10521,7 +10524,7 @@
         <v>1195</v>
       </c>
       <c r="H150" s="22" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I150" s="17">
         <v>60000</v>
@@ -10539,10 +10542,10 @@
         <v>0</v>
       </c>
       <c r="N150" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O150" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="151" customHeight="1" spans="3:15">
@@ -10550,7 +10553,7 @@
         <v>1145</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E151" s="2">
         <v>98</v>
@@ -10562,7 +10565,7 @@
         <v>1196</v>
       </c>
       <c r="H151" s="22" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I151" s="17">
         <v>60000</v>
@@ -10580,10 +10583,10 @@
         <v>0</v>
       </c>
       <c r="N151" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O151" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="152" customHeight="1" spans="3:15">
@@ -10591,7 +10594,7 @@
         <v>1146</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E152" s="2">
         <v>98</v>
@@ -10603,7 +10606,7 @@
         <v>1197</v>
       </c>
       <c r="H152" s="22" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I152" s="17">
         <v>60000</v>
@@ -10621,10 +10624,10 @@
         <v>0</v>
       </c>
       <c r="N152" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O152" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="153" customHeight="1" spans="3:15">
@@ -10632,7 +10635,7 @@
         <v>1147</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E153" s="2">
         <v>98</v>
@@ -10644,7 +10647,7 @@
         <v>1198</v>
       </c>
       <c r="H153" s="22" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I153" s="17">
         <v>60000</v>
@@ -10662,10 +10665,10 @@
         <v>0</v>
       </c>
       <c r="N153" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O153" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="154" customHeight="1" spans="3:15">
@@ -10673,7 +10676,7 @@
         <v>1148</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E154" s="2">
         <v>98</v>
@@ -10685,7 +10688,7 @@
         <v>1199</v>
       </c>
       <c r="H154" s="22" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="I154" s="17">
         <v>60000</v>
@@ -10703,10 +10706,10 @@
         <v>0</v>
       </c>
       <c r="N154" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O154" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="155" customHeight="1" spans="3:15">
@@ -10714,7 +10717,7 @@
         <v>1149</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E155" s="2">
         <v>98</v>
@@ -10726,7 +10729,7 @@
         <v>1200</v>
       </c>
       <c r="H155" s="22" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="I155" s="17">
         <v>60000</v>
@@ -10744,10 +10747,10 @@
         <v>0</v>
       </c>
       <c r="N155" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O155" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="156" customHeight="1" spans="3:15">
@@ -10755,7 +10758,7 @@
         <v>1150</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E156" s="2">
         <v>98</v>
@@ -10767,7 +10770,7 @@
         <v>1201</v>
       </c>
       <c r="H156" s="22" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I156" s="17">
         <v>60000</v>
@@ -10785,10 +10788,10 @@
         <v>0</v>
       </c>
       <c r="N156" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O156" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="157" customHeight="1" spans="3:15">
@@ -10796,7 +10799,7 @@
         <v>1151</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E157" s="2">
         <v>98</v>
@@ -10808,7 +10811,7 @@
         <v>1202</v>
       </c>
       <c r="H157" s="22" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I157" s="17">
         <v>60000</v>
@@ -10826,10 +10829,10 @@
         <v>0</v>
       </c>
       <c r="N157" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O157" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="158" customHeight="1" spans="3:15">
@@ -10837,7 +10840,7 @@
         <v>1152</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E158" s="2">
         <v>98</v>
@@ -10849,7 +10852,7 @@
         <v>1203</v>
       </c>
       <c r="H158" s="22" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I158" s="17">
         <v>60000</v>
@@ -10867,10 +10870,10 @@
         <v>0</v>
       </c>
       <c r="N158" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O158" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="159" customHeight="1" spans="3:15">
@@ -10878,7 +10881,7 @@
         <v>1153</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E159" s="2">
         <v>98</v>
@@ -10890,7 +10893,7 @@
         <v>1204</v>
       </c>
       <c r="H159" s="22" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="I159" s="17">
         <v>60000</v>
@@ -10908,10 +10911,10 @@
         <v>0</v>
       </c>
       <c r="N159" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O159" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="160" customHeight="1" spans="3:15">
@@ -10919,7 +10922,7 @@
         <v>1154</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E160" s="2">
         <v>98</v>
@@ -10931,7 +10934,7 @@
         <v>1205</v>
       </c>
       <c r="H160" s="22" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I160" s="17">
         <v>60000</v>
@@ -10949,10 +10952,10 @@
         <v>0</v>
       </c>
       <c r="N160" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O160" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="161" customHeight="1" spans="3:15">
@@ -10960,7 +10963,7 @@
         <v>1155</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E161" s="2">
         <v>98</v>
@@ -10972,7 +10975,7 @@
         <v>1206</v>
       </c>
       <c r="H161" s="22" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I161" s="17">
         <v>60000</v>
@@ -10990,10 +10993,10 @@
         <v>0</v>
       </c>
       <c r="N161" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O161" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="162" customHeight="1" spans="3:15">
@@ -11001,7 +11004,7 @@
         <v>1156</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E162" s="2">
         <v>98</v>
@@ -11013,7 +11016,7 @@
         <v>1207</v>
       </c>
       <c r="H162" s="22" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I162" s="17">
         <v>60000</v>
@@ -11031,10 +11034,10 @@
         <v>0</v>
       </c>
       <c r="N162" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O162" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="163" customHeight="1" spans="3:15">
@@ -11042,7 +11045,7 @@
         <v>1157</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E163" s="2">
         <v>98</v>
@@ -11054,7 +11057,7 @@
         <v>1208</v>
       </c>
       <c r="H163" s="22" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I163" s="17">
         <v>60000</v>
@@ -11072,10 +11075,10 @@
         <v>0</v>
       </c>
       <c r="N163" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O163" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="164" customHeight="1" spans="3:15">
@@ -11083,7 +11086,7 @@
         <v>1158</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E164" s="2">
         <v>98</v>
@@ -11095,7 +11098,7 @@
         <v>1209</v>
       </c>
       <c r="H164" s="22" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I164" s="17">
         <v>60000</v>
@@ -11113,10 +11116,10 @@
         <v>0</v>
       </c>
       <c r="N164" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O164" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -11309,7 +11312,7 @@
         <v>2000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -11321,7 +11324,7 @@
         <v>1070</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I6" s="2">
         <v>120000</v>
@@ -11342,10 +11345,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P6" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11353,7 +11356,7 @@
         <v>2001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -11365,7 +11368,7 @@
         <v>1071</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="I7" s="2">
         <v>120000</v>
@@ -11386,10 +11389,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P7" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11397,7 +11400,7 @@
         <v>2002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -11409,7 +11412,7 @@
         <v>1072</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="I8" s="2">
         <v>120000</v>
@@ -11430,10 +11433,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P8" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11441,7 +11444,7 @@
         <v>2003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -11453,7 +11456,7 @@
         <v>1073</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I9" s="2">
         <v>120000</v>
@@ -11474,10 +11477,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P9" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11485,7 +11488,7 @@
         <v>2004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -11497,7 +11500,7 @@
         <v>1074</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="I10" s="2">
         <v>120000</v>
@@ -11518,10 +11521,10 @@
         <v>0</v>
       </c>
       <c r="O10" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P10" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11529,7 +11532,7 @@
         <v>2005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -11541,7 +11544,7 @@
         <v>1104</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="I11" s="2">
         <v>20000</v>
@@ -11562,10 +11565,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P11" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
@@ -11587,7 +11590,7 @@
         <v>2006</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -11599,7 +11602,7 @@
         <v>1105</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I14" s="2">
         <v>360000</v>
@@ -11620,10 +11623,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P14" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11631,7 +11634,7 @@
         <v>2007</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -11643,7 +11646,7 @@
         <v>1106</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="I15" s="2">
         <v>360000</v>
@@ -11664,10 +11667,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P15" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11675,7 +11678,7 @@
         <v>2008</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -11687,7 +11690,7 @@
         <v>1107</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I16" s="2">
         <v>360000</v>
@@ -11708,10 +11711,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P16" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11719,7 +11722,7 @@
         <v>2009</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -11731,7 +11734,7 @@
         <v>1108</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="I17" s="2">
         <v>360000</v>
@@ -11752,10 +11755,10 @@
         <v>0</v>
       </c>
       <c r="O17" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P17" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11763,7 +11766,7 @@
         <v>2010</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -11775,7 +11778,7 @@
         <v>1139</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I18" s="2">
         <v>360000</v>
@@ -11796,10 +11799,10 @@
         <v>0</v>
       </c>
       <c r="O18" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P18" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11807,7 +11810,7 @@
         <v>2011</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -11819,7 +11822,7 @@
         <v>1139</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -11840,10 +11843,10 @@
         <v>0</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P19" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
@@ -11858,7 +11861,7 @@
         <v>2012</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -11870,7 +11873,7 @@
         <v>1140</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I21" s="2">
         <v>360000</v>
@@ -11891,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="O21" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P21" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11902,7 +11905,7 @@
         <v>2013</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -11914,7 +11917,7 @@
         <v>1141</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="I22" s="2">
         <v>360000</v>
@@ -11935,10 +11938,10 @@
         <v>0</v>
       </c>
       <c r="O22" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P22" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11946,7 +11949,7 @@
         <v>2014</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -11958,7 +11961,7 @@
         <v>1142</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I23" s="2">
         <v>360000</v>
@@ -11979,10 +11982,10 @@
         <v>0</v>
       </c>
       <c r="O23" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P23" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -11990,7 +11993,7 @@
         <v>2015</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -12002,7 +12005,7 @@
         <v>1143</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I24" s="2">
         <v>360000</v>
@@ -12023,10 +12026,10 @@
         <v>0</v>
       </c>
       <c r="O24" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P24" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -12034,7 +12037,7 @@
         <v>2016</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -12046,7 +12049,7 @@
         <v>1209</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I25" s="2">
         <v>360000</v>
@@ -12067,10 +12070,10 @@
         <v>0</v>
       </c>
       <c r="O25" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P25" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
@@ -12078,7 +12081,7 @@
         <v>2017</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -12090,7 +12093,7 @@
         <v>1209</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I26" s="2">
         <v>180000</v>
@@ -12111,24 +12114,24 @@
         <v>0</v>
       </c>
       <c r="O26" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P26" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C27" s="2">
         <v>2018</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -12140,7 +12143,7 @@
         <v>1174</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>
@@ -12161,10 +12164,10 @@
         <v>0</v>
       </c>
       <c r="O27" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P27" s="20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>教师节</t>
+    <t>国庆节</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>2025-09-12</t>
+    <t>2025-10-01</t>
+  </si>
+  <si>
+    <t>2025-10-10</t>
   </si>
   <si>
     <t>平时部分掉落</t>
@@ -1856,12 +1856,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-10-01</t>
-  </si>
-  <si>
-    <t>2025-10-10</t>
+    <t>2025-09-30</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
   </si>
   <si>
     <t>平时部分掉落</t>
@@ -1856,12 +1856,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -349,7 +349,7 @@
     <t>2025-09-30</t>
   </si>
   <si>
-    <t>2025-10-09</t>
+    <t>2025-10-16</t>
   </si>
   <si>
     <t>平时部分掉落</t>
@@ -1856,12 +1856,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -349,7 +349,7 @@
     <t>2025-09-30</t>
   </si>
   <si>
-    <t>2025-10-16</t>
+    <t>2025-10-07</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>国庆节</t>
+    <t>快乐11</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-09-30</t>
-  </si>
-  <si>
-    <t>2025-10-07</t>
+    <t>2025-11-07</t>
+  </si>
+  <si>
+    <t>2025-11-15</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>快乐11</t>
+    <t>快乐12</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-11-07</t>
-  </si>
-  <si>
-    <t>2025-11-15</t>
+    <t>2025-12-03</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
   </si>
   <si>
     <t>平时部分掉落</t>
@@ -2344,11 +2344,11 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2709,7 +2709,7 @@
     <col min="18" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" customHeight="1" spans="8:16">
+    <row r="1" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
@@ -2748,31 +2748,31 @@
       <c r="G3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="P3" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2792,31 +2792,31 @@
       <c r="G4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="N4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="10" t="s">
+      <c r="P4" s="8" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2857,10 +2857,10 @@
       <c r="N5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="P5" s="10" t="s">
+      <c r="P5" s="8" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="8:16">
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
       <c r="K25" s="11">
@@ -3949,7 +3949,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="9:16">
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="I34" s="11"/>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
@@ -4283,7 +4283,7 @@
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1"/>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="8:16">
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="H44" s="18"/>
       <c r="I44" s="18"/>
       <c r="J44" s="18"/>
@@ -4294,7 +4294,7 @@
       <c r="O44" s="18"/>
       <c r="P44" s="18"/>
     </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="8:16">
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="H45" s="18"/>
       <c r="I45" s="18"/>
       <c r="J45" s="18"/>
@@ -4305,7 +4305,7 @@
       <c r="O45" s="18"/>
       <c r="P45" s="18"/>
     </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="8:16">
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="H46" s="18"/>
       <c r="I46" s="18"/>
       <c r="J46" s="18"/>
@@ -4316,7 +4316,7 @@
       <c r="O46" s="18"/>
       <c r="P46" s="18"/>
     </row>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="8:16">
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="H47" s="18"/>
       <c r="I47" s="18"/>
       <c r="J47" s="18"/>
@@ -4378,7 +4378,7 @@
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="8:15">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -4424,13 +4424,13 @@
       <c r="J3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="8" t="s">
         <v>11</v>
       </c>
       <c r="N3" s="7" t="s">
@@ -4465,13 +4465,13 @@
       <c r="J4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="8" t="s">
         <v>19</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="8" t="s">
         <v>11</v>
       </c>
       <c r="N4" s="7" t="s">
@@ -4532,10 +4532,10 @@
       <c r="E6" s="2">
         <v>98</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="9">
         <v>1051</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="9">
         <v>1051</v>
       </c>
       <c r="H6" s="22" t="s">
@@ -4573,10 +4573,10 @@
       <c r="E7" s="2">
         <v>98</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="9">
         <v>1052</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="9">
         <v>1052</v>
       </c>
       <c r="H7" s="22" t="s">
@@ -4614,10 +4614,10 @@
       <c r="E8" s="2">
         <v>98</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="9">
         <v>1053</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="9">
         <v>1053</v>
       </c>
       <c r="H8" s="22" t="s">
@@ -4655,10 +4655,10 @@
       <c r="E9" s="2">
         <v>98</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="9">
         <v>1054</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="9">
         <v>1054</v>
       </c>
       <c r="H9" s="22" t="s">
@@ -4696,10 +4696,10 @@
       <c r="E10" s="2">
         <v>98</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="9">
         <v>1055</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="9">
         <v>1055</v>
       </c>
       <c r="H10" s="22" t="s">
@@ -4737,10 +4737,10 @@
       <c r="E11" s="2">
         <v>98</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="9">
         <v>1056</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="9">
         <v>1056</v>
       </c>
       <c r="H11" s="22" t="s">
@@ -4778,10 +4778,10 @@
       <c r="E12" s="2">
         <v>98</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="9">
         <v>1057</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="9">
         <v>1057</v>
       </c>
       <c r="H12" s="22" t="s">
@@ -4819,10 +4819,10 @@
       <c r="E13" s="2">
         <v>98</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="9">
         <v>1058</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="9">
         <v>1058</v>
       </c>
       <c r="H13" s="22" t="s">
@@ -4860,10 +4860,10 @@
       <c r="E14" s="2">
         <v>98</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="9">
         <v>1059</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="9">
         <v>1059</v>
       </c>
       <c r="H14" s="22" t="s">
@@ -4901,10 +4901,10 @@
       <c r="E15" s="2">
         <v>98</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="9">
         <v>1060</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="9">
         <v>1060</v>
       </c>
       <c r="H15" s="22" t="s">
@@ -4942,10 +4942,10 @@
       <c r="E16" s="2">
         <v>98</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="9">
         <v>1061</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="9">
         <v>1061</v>
       </c>
       <c r="H16" s="22" t="s">
@@ -4973,7 +4973,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C17" s="2">
         <v>1011</v>
       </c>
@@ -4983,10 +4983,10 @@
       <c r="E17" s="2">
         <v>98</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="9">
         <v>1062</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="9">
         <v>1062</v>
       </c>
       <c r="H17" s="22" t="s">
@@ -5014,7 +5014,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C18" s="2">
         <v>1012</v>
       </c>
@@ -5024,10 +5024,10 @@
       <c r="E18" s="2">
         <v>98</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="9">
         <v>1063</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="9">
         <v>1063</v>
       </c>
       <c r="H18" s="22" t="s">
@@ -5055,7 +5055,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C19" s="2">
         <v>1013</v>
       </c>
@@ -5065,10 +5065,10 @@
       <c r="E19" s="2">
         <v>98</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="9">
         <v>1064</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="9">
         <v>1064</v>
       </c>
       <c r="H19" s="22" t="s">
@@ -5096,7 +5096,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C20" s="2">
         <v>1014</v>
       </c>
@@ -5106,10 +5106,10 @@
       <c r="E20" s="2">
         <v>98</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="9">
         <v>1065</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="9">
         <v>1065</v>
       </c>
       <c r="H20" s="22" t="s">
@@ -5137,7 +5137,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C21" s="2">
         <v>1015</v>
       </c>
@@ -5147,10 +5147,10 @@
       <c r="E21" s="2">
         <v>98</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="9">
         <v>1066</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="9">
         <v>1066</v>
       </c>
       <c r="H21" s="22" t="s">
@@ -5178,7 +5178,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C22" s="2">
         <v>1016</v>
       </c>
@@ -5188,10 +5188,10 @@
       <c r="E22" s="2">
         <v>98</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="9">
         <v>1067</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="9">
         <v>1067</v>
       </c>
       <c r="H22" s="22" t="s">
@@ -5219,7 +5219,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C23" s="2">
         <v>1017</v>
       </c>
@@ -5229,10 +5229,10 @@
       <c r="E23" s="2">
         <v>98</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="9">
         <v>1068</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="9">
         <v>1068</v>
       </c>
       <c r="H23" s="22" t="s">
@@ -5260,7 +5260,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C24" s="2">
         <v>1018</v>
       </c>
@@ -5270,10 +5270,10 @@
       <c r="E24" s="2">
         <v>98</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="9">
         <v>1069</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="9">
         <v>1069</v>
       </c>
       <c r="H24" s="22" t="s">
@@ -5301,7 +5301,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C25" s="2">
         <v>1019</v>
       </c>
@@ -5311,10 +5311,10 @@
       <c r="E25" s="2">
         <v>98</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="9">
         <v>1070</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="9">
         <v>1070</v>
       </c>
       <c r="H25" s="22" t="s">
@@ -5342,7 +5342,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C26" s="2">
         <v>1020</v>
       </c>
@@ -5352,10 +5352,10 @@
       <c r="E26" s="2">
         <v>98</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="9">
         <v>1071</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="9">
         <v>1071</v>
       </c>
       <c r="H26" s="22" t="s">
@@ -5383,7 +5383,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C27" s="2">
         <v>1021</v>
       </c>
@@ -5393,10 +5393,10 @@
       <c r="E27" s="2">
         <v>98</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="9">
         <v>1072</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="9">
         <v>1072</v>
       </c>
       <c r="H27" s="22" t="s">
@@ -5424,7 +5424,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C28" s="2">
         <v>1022</v>
       </c>
@@ -5434,10 +5434,10 @@
       <c r="E28" s="2">
         <v>98</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="9">
         <v>1073</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="9">
         <v>1073</v>
       </c>
       <c r="H28" s="22" t="s">
@@ -5475,10 +5475,10 @@
       <c r="E29" s="2">
         <v>98</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="9">
         <v>1074</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="9">
         <v>1074</v>
       </c>
       <c r="H29" s="22" t="s">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="P29" s="2"/>
     </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C30" s="2">
         <v>1024</v>
       </c>
@@ -5517,10 +5517,10 @@
       <c r="E30" s="2">
         <v>98</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="9">
         <v>1075</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="9">
         <v>1075</v>
       </c>
       <c r="H30" s="22" t="s">
@@ -5548,7 +5548,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C31" s="2">
         <v>1025</v>
       </c>
@@ -5558,10 +5558,10 @@
       <c r="E31" s="2">
         <v>98</v>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="9">
         <v>1076</v>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="9">
         <v>1076</v>
       </c>
       <c r="H31" s="22" t="s">
@@ -5589,7 +5589,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C32" s="2">
         <v>1026</v>
       </c>
@@ -5599,10 +5599,10 @@
       <c r="E32" s="2">
         <v>98</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="9">
         <v>1077</v>
       </c>
-      <c r="G32" s="8">
+      <c r="G32" s="9">
         <v>1077</v>
       </c>
       <c r="H32" s="22" t="s">
@@ -5630,7 +5630,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C33" s="2">
         <v>1027</v>
       </c>
@@ -5640,10 +5640,10 @@
       <c r="E33" s="2">
         <v>98</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="9">
         <v>1078</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="9">
         <v>1078</v>
       </c>
       <c r="H33" s="22" t="s">
@@ -5681,10 +5681,10 @@
       <c r="E34" s="2">
         <v>98</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="9">
         <v>1079</v>
       </c>
-      <c r="G34" s="8">
+      <c r="G34" s="9">
         <v>1079</v>
       </c>
       <c r="H34" s="22" t="s">
@@ -5723,10 +5723,10 @@
       <c r="E35" s="2">
         <v>98</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="9">
         <v>1080</v>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="9">
         <v>1080</v>
       </c>
       <c r="H35" s="22" t="s">
@@ -5765,10 +5765,10 @@
       <c r="E36" s="2">
         <v>98</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="9">
         <v>1081</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="9">
         <v>1081</v>
       </c>
       <c r="H36" s="22" t="s">
@@ -5807,10 +5807,10 @@
       <c r="E37" s="2">
         <v>98</v>
       </c>
-      <c r="F37" s="8">
+      <c r="F37" s="9">
         <v>1082</v>
       </c>
-      <c r="G37" s="8">
+      <c r="G37" s="9">
         <v>1082</v>
       </c>
       <c r="H37" s="22" t="s">
@@ -5849,10 +5849,10 @@
       <c r="E38" s="2">
         <v>98</v>
       </c>
-      <c r="F38" s="8">
+      <c r="F38" s="9">
         <v>1083</v>
       </c>
-      <c r="G38" s="8">
+      <c r="G38" s="9">
         <v>1083</v>
       </c>
       <c r="H38" s="22" t="s">
@@ -5891,10 +5891,10 @@
       <c r="E39" s="2">
         <v>98</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="9">
         <v>1084</v>
       </c>
-      <c r="G39" s="8">
+      <c r="G39" s="9">
         <v>1084</v>
       </c>
       <c r="H39" s="22" t="s">
@@ -5933,10 +5933,10 @@
       <c r="E40" s="2">
         <v>98</v>
       </c>
-      <c r="F40" s="8">
+      <c r="F40" s="9">
         <v>1085</v>
       </c>
-      <c r="G40" s="8">
+      <c r="G40" s="9">
         <v>1085</v>
       </c>
       <c r="H40" s="22" t="s">
@@ -5975,10 +5975,10 @@
       <c r="E41" s="2">
         <v>98</v>
       </c>
-      <c r="F41" s="8">
+      <c r="F41" s="9">
         <v>1086</v>
       </c>
-      <c r="G41" s="8">
+      <c r="G41" s="9">
         <v>1086</v>
       </c>
       <c r="H41" s="22" t="s">
@@ -6017,10 +6017,10 @@
       <c r="E42" s="2">
         <v>98</v>
       </c>
-      <c r="F42" s="8">
+      <c r="F42" s="9">
         <v>1087</v>
       </c>
-      <c r="G42" s="8">
+      <c r="G42" s="9">
         <v>1087</v>
       </c>
       <c r="H42" s="22" t="s">
@@ -6059,10 +6059,10 @@
       <c r="E43" s="2">
         <v>98</v>
       </c>
-      <c r="F43" s="8">
+      <c r="F43" s="9">
         <v>1088</v>
       </c>
-      <c r="G43" s="8">
+      <c r="G43" s="9">
         <v>1088</v>
       </c>
       <c r="H43" s="22" t="s">
@@ -6101,10 +6101,10 @@
       <c r="E44" s="2">
         <v>98</v>
       </c>
-      <c r="F44" s="8">
+      <c r="F44" s="9">
         <v>1089</v>
       </c>
-      <c r="G44" s="8">
+      <c r="G44" s="9">
         <v>1089</v>
       </c>
       <c r="H44" s="22" t="s">
@@ -6143,10 +6143,10 @@
       <c r="E45" s="2">
         <v>98</v>
       </c>
-      <c r="F45" s="8">
+      <c r="F45" s="9">
         <v>1090</v>
       </c>
-      <c r="G45" s="8">
+      <c r="G45" s="9">
         <v>1090</v>
       </c>
       <c r="H45" s="22" t="s">
@@ -6185,10 +6185,10 @@
       <c r="E46" s="2">
         <v>98</v>
       </c>
-      <c r="F46" s="8">
+      <c r="F46" s="9">
         <v>1091</v>
       </c>
-      <c r="G46" s="8">
+      <c r="G46" s="9">
         <v>1091</v>
       </c>
       <c r="H46" s="22" t="s">
@@ -6227,10 +6227,10 @@
       <c r="E47" s="2">
         <v>98</v>
       </c>
-      <c r="F47" s="8">
+      <c r="F47" s="9">
         <v>1092</v>
       </c>
-      <c r="G47" s="8">
+      <c r="G47" s="9">
         <v>1092</v>
       </c>
       <c r="H47" s="22" t="s">
@@ -6269,10 +6269,10 @@
       <c r="E48" s="2">
         <v>98</v>
       </c>
-      <c r="F48" s="8">
+      <c r="F48" s="9">
         <v>1093</v>
       </c>
-      <c r="G48" s="8">
+      <c r="G48" s="9">
         <v>1093</v>
       </c>
       <c r="H48" s="22" t="s">
@@ -6311,10 +6311,10 @@
       <c r="E49" s="2">
         <v>98</v>
       </c>
-      <c r="F49" s="8">
+      <c r="F49" s="9">
         <v>1094</v>
       </c>
-      <c r="G49" s="8">
+      <c r="G49" s="9">
         <v>1094</v>
       </c>
       <c r="H49" s="22" t="s">
@@ -6353,10 +6353,10 @@
       <c r="E50" s="2">
         <v>98</v>
       </c>
-      <c r="F50" s="8">
+      <c r="F50" s="9">
         <v>1095</v>
       </c>
-      <c r="G50" s="8">
+      <c r="G50" s="9">
         <v>1095</v>
       </c>
       <c r="H50" s="22" t="s">
@@ -6395,10 +6395,10 @@
       <c r="E51" s="2">
         <v>98</v>
       </c>
-      <c r="F51" s="8">
+      <c r="F51" s="9">
         <v>1096</v>
       </c>
-      <c r="G51" s="8">
+      <c r="G51" s="9">
         <v>1096</v>
       </c>
       <c r="H51" s="22" t="s">
@@ -6437,10 +6437,10 @@
       <c r="E52" s="2">
         <v>98</v>
       </c>
-      <c r="F52" s="8">
+      <c r="F52" s="9">
         <v>1097</v>
       </c>
-      <c r="G52" s="8">
+      <c r="G52" s="9">
         <v>1097</v>
       </c>
       <c r="H52" s="22" t="s">
@@ -6479,10 +6479,10 @@
       <c r="E53" s="2">
         <v>98</v>
       </c>
-      <c r="F53" s="8">
+      <c r="F53" s="9">
         <v>1098</v>
       </c>
-      <c r="G53" s="8">
+      <c r="G53" s="9">
         <v>1098</v>
       </c>
       <c r="H53" s="22" t="s">
@@ -6521,10 +6521,10 @@
       <c r="E54" s="2">
         <v>98</v>
       </c>
-      <c r="F54" s="8">
+      <c r="F54" s="9">
         <v>1099</v>
       </c>
-      <c r="G54" s="8">
+      <c r="G54" s="9">
         <v>1099</v>
       </c>
       <c r="H54" s="22" t="s">
@@ -6563,10 +6563,10 @@
       <c r="E55" s="2">
         <v>98</v>
       </c>
-      <c r="F55" s="8">
+      <c r="F55" s="9">
         <v>1100</v>
       </c>
-      <c r="G55" s="8">
+      <c r="G55" s="9">
         <v>1100</v>
       </c>
       <c r="H55" s="22" t="s">
@@ -6605,10 +6605,10 @@
       <c r="E56" s="2">
         <v>98</v>
       </c>
-      <c r="F56" s="8">
+      <c r="F56" s="9">
         <v>1101</v>
       </c>
-      <c r="G56" s="8">
+      <c r="G56" s="9">
         <v>1101</v>
       </c>
       <c r="H56" s="22" t="s">
@@ -6647,10 +6647,10 @@
       <c r="E57" s="2">
         <v>98</v>
       </c>
-      <c r="F57" s="8">
+      <c r="F57" s="9">
         <v>1102</v>
       </c>
-      <c r="G57" s="8">
+      <c r="G57" s="9">
         <v>1102</v>
       </c>
       <c r="H57" s="22" t="s">
@@ -6689,10 +6689,10 @@
       <c r="E58" s="2">
         <v>98</v>
       </c>
-      <c r="F58" s="8">
+      <c r="F58" s="9">
         <v>1103</v>
       </c>
-      <c r="G58" s="8">
+      <c r="G58" s="9">
         <v>1103</v>
       </c>
       <c r="H58" s="22" t="s">
@@ -6731,10 +6731,10 @@
       <c r="E59" s="2">
         <v>98</v>
       </c>
-      <c r="F59" s="8">
+      <c r="F59" s="9">
         <v>1104</v>
       </c>
-      <c r="G59" s="8">
+      <c r="G59" s="9">
         <v>1104</v>
       </c>
       <c r="H59" s="22" t="s">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="P59" s="2"/>
     </row>
-    <row r="60" s="12" customFormat="1" customHeight="1" spans="3:15">
+    <row r="60" s="12" customFormat="1" customHeight="1" spans="3:16">
       <c r="C60" s="12">
         <v>1054</v>
       </c>
@@ -6804,7 +6804,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C61" s="2">
         <v>1055</v>
       </c>
@@ -6814,10 +6814,10 @@
       <c r="E61" s="2">
         <v>98</v>
       </c>
-      <c r="F61" s="8">
+      <c r="F61" s="9">
         <v>1106</v>
       </c>
-      <c r="G61" s="8">
+      <c r="G61" s="9">
         <v>1106</v>
       </c>
       <c r="H61" s="22" t="s">
@@ -6845,7 +6845,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C62" s="2">
         <v>1056</v>
       </c>
@@ -6855,10 +6855,10 @@
       <c r="E62" s="2">
         <v>98</v>
       </c>
-      <c r="F62" s="8">
+      <c r="F62" s="9">
         <v>1107</v>
       </c>
-      <c r="G62" s="8">
+      <c r="G62" s="9">
         <v>1107</v>
       </c>
       <c r="H62" s="22" t="s">
@@ -6886,7 +6886,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C63" s="2">
         <v>1057</v>
       </c>
@@ -6896,10 +6896,10 @@
       <c r="E63" s="2">
         <v>98</v>
       </c>
-      <c r="F63" s="8">
+      <c r="F63" s="9">
         <v>1108</v>
       </c>
-      <c r="G63" s="8">
+      <c r="G63" s="9">
         <v>1108</v>
       </c>
       <c r="H63" s="22" t="s">
@@ -6937,10 +6937,10 @@
       <c r="E64" s="2">
         <v>98</v>
       </c>
-      <c r="F64" s="8">
+      <c r="F64" s="9">
         <v>1109</v>
       </c>
-      <c r="G64" s="8">
+      <c r="G64" s="9">
         <v>1109</v>
       </c>
       <c r="H64" s="22" t="s">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="P64" s="2"/>
     </row>
-    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C65" s="2">
         <v>1059</v>
       </c>
@@ -6979,10 +6979,10 @@
       <c r="E65" s="2">
         <v>98</v>
       </c>
-      <c r="F65" s="8">
+      <c r="F65" s="9">
         <v>1110</v>
       </c>
-      <c r="G65" s="8">
+      <c r="G65" s="9">
         <v>1110</v>
       </c>
       <c r="H65" s="22" t="s">
@@ -7010,7 +7010,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C66" s="2">
         <v>1060</v>
       </c>
@@ -7020,10 +7020,10 @@
       <c r="E66" s="2">
         <v>98</v>
       </c>
-      <c r="F66" s="8">
+      <c r="F66" s="9">
         <v>1111</v>
       </c>
-      <c r="G66" s="8">
+      <c r="G66" s="9">
         <v>1111</v>
       </c>
       <c r="H66" s="22" t="s">
@@ -7051,7 +7051,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C67" s="2">
         <v>1061</v>
       </c>
@@ -7061,10 +7061,10 @@
       <c r="E67" s="2">
         <v>98</v>
       </c>
-      <c r="F67" s="8">
+      <c r="F67" s="9">
         <v>1112</v>
       </c>
-      <c r="G67" s="8">
+      <c r="G67" s="9">
         <v>1112</v>
       </c>
       <c r="H67" s="22" t="s">
@@ -7092,7 +7092,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C68" s="2">
         <v>1062</v>
       </c>
@@ -7102,10 +7102,10 @@
       <c r="E68" s="2">
         <v>98</v>
       </c>
-      <c r="F68" s="8">
+      <c r="F68" s="9">
         <v>1113</v>
       </c>
-      <c r="G68" s="8">
+      <c r="G68" s="9">
         <v>1113</v>
       </c>
       <c r="H68" s="22" t="s">
@@ -7143,10 +7143,10 @@
       <c r="E69" s="2">
         <v>98</v>
       </c>
-      <c r="F69" s="8">
+      <c r="F69" s="9">
         <v>1114</v>
       </c>
-      <c r="G69" s="8">
+      <c r="G69" s="9">
         <v>1114</v>
       </c>
       <c r="H69" s="22" t="s">
@@ -7185,10 +7185,10 @@
       <c r="E70" s="2">
         <v>98</v>
       </c>
-      <c r="F70" s="8">
+      <c r="F70" s="9">
         <v>1115</v>
       </c>
-      <c r="G70" s="8">
+      <c r="G70" s="9">
         <v>1115</v>
       </c>
       <c r="H70" s="22" t="s">
@@ -7227,10 +7227,10 @@
       <c r="E71" s="2">
         <v>98</v>
       </c>
-      <c r="F71" s="8">
+      <c r="F71" s="9">
         <v>1116</v>
       </c>
-      <c r="G71" s="8">
+      <c r="G71" s="9">
         <v>1116</v>
       </c>
       <c r="H71" s="22" t="s">
@@ -7269,10 +7269,10 @@
       <c r="E72" s="2">
         <v>98</v>
       </c>
-      <c r="F72" s="8">
+      <c r="F72" s="9">
         <v>1117</v>
       </c>
-      <c r="G72" s="8">
+      <c r="G72" s="9">
         <v>1117</v>
       </c>
       <c r="H72" s="22" t="s">
@@ -7311,10 +7311,10 @@
       <c r="E73" s="2">
         <v>98</v>
       </c>
-      <c r="F73" s="8">
+      <c r="F73" s="9">
         <v>1118</v>
       </c>
-      <c r="G73" s="8">
+      <c r="G73" s="9">
         <v>1118</v>
       </c>
       <c r="H73" s="22" t="s">
@@ -7353,10 +7353,10 @@
       <c r="E74" s="2">
         <v>98</v>
       </c>
-      <c r="F74" s="8">
+      <c r="F74" s="9">
         <v>1119</v>
       </c>
-      <c r="G74" s="8">
+      <c r="G74" s="9">
         <v>1119</v>
       </c>
       <c r="H74" s="22" t="s">
@@ -7395,10 +7395,10 @@
       <c r="E75" s="2">
         <v>98</v>
       </c>
-      <c r="F75" s="8">
+      <c r="F75" s="9">
         <v>1120</v>
       </c>
-      <c r="G75" s="8">
+      <c r="G75" s="9">
         <v>1120</v>
       </c>
       <c r="H75" s="22" t="s">
@@ -7437,10 +7437,10 @@
       <c r="E76" s="2">
         <v>98</v>
       </c>
-      <c r="F76" s="8">
+      <c r="F76" s="9">
         <v>1121</v>
       </c>
-      <c r="G76" s="8">
+      <c r="G76" s="9">
         <v>1121</v>
       </c>
       <c r="H76" s="22" t="s">
@@ -7479,10 +7479,10 @@
       <c r="E77" s="2">
         <v>98</v>
       </c>
-      <c r="F77" s="8">
+      <c r="F77" s="9">
         <v>1122</v>
       </c>
-      <c r="G77" s="8">
+      <c r="G77" s="9">
         <v>1122</v>
       </c>
       <c r="H77" s="22" t="s">
@@ -7521,10 +7521,10 @@
       <c r="E78" s="2">
         <v>98</v>
       </c>
-      <c r="F78" s="8">
+      <c r="F78" s="9">
         <v>1123</v>
       </c>
-      <c r="G78" s="8">
+      <c r="G78" s="9">
         <v>1123</v>
       </c>
       <c r="H78" s="22" t="s">
@@ -7563,10 +7563,10 @@
       <c r="E79" s="2">
         <v>98</v>
       </c>
-      <c r="F79" s="8">
+      <c r="F79" s="9">
         <v>1124</v>
       </c>
-      <c r="G79" s="8">
+      <c r="G79" s="9">
         <v>1124</v>
       </c>
       <c r="H79" s="22" t="s">
@@ -7605,10 +7605,10 @@
       <c r="E80" s="2">
         <v>98</v>
       </c>
-      <c r="F80" s="8">
+      <c r="F80" s="9">
         <v>1125</v>
       </c>
-      <c r="G80" s="8">
+      <c r="G80" s="9">
         <v>1125</v>
       </c>
       <c r="H80" s="22" t="s">
@@ -7647,10 +7647,10 @@
       <c r="E81" s="2">
         <v>98</v>
       </c>
-      <c r="F81" s="8">
+      <c r="F81" s="9">
         <v>1126</v>
       </c>
-      <c r="G81" s="8">
+      <c r="G81" s="9">
         <v>1126</v>
       </c>
       <c r="H81" s="22" t="s">
@@ -7689,10 +7689,10 @@
       <c r="E82" s="2">
         <v>98</v>
       </c>
-      <c r="F82" s="8">
+      <c r="F82" s="9">
         <v>1127</v>
       </c>
-      <c r="G82" s="8">
+      <c r="G82" s="9">
         <v>1127</v>
       </c>
       <c r="H82" s="22" t="s">
@@ -7731,10 +7731,10 @@
       <c r="E83" s="2">
         <v>98</v>
       </c>
-      <c r="F83" s="8">
+      <c r="F83" s="9">
         <v>1128</v>
       </c>
-      <c r="G83" s="8">
+      <c r="G83" s="9">
         <v>1128</v>
       </c>
       <c r="H83" s="22" t="s">
@@ -7773,10 +7773,10 @@
       <c r="E84" s="2">
         <v>98</v>
       </c>
-      <c r="F84" s="8">
+      <c r="F84" s="9">
         <v>1129</v>
       </c>
-      <c r="G84" s="8">
+      <c r="G84" s="9">
         <v>1129</v>
       </c>
       <c r="H84" s="22" t="s">
@@ -7815,10 +7815,10 @@
       <c r="E85" s="2">
         <v>98</v>
       </c>
-      <c r="F85" s="8">
+      <c r="F85" s="9">
         <v>1130</v>
       </c>
-      <c r="G85" s="8">
+      <c r="G85" s="9">
         <v>1130</v>
       </c>
       <c r="H85" s="22" t="s">
@@ -7857,10 +7857,10 @@
       <c r="E86" s="2">
         <v>98</v>
       </c>
-      <c r="F86" s="8">
+      <c r="F86" s="9">
         <v>1131</v>
       </c>
-      <c r="G86" s="8">
+      <c r="G86" s="9">
         <v>1131</v>
       </c>
       <c r="H86" s="22" t="s">
@@ -7899,10 +7899,10 @@
       <c r="E87" s="2">
         <v>98</v>
       </c>
-      <c r="F87" s="8">
+      <c r="F87" s="9">
         <v>1132</v>
       </c>
-      <c r="G87" s="8">
+      <c r="G87" s="9">
         <v>1132</v>
       </c>
       <c r="H87" s="22" t="s">
@@ -7941,10 +7941,10 @@
       <c r="E88" s="2">
         <v>98</v>
       </c>
-      <c r="F88" s="8">
+      <c r="F88" s="9">
         <v>1133</v>
       </c>
-      <c r="G88" s="8">
+      <c r="G88" s="9">
         <v>1133</v>
       </c>
       <c r="H88" s="22" t="s">
@@ -7983,10 +7983,10 @@
       <c r="E89" s="2">
         <v>98</v>
       </c>
-      <c r="F89" s="8">
+      <c r="F89" s="9">
         <v>1134</v>
       </c>
-      <c r="G89" s="8">
+      <c r="G89" s="9">
         <v>1134</v>
       </c>
       <c r="H89" s="22" t="s">
@@ -8025,10 +8025,10 @@
       <c r="E90" s="2">
         <v>98</v>
       </c>
-      <c r="F90" s="8">
+      <c r="F90" s="9">
         <v>1135</v>
       </c>
-      <c r="G90" s="8">
+      <c r="G90" s="9">
         <v>1135</v>
       </c>
       <c r="H90" s="22" t="s">
@@ -8067,10 +8067,10 @@
       <c r="E91" s="2">
         <v>98</v>
       </c>
-      <c r="F91" s="8">
+      <c r="F91" s="9">
         <v>1136</v>
       </c>
-      <c r="G91" s="8">
+      <c r="G91" s="9">
         <v>1136</v>
       </c>
       <c r="H91" s="22" t="s">
@@ -8109,10 +8109,10 @@
       <c r="E92" s="2">
         <v>98</v>
       </c>
-      <c r="F92" s="8">
+      <c r="F92" s="9">
         <v>1137</v>
       </c>
-      <c r="G92" s="8">
+      <c r="G92" s="9">
         <v>1137</v>
       </c>
       <c r="H92" s="22" t="s">
@@ -8151,10 +8151,10 @@
       <c r="E93" s="2">
         <v>98</v>
       </c>
-      <c r="F93" s="8">
+      <c r="F93" s="9">
         <v>1138</v>
       </c>
-      <c r="G93" s="8">
+      <c r="G93" s="9">
         <v>1138</v>
       </c>
       <c r="H93" s="22" t="s">
@@ -8193,10 +8193,10 @@
       <c r="E94" s="2">
         <v>98</v>
       </c>
-      <c r="F94" s="8">
+      <c r="F94" s="9">
         <v>1139</v>
       </c>
-      <c r="G94" s="8">
+      <c r="G94" s="9">
         <v>1139</v>
       </c>
       <c r="H94" s="22" t="s">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="P94" s="2"/>
     </row>
-    <row r="95" s="12" customFormat="1" customHeight="1" spans="3:15">
+    <row r="95" s="12" customFormat="1" customHeight="1" spans="3:16">
       <c r="C95" s="12">
         <v>1089</v>
       </c>
@@ -8266,7 +8266,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="96" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="96" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C96" s="2">
         <v>1090</v>
       </c>
@@ -8276,10 +8276,10 @@
       <c r="E96" s="2">
         <v>98</v>
       </c>
-      <c r="F96" s="8">
+      <c r="F96" s="9">
         <v>1141</v>
       </c>
-      <c r="G96" s="8">
+      <c r="G96" s="9">
         <v>1141</v>
       </c>
       <c r="H96" s="22" t="s">
@@ -8307,7 +8307,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="97" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="97" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C97" s="2">
         <v>1091</v>
       </c>
@@ -8317,10 +8317,10 @@
       <c r="E97" s="2">
         <v>98</v>
       </c>
-      <c r="F97" s="8">
+      <c r="F97" s="9">
         <v>1142</v>
       </c>
-      <c r="G97" s="8">
+      <c r="G97" s="9">
         <v>1142</v>
       </c>
       <c r="H97" s="22" t="s">
@@ -8348,7 +8348,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="98" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="98" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C98" s="2">
         <v>1092</v>
       </c>
@@ -8358,10 +8358,10 @@
       <c r="E98" s="2">
         <v>98</v>
       </c>
-      <c r="F98" s="8">
+      <c r="F98" s="9">
         <v>1143</v>
       </c>
-      <c r="G98" s="8">
+      <c r="G98" s="9">
         <v>1143</v>
       </c>
       <c r="H98" s="22" t="s">
@@ -8399,10 +8399,10 @@
       <c r="E99" s="2">
         <v>98</v>
       </c>
-      <c r="F99" s="8">
+      <c r="F99" s="9">
         <v>1144</v>
       </c>
-      <c r="G99" s="8">
+      <c r="G99" s="9">
         <v>1144</v>
       </c>
       <c r="H99" s="22" t="s">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="P99" s="2"/>
     </row>
-    <row r="100" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="100" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C100" s="2">
         <v>1094</v>
       </c>
@@ -8441,10 +8441,10 @@
       <c r="E100" s="2">
         <v>98</v>
       </c>
-      <c r="F100" s="8">
+      <c r="F100" s="9">
         <v>1145</v>
       </c>
-      <c r="G100" s="8">
+      <c r="G100" s="9">
         <v>1145</v>
       </c>
       <c r="H100" s="22" t="s">
@@ -8472,7 +8472,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="101" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="101" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C101" s="2">
         <v>1095</v>
       </c>
@@ -8482,10 +8482,10 @@
       <c r="E101" s="2">
         <v>98</v>
       </c>
-      <c r="F101" s="8">
+      <c r="F101" s="9">
         <v>1146</v>
       </c>
-      <c r="G101" s="8">
+      <c r="G101" s="9">
         <v>1146</v>
       </c>
       <c r="H101" s="22" t="s">
@@ -8513,7 +8513,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="102" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="102" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C102" s="2">
         <v>1096</v>
       </c>
@@ -8523,10 +8523,10 @@
       <c r="E102" s="2">
         <v>98</v>
       </c>
-      <c r="F102" s="8">
+      <c r="F102" s="9">
         <v>1147</v>
       </c>
-      <c r="G102" s="8">
+      <c r="G102" s="9">
         <v>1147</v>
       </c>
       <c r="H102" s="22" t="s">
@@ -8554,7 +8554,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="103" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="103" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C103" s="2">
         <v>1097</v>
       </c>
@@ -8564,10 +8564,10 @@
       <c r="E103" s="2">
         <v>98</v>
       </c>
-      <c r="F103" s="8">
+      <c r="F103" s="9">
         <v>1148</v>
       </c>
-      <c r="G103" s="8">
+      <c r="G103" s="9">
         <v>1148</v>
       </c>
       <c r="H103" s="22" t="s">
@@ -8605,10 +8605,10 @@
       <c r="E104" s="2">
         <v>98</v>
       </c>
-      <c r="F104" s="8">
+      <c r="F104" s="9">
         <v>1149</v>
       </c>
-      <c r="G104" s="8">
+      <c r="G104" s="9">
         <v>1149</v>
       </c>
       <c r="H104" s="22" t="s">
@@ -8647,10 +8647,10 @@
       <c r="E105" s="2">
         <v>98</v>
       </c>
-      <c r="F105" s="8">
+      <c r="F105" s="9">
         <v>1150</v>
       </c>
-      <c r="G105" s="8">
+      <c r="G105" s="9">
         <v>1150</v>
       </c>
       <c r="H105" s="22" t="s">
@@ -8689,10 +8689,10 @@
       <c r="E106" s="2">
         <v>98</v>
       </c>
-      <c r="F106" s="8">
+      <c r="F106" s="9">
         <v>1151</v>
       </c>
-      <c r="G106" s="8">
+      <c r="G106" s="9">
         <v>1151</v>
       </c>
       <c r="H106" s="22" t="s">
@@ -8731,10 +8731,10 @@
       <c r="E107" s="2">
         <v>98</v>
       </c>
-      <c r="F107" s="8">
+      <c r="F107" s="9">
         <v>1152</v>
       </c>
-      <c r="G107" s="8">
+      <c r="G107" s="9">
         <v>1152</v>
       </c>
       <c r="H107" s="22" t="s">
@@ -8773,10 +8773,10 @@
       <c r="E108" s="2">
         <v>98</v>
       </c>
-      <c r="F108" s="8">
+      <c r="F108" s="9">
         <v>1153</v>
       </c>
-      <c r="G108" s="8">
+      <c r="G108" s="9">
         <v>1153</v>
       </c>
       <c r="H108" s="22" t="s">
@@ -8815,10 +8815,10 @@
       <c r="E109" s="2">
         <v>98</v>
       </c>
-      <c r="F109" s="8">
+      <c r="F109" s="9">
         <v>1154</v>
       </c>
-      <c r="G109" s="8">
+      <c r="G109" s="9">
         <v>1154</v>
       </c>
       <c r="H109" s="22" t="s">
@@ -8857,10 +8857,10 @@
       <c r="E110" s="2">
         <v>98</v>
       </c>
-      <c r="F110" s="8">
+      <c r="F110" s="9">
         <v>1155</v>
       </c>
-      <c r="G110" s="8">
+      <c r="G110" s="9">
         <v>1155</v>
       </c>
       <c r="H110" s="22" t="s">
@@ -8899,10 +8899,10 @@
       <c r="E111" s="2">
         <v>98</v>
       </c>
-      <c r="F111" s="8">
+      <c r="F111" s="9">
         <v>1156</v>
       </c>
-      <c r="G111" s="8">
+      <c r="G111" s="9">
         <v>1156</v>
       </c>
       <c r="H111" s="22" t="s">
@@ -8941,10 +8941,10 @@
       <c r="E112" s="2">
         <v>98</v>
       </c>
-      <c r="F112" s="8">
+      <c r="F112" s="9">
         <v>1157</v>
       </c>
-      <c r="G112" s="8">
+      <c r="G112" s="9">
         <v>1157</v>
       </c>
       <c r="H112" s="22" t="s">
@@ -8983,10 +8983,10 @@
       <c r="E113" s="2">
         <v>98</v>
       </c>
-      <c r="F113" s="8">
+      <c r="F113" s="9">
         <v>1158</v>
       </c>
-      <c r="G113" s="8">
+      <c r="G113" s="9">
         <v>1158</v>
       </c>
       <c r="H113" s="22" t="s">
@@ -9025,10 +9025,10 @@
       <c r="E114" s="2">
         <v>98</v>
       </c>
-      <c r="F114" s="8">
+      <c r="F114" s="9">
         <v>1159</v>
       </c>
-      <c r="G114" s="8">
+      <c r="G114" s="9">
         <v>1159</v>
       </c>
       <c r="H114" s="22" t="s">
@@ -9067,10 +9067,10 @@
       <c r="E115" s="2">
         <v>98</v>
       </c>
-      <c r="F115" s="8">
+      <c r="F115" s="9">
         <v>1160</v>
       </c>
-      <c r="G115" s="8">
+      <c r="G115" s="9">
         <v>1160</v>
       </c>
       <c r="H115" s="22" t="s">
@@ -9109,10 +9109,10 @@
       <c r="E116" s="2">
         <v>98</v>
       </c>
-      <c r="F116" s="8">
+      <c r="F116" s="9">
         <v>1161</v>
       </c>
-      <c r="G116" s="8">
+      <c r="G116" s="9">
         <v>1161</v>
       </c>
       <c r="H116" s="22" t="s">
@@ -9151,10 +9151,10 @@
       <c r="E117" s="2">
         <v>98</v>
       </c>
-      <c r="F117" s="8">
+      <c r="F117" s="9">
         <v>1162</v>
       </c>
-      <c r="G117" s="8">
+      <c r="G117" s="9">
         <v>1162</v>
       </c>
       <c r="H117" s="22" t="s">
@@ -9193,10 +9193,10 @@
       <c r="E118" s="2">
         <v>98</v>
       </c>
-      <c r="F118" s="8">
+      <c r="F118" s="9">
         <v>1163</v>
       </c>
-      <c r="G118" s="8">
+      <c r="G118" s="9">
         <v>1163</v>
       </c>
       <c r="H118" s="22" t="s">
@@ -9235,10 +9235,10 @@
       <c r="E119" s="2">
         <v>98</v>
       </c>
-      <c r="F119" s="8">
+      <c r="F119" s="9">
         <v>1164</v>
       </c>
-      <c r="G119" s="8">
+      <c r="G119" s="9">
         <v>1164</v>
       </c>
       <c r="H119" s="22" t="s">
@@ -9277,10 +9277,10 @@
       <c r="E120" s="2">
         <v>98</v>
       </c>
-      <c r="F120" s="8">
+      <c r="F120" s="9">
         <v>1165</v>
       </c>
-      <c r="G120" s="8">
+      <c r="G120" s="9">
         <v>1165</v>
       </c>
       <c r="H120" s="22" t="s">
@@ -9319,10 +9319,10 @@
       <c r="E121" s="2">
         <v>98</v>
       </c>
-      <c r="F121" s="8">
+      <c r="F121" s="9">
         <v>1166</v>
       </c>
-      <c r="G121" s="8">
+      <c r="G121" s="9">
         <v>1166</v>
       </c>
       <c r="H121" s="22" t="s">
@@ -9361,10 +9361,10 @@
       <c r="E122" s="2">
         <v>98</v>
       </c>
-      <c r="F122" s="8">
+      <c r="F122" s="9">
         <v>1167</v>
       </c>
-      <c r="G122" s="8">
+      <c r="G122" s="9">
         <v>1167</v>
       </c>
       <c r="H122" s="22" t="s">
@@ -9403,10 +9403,10 @@
       <c r="E123" s="2">
         <v>98</v>
       </c>
-      <c r="F123" s="8">
+      <c r="F123" s="9">
         <v>1168</v>
       </c>
-      <c r="G123" s="8">
+      <c r="G123" s="9">
         <v>1168</v>
       </c>
       <c r="H123" s="22" t="s">
@@ -9445,10 +9445,10 @@
       <c r="E124" s="2">
         <v>98</v>
       </c>
-      <c r="F124" s="8">
+      <c r="F124" s="9">
         <v>1169</v>
       </c>
-      <c r="G124" s="8">
+      <c r="G124" s="9">
         <v>1169</v>
       </c>
       <c r="H124" s="22" t="s">
@@ -9487,10 +9487,10 @@
       <c r="E125" s="2">
         <v>98</v>
       </c>
-      <c r="F125" s="8">
+      <c r="F125" s="9">
         <v>1170</v>
       </c>
-      <c r="G125" s="8">
+      <c r="G125" s="9">
         <v>1170</v>
       </c>
       <c r="H125" s="22" t="s">
@@ -9529,10 +9529,10 @@
       <c r="E126" s="2">
         <v>98</v>
       </c>
-      <c r="F126" s="8">
+      <c r="F126" s="9">
         <v>1171</v>
       </c>
-      <c r="G126" s="8">
+      <c r="G126" s="9">
         <v>1171</v>
       </c>
       <c r="H126" s="22" t="s">
@@ -9571,10 +9571,10 @@
       <c r="E127" s="2">
         <v>98</v>
       </c>
-      <c r="F127" s="8">
+      <c r="F127" s="9">
         <v>1172</v>
       </c>
-      <c r="G127" s="8">
+      <c r="G127" s="9">
         <v>1172</v>
       </c>
       <c r="H127" s="22" t="s">
@@ -9613,10 +9613,10 @@
       <c r="E128" s="2">
         <v>98</v>
       </c>
-      <c r="F128" s="8">
+      <c r="F128" s="9">
         <v>1173</v>
       </c>
-      <c r="G128" s="8">
+      <c r="G128" s="9">
         <v>1173</v>
       </c>
       <c r="H128" s="22" t="s">
@@ -9655,10 +9655,10 @@
       <c r="E129" s="2">
         <v>98</v>
       </c>
-      <c r="F129" s="8">
+      <c r="F129" s="9">
         <v>1174</v>
       </c>
-      <c r="G129" s="8">
+      <c r="G129" s="9">
         <v>1174</v>
       </c>
       <c r="H129" s="22" t="s">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="P129" s="2"/>
     </row>
-    <row r="130" s="13" customFormat="1" customHeight="1" spans="3:15">
+    <row r="130" s="13" customFormat="1" customHeight="1" spans="3:16">
       <c r="C130" s="12">
         <v>1124</v>
       </c>
@@ -9728,7 +9728,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="131" customHeight="1" spans="3:15">
+    <row r="131" customHeight="1" spans="3:16">
       <c r="C131" s="2">
         <v>1125</v>
       </c>
@@ -9738,10 +9738,10 @@
       <c r="E131" s="2">
         <v>98</v>
       </c>
-      <c r="F131" s="8">
+      <c r="F131" s="9">
         <v>1176</v>
       </c>
-      <c r="G131" s="8">
+      <c r="G131" s="9">
         <v>1176</v>
       </c>
       <c r="H131" s="22" t="s">
@@ -9769,7 +9769,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="132" customHeight="1" spans="3:15">
+    <row r="132" customHeight="1" spans="3:16">
       <c r="C132" s="2">
         <v>1126</v>
       </c>
@@ -9779,10 +9779,10 @@
       <c r="E132" s="2">
         <v>98</v>
       </c>
-      <c r="F132" s="8">
+      <c r="F132" s="9">
         <v>1177</v>
       </c>
-      <c r="G132" s="8">
+      <c r="G132" s="9">
         <v>1177</v>
       </c>
       <c r="H132" s="22" t="s">
@@ -9810,7 +9810,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="133" customHeight="1" spans="3:15">
+    <row r="133" customHeight="1" spans="3:16">
       <c r="C133" s="2">
         <v>1127</v>
       </c>
@@ -9820,10 +9820,10 @@
       <c r="E133" s="2">
         <v>98</v>
       </c>
-      <c r="F133" s="8">
+      <c r="F133" s="9">
         <v>1178</v>
       </c>
-      <c r="G133" s="8">
+      <c r="G133" s="9">
         <v>1178</v>
       </c>
       <c r="H133" s="22" t="s">
@@ -9851,7 +9851,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="134" customHeight="1" spans="3:15">
+    <row r="134" customHeight="1" spans="3:16">
       <c r="C134" s="2">
         <v>1128</v>
       </c>
@@ -9861,10 +9861,10 @@
       <c r="E134" s="2">
         <v>98</v>
       </c>
-      <c r="F134" s="8">
+      <c r="F134" s="9">
         <v>1179</v>
       </c>
-      <c r="G134" s="8">
+      <c r="G134" s="9">
         <v>1179</v>
       </c>
       <c r="H134" s="22" t="s">
@@ -9892,7 +9892,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="135" customHeight="1" spans="3:15">
+    <row r="135" customHeight="1" spans="3:16">
       <c r="C135" s="2">
         <v>1129</v>
       </c>
@@ -9902,10 +9902,10 @@
       <c r="E135" s="2">
         <v>98</v>
       </c>
-      <c r="F135" s="8">
+      <c r="F135" s="9">
         <v>1180</v>
       </c>
-      <c r="G135" s="8">
+      <c r="G135" s="9">
         <v>1180</v>
       </c>
       <c r="H135" s="22" t="s">
@@ -9933,7 +9933,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="136" customHeight="1" spans="3:15">
+    <row r="136" customHeight="1" spans="3:16">
       <c r="C136" s="2">
         <v>1130</v>
       </c>
@@ -9943,10 +9943,10 @@
       <c r="E136" s="2">
         <v>98</v>
       </c>
-      <c r="F136" s="8">
+      <c r="F136" s="9">
         <v>1181</v>
       </c>
-      <c r="G136" s="8">
+      <c r="G136" s="9">
         <v>1181</v>
       </c>
       <c r="H136" s="22" t="s">
@@ -9974,7 +9974,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="137" customHeight="1" spans="3:15">
+    <row r="137" customHeight="1" spans="3:16">
       <c r="C137" s="2">
         <v>1131</v>
       </c>
@@ -9984,10 +9984,10 @@
       <c r="E137" s="2">
         <v>98</v>
       </c>
-      <c r="F137" s="8">
+      <c r="F137" s="9">
         <v>1182</v>
       </c>
-      <c r="G137" s="8">
+      <c r="G137" s="9">
         <v>1182</v>
       </c>
       <c r="H137" s="22" t="s">
@@ -10015,7 +10015,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="138" customHeight="1" spans="3:15">
+    <row r="138" customHeight="1" spans="3:16">
       <c r="C138" s="2">
         <v>1132</v>
       </c>
@@ -10025,10 +10025,10 @@
       <c r="E138" s="2">
         <v>98</v>
       </c>
-      <c r="F138" s="8">
+      <c r="F138" s="9">
         <v>1183</v>
       </c>
-      <c r="G138" s="8">
+      <c r="G138" s="9">
         <v>1183</v>
       </c>
       <c r="H138" s="22" t="s">
@@ -10056,7 +10056,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="139" customHeight="1" spans="3:15">
+    <row r="139" customHeight="1" spans="3:16">
       <c r="C139" s="2">
         <v>1133</v>
       </c>
@@ -10066,10 +10066,10 @@
       <c r="E139" s="2">
         <v>98</v>
       </c>
-      <c r="F139" s="8">
+      <c r="F139" s="9">
         <v>1184</v>
       </c>
-      <c r="G139" s="8">
+      <c r="G139" s="9">
         <v>1184</v>
       </c>
       <c r="H139" s="22" t="s">
@@ -10097,7 +10097,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="140" customHeight="1" spans="3:15">
+    <row r="140" customHeight="1" spans="3:16">
       <c r="C140" s="2">
         <v>1134</v>
       </c>
@@ -10107,10 +10107,10 @@
       <c r="E140" s="2">
         <v>98</v>
       </c>
-      <c r="F140" s="8">
+      <c r="F140" s="9">
         <v>1185</v>
       </c>
-      <c r="G140" s="8">
+      <c r="G140" s="9">
         <v>1185</v>
       </c>
       <c r="H140" s="22" t="s">
@@ -10138,7 +10138,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="141" customHeight="1" spans="3:15">
+    <row r="141" customHeight="1" spans="3:16">
       <c r="C141" s="2">
         <v>1135</v>
       </c>
@@ -10148,10 +10148,10 @@
       <c r="E141" s="2">
         <v>98</v>
       </c>
-      <c r="F141" s="8">
+      <c r="F141" s="9">
         <v>1186</v>
       </c>
-      <c r="G141" s="8">
+      <c r="G141" s="9">
         <v>1186</v>
       </c>
       <c r="H141" s="22" t="s">
@@ -10179,7 +10179,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="142" customHeight="1" spans="3:15">
+    <row r="142" customHeight="1" spans="3:16">
       <c r="C142" s="2">
         <v>1136</v>
       </c>
@@ -10189,10 +10189,10 @@
       <c r="E142" s="2">
         <v>98</v>
       </c>
-      <c r="F142" s="8">
+      <c r="F142" s="9">
         <v>1187</v>
       </c>
-      <c r="G142" s="8">
+      <c r="G142" s="9">
         <v>1187</v>
       </c>
       <c r="H142" s="22" t="s">
@@ -10220,7 +10220,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="143" customHeight="1" spans="3:15">
+    <row r="143" customHeight="1" spans="3:16">
       <c r="C143" s="2">
         <v>1137</v>
       </c>
@@ -10230,10 +10230,10 @@
       <c r="E143" s="2">
         <v>98</v>
       </c>
-      <c r="F143" s="8">
+      <c r="F143" s="9">
         <v>1188</v>
       </c>
-      <c r="G143" s="8">
+      <c r="G143" s="9">
         <v>1188</v>
       </c>
       <c r="H143" s="22" t="s">
@@ -10261,7 +10261,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="144" customHeight="1" spans="3:15">
+    <row r="144" customHeight="1" spans="3:16">
       <c r="C144" s="2">
         <v>1138</v>
       </c>
@@ -10271,10 +10271,10 @@
       <c r="E144" s="2">
         <v>98</v>
       </c>
-      <c r="F144" s="8">
+      <c r="F144" s="9">
         <v>1189</v>
       </c>
-      <c r="G144" s="8">
+      <c r="G144" s="9">
         <v>1189</v>
       </c>
       <c r="H144" s="22" t="s">
@@ -10312,10 +10312,10 @@
       <c r="E145" s="2">
         <v>98</v>
       </c>
-      <c r="F145" s="8">
+      <c r="F145" s="9">
         <v>1190</v>
       </c>
-      <c r="G145" s="8">
+      <c r="G145" s="9">
         <v>1190</v>
       </c>
       <c r="H145" s="22" t="s">
@@ -10353,10 +10353,10 @@
       <c r="E146" s="2">
         <v>98</v>
       </c>
-      <c r="F146" s="8">
+      <c r="F146" s="9">
         <v>1191</v>
       </c>
-      <c r="G146" s="8">
+      <c r="G146" s="9">
         <v>1191</v>
       </c>
       <c r="H146" s="22" t="s">
@@ -10394,10 +10394,10 @@
       <c r="E147" s="2">
         <v>98</v>
       </c>
-      <c r="F147" s="8">
+      <c r="F147" s="9">
         <v>1192</v>
       </c>
-      <c r="G147" s="8">
+      <c r="G147" s="9">
         <v>1192</v>
       </c>
       <c r="H147" s="22" t="s">
@@ -10435,10 +10435,10 @@
       <c r="E148" s="2">
         <v>98</v>
       </c>
-      <c r="F148" s="8">
+      <c r="F148" s="9">
         <v>1193</v>
       </c>
-      <c r="G148" s="8">
+      <c r="G148" s="9">
         <v>1193</v>
       </c>
       <c r="H148" s="22" t="s">
@@ -10476,10 +10476,10 @@
       <c r="E149" s="2">
         <v>98</v>
       </c>
-      <c r="F149" s="8">
+      <c r="F149" s="9">
         <v>1194</v>
       </c>
-      <c r="G149" s="8">
+      <c r="G149" s="9">
         <v>1194</v>
       </c>
       <c r="H149" s="22" t="s">
@@ -10517,10 +10517,10 @@
       <c r="E150" s="2">
         <v>98</v>
       </c>
-      <c r="F150" s="8">
+      <c r="F150" s="9">
         <v>1195</v>
       </c>
-      <c r="G150" s="8">
+      <c r="G150" s="9">
         <v>1195</v>
       </c>
       <c r="H150" s="22" t="s">
@@ -10558,10 +10558,10 @@
       <c r="E151" s="2">
         <v>98</v>
       </c>
-      <c r="F151" s="8">
+      <c r="F151" s="9">
         <v>1196</v>
       </c>
-      <c r="G151" s="8">
+      <c r="G151" s="9">
         <v>1196</v>
       </c>
       <c r="H151" s="22" t="s">
@@ -10599,10 +10599,10 @@
       <c r="E152" s="2">
         <v>98</v>
       </c>
-      <c r="F152" s="8">
+      <c r="F152" s="9">
         <v>1197</v>
       </c>
-      <c r="G152" s="8">
+      <c r="G152" s="9">
         <v>1197</v>
       </c>
       <c r="H152" s="22" t="s">
@@ -10640,10 +10640,10 @@
       <c r="E153" s="2">
         <v>98</v>
       </c>
-      <c r="F153" s="8">
+      <c r="F153" s="9">
         <v>1198</v>
       </c>
-      <c r="G153" s="8">
+      <c r="G153" s="9">
         <v>1198</v>
       </c>
       <c r="H153" s="22" t="s">
@@ -10681,10 +10681,10 @@
       <c r="E154" s="2">
         <v>98</v>
       </c>
-      <c r="F154" s="8">
+      <c r="F154" s="9">
         <v>1199</v>
       </c>
-      <c r="G154" s="8">
+      <c r="G154" s="9">
         <v>1199</v>
       </c>
       <c r="H154" s="22" t="s">
@@ -10722,10 +10722,10 @@
       <c r="E155" s="2">
         <v>98</v>
       </c>
-      <c r="F155" s="8">
+      <c r="F155" s="9">
         <v>1200</v>
       </c>
-      <c r="G155" s="8">
+      <c r="G155" s="9">
         <v>1200</v>
       </c>
       <c r="H155" s="22" t="s">
@@ -10763,10 +10763,10 @@
       <c r="E156" s="2">
         <v>98</v>
       </c>
-      <c r="F156" s="8">
+      <c r="F156" s="9">
         <v>1201</v>
       </c>
-      <c r="G156" s="8">
+      <c r="G156" s="9">
         <v>1201</v>
       </c>
       <c r="H156" s="22" t="s">
@@ -10804,10 +10804,10 @@
       <c r="E157" s="2">
         <v>98</v>
       </c>
-      <c r="F157" s="8">
+      <c r="F157" s="9">
         <v>1202</v>
       </c>
-      <c r="G157" s="8">
+      <c r="G157" s="9">
         <v>1202</v>
       </c>
       <c r="H157" s="22" t="s">
@@ -10845,10 +10845,10 @@
       <c r="E158" s="2">
         <v>98</v>
       </c>
-      <c r="F158" s="8">
+      <c r="F158" s="9">
         <v>1203</v>
       </c>
-      <c r="G158" s="8">
+      <c r="G158" s="9">
         <v>1203</v>
       </c>
       <c r="H158" s="22" t="s">
@@ -10886,10 +10886,10 @@
       <c r="E159" s="2">
         <v>98</v>
       </c>
-      <c r="F159" s="8">
+      <c r="F159" s="9">
         <v>1204</v>
       </c>
-      <c r="G159" s="8">
+      <c r="G159" s="9">
         <v>1204</v>
       </c>
       <c r="H159" s="22" t="s">
@@ -10927,10 +10927,10 @@
       <c r="E160" s="2">
         <v>98</v>
       </c>
-      <c r="F160" s="8">
+      <c r="F160" s="9">
         <v>1205</v>
       </c>
-      <c r="G160" s="8">
+      <c r="G160" s="9">
         <v>1205</v>
       </c>
       <c r="H160" s="22" t="s">
@@ -10968,10 +10968,10 @@
       <c r="E161" s="2">
         <v>98</v>
       </c>
-      <c r="F161" s="8">
+      <c r="F161" s="9">
         <v>1206</v>
       </c>
-      <c r="G161" s="8">
+      <c r="G161" s="9">
         <v>1206</v>
       </c>
       <c r="H161" s="22" t="s">
@@ -11009,10 +11009,10 @@
       <c r="E162" s="2">
         <v>98</v>
       </c>
-      <c r="F162" s="8">
+      <c r="F162" s="9">
         <v>1207</v>
       </c>
-      <c r="G162" s="8">
+      <c r="G162" s="9">
         <v>1207</v>
       </c>
       <c r="H162" s="22" t="s">
@@ -11050,10 +11050,10 @@
       <c r="E163" s="2">
         <v>98</v>
       </c>
-      <c r="F163" s="8">
+      <c r="F163" s="9">
         <v>1208</v>
       </c>
-      <c r="G163" s="8">
+      <c r="G163" s="9">
         <v>1208</v>
       </c>
       <c r="H163" s="22" t="s">
@@ -11091,10 +11091,10 @@
       <c r="E164" s="2">
         <v>98</v>
       </c>
-      <c r="F164" s="8">
+      <c r="F164" s="9">
         <v>1209</v>
       </c>
-      <c r="G164" s="8">
+      <c r="G164" s="9">
         <v>1209</v>
       </c>
       <c r="H164" s="22" t="s">
@@ -11152,7 +11152,7 @@
     <col min="17" max="16383" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="8:16">
+    <row r="1" s="1" customFormat="1" spans="3:16">
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -11200,16 +11200,16 @@
       <c r="J3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="8" t="s">
         <v>9</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="8" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="7" t="s">
@@ -11244,16 +11244,16 @@
       <c r="J4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="8" t="s">
         <v>20</v>
       </c>
       <c r="M4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="N4" s="8" t="s">
         <v>11</v>
       </c>
       <c r="O4" s="7" t="s">
@@ -11317,10 +11317,10 @@
       <c r="E6" s="2">
         <v>98</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="9">
         <v>1070</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="9">
         <v>1070</v>
       </c>
       <c r="H6" s="22" t="s">
@@ -11361,10 +11361,10 @@
       <c r="E7" s="2">
         <v>98</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="9">
         <v>1071</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="9">
         <v>1071</v>
       </c>
       <c r="H7" s="22" t="s">
@@ -11405,10 +11405,10 @@
       <c r="E8" s="2">
         <v>98</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="9">
         <v>1072</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="9">
         <v>1072</v>
       </c>
       <c r="H8" s="22" t="s">
@@ -11449,10 +11449,10 @@
       <c r="E9" s="2">
         <v>98</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="9">
         <v>1073</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="9">
         <v>1073</v>
       </c>
       <c r="H9" s="22" t="s">
@@ -11493,10 +11493,10 @@
       <c r="E10" s="2">
         <v>98</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="9">
         <v>1074</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="9">
         <v>1074</v>
       </c>
       <c r="H10" s="22" t="s">
@@ -11537,7 +11537,7 @@
       <c r="E11" s="2">
         <v>98</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="9">
         <v>1075</v>
       </c>
       <c r="G11" s="2">
@@ -11571,17 +11571,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="9"/>
+    <row r="12" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="10"/>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
     </row>
-    <row r="13" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="9"/>
+    <row r="13" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="10"/>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
     </row>
@@ -11717,7 +11717,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+    <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
       <c r="C17" s="2">
         <v>2009</v>
       </c>
@@ -11761,7 +11761,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+    <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
       <c r="C18" s="2">
         <v>2010</v>
       </c>
@@ -11805,7 +11805,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+    <row r="19" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
       <c r="C19" s="2">
         <v>2011</v>
       </c>
@@ -11849,14 +11849,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="9"/>
+    <row r="20" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="10"/>
       <c r="O20" s="11"/>
       <c r="P20" s="11"/>
     </row>
-    <row r="21" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+    <row r="21" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
       <c r="C21" s="2">
         <v>2012</v>
       </c>
@@ -11900,7 +11900,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+    <row r="22" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
       <c r="C22" s="2">
         <v>2013</v>
       </c>
@@ -11944,7 +11944,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+    <row r="23" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
       <c r="C23" s="2">
         <v>2014</v>
       </c>
@@ -11988,7 +11988,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+    <row r="24" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
       <c r="C24" s="2">
         <v>2015</v>
       </c>
@@ -12032,7 +12032,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+    <row r="25" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
       <c r="C25" s="2">
         <v>2016</v>
       </c>
@@ -12076,7 +12076,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+    <row r="26" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
       <c r="C26" s="2">
         <v>2017</v>
       </c>
@@ -12170,136 +12170,136 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="9"/>
+    <row r="28" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="10"/>
       <c r="O28" s="11"/>
       <c r="P28" s="11"/>
     </row>
-    <row r="29" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="9"/>
+    <row r="29" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="10"/>
       <c r="O29" s="11"/>
       <c r="P29" s="11"/>
     </row>
-    <row r="30" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="9"/>
+    <row r="30" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="10"/>
       <c r="O30" s="11"/>
       <c r="P30" s="11"/>
     </row>
-    <row r="31" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="9"/>
+    <row r="31" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="10"/>
       <c r="O31" s="11"/>
       <c r="P31" s="11"/>
     </row>
-    <row r="32" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="9"/>
+    <row r="32" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="10"/>
       <c r="O32" s="11"/>
       <c r="P32" s="11"/>
     </row>
     <row r="33" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="10"/>
       <c r="O33" s="11"/>
       <c r="P33" s="11"/>
     </row>
     <row r="34" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="10"/>
       <c r="O34" s="11"/>
       <c r="P34" s="11"/>
     </row>
     <row r="35" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="10"/>
       <c r="O35" s="11"/>
       <c r="P35" s="11"/>
     </row>
     <row r="36" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="10"/>
       <c r="O36" s="11"/>
       <c r="P36" s="11"/>
     </row>
     <row r="37" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="10"/>
       <c r="O37" s="11"/>
       <c r="P37" s="11"/>
     </row>
     <row r="38" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="10"/>
       <c r="O38" s="11"/>
       <c r="P38" s="11"/>
     </row>
     <row r="39" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="10"/>
       <c r="O39" s="11"/>
       <c r="P39" s="11"/>
     </row>
     <row r="40" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="10"/>
       <c r="O40" s="11"/>
       <c r="P40" s="11"/>
     </row>
     <row r="41" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="10"/>
       <c r="O41" s="11"/>
       <c r="P41" s="11"/>
     </row>
     <row r="42" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="10"/>
       <c r="O42" s="11"/>
       <c r="P42" s="11"/>
     </row>
     <row r="43" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="10"/>
       <c r="O43" s="11"/>
       <c r="P43" s="11"/>
     </row>
     <row r="44" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="10"/>
       <c r="O44" s="11"/>
       <c r="P44" s="11"/>
     </row>
     <row r="45" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="10"/>
       <c r="O45" s="11"/>
       <c r="P45" s="11"/>
     </row>
     <row r="46" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="10"/>
       <c r="O46" s="11"/>
       <c r="P46" s="11"/>
     </row>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -346,7 +346,7 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-12-03</t>
+    <t>2025-12-06</t>
   </si>
   <si>
     <t>2025-12-15</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-12-06</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
+    <t>2025-12-09</t>
+  </si>
+  <si>
+    <t>2025-12-14</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -346,7 +346,7 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-12-09</t>
+    <t>2025-12-08</t>
   </si>
   <si>
     <t>2025-12-14</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>快乐12</t>
+    <t>元旦快乐</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-12-08</t>
-  </si>
-  <si>
-    <t>2025-12-14</t>
+    <t>2025-12-26</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -346,7 +346,7 @@
     <t>50</t>
   </si>
   <si>
-    <t>2025-12-26</t>
+    <t>2026-01-01</t>
   </si>
   <si>
     <t>2026-01-08</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="470">
   <si>
     <t>_id</t>
   </si>
@@ -523,6 +523,30 @@
     <t>40000</t>
   </si>
   <si>
+    <t>第五时装</t>
+  </si>
+  <si>
+    <t>3005</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>180000</t>
+  </si>
+  <si>
+    <t>第六时装</t>
+  </si>
+  <si>
+    <t>3006</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>210000</t>
+  </si>
+  <si>
     <t>专属之心</t>
   </si>
   <si>
@@ -556,9 +580,6 @@
     <t>2006</t>
   </si>
   <si>
-    <t>60000</t>
-  </si>
-  <si>
     <t>240000</t>
   </si>
   <si>
@@ -568,9 +589,6 @@
     <t>2007</t>
   </si>
   <si>
-    <t>50000</t>
-  </si>
-  <si>
     <t>250000</t>
   </si>
   <si>
@@ -1562,9 +1580,6 @@
   </si>
   <si>
     <t>武器衣服红装</t>
-  </si>
-  <si>
-    <t>210000</t>
   </si>
   <si>
     <t>项链头盔红装</t>
@@ -1856,12 +1871,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2693,7 +2708,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P47"/>
+  <dimension ref="C1:P49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -3816,37 +3831,80 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" s="2" customFormat="1" customHeight="1"/>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C30" s="2">
+        <v>305</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E30" s="2">
+        <v>98</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1140</v>
+      </c>
+      <c r="G30" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H30" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="I30" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="K30" s="11">
+        <v>0</v>
+      </c>
+      <c r="L30" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="M30" s="2">
+        <v>0</v>
+      </c>
+      <c r="N30" s="11">
+        <v>0</v>
+      </c>
+      <c r="O30" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P30" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C31" s="2">
-        <v>801</v>
+        <v>306</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E31" s="2">
         <v>98</v>
       </c>
       <c r="F31" s="2">
-        <v>1000</v>
+        <v>1175</v>
       </c>
       <c r="G31" s="2">
         <v>2000</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I31" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="J31" s="21" t="s">
-        <v>59</v>
+        <v>94</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>95</v>
       </c>
       <c r="K31" s="11">
         <v>0</v>
       </c>
-      <c r="L31" s="11">
-        <v>0</v>
+      <c r="L31" s="21" t="s">
+        <v>94</v>
       </c>
       <c r="M31" s="2">
         <v>0</v>
@@ -3861,127 +3919,119 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C32" s="2">
-        <v>802</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E32" s="2">
-        <v>98</v>
-      </c>
-      <c r="F32" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G32" s="2">
-        <v>2000</v>
-      </c>
-      <c r="H32" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="I32" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="J32" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="K32" s="11">
-        <v>0</v>
-      </c>
-      <c r="L32" s="11">
-        <v>0</v>
-      </c>
-      <c r="M32" s="11">
-        <v>1</v>
-      </c>
-      <c r="N32" s="11">
-        <v>0</v>
-      </c>
-      <c r="O32" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="P32" s="20" t="s">
-        <v>34</v>
-      </c>
-    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1"/>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C33" s="2">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
       </c>
       <c r="F33" s="2">
-        <v>1105</v>
+        <v>1000</v>
       </c>
       <c r="G33" s="2">
         <v>2000</v>
       </c>
-      <c r="H33" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="I33" s="20" t="s">
+      <c r="H33" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="I33" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="J33" s="20" t="s">
+      <c r="J33" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="K33" s="11">
+        <v>0</v>
+      </c>
+      <c r="L33" s="11">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2">
+        <v>0</v>
+      </c>
+      <c r="N33" s="11">
+        <v>0</v>
+      </c>
+      <c r="O33" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P33" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C34" s="2">
+        <v>802</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" s="2">
+        <v>98</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G34" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H34" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="I34" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J34" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="K33" s="11">
-        <v>0</v>
-      </c>
-      <c r="L33" s="11">
-        <v>0</v>
-      </c>
-      <c r="M33" s="2">
-        <v>0</v>
-      </c>
-      <c r="N33" s="11">
-        <v>0</v>
-      </c>
-      <c r="O33" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="P33" s="20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="11"/>
-      <c r="P34" s="11"/>
+      <c r="K34" s="11">
+        <v>0</v>
+      </c>
+      <c r="L34" s="11">
+        <v>0</v>
+      </c>
+      <c r="M34" s="11">
+        <v>1</v>
+      </c>
+      <c r="N34" s="11">
+        <v>0</v>
+      </c>
+      <c r="O34" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P34" s="20" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C35" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
       </c>
       <c r="F35" s="2">
-        <v>1000</v>
+        <v>1105</v>
       </c>
       <c r="G35" s="2">
         <v>2000</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="I35" s="21" t="s">
-        <v>59</v>
+        <v>101</v>
+      </c>
+      <c r="I35" s="20" t="s">
+        <v>50</v>
       </c>
       <c r="J35" s="20" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K35" s="11">
         <v>0</v>
@@ -4003,70 +4053,35 @@
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C36" s="2">
-        <v>805</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E36" s="2">
-        <v>98</v>
-      </c>
-      <c r="F36" s="2">
-        <v>1105</v>
-      </c>
-      <c r="G36" s="2">
-        <v>2000</v>
-      </c>
-      <c r="H36" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="I36" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="J36" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="K36" s="11">
-        <v>0</v>
-      </c>
-      <c r="L36" s="11">
-        <v>0</v>
-      </c>
-      <c r="M36" s="2">
-        <v>0</v>
-      </c>
-      <c r="N36" s="11">
-        <v>0</v>
-      </c>
-      <c r="O36" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="P36" s="20" t="s">
-        <v>34</v>
-      </c>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="11"/>
+      <c r="P36" s="11"/>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C37" s="2">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
       </c>
       <c r="F37" s="2">
-        <v>1105</v>
+        <v>1000</v>
       </c>
       <c r="G37" s="2">
         <v>2000</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I37" s="21" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="J37" s="20" t="s">
         <v>104</v>
@@ -4074,7 +4089,7 @@
       <c r="K37" s="11">
         <v>0</v>
       </c>
-      <c r="L37" s="2">
+      <c r="L37" s="11">
         <v>0</v>
       </c>
       <c r="M37" s="2">
@@ -4092,7 +4107,7 @@
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C38" s="2">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>105</v>
@@ -4110,16 +4125,16 @@
         <v>106</v>
       </c>
       <c r="I38" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="J38" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="J38" s="20" t="s">
-        <v>108</v>
-      </c>
       <c r="K38" s="11">
         <v>0</v>
       </c>
-      <c r="L38" s="2">
-        <v>150000</v>
+      <c r="L38" s="11">
+        <v>0</v>
       </c>
       <c r="M38" s="2">
         <v>0</v>
@@ -4136,10 +4151,10 @@
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C39" s="2">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E39" s="2">
         <v>98</v>
@@ -4151,160 +4166,226 @@
         <v>2000</v>
       </c>
       <c r="H39" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="I39" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="J39" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="I39" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="J39" s="20" t="s">
+      <c r="K39" s="11">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2">
+        <v>0</v>
+      </c>
+      <c r="N39" s="11">
+        <v>0</v>
+      </c>
+      <c r="O39" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P39" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C40" s="2">
+        <v>807</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="K39" s="11">
-        <v>0</v>
-      </c>
-      <c r="L39" s="2">
-        <v>200000</v>
-      </c>
-      <c r="M39" s="2">
-        <v>0</v>
-      </c>
-      <c r="N39" s="11">
-        <v>0</v>
-      </c>
-      <c r="O39" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="P39" s="20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="18"/>
-      <c r="K40" s="18"/>
-      <c r="L40" s="18"/>
-      <c r="M40" s="18"/>
-      <c r="N40" s="18"/>
-      <c r="O40" s="18"/>
-      <c r="P40" s="18"/>
+      <c r="E40" s="2">
+        <v>98</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1105</v>
+      </c>
+      <c r="G40" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H40" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="I40" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="K40" s="11">
+        <v>0</v>
+      </c>
+      <c r="L40" s="2">
+        <v>150000</v>
+      </c>
+      <c r="M40" s="2">
+        <v>0</v>
+      </c>
+      <c r="N40" s="11">
+        <v>0</v>
+      </c>
+      <c r="O40" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P40" s="20" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C41" s="2">
+        <v>808</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E41" s="2">
+        <v>98</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1105</v>
+      </c>
+      <c r="G41" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H41" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="I41" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="J41" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="K41" s="11">
+        <v>0</v>
+      </c>
+      <c r="L41" s="2">
+        <v>200000</v>
+      </c>
+      <c r="M41" s="2">
+        <v>0</v>
+      </c>
+      <c r="N41" s="11">
+        <v>0</v>
+      </c>
+      <c r="O41" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P41" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="18"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="18"/>
+      <c r="P42" s="18"/>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C43" s="2">
         <v>991</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E41" s="2">
+      <c r="D43" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E43" s="2">
         <v>99</v>
       </c>
-      <c r="F41" s="2">
-        <v>0</v>
-      </c>
-      <c r="G41" s="2">
-        <v>0</v>
-      </c>
-      <c r="H41" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="I41" s="11">
-        <v>0</v>
-      </c>
-      <c r="J41" s="2">
+      <c r="F43" s="2">
+        <v>0</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0</v>
+      </c>
+      <c r="H43" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="I43" s="11">
+        <v>0</v>
+      </c>
+      <c r="J43" s="2">
         <v>1</v>
       </c>
-      <c r="K41" s="11">
-        <v>0</v>
-      </c>
-      <c r="L41" s="11">
-        <v>0</v>
-      </c>
-      <c r="M41" s="2">
-        <v>0</v>
-      </c>
-      <c r="N41" s="2">
+      <c r="K43" s="11">
+        <v>0</v>
+      </c>
+      <c r="L43" s="11">
+        <v>0</v>
+      </c>
+      <c r="M43" s="2">
+        <v>0</v>
+      </c>
+      <c r="N43" s="2">
         <v>1</v>
       </c>
-      <c r="O41" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="P41" s="20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C42" s="2">
+      <c r="O43" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P43" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C44" s="2">
         <v>992</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E42" s="2">
+      <c r="D44" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E44" s="2">
         <v>101</v>
       </c>
-      <c r="F42" s="2">
-        <v>0</v>
-      </c>
-      <c r="G42" s="2">
-        <v>0</v>
-      </c>
-      <c r="H42" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="I42" s="11">
-        <v>0</v>
-      </c>
-      <c r="J42" s="2">
+      <c r="F44" s="2">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2">
+        <v>0</v>
+      </c>
+      <c r="H44" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="I44" s="11">
+        <v>0</v>
+      </c>
+      <c r="J44" s="2">
         <v>1</v>
       </c>
-      <c r="K42" s="11">
-        <v>0</v>
-      </c>
-      <c r="L42" s="11">
-        <v>0</v>
-      </c>
-      <c r="M42" s="2">
-        <v>0</v>
-      </c>
-      <c r="N42" s="2">
+      <c r="K44" s="11">
+        <v>0</v>
+      </c>
+      <c r="L44" s="11">
+        <v>0</v>
+      </c>
+      <c r="M44" s="2">
+        <v>0</v>
+      </c>
+      <c r="N44" s="2">
         <v>1</v>
       </c>
-      <c r="O42" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="P42" s="20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1"/>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="18"/>
-      <c r="K44" s="18"/>
-      <c r="L44" s="18"/>
-      <c r="M44" s="18"/>
-      <c r="N44" s="18"/>
-      <c r="O44" s="18"/>
-      <c r="P44" s="18"/>
-    </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
-      <c r="J45" s="18"/>
-      <c r="K45" s="18"/>
-      <c r="L45" s="18"/>
-      <c r="M45" s="18"/>
-      <c r="N45" s="18"/>
-      <c r="O45" s="18"/>
-      <c r="P45" s="18"/>
-    </row>
+      <c r="O44" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="P44" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1"/>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="H46" s="18"/>
       <c r="I46" s="18"/>
@@ -4327,30 +4408,52 @@
       <c r="O47" s="18"/>
       <c r="P47" s="18"/>
     </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18"/>
+      <c r="L48" s="18"/>
+      <c r="M48" s="18"/>
+      <c r="N48" s="18"/>
+      <c r="O48" s="18"/>
+      <c r="P48" s="18"/>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="8:16">
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="18"/>
+      <c r="N49" s="18"/>
+      <c r="O49" s="18"/>
+      <c r="P49" s="18"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F32">
+  <conditionalFormatting sqref="F34">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
+  <conditionalFormatting sqref="F35">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F34">
+  <conditionalFormatting sqref="F36">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F36">
+  <conditionalFormatting sqref="F38">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F37">
+  <conditionalFormatting sqref="F39">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F38">
+  <conditionalFormatting sqref="F40">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F39">
+  <conditionalFormatting sqref="F41">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:C5 F32:F34 F36:F39 F3:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:C5 F34:F36 F38:F41 F3:G5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -4527,7 +4630,7 @@
         <v>1000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -4539,7 +4642,7 @@
         <v>1051</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I6" s="2">
         <v>40000</v>
@@ -4568,7 +4671,7 @@
         <v>1001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -4580,7 +4683,7 @@
         <v>1052</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I7" s="2">
         <v>40000</v>
@@ -4609,7 +4712,7 @@
         <v>1002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -4621,7 +4724,7 @@
         <v>1053</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="I8" s="2">
         <v>40000</v>
@@ -4650,7 +4753,7 @@
         <v>1003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -4662,7 +4765,7 @@
         <v>1054</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="I9" s="2">
         <v>40000</v>
@@ -4691,7 +4794,7 @@
         <v>1004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -4703,7 +4806,7 @@
         <v>1055</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I10" s="2">
         <v>40000</v>
@@ -4732,7 +4835,7 @@
         <v>1005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -4744,7 +4847,7 @@
         <v>1056</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I11" s="2">
         <v>40000</v>
@@ -4773,7 +4876,7 @@
         <v>1006</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E12" s="2">
         <v>98</v>
@@ -4785,7 +4888,7 @@
         <v>1057</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="I12" s="2">
         <v>40000</v>
@@ -4814,7 +4917,7 @@
         <v>1007</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E13" s="2">
         <v>98</v>
@@ -4826,7 +4929,7 @@
         <v>1058</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="I13" s="2">
         <v>40000</v>
@@ -4855,7 +4958,7 @@
         <v>1008</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -4867,7 +4970,7 @@
         <v>1059</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="I14" s="2">
         <v>40000</v>
@@ -4896,7 +4999,7 @@
         <v>1009</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -4908,7 +5011,7 @@
         <v>1060</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="I15" s="2">
         <v>40000</v>
@@ -4937,7 +5040,7 @@
         <v>1010</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -4949,7 +5052,7 @@
         <v>1061</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="I16" s="2">
         <v>40000</v>
@@ -4978,7 +5081,7 @@
         <v>1011</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -4990,7 +5093,7 @@
         <v>1062</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="I17" s="2">
         <v>40000</v>
@@ -5019,7 +5122,7 @@
         <v>1012</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -5031,7 +5134,7 @@
         <v>1063</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I18" s="2">
         <v>40000</v>
@@ -5060,7 +5163,7 @@
         <v>1013</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -5072,7 +5175,7 @@
         <v>1064</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -5101,7 +5204,7 @@
         <v>1014</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E20" s="2">
         <v>98</v>
@@ -5113,7 +5216,7 @@
         <v>1065</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I20" s="2">
         <v>40000</v>
@@ -5142,7 +5245,7 @@
         <v>1015</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -5154,7 +5257,7 @@
         <v>1066</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="I21" s="2">
         <v>40000</v>
@@ -5183,7 +5286,7 @@
         <v>1016</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -5195,7 +5298,7 @@
         <v>1067</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="I22" s="2">
         <v>40000</v>
@@ -5224,7 +5327,7 @@
         <v>1017</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -5236,7 +5339,7 @@
         <v>1068</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="I23" s="2">
         <v>40000</v>
@@ -5265,7 +5368,7 @@
         <v>1018</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -5277,7 +5380,7 @@
         <v>1069</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="I24" s="2">
         <v>40000</v>
@@ -5306,7 +5409,7 @@
         <v>1019</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -5318,7 +5421,7 @@
         <v>1070</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="I25" s="2">
         <v>40000</v>
@@ -5347,7 +5450,7 @@
         <v>1020</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -5359,7 +5462,7 @@
         <v>1071</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="I26" s="2">
         <v>40000</v>
@@ -5388,7 +5491,7 @@
         <v>1021</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -5400,7 +5503,7 @@
         <v>1072</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>
@@ -5429,7 +5532,7 @@
         <v>1022</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E28" s="2">
         <v>98</v>
@@ -5441,7 +5544,7 @@
         <v>1073</v>
       </c>
       <c r="H28" s="22" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="I28" s="2">
         <v>40000</v>
@@ -5470,7 +5573,7 @@
         <v>1023</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="E29" s="2">
         <v>98</v>
@@ -5482,7 +5585,7 @@
         <v>1074</v>
       </c>
       <c r="H29" s="22" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="I29" s="2">
         <v>40000</v>
@@ -5512,7 +5615,7 @@
         <v>1024</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E30" s="2">
         <v>98</v>
@@ -5524,7 +5627,7 @@
         <v>1075</v>
       </c>
       <c r="H30" s="22" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="I30" s="2">
         <v>4000</v>
@@ -5553,7 +5656,7 @@
         <v>1025</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E31" s="2">
         <v>98</v>
@@ -5565,7 +5668,7 @@
         <v>1076</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I31" s="2">
         <v>4000</v>
@@ -5594,7 +5697,7 @@
         <v>1026</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E32" s="2">
         <v>98</v>
@@ -5606,7 +5709,7 @@
         <v>1077</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="I32" s="2">
         <v>4000</v>
@@ -5635,7 +5738,7 @@
         <v>1027</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E33" s="2">
         <v>98</v>
@@ -5647,7 +5750,7 @@
         <v>1078</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I33" s="2">
         <v>4000</v>
@@ -5676,7 +5779,7 @@
         <v>1028</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E34" s="2">
         <v>98</v>
@@ -5688,7 +5791,7 @@
         <v>1079</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="I34" s="2">
         <v>4000</v>
@@ -5718,7 +5821,7 @@
         <v>1029</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="E35" s="2">
         <v>98</v>
@@ -5730,7 +5833,7 @@
         <v>1080</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="I35" s="2">
         <v>4000</v>
@@ -5760,7 +5863,7 @@
         <v>1030</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E36" s="2">
         <v>98</v>
@@ -5772,7 +5875,7 @@
         <v>1081</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I36" s="2">
         <v>4000</v>
@@ -5802,7 +5905,7 @@
         <v>1031</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E37" s="2">
         <v>98</v>
@@ -5814,7 +5917,7 @@
         <v>1082</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="I37" s="2">
         <v>4000</v>
@@ -5844,7 +5947,7 @@
         <v>1032</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E38" s="2">
         <v>98</v>
@@ -5856,7 +5959,7 @@
         <v>1083</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I38" s="2">
         <v>4000</v>
@@ -5886,7 +5989,7 @@
         <v>1033</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E39" s="2">
         <v>98</v>
@@ -5898,7 +6001,7 @@
         <v>1084</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="I39" s="2">
         <v>4000</v>
@@ -5928,7 +6031,7 @@
         <v>1034</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E40" s="2">
         <v>98</v>
@@ -5940,7 +6043,7 @@
         <v>1085</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="I40" s="2">
         <v>4000</v>
@@ -5970,7 +6073,7 @@
         <v>1035</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E41" s="2">
         <v>98</v>
@@ -5982,7 +6085,7 @@
         <v>1086</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="I41" s="2">
         <v>4000</v>
@@ -6012,7 +6115,7 @@
         <v>1036</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E42" s="2">
         <v>98</v>
@@ -6024,7 +6127,7 @@
         <v>1087</v>
       </c>
       <c r="H42" s="22" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="I42" s="2">
         <v>4000</v>
@@ -6054,7 +6157,7 @@
         <v>1037</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="E43" s="2">
         <v>98</v>
@@ -6066,7 +6169,7 @@
         <v>1088</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="I43" s="2">
         <v>4000</v>
@@ -6096,7 +6199,7 @@
         <v>1038</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E44" s="2">
         <v>98</v>
@@ -6108,7 +6211,7 @@
         <v>1089</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="I44" s="2">
         <v>4000</v>
@@ -6138,7 +6241,7 @@
         <v>1039</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E45" s="2">
         <v>98</v>
@@ -6150,7 +6253,7 @@
         <v>1090</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="I45" s="2">
         <v>4000</v>
@@ -6180,7 +6283,7 @@
         <v>1040</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E46" s="2">
         <v>98</v>
@@ -6192,7 +6295,7 @@
         <v>1091</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="I46" s="2">
         <v>4000</v>
@@ -6222,7 +6325,7 @@
         <v>1041</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E47" s="2">
         <v>98</v>
@@ -6234,7 +6337,7 @@
         <v>1092</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="I47" s="2">
         <v>4000</v>
@@ -6264,7 +6367,7 @@
         <v>1042</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E48" s="2">
         <v>98</v>
@@ -6276,7 +6379,7 @@
         <v>1093</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="I48" s="2">
         <v>4000</v>
@@ -6306,7 +6409,7 @@
         <v>1043</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E49" s="2">
         <v>98</v>
@@ -6318,7 +6421,7 @@
         <v>1094</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="I49" s="2">
         <v>4000</v>
@@ -6348,7 +6451,7 @@
         <v>1044</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E50" s="2">
         <v>98</v>
@@ -6360,7 +6463,7 @@
         <v>1095</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="I50" s="2">
         <v>4000</v>
@@ -6390,7 +6493,7 @@
         <v>1045</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E51" s="2">
         <v>98</v>
@@ -6402,7 +6505,7 @@
         <v>1096</v>
       </c>
       <c r="H51" s="22" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="I51" s="2">
         <v>4000</v>
@@ -6432,7 +6535,7 @@
         <v>1046</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E52" s="2">
         <v>98</v>
@@ -6444,7 +6547,7 @@
         <v>1097</v>
       </c>
       <c r="H52" s="22" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="I52" s="2">
         <v>4000</v>
@@ -6474,7 +6577,7 @@
         <v>1047</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E53" s="2">
         <v>98</v>
@@ -6486,7 +6589,7 @@
         <v>1098</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="I53" s="2">
         <v>4000</v>
@@ -6516,7 +6619,7 @@
         <v>1048</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="E54" s="2">
         <v>98</v>
@@ -6528,7 +6631,7 @@
         <v>1099</v>
       </c>
       <c r="H54" s="22" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I54" s="2">
         <v>4000</v>
@@ -6558,7 +6661,7 @@
         <v>1049</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="E55" s="2">
         <v>98</v>
@@ -6570,7 +6673,7 @@
         <v>1100</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="I55" s="2">
         <v>4000</v>
@@ -6600,7 +6703,7 @@
         <v>1050</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="E56" s="2">
         <v>98</v>
@@ -6612,7 +6715,7 @@
         <v>1101</v>
       </c>
       <c r="H56" s="22" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="I56" s="2">
         <v>4000</v>
@@ -6642,7 +6745,7 @@
         <v>1051</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E57" s="2">
         <v>98</v>
@@ -6654,7 +6757,7 @@
         <v>1102</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="I57" s="2">
         <v>4000</v>
@@ -6684,7 +6787,7 @@
         <v>1052</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E58" s="2">
         <v>98</v>
@@ -6696,7 +6799,7 @@
         <v>1103</v>
       </c>
       <c r="H58" s="22" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="I58" s="2">
         <v>4000</v>
@@ -6726,7 +6829,7 @@
         <v>1053</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E59" s="2">
         <v>98</v>
@@ -6738,7 +6841,7 @@
         <v>1104</v>
       </c>
       <c r="H59" s="22" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="I59" s="2">
         <v>4000</v>
@@ -6768,7 +6871,7 @@
         <v>1054</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E60" s="12">
         <v>98</v>
@@ -6780,7 +6883,7 @@
         <v>1105</v>
       </c>
       <c r="H60" s="23" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I60" s="12">
         <v>20000</v>
@@ -6809,7 +6912,7 @@
         <v>1055</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="E61" s="2">
         <v>98</v>
@@ -6821,7 +6924,7 @@
         <v>1106</v>
       </c>
       <c r="H61" s="22" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="I61" s="2">
         <v>20000</v>
@@ -6850,7 +6953,7 @@
         <v>1056</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E62" s="2">
         <v>98</v>
@@ -6862,7 +6965,7 @@
         <v>1107</v>
       </c>
       <c r="H62" s="22" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="I62" s="2">
         <v>20000</v>
@@ -6891,7 +6994,7 @@
         <v>1057</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E63" s="2">
         <v>98</v>
@@ -6903,7 +7006,7 @@
         <v>1108</v>
       </c>
       <c r="H63" s="22" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="I63" s="2">
         <v>20000</v>
@@ -6932,7 +7035,7 @@
         <v>1058</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E64" s="2">
         <v>98</v>
@@ -6944,7 +7047,7 @@
         <v>1109</v>
       </c>
       <c r="H64" s="22" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="I64" s="2">
         <v>20000</v>
@@ -6974,7 +7077,7 @@
         <v>1059</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="E65" s="2">
         <v>98</v>
@@ -6986,7 +7089,7 @@
         <v>1110</v>
       </c>
       <c r="H65" s="22" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="I65" s="2">
         <v>20000</v>
@@ -7015,7 +7118,7 @@
         <v>1060</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E66" s="2">
         <v>98</v>
@@ -7027,7 +7130,7 @@
         <v>1111</v>
       </c>
       <c r="H66" s="22" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="I66" s="2">
         <v>20000</v>
@@ -7056,7 +7159,7 @@
         <v>1061</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E67" s="2">
         <v>98</v>
@@ -7068,7 +7171,7 @@
         <v>1112</v>
       </c>
       <c r="H67" s="22" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="I67" s="2">
         <v>20000</v>
@@ -7097,7 +7200,7 @@
         <v>1062</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="E68" s="2">
         <v>98</v>
@@ -7109,7 +7212,7 @@
         <v>1113</v>
       </c>
       <c r="H68" s="22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="I68" s="2">
         <v>20000</v>
@@ -7138,7 +7241,7 @@
         <v>1063</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E69" s="2">
         <v>98</v>
@@ -7150,7 +7253,7 @@
         <v>1114</v>
       </c>
       <c r="H69" s="22" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="I69" s="2">
         <v>20000</v>
@@ -7180,7 +7283,7 @@
         <v>1064</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E70" s="2">
         <v>98</v>
@@ -7192,7 +7295,7 @@
         <v>1115</v>
       </c>
       <c r="H70" s="22" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="I70" s="2">
         <v>20000</v>
@@ -7222,7 +7325,7 @@
         <v>1065</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E71" s="2">
         <v>98</v>
@@ -7234,7 +7337,7 @@
         <v>1116</v>
       </c>
       <c r="H71" s="22" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="I71" s="2">
         <v>20000</v>
@@ -7264,7 +7367,7 @@
         <v>1066</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E72" s="2">
         <v>98</v>
@@ -7276,7 +7379,7 @@
         <v>1117</v>
       </c>
       <c r="H72" s="22" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="I72" s="2">
         <v>20000</v>
@@ -7306,7 +7409,7 @@
         <v>1067</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E73" s="2">
         <v>98</v>
@@ -7318,7 +7421,7 @@
         <v>1118</v>
       </c>
       <c r="H73" s="22" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="I73" s="2">
         <v>20000</v>
@@ -7348,7 +7451,7 @@
         <v>1068</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="E74" s="2">
         <v>98</v>
@@ -7360,7 +7463,7 @@
         <v>1119</v>
       </c>
       <c r="H74" s="22" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="I74" s="2">
         <v>20000</v>
@@ -7390,7 +7493,7 @@
         <v>1069</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E75" s="2">
         <v>98</v>
@@ -7402,7 +7505,7 @@
         <v>1120</v>
       </c>
       <c r="H75" s="22" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="I75" s="2">
         <v>20000</v>
@@ -7432,7 +7535,7 @@
         <v>1070</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="E76" s="2">
         <v>98</v>
@@ -7444,7 +7547,7 @@
         <v>1121</v>
       </c>
       <c r="H76" s="22" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="I76" s="2">
         <v>20000</v>
@@ -7474,7 +7577,7 @@
         <v>1071</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E77" s="2">
         <v>98</v>
@@ -7486,7 +7589,7 @@
         <v>1122</v>
       </c>
       <c r="H77" s="22" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="I77" s="2">
         <v>20000</v>
@@ -7516,7 +7619,7 @@
         <v>1072</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E78" s="2">
         <v>98</v>
@@ -7528,7 +7631,7 @@
         <v>1123</v>
       </c>
       <c r="H78" s="22" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="I78" s="2">
         <v>20000</v>
@@ -7558,7 +7661,7 @@
         <v>1073</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E79" s="2">
         <v>98</v>
@@ -7570,7 +7673,7 @@
         <v>1124</v>
       </c>
       <c r="H79" s="22" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="I79" s="2">
         <v>20000</v>
@@ -7600,7 +7703,7 @@
         <v>1074</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E80" s="2">
         <v>98</v>
@@ -7612,7 +7715,7 @@
         <v>1125</v>
       </c>
       <c r="H80" s="22" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="I80" s="2">
         <v>20000</v>
@@ -7642,7 +7745,7 @@
         <v>1075</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E81" s="2">
         <v>98</v>
@@ -7654,7 +7757,7 @@
         <v>1126</v>
       </c>
       <c r="H81" s="22" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="I81" s="2">
         <v>20000</v>
@@ -7684,7 +7787,7 @@
         <v>1076</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E82" s="2">
         <v>98</v>
@@ -7696,7 +7799,7 @@
         <v>1127</v>
       </c>
       <c r="H82" s="22" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="I82" s="2">
         <v>20000</v>
@@ -7726,7 +7829,7 @@
         <v>1077</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E83" s="2">
         <v>98</v>
@@ -7738,7 +7841,7 @@
         <v>1128</v>
       </c>
       <c r="H83" s="22" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I83" s="2">
         <v>20000</v>
@@ -7768,7 +7871,7 @@
         <v>1078</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="E84" s="2">
         <v>98</v>
@@ -7780,7 +7883,7 @@
         <v>1129</v>
       </c>
       <c r="H84" s="22" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="I84" s="2">
         <v>20000</v>
@@ -7810,7 +7913,7 @@
         <v>1079</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E85" s="2">
         <v>98</v>
@@ -7822,7 +7925,7 @@
         <v>1130</v>
       </c>
       <c r="H85" s="22" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="I85" s="2">
         <v>20000</v>
@@ -7852,7 +7955,7 @@
         <v>1080</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="E86" s="2">
         <v>98</v>
@@ -7864,7 +7967,7 @@
         <v>1131</v>
       </c>
       <c r="H86" s="22" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="I86" s="2">
         <v>20000</v>
@@ -7894,7 +7997,7 @@
         <v>1081</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E87" s="2">
         <v>98</v>
@@ -7906,7 +8009,7 @@
         <v>1132</v>
       </c>
       <c r="H87" s="22" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="I87" s="2">
         <v>20000</v>
@@ -7936,7 +8039,7 @@
         <v>1082</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E88" s="2">
         <v>98</v>
@@ -7948,7 +8051,7 @@
         <v>1133</v>
       </c>
       <c r="H88" s="22" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="I88" s="2">
         <v>20000</v>
@@ -7978,7 +8081,7 @@
         <v>1083</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E89" s="2">
         <v>98</v>
@@ -7990,7 +8093,7 @@
         <v>1134</v>
       </c>
       <c r="H89" s="22" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="I89" s="2">
         <v>20000</v>
@@ -8020,7 +8123,7 @@
         <v>1084</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="E90" s="2">
         <v>98</v>
@@ -8032,7 +8135,7 @@
         <v>1135</v>
       </c>
       <c r="H90" s="22" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="I90" s="2">
         <v>20000</v>
@@ -8062,7 +8165,7 @@
         <v>1085</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E91" s="2">
         <v>98</v>
@@ -8074,7 +8177,7 @@
         <v>1136</v>
       </c>
       <c r="H91" s="22" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="I91" s="2">
         <v>20000</v>
@@ -8104,7 +8207,7 @@
         <v>1086</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E92" s="2">
         <v>98</v>
@@ -8116,7 +8219,7 @@
         <v>1137</v>
       </c>
       <c r="H92" s="22" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="I92" s="2">
         <v>20000</v>
@@ -8146,7 +8249,7 @@
         <v>1087</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E93" s="2">
         <v>98</v>
@@ -8158,7 +8261,7 @@
         <v>1138</v>
       </c>
       <c r="H93" s="22" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="I93" s="2">
         <v>20000</v>
@@ -8188,7 +8291,7 @@
         <v>1088</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E94" s="2">
         <v>98</v>
@@ -8200,7 +8303,7 @@
         <v>1139</v>
       </c>
       <c r="H94" s="22" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="I94" s="2">
         <v>20000</v>
@@ -8230,7 +8333,7 @@
         <v>1089</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E95" s="12">
         <v>98</v>
@@ -8242,7 +8345,7 @@
         <v>1140</v>
       </c>
       <c r="H95" s="23" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="I95" s="12">
         <v>30000</v>
@@ -8271,7 +8374,7 @@
         <v>1090</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="E96" s="2">
         <v>98</v>
@@ -8283,7 +8386,7 @@
         <v>1141</v>
       </c>
       <c r="H96" s="22" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="I96" s="2">
         <v>30000</v>
@@ -8312,7 +8415,7 @@
         <v>1091</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E97" s="2">
         <v>98</v>
@@ -8324,7 +8427,7 @@
         <v>1142</v>
       </c>
       <c r="H97" s="22" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="I97" s="2">
         <v>30000</v>
@@ -8353,7 +8456,7 @@
         <v>1092</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="E98" s="2">
         <v>98</v>
@@ -8365,7 +8468,7 @@
         <v>1143</v>
       </c>
       <c r="H98" s="22" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="I98" s="2">
         <v>30000</v>
@@ -8394,7 +8497,7 @@
         <v>1093</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="E99" s="2">
         <v>98</v>
@@ -8406,7 +8509,7 @@
         <v>1144</v>
       </c>
       <c r="H99" s="22" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="I99" s="2">
         <v>30000</v>
@@ -8436,7 +8539,7 @@
         <v>1094</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="E100" s="2">
         <v>98</v>
@@ -8448,7 +8551,7 @@
         <v>1145</v>
       </c>
       <c r="H100" s="22" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="I100" s="2">
         <v>30000</v>
@@ -8477,7 +8580,7 @@
         <v>1095</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E101" s="2">
         <v>98</v>
@@ -8489,7 +8592,7 @@
         <v>1146</v>
       </c>
       <c r="H101" s="22" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="I101" s="2">
         <v>30000</v>
@@ -8518,7 +8621,7 @@
         <v>1096</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="E102" s="2">
         <v>98</v>
@@ -8530,7 +8633,7 @@
         <v>1147</v>
       </c>
       <c r="H102" s="22" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="I102" s="2">
         <v>30000</v>
@@ -8559,7 +8662,7 @@
         <v>1097</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="E103" s="2">
         <v>98</v>
@@ -8571,7 +8674,7 @@
         <v>1148</v>
       </c>
       <c r="H103" s="22" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="I103" s="2">
         <v>30000</v>
@@ -8600,7 +8703,7 @@
         <v>1098</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E104" s="2">
         <v>98</v>
@@ -8612,7 +8715,7 @@
         <v>1149</v>
       </c>
       <c r="H104" s="22" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="I104" s="2">
         <v>30000</v>
@@ -8642,7 +8745,7 @@
         <v>1099</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="E105" s="2">
         <v>98</v>
@@ -8654,7 +8757,7 @@
         <v>1150</v>
       </c>
       <c r="H105" s="22" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="I105" s="2">
         <v>30000</v>
@@ -8684,7 +8787,7 @@
         <v>1100</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="E106" s="2">
         <v>98</v>
@@ -8696,7 +8799,7 @@
         <v>1151</v>
       </c>
       <c r="H106" s="22" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="I106" s="2">
         <v>30000</v>
@@ -8726,7 +8829,7 @@
         <v>1101</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="E107" s="2">
         <v>98</v>
@@ -8738,7 +8841,7 @@
         <v>1152</v>
       </c>
       <c r="H107" s="22" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="I107" s="2">
         <v>30000</v>
@@ -8768,7 +8871,7 @@
         <v>1102</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="E108" s="2">
         <v>98</v>
@@ -8780,7 +8883,7 @@
         <v>1153</v>
       </c>
       <c r="H108" s="22" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="I108" s="2">
         <v>30000</v>
@@ -8810,7 +8913,7 @@
         <v>1103</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E109" s="2">
         <v>98</v>
@@ -8822,7 +8925,7 @@
         <v>1154</v>
       </c>
       <c r="H109" s="22" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="I109" s="2">
         <v>30000</v>
@@ -8852,7 +8955,7 @@
         <v>1104</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="E110" s="2">
         <v>98</v>
@@ -8864,7 +8967,7 @@
         <v>1155</v>
       </c>
       <c r="H110" s="22" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="I110" s="2">
         <v>30000</v>
@@ -8894,7 +8997,7 @@
         <v>1105</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="E111" s="2">
         <v>98</v>
@@ -8906,7 +9009,7 @@
         <v>1156</v>
       </c>
       <c r="H111" s="22" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="I111" s="2">
         <v>30000</v>
@@ -8936,7 +9039,7 @@
         <v>1106</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="E112" s="2">
         <v>98</v>
@@ -8948,7 +9051,7 @@
         <v>1157</v>
       </c>
       <c r="H112" s="22" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="I112" s="2">
         <v>30000</v>
@@ -8978,7 +9081,7 @@
         <v>1107</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="E113" s="2">
         <v>98</v>
@@ -8990,7 +9093,7 @@
         <v>1158</v>
       </c>
       <c r="H113" s="22" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="I113" s="2">
         <v>30000</v>
@@ -9020,7 +9123,7 @@
         <v>1108</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="E114" s="2">
         <v>98</v>
@@ -9032,7 +9135,7 @@
         <v>1159</v>
       </c>
       <c r="H114" s="22" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="I114" s="2">
         <v>30000</v>
@@ -9062,7 +9165,7 @@
         <v>1109</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="E115" s="2">
         <v>98</v>
@@ -9074,7 +9177,7 @@
         <v>1160</v>
       </c>
       <c r="H115" s="22" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="I115" s="2">
         <v>30000</v>
@@ -9104,7 +9207,7 @@
         <v>1110</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="E116" s="2">
         <v>98</v>
@@ -9116,7 +9219,7 @@
         <v>1161</v>
       </c>
       <c r="H116" s="22" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="I116" s="2">
         <v>30000</v>
@@ -9146,7 +9249,7 @@
         <v>1111</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E117" s="2">
         <v>98</v>
@@ -9158,7 +9261,7 @@
         <v>1162</v>
       </c>
       <c r="H117" s="22" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="I117" s="2">
         <v>30000</v>
@@ -9188,7 +9291,7 @@
         <v>1112</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E118" s="2">
         <v>98</v>
@@ -9200,7 +9303,7 @@
         <v>1163</v>
       </c>
       <c r="H118" s="22" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="I118" s="2">
         <v>30000</v>
@@ -9230,7 +9333,7 @@
         <v>1113</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E119" s="2">
         <v>98</v>
@@ -9242,7 +9345,7 @@
         <v>1164</v>
       </c>
       <c r="H119" s="22" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="I119" s="2">
         <v>30000</v>
@@ -9272,7 +9375,7 @@
         <v>1114</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="E120" s="2">
         <v>98</v>
@@ -9284,7 +9387,7 @@
         <v>1165</v>
       </c>
       <c r="H120" s="22" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="I120" s="2">
         <v>30000</v>
@@ -9314,7 +9417,7 @@
         <v>1115</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E121" s="2">
         <v>98</v>
@@ -9326,7 +9429,7 @@
         <v>1166</v>
       </c>
       <c r="H121" s="22" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="I121" s="2">
         <v>30000</v>
@@ -9356,7 +9459,7 @@
         <v>1116</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E122" s="2">
         <v>98</v>
@@ -9368,7 +9471,7 @@
         <v>1167</v>
       </c>
       <c r="H122" s="22" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="I122" s="2">
         <v>30000</v>
@@ -9398,7 +9501,7 @@
         <v>1117</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="E123" s="2">
         <v>98</v>
@@ -9410,7 +9513,7 @@
         <v>1168</v>
       </c>
       <c r="H123" s="22" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="I123" s="2">
         <v>30000</v>
@@ -9440,7 +9543,7 @@
         <v>1118</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="E124" s="2">
         <v>98</v>
@@ -9452,7 +9555,7 @@
         <v>1169</v>
       </c>
       <c r="H124" s="22" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="I124" s="2">
         <v>30000</v>
@@ -9482,7 +9585,7 @@
         <v>1119</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="E125" s="2">
         <v>98</v>
@@ -9494,7 +9597,7 @@
         <v>1170</v>
       </c>
       <c r="H125" s="22" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="I125" s="2">
         <v>30000</v>
@@ -9524,7 +9627,7 @@
         <v>1120</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E126" s="2">
         <v>98</v>
@@ -9536,7 +9639,7 @@
         <v>1171</v>
       </c>
       <c r="H126" s="22" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="I126" s="2">
         <v>30000</v>
@@ -9566,7 +9669,7 @@
         <v>1121</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E127" s="2">
         <v>98</v>
@@ -9578,7 +9681,7 @@
         <v>1172</v>
       </c>
       <c r="H127" s="22" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="I127" s="2">
         <v>30000</v>
@@ -9608,7 +9711,7 @@
         <v>1122</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="E128" s="2">
         <v>98</v>
@@ -9620,7 +9723,7 @@
         <v>1173</v>
       </c>
       <c r="H128" s="22" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="I128" s="2">
         <v>30000</v>
@@ -9650,7 +9753,7 @@
         <v>1123</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="E129" s="2">
         <v>98</v>
@@ -9662,7 +9765,7 @@
         <v>1174</v>
       </c>
       <c r="H129" s="22" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="I129" s="2">
         <v>30000</v>
@@ -9692,7 +9795,7 @@
         <v>1124</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="E130" s="12">
         <v>98</v>
@@ -9704,7 +9807,7 @@
         <v>1175</v>
       </c>
       <c r="H130" s="23" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="I130" s="12">
         <v>60000</v>
@@ -9733,7 +9836,7 @@
         <v>1125</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="E131" s="2">
         <v>98</v>
@@ -9745,7 +9848,7 @@
         <v>1176</v>
       </c>
       <c r="H131" s="22" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="I131" s="17">
         <v>60000</v>
@@ -9774,7 +9877,7 @@
         <v>1126</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="E132" s="2">
         <v>98</v>
@@ -9786,7 +9889,7 @@
         <v>1177</v>
       </c>
       <c r="H132" s="22" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="I132" s="17">
         <v>60000</v>
@@ -9815,7 +9918,7 @@
         <v>1127</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="E133" s="2">
         <v>98</v>
@@ -9827,7 +9930,7 @@
         <v>1178</v>
       </c>
       <c r="H133" s="22" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="I133" s="17">
         <v>60000</v>
@@ -9856,7 +9959,7 @@
         <v>1128</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="E134" s="2">
         <v>98</v>
@@ -9868,7 +9971,7 @@
         <v>1179</v>
       </c>
       <c r="H134" s="22" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="I134" s="17">
         <v>60000</v>
@@ -9897,7 +10000,7 @@
         <v>1129</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="E135" s="2">
         <v>98</v>
@@ -9909,7 +10012,7 @@
         <v>1180</v>
       </c>
       <c r="H135" s="22" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="I135" s="17">
         <v>60000</v>
@@ -9938,7 +10041,7 @@
         <v>1130</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="E136" s="2">
         <v>98</v>
@@ -9950,7 +10053,7 @@
         <v>1181</v>
       </c>
       <c r="H136" s="22" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="I136" s="17">
         <v>60000</v>
@@ -9979,7 +10082,7 @@
         <v>1131</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="E137" s="2">
         <v>98</v>
@@ -9991,7 +10094,7 @@
         <v>1182</v>
       </c>
       <c r="H137" s="22" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="I137" s="17">
         <v>60000</v>
@@ -10020,7 +10123,7 @@
         <v>1132</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="E138" s="2">
         <v>98</v>
@@ -10032,7 +10135,7 @@
         <v>1183</v>
       </c>
       <c r="H138" s="22" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="I138" s="17">
         <v>60000</v>
@@ -10061,7 +10164,7 @@
         <v>1133</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="E139" s="2">
         <v>98</v>
@@ -10073,7 +10176,7 @@
         <v>1184</v>
       </c>
       <c r="H139" s="22" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I139" s="17">
         <v>60000</v>
@@ -10102,7 +10205,7 @@
         <v>1134</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="E140" s="2">
         <v>98</v>
@@ -10114,7 +10217,7 @@
         <v>1185</v>
       </c>
       <c r="H140" s="22" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="I140" s="17">
         <v>60000</v>
@@ -10143,7 +10246,7 @@
         <v>1135</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="E141" s="2">
         <v>98</v>
@@ -10155,7 +10258,7 @@
         <v>1186</v>
       </c>
       <c r="H141" s="22" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="I141" s="17">
         <v>60000</v>
@@ -10184,7 +10287,7 @@
         <v>1136</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="E142" s="2">
         <v>98</v>
@@ -10196,7 +10299,7 @@
         <v>1187</v>
       </c>
       <c r="H142" s="22" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="I142" s="17">
         <v>60000</v>
@@ -10225,7 +10328,7 @@
         <v>1137</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="E143" s="2">
         <v>98</v>
@@ -10237,7 +10340,7 @@
         <v>1188</v>
       </c>
       <c r="H143" s="22" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="I143" s="17">
         <v>60000</v>
@@ -10266,7 +10369,7 @@
         <v>1138</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="E144" s="2">
         <v>98</v>
@@ -10278,7 +10381,7 @@
         <v>1189</v>
       </c>
       <c r="H144" s="22" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="I144" s="17">
         <v>60000</v>
@@ -10307,7 +10410,7 @@
         <v>1139</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="E145" s="2">
         <v>98</v>
@@ -10319,7 +10422,7 @@
         <v>1190</v>
       </c>
       <c r="H145" s="22" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="I145" s="17">
         <v>60000</v>
@@ -10348,7 +10451,7 @@
         <v>1140</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="E146" s="2">
         <v>98</v>
@@ -10360,7 +10463,7 @@
         <v>1191</v>
       </c>
       <c r="H146" s="22" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="I146" s="17">
         <v>60000</v>
@@ -10389,7 +10492,7 @@
         <v>1141</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="E147" s="2">
         <v>98</v>
@@ -10401,7 +10504,7 @@
         <v>1192</v>
       </c>
       <c r="H147" s="22" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="I147" s="17">
         <v>60000</v>
@@ -10430,7 +10533,7 @@
         <v>1142</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="E148" s="2">
         <v>98</v>
@@ -10442,7 +10545,7 @@
         <v>1193</v>
       </c>
       <c r="H148" s="22" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="I148" s="17">
         <v>60000</v>
@@ -10471,7 +10574,7 @@
         <v>1143</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="E149" s="2">
         <v>98</v>
@@ -10483,7 +10586,7 @@
         <v>1194</v>
       </c>
       <c r="H149" s="22" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="I149" s="17">
         <v>60000</v>
@@ -10512,7 +10615,7 @@
         <v>1144</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="E150" s="2">
         <v>98</v>
@@ -10524,7 +10627,7 @@
         <v>1195</v>
       </c>
       <c r="H150" s="22" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="I150" s="17">
         <v>60000</v>
@@ -10553,7 +10656,7 @@
         <v>1145</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E151" s="2">
         <v>98</v>
@@ -10565,7 +10668,7 @@
         <v>1196</v>
       </c>
       <c r="H151" s="22" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="I151" s="17">
         <v>60000</v>
@@ -10594,7 +10697,7 @@
         <v>1146</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E152" s="2">
         <v>98</v>
@@ -10606,7 +10709,7 @@
         <v>1197</v>
       </c>
       <c r="H152" s="22" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="I152" s="17">
         <v>60000</v>
@@ -10635,7 +10738,7 @@
         <v>1147</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E153" s="2">
         <v>98</v>
@@ -10647,7 +10750,7 @@
         <v>1198</v>
       </c>
       <c r="H153" s="22" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="I153" s="17">
         <v>60000</v>
@@ -10676,7 +10779,7 @@
         <v>1148</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="E154" s="2">
         <v>98</v>
@@ -10688,7 +10791,7 @@
         <v>1199</v>
       </c>
       <c r="H154" s="22" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="I154" s="17">
         <v>60000</v>
@@ -10717,7 +10820,7 @@
         <v>1149</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="E155" s="2">
         <v>98</v>
@@ -10729,7 +10832,7 @@
         <v>1200</v>
       </c>
       <c r="H155" s="22" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="I155" s="17">
         <v>60000</v>
@@ -10758,7 +10861,7 @@
         <v>1150</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="E156" s="2">
         <v>98</v>
@@ -10770,7 +10873,7 @@
         <v>1201</v>
       </c>
       <c r="H156" s="22" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="I156" s="17">
         <v>60000</v>
@@ -10799,7 +10902,7 @@
         <v>1151</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="E157" s="2">
         <v>98</v>
@@ -10811,7 +10914,7 @@
         <v>1202</v>
       </c>
       <c r="H157" s="22" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="I157" s="17">
         <v>60000</v>
@@ -10840,7 +10943,7 @@
         <v>1152</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="E158" s="2">
         <v>98</v>
@@ -10852,7 +10955,7 @@
         <v>1203</v>
       </c>
       <c r="H158" s="22" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="I158" s="17">
         <v>60000</v>
@@ -10881,7 +10984,7 @@
         <v>1153</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="E159" s="2">
         <v>98</v>
@@ -10893,7 +10996,7 @@
         <v>1204</v>
       </c>
       <c r="H159" s="22" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="I159" s="17">
         <v>60000</v>
@@ -10922,7 +11025,7 @@
         <v>1154</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="E160" s="2">
         <v>98</v>
@@ -10934,7 +11037,7 @@
         <v>1205</v>
       </c>
       <c r="H160" s="22" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="I160" s="17">
         <v>60000</v>
@@ -10963,7 +11066,7 @@
         <v>1155</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E161" s="2">
         <v>98</v>
@@ -10975,7 +11078,7 @@
         <v>1206</v>
       </c>
       <c r="H161" s="22" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="I161" s="17">
         <v>60000</v>
@@ -11004,7 +11107,7 @@
         <v>1156</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="E162" s="2">
         <v>98</v>
@@ -11016,7 +11119,7 @@
         <v>1207</v>
       </c>
       <c r="H162" s="22" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="I162" s="17">
         <v>60000</v>
@@ -11045,7 +11148,7 @@
         <v>1157</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="E163" s="2">
         <v>98</v>
@@ -11057,7 +11160,7 @@
         <v>1208</v>
       </c>
       <c r="H163" s="22" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="I163" s="17">
         <v>60000</v>
@@ -11086,7 +11189,7 @@
         <v>1158</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="E164" s="2">
         <v>98</v>
@@ -11098,7 +11201,7 @@
         <v>1209</v>
       </c>
       <c r="H164" s="22" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="I164" s="17">
         <v>60000</v>
@@ -11312,7 +11415,7 @@
         <v>2000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -11324,7 +11427,7 @@
         <v>1070</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>435</v>
+        <v>95</v>
       </c>
       <c r="I6" s="2">
         <v>120000</v>
@@ -11356,7 +11459,7 @@
         <v>2001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -11368,7 +11471,7 @@
         <v>1071</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="I7" s="2">
         <v>120000</v>
@@ -11400,7 +11503,7 @@
         <v>2002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -11412,7 +11515,7 @@
         <v>1072</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="I8" s="2">
         <v>120000</v>
@@ -11444,7 +11547,7 @@
         <v>2003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -11456,7 +11559,7 @@
         <v>1073</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="I9" s="2">
         <v>120000</v>
@@ -11488,7 +11591,7 @@
         <v>2004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -11500,7 +11603,7 @@
         <v>1074</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="I10" s="2">
         <v>120000</v>
@@ -11532,7 +11635,7 @@
         <v>2005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -11544,7 +11647,7 @@
         <v>1104</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="I11" s="2">
         <v>20000</v>
@@ -11590,7 +11693,7 @@
         <v>2006</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -11602,7 +11705,7 @@
         <v>1105</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="I14" s="2">
         <v>360000</v>
@@ -11634,7 +11737,7 @@
         <v>2007</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -11646,7 +11749,7 @@
         <v>1106</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="I15" s="2">
         <v>360000</v>
@@ -11678,7 +11781,7 @@
         <v>2008</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -11690,7 +11793,7 @@
         <v>1107</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="I16" s="2">
         <v>360000</v>
@@ -11722,7 +11825,7 @@
         <v>2009</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -11734,7 +11837,7 @@
         <v>1108</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="I17" s="2">
         <v>360000</v>
@@ -11766,7 +11869,7 @@
         <v>2010</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -11778,7 +11881,7 @@
         <v>1139</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="I18" s="2">
         <v>360000</v>
@@ -11810,7 +11913,7 @@
         <v>2011</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -11822,7 +11925,7 @@
         <v>1139</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -11861,7 +11964,7 @@
         <v>2012</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -11873,7 +11976,7 @@
         <v>1140</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="I21" s="2">
         <v>360000</v>
@@ -11905,7 +12008,7 @@
         <v>2013</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -11917,7 +12020,7 @@
         <v>1141</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="I22" s="2">
         <v>360000</v>
@@ -11949,7 +12052,7 @@
         <v>2014</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -11961,7 +12064,7 @@
         <v>1142</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="I23" s="2">
         <v>360000</v>
@@ -11993,7 +12096,7 @@
         <v>2015</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -12005,7 +12108,7 @@
         <v>1143</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="I24" s="2">
         <v>360000</v>
@@ -12037,7 +12140,7 @@
         <v>2016</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -12049,7 +12152,7 @@
         <v>1209</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="I25" s="2">
         <v>360000</v>
@@ -12081,7 +12184,7 @@
         <v>2017</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -12093,7 +12196,7 @@
         <v>1209</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="I26" s="2">
         <v>180000</v>
@@ -12122,16 +12225,16 @@
     </row>
     <row r="27" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C27" s="2">
         <v>2018</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -12143,7 +12246,7 @@
         <v>1174</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>
@@ -12341,7 +12444,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 C2:C5 F3:G5 F14:G19 F21:G27" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 C2:C5 F14:G19 F3:G5 F21:G27" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>元旦快乐</t>
+    <t>春节快乐</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2026-01-01</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
+    <t>2026-02-12</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
   </si>
   <si>
     <t>平时部分掉落</t>
@@ -12444,7 +12444,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 C2:C5 F14:G19 F3:G5 F21:G27" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 C2:C5 F3:G5 F14:G19 F21:G27" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -346,7 +346,7 @@
     <t>50</t>
   </si>
   <si>
-    <t>2026-02-12</t>
+    <t>2026-02-11</t>
   </si>
   <si>
     <t>2026-02-23</t>
@@ -1871,12 +1871,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>春节快乐</t>
+    <t>元宵快乐</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2026-02-11</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
+    <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="540">
   <si>
     <t>_id</t>
   </si>
@@ -1577,6 +1577,216 @@
   </si>
   <si>
     <t>1400158</t>
+  </si>
+  <si>
+    <t>虚无鸡爪</t>
+  </si>
+  <si>
+    <t>1400159</t>
+  </si>
+  <si>
+    <t>虚无鹿茸</t>
+  </si>
+  <si>
+    <t>1400160</t>
+  </si>
+  <si>
+    <t>虚无草帽</t>
+  </si>
+  <si>
+    <t>1400161</t>
+  </si>
+  <si>
+    <t>虚无猫爪</t>
+  </si>
+  <si>
+    <t>1400162</t>
+  </si>
+  <si>
+    <t>虚无花朵</t>
+  </si>
+  <si>
+    <t>1400163</t>
+  </si>
+  <si>
+    <t>虚无冰晶</t>
+  </si>
+  <si>
+    <t>1400164</t>
+  </si>
+  <si>
+    <t>虚无蝠翼</t>
+  </si>
+  <si>
+    <t>1400165</t>
+  </si>
+  <si>
+    <t>虚无魂火</t>
+  </si>
+  <si>
+    <t>1400166</t>
+  </si>
+  <si>
+    <t>虚无腐肉</t>
+  </si>
+  <si>
+    <t>1400167</t>
+  </si>
+  <si>
+    <t>虚无蛇胆</t>
+  </si>
+  <si>
+    <t>1400168</t>
+  </si>
+  <si>
+    <t>虚无狼爪</t>
+  </si>
+  <si>
+    <t>1400169</t>
+  </si>
+  <si>
+    <t>虚无虫皮</t>
+  </si>
+  <si>
+    <t>1400170</t>
+  </si>
+  <si>
+    <t>虚无鹰羽</t>
+  </si>
+  <si>
+    <t>1400171</t>
+  </si>
+  <si>
+    <t>虚无虫角</t>
+  </si>
+  <si>
+    <t>1400172</t>
+  </si>
+  <si>
+    <t>虚无蜈膏</t>
+  </si>
+  <si>
+    <t>1400173</t>
+  </si>
+  <si>
+    <t>虚无虫心</t>
+  </si>
+  <si>
+    <t>1400174</t>
+  </si>
+  <si>
+    <t>虚无龙皮</t>
+  </si>
+  <si>
+    <t>1400175</t>
+  </si>
+  <si>
+    <t>虚无猪皮</t>
+  </si>
+  <si>
+    <t>1400176</t>
+  </si>
+  <si>
+    <t>虚无猪心</t>
+  </si>
+  <si>
+    <t>1400177</t>
+  </si>
+  <si>
+    <t>虚无蝎皮</t>
+  </si>
+  <si>
+    <t>1400178</t>
+  </si>
+  <si>
+    <t>虚无宝甲</t>
+  </si>
+  <si>
+    <t>1400179</t>
+  </si>
+  <si>
+    <t>虚无号角</t>
+  </si>
+  <si>
+    <t>1400180</t>
+  </si>
+  <si>
+    <t>虚无雕像</t>
+  </si>
+  <si>
+    <t>1400181</t>
+  </si>
+  <si>
+    <t>虚无神像</t>
+  </si>
+  <si>
+    <t>1400182</t>
+  </si>
+  <si>
+    <t>虚无獠牙</t>
+  </si>
+  <si>
+    <t>1400183</t>
+  </si>
+  <si>
+    <t>虚无树心</t>
+  </si>
+  <si>
+    <t>1400184</t>
+  </si>
+  <si>
+    <t>虚无魔心</t>
+  </si>
+  <si>
+    <t>1400185</t>
+  </si>
+  <si>
+    <t>虚无尸心</t>
+  </si>
+  <si>
+    <t>1400186</t>
+  </si>
+  <si>
+    <t>虚无法杖</t>
+  </si>
+  <si>
+    <t>1400187</t>
+  </si>
+  <si>
+    <t>虚无权杖</t>
+  </si>
+  <si>
+    <t>1400188</t>
+  </si>
+  <si>
+    <t>虚无战锤</t>
+  </si>
+  <si>
+    <t>1400189</t>
+  </si>
+  <si>
+    <t>虚无血核</t>
+  </si>
+  <si>
+    <t>1400190</t>
+  </si>
+  <si>
+    <t>虚无魔核</t>
+  </si>
+  <si>
+    <t>1400191</t>
+  </si>
+  <si>
+    <t>虚无龙甲</t>
+  </si>
+  <si>
+    <t>1400192</t>
+  </si>
+  <si>
+    <t>虚无龙爪</t>
+  </si>
+  <si>
+    <t>1400193</t>
   </si>
   <si>
     <t>武器衣服红装</t>
@@ -4466,7 +4676,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P164"/>
+  <dimension ref="C1:P199"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -11222,6 +11432,1441 @@
         <v>38</v>
       </c>
       <c r="O164" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="165" customHeight="1" spans="3:15">
+      <c r="C165" s="12">
+        <v>1159</v>
+      </c>
+      <c r="D165" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="E165" s="12">
+        <v>98</v>
+      </c>
+      <c r="F165" s="14">
+        <v>1210</v>
+      </c>
+      <c r="G165" s="14">
+        <v>1210</v>
+      </c>
+      <c r="H165" s="23" t="s">
+        <v>441</v>
+      </c>
+      <c r="I165" s="12">
+        <v>90000</v>
+      </c>
+      <c r="J165" s="12">
+        <v>700000</v>
+      </c>
+      <c r="K165" s="12">
+        <v>0</v>
+      </c>
+      <c r="L165" s="12">
+        <v>0</v>
+      </c>
+      <c r="M165" s="12">
+        <v>0</v>
+      </c>
+      <c r="N165" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="O165" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="166" customHeight="1" spans="3:15">
+      <c r="C166" s="2">
+        <v>1160</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="E166" s="2">
+        <v>98</v>
+      </c>
+      <c r="F166" s="9">
+        <v>1211</v>
+      </c>
+      <c r="G166" s="9">
+        <v>1211</v>
+      </c>
+      <c r="H166" s="22" t="s">
+        <v>443</v>
+      </c>
+      <c r="I166" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J166" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K166" s="2">
+        <v>0</v>
+      </c>
+      <c r="L166" s="2">
+        <v>0</v>
+      </c>
+      <c r="M166" s="2">
+        <v>0</v>
+      </c>
+      <c r="N166" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O166" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="167" customHeight="1" spans="3:15">
+      <c r="C167" s="2">
+        <v>1161</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E167" s="2">
+        <v>98</v>
+      </c>
+      <c r="F167" s="9">
+        <v>1212</v>
+      </c>
+      <c r="G167" s="9">
+        <v>1212</v>
+      </c>
+      <c r="H167" s="22" t="s">
+        <v>445</v>
+      </c>
+      <c r="I167" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J167" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K167" s="2">
+        <v>0</v>
+      </c>
+      <c r="L167" s="2">
+        <v>0</v>
+      </c>
+      <c r="M167" s="2">
+        <v>0</v>
+      </c>
+      <c r="N167" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O167" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="168" customHeight="1" spans="3:15">
+      <c r="C168" s="2">
+        <v>1162</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E168" s="2">
+        <v>98</v>
+      </c>
+      <c r="F168" s="9">
+        <v>1213</v>
+      </c>
+      <c r="G168" s="9">
+        <v>1213</v>
+      </c>
+      <c r="H168" s="22" t="s">
+        <v>447</v>
+      </c>
+      <c r="I168" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J168" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K168" s="2">
+        <v>0</v>
+      </c>
+      <c r="L168" s="2">
+        <v>0</v>
+      </c>
+      <c r="M168" s="2">
+        <v>0</v>
+      </c>
+      <c r="N168" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O168" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="169" customHeight="1" spans="3:15">
+      <c r="C169" s="2">
+        <v>1163</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E169" s="2">
+        <v>98</v>
+      </c>
+      <c r="F169" s="9">
+        <v>1214</v>
+      </c>
+      <c r="G169" s="9">
+        <v>1214</v>
+      </c>
+      <c r="H169" s="22" t="s">
+        <v>449</v>
+      </c>
+      <c r="I169" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J169" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K169" s="2">
+        <v>0</v>
+      </c>
+      <c r="L169" s="2">
+        <v>0</v>
+      </c>
+      <c r="M169" s="2">
+        <v>0</v>
+      </c>
+      <c r="N169" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O169" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="170" customHeight="1" spans="3:15">
+      <c r="C170" s="2">
+        <v>1164</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E170" s="2">
+        <v>98</v>
+      </c>
+      <c r="F170" s="9">
+        <v>1215</v>
+      </c>
+      <c r="G170" s="9">
+        <v>1215</v>
+      </c>
+      <c r="H170" s="22" t="s">
+        <v>451</v>
+      </c>
+      <c r="I170" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J170" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K170" s="2">
+        <v>0</v>
+      </c>
+      <c r="L170" s="2">
+        <v>0</v>
+      </c>
+      <c r="M170" s="2">
+        <v>0</v>
+      </c>
+      <c r="N170" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O170" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="171" customHeight="1" spans="3:15">
+      <c r="C171" s="2">
+        <v>1165</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E171" s="2">
+        <v>98</v>
+      </c>
+      <c r="F171" s="9">
+        <v>1216</v>
+      </c>
+      <c r="G171" s="9">
+        <v>1216</v>
+      </c>
+      <c r="H171" s="22" t="s">
+        <v>453</v>
+      </c>
+      <c r="I171" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J171" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K171" s="2">
+        <v>0</v>
+      </c>
+      <c r="L171" s="2">
+        <v>0</v>
+      </c>
+      <c r="M171" s="2">
+        <v>0</v>
+      </c>
+      <c r="N171" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O171" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="172" customHeight="1" spans="3:15">
+      <c r="C172" s="2">
+        <v>1166</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="E172" s="2">
+        <v>98</v>
+      </c>
+      <c r="F172" s="9">
+        <v>1217</v>
+      </c>
+      <c r="G172" s="9">
+        <v>1217</v>
+      </c>
+      <c r="H172" s="22" t="s">
+        <v>455</v>
+      </c>
+      <c r="I172" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J172" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K172" s="2">
+        <v>0</v>
+      </c>
+      <c r="L172" s="2">
+        <v>0</v>
+      </c>
+      <c r="M172" s="2">
+        <v>0</v>
+      </c>
+      <c r="N172" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O172" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="173" customHeight="1" spans="3:15">
+      <c r="C173" s="2">
+        <v>1167</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E173" s="2">
+        <v>98</v>
+      </c>
+      <c r="F173" s="9">
+        <v>1218</v>
+      </c>
+      <c r="G173" s="9">
+        <v>1218</v>
+      </c>
+      <c r="H173" s="22" t="s">
+        <v>457</v>
+      </c>
+      <c r="I173" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J173" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K173" s="2">
+        <v>0</v>
+      </c>
+      <c r="L173" s="2">
+        <v>0</v>
+      </c>
+      <c r="M173" s="2">
+        <v>0</v>
+      </c>
+      <c r="N173" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O173" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="174" customHeight="1" spans="3:15">
+      <c r="C174" s="2">
+        <v>1168</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E174" s="2">
+        <v>98</v>
+      </c>
+      <c r="F174" s="9">
+        <v>1219</v>
+      </c>
+      <c r="G174" s="9">
+        <v>1219</v>
+      </c>
+      <c r="H174" s="22" t="s">
+        <v>459</v>
+      </c>
+      <c r="I174" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J174" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K174" s="2">
+        <v>0</v>
+      </c>
+      <c r="L174" s="2">
+        <v>0</v>
+      </c>
+      <c r="M174" s="2">
+        <v>0</v>
+      </c>
+      <c r="N174" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O174" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="175" customHeight="1" spans="3:15">
+      <c r="C175" s="2">
+        <v>1169</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E175" s="2">
+        <v>98</v>
+      </c>
+      <c r="F175" s="9">
+        <v>1220</v>
+      </c>
+      <c r="G175" s="9">
+        <v>1220</v>
+      </c>
+      <c r="H175" s="22" t="s">
+        <v>461</v>
+      </c>
+      <c r="I175" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J175" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K175" s="2">
+        <v>0</v>
+      </c>
+      <c r="L175" s="2">
+        <v>0</v>
+      </c>
+      <c r="M175" s="2">
+        <v>0</v>
+      </c>
+      <c r="N175" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O175" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="176" customHeight="1" spans="3:15">
+      <c r="C176" s="2">
+        <v>1170</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E176" s="2">
+        <v>98</v>
+      </c>
+      <c r="F176" s="9">
+        <v>1221</v>
+      </c>
+      <c r="G176" s="9">
+        <v>1221</v>
+      </c>
+      <c r="H176" s="22" t="s">
+        <v>463</v>
+      </c>
+      <c r="I176" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J176" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K176" s="2">
+        <v>0</v>
+      </c>
+      <c r="L176" s="2">
+        <v>0</v>
+      </c>
+      <c r="M176" s="2">
+        <v>0</v>
+      </c>
+      <c r="N176" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O176" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="177" customHeight="1" spans="3:15">
+      <c r="C177" s="2">
+        <v>1171</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E177" s="2">
+        <v>98</v>
+      </c>
+      <c r="F177" s="9">
+        <v>1222</v>
+      </c>
+      <c r="G177" s="9">
+        <v>1222</v>
+      </c>
+      <c r="H177" s="22" t="s">
+        <v>465</v>
+      </c>
+      <c r="I177" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J177" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K177" s="2">
+        <v>0</v>
+      </c>
+      <c r="L177" s="2">
+        <v>0</v>
+      </c>
+      <c r="M177" s="2">
+        <v>0</v>
+      </c>
+      <c r="N177" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O177" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="178" customHeight="1" spans="3:15">
+      <c r="C178" s="2">
+        <v>1172</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="E178" s="2">
+        <v>98</v>
+      </c>
+      <c r="F178" s="9">
+        <v>1223</v>
+      </c>
+      <c r="G178" s="9">
+        <v>1223</v>
+      </c>
+      <c r="H178" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="I178" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J178" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K178" s="2">
+        <v>0</v>
+      </c>
+      <c r="L178" s="2">
+        <v>0</v>
+      </c>
+      <c r="M178" s="2">
+        <v>0</v>
+      </c>
+      <c r="N178" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O178" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="179" customHeight="1" spans="3:15">
+      <c r="C179" s="2">
+        <v>1173</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E179" s="2">
+        <v>98</v>
+      </c>
+      <c r="F179" s="9">
+        <v>1224</v>
+      </c>
+      <c r="G179" s="9">
+        <v>1224</v>
+      </c>
+      <c r="H179" s="22" t="s">
+        <v>469</v>
+      </c>
+      <c r="I179" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J179" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K179" s="2">
+        <v>0</v>
+      </c>
+      <c r="L179" s="2">
+        <v>0</v>
+      </c>
+      <c r="M179" s="2">
+        <v>0</v>
+      </c>
+      <c r="N179" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O179" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="180" customHeight="1" spans="3:15">
+      <c r="C180" s="2">
+        <v>1174</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E180" s="2">
+        <v>98</v>
+      </c>
+      <c r="F180" s="9">
+        <v>1225</v>
+      </c>
+      <c r="G180" s="9">
+        <v>1225</v>
+      </c>
+      <c r="H180" s="22" t="s">
+        <v>471</v>
+      </c>
+      <c r="I180" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J180" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K180" s="2">
+        <v>0</v>
+      </c>
+      <c r="L180" s="2">
+        <v>0</v>
+      </c>
+      <c r="M180" s="2">
+        <v>0</v>
+      </c>
+      <c r="N180" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O180" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="181" customHeight="1" spans="3:15">
+      <c r="C181" s="2">
+        <v>1175</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="E181" s="2">
+        <v>98</v>
+      </c>
+      <c r="F181" s="9">
+        <v>1226</v>
+      </c>
+      <c r="G181" s="9">
+        <v>1226</v>
+      </c>
+      <c r="H181" s="22" t="s">
+        <v>473</v>
+      </c>
+      <c r="I181" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J181" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K181" s="2">
+        <v>0</v>
+      </c>
+      <c r="L181" s="2">
+        <v>0</v>
+      </c>
+      <c r="M181" s="2">
+        <v>0</v>
+      </c>
+      <c r="N181" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O181" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" spans="3:15">
+      <c r="C182" s="2">
+        <v>1176</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E182" s="2">
+        <v>98</v>
+      </c>
+      <c r="F182" s="9">
+        <v>1227</v>
+      </c>
+      <c r="G182" s="9">
+        <v>1227</v>
+      </c>
+      <c r="H182" s="22" t="s">
+        <v>475</v>
+      </c>
+      <c r="I182" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J182" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K182" s="2">
+        <v>0</v>
+      </c>
+      <c r="L182" s="2">
+        <v>0</v>
+      </c>
+      <c r="M182" s="2">
+        <v>0</v>
+      </c>
+      <c r="N182" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O182" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" spans="3:15">
+      <c r="C183" s="2">
+        <v>1177</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E183" s="2">
+        <v>98</v>
+      </c>
+      <c r="F183" s="9">
+        <v>1228</v>
+      </c>
+      <c r="G183" s="9">
+        <v>1228</v>
+      </c>
+      <c r="H183" s="22" t="s">
+        <v>477</v>
+      </c>
+      <c r="I183" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J183" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K183" s="2">
+        <v>0</v>
+      </c>
+      <c r="L183" s="2">
+        <v>0</v>
+      </c>
+      <c r="M183" s="2">
+        <v>0</v>
+      </c>
+      <c r="N183" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O183" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" spans="3:15">
+      <c r="C184" s="2">
+        <v>1178</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E184" s="2">
+        <v>98</v>
+      </c>
+      <c r="F184" s="9">
+        <v>1229</v>
+      </c>
+      <c r="G184" s="9">
+        <v>1229</v>
+      </c>
+      <c r="H184" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="I184" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J184" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K184" s="2">
+        <v>0</v>
+      </c>
+      <c r="L184" s="2">
+        <v>0</v>
+      </c>
+      <c r="M184" s="2">
+        <v>0</v>
+      </c>
+      <c r="N184" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O184" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="185" customHeight="1" spans="3:15">
+      <c r="C185" s="2">
+        <v>1179</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E185" s="2">
+        <v>98</v>
+      </c>
+      <c r="F185" s="9">
+        <v>1230</v>
+      </c>
+      <c r="G185" s="9">
+        <v>1230</v>
+      </c>
+      <c r="H185" s="22" t="s">
+        <v>481</v>
+      </c>
+      <c r="I185" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J185" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K185" s="2">
+        <v>0</v>
+      </c>
+      <c r="L185" s="2">
+        <v>0</v>
+      </c>
+      <c r="M185" s="2">
+        <v>0</v>
+      </c>
+      <c r="N185" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O185" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="186" customHeight="1" spans="3:15">
+      <c r="C186" s="2">
+        <v>1180</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E186" s="2">
+        <v>98</v>
+      </c>
+      <c r="F186" s="9">
+        <v>1231</v>
+      </c>
+      <c r="G186" s="9">
+        <v>1231</v>
+      </c>
+      <c r="H186" s="22" t="s">
+        <v>483</v>
+      </c>
+      <c r="I186" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J186" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K186" s="2">
+        <v>0</v>
+      </c>
+      <c r="L186" s="2">
+        <v>0</v>
+      </c>
+      <c r="M186" s="2">
+        <v>0</v>
+      </c>
+      <c r="N186" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O186" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" spans="3:15">
+      <c r="C187" s="2">
+        <v>1181</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E187" s="2">
+        <v>98</v>
+      </c>
+      <c r="F187" s="9">
+        <v>1232</v>
+      </c>
+      <c r="G187" s="9">
+        <v>1232</v>
+      </c>
+      <c r="H187" s="22" t="s">
+        <v>485</v>
+      </c>
+      <c r="I187" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J187" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K187" s="2">
+        <v>0</v>
+      </c>
+      <c r="L187" s="2">
+        <v>0</v>
+      </c>
+      <c r="M187" s="2">
+        <v>0</v>
+      </c>
+      <c r="N187" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O187" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="188" customHeight="1" spans="3:15">
+      <c r="C188" s="2">
+        <v>1182</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E188" s="2">
+        <v>98</v>
+      </c>
+      <c r="F188" s="9">
+        <v>1233</v>
+      </c>
+      <c r="G188" s="9">
+        <v>1233</v>
+      </c>
+      <c r="H188" s="22" t="s">
+        <v>487</v>
+      </c>
+      <c r="I188" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J188" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K188" s="2">
+        <v>0</v>
+      </c>
+      <c r="L188" s="2">
+        <v>0</v>
+      </c>
+      <c r="M188" s="2">
+        <v>0</v>
+      </c>
+      <c r="N188" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O188" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" spans="3:15">
+      <c r="C189" s="2">
+        <v>1183</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="E189" s="2">
+        <v>98</v>
+      </c>
+      <c r="F189" s="9">
+        <v>1234</v>
+      </c>
+      <c r="G189" s="9">
+        <v>1234</v>
+      </c>
+      <c r="H189" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="I189" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J189" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K189" s="2">
+        <v>0</v>
+      </c>
+      <c r="L189" s="2">
+        <v>0</v>
+      </c>
+      <c r="M189" s="2">
+        <v>0</v>
+      </c>
+      <c r="N189" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O189" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" spans="3:15">
+      <c r="C190" s="2">
+        <v>1184</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E190" s="2">
+        <v>98</v>
+      </c>
+      <c r="F190" s="9">
+        <v>1235</v>
+      </c>
+      <c r="G190" s="9">
+        <v>1235</v>
+      </c>
+      <c r="H190" s="22" t="s">
+        <v>491</v>
+      </c>
+      <c r="I190" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J190" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K190" s="2">
+        <v>0</v>
+      </c>
+      <c r="L190" s="2">
+        <v>0</v>
+      </c>
+      <c r="M190" s="2">
+        <v>0</v>
+      </c>
+      <c r="N190" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O190" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="191" customHeight="1" spans="3:15">
+      <c r="C191" s="2">
+        <v>1185</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E191" s="2">
+        <v>98</v>
+      </c>
+      <c r="F191" s="9">
+        <v>1236</v>
+      </c>
+      <c r="G191" s="9">
+        <v>1236</v>
+      </c>
+      <c r="H191" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="I191" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J191" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K191" s="2">
+        <v>0</v>
+      </c>
+      <c r="L191" s="2">
+        <v>0</v>
+      </c>
+      <c r="M191" s="2">
+        <v>0</v>
+      </c>
+      <c r="N191" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O191" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="192" customHeight="1" spans="3:15">
+      <c r="C192" s="2">
+        <v>1186</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E192" s="2">
+        <v>98</v>
+      </c>
+      <c r="F192" s="9">
+        <v>1237</v>
+      </c>
+      <c r="G192" s="9">
+        <v>1237</v>
+      </c>
+      <c r="H192" s="22" t="s">
+        <v>495</v>
+      </c>
+      <c r="I192" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J192" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K192" s="2">
+        <v>0</v>
+      </c>
+      <c r="L192" s="2">
+        <v>0</v>
+      </c>
+      <c r="M192" s="2">
+        <v>0</v>
+      </c>
+      <c r="N192" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O192" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="193" customHeight="1" spans="3:15">
+      <c r="C193" s="2">
+        <v>1187</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E193" s="2">
+        <v>98</v>
+      </c>
+      <c r="F193" s="9">
+        <v>1238</v>
+      </c>
+      <c r="G193" s="9">
+        <v>1238</v>
+      </c>
+      <c r="H193" s="22" t="s">
+        <v>497</v>
+      </c>
+      <c r="I193" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J193" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K193" s="2">
+        <v>0</v>
+      </c>
+      <c r="L193" s="2">
+        <v>0</v>
+      </c>
+      <c r="M193" s="2">
+        <v>0</v>
+      </c>
+      <c r="N193" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O193" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="194" customHeight="1" spans="3:15">
+      <c r="C194" s="2">
+        <v>1188</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E194" s="2">
+        <v>98</v>
+      </c>
+      <c r="F194" s="9">
+        <v>1239</v>
+      </c>
+      <c r="G194" s="9">
+        <v>1239</v>
+      </c>
+      <c r="H194" s="22" t="s">
+        <v>499</v>
+      </c>
+      <c r="I194" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J194" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K194" s="2">
+        <v>0</v>
+      </c>
+      <c r="L194" s="2">
+        <v>0</v>
+      </c>
+      <c r="M194" s="2">
+        <v>0</v>
+      </c>
+      <c r="N194" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O194" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="195" customHeight="1" spans="3:15">
+      <c r="C195" s="2">
+        <v>1189</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E195" s="2">
+        <v>98</v>
+      </c>
+      <c r="F195" s="9">
+        <v>1240</v>
+      </c>
+      <c r="G195" s="9">
+        <v>1240</v>
+      </c>
+      <c r="H195" s="22" t="s">
+        <v>501</v>
+      </c>
+      <c r="I195" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J195" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K195" s="2">
+        <v>0</v>
+      </c>
+      <c r="L195" s="2">
+        <v>0</v>
+      </c>
+      <c r="M195" s="2">
+        <v>0</v>
+      </c>
+      <c r="N195" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O195" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="196" customHeight="1" spans="3:15">
+      <c r="C196" s="2">
+        <v>1190</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E196" s="2">
+        <v>98</v>
+      </c>
+      <c r="F196" s="9">
+        <v>1241</v>
+      </c>
+      <c r="G196" s="9">
+        <v>1241</v>
+      </c>
+      <c r="H196" s="22" t="s">
+        <v>503</v>
+      </c>
+      <c r="I196" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J196" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K196" s="2">
+        <v>0</v>
+      </c>
+      <c r="L196" s="2">
+        <v>0</v>
+      </c>
+      <c r="M196" s="2">
+        <v>0</v>
+      </c>
+      <c r="N196" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O196" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="197" customHeight="1" spans="3:15">
+      <c r="C197" s="2">
+        <v>1191</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E197" s="2">
+        <v>98</v>
+      </c>
+      <c r="F197" s="9">
+        <v>1242</v>
+      </c>
+      <c r="G197" s="9">
+        <v>1242</v>
+      </c>
+      <c r="H197" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="I197" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J197" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K197" s="2">
+        <v>0</v>
+      </c>
+      <c r="L197" s="2">
+        <v>0</v>
+      </c>
+      <c r="M197" s="2">
+        <v>0</v>
+      </c>
+      <c r="N197" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O197" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="198" customHeight="1" spans="3:15">
+      <c r="C198" s="2">
+        <v>1192</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E198" s="2">
+        <v>98</v>
+      </c>
+      <c r="F198" s="9">
+        <v>1243</v>
+      </c>
+      <c r="G198" s="9">
+        <v>1243</v>
+      </c>
+      <c r="H198" s="22" t="s">
+        <v>507</v>
+      </c>
+      <c r="I198" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J198" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K198" s="2">
+        <v>0</v>
+      </c>
+      <c r="L198" s="2">
+        <v>0</v>
+      </c>
+      <c r="M198" s="2">
+        <v>0</v>
+      </c>
+      <c r="N198" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O198" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="199" customHeight="1" spans="3:15">
+      <c r="C199" s="2">
+        <v>1193</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E199" s="2">
+        <v>98</v>
+      </c>
+      <c r="F199" s="9">
+        <v>1244</v>
+      </c>
+      <c r="G199" s="9">
+        <v>1244</v>
+      </c>
+      <c r="H199" s="22" t="s">
+        <v>509</v>
+      </c>
+      <c r="I199" s="17">
+        <v>90000</v>
+      </c>
+      <c r="J199" s="17">
+        <v>700000</v>
+      </c>
+      <c r="K199" s="2">
+        <v>0</v>
+      </c>
+      <c r="L199" s="2">
+        <v>0</v>
+      </c>
+      <c r="M199" s="2">
+        <v>0</v>
+      </c>
+      <c r="N199" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="O199" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -11415,7 +13060,7 @@
         <v>2000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>440</v>
+        <v>510</v>
       </c>
       <c r="E6" s="2">
         <v>98</v>
@@ -11459,7 +13104,7 @@
         <v>2001</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>441</v>
+        <v>511</v>
       </c>
       <c r="E7" s="2">
         <v>98</v>
@@ -11471,7 +13116,7 @@
         <v>1071</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>442</v>
+        <v>512</v>
       </c>
       <c r="I7" s="2">
         <v>120000</v>
@@ -11503,7 +13148,7 @@
         <v>2002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>443</v>
+        <v>513</v>
       </c>
       <c r="E8" s="2">
         <v>98</v>
@@ -11515,7 +13160,7 @@
         <v>1072</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>444</v>
+        <v>514</v>
       </c>
       <c r="I8" s="2">
         <v>120000</v>
@@ -11547,7 +13192,7 @@
         <v>2003</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>445</v>
+        <v>515</v>
       </c>
       <c r="E9" s="2">
         <v>98</v>
@@ -11559,7 +13204,7 @@
         <v>1073</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>446</v>
+        <v>516</v>
       </c>
       <c r="I9" s="2">
         <v>120000</v>
@@ -11591,7 +13236,7 @@
         <v>2004</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>447</v>
+        <v>517</v>
       </c>
       <c r="E10" s="2">
         <v>98</v>
@@ -11603,7 +13248,7 @@
         <v>1074</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>448</v>
+        <v>518</v>
       </c>
       <c r="I10" s="2">
         <v>120000</v>
@@ -11635,7 +13280,7 @@
         <v>2005</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>447</v>
+        <v>517</v>
       </c>
       <c r="E11" s="2">
         <v>98</v>
@@ -11647,7 +13292,7 @@
         <v>1104</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>448</v>
+        <v>518</v>
       </c>
       <c r="I11" s="2">
         <v>20000</v>
@@ -11693,7 +13338,7 @@
         <v>2006</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>449</v>
+        <v>519</v>
       </c>
       <c r="E14" s="2">
         <v>98</v>
@@ -11705,7 +13350,7 @@
         <v>1105</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="I14" s="2">
         <v>360000</v>
@@ -11737,7 +13382,7 @@
         <v>2007</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>451</v>
+        <v>521</v>
       </c>
       <c r="E15" s="2">
         <v>98</v>
@@ -11749,7 +13394,7 @@
         <v>1106</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>452</v>
+        <v>522</v>
       </c>
       <c r="I15" s="2">
         <v>360000</v>
@@ -11781,7 +13426,7 @@
         <v>2008</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>453</v>
+        <v>523</v>
       </c>
       <c r="E16" s="2">
         <v>98</v>
@@ -11793,7 +13438,7 @@
         <v>1107</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>454</v>
+        <v>524</v>
       </c>
       <c r="I16" s="2">
         <v>360000</v>
@@ -11825,7 +13470,7 @@
         <v>2009</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>455</v>
+        <v>525</v>
       </c>
       <c r="E17" s="2">
         <v>98</v>
@@ -11837,7 +13482,7 @@
         <v>1108</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>456</v>
+        <v>526</v>
       </c>
       <c r="I17" s="2">
         <v>360000</v>
@@ -11869,7 +13514,7 @@
         <v>2010</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>457</v>
+        <v>527</v>
       </c>
       <c r="E18" s="2">
         <v>98</v>
@@ -11881,7 +13526,7 @@
         <v>1139</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>458</v>
+        <v>528</v>
       </c>
       <c r="I18" s="2">
         <v>360000</v>
@@ -11913,7 +13558,7 @@
         <v>2011</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>447</v>
+        <v>517</v>
       </c>
       <c r="E19" s="2">
         <v>98</v>
@@ -11925,7 +13570,7 @@
         <v>1139</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>448</v>
+        <v>518</v>
       </c>
       <c r="I19" s="2">
         <v>40000</v>
@@ -11964,7 +13609,7 @@
         <v>2012</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>459</v>
+        <v>529</v>
       </c>
       <c r="E21" s="2">
         <v>98</v>
@@ -11976,7 +13621,7 @@
         <v>1140</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>460</v>
+        <v>530</v>
       </c>
       <c r="I21" s="2">
         <v>360000</v>
@@ -12008,7 +13653,7 @@
         <v>2013</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>461</v>
+        <v>531</v>
       </c>
       <c r="E22" s="2">
         <v>98</v>
@@ -12020,7 +13665,7 @@
         <v>1141</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>462</v>
+        <v>532</v>
       </c>
       <c r="I22" s="2">
         <v>360000</v>
@@ -12052,7 +13697,7 @@
         <v>2014</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>463</v>
+        <v>533</v>
       </c>
       <c r="E23" s="2">
         <v>98</v>
@@ -12064,7 +13709,7 @@
         <v>1142</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>464</v>
+        <v>534</v>
       </c>
       <c r="I23" s="2">
         <v>360000</v>
@@ -12096,7 +13741,7 @@
         <v>2015</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>465</v>
+        <v>535</v>
       </c>
       <c r="E24" s="2">
         <v>98</v>
@@ -12108,7 +13753,7 @@
         <v>1143</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>466</v>
+        <v>536</v>
       </c>
       <c r="I24" s="2">
         <v>360000</v>
@@ -12140,7 +13785,7 @@
         <v>2016</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>467</v>
+        <v>537</v>
       </c>
       <c r="E25" s="2">
         <v>98</v>
@@ -12152,7 +13797,7 @@
         <v>1209</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>468</v>
+        <v>538</v>
       </c>
       <c r="I25" s="2">
         <v>360000</v>
@@ -12184,7 +13829,7 @@
         <v>2017</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>457</v>
+        <v>527</v>
       </c>
       <c r="E26" s="2">
         <v>98</v>
@@ -12196,7 +13841,7 @@
         <v>1209</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>458</v>
+        <v>528</v>
       </c>
       <c r="I26" s="2">
         <v>180000</v>
@@ -12225,16 +13870,16 @@
     </row>
     <row r="27" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>469</v>
+        <v>539</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>469</v>
+        <v>539</v>
       </c>
       <c r="C27" s="2">
         <v>2018</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>447</v>
+        <v>517</v>
       </c>
       <c r="E27" s="2">
         <v>98</v>
@@ -12246,7 +13891,7 @@
         <v>1174</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>448</v>
+        <v>518</v>
       </c>
       <c r="I27" s="2">
         <v>40000</v>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="539">
   <si>
     <t>_id</t>
   </si>
@@ -1874,9 +1874,6 @@
   </si>
   <si>
     <t>209994</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
 </sst>
 </file>
@@ -12885,7 +12882,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P46"/>
+  <dimension ref="C1:P45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -13465,7 +13462,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+    <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
       <c r="C17" s="2">
         <v>2009</v>
       </c>
@@ -13509,7 +13506,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+    <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
       <c r="C18" s="2">
         <v>2010</v>
       </c>
@@ -13553,7 +13550,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+    <row r="19" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
       <c r="C19" s="2">
         <v>2011</v>
       </c>
@@ -13597,14 +13594,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+    <row r="20" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="10"/>
       <c r="O20" s="11"/>
       <c r="P20" s="11"/>
     </row>
-    <row r="21" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+    <row r="21" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
       <c r="C21" s="2">
         <v>2012</v>
       </c>
@@ -13648,7 +13645,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+    <row r="22" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
       <c r="C22" s="2">
         <v>2013</v>
       </c>
@@ -13692,7 +13689,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+    <row r="23" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
       <c r="C23" s="2">
         <v>2014</v>
       </c>
@@ -13736,7 +13733,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+    <row r="24" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
       <c r="C24" s="2">
         <v>2015</v>
       </c>
@@ -13780,7 +13777,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+    <row r="25" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
       <c r="C25" s="2">
         <v>2016</v>
       </c>
@@ -13824,7 +13821,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+    <row r="26" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
       <c r="C26" s="2">
         <v>2017</v>
       </c>
@@ -13868,85 +13865,42 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
-      <c r="A27" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="C27" s="2">
-        <v>2018</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="E27" s="2">
-        <v>98</v>
-      </c>
-      <c r="F27" s="2">
-        <v>1140</v>
-      </c>
-      <c r="G27" s="2">
-        <v>1174</v>
-      </c>
-      <c r="H27" s="22" t="s">
-        <v>518</v>
-      </c>
-      <c r="I27" s="2">
-        <v>40000</v>
-      </c>
-      <c r="J27" s="2">
-        <v>540000</v>
-      </c>
-      <c r="K27" s="2">
-        <v>0</v>
-      </c>
-      <c r="L27" s="2">
-        <v>30000</v>
-      </c>
-      <c r="M27" s="2">
-        <v>0</v>
-      </c>
-      <c r="N27" s="2">
-        <v>0</v>
-      </c>
-      <c r="O27" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="P27" s="20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+    <row r="27" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="10"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+    </row>
+    <row r="28" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
       <c r="H28" s="10"/>
       <c r="O28" s="11"/>
       <c r="P28" s="11"/>
     </row>
-    <row r="29" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+    <row r="29" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
       <c r="H29" s="10"/>
       <c r="O29" s="11"/>
       <c r="P29" s="11"/>
     </row>
-    <row r="30" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+    <row r="30" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
       <c r="H30" s="10"/>
       <c r="O30" s="11"/>
       <c r="P30" s="11"/>
     </row>
-    <row r="31" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+    <row r="31" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
       <c r="H31" s="10"/>
       <c r="O31" s="11"/>
       <c r="P31" s="11"/>
     </row>
-    <row r="32" s="2" customFormat="1" ht="18" customHeight="1" spans="1:16">
+    <row r="32" s="2" customFormat="1" ht="18" customHeight="1" spans="3:16">
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="10"/>
@@ -14043,13 +13997,6 @@
       <c r="H45" s="10"/>
       <c r="O45" s="11"/>
       <c r="P45" s="11"/>
-    </row>
-    <row r="46" s="2" customFormat="1" ht="18" customHeight="1" spans="6:16">
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="10"/>
-      <c r="O46" s="11"/>
-      <c r="P46" s="11"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G11">
@@ -14070,12 +14017,6 @@
   <conditionalFormatting sqref="G26">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G27">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F14:F18">
     <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
@@ -14089,7 +14030,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 C2:C5 F3:G5 F14:G19 F21:G27" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G11 C2:C5 F3:G5 F14:G19 F21:G26" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>元宵快乐</t>
+    <t>清明节</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2026-03-02</t>
-  </si>
-  <si>
-    <t>2026-03-06</t>
+    <t>2026-04-05</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>清明节</t>
+    <t>51快乐</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2026-04-05</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -13791,7 +13791,7 @@
         <v>1144</v>
       </c>
       <c r="G25" s="2">
-        <v>1209</v>
+        <v>1244</v>
       </c>
       <c r="H25" s="22" t="s">
         <v>538</v>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>51快乐</t>
+    <t>61快乐</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-06</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>61快乐</t>
+    <t>端午快乐</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-06-06</t>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -337,7 +337,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>端午快乐</t>
+    <t>七月金秋</t>
   </si>
   <si>
     <t>1005</t>
@@ -346,10 +346,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>2026-06-24</t>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -346,7 +346,7 @@
     <t>50</t>
   </si>
   <si>
-    <t>2026-07-16</t>
+    <t>2026-07-19</t>
   </si>
   <si>
     <t>2026-07-23</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -337,19 +342,19 @@
     <t>string</t>
   </si>
   <si>
-    <t>七月金秋</t>
+    <t>周年庆</t>
   </si>
   <si>
     <t>1005</t>
   </si>
   <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>2026-07-19</t>
-  </si>
-  <si>
-    <t>2026-07-23</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -354,7 +354,7 @@
     <t>2026-08-01</t>
   </si>
   <si>
-    <t>2026-08-08</t>
+    <t>2026-08-11</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -354,7 +354,7 @@
     <t>2026-08-01</t>
   </si>
   <si>
-    <t>2026-08-11</t>
+    <t>2026-08-09</t>
   </si>
   <si>
     <t>平时部分掉落</t>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -348,7 +348,7 @@
     <t>1005</t>
   </si>
   <si>
-    <t>30</t>
+    <t>50</t>
   </si>
   <si>
     <t>2026-08-01</t>
@@ -2083,12 +2083,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -342,7 +342,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>周年庆</t>
+    <t>九月金秋</t>
   </si>
   <si>
     <t>1005</t>
@@ -351,10 +351,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2026-08-01</t>
-  </si>
-  <si>
-    <t>2026-08-09</t>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
   </si>
   <si>
     <t>平时部分掉落</t>
@@ -2083,12 +2083,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/DropLimitConfig.xlsx
+++ b/Excel/DropLimitConfig.xlsx
@@ -351,10 +351,10 @@
     <t>50</t>
   </si>
   <si>
-    <t>2026-09-01</t>
-  </si>
-  <si>
-    <t>2026-09-09</t>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
   </si>
   <si>
     <t>平时部分掉落</t>
